--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="427">
   <si>
     <t xml:space="preserve">FRISE DES COURANTS DE PENSÉE ORIENTALE — Données source</t>
   </si>
@@ -507,6 +507,7 @@
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">法家</t>
     </r>
@@ -669,6 +670,23 @@
     <t xml:space="preserve">philosophie &amp; courant de pensée indien troisième grande forme du bouddhisme.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kalâm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kal%C3%A2m"  title=" Wikipedia"&gt;Le Kalâm &lt;/a&gt; (en arabe ʿilm al-kalām, « science du discours ») désigne la théologie spéculative et dialectique de l’islam, c’est-à-dire l’effort rationnel pour exposer, défendre et argumenter les dogmes de la foi musulmane. Né aux premiers siècles de l’islam, il s’est développé comme une discipline à part entière, distincte mais en dialogue avec la philosophie (falsafa) et le droit (fiqh). &lt;/p&gt; &lt;p&gt; Le terme kalām signifie littéralement « parole » ou « discours », et fait souvent référence à la « parole de Dieu » (kalām Allāh), c’est-à-dire le Coran. En tant que science religieuse, il a pour objet les fondements de la religion (uṣūl al-dīn) : l’existence et l’unicité de Dieu, ses attributs, la prophétie, la révélation, la justice divine, le libre arbitre, la résurrection et le Jugement dernier. Il cherche à établir ces croyances par des preuves rationnelles et à réfuter les doutes ou les doctrines considérées comme déviantes. &lt;/p&gt; &lt;p&gt; Il est une théologie scolastique qui combine révélation et raison : il part des textes sacrés (Coran, sunna) mais utilise la logique, la dialectique et parfois des concepts empruntés à la philosophie grecque (Aristote, stoïciens, néoplatoniciens). Certains auteurs le définissent comme « la contemplation des fondements de la religion sur la base de la raison seule », d’autres insistent sur son rôle apologétique : défendre la foi contre les hérétiques, les philosophes ou les adeptes d’autres religions. Ibn Khaldūn le décrit comme une discipline de dispute rationnelle au service du dogme. &lt;/p&gt; &lt;p&gt; Bien que proche de la philosophie (falsafa), il s’en distingue par son point de départ : il prend comme principes premiers les dogmes révélés par l’islam, alors que la philosophie part de la raison pure et des démonstrations métaphysiques. Certains philosophes (comme Avicenne) ont influencé les mutakallimūn (théologiens du Kalâm), et inversement, mais les théologiens reprochent souvent aux philosophes de subordonner la révélation à la raison. Le Kalâm occupe ainsi une position intermédiaire entre théologie dogmatique, philosophie et apologétique. &lt;/p&gt; &lt;p&gt; Il 
+ a structuré pendant des siècles l’enseignement théologique dans le monde sunnite comme shiʿite, et reste une référence centrale dans les facultés de sciences religieuses. Au XIXe–XXe siècles, des réformateurs musulmans ont cherché à « moderniser » il en le rapprochant davantage de la philosophie contemporaine et des sciences, tout en conservant sa fonction de défense rationnelle de la foi. Aujourd’hui, il continue d’alimenter des débats sur la place de la raison, la lecture du Coran, la liberté humaine et la nature de Dieu dans la pensée islamique.&lt;/p&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jnuSRt72dqw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduction à la philosophie juive ; le kalâm musulman par ikarim</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> théologie spéculative et dialectique de l’islam, c’est-à-dire l’effort rationnel pour exposer, défendre et argumenter les dogmes de la foi musulmane.</t>
+  </si>
+  <si>
     <t xml:space="preserve">750</t>
   </si>
   <si>
@@ -680,7 +698,7 @@
 &lt;dd&gt;Tawhid : l'unicité de Dieu, affirmant qu'il n'y a qu'un seul Dieu et qu'il est indivisible. &lt;/dd&gt;
 &lt;dd&gt;Adl : la justice de Dieu, soutenant que Dieu est juste et ne peut commettre d'injustice. &lt;/dd&gt;
 &lt;dd&gt; Al-'Aql wa al-Naql : affirmant que la raison et la révélation divine doivent être en harmonie. &lt;/dd&gt;
-&lt;p&gt;A partir du IXe siècle, le courant a perdu de son influence en raison de l'opposition des théologiens conservateurs et de l'arrivée au pouvoir de califes plus traditionalistes et a graduellement décliné en tant que courant théologique distinct, bien qu'il ait laissé une empreinte durable sur le développement de la pensée islamique. &lt;/p&gt; &lt;audio controls title="Le néo mutazilisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-13.10.2019-ITEMA_22174473-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+&lt;p&gt;A partir du IXe siècle, le courant a perdu de son influence en raison de l'opposition des théologiens conservateurs et de l'arrivée au pouvoir de califes plus traditionalistes et a graduellement décliné en tant que courant théologique distinct, bien qu'il ait laissé une empreinte durable sur le développement de la pensée islamique. &lt;/p&gt; &lt;audio controls title="Le néo mutazilisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-13.10.2019-ITEMA_22174473-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">cuXmP26Mv4o</t>
@@ -878,6 +896,40 @@
   </si>
   <si>
     <t xml:space="preserve">syncrétisme vietnamien du confucianisme, du bouddhisme et du taoïsme (Tam Giáo), avec les cultes populaires locaux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamanisme</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chamanisme"   title=" Wikipedia"&gt;Le Chamanisme&lt;/a&gt; est un système de croyances et de pratiques spirituelles anciennes, centré sur la médiation entre le monde humain et le monde des esprits par l’intermédiaire d’un spécialiste rituel, le chaman. Présent dans de nombreuses cultures autochtones, notamment en Sibérie, en Amérique, en Asie centrale et chez certains peuples premiers, il repose sur une vision animiste du monde où chaque être et phénomène possède une dimension spirituelle. &lt;/p&gt; &lt;p&gt; Le terme « chaman » provient du mot toungouse (langue de Sibérie) šaman, signifiant « celui qui est agité » ou « transporté ». Historiquement, le chamanisme désigne moins une religion organisée qu’un ensemble de techniques et de conceptions visant à établir un contact avec des réalités invisibles. Pour l’anthropologie contemporaine, il s’agit d’un système de pensée dans lequel le chaman, grâce à des états de conscience modifiés (trance, extase), voyage dans d’autres mondes afin d’acquérir des pouvoirs ou des connaissances au service de sa communauté. &lt;/p&gt; &lt;p&gt; Le chamanisme s’enracine dans l’animisme : la conviction que les animaux, les plantes, les rivières, les montagnes et même les objets sont habités par des esprits. Le cosmos est souvent conçu comme divisé en plusieurs niveaux (monde d’en haut, monde intermédiaire des humains, monde d’en bas), reliés par un axe central symbolique (arbre, montagne, poteau). Les esprits peuvent être bienveillants ou malfaisants, et le rôle du chaman est de négocier avec eux pour rétablir l’harmonie, guérir, prédire ou accompagner les âmes. &lt;/p&gt; &lt;p&gt; Le chamanisme est considéré par certains chercheurs comme l’une des formes les plus anciennes de conscience religieuse et intellectuelle de l’humanité, antérieure aux grandes religions organisées. Il représente une manière spécifique de penser le monde, fondée sur l’expérience directe du sacré, l’interdépendance entre humains et non-humains, et la conviction que la réalité sensible n’est qu’une partie d’un tout plus vaste. En ce sens, il constitue un courant de pensée à part entière, offrant une grille de lecture alternative à celles de la philosophie classique ou des religions monothéistes. &lt;/p&gt; 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;audio controls title="les religions ; le chamanisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14864-05.06.2002-ITEMA_24411099-2002F4864S0099-NET_MFI_F04EFC00-E305-41BC-A7E1-BCEC874397A5-27-9a2657b35c58dcf0b132a47f2ef04912.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">pBv219s30BU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Chamanisme c’est quoi par Conscience Rationnelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">croyance et de pratique spirituelle ancienne, centré sur la médiation entre le monde humain et le monde des esprits.</t>
   </si>
   <si>
     <t xml:space="preserve">1680</t>
@@ -1373,7 +1425,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1484,6 +1536,7 @@
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1498,6 +1551,24 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -1652,124 +1723,132 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2025,7 +2104,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -2034,7 +2113,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="69.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="7.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="33.67"/>
@@ -2960,83 +3039,83 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9" t="s">
+    <row r="35" customFormat="false" ht="353.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
+        <v>720</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>720</v>
+      </c>
+      <c r="D35" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="E35" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="F35" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="G35" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="J35" s="22" t="s">
         <v>198</v>
-      </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="n">
+    <row r="36" customFormat="false" ht="307.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="n">
         <v>750</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="B36" s="9"/>
+      <c r="C36" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
       <c r="J36" s="2" t="s">
         <v>204</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>800</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>800</v>
-      </c>
-      <c r="D37" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="n">
+        <v>750</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="16" t="s">
         <v>208</v>
       </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="2" t="s">
         <v>209</v>
       </c>
@@ -3044,54 +3123,54 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="n">
+    <row r="38" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="n">
         <v>820</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="2" t="s">
+      <c r="B39" s="9"/>
+      <c r="C39" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>850</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>850</v>
-      </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="11" t="s">
         <v>219</v>
       </c>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
       <c r="J39" s="2" t="s">
         <v>220</v>
       </c>
@@ -3099,54 +3178,54 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="n">
-        <v>890</v>
-      </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14" t="s">
+    <row r="40" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
+        <v>850</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>850</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="E40" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="F40" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="G40" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="J40" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="197.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D41" s="12" t="s">
+    <row r="41" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="n">
+        <v>890</v>
+      </c>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="D41" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="16" t="s">
         <v>230</v>
       </c>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
       <c r="J41" s="2" t="s">
         <v>231</v>
       </c>
@@ -3154,7 +3233,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="180.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="61.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>1000</v>
       </c>
@@ -3180,12 +3259,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="146.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="228.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
-        <v>1150</v>
+        <v>1000</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>1150</v>
+        <v>1000</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>237</v>
@@ -3206,277 +3285,271 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="147.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="n">
+    <row r="44" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="n">
         <v>1150</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="1" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="E44" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="F44" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="G44" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="J44" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D45" s="12" t="s">
+    <row r="45" customFormat="false" ht="219.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="11" t="s">
         <v>251</v>
       </c>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
       <c r="J45" s="2" t="s">
         <v>252</v>
       </c>
       <c r="K45" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
+      <c r="E46" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
         <v>1300</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C47" s="1" t="n">
         <v>1300</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="14" t="n">
-        <v>1680</v>
-      </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14" t="s">
+      <c r="D47" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="E47" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="F47" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="G47" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="G47" s="16" t="s">
+      <c r="J47" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="366.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
-        <v>1750</v>
+        <v>1650</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>1750</v>
+        <v>1650</v>
       </c>
       <c r="D48" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E48" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="F48" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="J48" s="24" t="s">
         <v>268</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9" t="n">
-        <v>1760</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9" t="s">
+    <row r="49" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D49" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="E49" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="F49" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="G49" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="H49" s="9"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="195" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="n">
-        <v>1820</v>
-      </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14" t="n">
-        <v>1820</v>
-      </c>
-      <c r="D50" s="15" t="s">
+    <row r="50" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="E50" s="16" t="s">
+      <c r="F50" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="G50" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="G50" s="16" t="s">
+      <c r="J50" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="2" t="s">
+      <c r="K50" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>1840</v>
-      </c>
-      <c r="C51" s="1" t="s">
+      <c r="D51" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="E51" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="305.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="n">
-        <v>1845</v>
+        <v>1820</v>
       </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14" t="n">
-        <v>1845</v>
+        <v>1820</v>
       </c>
       <c r="D52" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="E52" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="F52" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="G52" s="16" t="s">
         <v>289</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>290</v>
       </c>
       <c r="H52" s="14"/>
       <c r="I52" s="16"/>
       <c r="J52" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K52" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D53" s="22" t="s">
+    <row r="53" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="E53" s="23" t="s">
+      <c r="E53" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="G53" s="16" t="s">
+      <c r="G53" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="16"/>
       <c r="J53" s="2" t="s">
         <v>296</v>
       </c>
@@ -3484,13 +3557,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="n">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="B54" s="14"/>
       <c r="C54" s="14" t="n">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>297</v>
@@ -3510,156 +3583,162 @@
         <v>301</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>1865</v>
-      </c>
-      <c r="C55" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="329.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B55" s="14"/>
+      <c r="C55" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D55" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="G55" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="H55" s="14"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="D56" s="10" t="s">
+    <row r="56" customFormat="false" ht="267.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="E56" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="F56" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="G56" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="G56" s="11" t="s">
+      <c r="H56" s="14"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="H56" s="9"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="2" t="s">
+      <c r="K56" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
+        <v>1865</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="14" t="n">
-        <v>1878</v>
-      </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14" t="n">
-        <v>1878</v>
-      </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E57" s="16" t="s">
+      <c r="E57" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F57" s="14" t="s">
+      <c r="F57" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G57" s="16" t="s">
+      <c r="G57" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="H57" s="14"/>
-      <c r="I57" s="16"/>
       <c r="J57" s="2" t="s">
         <v>317</v>
       </c>
       <c r="K57" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="D58" s="12" t="s">
+      <c r="E58" s="27" t="s">
         <v>319</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="D59" s="12" t="s">
+    <row r="59" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="E59" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="F59" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="G59" s="2" t="s">
+      <c r="H59" s="14"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="J59" s="2" t="s">
+      <c r="K59" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="60" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="E60" s="25" t="s">
+      <c r="E60" s="2" t="s">
         <v>330</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -3668,19 +3747,19 @@
       <c r="G60" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="J60" s="25" t="s">
+      <c r="J60" s="2" t="s">
         <v>333</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
-        <v>1920</v>
+        <v>1905</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>1920</v>
+        <v>1905</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>334</v>
@@ -3701,106 +3780,106 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="J62" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="J62" s="2" t="s">
+      <c r="C63" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D63" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="14" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14" t="s">
+      <c r="E63" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="F63" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="E63" s="16" t="s">
+      <c r="G63" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="J63" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="K63" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="D64" s="12" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E64" s="26" t="s">
+      <c r="F64" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="G64" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="J64" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="J64" s="26" t="s">
+      <c r="K64" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="14" t="n">
+        <v>1935</v>
+      </c>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E65" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="16" t="s">
         <v>359</v>
       </c>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
       <c r="J65" s="2" t="s">
         <v>360</v>
       </c>
@@ -3808,17 +3887,17 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
-        <v>1964</v>
+        <v>1940</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>1964</v>
+        <v>1940</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E66" s="28" t="s">
         <v>362</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -3827,19 +3906,19 @@
       <c r="G66" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="J66" s="28" t="s">
         <v>365</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="159" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
-        <v>1990</v>
+        <v>1945</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>1990</v>
+        <v>1945</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>366</v>
@@ -3857,18 +3936,70 @@
         <v>370</v>
       </c>
       <c r="K67" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="250" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="K69" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="134.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="J68" s="1"/>
-    </row>
-    <row r="69" customFormat="false" ht="185.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="134.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="J70" s="1"/>
+    </row>
+    <row r="71" customFormat="false" ht="185.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -3887,16 +4018,16 @@
     <hyperlink ref="E30" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_mah%C4%81y%C4%81na&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Mahayana&lt;/a&gt; (« Grand Véhicule ») est apparu en Inde au tournant de l'ère chrétienne, s'étendant progressivement vers la Chine, le Japon, la Corée et le Vietnam. Par rapport au Theravada, il représente une transformation profonde de la vision bouddhiste : l'éveil n'est plus un idéal solitaire mais une aspiration collective.&lt;/p&gt;&lt;p&gt;L'idéal central du Mahayana est le bodhisattva : l'être qui, sur le point d'atteindre le Nirvana, choisit de demeurer dans le cycle des renaissances (samsara) pour guider et libérer tous les êtres sensibles. Cette compassion universelle (karuna) devient le moteur de la voie spirituelle, indissociable de la sagesse (prajna).&lt;/p&gt;&lt;p&gt;Le Mahayana introduit également la notion révolutionnaire de sunyata (vacuité) : toutes choses sont dénues d'existence propre et intrinsèque — elles n'existent que de façon interdependante. Nagarjuna, au IIe siècle, en développa la philosophie dans ses Stances du Milieu, fondant l'école Madhyamaka qui influencça toute la pensée bouddhiste ultérieure.&lt;/p&gt;&lt;p&gt;C'est sur le sol du Mahayana que fleuriront le bouddhisme Zen, le bouddhisme tibétain Vajrayana, et l'École de la Terre Pure. Avec ses sutras nouveaux (Lotus, Vimalakirti, Prajnaparamita), le Mahayana offre une vision du monde d'une richesse philosophique et spirituelle sans équivalent.&lt;/p&gt;"/>
     <hyperlink ref="E32" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mazdakisme&quot; title=&quot;Wikipedia&quot;&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse sous l’Empire sassanide. Fondé par le réformateur Mazdak, ce courant tire ses origines à la fois du mazdéisme et du manichéisme, en proposant une relecture dualiste du monde axée sur la lumière et les ténèbres. &lt;/p&gt; &lt;p&gt; Contrairement aux structures sociales hiérarchisées de l’époque, le mazdakisme prônait une égalité radicale entre les individus. Mazdak soutenait que les causes des conflits humains résidaient dans la soif de richesses et de pouvoir, ce qui l'a conduit à prôner la mise en commun des biens matériels et, selon certaines sources, des femmes. &lt;/p&gt; &lt;p&gt; Cette doctrine a été perçue comme une menace par l’aristocratie et le clergé zoroastrien traditionnel, qui y voyaient une hérésie dangereuse pour l'ordre établi. Après avoir initialement bénéficié de l'intérêt de l'empereur Kavadh Ier, le mouvement fut sévèrement réprimé lors de grandes purges organisées entre 524 et 529. &lt;/p&gt; &lt;p&gt; Bien que le mazdakisme ait été marginalisé après ces persécutions, il a laissé une trace durable dans la pensée iranienne. Parfois qualifié, de manière anachronique, de mouvement proto-socialiste, son idéal de justice sociale a influencé certains courants contestataires qui se sont manifestés en Iran jusqu'au XIVe siècle environ. &lt;/p&gt; &#10;"/>
     <hyperlink ref="E34" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_vajrayana&quot;  title=&quot;Wikipedia&quot;&gt;Le Vajrayana&lt;/a&gt; (« Véhicule de Diamant ») est la troisième grande forme du bouddhisme, développée en Inde entre le VIIe et le Xe siècle, puis transmise au Tibet, en Mongolie et dans l'Himalaya. Il représente la voie tantrique du bouddhisme, utilisant des pratiques ésotériques pour accélérer le chemin vers l'éveil.&lt;/p&gt;&lt;p&gt;Là où le Theravada vise l'éveil en de nombreuses vies et le Mahayana en d'innombrables éons, le Vajrayana affirme qu'il est possible d'atteindre l'éveil en une seule vie — voire en un seul instant. Pour cela, il mobilise un arsenal de techniques : mantras, mandalas, mudras, visualisations de divinités, pratiques yogiques subtiles sur les énergies intérieures du corps.&lt;/p&gt;&lt;p&gt;Le Bouddhisme tibétain, la forme la plus répandue du Vajrayana, s'est développé dès le VIIe siècle sous le règne du roi Songtsen Gampo. Il intègre des éléments de la religion Bön préexistante et du Mahayana indien. Ses figures tutlaires — Padmasambhava, Milarepa, Tsongkhapa — sont au cœur d'une tradition d'une richesse philosophique et rituelle incomparable.&lt;/p&gt;&lt;p&gt;La notion de &quot;nature de bouddha&quot; (tathagatagarbha) — l'idée que chaque être possède en lui la graine de l'éveil — est centrale dans le Vajrayana. La pratique vise à reconnaître directement cette nature lumineuse originelle, au-delà des voiles de l'ignorance et de l'égo.&lt;/p&gt;"/>
-    <hyperlink ref="E36" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/V%C3%A9danta&quot;  title=&quot; Wikipedia&quot;&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).https://fr.wikipedia.org/wiki/Védanta&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="E38" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E41" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>
-    <hyperlink ref="E45" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bushido&quot; title=&quot;Wikipedia&quot;&gt;Le Bushido&lt;/a&gt; (« Voie du Guerrier ») est le code éthique de la classe des samouraïs du Japon féodal, progressivement formalisé entre l'époque Kamakura (XIIe siècle) et la période Edo. Il synthétise en une philosophie de vie cohérente des valeurs empruntées au bouddhisme zen, au shintoïsme et au confucianisme.&lt;/p&gt;&lt;p&gt;Les sept vertus cardinales du Bushido sont : la rectitude (gi), le courage (yu), la bienveillance (jin), le respect (rei), la sincérité (makoto), l'honneur (meiyo) et la loyauté (chugi). À celles-ci s'ajoute la maîtrise de soi, la frugalité et l'acceptation stoïque de la mort — le samouraï doit &quot;vivre comme s'il était déjà mort&quot; pour agir sans attachement ni peur.&lt;/p&gt;&lt;p&gt;La pratique de seppuku (suicide rituel) illustre à l'extrême cette philosophie : la mort honorable vaut mieux qu'une vie dans la honte. Cette acceptation de la mort comme acte ultime de liberté et de dignité a fasciné les philosophes — de Nitobe Inazo, qui codafia le Bushido en 1900, à ceux qui y voient une forme de stoïcisme oriental.&lt;/p&gt;&lt;p&gt;Après la fin de l'ère des samouraïs au XIXe siècle, le Bushido survit dans les arts martiaux japonais (kendo, judo, aïkido), dans la culture d'entreprise japonaise et dans une vision de l'excellence par la maîtrise de soi qui continue d'inspirer bien au-delà du Japon.&lt;/p&gt;"/>
-    <hyperlink ref="E52" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E56" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E57" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E58" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
-    <hyperlink ref="E63" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E64" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E37" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/V%C3%A9danta&quot;  title=&quot; Wikipedia&quot;&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).https://fr.wikipedia.org/wiki/Védanta&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="E39" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E42" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>
+    <hyperlink ref="E46" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bushido&quot; title=&quot;Wikipedia&quot;&gt;Le Bushido&lt;/a&gt; (« Voie du Guerrier ») est le code éthique de la classe des samouraïs du Japon féodal, progressivement formalisé entre l'époque Kamakura (XIIe siècle) et la période Edo. Il synthétise en une philosophie de vie cohérente des valeurs empruntées au bouddhisme zen, au shintoïsme et au confucianisme.&lt;/p&gt;&lt;p&gt;Les sept vertus cardinales du Bushido sont : la rectitude (gi), le courage (yu), la bienveillance (jin), le respect (rei), la sincérité (makoto), l'honneur (meiyo) et la loyauté (chugi). À celles-ci s'ajoute la maîtrise de soi, la frugalité et l'acceptation stoïque de la mort — le samouraï doit &quot;vivre comme s'il était déjà mort&quot; pour agir sans attachement ni peur.&lt;/p&gt;&lt;p&gt;La pratique de seppuku (suicide rituel) illustre à l'extrême cette philosophie : la mort honorable vaut mieux qu'une vie dans la honte. Cette acceptation de la mort comme acte ultime de liberté et de dignité a fasciné les philosophes — de Nitobe Inazo, qui codafia le Bushido en 1900, à ceux qui y voient une forme de stoïcisme oriental.&lt;/p&gt;&lt;p&gt;Après la fin de l'ère des samouraïs au XIXe siècle, le Bushido survit dans les arts martiaux japonais (kendo, judo, aïkido), dans la culture d'entreprise japonaise et dans une vision de l'excellence par la maîtrise de soi qui continue d'inspirer bien au-delà du Japon.&lt;/p&gt;"/>
+    <hyperlink ref="E54" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E58" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E59" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E60" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
+    <hyperlink ref="E65" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E66" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3917,193 +4048,193 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="27" t="s">
-        <v>371</v>
+      <c r="B3" s="29" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="s">
-        <v>372</v>
+      <c r="B5" s="29" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>374</v>
+      <c r="B6" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>376</v>
+      <c r="B7" s="30" t="s">
+        <v>385</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>377</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>378</v>
+      <c r="B8" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>380</v>
+      <c r="B9" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>382</v>
+      <c r="B10" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>383</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>384</v>
+      <c r="B11" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>386</v>
+      <c r="B12" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>388</v>
+      <c r="B13" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>389</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>390</v>
+      <c r="B14" s="30" t="s">
+        <v>399</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="27" t="s">
-        <v>391</v>
+      <c r="B16" s="29" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="28" t="s">
-        <v>392</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>393</v>
+      <c r="B17" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>395</v>
+      <c r="B18" s="30" t="s">
+        <v>404</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>397</v>
+      <c r="B19" s="30" t="s">
+        <v>406</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27" t="s">
-        <v>398</v>
+      <c r="B21" s="29" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="28" t="s">
-        <v>399</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>400</v>
+      <c r="B22" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>402</v>
+      <c r="B23" s="30" t="s">
+        <v>411</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="27" t="s">
-        <v>403</v>
+      <c r="B25" s="29" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="28" t="s">
-        <v>404</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>405</v>
+      <c r="B26" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="28" t="s">
-        <v>406</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>407</v>
+      <c r="B27" s="30" t="s">
+        <v>416</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="28" t="s">
-        <v>408</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>409</v>
+      <c r="B28" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="28" t="s">
-        <v>410</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>411</v>
+      <c r="B29" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="27" t="s">
-        <v>412</v>
+      <c r="B31" s="29" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="28" t="s">
-        <v>413</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>414</v>
+      <c r="B32" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="28" t="s">
-        <v>415</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>416</v>
+      <c r="B33" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="432">
   <si>
     <t xml:space="preserve">FRISE DES COURANTS DE PENSÉE ORIENTALE — Données source</t>
   </si>
@@ -907,6 +907,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chamanisme"   title=" Wikipedia"&gt;Le Chamanisme&lt;/a&gt; est un système de croyances et de pratiques spirituelles anciennes, centré sur la médiation entre le monde humain et le monde des esprits par l’intermédiaire d’un spécialiste rituel, le chaman. Présent dans de nombreuses cultures autochtones, notamment en Sibérie, en Amérique, en Asie centrale et chez certains peuples premiers, il repose sur une vision animiste du monde où chaque être et phénomène possède une dimension spirituelle. &lt;/p&gt; &lt;p&gt; Le terme « chaman » provient du mot toungouse (langue de Sibérie) šaman, signifiant « celui qui est agité » ou « transporté ». Historiquement, le chamanisme désigne moins une religion organisée qu’un ensemble de techniques et de conceptions visant à établir un contact avec des réalités invisibles. Pour l’anthropologie contemporaine, il s’agit d’un système de pensée dans lequel le chaman, grâce à des états de conscience modifiés (trance, extase), voyage dans d’autres mondes afin d’acquérir des pouvoirs ou des connaissances au service de sa communauté. &lt;/p&gt; &lt;p&gt; Le chamanisme s’enracine dans l’animisme : la conviction que les animaux, les plantes, les rivières, les montagnes et même les objets sont habités par des esprits. Le cosmos est souvent conçu comme divisé en plusieurs niveaux (monde d’en haut, monde intermédiaire des humains, monde d’en bas), reliés par un axe central symbolique (arbre, montagne, poteau). Les esprits peuvent être bienveillants ou malfaisants, et le rôle du chaman est de négocier avec eux pour rétablir l’harmonie, guérir, prédire ou accompagner les âmes. &lt;/p&gt; &lt;p&gt; Le chamanisme est considéré par certains chercheurs comme l’une des formes les plus anciennes de conscience religieuse et intellectuelle de l’humanité, antérieure aux grandes religions organisées. Il représente une manière spécifique de penser le monde, fondée sur l’expérience directe du sacré, l’interdépendance entre humains et non-humains, et la conviction que la réalité sensible n’est qu’une partie d’un tout plus vaste. En ce sens, il constitue un courant de pensée à part entière, offrant une grille de lecture alternative à celles de la philosophie classique ou des religions monothéistes. &lt;/p&gt; 
 </t>
@@ -917,6 +918,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> &lt;audio controls title="les religions ; le chamanisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14864-05.06.2002-ITEMA_24411099-2002F4864S0099-NET_MFI_F04EFC00-E305-41BC-A7E1-BCEC874397A5-27-9a2657b35c58dcf0b132a47f2ef04912.m4a" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
@@ -940,7 +942,7 @@
   <si>
     <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kokugaku"   title=" Wikipedia"&gt;Le Kokugaku&lt;/a&gt; est un mouvement intellectuel japonais qui a émergé à la fin du 17e siècle et a prospéré au 18e siècle. "Kokugaku" se traduit littéralement par "étude du pays" ou "étude de la nation" en français. &lt;/p&gt; &lt;p&gt;
 Le kokugaku visait à redécouvrir, étudier et promouvoir la culture et la littérature japonaises traditionnelles, en particulier les textes anciens tels que le Kojiki (Chronique des faits anciens) et le Nihon Shoki (Chroniques du Japon).  Il était une réaction à l'influence croissante du confucianisme et du bouddhisme dans la société japonaise de l'époque, ainsi qu'à l'introduction de nombreuses idées étrangères via le contact avec l'Occident. Les érudits kokugaku cherchaient à renouer avec les anciennes traditions japonaises, notamment la mythologie, la littérature, la poésie, les rites religieux et la linguistique. &lt;/p&gt; &lt;p&gt;
-Les chercheurs kokugaku ont étudié les caractères et les termes anciens, ainsi que les mythes et les légendes japonaises, dans le but de comprendre la culture et la spiritualité autochtones. Les érudits ont exploré des œuvres telles que le Kojiki (Chronique des faits anciens) et le Nihon Shoki (Chroniques du Japon), considérés comme des sources précieuses de la culture et de l'histoire japonaises. Ils ont cherché à redécouvrir les racines authentiques de la nation japonaise.Ils ont cherché à préserver et à promouvoir l'identité japonaise distincte, en s'appuyant sur des éléments tels que la langue, la littérature, l'histoire et les coutumes traditionnelles. &lt;/p&gt; &lt;p&gt;  Le kokugaku a également eu un aspect linguistique par l'étude de la langue japonaise ancienne et en rejetant l'utilisation excessive de termes chinois dans la langue écrite tout en cherchant à promouvoir un style d'écriture plus proche de la langue parlée japonaise. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;</t>
+Les chercheurs kokugaku ont étudié les caractères et les termes anciens, ainsi que les mythes et les légendes japonaises, dans le but de comprendre la culture et la spiritualité autochtones. Les érudits ont exploré des œuvres telles que le Kojiki (Chronique des faits anciens) et le Nihon Shoki (Chroniques du Japon), considérés comme des sources précieuses de la culture et de l'histoire japonaises. Ils ont cherché à redécouvrir les racines authentiques de la nation japonaise.Ils ont cherché à préserver et à promouvoir l'identité japonaise distincte, en s'appuyant sur des éléments tels que la langue, la littérature, l'histoire et les coutumes traditionnelles. &lt;/p&gt; &lt;p&gt;  Le kokugaku a également eu un aspect linguistique par l'étude de la langue japonaise ancienne et en rejetant l'utilisation excessive de termes chinois dans la langue écrite tout en cherchant à promouvoir un style d'écriture plus proche de la langue parlée japonaise. &lt;/p&gt; </t>
   </si>
   <si>
     <t xml:space="preserve">3_doT59c2XA</t>
@@ -949,7 +951,40 @@
     <t xml:space="preserve">"Kokugakuin archives, what is Kokugaku" par Online Museum</t>
   </si>
   <si>
-    <t xml:space="preserve">philosophie japonnaise prônant à promouvoir la culture traditionnelle du Japon.</t>
+    <t xml:space="preserve">philosophie japonaise prônant à promouvoir la culture traditionnelle du Japon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fondamentalisme</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1E1208"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fondamentalisme"   title=" Wikipedia"&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient , principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">&lt;audio controls title="les religions ; le fondamentalisme chrétien par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CO5eTw6ADrE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fondamentalisme par le savoir partagé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie,</t>
   </si>
   <si>
     <t xml:space="preserve">Silhak</t>
@@ -1555,12 +1590,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF1E1208"/>
       <name val="Arial"/>
       <family val="0"/>
     </font>
@@ -1571,16 +1607,15 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FF1E1208"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1812,19 +1847,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1834,10 +1873,6 @@
     </xf>
     <xf numFmtId="164" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2104,7 +2139,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -3058,7 +3093,7 @@
       <c r="G35" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="J35" s="22" t="s">
+      <c r="J35" s="21" t="s">
         <v>198</v>
       </c>
       <c r="K35" s="1" t="s">
@@ -3322,7 +3357,7 @@
       <c r="D45" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="E45" s="22" t="s">
         <v>249</v>
       </c>
       <c r="F45" s="9" t="s">
@@ -3402,7 +3437,7 @@
       <c r="D48" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="E48" s="24" t="s">
+      <c r="E48" s="23" t="s">
         <v>265</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -3411,14 +3446,14 @@
       <c r="G48" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="J48" s="24" t="s">
+      <c r="J48" s="23" t="s">
         <v>268</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="n">
         <v>1680</v>
       </c>
@@ -3447,157 +3482,157 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="186" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>1750</v>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>1750</v>
-      </c>
-      <c r="D50" s="12" t="s">
+    <row r="50" customFormat="false" ht="395.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D50" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="25" t="s">
         <v>279</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="n">
-        <v>1760</v>
-      </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9" t="s">
+    <row r="51" customFormat="false" ht="241" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="E51" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="F51" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="G51" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="J51" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="K51" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="305.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="14" t="n">
-        <v>1820</v>
-      </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14" t="n">
-        <v>1820</v>
-      </c>
-      <c r="D52" s="15" t="s">
+    <row r="52" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E52" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="G52" s="16" t="s">
+      <c r="G52" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="16"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
       <c r="J52" s="2" t="s">
         <v>290</v>
       </c>
       <c r="K52" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="305.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="14" t="n">
+        <v>1820</v>
+      </c>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14" t="n">
+        <v>1820</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="H53" s="14"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="K53" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
+    <row r="54" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="n">
         <v>1840</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="J53" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="14" t="n">
-        <v>1845</v>
-      </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14" t="n">
-        <v>1845</v>
-      </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="E54" s="16" t="s">
+      <c r="E54" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="G54" s="16" t="s">
+      <c r="G54" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H54" s="14"/>
-      <c r="I54" s="16"/>
       <c r="J54" s="2" t="s">
         <v>301</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="329.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="n">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D55" s="25" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D55" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="E55" s="26" t="s">
+      <c r="E55" s="16" t="s">
         <v>303</v>
       </c>
       <c r="F55" s="14" t="s">
@@ -3612,10 +3647,10 @@
         <v>306</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="267.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="329.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="n">
         <v>1850</v>
       </c>
@@ -3623,10 +3658,10 @@
       <c r="C56" s="14" t="n">
         <v>1850</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="E56" s="16" t="s">
+      <c r="E56" s="27" t="s">
         <v>308</v>
       </c>
       <c r="F56" s="14" t="s">
@@ -3641,125 +3676,128 @@
         <v>311</v>
       </c>
       <c r="K56" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="267.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="H57" s="14"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+    <row r="58" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="n">
         <v>1865</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="J57" s="2" t="s">
+      <c r="C58" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E58" s="27" t="s">
+      <c r="E58" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G58" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9"/>
       <c r="J58" s="2" t="s">
         <v>322</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="14" t="n">
-        <v>1878</v>
-      </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14" t="n">
-        <v>1878</v>
-      </c>
-      <c r="D59" s="15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D59" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="G59" s="16" t="s">
+      <c r="G59" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="H59" s="14"/>
-      <c r="I59" s="16"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
       <c r="J59" s="2" t="s">
         <v>327</v>
       </c>
       <c r="K59" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D60" s="15" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
+      <c r="E60" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="H60" s="14"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="n">
         <v>1900</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C61" s="1" t="n">
         <v>1900</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>1905</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>334</v>
@@ -3780,7 +3818,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
         <v>1905</v>
       </c>
@@ -3790,7 +3828,7 @@
       <c r="D62" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="E62" s="21" t="s">
+      <c r="E62" s="2" t="s">
         <v>340</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -3799,24 +3837,24 @@
       <c r="G62" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="J62" s="21" t="s">
+      <c r="J62" s="2" t="s">
         <v>343</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="131.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
-        <v>1920</v>
+        <v>1905</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>1920</v>
+        <v>1905</v>
       </c>
       <c r="D63" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" s="21" t="s">
         <v>345</v>
       </c>
       <c r="F63" s="1" t="s">
@@ -3825,105 +3863,105 @@
       <c r="G63" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="J63" s="2" t="s">
+      <c r="J63" s="21" t="s">
         <v>348</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="F64" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="G64" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="J64" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="J64" s="2" t="s">
+      <c r="K64" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="D65" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="K65" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14" t="n">
+    <row r="66" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="14" t="n">
         <v>1935</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>358</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>359</v>
-      </c>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="2" t="s">
+      <c r="B66" s="14"/>
+      <c r="C66" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="15" t="s">
         <v>361</v>
       </c>
-      <c r="E66" s="28" t="s">
+      <c r="E66" s="16" t="s">
         <v>362</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G66" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="J66" s="28" t="s">
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="2" t="s">
         <v>365</v>
       </c>
       <c r="K66" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="D67" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="E67" s="23" t="s">
         <v>367</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -3932,19 +3970,19 @@
       <c r="G67" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="J67" s="23" t="s">
         <v>370</v>
       </c>
       <c r="K67" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
-        <v>1964</v>
+        <v>1945</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>1964</v>
+        <v>1945</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>371</v>
@@ -3965,12 +4003,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="250" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
-        <v>1990</v>
+        <v>1964</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>1990</v>
+        <v>1964</v>
       </c>
       <c r="D69" s="12" t="s">
         <v>376</v>
@@ -3988,18 +4026,44 @@
         <v>380</v>
       </c>
       <c r="K69" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="250" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="134.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="J70" s="1"/>
-    </row>
-    <row r="71" customFormat="false" ht="185.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="134.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="J71" s="1"/>
+    </row>
+    <row r="72" customFormat="false" ht="185.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -4022,12 +4086,13 @@
     <hyperlink ref="E39" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
     <hyperlink ref="E42" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>
     <hyperlink ref="E46" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bushido&quot; title=&quot;Wikipedia&quot;&gt;Le Bushido&lt;/a&gt; (« Voie du Guerrier ») est le code éthique de la classe des samouraïs du Japon féodal, progressivement formalisé entre l'époque Kamakura (XIIe siècle) et la période Edo. Il synthétise en une philosophie de vie cohérente des valeurs empruntées au bouddhisme zen, au shintoïsme et au confucianisme.&lt;/p&gt;&lt;p&gt;Les sept vertus cardinales du Bushido sont : la rectitude (gi), le courage (yu), la bienveillance (jin), le respect (rei), la sincérité (makoto), l'honneur (meiyo) et la loyauté (chugi). À celles-ci s'ajoute la maîtrise de soi, la frugalité et l'acceptation stoïque de la mort — le samouraï doit &quot;vivre comme s'il était déjà mort&quot; pour agir sans attachement ni peur.&lt;/p&gt;&lt;p&gt;La pratique de seppuku (suicide rituel) illustre à l'extrême cette philosophie : la mort honorable vaut mieux qu'une vie dans la honte. Cette acceptation de la mort comme acte ultime de liberté et de dignité a fasciné les philosophes — de Nitobe Inazo, qui codafia le Bushido en 1900, à ceux qui y voient une forme de stoïcisme oriental.&lt;/p&gt;&lt;p&gt;Après la fin de l'ère des samouraïs au XIXe siècle, le Bushido survit dans les arts martiaux japonais (kendo, judo, aïkido), dans la culture d'entreprise japonaise et dans une vision de l'excellence par la maîtrise de soi qui continue d'inspirer bien au-delà du Japon.&lt;/p&gt;"/>
-    <hyperlink ref="E54" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E58" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E59" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E60" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
-    <hyperlink ref="E65" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E66" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E50" r:id="rId17" display="https://fr.wikipedia.org/wiki/Fondamentalisme"/>
+    <hyperlink ref="E55" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E59" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E60" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E61" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
+    <hyperlink ref="E66" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E67" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4049,192 +4114,192 @@
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="29" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="29" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="30" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="30" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="30" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="30" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="30" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="30" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="30" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="30" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="30" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="29" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="30" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="30" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="30" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="29" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="30" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="30" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="29" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="30" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="30" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="30" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="30" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="29" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="30" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="30" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2204,6 +2204,16 @@
       <c r="L3" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="n">
@@ -2233,6 +2243,11 @@
       <c r="K4" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -2259,6 +2274,11 @@
       <c r="K5" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -2284,6 +2304,11 @@
       </c>
       <c r="K6" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2314,6 +2339,16 @@
       <c r="K7" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien;islam-juif;russe</t>
+        </is>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -2340,6 +2375,16 @@
       <c r="K8" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -2365,6 +2410,11 @@
       </c>
       <c r="K9" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2395,13 +2445,23 @@
       <c r="K10" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>-600</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>55</v>
+      <c r="A11" s="1">
+        <v>1340</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1340</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>56</v>
@@ -2420,6 +2480,16 @@
       </c>
       <c r="K11" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
       </c>
     </row>
     <row r="12" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2450,6 +2520,11 @@
       <c r="K12" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
@@ -2476,6 +2551,11 @@
       <c r="K13" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -2501,6 +2581,11 @@
       </c>
       <c r="K14" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
       </c>
     </row>
     <row r="15" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2531,6 +2616,11 @@
       <c r="K15" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="n">
@@ -2560,6 +2650,11 @@
       <c r="K16" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2586,6 +2681,11 @@
       <c r="K17" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -2611,6 +2711,11 @@
       </c>
       <c r="K18" s="1" t="s">
         <v>102</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
       </c>
     </row>
     <row r="19" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2641,6 +2746,11 @@
       <c r="K19" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="n">
@@ -2670,6 +2780,16 @@
       <c r="K20" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="n">
@@ -2699,6 +2819,11 @@
       <c r="K21" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="n">
@@ -2728,6 +2853,11 @@
       <c r="K22" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="n">
@@ -2757,6 +2887,11 @@
       <c r="K23" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
@@ -2782,6 +2917,11 @@
       </c>
       <c r="K24" s="1" t="s">
         <v>137</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
       </c>
     </row>
     <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2812,6 +2952,11 @@
       <c r="K25" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
@@ -2838,6 +2983,11 @@
       <c r="K26" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -2863,6 +3013,11 @@
       </c>
       <c r="K27" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
       </c>
     </row>
     <row r="28" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2893,6 +3048,11 @@
       <c r="K28" s="1" t="s">
         <v>137</v>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="n">
@@ -2922,6 +3082,11 @@
       <c r="K29" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
@@ -2947,6 +3112,16 @@
       </c>
       <c r="K30" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
       </c>
     </row>
     <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2977,6 +3152,11 @@
       <c r="K31" s="1" t="s">
         <v>178</v>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="n">
@@ -3006,6 +3186,11 @@
       <c r="K32" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
@@ -3032,6 +3217,11 @@
       <c r="K33" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
@@ -3058,6 +3248,16 @@
       <c r="K34" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="353.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
@@ -3083,6 +3283,11 @@
       </c>
       <c r="K35" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
       </c>
     </row>
     <row r="36" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3113,6 +3318,11 @@
       <c r="K36" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="n">
@@ -3142,6 +3352,11 @@
       <c r="K37" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
@@ -3167,6 +3382,11 @@
       </c>
       <c r="K38" s="1" t="s">
         <v>71</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
       </c>
     </row>
     <row r="39" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3197,6 +3417,16 @@
       <c r="K39" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident;inde</t>
+        </is>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
@@ -3222,6 +3452,11 @@
       </c>
       <c r="K40" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
       </c>
     </row>
     <row r="41" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3252,6 +3487,11 @@
       <c r="K41" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
@@ -3281,6 +3521,11 @@
       <c r="L42" s="2" t="s">
         <v>239</v>
       </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
       <c r="XFC42" s="0"/>
       <c r="XFD42" s="0"/>
     </row>
@@ -3309,6 +3554,11 @@
       <c r="K43" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
@@ -3335,6 +3585,11 @@
       <c r="K44" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
@@ -3360,6 +3615,16 @@
       </c>
       <c r="K45" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
       </c>
     </row>
     <row r="46" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3390,6 +3655,11 @@
       <c r="K46" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
@@ -3416,6 +3686,11 @@
       <c r="K47" s="1" t="s">
         <v>266</v>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
@@ -3442,6 +3717,11 @@
       <c r="K48" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="366" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
@@ -3467,6 +3747,11 @@
       </c>
       <c r="K49" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
       </c>
     </row>
     <row r="50" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3497,6 +3782,11 @@
       <c r="K50" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="n">
@@ -3526,6 +3816,11 @@
       <c r="K51" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
@@ -3551,6 +3846,11 @@
       </c>
       <c r="K52" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
       </c>
     </row>
     <row r="53" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3581,6 +3881,11 @@
       <c r="K53" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="n">
@@ -3610,6 +3915,11 @@
       <c r="K54" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
@@ -3639,6 +3949,11 @@
       <c r="L55" s="2" t="s">
         <v>311</v>
       </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
@@ -3664,6 +3979,11 @@
       </c>
       <c r="K56" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
       </c>
     </row>
     <row r="57" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3694,6 +4014,16 @@
       <c r="K57" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="n">
@@ -3723,6 +4053,11 @@
       <c r="K58" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="n">
@@ -3752,6 +4087,11 @@
       <c r="K59" s="1" t="s">
         <v>178</v>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
@@ -3777,6 +4117,11 @@
       </c>
       <c r="K60" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
       </c>
     </row>
     <row r="61" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3807,6 +4152,11 @@
       <c r="K61" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="n">
@@ -3836,6 +4186,11 @@
       <c r="K62" s="1" t="s">
         <v>349</v>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
@@ -3862,6 +4217,16 @@
       <c r="K63" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
@@ -3888,6 +4253,11 @@
       <c r="K64" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="n">
@@ -3914,6 +4284,11 @@
       <c r="K65" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
@@ -3940,6 +4315,11 @@
       <c r="K66" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
@@ -3965,6 +4345,11 @@
       </c>
       <c r="K67" s="1" t="s">
         <v>137</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
       </c>
     </row>
     <row r="68" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3995,6 +4380,11 @@
       <c r="K68" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
@@ -4021,6 +4411,11 @@
       <c r="K69" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
@@ -4047,6 +4442,11 @@
       <c r="K70" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
@@ -4073,6 +4473,11 @@
       <c r="K71" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="n">
@@ -4098,6 +4503,11 @@
       </c>
       <c r="K72" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
       </c>
     </row>
     <row r="73" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2312,12 +2312,14 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="n">
-        <v>-1400</v>
+      <c r="A7" s="14">
+        <v>1090</v>
       </c>
       <c r="B7" s="14"/>
-      <c r="C7" s="14" t="s">
-        <v>32</v>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1090</t>
+        </is>
       </c>
       <c r="D7" s="15" t="s">
         <v>33</v>
@@ -2346,7 +2348,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">orient-ancien;islam-juif;russe</t>
+          <t xml:space="preserve">islam-juif;russe</t>
         </is>
       </c>
     </row>
@@ -4511,18 +4513,49 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0"/>
+      <c r="A73" s="0">
+        <v>-2600</v>
+      </c>
       <c r="B73" s="0"/>
-      <c r="C73" s="0"/>
-      <c r="D73" s="0"/>
-      <c r="E73" s="0"/>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600 av. J.-C.</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie antique</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/M%C3%A9sopotamie"  title=" Wikipedia"&gt;La pensée de la Mésopotamie antique&lt;/a&gt; est née entre le Tigre et l'Euphrate, chez les Sumériens puis les Akkadiens, les Babyloniens et les Assyriens, du IIIe millénaire avant J.-C. jusqu'à l'époque hellénistique. Elle ne s'exprime pas en traités mais dans des textes de sagesse, des hymnes, des épopées et des recueils de lois, écrits en cunéiforme sur des tablettes d'argile.&lt;/p&gt; &lt;p&gt;Les &lt;em&gt;Instructions de Shuruppak&lt;/em&gt;, parmi les plus anciens textes connus, donnent des conseils de prudence et de justice. Les hymnes d'Enheduanna, première autrice connue de l'histoire, font de la relation au divin une expérience personnelle. L'&lt;em&gt;Épopée de Gilgamesh&lt;/em&gt; médite sur l'amitié, la mort et la vanité de la quête d'immortalité, et le &lt;em&gt;Code de Hammurabi&lt;/em&gt; pense la justice royale et l'ordre de la cité.&lt;/p&gt; &lt;p&gt;D'autres textes posent déjà la question du mal : le &lt;em&gt;Ludlul bēl nēmeqi&lt;/em&gt; fait parler un juste éprouvé qui ne comprend pas pourquoi les dieux le frappent, et le &lt;em&gt;Dialogue du pessimisme&lt;/em&gt; met en scène, avec une ironie grinçante, un maître qui doute de toute action. La &lt;em&gt;Sagesse d'Ahiqar&lt;/em&gt; circulera ensuite dans tout le Proche-Orient, et Bérose transmettra au monde grec l'histoire et le savoir de Babylone.&lt;/p&gt; &lt;p&gt;Cette pensée, centrée sur l'ordre du monde, la justice, le destin et la condition humaine face aux dieux, a nourri les sagesses de la Bible et de la Grèce : elle est l'une des sources les plus anciennes de la réflexion philosophique.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="F73" s="0"/>
       <c r="G73" s="0"/>
       <c r="H73" s="0"/>
       <c r="I73" s="0"/>
-      <c r="J73" s="0"/>
-      <c r="K73" s="0"/>
-      <c r="L73" s="0"/>
+      <c r="J73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sagesses de Sumer et de Babylone sur la justice, le destin et la condition humaine.</t>
+        </is>
+      </c>
+      <c r="K73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Éthique;Philosophie politique</t>
+        </is>
+      </c>
+      <c r="L73" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENHEDUANNA;GILGAMESH;HAMMURABI;SHURUPPAK</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orient-ancien</t>
+        </is>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="0"/>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2327,8 +2327,10 @@
       <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>28</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mésopotamie : la 1ʳᵉ civilisation par les mondes de l’histoire</t>
+        </is>
       </c>
       <c r="J5" s="2" t="s">
         <v>29</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="485">
   <si>
     <t xml:space="preserve">FRISE DES COURANTS DE PENSÉE ORIENTALE — Données source</t>
   </si>
@@ -112,7 +112,7 @@
     <t xml:space="preserve">lrjRbKXjjeI</t>
   </si>
   <si>
-    <t xml:space="preserve">Mésopotamie : le 1ere civilisation par les mondes de l’histoire</t>
+    <t xml:space="preserve">Mésopotamie : la 1ʳᵉ civilisation par les mondes de l’histoire</t>
   </si>
   <si>
     <t xml:space="preserve">sagesses de Sumer et de Babylone sur la justice, le destin et la condition humaine.</t>
@@ -1382,6 +1382,60 @@
   </si>
   <si>
     <t xml:space="preserve">philosophie andine du bien-vivre en harmonie avec la nature, intégrée aux constitutions équatorienne et bolivienne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donghak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt; Le Donghak&lt;/a&gt; (« savoir de l’Orient ») est un mouvement de pensée religieuse et sociale fondé en 1860 par Choe Je-u, en réaction à la fois contre la pénétration du « savoir de l’Occident » (seohak, le catholicisme) et contre la crise d’une société Joseon minée par l’injustice et la misère paysanne.&lt;/p&gt;&lt;p&gt;Sa doctrine puise dans le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale, « l’être humain porte en lui le Ciel » (si cheonju), puis « l’être humain est le Ciel » (in nae cheon), fonde une égalité radicale entre tous, sans distinction de rang, de sexe ni de fortune.&lt;/p&gt;&lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement se diffuse dans les campagnes et inspire la grande révolte paysanne de 1894, dont la répression sert de prétexte à l’intervention chinoise et japonaise en Corée.&lt;/p&gt;&lt;p&gt;Renommé Cheondogyo (« religion de la Voie céleste ») en 1905, le Donghak joue un rôle majeur dans le mouvement d’indépendance du 1er mars 1919 et reste l’une des premières expressions d’une pensée moderne proprement coréenne.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mouvement religieux et social coréen fondé par Choe Je-u, affirmant que le Ciel réside en chaque être humain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minjung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Minjung_theology" title=" Wikipedia (en)"&gt; La pensée Minjung&lt;/a&gt; (« le peuple », au sens des masses opprimées) est un courant théologique et philosophique sud-coréen qui prend forme dans les années 1970, sous la dictature de Park Chung-hee, au sein des chrétiens engagés dans la lutte pour la démocratie et les droits des travailleurs.&lt;/p&gt;&lt;p&gt;Le minjung désigne ceux qui sont opprimés politiquement, exploités économiquement et tenus à l’écart de la culture. Pour Ahn Byung-mu et Suh Nam-dong, ce peuple souffrant n’est pas seulement l’objet de la compassion : il est le véritable sujet de l’histoire, et c’est dans ses luttes que se révèle le sens des Écritures.&lt;/p&gt;&lt;p&gt;La pensée Minjung s’appuie sur l’expérience coréenne du han, ce sentiment collectif de souffrance et de ressentiment accumulés, et sur les formes populaires comme le théâtre masqué. Elle trouve un précurseur dans la philosophie de la « graine » (ssial) de Ham Seok-heon, qui voyait dans le peuple le germe vivant de l’histoire.&lt;/p&gt;&lt;p&gt;Proche des théologies de la libération d’Amérique latine, elle a nourri le mouvement démocratique coréen des années 1980 et reste une référence majeure de la pensée sociale en Asie.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">courant théologique sud-coréen des années 1970 faisant du peuple opprimé le sujet de l’histoire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Théologie et spiritualité ; Philosophie politique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaozheng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Kaozheng"  title=" Wikipedia (en)"&gt;Le Kaozheng&lt;/a&gt; (« recherche des preuves ») désigne le grand mouvement d’érudition qui domine la vie intellectuelle chinoise sous la dynastie Qing, du XVIIe au début du XIXe siècle. Né du traumatisme de la chute des Ming en 1644, il reproche au néoconfucianisme, et surtout à l’école de Wang Yangming, de s’être perdu dans des spéculations creuses sur l’esprit et le principe.&lt;/p&gt; &lt;p&gt;Contre ces « paroles vides », ses lettrés prônent une « étude solide » : retrouver le sens originel des classiques confucéens en les débarrassant des commentaires des Song, grâce à la philologie, à la phonétique ancienne, à l’épigraphie, à l’astronomie et aux mathématiques. Chaque affirmation doit reposer sur des preuves vérifiables, selon une méthode que les historiens ont souvent comparée à la critique historique européenne.&lt;/p&gt; &lt;p&gt;Fondé par Gu Yanwu, le mouvement atteint son apogée au XVIIIe siècle avec Dai Zhen et les savants des écoles de Suzhou et de l’Anhui, portés par les grands chantiers éditoriaux de l’empereur Qianlong. Mais la critique des textes conduit aussi à une critique des idées : Dai Zhen s’en sert pour contester une morale du principe opposée aux désirs.&lt;/p&gt; &lt;p&gt;Au début du XXe siècle, Liang Qichao et Hu Shi virent dans le Kaozheng une « renaissance » chinoise et une préfiguration de l’esprit scientifique moderne.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">école philologique des Qing, qui veut retrouver le sens originel des classiques par la critique des textes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GU Yanwu;DAI Zhen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nouveau confucianisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nouveau_confucianisme"  title=" Wikipedia"&gt;Le nouveau confucianisme&lt;/a&gt; est un courant philosophique né dans les années 1920, en réaction au mouvement du 4 Mai 1919, qui rejetait la tradition confucéenne comme responsable du retard de la Chine. Ses penseurs veulent au contraire montrer que le confucianisme, repensé, peut répondre aux défis de la modernité.&lt;/p&gt; &lt;p&gt;Le livre de Liang Shuming sur les cultures d’Orient et d’Occident (1921) en marque le point de départ. Xiong Shili lui donne ensuite une métaphysique, inspirée du &lt;em&gt;Livre des mutations&lt;/em&gt; et d’une critique du bouddhisme, tandis que Feng Youlan relit Zhu Xi à l’aide de la logique moderne. Tous cherchent à concilier la sagesse morale chinoise avec la science et la démocratie venues d’Occident.&lt;/p&gt; &lt;p&gt;Après 1949, le courant se poursuit surtout à Hong Kong et à Taïwan, autour de Mou Zongsan, Tang Junyi et Xu Fuguan, qui publient en 1958 un &lt;em&gt;Manifeste pour une réévaluation de la culture chinoise&lt;/em&gt;. Mou Zongsan y engage un dialogue approfondi avec Kant pour fonder une « métaphysique morale ».&lt;/p&gt; &lt;p&gt;Une troisième génération, avec Tu Weiming ou Liu Shu-hsien, a porté ce courant dans les universités américaines, et il connaît depuis les années 1980 un important renouveau en Chine continentale.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">courant du XXe siècle qui renouvelle la pensée confucéenne pour répondre à la science et à la démocratie modernes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Métaphysique;Éthique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIANG Shuming;XIONG Shili;FENG Youlan;MOU Zongsan;TANG Junyi</t>
   </si>
   <si>
     <t xml:space="preserve">📖 MODE D'EMPLOI</t>
@@ -1809,7 +1863,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1819,10 +1873,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2190,7 +2240,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD78"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -2205,68 +2255,68 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="19.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="25.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="6" t="s">
         <v>12</v>
       </c>
       <c r="L3" s="2" t="s">
@@ -2280,34 +2330,34 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="9" t="n">
         <v>-2500</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
       <c r="J4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2318,7 +2368,7 @@
       <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -2327,10 +2377,8 @@
       <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mésopotamie : la 1ʳᵉ civilisation par les mondes de l’histoire</t>
-        </is>
+      <c r="G5" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>29</v>
@@ -2341,11 +2389,9 @@
       <c r="L5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="XFC5" s="0"/>
-      <c r="XFD5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="226.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -2354,7 +2400,7 @@
       <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="13" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -2372,7 +2418,7 @@
       <c r="K6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="M6" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2383,10 +2429,10 @@
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -2395,48 +2441,48 @@
       <c r="G7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="14" t="s">
         <v>42</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="M7" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="15" t="n">
         <v>1090</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
       <c r="J8" s="2" t="s">
         <v>49</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="0" t="s">
+      <c r="N8" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2465,10 +2511,10 @@
       <c r="K9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N9" s="0" t="s">
+      <c r="N9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2497,42 +2543,42 @@
       <c r="K10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="M10" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="9" t="n">
         <v>-700</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
       <c r="J11" s="2" t="s">
         <v>70</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="0" t="s">
+      <c r="N11" s="1" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2561,42 +2607,42 @@
       <c r="K12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N12" s="0" t="s">
+      <c r="N12" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="15" t="n">
         <v>-600</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
       <c r="J13" s="2" t="s">
         <v>82</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="M13" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2607,7 +2653,7 @@
       <c r="C14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>83</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -2625,7 +2671,7 @@
       <c r="K14" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2633,13 +2679,13 @@
       <c r="A15" s="1" t="n">
         <v>-550</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="14" t="s">
         <v>91</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -2648,77 +2694,77 @@
       <c r="G15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="14" t="s">
         <v>94</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="9" t="n">
         <v>-520</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
       <c r="J16" s="2" t="s">
         <v>100</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="M16" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="15" t="n">
         <v>-510</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16" t="s">
+      <c r="B17" s="15"/>
+      <c r="C17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
       <c r="J17" s="2" t="s">
         <v>107</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="M17" s="2" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2729,7 +2775,7 @@
       <c r="C18" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>110</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -2747,7 +2793,7 @@
       <c r="K18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="M18" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2758,7 +2804,7 @@
       <c r="C19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="13" t="s">
         <v>115</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -2776,170 +2822,170 @@
       <c r="K19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="M19" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="9" t="n">
         <v>-500</v>
       </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10" t="s">
+      <c r="B20" s="9"/>
+      <c r="C20" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="2" t="s">
         <v>125</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="M20" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="9" t="n">
         <v>-470</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
       <c r="J21" s="2" t="s">
         <v>131</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="M21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N21" s="0" t="s">
+      <c r="N21" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="n">
+      <c r="A22" s="15" t="n">
         <v>-450</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
       <c r="J22" s="2" t="s">
         <v>137</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="M22" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="9" t="n">
         <v>-410</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
       <c r="J23" s="2" t="s">
         <v>143</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="M23" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="n">
+      <c r="A24" s="15" t="n">
         <v>-400</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
       <c r="J24" s="2" t="s">
         <v>149</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="M24" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2950,7 +2996,7 @@
       <c r="C25" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>150</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -2968,39 +3014,39 @@
       <c r="K25" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="M25" s="3" t="s">
+      <c r="M25" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="9" t="n">
         <v>-350</v>
       </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10" t="s">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
       <c r="J26" s="2" t="s">
         <v>161</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="M26" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3011,7 +3057,7 @@
       <c r="C27" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="13" t="s">
         <v>162</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -3029,7 +3075,7 @@
       <c r="K27" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="M27" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3040,7 +3086,7 @@
       <c r="C28" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="13" t="s">
         <v>168</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -3058,71 +3104,71 @@
       <c r="K28" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="M28" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="n">
+      <c r="A29" s="15" t="n">
         <v>-150</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
       <c r="J29" s="2" t="s">
         <v>178</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="M29" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="9" t="n">
         <v>-100</v>
       </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10" t="s">
+      <c r="B30" s="9"/>
+      <c r="C30" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
       <c r="J30" s="2" t="s">
         <v>184</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="M30" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3133,7 +3179,7 @@
       <c r="C31" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="13" t="s">
         <v>185</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -3151,74 +3197,74 @@
       <c r="K31" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M31" s="3" t="s">
+      <c r="M31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N31" s="0" t="s">
+      <c r="N31" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16" t="n">
+      <c r="A32" s="15" t="n">
         <v>250</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16" t="s">
+      <c r="B32" s="15"/>
+      <c r="C32" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
       <c r="J32" s="2" t="s">
         <v>195</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="M32" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="15" t="n">
         <v>450</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16" t="n">
+      <c r="B33" s="15"/>
+      <c r="C33" s="15" t="n">
         <v>450</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
       <c r="J33" s="2" t="s">
         <v>201</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M33" s="3" t="s">
+      <c r="M33" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3229,7 +3275,7 @@
       <c r="C34" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="13" t="s">
         <v>202</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -3247,7 +3293,7 @@
       <c r="K34" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="M34" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3258,7 +3304,7 @@
       <c r="C35" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="13" t="s">
         <v>207</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -3276,10 +3322,10 @@
       <c r="K35" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="M35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N35" s="0" t="s">
+      <c r="N35" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3290,10 +3336,10 @@
       <c r="C36" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="22" t="s">
         <v>213</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -3302,77 +3348,77 @@
       <c r="G36" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="J36" s="23" t="s">
+      <c r="J36" s="22" t="s">
         <v>216</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="M36" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="9" t="n">
         <v>750</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
         <v>222</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M37" s="3" t="s">
+      <c r="M37" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16" t="n">
+      <c r="A38" s="15" t="n">
         <v>750</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
       <c r="J38" s="2" t="s">
         <v>227</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="M38" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3383,7 +3429,7 @@
       <c r="C39" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="13" t="s">
         <v>228</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -3401,42 +3447,42 @@
       <c r="K39" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="M39" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="9" t="n">
         <v>820</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G40" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
       <c r="J40" s="2" t="s">
         <v>238</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M40" s="3" t="s">
+      <c r="M40" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N40" s="0" t="s">
+      <c r="N40" s="1" t="s">
         <v>239</v>
       </c>
     </row>
@@ -3447,7 +3493,7 @@
       <c r="C41" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="13" t="s">
         <v>240</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -3465,39 +3511,39 @@
       <c r="K41" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="M41" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="n">
+      <c r="A42" s="15" t="n">
         <v>890</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16" t="s">
+      <c r="B42" s="15"/>
+      <c r="C42" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
       <c r="J42" s="2" t="s">
         <v>250</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M42" s="3" t="s">
+      <c r="M42" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3508,7 +3554,7 @@
       <c r="C43" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="13" t="s">
         <v>252</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -3540,7 +3586,7 @@
       <c r="C44" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="13" t="s">
         <v>259</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -3558,7 +3604,7 @@
       <c r="K44" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M44" s="3" t="s">
+      <c r="M44" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3569,7 +3615,7 @@
       <c r="C45" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="13" t="s">
         <v>264</v>
       </c>
       <c r="E45" s="2" t="s">
@@ -3587,7 +3633,7 @@
       <c r="K45" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="M45" s="2" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3598,7 +3644,7 @@
       <c r="C46" s="1" t="n">
         <v>1150</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="13" t="s">
         <v>269</v>
       </c>
       <c r="E46" s="2" t="s">
@@ -3616,42 +3662,42 @@
       <c r="K46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M46" s="3" t="s">
+      <c r="M46" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N46" s="0" t="s">
+      <c r="N46" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10" t="n">
+      <c r="A47" s="9" t="n">
         <v>1150</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10" t="s">
+      <c r="B47" s="9"/>
+      <c r="C47" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="E47" s="24" t="s">
+      <c r="E47" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
       <c r="J47" s="2" t="s">
         <v>279</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M47" s="3" t="s">
+      <c r="M47" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3662,7 +3708,7 @@
       <c r="C48" s="1" t="n">
         <v>1200</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="13" t="s">
         <v>280</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -3680,7 +3726,7 @@
       <c r="K48" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="M48" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3691,7 +3737,7 @@
       <c r="C49" s="1" t="n">
         <v>1300</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="13" t="s">
         <v>286</v>
       </c>
       <c r="E49" s="2" t="s">
@@ -3709,7 +3755,7 @@
       <c r="K49" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M49" s="3" t="s">
+      <c r="M49" s="2" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3720,10 +3766,10 @@
       <c r="C50" s="1" t="n">
         <v>1650</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="E50" s="25" t="s">
+      <c r="E50" s="24" t="s">
         <v>292</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -3732,77 +3778,77 @@
       <c r="G50" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="J50" s="25" t="s">
+      <c r="J50" s="24" t="s">
         <v>295</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="3" t="s">
+      <c r="M50" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="n">
+      <c r="A51" s="15" t="n">
         <v>1680</v>
       </c>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16" t="s">
+      <c r="B51" s="15"/>
+      <c r="C51" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="16" t="s">
+      <c r="F51" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="G51" s="18" t="s">
+      <c r="G51" s="17" t="s">
         <v>300</v>
       </c>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
       <c r="J51" s="2" t="s">
         <v>301</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M51" s="3" t="s">
+      <c r="M51" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="16" t="n">
+      <c r="A52" s="15" t="n">
         <v>1720</v>
       </c>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16" t="n">
+      <c r="B52" s="15"/>
+      <c r="C52" s="15" t="n">
         <v>1720</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="E52" s="21" t="s">
+      <c r="E52" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="F52" s="16" t="s">
+      <c r="F52" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="G52" s="18" t="s">
+      <c r="G52" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="H52" s="16"/>
-      <c r="I52" s="16"/>
-      <c r="J52" s="25" t="s">
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="24" t="s">
         <v>306</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="M52" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3813,7 +3859,7 @@
       <c r="C53" s="1" t="n">
         <v>1750</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="13" t="s">
         <v>307</v>
       </c>
       <c r="E53" s="2" t="s">
@@ -3831,71 +3877,71 @@
       <c r="K53" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M53" s="3" t="s">
+      <c r="M53" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="10" t="n">
+      <c r="A54" s="9" t="n">
         <v>1760</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10" t="s">
+      <c r="B54" s="9"/>
+      <c r="C54" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
         <v>317</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="M54" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="16" t="n">
+      <c r="A55" s="15" t="n">
         <v>1820</v>
       </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16" t="n">
+      <c r="B55" s="15"/>
+      <c r="C55" s="15" t="n">
         <v>1820</v>
       </c>
-      <c r="D55" s="17" t="s">
+      <c r="D55" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="F55" s="16" t="s">
+      <c r="F55" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="G55" s="18" t="s">
+      <c r="G55" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="H55" s="16"/>
-      <c r="I55" s="18"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="17"/>
       <c r="J55" s="2" t="s">
         <v>322</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M55" s="3" t="s">
+      <c r="M55" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3906,7 +3952,7 @@
       <c r="C56" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="13" t="s">
         <v>324</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -3938,7 +3984,7 @@
       <c r="C57" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="13" t="s">
         <v>332</v>
       </c>
       <c r="E57" s="2" t="s">
@@ -3956,106 +4002,106 @@
       <c r="K57" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M57" s="3" t="s">
+      <c r="M57" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="16" t="n">
+      <c r="A58" s="15" t="n">
         <v>1845</v>
       </c>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16" t="n">
+      <c r="B58" s="15"/>
+      <c r="C58" s="15" t="n">
         <v>1845</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="F58" s="16" t="s">
+      <c r="F58" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="G58" s="18" t="s">
+      <c r="G58" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="H58" s="16"/>
-      <c r="I58" s="18"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="17"/>
       <c r="J58" s="2" t="s">
         <v>341</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="M58" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N58" s="0" t="s">
+      <c r="N58" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16" t="n">
+      <c r="A59" s="15" t="n">
         <v>1850</v>
       </c>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16" t="n">
+      <c r="B59" s="15"/>
+      <c r="C59" s="15" t="n">
         <v>1850</v>
       </c>
-      <c r="D59" s="26" t="s">
+      <c r="D59" s="25" t="s">
         <v>342</v>
       </c>
-      <c r="E59" s="27" t="s">
+      <c r="E59" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="F59" s="16" t="s">
+      <c r="F59" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="G59" s="17" t="s">
         <v>345</v>
       </c>
-      <c r="H59" s="16"/>
-      <c r="I59" s="18"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="17"/>
       <c r="J59" s="2" t="s">
         <v>346</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M59" s="3" t="s">
+      <c r="M59" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="16" t="n">
+      <c r="A60" s="15" t="n">
         <v>1850</v>
       </c>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16" t="n">
+      <c r="B60" s="15"/>
+      <c r="C60" s="15" t="n">
         <v>1850</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="E60" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="F60" s="16" t="s">
+      <c r="F60" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="G60" s="18" t="s">
+      <c r="G60" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="H60" s="16"/>
-      <c r="I60" s="18"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="17"/>
       <c r="J60" s="2" t="s">
         <v>351</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="M60" s="3" t="s">
+      <c r="M60" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4084,71 +4130,71 @@
       <c r="K61" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M61" s="3" t="s">
+      <c r="M61" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="9" t="n">
         <v>1870</v>
       </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10" t="n">
+      <c r="B62" s="9"/>
+      <c r="C62" s="9" t="n">
         <v>1870</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="E62" s="28" t="s">
+      <c r="E62" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="F62" s="10" t="s">
+      <c r="F62" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="G62" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
       <c r="J62" s="2" t="s">
         <v>362</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M62" s="3" t="s">
+      <c r="M62" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="16" t="n">
+      <c r="A63" s="15" t="n">
         <v>1878</v>
       </c>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16" t="n">
+      <c r="B63" s="15"/>
+      <c r="C63" s="15" t="n">
         <v>1878</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="F63" s="16" t="s">
+      <c r="F63" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="G63" s="18" t="s">
+      <c r="G63" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="H63" s="16"/>
-      <c r="I63" s="18"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="17"/>
       <c r="J63" s="2" t="s">
         <v>367</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="M63" s="3" t="s">
+      <c r="M63" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4159,7 +4205,7 @@
       <c r="C64" s="1" t="n">
         <v>1900</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="13" t="s">
         <v>369</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -4177,10 +4223,10 @@
       <c r="K64" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M64" s="3" t="s">
+      <c r="M64" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="N64" s="0" t="s">
+      <c r="N64" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -4191,7 +4237,7 @@
       <c r="C65" s="1" t="n">
         <v>1905</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="13" t="s">
         <v>374</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -4209,7 +4255,7 @@
       <c r="K65" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M65" s="3" t="s">
+      <c r="M65" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4220,10 +4266,10 @@
       <c r="C66" s="1" t="n">
         <v>1905</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D66" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="E66" s="23" t="s">
+      <c r="E66" s="22" t="s">
         <v>380</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -4232,13 +4278,13 @@
       <c r="G66" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="J66" s="23" t="s">
+      <c r="J66" s="22" t="s">
         <v>383</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="M66" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4249,7 +4295,7 @@
       <c r="C67" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="D67" s="14" t="s">
+      <c r="D67" s="13" t="s">
         <v>384</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -4267,7 +4313,7 @@
       <c r="K67" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M67" s="3" t="s">
+      <c r="M67" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4296,39 +4342,39 @@
       <c r="K68" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="M68" s="3" t="s">
+      <c r="M68" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="16" t="n">
+      <c r="A69" s="15" t="n">
         <v>1935</v>
       </c>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16" t="s">
+      <c r="B69" s="15"/>
+      <c r="C69" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="E69" s="18" t="s">
+      <c r="E69" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="F69" s="16" t="s">
+      <c r="F69" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="G69" s="18" t="s">
+      <c r="G69" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
       <c r="J69" s="2" t="s">
         <v>400</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M69" s="3" t="s">
+      <c r="M69" s="2" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4339,10 +4385,10 @@
       <c r="C70" s="1" t="n">
         <v>1940</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="13" t="s">
         <v>401</v>
       </c>
-      <c r="E70" s="25" t="s">
+      <c r="E70" s="24" t="s">
         <v>402</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -4351,13 +4397,13 @@
       <c r="G70" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="J70" s="25" t="s">
+      <c r="J70" s="24" t="s">
         <v>405</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M70" s="3" t="s">
+      <c r="M70" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4368,7 +4414,7 @@
       <c r="C71" s="1" t="n">
         <v>1945</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="13" t="s">
         <v>406</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -4386,7 +4432,7 @@
       <c r="K71" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M71" s="3" t="s">
+      <c r="M71" s="2" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4397,7 +4443,7 @@
       <c r="C72" s="1" t="n">
         <v>1964</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="13" t="s">
         <v>411</v>
       </c>
       <c r="E72" s="2" t="s">
@@ -4415,18 +4461,18 @@
       <c r="K72" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M72" s="3" t="s">
+      <c r="M72" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="n">
         <v>1990</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>1990</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="13" t="s">
         <v>416</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -4444,31 +4490,111 @@
       <c r="K73" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M73" s="3" t="s">
+      <c r="M73" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0"/>
-      <c r="B74" s="0"/>
-      <c r="C74" s="0"/>
-      <c r="D74" s="0"/>
-      <c r="E74" s="0"/>
-      <c r="F74" s="0"/>
-      <c r="G74" s="0"/>
-      <c r="H74" s="0"/>
-      <c r="I74" s="0"/>
-      <c r="J74" s="0"/>
-      <c r="K74" s="0"/>
-      <c r="L74" s="0"/>
-      <c r="M74" s="0"/>
-    </row>
-    <row r="75" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D75" s="1"/>
+    <row r="74" customFormat="false" ht="273.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G74" s="1"/>
+      <c r="J74" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="n">
+        <v>1970</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>1970</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>427</v>
+      </c>
       <c r="L75" s="1"/>
-    </row>
-    <row r="76" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="M75" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
+        <v>1921</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
@@ -4519,193 +4645,193 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="29" t="s">
-        <v>421</v>
+      <c r="B3" s="28" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="s">
-        <v>422</v>
+      <c r="B5" s="28" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>424</v>
+      <c r="B6" s="29" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>426</v>
+      <c r="B7" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="s">
-        <v>427</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>428</v>
+      <c r="B8" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="s">
-        <v>429</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>430</v>
+      <c r="B9" s="29" t="s">
+        <v>447</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>432</v>
+      <c r="B10" s="29" t="s">
+        <v>449</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>434</v>
+      <c r="B11" s="29" t="s">
+        <v>451</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="s">
-        <v>435</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>436</v>
+      <c r="B12" s="29" t="s">
+        <v>453</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30" t="s">
-        <v>437</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>438</v>
+      <c r="B13" s="29" t="s">
+        <v>455</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30" t="s">
-        <v>439</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>440</v>
+      <c r="B14" s="29" t="s">
+        <v>457</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="29" t="s">
-        <v>441</v>
+      <c r="B16" s="28" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="30" t="s">
-        <v>442</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>443</v>
+      <c r="B17" s="29" t="s">
+        <v>460</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30" t="s">
-        <v>444</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>445</v>
+      <c r="B18" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30" t="s">
-        <v>446</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>447</v>
+      <c r="B19" s="29" t="s">
+        <v>464</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="29" t="s">
-        <v>448</v>
+      <c r="B21" s="28" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="s">
-        <v>449</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>450</v>
+      <c r="B22" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30" t="s">
-        <v>451</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>452</v>
+      <c r="B23" s="29" t="s">
+        <v>469</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="29" t="s">
-        <v>453</v>
+      <c r="B25" s="28" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30" t="s">
-        <v>454</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>455</v>
+      <c r="B26" s="29" t="s">
+        <v>472</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="30" t="s">
-        <v>456</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>457</v>
+      <c r="B27" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="30" t="s">
-        <v>458</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>459</v>
+      <c r="B28" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="30" t="s">
-        <v>460</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>461</v>
+      <c r="B29" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="29" t="s">
-        <v>462</v>
+      <c r="B31" s="28" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="30" t="s">
-        <v>463</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>464</v>
+      <c r="B32" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="30" t="s">
-        <v>465</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>466</v>
+      <c r="B33" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>484</v>
       </c>
     </row>
   </sheetData>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -4595,7 +4595,46 @@
         <v>101</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1">
+        <v>1911</v>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1911</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École de Kyōto</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Ky%C5%8Dto"  title=" Wikipedia"&gt;L’école de Kyōto&lt;/a&gt; désigne le premier grand courant de philosophie moderne né au Japon, autour de Kitarō Nishida et de ses successeurs à l’université impériale de Kyōto. Son point de départ est souvent fixé à 1911, date de la &lt;em&gt;Recherche sur le bien&lt;/em&gt; de Nishida.&lt;/p&gt; &lt;p&gt;Ses penseurs, formés à la philosophie allemande, de Kant et Hegel à Husserl et Heidegger, veulent exprimer dans le langage de la philosophie occidentale l’expérience spirituelle de l’Asie, en particulier celle du bouddhisme zen et de la Terre pure. Au centre de leur réflexion se trouve la notion de « néant absolu » : non pas un simple manque, mais le fond ouvert d’où tout surgit, que Nishida pense comme le « lieu » de toute réalité.&lt;/p&gt; &lt;p&gt;Tanabe Hajime, Nishitani Keiji, puis Ueda Shizuteru développèrent cette pensée, tandis que Watsuji Tetsurō et Kuki Shūzō, proches du groupe, l’ouvrirent à l’éthique et à l’esthétique. Plusieurs de ses membres furent compromis dans la justification idéologique de la guerre du Pacifique, ce qui a longtemps pesé sur sa réception.&lt;/p&gt; &lt;p&gt;Depuis les années 1980, l’école de Kyōto est étudiée dans le monde entier comme le lieu d’un dialogue majeur entre la philosophie occidentale et les traditions spirituelles d’Asie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premier grand courant de philosophie moderne né au Japon, autour de Nishida, Tanabe et Nishitani.</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kitaro NISHIDA;Hajime TANABE;Keiji NISHITANI;Tetsurō WATSUJI;Shūzō KUKI</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="500">
   <si>
     <t xml:space="preserve">FRISE DES COURANTS DE PENSÉE ORIENTALE — Données source</t>
   </si>
@@ -996,6 +996,24 @@
     <t xml:space="preserve">croyance et pratique spirituelle ancienne, centrée sur la médiation entre le monde humain et le monde des esprits.</t>
   </si>
   <si>
+    <t xml:space="preserve">1650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaozheng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Kaozheng"  title=" Wikipedia (en)"&gt;Le Kaozheng&lt;/a&gt; (« recherche des preuves ») désigne le grand mouvement d’érudition qui domine la vie intellectuelle chinoise sous la dynastie Qing, du XVIIe au début du XIXe siècle. Né du traumatisme de la chute des Ming en 1644, il reproche au néoconfucianisme, et surtout à l’école de Wang Yangming, de s’être perdu dans des spéculations creuses sur l’esprit et le principe.&lt;/p&gt; &lt;p&gt;Contre ces « paroles vides », ses lettrés prônent une « étude solide » : retrouver le sens originel des classiques confucéens en les débarrassant des commentaires des Song, grâce à la philologie, à la phonétique ancienne, à l’épigraphie, à l’astronomie et aux mathématiques. Chaque affirmation doit reposer sur des preuves vérifiables, selon une méthode que les historiens ont souvent comparée à la critique historique européenne.&lt;/p&gt; &lt;p&gt;Fondé par Gu Yanwu, le mouvement atteint son apogée au XVIIIe siècle avec Dai Zhen et les savants des écoles de Suzhou et de l’Anhui, portés par les grands chantiers éditoriaux de l’empereur Qianlong. Mais la critique des textes conduit aussi à une critique des idées : Dai Zhen s’en sert pour contester une morale du principe opposée aux désirs.&lt;/p&gt; &lt;p&gt;Au début du XXe siècle, Liang Qichao et Hu Shi virent dans le Kaozheng une « renaissance » chinoise et une préfiguration de l’esprit scientifique moderne.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o72U2d_z4S0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">école philologique des Qing, qui veut retrouver le sens originel des classiques par la critique des textes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GU Yanwu;DAI Zhen</t>
+  </si>
+  <si>
     <t xml:space="preserve">1680</t>
   </si>
   <si>
@@ -1172,6 +1190,42 @@
     <t xml:space="preserve">courant philosophique russe qui privilégie la connaissance immédiate par l'intuition.</t>
   </si>
   <si>
+    <t xml:space="preserve">Donghak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt; Le Donghak&lt;/a&gt; (« savoir de l’Orient ») est un mouvement de pensée religieuse et sociale fondé par Choe Je-u, en réaction à la fois contre la pénétration du « savoir de l’Occident » (seohak, le catholicisme) et contre la crise d’une société Joseon minée par l’injustice et la misère paysanne.&lt;/p&gt;&lt;p&gt;Sa doctrine puise dans le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale, « l’être humain porte en lui le Ciel » (si cheonju), puis « l’être humain est le Ciel » (in nae cheon), fonde une égalité radicale entre tous, sans distinction de rang, de sexe ni de fortune.&lt;/p&gt;&lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement se diffuse dans les campagnes et inspire la grande révolte paysanne de 1894, dont la répression sert de prétexte à l’intervention chinoise et japonaise en Corée.&lt;/p&gt;&lt;p&gt;Renommé Cheondogyo (« religion de la Voie céleste ») en 1905, il joue un rôle majeur dans le mouvement d’indépendance du 1er mars 1919 et reste l’une des premières expressions d’une pensée moderne proprement coréenne.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zU_Ui_nE_eU</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="22"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Donghak Thought Modernity par Yinyangwuxing</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mouvement religieux et social coréen fondé par Choe Je-u, affirmant que le Ciel réside en chaque être humain.</t>
+  </si>
+  <si>
     <t xml:space="preserve">1865</t>
   </si>
   <si>
@@ -1271,6 +1325,48 @@
     <t xml:space="preserve">doctrine philosophique développée par A. Bogdanov qui pense la réalité comme une expérience unique et organisée.</t>
   </si>
   <si>
+    <t xml:space="preserve">1911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">École de Kyōto</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Ky%C5%8Dto"  title=" Wikipedia"&gt;L’école de Kyōto&lt;/a&gt; désigne le premier grand courant de philosophie moderne né au Japon, autour de Kitarō Nishida et de ses successeurs à l’université impériale de Kyōto. Son point de départ est souvent fixé à 1911, date de la &lt;em&gt;Recherche sur le bien&lt;/em&gt; de Nishida.&lt;/p&gt; &lt;p&gt;Ses penseurs, formés à la philosophie allemande, de Kant et Hegel à Husserl et Heidegger, veulent exprimer dans le langage de la philosophie occidentale l’expérience spirituelle de l’Asie, en particulier celle du bouddhisme zen et de la Terre pure. Au centre de leur réflexion se trouve la notion de « néant absolu » : non pas un simple manque, mais le fond ouvert d’où tout surgit, que Nishida pense comme le « lieu » de toute réalité.&lt;/p&gt; &lt;p&gt;Tanabe Hajime, Nishitani Keiji, puis Ueda Shizuteru développèrent cette pensée, tandis que Watsuji Tetsurō et Kuki Shūzō, proches du groupe, l’ouvrirent à l’éthique et à l’esthétique. Plusieurs de ses membres furent compromis dans la justification idéologique de la guerre du Pacifique, ce qui a longtemps pesé sur sa réception.&lt;/p&gt; &lt;p&gt;Depuis les années 1980, l’école de Kyōto est étudiée dans le monde entier comme le lieu d’un dialogue majeur entre la philosophie occidentale et les traditions spirituelles d’Asie.&lt;/p&gt;  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">&lt;audio controls title="Philosophie japonaise: l’école de Kyôto par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.11.2013-ITEMA_20549374-2013C12410E0320-NET_FC_EE7092B3-7D80-40AA-947D-AFAD338FBA01-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CvHOBoIpJB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’écolede Kyôto par Rien ne veut rien dire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">premier grand courant de philosophie moderne né au Japon, autour de Nishida, Tanabe et Nishitani.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitaro NISHIDA;Hajime TANABE;Keiji NISHITANI;Tetsurō WATSUJI;Shūzō KUKI</t>
+  </si>
+  <si>
     <t xml:space="preserve">Philosophie Dalit</t>
   </si>
   <si>
@@ -1302,6 +1398,30 @@
   </si>
   <si>
     <t xml:space="preserve">système logique qui tolère les contradictions sans que cela entraîne l'explosion logique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nouveau confucianisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nouveau_confucianisme"  title=" Wikipedia"&gt;Le nouveau confucianisme&lt;/a&gt; est un courant philosophique en réaction au mouvement du 4 Mai 1919, qui rejetait la tradition confucéenne comme responsable du retard de la Chine. Ses penseurs veulent au contraire montrer que le confucianisme, repensé, peut répondre aux défis de la modernité.&lt;/p&gt; &lt;p&gt;Le livre de Liang Shuming sur les cultures d’Orient et d’Occident (1921) en marque le point de départ. Xiong Shili lui donne ensuite une métaphysique, inspirée du &lt;em&gt;Livre des mutations&lt;/em&gt; et d’une critique du bouddhisme, tandis que Feng Youlan relit Zhu Xi à l’aide de la logique moderne. Tous cherchent à concilier la sagesse morale chinoise avec la science et la démocratie venues d’Occident.&lt;/p&gt; &lt;p&gt;Après 1949, le courant se poursuit surtout à Hong Kong et à Taïwan, autour de Mou Zongsan, Tang Junyi et Xu Fuguan, qui publient en 1958 un &lt;em&gt;Manifeste pour une réévaluation de la culture chinoise&lt;/em&gt;. Mou Zongsan y engage un dialogue approfondi avec Kant pour fonder une « métaphysique morale ».&lt;/p&gt; &lt;p&gt;Une troisième génération, avec Tu Weiming ou Liu Shu-hsien, a porté ce courant dans les universités américaines, et il connaît depuis les années 1980 un important renouveau en Chine continentale.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dfCu_jdATxo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confucius revisité , nouveau discours par Histoire et archéologie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">courant du XXe siècle qui renouvelle la pensée confucéenne pour répondre à la science et à la démocratie modernes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Métaphysique;Éthique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIANG Shuming;XIONG Shili;FENG Youlan;MOU Zongsan;TANG Junyi</t>
   </si>
   <si>
     <t xml:space="preserve">1935</t>
@@ -1369,6 +1489,24 @@
     <t xml:space="preserve">philosophie politique de Kwame Nkrumah synthétisant communalisme africain, marxisme et décolonisation.</t>
   </si>
   <si>
+    <t xml:space="preserve">Minjung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Minjung_theology" title=" Wikipedia (en)"&gt; La pensée Minjung&lt;/a&gt; (« le peuple », au sens des masses opprimées) est un courant théologique et philosophique sud-coréen qui prend forme sous la dictature de Park Chung-hee, au sein des chrétiens engagés dans la lutte pour la démocratie et les droits des travailleurs.&lt;/p&gt;&lt;p&gt;Il désigne ceux qui sont opprimés politiquement, exploités économiquement et tenus à l’écart de la culture. Pour Ahn Byung-mu et Suh Nam-dong, ce peuple souffrant n’est pas seulement l’objet de la compassion : il est le véritable sujet de l’histoire, et c’est dans ses luttes que se révèle le sens des Écritures.&lt;/p&gt;&lt;p&gt;La pensée Minjung s’appuie sur l’expérience coréenne du han, ce sentiment collectif de souffrance et de ressentiment accumulés, et sur les formes populaires comme le théâtre masqué. Elle trouve un précurseur dans la philosophie de la « graine » (ssial) de Ham Seok-heon, qui voyait dans le peuple le germe vivant de l’histoire.&lt;/p&gt;&lt;p&gt;Proche des théologies de la libération d’Amérique latine, elle a nourri le mouvement démocratique coréen des années 1980 et reste une référence majeure de la pensée sociale en Asie.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7oAG8x5qBH0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minjung Theology par Lindsey Bender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">courant théologique sud-coréen des années 1970 faisant du peuple opprimé le sujet de l’histoire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Théologie et spiritualité ; Philosophie politique</t>
+  </si>
+  <si>
     <t xml:space="preserve">Buen Vivir (cosmovision andine)</t>
   </si>
   <si>
@@ -1382,60 +1520,6 @@
   </si>
   <si>
     <t xml:space="preserve">philosophie andine du bien-vivre en harmonie avec la nature, intégrée aux constitutions équatorienne et bolivienne.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donghak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt; Le Donghak&lt;/a&gt; (« savoir de l’Orient ») est un mouvement de pensée religieuse et sociale fondé en 1860 par Choe Je-u, en réaction à la fois contre la pénétration du « savoir de l’Occident » (seohak, le catholicisme) et contre la crise d’une société Joseon minée par l’injustice et la misère paysanne.&lt;/p&gt;&lt;p&gt;Sa doctrine puise dans le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale, « l’être humain porte en lui le Ciel » (si cheonju), puis « l’être humain est le Ciel » (in nae cheon), fonde une égalité radicale entre tous, sans distinction de rang, de sexe ni de fortune.&lt;/p&gt;&lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement se diffuse dans les campagnes et inspire la grande révolte paysanne de 1894, dont la répression sert de prétexte à l’intervention chinoise et japonaise en Corée.&lt;/p&gt;&lt;p&gt;Renommé Cheondogyo (« religion de la Voie céleste ») en 1905, le Donghak joue un rôle majeur dans le mouvement d’indépendance du 1er mars 1919 et reste l’une des premières expressions d’une pensée moderne proprement coréenne.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mouvement religieux et social coréen fondé par Choe Je-u, affirmant que le Ciel réside en chaque être humain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minjung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Minjung_theology" title=" Wikipedia (en)"&gt; La pensée Minjung&lt;/a&gt; (« le peuple », au sens des masses opprimées) est un courant théologique et philosophique sud-coréen qui prend forme dans les années 1970, sous la dictature de Park Chung-hee, au sein des chrétiens engagés dans la lutte pour la démocratie et les droits des travailleurs.&lt;/p&gt;&lt;p&gt;Le minjung désigne ceux qui sont opprimés politiquement, exploités économiquement et tenus à l’écart de la culture. Pour Ahn Byung-mu et Suh Nam-dong, ce peuple souffrant n’est pas seulement l’objet de la compassion : il est le véritable sujet de l’histoire, et c’est dans ses luttes que se révèle le sens des Écritures.&lt;/p&gt;&lt;p&gt;La pensée Minjung s’appuie sur l’expérience coréenne du han, ce sentiment collectif de souffrance et de ressentiment accumulés, et sur les formes populaires comme le théâtre masqué. Elle trouve un précurseur dans la philosophie de la « graine » (ssial) de Ham Seok-heon, qui voyait dans le peuple le germe vivant de l’histoire.&lt;/p&gt;&lt;p&gt;Proche des théologies de la libération d’Amérique latine, elle a nourri le mouvement démocratique coréen des années 1980 et reste une référence majeure de la pensée sociale en Asie.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">courant théologique sud-coréen des années 1970 faisant du peuple opprimé le sujet de l’histoire.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Théologie et spiritualité ; Philosophie politique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1650</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaozheng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Kaozheng"  title=" Wikipedia (en)"&gt;Le Kaozheng&lt;/a&gt; (« recherche des preuves ») désigne le grand mouvement d’érudition qui domine la vie intellectuelle chinoise sous la dynastie Qing, du XVIIe au début du XIXe siècle. Né du traumatisme de la chute des Ming en 1644, il reproche au néoconfucianisme, et surtout à l’école de Wang Yangming, de s’être perdu dans des spéculations creuses sur l’esprit et le principe.&lt;/p&gt; &lt;p&gt;Contre ces « paroles vides », ses lettrés prônent une « étude solide » : retrouver le sens originel des classiques confucéens en les débarrassant des commentaires des Song, grâce à la philologie, à la phonétique ancienne, à l’épigraphie, à l’astronomie et aux mathématiques. Chaque affirmation doit reposer sur des preuves vérifiables, selon une méthode que les historiens ont souvent comparée à la critique historique européenne.&lt;/p&gt; &lt;p&gt;Fondé par Gu Yanwu, le mouvement atteint son apogée au XVIIIe siècle avec Dai Zhen et les savants des écoles de Suzhou et de l’Anhui, portés par les grands chantiers éditoriaux de l’empereur Qianlong. Mais la critique des textes conduit aussi à une critique des idées : Dai Zhen s’en sert pour contester une morale du principe opposée aux désirs.&lt;/p&gt; &lt;p&gt;Au début du XXe siècle, Liang Qichao et Hu Shi virent dans le Kaozheng une « renaissance » chinoise et une préfiguration de l’esprit scientifique moderne.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">école philologique des Qing, qui veut retrouver le sens originel des classiques par la critique des textes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GU Yanwu;DAI Zhen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nouveau confucianisme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nouveau_confucianisme"  title=" Wikipedia"&gt;Le nouveau confucianisme&lt;/a&gt; est un courant philosophique né dans les années 1920, en réaction au mouvement du 4 Mai 1919, qui rejetait la tradition confucéenne comme responsable du retard de la Chine. Ses penseurs veulent au contraire montrer que le confucianisme, repensé, peut répondre aux défis de la modernité.&lt;/p&gt; &lt;p&gt;Le livre de Liang Shuming sur les cultures d’Orient et d’Occident (1921) en marque le point de départ. Xiong Shili lui donne ensuite une métaphysique, inspirée du &lt;em&gt;Livre des mutations&lt;/em&gt; et d’une critique du bouddhisme, tandis que Feng Youlan relit Zhu Xi à l’aide de la logique moderne. Tous cherchent à concilier la sagesse morale chinoise avec la science et la démocratie venues d’Occident.&lt;/p&gt; &lt;p&gt;Après 1949, le courant se poursuit surtout à Hong Kong et à Taïwan, autour de Mou Zongsan, Tang Junyi et Xu Fuguan, qui publient en 1958 un &lt;em&gt;Manifeste pour une réévaluation de la culture chinoise&lt;/em&gt;. Mou Zongsan y engage un dialogue approfondi avec Kant pour fonder une « métaphysique morale ».&lt;/p&gt; &lt;p&gt;Une troisième génération, avec Tu Weiming ou Liu Shu-hsien, a porté ce courant dans les universités américaines, et il connaît depuis les années 1980 un important renouveau en Chine continentale.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">courant du XXe siècle qui renouvelle la pensée confucéenne pour répondre à la science et à la démocratie modernes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Métaphysique;Éthique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIANG Shuming;XIONG Shili;FENG Youlan;MOU Zongsan;TANG Junyi</t>
   </si>
   <si>
     <t xml:space="preserve">📖 MODE D'EMPLOI</t>
@@ -1583,7 +1667,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1724,6 +1808,20 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -1913,10 +2011,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1972,19 +2066,23 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2240,7 +2338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:XFD1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -2248,7 +2346,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8.06"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="20.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="69.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="25.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="7.37"/>
@@ -2400,7 +2498,7 @@
       <c r="C6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -2429,10 +2527,10 @@
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="13" t="s">
         <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -2441,7 +2539,7 @@
       <c r="G7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="13" t="s">
         <v>42</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -2452,27 +2550,27 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="14" t="n">
         <v>1090</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
       <c r="J8" s="2" t="s">
         <v>49</v>
       </c>
@@ -2615,27 +2713,27 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="14" t="n">
         <v>-600</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
       <c r="J13" s="2" t="s">
         <v>82</v>
       </c>
@@ -2653,7 +2751,7 @@
       <c r="C14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>83</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -2679,13 +2777,13 @@
       <c r="A15" s="1" t="n">
         <v>-550</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="13" t="s">
         <v>91</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -2694,7 +2792,7 @@
       <c r="G15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="13" t="s">
         <v>94</v>
       </c>
       <c r="K15" s="2" t="s">
@@ -2737,27 +2835,27 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="14" t="n">
         <v>-510</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15" t="s">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
       <c r="J17" s="2" t="s">
         <v>107</v>
       </c>
@@ -2775,7 +2873,7 @@
       <c r="C18" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="12" t="s">
         <v>110</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -2804,7 +2902,7 @@
       <c r="C19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="12" t="s">
         <v>115</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -2894,27 +2992,27 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="14" t="n">
         <v>-450</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
       <c r="J22" s="2" t="s">
         <v>137</v>
       </c>
@@ -2958,27 +3056,27 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="14" t="n">
         <v>-400</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
       <c r="J24" s="2" t="s">
         <v>149</v>
       </c>
@@ -2996,7 +3094,7 @@
       <c r="C25" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="12" t="s">
         <v>150</v>
       </c>
       <c r="E25" s="2" t="s">
@@ -3029,7 +3127,7 @@
       <c r="D26" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="18" t="s">
         <v>158</v>
       </c>
       <c r="F26" s="9" t="s">
@@ -3057,7 +3155,7 @@
       <c r="C27" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="12" t="s">
         <v>162</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -3086,7 +3184,7 @@
       <c r="C28" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="12" t="s">
         <v>168</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -3109,27 +3207,27 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="14" t="n">
         <v>-150</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="14"/>
+      <c r="C29" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="2" t="s">
         <v>178</v>
       </c>
@@ -3151,7 +3249,7 @@
       <c r="D30" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="18" t="s">
         <v>181</v>
       </c>
       <c r="F30" s="9" t="s">
@@ -3179,7 +3277,7 @@
       <c r="C31" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="12" t="s">
         <v>185</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -3205,27 +3303,27 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15" t="s">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="2" t="s">
         <v>195</v>
       </c>
@@ -3237,27 +3335,27 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="14" t="n">
         <v>450</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15" t="n">
+      <c r="B33" s="14"/>
+      <c r="C33" s="14" t="n">
         <v>450</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
       <c r="J33" s="2" t="s">
         <v>201</v>
       </c>
@@ -3275,7 +3373,7 @@
       <c r="C34" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="12" t="s">
         <v>202</v>
       </c>
       <c r="E34" s="2" t="s">
@@ -3304,7 +3402,7 @@
       <c r="C35" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>207</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -3336,10 +3434,10 @@
       <c r="C36" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="21" t="s">
         <v>213</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -3348,7 +3446,7 @@
       <c r="G36" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="J36" s="22" t="s">
+      <c r="J36" s="21" t="s">
         <v>216</v>
       </c>
       <c r="K36" s="2" t="s">
@@ -3391,27 +3489,27 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="n">
+      <c r="A38" s="14" t="n">
         <v>750</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15" t="s">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="G38" s="17" t="s">
+      <c r="G38" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
       <c r="J38" s="2" t="s">
         <v>227</v>
       </c>
@@ -3429,7 +3527,7 @@
       <c r="C39" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="12" t="s">
         <v>228</v>
       </c>
       <c r="E39" s="2" t="s">
@@ -3493,7 +3591,7 @@
       <c r="C41" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="12" t="s">
         <v>240</v>
       </c>
       <c r="E41" s="2" t="s">
@@ -3516,27 +3614,27 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15" t="n">
+      <c r="A42" s="14" t="n">
         <v>890</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15" t="s">
+      <c r="B42" s="14"/>
+      <c r="C42" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="G42" s="17" t="s">
+      <c r="G42" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
       <c r="J42" s="2" t="s">
         <v>250</v>
       </c>
@@ -3554,7 +3652,7 @@
       <c r="C43" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="12" t="s">
         <v>252</v>
       </c>
       <c r="E43" s="2" t="s">
@@ -3586,7 +3684,7 @@
       <c r="C44" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="12" t="s">
         <v>259</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -3615,7 +3713,7 @@
       <c r="C45" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="12" t="s">
         <v>264</v>
       </c>
       <c r="E45" s="2" t="s">
@@ -3644,7 +3742,7 @@
       <c r="C46" s="1" t="n">
         <v>1150</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="12" t="s">
         <v>269</v>
       </c>
       <c r="E46" s="2" t="s">
@@ -3680,7 +3778,7 @@
       <c r="D47" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="E47" s="23" t="s">
+      <c r="E47" s="22" t="s">
         <v>276</v>
       </c>
       <c r="F47" s="9" t="s">
@@ -3708,7 +3806,7 @@
       <c r="C48" s="1" t="n">
         <v>1200</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="12" t="s">
         <v>280</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -3737,7 +3835,7 @@
       <c r="C49" s="1" t="n">
         <v>1300</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="12" t="s">
         <v>286</v>
       </c>
       <c r="E49" s="2" t="s">
@@ -3766,10 +3864,10 @@
       <c r="C50" s="1" t="n">
         <v>1650</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="E50" s="23" t="s">
         <v>292</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -3778,7 +3876,7 @@
       <c r="G50" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="J50" s="24" t="s">
+      <c r="J50" s="23" t="s">
         <v>295</v>
       </c>
       <c r="K50" s="2" t="s">
@@ -3788,121 +3886,121 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15" t="n">
-        <v>1680</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15" t="s">
+    <row r="51" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="F51" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="G51" s="17" t="s">
+      <c r="G51" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J51" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="2" t="s">
+      <c r="K51" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="n">
-        <v>1720</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15" t="n">
-        <v>1720</v>
-      </c>
-      <c r="D52" s="16" t="s">
+    <row r="52" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="14" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="D52" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="F52" s="15" t="s">
+      <c r="E52" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="G52" s="17" t="s">
+      <c r="F52" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="24" t="s">
+      <c r="G52" s="16" t="s">
         <v>306</v>
+      </c>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
-        <v>1750</v>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>1750</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="E53" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="14" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D53" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="E53" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="F53" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="J53" s="2" t="s">
+      <c r="G53" s="16" t="s">
         <v>311</v>
+      </c>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="23" t="s">
+        <v>312</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="9" t="n">
-        <v>1760</v>
-      </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="D54" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G54" s="11" t="s">
+      <c r="G54" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
         <v>317</v>
       </c>
@@ -3910,313 +4008,316 @@
         <v>22</v>
       </c>
       <c r="M54" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M55" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15" t="n">
+    <row r="56" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="n">
         <v>1820</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15" t="n">
+      <c r="B56" s="14"/>
+      <c r="C56" s="14" t="n">
         <v>1820</v>
       </c>
-      <c r="D55" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>320</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="H55" s="15"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
-        <v>1830</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D56" s="13" t="s">
+      <c r="D56" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="16" t="s">
         <v>327</v>
       </c>
+      <c r="H56" s="14"/>
+      <c r="I56" s="16"/>
       <c r="J56" s="2" t="s">
         <v>328</v>
       </c>
       <c r="K56" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
+        <v>1830</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="D57" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="E57" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
+    <row r="58" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="n">
         <v>1840</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="K57" s="2" t="s">
+      <c r="C58" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="K58" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="n">
-        <v>1845</v>
-      </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15" t="n">
-        <v>1845</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="E58" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="F58" s="15" t="s">
-        <v>339</v>
-      </c>
-      <c r="G58" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="H58" s="15"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="N58" s="1" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="14" t="n">
+        <v>1845</v>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14" t="n">
+        <v>1845</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="H59" s="14"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N59" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="15" t="n">
+    <row r="60" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="14" t="n">
         <v>1850</v>
       </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15" t="n">
+      <c r="B60" s="14"/>
+      <c r="C60" s="14" t="n">
         <v>1850</v>
       </c>
-      <c r="D59" s="25" t="s">
-        <v>342</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="G59" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="H59" s="15"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="K59" s="2" t="s">
+      <c r="D60" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="H60" s="14"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="K60" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="M60" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="n">
+    <row r="61" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="14" t="n">
         <v>1850</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15" t="n">
+      <c r="B61" s="14"/>
+      <c r="C61" s="14" t="n">
         <v>1850</v>
       </c>
-      <c r="D60" s="16" t="s">
-        <v>347</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="G60" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="H60" s="15"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>1865</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="16" t="s">
         <v>356</v>
       </c>
+      <c r="H61" s="14"/>
+      <c r="I61" s="16"/>
       <c r="J61" s="2" t="s">
         <v>357</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="D62" s="10" t="s">
+    <row r="62" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="D62" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="E62" s="27" t="s">
+      <c r="E62" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="G62" s="11" t="s">
+      <c r="G62" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="2" t="s">
+      <c r="J62" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="K62" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="15" t="n">
-        <v>1878</v>
-      </c>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15" t="n">
-        <v>1878</v>
-      </c>
-      <c r="D63" s="16" t="s">
+      <c r="K62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="XFC62" s="0"/>
+      <c r="XFD62" s="0"/>
+    </row>
+    <row r="63" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="n">
+        <v>1865</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="D63" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="F63" s="15" t="s">
+      <c r="E63" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="F63" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="H63" s="15"/>
-      <c r="I63" s="17"/>
+      <c r="G63" s="2" t="s">
+        <v>367</v>
+      </c>
       <c r="J63" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>368</v>
+        <v>22</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="D64" s="13" t="s">
+    <row r="64" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D64" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E64" s="27" t="s">
         <v>370</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="11" t="s">
         <v>372</v>
       </c>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
       <c r="J64" s="2" t="s">
         <v>373</v>
       </c>
@@ -4224,91 +4325,94 @@
         <v>108</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="D65" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D65" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E65" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="16" t="s">
         <v>377</v>
       </c>
+      <c r="H65" s="14"/>
+      <c r="I65" s="16"/>
       <c r="J65" s="2" t="s">
         <v>378</v>
       </c>
       <c r="K65" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K66" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M65" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
+      <c r="M66" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="n">
         <v>1905</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C67" s="1" t="n">
         <v>1905</v>
       </c>
-      <c r="D66" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="E66" s="22" t="s">
-        <v>380</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="J66" s="22" t="s">
-        <v>383</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
-        <v>1920</v>
-      </c>
-      <c r="C67" s="1" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D67" s="13" t="s">
-        <v>384</v>
+      <c r="D67" s="12" t="s">
+        <v>385</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>108</v>
@@ -4317,17 +4421,17 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
-        <v>1920</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D68" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D68" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="E68" s="21" t="s">
         <v>391</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -4336,305 +4440,351 @@
       <c r="G68" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="J68" s="2" t="s">
+      <c r="J68" s="21" t="s">
         <v>394</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="15" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="n">
+        <v>1911</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="D69" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="F69" s="15" t="s">
+      <c r="F69" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="G69" s="17" t="s">
+      <c r="G69" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="H69" s="15"/>
-      <c r="I69" s="15"/>
       <c r="J69" s="2" t="s">
         <v>400</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>108</v>
+        <v>401</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
-        <v>1940</v>
+        <v>1920</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>1940</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="E70" s="24" t="s">
-        <v>402</v>
+        <v>1920</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>404</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="J70" s="24" t="s">
-        <v>405</v>
+        <v>406</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>407</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>108</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="D71" s="13" t="s">
-        <v>406</v>
+        <v>1920</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>409</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K71" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
+        <v>1921</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="14" t="n">
+        <v>1935</v>
+      </c>
+      <c r="B73" s="14"/>
+      <c r="C73" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="F73" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="H73" s="14"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="K73" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>1964</v>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>1964</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="273.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
-        <v>1860</v>
+        <v>1940</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>1860</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="G74" s="1"/>
-      <c r="J74" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L74" s="1"/>
-      <c r="M74" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1940</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="E74" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J74" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
         <v>1970</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C77" s="1" t="n">
         <v>1970</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="L75" s="1"/>
-      <c r="M75" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>1650</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
-        <v>1921</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>434</v>
+      <c r="D77" s="12" t="s">
+        <v>443</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>435</v>
+        <v>444</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>438</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="L77" s="1"/>
       <c r="M77" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1">
-        <v>1911</v>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1911</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">École de Kyōto</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Ky%C5%8Dto"  title=" Wikipedia"&gt;L’école de Kyōto&lt;/a&gt; désigne le premier grand courant de philosophie moderne né au Japon, autour de Kitarō Nishida et de ses successeurs à l’université impériale de Kyōto. Son point de départ est souvent fixé à 1911, date de la &lt;em&gt;Recherche sur le bien&lt;/em&gt; de Nishida.&lt;/p&gt; &lt;p&gt;Ses penseurs, formés à la philosophie allemande, de Kant et Hegel à Husserl et Heidegger, veulent exprimer dans le langage de la philosophie occidentale l’expérience spirituelle de l’Asie, en particulier celle du bouddhisme zen et de la Terre pure. Au centre de leur réflexion se trouve la notion de « néant absolu » : non pas un simple manque, mais le fond ouvert d’où tout surgit, que Nishida pense comme le « lieu » de toute réalité.&lt;/p&gt; &lt;p&gt;Tanabe Hajime, Nishitani Keiji, puis Ueda Shizuteru développèrent cette pensée, tandis que Watsuji Tetsurō et Kuki Shūzō, proches du groupe, l’ouvrirent à l’éthique et à l’esthétique. Plusieurs de ses membres furent compromis dans la justification idéologique de la guerre du Pacifique, ce qui a longtemps pesé sur sa réception.&lt;/p&gt; &lt;p&gt;Depuis les années 1980, l’école de Kyōto est étudiée dans le monde entier comme le lieu d’un dialogue majeur entre la philosophie occidentale et les traditions spirituelles d’Asie.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premier grand courant de philosophie moderne né au Japon, autour de Nishida, Tanabe et Nishitani.</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
-        </is>
-      </c>
-      <c r="L78" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kitaro NISHIDA;Hajime TANABE;Keiji NISHITANI;Tetsurō WATSUJI;Shūzō KUKI</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-    </row>
+    <row r="78" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="0"/>
+      <c r="B79" s="0"/>
+      <c r="C79" s="0"/>
+      <c r="D79" s="0"/>
+      <c r="E79" s="0"/>
+      <c r="F79" s="0"/>
+      <c r="G79" s="0"/>
+      <c r="H79" s="0"/>
+      <c r="I79" s="0"/>
+      <c r="J79" s="0"/>
+      <c r="K79" s="0"/>
+      <c r="L79" s="0"/>
+      <c r="M79" s="0"/>
+      <c r="XFC79" s="0"/>
+      <c r="XFD79" s="0"/>
+    </row>
+    <row r="80" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="0"/>
+      <c r="B80" s="0"/>
+      <c r="C80" s="0"/>
+      <c r="D80" s="0"/>
+      <c r="E80" s="0"/>
+      <c r="F80" s="0"/>
+      <c r="G80" s="0"/>
+      <c r="H80" s="0"/>
+      <c r="I80" s="0"/>
+      <c r="J80" s="0"/>
+      <c r="K80" s="0"/>
+      <c r="L80" s="0"/>
+      <c r="M80" s="0"/>
+      <c r="XFC80" s="0"/>
+      <c r="XFD80" s="0"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -4657,13 +4807,13 @@
     <hyperlink ref="E40" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
     <hyperlink ref="E44" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>
     <hyperlink ref="E48" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bushido&quot; title=&quot;Wikipedia&quot;&gt;Le Bushido&lt;/a&gt; (« Voie du Guerrier ») est le code éthique de la classe des samouraïs du Japon féodal, progressivement formalisé entre l'époque Kamakura (XIIe siècle) et la période Edo. Il synthétise en une philosophie de vie cohérente des valeurs empruntées au bouddhisme zen, au shintoïsme et au confucianisme.&lt;/p&gt;&lt;p&gt;Les sept vertus cardinales du Bushido sont : la rectitude (gi), le courage (yu), la bienveillance (jin), le respect (rei), la sincérité (makoto), l'honneur (meiyo) et la loyauté (chugi). À celles-ci s'ajoute la maîtrise de soi, la frugalité et l'acceptation stoïque de la mort — le samouraï doit &quot;vivre comme s'il était déjà mort&quot; pour agir sans attachement ni peur.&lt;/p&gt;&lt;p&gt;La pratique de seppuku (suicide rituel) illustre à l'extrême cette philosophie : la mort honorable vaut mieux qu'une vie dans la honte. Cette acceptation de la mort comme acte ultime de liberté et de dignité a fasciné les philosophes — de Nitobe Inazo, qui codafia le Bushido en 1900, à ceux qui y voient une forme de stoïcisme oriental.&lt;/p&gt;&lt;p&gt;Après la fin de l'ère des samouraïs au XIXe siècle, le Bushido survit dans les arts martiaux japonais (kendo, judo, aïkido), dans la culture d'entreprise japonaise et dans une vision de l'excellence par la maîtrise de soi qui continue d'inspirer bien au-delà du Japon.&lt;/p&gt;"/>
-    <hyperlink ref="E52" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fondamentalisme&quot;   title=&quot; Wikipedia&quot;&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient , principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les religions ; le fondamentalisme chrétien par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E58" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E62" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E63" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E64" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
-    <hyperlink ref="E69" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E70" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E53" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fondamentalisme&quot;   title=&quot; Wikipedia&quot;&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient , principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les religions ; le fondamentalisme chrétien par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E59" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E64" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E65" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E66" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
+    <hyperlink ref="E73" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E74" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4685,192 +4835,192 @@
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="28" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="28" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="29" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="29" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="29" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="29" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="29" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="29" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="29" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="C14" s="30" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="29" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="C17" s="30" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="29" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="C18" s="30" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="29" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="28" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C22" s="30" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="C23" s="30" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="28" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="29" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="29" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="29" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="28" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="29" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="29" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="506">
   <si>
     <t xml:space="preserve">FRISE DES COURANTS DE PENSÉE ORIENTALE — Données source</t>
   </si>
@@ -1161,7 +1161,7 @@
     <t xml:space="preserve">Brahmoïsme</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marxisme"  title=" Wikipedia"&gt; Le Brahmoïsme &lt;/a&gt; est un mouvement religieux et philosophique hindou réformiste qui est né au milieu du XIXe siècle lors de la Renaissance bengalie, fondé en 1828 à Calcutta par Raja Ram Mohan Roy. Ce mouvement considère Dieu comme un principe divin unique, infini et illimité, et ses adeptes, appelés Brahmos, se déclarent « ni hindous, ni musulmans, ni chrétiens », mais adhérents à une nouvelle religion de l'Inde.  &lt;/p&gt; &lt;p&gt; La philosophie brahmo repose sur le monothéisme absolu et le rejet total des traditions hindoues conventionnelles : elle ne reconnaît pas l'autorité des Vedas, ne croit pas aux avatars (incarnations divines), rejette le karma et le samsara, et abandonne le culte des images et les rituels traditionnels. Debendranath Tagore a codifié cette doctrine en 1848 avec le Brahmo Dharma, faisant de la raison et de l'intuition vertueuse les fondements de la foi plutôt que l'autorité scripturaire. &lt;/p&gt; &lt;p&gt; Au cœur du Brahmoïsme se trouve le concept de Brahman, la réalité ultime impersonnelle et transcendante dont émane toute existence, immanente et présente en tout, du plus petit plant au plus grand chêne. Cette philosophie enseigne que l'âme individuelle (Atman) est identique au Brahman universel, et que Dieu est à la fois immanent dans l'univers et transcendant au-delà de lui, inaccessible à la connaissance directe mais accessible par la méditation. &lt;/p&gt; &lt;p&gt; Au cœur du Brahmoïsme se trouve le concept de Brahman, la réalité ultime impersonnelle et transcendante dont émane toute existence, immanente et présente en tout, du plus petit plant au plus grand chêne. Cette philosophie enseigne que l'âme individuelle (Atman) est identique au Brahman universel, et que Dieu est à la fois immanent dans l'univers et transcendant au-delà de lui, inaccessible à la connaissance directe mais accessible par la méditation. &lt;/p&gt; &lt;p&gt; L'éthique brahmo est fondée sur la droiture comme seul mode de vie, la vérité, la connaissance, le libre arbitre et l'égalité fondamentale entre tous les êtres humains, avec un rejet radical du système des castes. Le mouvement a joué un rôle considérable dans les réformes sociales : il a lutté contre le sati (veuves brûlées sur le bûcher), encouragé l'éducation des femmes, soutenu la tempérance et promu l'indépendance nationale indienne, devenant ainsi un moteur de la modernisation de l'Inde. &lt;/p&gt; 
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Brahmo%C3%AFsme"  title=" Wikipedia"&gt; Le Brahmoïsme &lt;/a&gt; est un mouvement religieux et philosophique hindou réformiste qui est né au milieu du XIXe siècle lors de la Renaissance bengalie, fondé en 1828 à Calcutta par Raja Ram Mohan Roy. Ce mouvement considère Dieu comme un principe divin unique, infini et illimité, et ses adeptes, appelés Brahmos, se déclarent « ni hindous, ni musulmans, ni chrétiens », mais adhérents à une nouvelle religion de l'Inde.  &lt;/p&gt; &lt;p&gt; La philosophie brahmo repose sur le monothéisme absolu et le rejet total des traditions hindoues conventionnelles : elle ne reconnaît pas l'autorité des Vedas, ne croit pas aux avatars (incarnations divines), rejette le karma et le samsara, et abandonne le culte des images et les rituels traditionnels. Debendranath Tagore a codifié cette doctrine en 1848 avec le Brahmo Dharma, faisant de la raison et de l'intuition vertueuse les fondements de la foi plutôt que l'autorité scripturaire. &lt;/p&gt; &lt;p&gt; Au cœur du Brahmoïsme se trouve le concept de Brahman, la réalité ultime impersonnelle et transcendante dont émane toute existence, immanente et présente en tout, du plus petit plant au plus grand chêne. Cette philosophie enseigne que l'âme individuelle (Atman) est identique au Brahman universel, et que Dieu est à la fois immanent dans l'univers et transcendant au-delà de lui, inaccessible à la connaissance directe mais accessible par la méditation. &lt;/p&gt; &lt;p&gt; Au cœur du Brahmoïsme se trouve le concept de Brahman, la réalité ultime impersonnelle et transcendante dont émane toute existence, immanente et présente en tout, du plus petit plant au plus grand chêne. Cette philosophie enseigne que l'âme individuelle (Atman) est identique au Brahman universel, et que Dieu est à la fois immanent dans l'univers et transcendant au-delà de lui, inaccessible à la connaissance directe mais accessible par la méditation. &lt;/p&gt; &lt;p&gt; L'éthique brahmo est fondée sur la droiture comme seul mode de vie, la vérité, la connaissance, le libre arbitre et l'égalité fondamentale entre tous les êtres humains, avec un rejet radical du système des castes. Le mouvement a joué un rôle considérable dans les réformes sociales : il a lutté contre le sati (veuves brûlées sur le bûcher), encouragé l'éducation des femmes, soutenu la tempérance et promu l'indépendance nationale indienne, devenant ainsi un moteur de la modernisation de l'Inde. &lt;/p&gt; 
 </t>
   </si>
   <si>
@@ -1347,6 +1347,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">&lt;audio controls title="Philosophie japonaise: l’école de Kyôto par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.11.2013-ITEMA_20549374-2013C12410E0320-NET_FC_EE7092B3-7D80-40AA-947D-AFAD338FBA01-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
     </r>
@@ -1520,6 +1521,24 @@
   </si>
   <si>
     <t xml:space="preserve">philosophie andine du bien-vivre en harmonie avec la nature, intégrée aux constitutions équatorienne et bolivienne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sikhisme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sikhisme" title=" Wikipedia"&gt;Le sikhisme&lt;/a&gt; est une religion et une sagesse nées au Pendjab, au nord de l’Inde, à la fin du XVe siècle, dans l’enseignement de Guru Nanak ; le mot « sikh » signifie « disciple ». Dans une région où se côtoient l’hindouisme, l’islam et les mouvements mystiques de la &lt;em&gt;bhakti&lt;/em&gt; et du soufisme, il affirme qu’il n’y a qu’un seul Dieu, sans forme ni incarnation, présent en toute chose, que l’on rejoint par l’amour, la méditation de son Nom et une vie juste, plutôt que par les rites, les idoles ou l’ascèse.&lt;/p&gt; &lt;p&gt;Dix gurus se succèdent de Nanak à Gobind Singh, qui fonde en 1699 le &lt;em&gt;Khalsa&lt;/em&gt;, la communauté des initiés, reconnaissables à cinq signes dont les cheveux jamais coupés, et décide qu’après lui le seul guru sera le livre saint, le &lt;a href="https://fr.wikipedia.org/wiki/Guru_Granth_Sahib" title=" Wikipedia"&gt;&lt;em&gt;Guru Granth Sahib&lt;/em&gt;&lt;/a&gt;. Celui-ci réunit les hymnes des gurus, mais aussi ceux de saints hindous et musulmans comme Kabir : la vérité n’appartient à aucune religion particulière. Le Temple d’or d’Amritsar, ouvert sur quatre côtés, symbolise cet accueil de tous.&lt;/p&gt; &lt;p&gt;Sa philosophie refuse les castes et affirme l’égalité de tous les êtres humains, hommes et femmes. Elle tient la vie juste en trois préceptes : se souvenir de Dieu, gagner honnêtement sa vie, partager avec les autres. La cuisine commune, le &lt;a href="https://fr.wikipedia.org/wiki/Langar" title=" Wikipedia"&gt;&lt;em&gt;langar&lt;/em&gt;&lt;/a&gt;, où tous mangent assis au même rang, en est l’expression concrète. Le sikhisme ne prône pas la fuite du monde mais la sainteté dans la vie ordinaire, au travail et en famille, unie au service désintéressé des autres. Il compte aujourd’hui près de trente millions de fidèles.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">religion et sagesse du Pendjab fondée par Guru Nanak : un Dieu unique, l’égalité de tous et la sainteté dans la vie ordinaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GURU NANAK</t>
   </si>
   <si>
     <t xml:space="preserve">📖 MODE D'EMPLOI</t>
@@ -1667,7 +1686,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1818,12 +1837,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FFD4A843"/>
@@ -1961,7 +1974,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2074,15 +2087,19 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2338,7 +2355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048576"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -4257,15 +4274,13 @@
       <c r="J62" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="K62" s="2" t="s">
         <v>22</v>
       </c>
       <c r="L62" s="1"/>
       <c r="M62" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="XFC62" s="0"/>
-      <c r="XFD62" s="0"/>
     </row>
     <row r="63" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
@@ -4750,41 +4765,40 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0"/>
-      <c r="B79" s="0"/>
-      <c r="C79" s="0"/>
-      <c r="D79" s="0"/>
-      <c r="E79" s="0"/>
-      <c r="F79" s="0"/>
-      <c r="G79" s="0"/>
-      <c r="H79" s="0"/>
-      <c r="I79" s="0"/>
-      <c r="J79" s="0"/>
-      <c r="K79" s="0"/>
-      <c r="L79" s="0"/>
-      <c r="M79" s="0"/>
-      <c r="XFC79" s="0"/>
-      <c r="XFD79" s="0"/>
+    <row r="79" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D79" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="J79" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="M79" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0"/>
-      <c r="B80" s="0"/>
-      <c r="C80" s="0"/>
-      <c r="D80" s="0"/>
-      <c r="E80" s="0"/>
-      <c r="F80" s="0"/>
-      <c r="G80" s="0"/>
-      <c r="H80" s="0"/>
-      <c r="I80" s="0"/>
-      <c r="J80" s="0"/>
-      <c r="K80" s="0"/>
-      <c r="L80" s="0"/>
-      <c r="M80" s="0"/>
-      <c r="XFC80" s="0"/>
-      <c r="XFD80" s="0"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -4834,193 +4848,193 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="28" t="s">
-        <v>454</v>
+      <c r="B3" s="29" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
-        <v>455</v>
+      <c r="B5" s="29" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="s">
-        <v>456</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>457</v>
+      <c r="B6" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="29" t="s">
-        <v>458</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>459</v>
+      <c r="B7" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="s">
-        <v>460</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>461</v>
+      <c r="B8" s="30" t="s">
+        <v>466</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="s">
-        <v>462</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>463</v>
+      <c r="B9" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="29" t="s">
-        <v>464</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>465</v>
+      <c r="B10" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="29" t="s">
-        <v>466</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>467</v>
+      <c r="B11" s="30" t="s">
+        <v>472</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="29" t="s">
-        <v>468</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>469</v>
+      <c r="B12" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="29" t="s">
-        <v>470</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>471</v>
+      <c r="B13" s="30" t="s">
+        <v>476</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="29" t="s">
-        <v>472</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>473</v>
+      <c r="B14" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>474</v>
+      <c r="B16" s="29" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>476</v>
+      <c r="B17" s="30" t="s">
+        <v>481</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="29" t="s">
-        <v>477</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>478</v>
+      <c r="B18" s="30" t="s">
+        <v>483</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>480</v>
+      <c r="B19" s="30" t="s">
+        <v>485</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="28" t="s">
-        <v>481</v>
+      <c r="B21" s="29" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>483</v>
+      <c r="B22" s="30" t="s">
+        <v>488</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="29" t="s">
-        <v>484</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>485</v>
+      <c r="B23" s="30" t="s">
+        <v>490</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
-        <v>486</v>
+      <c r="B25" s="29" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="29" t="s">
-        <v>487</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>488</v>
+      <c r="B26" s="30" t="s">
+        <v>493</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="29" t="s">
-        <v>489</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>490</v>
+      <c r="B27" s="30" t="s">
+        <v>495</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="29" t="s">
-        <v>491</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>492</v>
+      <c r="B28" s="30" t="s">
+        <v>497</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="74.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="29" t="s">
-        <v>493</v>
-      </c>
-      <c r="C29" s="30" t="s">
-        <v>494</v>
+      <c r="B29" s="30" t="s">
+        <v>499</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="28" t="s">
-        <v>495</v>
+      <c r="B31" s="29" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="29" t="s">
-        <v>496</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>497</v>
+      <c r="B32" s="30" t="s">
+        <v>502</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="29" t="s">
-        <v>498</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>499</v>
+      <c r="B33" s="30" t="s">
+        <v>504</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2355,7 +2355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -4793,11 +4793,931 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D80" s="1"/>
+      <c r="A80" s="1">
+        <v>150</v>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Madhyamaka</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Madhyamaka" title=" Wikipedia"&gt;Le Madhyamaka&lt;/a&gt;, ou « école de la Voie du milieu », est l’une des deux grandes écoles philosophiques du bouddhisme mahāyāna. Il naît en Inde vers le IIe siècle avec Nāgārjuna, dont les &lt;a href="https://fr.wikipedia.org/wiki/Mulamadhyamakakarika" title=" Wikipedia"&gt;&lt;em&gt;Stances de la Voie du milieu&lt;/em&gt;&lt;/a&gt; sont le texte fondateur, et son disciple Āryadeva. Le « milieu » qu’il cherche se tient entre deux extrêmes : croire que les choses existent en elles-mêmes, ou croire qu’elles n’existent pas du tout.&lt;/p&gt; &lt;p&gt;Sa thèse centrale est la &lt;a href="https://fr.wikipedia.org/wiki/%C5%9A%C5%ABnyat%C4%81" title=" Wikipedia"&gt;vacuité&lt;/a&gt; (&lt;em&gt;śūnyatā&lt;/em&gt;) : aucune chose n’a d’existence propre, car toute chose dépend d’autre chose, de ses causes, de ses parties et de l’esprit qui la nomme. La vacuité n’est donc pas le néant, mais l’autre nom de la « production conditionnée » enseignée par le Bouddha. Nāgārjuna procède par réfutation : il montre que toute thèse sur l’être, le mouvement, le temps ou la causalité aboutit à des contradictions dès qu’on la tient pour absolue. Il distingue la vérité conventionnelle, celle du langage et de la vie ordinaire, de la vérité ultime, qui échappe aux concepts ; et la vacuité est elle-même vide : ce n’est pas une nouvelle doctrine à laquelle s’accrocher.&lt;/p&gt; &lt;p&gt;L’école se divise ensuite entre ceux qui admettent des raisonnements autonomes et les « Prāsaṅgika » de Candrakīrti, qui se contentent de montrer l’absurdité des thèses adverses. Śāntideva en tire une éthique de la compassion. Transmis au Tibet par Atiśa et systématisé par Tsongkhapa, le Madhyamaka reste la philosophie de référence du bouddhisme tibétain. On l’a souvent rapproché, au XXe siècle, de la critique du langage chez Wittgenstein.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="G80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="L80" s="1"/>
-      <c r="M80" s="1"/>
+      <c r="J80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école bouddhiste de la Voie du milieu fondée par Nāgārjuna : rien n’existe en soi, tout est vide parce qu’interdépendant.</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Épistémologie</t>
+        </is>
+      </c>
+      <c r="L80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAGARJUNA;SHANTIDEVA;Je TSONGKHAPA</t>
+        </is>
+      </c>
+      <c r="M80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1">
+        <v>350</v>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">350</t>
+        </is>
+      </c>
+      <c r="D81" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yogācāra</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chittamatra" title=" Wikipedia"&gt;Le Yogācāra&lt;/a&gt;, « pratique du yoga », appelé aussi Cittamātra, « esprit seul », est avec le Madhyamaka l’une des deux grandes écoles philosophiques du bouddhisme mahāyāna. Il se forme en Inde au IVe siècle autour de deux frères, Asaṅga et Vasubandhu, à partir de l’expérience des méditants : ce que l’on observe en méditation montre combien le monde vécu est façonné par l’esprit. On doit à Vasubandhu deux courts traités, les &lt;em&gt;Vingt stances&lt;/em&gt; et les &lt;em&gt;Trente stances&lt;/em&gt;, qui résument la doctrine.&lt;/p&gt; &lt;p&gt;Sa thèse est que nous ne connaissons jamais que des représentations : les objets que nous croyons extérieurs sont des apparitions de la conscience, comme dans un rêve. Pour l’expliquer, il ajoute aux six consciences reconnues par le bouddhisme une conscience souillée, qui produit l’illusion d’un moi, et surtout une &lt;a href="https://fr.wikipedia.org/wiki/%C4%80layavij%C3%B1%C4%81na" title=" Wikipedia"&gt;conscience-réceptacle&lt;/a&gt; (&lt;em&gt;ālayavijñāna&lt;/em&gt;), sorte d’inconscient où les actes passés déposent des traces, comme des graines qui germeront plus tard. Il décrit aussi « trois natures » des choses : imaginaire, dépendante et parfaitement accomplie. L’éveil consiste à transformer ce fond de la conscience, jusqu’à ce que cesse le partage entre un sujet qui saisit et un objet saisi.&lt;/p&gt; &lt;p&gt;Ses logiciens, Dignāga puis Dharmakīrti, fondent la grande épistémologie bouddhique. Le pèlerin chinois &lt;a href="https://fr.wikipedia.org/wiki/Xuanzang" title=" Wikipedia"&gt;Xuanzang&lt;/a&gt; rapporte ses textes d’Inde au VIIe siècle et fonde en Chine l’école de la « conscience seule ». Le Yogācāra a nourri le zen, le bouddhisme tibétain et, aujourd’hui, le dialogue avec la phénoménologie et les sciences cognitives.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école bouddhiste de « l’esprit seul » : le monde que nous percevons est une construction de la conscience.</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie de l'esprit;Métaphysique;Épistémologie</t>
+        </is>
+      </c>
+      <c r="L81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASANGA;VASUBANDHU;XUANZANG</t>
+        </is>
+      </c>
+      <c r="M81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1">
+        <v>402</v>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">402</t>
+        </is>
+      </c>
+      <c r="D82" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme de la Terre pure</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le bouddhisme de la &lt;a href="https://fr.wikipedia.org/wiki/Terre_pure" title=" Wikipedia"&gt;Terre pure&lt;/a&gt; est le courant du bouddhisme mahāyāna centré sur la dévotion au bouddha Amitābha (Amida en japonais) qui, selon les sūtras, a fait le vœu d’accueillir dans sa « Terre pure », un paradis situé à l’Occident, tous ceux qui l’invoquent avec foi. Né en Chine, il remonte à Huiyuan, qui réunit en 402 au mont Lu une communauté vouée à Amitābha, puis à &lt;a href="https://fr.wikipedia.org/wiki/Tanluan" title=" Wikipedia"&gt;Tanluan&lt;/a&gt; et à Shandao, qui en font une école.&lt;/p&gt; &lt;p&gt;Sa philosophie part d’un constat : en cette époque de « déclin de la Loi », les êtres humains ne peuvent plus atteindre l’éveil par leurs propres forces, par la méditation ou l’ascèse. Il faut s’en remettre à la « force de l’autre », la compassion d’Amitābha. La pratique principale devient la récitation de son nom, le &lt;em&gt;nembutsu&lt;/em&gt; : « Namu Amida Butsu ». Au Japon, Hōnen fonde en 1175 l’école &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_sh%C5%AB" title=" Wikipedia"&gt;Jōdo shū&lt;/a&gt; et affirme que cette seule récitation suffit au salut, ce qui ouvre le bouddhisme aux gens simples, aux paysans et aux femmes. Son disciple Shinran va plus loin avec le &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_shinsh%C5%AB" title=" Wikipedia"&gt;Jōdo shinshū&lt;/a&gt; : le salut est entièrement un don reçu dans la foi, et c’est le « méchant » conscient de ses fautes, plus encore que le juste, que le Bouddha veut sauver. Shinran se marie, quitte la vie monastique et vit parmi le peuple.&lt;/p&gt; &lt;p&gt;Devenue l’une des formes du bouddhisme les plus pratiquées d’Asie de l’Est, la Terre pure évoque la doctrine chrétienne de la grâce, rapprochement qui a fasciné bien des théologiens occidentaux. Elle compte aujourd’hui des dizaines de millions de fidèles au Japon, en Chine, en Corée et au Viêt Nam.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouddhisme de la foi en Amitābha : le salut par la récitation de son nom et la « force de l’autre ».</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HŌNEN;SHINRAN</t>
+        </is>
+      </c>
+      <c r="M82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N82"/>
+    </row>
+    <row r="83" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1">
+        <v>575</v>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">575</t>
+        </is>
+      </c>
+      <c r="D83" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tiantai</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tiantai" title=" Wikipedia"&gt;Le Tiantai&lt;/a&gt; est la première grande école du bouddhisme née en Chine plutôt qu’importée d’Inde. Elle tire son nom du mont Tiantai, dans le Zhejiang, où le moine Zhiyi (538-597) s’installe en 575 et élabore sa doctrine. Face à la masse des sūtras traduits en chinois, souvent contradictoires, Zhiyi les classe en périodes et en méthodes d’enseignement : le Bouddha aurait adapté sa parole à ses auditeurs, et le &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_du_Lotus" title=" Wikipedia"&gt;&lt;em&gt;Sūtra du Lotus&lt;/em&gt;&lt;/a&gt; en serait le sommet, qui révèle que tous les êtres peuvent devenir bouddhas.&lt;/p&gt; &lt;p&gt;Sa philosophie repose sur la doctrine des « trois vérités » : toute chose est vide, car sans existence propre ; elle existe pourtant provisoirement, comme apparence ; et elle est le « milieu », qui unit les deux sans les séparer. Zhiyi en tire l’idée qu’« un instant de pensée contient trois mille mondes » : chaque moment de conscience renferme la totalité des états possibles de l’existence, des enfers jusqu’à l’éveil. Le salut n’est donc pas ailleurs : il se découvre au cœur même du monde ordinaire. Zhiyi va jusqu’à soutenir que la nature de bouddha contient aussi le mal, ce qui fait l’originalité de l’école. Il unit étroitement l’étude des textes et la méditation, qu’il expose dans de grands traités sur « l’arrêt et la contemplation ».&lt;/p&gt; &lt;p&gt;Introduite au Japon en 805 par Saichō sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Tendai" title=" Wikipedia"&gt;Tendai&lt;/a&gt;, l’école fait du monastère du mont Hiei le grand centre du bouddhisme japonais. Elle y forme la plupart des fondateurs des écoles ultérieures, dont Hōnen, Shinran, Dōgen et Nichiren, qui en reprend la dévotion au Lotus.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école bouddhiste chinoise fondée par Zhiyi sur le Sūtra du Lotus : trois vérités et trois mille mondes dans un instant de pensée.</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
+        </is>
+      </c>
+      <c r="L83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZHIYI;SAICHŌ</t>
+        </is>
+      </c>
+      <c r="M83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N83"/>
+    </row>
+    <row r="84" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1">
+        <v>600</v>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
+        </is>
+      </c>
+      <c r="D84" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huayan</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Huayan" title=" Wikipedia"&gt;Le Huayan&lt;/a&gt;, ou « école de l’Ornementation fleurie », est une école du bouddhisme chinois fondée sur l’&lt;a href="https://fr.wikipedia.org/wiki/Avata%E1%B9%83saka_s%C5%ABtra" title=" Wikipedia"&gt;&lt;em&gt;Avataṃsaka sūtra&lt;/em&gt;&lt;/a&gt;, immense texte qui décrit l’univers tel que le voit un bouddha éveillé. Elle se forme aux VIe et VIIe siècles autour de &lt;a href="https://fr.wikipedia.org/wiki/Dushun" title=" Wikipedia"&gt;Dushun&lt;/a&gt;, son premier patriarche, puis de Zhiyan, et trouve son grand systématicien en Fazang (643-712), qui l’expose à la cour de l’impératrice Wu Zetian.&lt;/p&gt; &lt;p&gt;Sa philosophie est celle de l’interdépendance totale : chaque chose contient toutes les autres et se trouve contenue en elles, sans que leurs différences soient abolies. Pour le faire comprendre à l’impératrice, Fazang prend l’image d’un lion d’or : l’or est la nature unique et vide, le lion la forme qu’elle prend, et chaque poil du lion contient le lion tout entier. Il reprend aussi celle du filet d’Indra, filet céleste dont chaque nœud porte une perle qui reflète toutes les autres perles, à l’infini. Le Huayan distingue quatre plans de réalité : celui des phénomènes, celui du principe, celui de leur non-obstruction mutuelle, et enfin celui de la non-obstruction de tous les phénomènes entre eux, qui est la vision de l’éveil.&lt;/p&gt; &lt;p&gt;En Chine, &lt;a href="https://fr.wikipedia.org/wiki/Zongmi" title=" Wikipedia"&gt;Zongmi&lt;/a&gt; (780-841) le concilie avec le chan. Ŭisang l’apporte en Corée, où il devient l’école Hwaeom, que Chinul unira plus tard à la méditation seon ; au Japon, il prend le nom de &lt;a href="https://fr.wikipedia.org/wiki/Kegon" title=" Wikipedia"&gt;Kegon&lt;/a&gt; et c’est à lui que se rattache le grand Bouddha de Nara. Le Huayan a profondément marqué le zen et le néoconfucianisme. On rapproche parfois aujourd’hui sa vision d’un monde entièrement relié de la pensée écologique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école bouddhiste chinoise de l’interdépendance totale, où chaque chose contient toutes les autres.</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAZANG;UISANG</t>
+        </is>
+      </c>
+      <c r="M84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N84"/>
+    </row>
+    <row r="85" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1">
+        <v>600</v>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">600</t>
+        </is>
+      </c>
+      <c r="D85" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bhakti</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bhakti" title=" Wikipedia"&gt;La bhakti&lt;/a&gt;, la « dévotion » ou « l’amour de Dieu », est une voie spirituelle de l’hindouisme qui place l’amour personnel d’une divinité au-dessus des rites, des sacrifices et du savoir. Annoncée dans la &lt;em&gt;Bhagavad-Gītā&lt;/em&gt;, où Krishna enseigne que l’abandon aimant à Dieu est le plus sûr chemin vers la délivrance, elle devient un grand mouvement dans l’Inde du Sud entre le VIe et le IXe siècle, avec les poètes tamouls : les &lt;a href="https://fr.wikipedia.org/wiki/Alvar" title=" Wikipedia"&gt;Alvars&lt;/a&gt;, dévots de Vishnou, et les &lt;a href="https://fr.wikipedia.org/wiki/Nayanar" title=" Wikipedia"&gt;Nayanars&lt;/a&gt;, dévots de Shiva.&lt;/p&gt; &lt;p&gt;Ces saints chantent leur dieu dans la langue du peuple et non en sanskrit, et beaucoup viennent de basses castes : la bhakti affirme que l’amour de Dieu est ouvert à tous, sans distinction de naissance ni de sexe. Elle reçoit une base philosophique avec Rāmānuja, au XIe siècle, qui défend contre Shankara la réalité de l’âme et du monde, distincts de Dieu tout en dépendant de lui ; Madhva va plus loin dans le dualisme. L’âme ne se fond pas dans l’absolu : elle demeure, pour aimer. Du XIIIe au XVIIe siècle, la bhakti gagne l’Inde du Nord : Kabir, tisserand de Bénarès, unit hindous et musulmans dans le culte d’un Dieu sans forme ; la princesse Mīrābāī chante Krishna en bravant les conventions ; Chaitanya, au Bengale, fait du chant et de la danse une prière extatique ; &lt;a href="https://fr.wikipedia.org/wiki/Tuls%C3%AEd%C3%A2s" title=" Wikipedia"&gt;Tulsîdâs&lt;/a&gt; écrit le &lt;em&gt;Ramcharitmanas&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Mouvement de réforme autant que de piété, la bhakti a façonné l’hindouisme populaire, inspiré le sikhisme et nourri, jusqu’à Gandhi, l’idée que la religion se vit d’abord dans le cœur.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voie hindoue de la dévotion amoureuse à Dieu, ouverte à tous sans distinction de caste ni de sexe.</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
+        </is>
+      </c>
+      <c r="L85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMANUJA;KABIR;MIRABAI</t>
+        </is>
+      </c>
+      <c r="M85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N85"/>
+    </row>
+    <row r="86" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1">
+        <v>850</v>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850</t>
+        </is>
+      </c>
+      <c r="D86" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shivaïsme du Cachemire</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shiva%C3%AFsme_du_Cachemire" title=" Wikipedia"&gt;Le shivaïsme du Cachemire&lt;/a&gt; est une école philosophique et mystique hindoue qui s’épanouit dans la vallée du Cachemire entre le IXe et le XIe siècle. Il naît, selon la tradition, des &lt;em&gt;Śiva Sūtra&lt;/em&gt; que &lt;a href="https://fr.wikipedia.org/wiki/Vasugupta" title=" Wikipedia"&gt;Vasugupta&lt;/a&gt; aurait reçus en rêve. À la différence du shivaïsme dualiste du Sud, il est résolument non dualiste : il n’existe qu’une seule réalité, Shiva, conscience absolue, libre et lumineuse, dont l’univers entier est la manifestation. Il appartient au monde des tantras, qui valorise le corps, l’énergie et la vie dans le monde plutôt que le renoncement.&lt;/p&gt; &lt;p&gt;Là où l’Advaita Védanta de Shankara voit dans le monde une illusion, le shivaïsme du Cachemire y voit le jeu bien réel de la liberté divine. La conscience n’est pas seulement une lumière immobile ; elle est aussi &lt;a href="https://fr.wikipedia.org/wiki/Spanda" title=" Wikipedia"&gt;&lt;em&gt;spanda&lt;/em&gt;&lt;/a&gt;, « vibration », énergie créatrice qui se déploie sous la forme des choses. Utpaladeva fonde l’école de la « Reconnaissance » (&lt;em&gt;Pratyabhijñā&lt;/em&gt;) : l’être humain n’a pas à devenir Shiva, il l’est déjà, et la libération consiste à le reconnaître, comme on reconnaît soudain un ami qu’on avait sous les yeux. Le grand penseur de l’école, Abhinavagupta, en fait la synthèse dans son immense &lt;em&gt;Tantrāloka&lt;/em&gt;, « Lumière sur les tantras ». Il pense aussi l’art : l’émotion esthétique (&lt;em&gt;rasa&lt;/em&gt;) éprouvée au théâtre ou devant un poème est un avant-goût de la joie de la conscience libérée.&lt;/p&gt; &lt;p&gt;Presque oublié après le XIIe siècle, il a été redécouvert au XXe siècle, notamment grâce à l’indianiste &lt;a href="https://fr.wikipedia.org/wiki/Lilian_Silburn" title=" Wikipedia"&gt;Lilian Silburn&lt;/a&gt; en France et au maître cachemirien Swami Lakshman Joo.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">non-dualisme hindou pour qui le monde est le libre jeu de la conscience divine, Shiva, que l’être humain doit reconnaître en lui.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABHINAVAGUPTA;UTPALADEVA</t>
+        </is>
+      </c>
+      <c r="M86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N86"/>
+    </row>
+    <row r="87" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1">
+        <v>1890</v>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1890</t>
+        </is>
+      </c>
+      <c r="D87" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néo-védanta</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9o-v%C3%A9danta" title=" Wikipedia"&gt;néo-védanta&lt;/a&gt; la forme moderne du Védanta qui se développe en Inde à partir du XIXe siècle, en anglais plutôt qu’en sanskrit, au contact de l’Occident et de la domination britannique. Elle renouvelle la philosophie non dualiste de Shankara pour en faire une réponse aux critiques des missionnaires et un fondement de la fierté indienne.&lt;/p&gt; &lt;p&gt;Son point de départ est le mystique bengali &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A2makrishna" title=" Wikipedia"&gt;Râmakrishna&lt;/a&gt; (1836-1886), qui affirme, après avoir pratiqué plusieurs religions, que toutes mènent au même but. Son disciple Vivekananda porte ce message au &lt;a href="https://fr.wikipedia.org/wiki/Parlement_des_religions" title=" Wikipedia"&gt;Parlement des religions&lt;/a&gt; de Chicago, en 1893 : le Védanta y devient une religion universelle et rationnelle, compatible avec la science, qui reconnaît la divinité présente en chaque être humain. Il en découle une éthique de l’action : servir les pauvres, c’est servir Dieu ; Vivekananda fonde à cette fin la Mission Ramakrishna, vouée à l’enseignement et aux soins. Au XXe siècle, Sri Aurobindo en propose, depuis son ashram de Pondichéry, une version évolutionniste, où la conscience divine descend dans la matière et où l’humanité doit s’élever vers un « supramental ». Sarvepalli Radhakrishnan, professeur à Oxford devenu président de l’Inde, en donne l’exposé savant et le présente comme la synthèse de l’expérience religieuse de l’humanité.&lt;/p&gt; &lt;p&gt;Le néo-védanta a façonné l’image de l’hindouisme dans le monde et nourri le nationalisme indien. Des historiens lui reprochent cependant d’avoir unifié une tradition très diverse en la lisant à travers des catégories occidentales.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relecture moderne du Védanta par Vivekananda, Aurobindo et Radhakrishnan : une religion universelle et rationnelle.</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIVEKANANDA;Sri AUROBINDO;Sarvepalli RADHAKRISHNAN</t>
+        </is>
+      </c>
+      <c r="M87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N87"/>
+    </row>
+    <row r="88" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1">
+        <v>765</v>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">765</t>
+        </is>
+      </c>
+      <c r="D88" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ismaélisme</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isma%C3%A9lisme" title=" Wikipedia"&gt;L’ismaélisme&lt;/a&gt; est une branche du chiisme née au VIIIe siècle d’une querelle de succession : à la mort de l’imam Ja’far al-Sadiq, en 765, ses fidèles reconnaissent pour héritier son fils Ismaïl, et non son frère. Pour les ismaéliens, l’imam vivant, descendant du Prophète, est le guide qui détient le sens véritable de la révélation.&lt;/p&gt; &lt;p&gt;Leur pensée repose sur la distinction entre l’apparent (&lt;em&gt;zâhir&lt;/em&gt;), la lettre de la Loi et les rites, et le caché (&lt;em&gt;bâtin&lt;/em&gt;), la vérité spirituelle qu’ils contiennent. L’interprétation (&lt;em&gt;ta’wîl&lt;/em&gt;) consiste à remonter de l’un à l’autre. Pour exprimer ce sens caché, les penseurs ismaéliens des Xe et XIe siècles bâtissent une grande philosophie inspirée du néoplatonisme : Dieu, au-delà de tout attribut, fait émaner un premier Intellect, dont procèdent l’Âme et l’univers ; &lt;a href="https://fr.wikipedia.org/wiki/Hamid_al-Din_al-Kirmani" title=" Wikipedia"&gt;al-Kirmani&lt;/a&gt; décrit ainsi une hiérarchie de dix intelligences. On rattache souvent à ce milieu les &lt;a href="https://fr.wikipedia.org/wiki/Ikhwan_al-Safa" title=" Wikipedia"&gt;Frères de la Pureté&lt;/a&gt;, auteurs d’une encyclopédie des sciences. Le califat des &lt;a href="https://fr.wikipedia.org/wiki/Fatimides" title=" Wikipedia"&gt;Fatimides&lt;/a&gt;, qui règne sur l’Égypte de 969 à 1171 et fonde Le Caire et la mosquée al-Azhar, en fait une doctrine d’État.&lt;/p&gt; &lt;p&gt;Le poète persan Nasir Khusraw en est l’un des grands maîtres ; la branche nizârite s’établit en Iran dans la forteresse d’&lt;a href="https://fr.wikipedia.org/wiki/Alamut" title=" Wikipedia"&gt;Alamut&lt;/a&gt;, où le savant Nasir al-Din al-Tusi travaille de longues années, jusqu’à sa prise par les Mongols en 1256. Dépeints à tort par leurs ennemis comme une secte d’« Assassins », les ismaéliens sont aujourd’hui plusieurs millions dans le monde, et la branche nizârite reconnaît pour imam l’&lt;a href="https://fr.wikipedia.org/wiki/Aga_Khan" title=" Wikipedia"&gt;Aga Khan&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">branche du chiisme qui cherche le sens caché du Coran et l’exprime dans une grande philosophie néoplatonicienne.</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
+        </is>
+      </c>
+      <c r="L88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hamid al-Din AL-KIRMANI;NASIR KHUSRAW;Nasir AL-DIN AL-TUSI</t>
+        </is>
+      </c>
+      <c r="M88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N88"/>
+    </row>
+    <row r="89" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1">
+        <v>900</v>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">900</t>
+        </is>
+      </c>
+      <c r="D89" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maturidisme</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maturidisme" title=" Wikipedia"&gt;Le maturidisme&lt;/a&gt; est l’une des deux grandes écoles de théologie rationnelle (&lt;em&gt;kalâm&lt;/em&gt;) de l’islam sunnite, avec l’acharisme. Il est fondé au Xe siècle à Samarcande, en Asie centrale, par Abu Mansur al-Maturidi, qui se réclame de l’héritage de l’imam &lt;a href="https://fr.wikipedia.org/wiki/Ab%C3%BB_Han%C3%AEfa" title=" Wikipedia"&gt;Abû Hanîfa&lt;/a&gt;, fondateur de l’école juridique &lt;a href="https://fr.wikipedia.org/wiki/Hanafisme" title=" Wikipedia"&gt;hanafite&lt;/a&gt;. Comme son contemporain al-Ash’ari, al-Maturidi cherche une voie moyenne entre les mutazilites, qui soumettaient la foi à la raison, et les traditionalistes, qui refusaient tout raisonnement sur Dieu.&lt;/p&gt; &lt;p&gt;Mais il fait une plus grande place à la raison. Pour les maturidites, l’être humain peut savoir par sa seule intelligence que Dieu existe et distinguer le bien du mal, même sans avoir reçu de révélation : le bien et le mal sont inscrits dans les choses, et la révélation vient confirmer et préciser ce que la raison entrevoit. Ils défendent aussi plus nettement la liberté humaine : Dieu crée les actes, mais l’être humain les choisit réellement et en porte la responsabilité. La foi, enfin, est l’adhésion du cœur, confirmée par la parole ; elle ne grandit ni ne diminue avec les œuvres. Les différences avec l’acharisme sont subtiles, et les deux écoles finissent par se reconnaître mutuellement comme orthodoxes.&lt;/p&gt; &lt;p&gt;Porté par les dynasties turques, le maturidisme devient la théologie dominante de l’Asie centrale, de l’Empire ottoman et du monde indien. Le petit credo d’al-Nasafi, au XIIe siècle, commenté par al-Taftazani, est étudié dans les écoles jusqu’à nos jours. Il reste aujourd’hui la théologie de référence d’une grande partie des musulmans sunnites, de la Turquie au Pakistan.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école de théologie sunnite fondée à Samarcande par al-Maturidi : la raison peut connaître Dieu et le bien avant toute révélation.</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Épistémologie</t>
+        </is>
+      </c>
+      <c r="L89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abu Mansur AL-MATURIDI;Abu Hafs AL-NASAFI</t>
+        </is>
+      </c>
+      <c r="M89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N89"/>
+    </row>
+    <row r="90" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1">
+        <v>1200</v>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200</t>
+        </is>
+      </c>
+      <c r="D90" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kabbale" title=" Wikipedia"&gt;La Kabbale&lt;/a&gt;, la « tradition reçue », est la grande tradition mystique et ésotérique du judaïsme. Elle apparaît à la fin du XIIe siècle en Provence, puis en Catalogne, où Nahmanide, à Gérone, lui donne son autorité, et en Castille, où &lt;a href="https://fr.wikipedia.org/wiki/Mo%C3%AFse_de_Le%C3%B3n" title=" Wikipedia"&gt;Moïse de León&lt;/a&gt; compose vers 1280 le &lt;em&gt;Zohar&lt;/em&gt;, « livre de la Splendeur », qui en devient le texte majeur.&lt;/p&gt; &lt;p&gt;Elle distingue en Dieu l’&lt;em&gt;En Sof&lt;/em&gt;, « l’Infini », absolument caché, et les dix &lt;a href="https://fr.wikipedia.org/wiki/Sephiroth_%28Kabbale%29" title=" Wikipedia"&gt;&lt;em&gt;sefirot&lt;/em&gt;&lt;/a&gt;, émanations par lesquelles il se manifeste : sagesse, intelligence, amour, rigueur, beauté, jusqu’à la &lt;a href="https://fr.wikipedia.org/wiki/Shekhina" title=" Wikipedia"&gt;&lt;em&gt;Shekhina&lt;/em&gt;&lt;/a&gt;, la présence divine dans le monde, que la Kabbale conçoit comme féminine et exilée avec le peuple. Chaque mot de la Torah, chaque commandement accompli, agit sur l’harmonie de ces puissances. Après l’expulsion des Juifs d’Espagne, en 1492, la Kabbale se renouvelle à Safed, en Galilée, autour d’&lt;a href="https://fr.wikipedia.org/wiki/Isaac_Louria" title=" Wikipedia"&gt;Isaac Louria&lt;/a&gt;. Pour faire place au monde, l’Infini a dû se retirer en lui-même : c’est le &lt;a href="https://fr.wikipedia.org/wiki/Tsimtsoum" title=" Wikipedia"&gt;&lt;em&gt;tsimtsoum&lt;/em&gt;&lt;/a&gt;. Puis les « vases » qui devaient recevoir sa lumière se sont brisés, et des étincelles divines sont tombées dans la matière. La tâche de l’être humain est le &lt;a href="https://fr.wikipedia.org/wiki/Tikkoun_Olam" title=" Wikipedia"&gt;&lt;em&gt;tikkoun&lt;/em&gt;&lt;/a&gt;, la réparation du monde, en relevant ces étincelles par la prière et les actes justes. Ce messianisme intérieur nourrit au XVIIe siècle l’aventure de Sabbataï Tsevi, puis, au XVIIIe, le hassidisme.&lt;/p&gt; &lt;p&gt;À la Renaissance, Pic de la Mirandole fonde une « Kabbale chrétienne ». Longtemps méprisée par les historiens, la Kabbale a été réhabilitée au XXe siècle par les travaux de Gershom Scholem, qui en a fait un objet d’étude majeur.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tradition mystique du judaïsme qui contemple les dix émanations de Dieu et appelle l’être humain à réparer le monde.</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
+        </is>
+      </c>
+      <c r="L90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac LOURIA;Moïse de LEÓN;NAHMANIDE;Abraham ABOULAFIA</t>
+        </is>
+      </c>
+      <c r="M90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1">
+        <v>1740</v>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1740</t>
+        </is>
+      </c>
+      <c r="D91" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hassidisme</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;Le hassidisme&lt;/a&gt;, de l’hébreu &lt;em&gt;hassid&lt;/em&gt;, « pieux », est un mouvement de renouveau mystique du judaïsme né au XVIIIe siècle en Podolie, dans l’actuelle Ukraine, alors polonaise, autour du Baal Shem Tov, le « Maître du Bon Nom ». Il paraît dans des communautés juives pauvres et éprouvées par les massacres et par la faillite du faux messie Sabbataï Tsevi, où le savoir talmudique est réservé à une élite.&lt;/p&gt; &lt;p&gt;Reprenant les idées de la Kabbale, le hassidisme les met à la portée de tous. Dieu est présent partout, jusque dans les choses les plus humbles : on peut donc le servir non seulement par l’étude, mais par la prière fervente, le chant, la danse et chaque geste du quotidien, accompli avec attention. La joie est une forme de piété, la tristesse un obstacle. La ferveur du cœur compte plus que l’érudition, et le plus simple des fidèles peut s’unir à Dieu. Au centre de chaque communauté se tient le &lt;a href="https://fr.wikipedia.org/wiki/Tsadik" title=" Wikipedia"&gt;&lt;em&gt;tsaddik&lt;/em&gt;&lt;/a&gt;, le « juste », maître spirituel qui guide ses disciples et intercède pour eux. Les maîtres hassidiques enseignent par des récits et des paraboles, comme ceux de &lt;a href="https://fr.wikipedia.org/wiki/Nahman_de_Bratslav" title=" Wikipedia"&gt;Nahman de Bratslav&lt;/a&gt;, arrière-petit-fils du Baal Shem Tov.&lt;/p&gt; &lt;p&gt;Combattu d’abord par les rabbins traditionnels, les &lt;a href="https://fr.wikipedia.org/wiki/Mitnagdim" title=" Wikipedia"&gt;Mitnagdim&lt;/a&gt;, le mouvement gagne une grande partie des Juifs d’Europe de l’Est. Presque anéanti par la Shoah, il renaît aux États-Unis et en Israël, où ses communautés, comme celle de Loubavitch, sont aujourd’hui très vivantes. Martin Buber a fait connaître ses récits en Occident ; Abraham Heschel et Elie Wiesel, issus de familles hassidiques, en ont transmis l’esprit.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement mystique juif né en Ukraine autour du Baal Shem Tov : servir Dieu dans la joie, l’humilité et chaque geste du quotidien.</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
+        </is>
+      </c>
+      <c r="L91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAAL SHEM TOV;Martin BUBER</t>
+        </is>
+      </c>
+      <c r="M91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N91"/>
+    </row>
+    <row r="92" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1">
+        <v>1770</v>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1770</t>
+        </is>
+      </c>
+      <c r="D92" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haskala</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Haskala" title=" Wikipedia"&gt;La Haskala&lt;/a&gt;, de l’hébreu &lt;em&gt;sekhel&lt;/em&gt;, « intelligence », est le mouvement des Lumières juives, né à Berlin dans les années 1770. Ses partisans, les &lt;em&gt;maskilim&lt;/em&gt;, veulent faire sortir les Juifs du ghetto culturel où les ont enfermés des siècles de discriminations, en les ouvrant aux sciences, à la philosophie et aux langues de l’Europe, sans qu’ils renoncent pour autant à leur foi.&lt;/p&gt; &lt;p&gt;Son inspirateur est Moses Mendelssohn, surnommé le « Socrate de Berlin », admiré de Kant et ami de &lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing" title=" Wikipedia"&gt;Lessing&lt;/a&gt;, qui fait de lui le modèle de son &lt;em&gt;Nathan le Sage&lt;/em&gt;. Il traduit la Torah en allemand, imprimée en caractères hébraïques, pour que les Juifs apprennent la langue du pays. Dans &lt;em&gt;Jérusalem&lt;/em&gt; (1783), il défend la liberté de conscience et la séparation de l’État et de la religion : le judaïsme, dit-il, n’impose pas de croyances, il prescrit des pratiques, et ses vérités sont celles de la raison, accessibles à tous les hommes. Autour de lui, le médecin Marcus Herz, élève de Kant, et David Friedländer, qui plaide pour l’émancipation civile des Juifs de Prusse, poursuivent son œuvre. La Haskala fonde des écoles modernes, une presse et fait renaître l’hébreu comme langue littéraire profane.&lt;/p&gt; &lt;p&gt;Au XIXe siècle, elle gagne la Galicie et l’Empire russe. Elle prépare le &lt;a href="https://fr.wikipedia.org/wiki/Juda%C3%AFsme_r%C3%A9form%C3%A9" title=" Wikipedia"&gt;judaïsme libéral&lt;/a&gt;, la &lt;a href="https://fr.wikipedia.org/wiki/Wissenschaft_des_Judentums" title=" Wikipedia"&gt;« science du judaïsme »&lt;/a&gt;, l’étude historique de sa tradition, et indirectement le sionisme. Ses adversaires lui ont reproché d’ouvrir la voie à l’assimilation ; ses héritiers y voient l’entrée du judaïsme dans la modernité.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">les « Lumières juives » de Mendelssohn : unir la fidélité au judaïsme, la raison et la culture européenne.</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie politique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moses MENDELSSOHN</t>
+        </is>
+      </c>
+      <c r="M92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="1">
+        <v>1600</v>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1600</t>
+        </is>
+      </c>
+      <c r="D93" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École d'Ispahan</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_d%27Ispahan" title=" Wikipedia"&gt;École d’Ispahan&lt;/a&gt; le grand renouveau philosophique qui se produit en Iran au XVIIe siècle, à Ispahan, capitale de la dynastie &lt;a href="https://fr.wikipedia.org/wiki/Dynastie_des_S%C3%A9f%C3%A9vides" title=" Wikipedia"&gt;safavide&lt;/a&gt; qui a fait du chiisme la religion d’État. Alors que l’on a longtemps cru la philosophie islamique morte après Averroès, elle connaît là une nouvelle floraison, qui unit l’héritage d’Avicenne, la sagesse de l’illumination de Sohrawardi, la mystique d’Ibn Arabî et la théologie chiite.&lt;/p&gt; &lt;p&gt;Son premier maître est &lt;a href="https://fr.wikipedia.org/wiki/Mir_Damad" title=" Wikipedia"&gt;Mir Damad&lt;/a&gt;, philosophe et théologien, qui réfléchit sur le rapport entre l’éternité et le temps et signe ses poèmes du nom d’« Ishrâq », l’illumination. Son disciple Molla Sadra en est le génie. Dans ses &lt;em&gt;Quatre voyages de l’intellect&lt;/em&gt;, il fonde la « sagesse transcendante » (&lt;em&gt;al-hikma al-muta’aliya&lt;/em&gt;), qui veut unir la démonstration rationnelle, l’expérience spirituelle et la révélation. Sa thèse centrale est la primauté de l’existence : ce qui est réel, ce n’est pas l’essence, la définition des choses, mais l’acte d’exister, unique et présent en toutes choses à des degrés différents, comme une même lumière plus ou moins intense. Il affirme aussi le « mouvement substantiel » : l’être des choses n’est pas fixe, il est lui-même en devenir, si bien que le monde tout entier est en marche vers sa perfection.&lt;/p&gt; &lt;p&gt;Prolongée en Iran jusqu’à nos jours, par Sabzevari au XIXe siècle puis par Allameh Tabatabaï et Morteza Motahhari, cette école a été révélée au public occidental par &lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin" title=" Wikipedia"&gt;Henry Corbin&lt;/a&gt;, qui lui a donné son nom. Elle a aussi profondément marqué le clergé chiite iranien du XXe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">renaissance de la philosophie dans l’Iran chiite des Safavides, dont Molla Sadra est le sommet avec sa « sagesse transcendante ».</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Molla SADRA;MIR DAMAD;Allameh TABATABAÏ</t>
+        </is>
+      </c>
+      <c r="M93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N93"/>
+    </row>
+    <row r="94" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1">
+        <v>1878</v>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1878</t>
+        </is>
+      </c>
+      <c r="D94" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophiologie</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sophiologie" title=" Wikipedia"&gt;La sophiologie&lt;/a&gt; est un courant de la philosophie religieuse russe, né à la fin du XIXe siècle, qui fait de la &lt;a href="https://fr.wikipedia.org/wiki/Sophia_%28philosophie%29" title=" Wikipedia"&gt;Sagesse divine&lt;/a&gt;, Sophia, le cœur de sa réflexion. Elle reprend une figure de la Bible, où la Sagesse est présentée comme la compagne de Dieu lors de la création, et une longue tradition mystique, du platonisme à Jacob Boehme. Son fondateur est Vladimir Soloviev, qui raconte avoir eu trois visions de Sophia, la dernière dans le désert d’Égypte, en 1875.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Leçons sur la divino-humanité&lt;/em&gt; (1878), Soloviev décrit Sophia comme l’âme du monde, l’unité idéale de toutes les créatures en Dieu : elle est le lien entre le Créateur et la création, ce par quoi le monde n’est pas étranger à Dieu. L’histoire a pour sens la réunion progressive de l’humanité et du divin, dont le Christ, Dieu fait homme, est le modèle. Le prêtre et savant Pavel Florensky reprend cette intuition dans &lt;em&gt;La Colonne et le Fondement de la vérité&lt;/em&gt; (1914), en y mêlant mathématiques, théologie et histoire de l’art. Mais c’est Sergueï Boulgakov, économiste marxiste devenu prêtre orthodoxe, qui en fait un vaste système théologique dans son exil parisien, à l’&lt;a href="https://fr.wikipedia.org/wiki/Institut_Saint-Serge" title=" Wikipedia"&gt;Institut Saint-Serge&lt;/a&gt; : la Sagesse est la nature même de Dieu, qui se révèle dans le monde créé, si bien que la création tout entière est appelée à être transfigurée.&lt;/p&gt; &lt;p&gt;En 1935, l’Église orthodoxe russe condamne les thèses de Boulgakov, et les théologiens Vladimir Lossky et Georges Florovsky les critiquent sévèrement. La sophiologie a pourtant marqué les poètes symbolistes, comme Alexandre Blok et Andreï Biély, et elle inspire aujourd’hui une théologie de la création attentive à l’écologie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J94" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophie religieuse russe de la Sagesse divine, Sophia, qui unit Dieu et le monde : Soloviev, Florensky, Boulgakov.</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
+        </is>
+      </c>
+      <c r="L94" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vladimir SOLOVIEV;Sergueï BOULGAKOV;Pavel FLORENSKY</t>
+        </is>
+      </c>
+      <c r="M94" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="N94"/>
+    </row>
+    <row r="95" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1">
+        <v>1921</v>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921</t>
+        </is>
+      </c>
+      <c r="D95" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eurasisme</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;L’eurasisme&lt;/a&gt; est un courant de pensée né en 1921 dans l’émigration russe, après la révolution bolchevique, avec le recueil &lt;em&gt;L’Exode vers l’Orient&lt;/em&gt;, publié à Sofia par un petit groupe de jeunes intellectuels exilés : le linguiste &lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Sergue%C3%AFevitch_Troubetsko%C3%AF" title=" Wikipedia"&gt;Nikolaï Troubetskoï&lt;/a&gt;, le géographe Piotr Savitski, le musicologue Pierre Souvtchinski et le théologien Georges Florovsky.&lt;/p&gt; &lt;p&gt;Leur thèse est que la Russie n’est ni une partie de l’Europe ni une partie de l’Asie, mais un monde à part, l’« Eurasie », dont la grande plaine, des Carpates au Pacifique, a façonné l’unité des peuples slaves, turcs et finno-ougriens. Contre les occidentalistes, ils refusent l’idée d’une civilisation européenne universelle : dans &lt;em&gt;L’Europe et l’humanité&lt;/em&gt; (1920), Troubetskoï y voit l’égoïsme d’une culture « romano-germanique » qui s’impose aux autres. Contre les slavophiles, ils réhabilitent l’héritage asiatique de la Russie, et jusqu’à l’empire de Gengis Khan, qui aurait le premier unifié cet espace. Ils rêvent d’un État fondé sur une idéologie commune et sur l’orthodoxie, distinct à la fois de la démocratie libérale et du communisme. Florovsky s’en éloigne vite et critique en 1928 ce qu’il appelle une « vérité des questions » devenue une « erreur des réponses ». Le mouvement se divise à la fin des années 1920, une partie se rapprochant du régime soviétique.&lt;/p&gt; &lt;p&gt;Prolongé en URSS par l’historien &lt;a href="https://fr.wikipedia.org/wiki/Lev_Goumilev" title=" Wikipedia"&gt;Lev Goumilev&lt;/a&gt;, l’eurasisme renaît après 1991 sous la forme d’un « néo-eurasisme » porté par &lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Douguine" title=" Wikipedia"&gt;Alexandre Douguine&lt;/a&gt;, idéologue d’extrême droite, et influence aujourd’hui la géopolitique nationaliste et impériale de la Russie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doctrine née dans l’émigration russe : la Russie ne serait ni l’Europe ni l’Asie, mais une civilisation à part, l’« Eurasie ».</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie politique</t>
+        </is>
+      </c>
+      <c r="L95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nikolaï TROUBETSKOÏ;Georges FLOROVSKY</t>
+        </is>
+      </c>
+      <c r="M95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1">
+        <v>1945</v>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1945</t>
+        </is>
+      </c>
+      <c r="D96" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ethnophilosophie</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ethnophilosophy" title=" Wikipedia (en)"&gt;L’ethnophilosophie&lt;/a&gt; désigne la démarche qui cherche la philosophie d’un peuple dans ses langues, ses proverbes, ses mythes et ses croyances, plutôt que dans les œuvres de penseurs individuels. Elle naît en 1945 avec &lt;a href="https://fr.wikipedia.org/wiki/La_Philosophie_bantoue" title=" Wikipedia"&gt;&lt;em&gt;La Philosophie bantoue&lt;/em&gt;&lt;/a&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;, qui veut montrer, contre le préjugé colonial, que les Africains ont une pensée cohérente, fondée sur l’idée de « force vitale » : pour les Bantous, l’être est force, et toute chose est une force qui peut croître ou décroître.&lt;/p&gt; &lt;p&gt;Des penseurs africains reprennent cette démarche en la retournant contre le regard colonial. Le prêtre rwandais Alexis Kagame, dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), dégage les catégories de la pensée à partir de la grammaire du kinyarwanda, comme Aristote l’avait fait, selon lui, à partir du grec. Le théologien kényan John Mbiti décrit dans &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969) une conception du temps tournée vers le passé plus que vers l’avenir. Dans l’esprit de la Négritude, il s’agit d’affirmer la dignité des cultures africaines.&lt;/p&gt; &lt;p&gt;À partir des années 1970, cette démarche est vivement critiquée par d’autres philosophes africains. Paulin Hountondji, dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976), dénonce le « mythe de l’unanimité » : une philosophie n’est pas une vision du monde collective et figée, mais un discours critique, signé, argumenté et ouvert à la discussion. Marcien Towa et Fabien Eboussi Boulaga vont dans le même sens. Le débat sur l’ethnophilosophie a structuré toute la philosophie africaine contemporaine.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recherche d’une philosophie africaine dans les langues, les croyances et les traditions des peuples, et débat qu’elle a suscité.</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Épistémologie</t>
+        </is>
+      </c>
+      <c r="L96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placide TEMPELS;Alexis KAGAME;John MBITI</t>
+        </is>
+      </c>
+      <c r="M96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N96"/>
+    </row>
+    <row r="97" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1">
+        <v>1960</v>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1960</t>
+        </is>
+      </c>
+      <c r="D97" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socialisme africain</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/Socialisme_africain" title=" Wikipedia"&gt;socialisme africain&lt;/a&gt; l’ensemble des doctrines par lesquelles plusieurs dirigeants des indépendances africaines, autour de 1960, ont voulu définir une voie propre de développement, distincte à la fois du capitalisme des anciennes puissances coloniales et du communisme soviétique.&lt;/p&gt; &lt;p&gt;Leur idée commune est que l’Afrique n’a pas besoin d’importer le socialisme, car elle le porte déjà dans ses traditions : la solidarité de la famille élargie et du village, la propriété commune de la terre, le partage des biens. Il ne s’agit donc pas de mener une lutte des classes, que les sociétés africaines n’auraient pas connue, mais de moderniser ces solidarités. Au Sénégal, Léopold Sédar Senghor défend un socialisme humaniste et spirituel, nourri de la Négritude et de la pensée de Teilhard de Chardin, qui refuse l’athéisme marxiste. Au Ghana, Kwame Nkrumah, plus proche du marxisme, cherche dans son « consciencisme » une synthèse entre la tradition africaine, l’islam et le christianisme. En Tanzanie, Julius Nyerere en donne la version la plus élaborée avec l’&lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt;, mot swahili qui signifie « esprit de famille » : la nation doit vivre comme une grande famille où chacun travaille et où personne n’exploite personne. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;déclaration d’Arusha&lt;/a&gt; (1967) en fait le programme du pays.&lt;/p&gt; &lt;p&gt;Dans les faits, ces politiques ont souvent abouti à des partis uniques et, en Tanzanie, au regroupement forcé des paysans dans des villages collectifs, qui fut un échec économique, reconnu par Nyerere lui-même. Elles restent pourtant une tentative originale de penser le développement à partir des valeurs africaines.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">socialisme des indépendances fondé sur les solidarités communautaires africaines plutôt que sur la lutte des classes.</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie politique;Éthique</t>
+        </is>
+      </c>
+      <c r="L97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Julius NYERERE;Léopold Sédar SENGHOR;Kwame NKRUMAH</t>
+        </is>
+      </c>
+      <c r="M97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N97"/>
+    </row>
+    <row r="98" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1">
+        <v>1968</v>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1968</t>
+        </is>
+      </c>
+      <c r="D98" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de la libération</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;La théologie de la libération&lt;/a&gt; est un courant de pensée chrétien, surtout catholique, né en Amérique latine à la fin des années 1960, dans un continent marqué par la misère, les inégalités et les dictatures. Elle s’appuie sur le renouveau du concile Vatican II et sur la &lt;a href="https://fr.wikipedia.org/wiki/Conf%C3%A9rence_de_Medell%C3%ADn" title=" Wikipedia"&gt;conférence des évêques latino-américains de Medellín&lt;/a&gt;, en 1968, qui dénonce la « violence institutionnalisée » de l’injustice sociale.&lt;/p&gt; &lt;p&gt;Son texte fondateur est &lt;em&gt;Théologie de la libération&lt;/em&gt; (1971) du prêtre péruvien &lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo Gutiérrez&lt;/a&gt;. La théologie n’y est plus seulement une réflexion abstraite sur Dieu, mais une « réflexion critique sur la pratique » : elle part de la situation concrète des pauvres et de leur lutte pour leur dignité. Dieu prend parti pour les opprimés, comme il a libéré Israël de l’esclavage en Égypte ; le salut ne concerne pas seulement l’au-delà, il commence par la libération de toutes les servitudes. D’où l’« option préférentielle pour les pauvres ». Pour comprendre les causes de la pauvreté, ces théologiens utilisent les sciences sociales, y compris l’analyse marxiste. La foi se vit dans les &lt;a href="https://fr.wikipedia.org/wiki/Communaut%C3%A9_eccl%C3%A9siale_de_base" title=" Wikipedia"&gt;communautés ecclésiales de base&lt;/a&gt;, où les pauvres lisent eux-mêmes la Bible à la lumière de leur vie. Le Brésilien Leonardo Boff, le jésuite Ignacio Ellacuría, assassiné au Salvador en 1989, et les réflexions de Paulo Freire et d’Enrique Dussel lui sont proches.&lt;/p&gt; &lt;p&gt;Rome, sous Jean-Paul II, critique dans les années 1980 son usage du marxisme et impose le silence à Boff. Sa reconnaissance vient avec le pape François, et l’option pour les pauvres est aujourd’hui reprise par toute l’Église catholique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J98" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">courant chrétien latino-américain qui place au cœur de la foi l’engagement aux côtés des pauvres et contre l’injustice.</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Philosophie politique</t>
+        </is>
+      </c>
+      <c r="L98" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gustavo GUTIÉRREZ;Leonardo BOFF;Enrique DUSSEL;Paulo FREIRE</t>
+        </is>
+      </c>
+      <c r="M98" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1">
+        <v>1971</v>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1971</t>
+        </is>
+      </c>
+      <c r="D99" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie de la libération</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;La philosophie de la libération&lt;/a&gt; est un mouvement philosophique latino-américain apparu au début des années 1970, en Argentine surtout, autour du congrès national de philosophie de Córdoba en 1971. Il veut faire de la philosophie un instrument d’émancipation pour les peuples d’Amérique latine, dominés économiquement et culturellement, en écho à la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt; des économistes.&lt;/p&gt; &lt;p&gt;Il naît d’un débat. En 1968, le Péruvien Augusto Salazar Bondy demande « Existe-t-il une philosophie de notre Amérique ? » et répond qu’une culture dépendante ne peut produire qu’une pensée imitée, inauthentique, tant que dure la domination. Le Mexicain Leopoldo Zea lui répond que la pensée latino-américaine est déjà une philosophie à part entière, qui réfléchit sur sa propre histoire. L’Argentin Enrique Dussel en devient la figure majeure. S’inspirant d’&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Levinas" title=" Wikipedia"&gt;Emmanuel Levinas&lt;/a&gt;, il fait de l’Autre, le pauvre, l’Indien, le colonisé, la femme, le point de départ de l’éthique : la philosophie doit écouter la parole de celui que le système exclut. Pour lui, la modernité ne commence pas avec le « je pense » de Descartes, mais en 1492, avec le « je conquiers » des conquistadors. Rodolfo Kusch, de son côté, cherche dans la pensée des peuples andins une autre manière d’être au monde, celle de l’« être là » plutôt que de l’« être quelqu’un ».&lt;/p&gt; &lt;p&gt;Persécutés par la dictature militaire, Dussel et plusieurs autres partent en exil en 1975. Le mouvement a nourri la théologie de la libération, puis la pensée décoloniale, et reste une référence des philosophies du Sud.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J99" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophie latino-américaine qui pense à partir des peuples dominés et dénonce la dépendance culturelle envers l’Europe.</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Éthique;Philosophie politique</t>
+        </is>
+      </c>
+      <c r="L99" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enrique DUSSEL;Augusto SALAZAR BONDY;Leopoldo ZEA-AGUILAR</t>
+        </is>
+      </c>
+      <c r="M99" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N99"/>
+    </row>
+    <row r="100" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1">
+        <v>1981</v>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1981</t>
+        </is>
+      </c>
+      <c r="D100" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Créolisation</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;La &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olisation_%28concept%29" title=" Wikipedia"&gt;créolisation&lt;/a&gt; est un courant de pensée né aux Antilles autour de l’œuvre d’Édouard Glissant. Le mot désigne d’abord la naissance des langues et des cultures créoles dans les sociétés de plantation des Caraïbes, où des peuples arrachés à l’Afrique, des colons européens, des Amérindiens et plus tard des travailleurs venus d’Inde ont dû inventer ensemble un monde nouveau. Glissant en fait un concept philosophique pour penser le monde entier.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Discours_antillais" title=" Wikipedia"&gt;&lt;em&gt;Le Discours antillais&lt;/em&gt;&lt;/a&gt; (1981), il développe d’abord l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : l’identité des Antilles ne se trouve ni dans un retour à l’Afrique, comme le voulait la Négritude, ni dans l’imitation de la France, mais dans l’archipel caribéen lui-même. Avec la créolisation, il montre que la rencontre des cultures ne produit pas un simple mélange prévisible, mais de l’inédit. Reprenant une image de Deleuze et Guattari, il oppose l’« identité-racine », unique, qui exclut l’autre, à l’« identité-rhizome », qui se construit dans la relation. Dans &lt;em&gt;Poétique de la Relation&lt;/em&gt; (1990), il défend le « droit à l’opacité » : comprendre l’autre ne signifie pas le réduire à soi. Il appelle &lt;a href="https://fr.wikipedia.org/wiki/Tout-monde" title=" Wikipedia"&gt;« Tout-Monde »&lt;/a&gt; ce monde où toutes les cultures sont désormais en contact, pour le meilleur et pour le pire, et où nul ne peut plus vivre à l’écart des autres.&lt;/p&gt; &lt;p&gt;En 1989, les écrivains martiniquais Jean Bernabé, &lt;a href="https://fr.wikipedia.org/wiki/Patrick_Chamoiseau" title=" Wikipedia"&gt;Patrick Chamoiseau&lt;/a&gt; et Raphaël Confiant prolongent ce mouvement dans leur &lt;em&gt;Éloge de la &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olit%C3%A9" title=" Wikipedia"&gt;créolité&lt;/a&gt;&lt;/em&gt;. La pensée de Glissant est aujourd’hui l’une des grandes références de la réflexion sur la mondialisation et les identités.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J100" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pensée antillaise de Glissant : les cultures en contact créent de l’imprévisible ; à l’identité-racine s’oppose l’identité-relation.</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Philosophie politique</t>
+        </is>
+      </c>
+      <c r="L100" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Édouard GLISSANT</t>
+        </is>
+      </c>
+      <c r="M100" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N100"/>
+    </row>
+    <row r="101" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1">
+        <v>1992</v>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1992</t>
+        </is>
+      </c>
+      <c r="D101" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée décoloniale</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;La pensée décoloniale, ou &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;études décoloniales&lt;/a&gt;, est un courant né en Amérique latine dans les années 1990. Son point de départ est un article de 1992 du sociologue péruvien &lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal Quijano&lt;/a&gt;, qui forge la notion de « colonialité du pouvoir » : le colonialisme, comme domination politique directe, a pris fin, mais la colonialité, elle, a survécu.&lt;/p&gt; &lt;p&gt;Pour ces penseurs, la modernité européenne et la colonisation des Amériques, à partir de 1492, sont les deux faces d’un même processus. La colonisation a installé une hiérarchie des êtres humains fondée sur la race, une division du travail mondiale et une hiérarchie des savoirs, qui présente la science et la philosophie européennes comme universelles et relègue les autres savoirs au rang de croyances ou de folklore. Cette colonialité continue d’organiser le monde après les indépendances. Le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt;, qui réunit autour de Quijano l’Argentin &lt;a href="https://fr.wikipedia.org/wiki/Walter_Mignolo" title=" Wikipedia"&gt;Walter Mignolo&lt;/a&gt;, Enrique Dussel et d’autres, appelle à une « désobéissance épistémique » : penser à partir des expériences et des savoirs des peuples colonisés, pour un monde où plusieurs mondes seraient possibles. Sylvia Wynter et Lewis Gordon prolongent cette réflexion dans la Caraïbe et chez les Afro-Américains.&lt;/p&gt; &lt;p&gt;Le courant se distingue des études postcoloniales anglophones d’Edward Saïd ou de &lt;a href="https://fr.wikipedia.org/wiki/Gayatri_Chakravorty_Spivak" title=" Wikipedia"&gt;Gayatri Spivak&lt;/a&gt;, nées de la critique littéraire et centrées sur l’Asie et le Moyen-Orient. Il suscite aussi des critiques, y compris en Amérique latine, où Silvia Rivera Cusicanqui lui reproche d’être devenu une mode universitaire du Nord.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J101" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">courant latino-américain pour qui la colonialité du pouvoir et du savoir a survécu à la fin des colonies.</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie politique;Épistémologie</t>
+        </is>
+      </c>
+      <c r="L101" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aníbal QUIJANO;Walter MIGNOLO;Enrique DUSSEL;Sylvia WYNTER</t>
+        </is>
+      </c>
+      <c r="M101" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N101"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2355,7 +2355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -5718,6 +5718,88 @@
         </is>
       </c>
       <c r="N101"/>
+    </row>
+    <row r="102" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1">
+        <v>-300</v>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-300</t>
+        </is>
+      </c>
+      <c r="D102" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École du Yin-Yang</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_du_Yin-Yang" title=" Wikipedia"&gt;L’école du Yin-Yang&lt;/a&gt; est l’un des grands courants de la pensée chinoise de l’Antiquité, né à la fin de la période des Royaumes combattants, au IVe et au IIIe siècle avant notre ère. Son maître est &lt;a href="https://fr.wikipedia.org/wiki/Zou_Yan" title=" Wikipedia"&gt;Zou Yan&lt;/a&gt;, savant de l’État de Qi, dont les œuvres sont perdues, mais que l’historien Sima Qian présente comme l’un des penseurs les plus écoutés de son temps par les princes.&lt;/p&gt; &lt;p&gt;Elle explique toute la réalité par deux principes complémentaires, le &lt;a href="https://fr.wikipedia.org/wiki/Yin_et_yang" title=" Wikipedia"&gt;yin et le yang&lt;/a&gt; : le sombre et le lumineux, le froid et le chaud, le repos et le mouvement, le féminin et le masculin. Aucun n’existe sans l’autre, chacun contient le germe de son contraire et le monde naît de leur alternance, comme le jour succède à la nuit. Zou Yan y joint la théorie des &lt;a href="https://fr.wikipedia.org/wiki/Wuxing_%28cosmologie%29" title=" Wikipedia"&gt;cinq phases&lt;/a&gt; ou cinq éléments, le bois, le feu, la terre, le métal et l’eau, qui s’engendrent et se dominent les uns les autres selon des cycles réguliers. Il en tire une philosophie de l’histoire : chaque dynastie règne sous le signe d’une phase et sera remplacée par celle qui la domine. Le premier empereur de Chine, Qin Shi Huangdi, place ainsi son règne sous le signe de l’eau. L’école décrit aussi la géographie du monde, qui compterait neuf grands continents, dont la Chine ne serait qu’une partie.&lt;/p&gt; &lt;p&gt;Elle disparaît comme école indépendante sous les Han, mais ses idées se fondent dans toute la culture chinoise. Dong Zhongshu les intègre au confucianisme officiel, en faisant correspondre l’ordre du ciel et celui de la société. Elles fondent aussi la médecine chinoise, l’astrologie, la géomancie et la lecture du &lt;em&gt;Yijing&lt;/em&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J102" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école chinoise de Zou Yan qui explique la nature et l’histoire par le yin et le yang et les cinq phases.</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Philosophie des sciences et du vivant</t>
+        </is>
+      </c>
+      <c r="L102" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zou YAN;Dong ZHONGSHU</t>
+        </is>
+      </c>
+      <c r="M102" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N102"/>
+    </row>
+    <row r="103" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1">
+        <v>240</v>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240</t>
+        </is>
+      </c>
+      <c r="D103" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xuanxue</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Xuanxue" title=" Wikipedia"&gt;Xuanxue&lt;/a&gt;, « étude du mystère », parfois appelé néotaoïsme, est un grand courant de la philosophie chinoise des IIIe et IVe siècles, né après la chute de la dynastie Han, dans une période de guerres et de désordres où le confucianisme officiel a perdu son crédit. Les lettrés se tournent alors vers les « trois livres du mystère » : le &lt;em&gt;Laozi&lt;/em&gt;, le &lt;em&gt;Zhuangzi&lt;/em&gt; et le &lt;em&gt;Yijing&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Le jeune Wang Bi, mort à vingt-trois ans, en est le génie. Dans ses commentaires du &lt;em&gt;Laozi&lt;/em&gt; et du &lt;em&gt;Yijing&lt;/em&gt;, il affirme que toutes les choses ont pour fondement le « non-être » (&lt;em&gt;wu&lt;/em&gt;), réalité sans forme ni nom, que l’on ne peut pas dire mais d’où tout procède. Le sage n’est pas celui qui en parle le plus, mais celui qui l’incarne : c’est pourquoi Confucius, qui n’en parlait jamais, était plus sage que Laozi. Un demi-siècle plus tard, &lt;a href="https://fr.wikipedia.org/wiki/Guo_Xiang" title=" Wikipedia"&gt;Guo Xiang&lt;/a&gt;, éditeur et commentateur du &lt;em&gt;Zhuangzi&lt;/em&gt;, soutient au contraire que le non-être n’est rien et ne peut rien produire : chaque chose « advient d’elle-même », spontanément, sans créateur ni cause extérieure, et trouve son bonheur à suivre sa propre nature. Ces débats se poursuivent dans les « &lt;a href="https://fr.wikipedia.org/wiki/Qingtan" title=" Wikipedia"&gt;pures conversations&lt;/a&gt; », joutes philosophiques raffinées de l’aristocratie.&lt;/p&gt; &lt;p&gt;Les &lt;a href="https://fr.wikipedia.org/wiki/Sept_Sages_de_la_for%C3%AAt_de_bambous" title=" Wikipedia"&gt;Sept Sages de la forêt de bambous&lt;/a&gt;, poètes et musiciens comme Ji Kang et Ruan Ji, en vivent l’idéal de liberté, en marge des rites et des honneurs. Le Xuanxue prépare surtout l’accueil du bouddhisme en Chine : les premiers traducteurs expriment la vacuité bouddhique dans son vocabulaire du non-être.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="J103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">« étude du mystère » : renouveau taoïste des IIIe et IVe siècles chinois, autour de Wang Bi et de Guo Xiang.</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wang BI;Guo XIANG;Ji KANG</t>
+        </is>
+      </c>
+      <c r="M103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N103"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -3330,8 +3330,10 @@
       <c r="D32" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="E32" s="19" t="s">
-        <v>192</v>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F32" s="14" t="s">
         <v>193</v>
@@ -3704,8 +3706,10 @@
       <c r="D44" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>260</v>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e" title=" Wikipedia"&gt;Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement de la pensée confucéenne dans la péninsule coréenne. Arrivé dès l’époque des Trois Royaumes, le confucianisme inspire sous la dynastie Goryeo l’organisation de l’État, avec l’instauration en 958 d’examens pour recruter les fonctionnaires. À la fin du XIIIe siècle, le néoconfucianisme de Zhu Xi est introduit depuis la Chine. Il devient la doctrine officielle de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9riode_Joseon" title=" Wikipedia"&gt;dynastie Joseon&lt;/a&gt; (1392-1910), dont les fondateurs s’appuient sur des lettrés qui veulent réformer l’État et réduire l’influence du bouddhisme.&lt;/p&gt; &lt;p&gt;Deux figures dominent ce courant au XVIe siècle. &lt;a href="https://fr.wikipedia.org/wiki/Yi_Hwang" title=" Wikipedia"&gt;Yi Hwang&lt;/a&gt;, dit Toegye (1501-1570), affirme la primauté du principe (&lt;em&gt;li&lt;/em&gt;), réalité immatérielle et morale, sur l’énergie matérielle (&lt;em&gt;gi&lt;/em&gt;). Il en sort une célèbre controverse, le « débat des quatre et des sept » : les quatre sentiments moraux, comme la compassion, naissent-ils du principe, et les sept émotions ordinaires, comme la colère ou la joie, de l’énergie ? &lt;a href="https://fr.wikipedia.org/wiki/Yi_I" title=" Wikipedia"&gt;Yi I&lt;/a&gt;, dit Yulgok (1536-1584), défend au contraire leur unité dynamique : le principe n’agit jamais sans l’énergie. Ce débat, qui oppose ensuite des écoles rivales, structure la philosophie coréenne pendant des siècles.&lt;/p&gt; &lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (&lt;em&gt;seonbi&lt;/em&gt;) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (&lt;em&gt;seowon&lt;/em&gt;) diffusent cet idéal dans tout le pays. Au XVIIIe siècle, le mouvement Silhak, le « savoir pratique », le tourne vers les réformes concrètes. Son empreinte demeure profonde dans la Corée d’aujourd’hui : respect des aînés, valorisation de l’éducation, rites familiaux et éthique du travail.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F44" s="1" t="s">
         <v>261</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2611,8 +2611,10 @@
       <c r="D9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>54</v>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9neutique_biblique" title=" Wikipedia"&gt;L’Herméneutique juive&lt;/a&gt; désigne l’ensemble des méthodes d’interprétation des textes sacrés du judaïsme : la Torah et la Bible hébraïque, puis la Mishna et le &lt;a href="https://fr.wikipedia.org/wiki/Talmud" title=" Wikipedia"&gt;Talmud&lt;/a&gt;. Elle repose sur une idée fondatrice : à côté de la Torah écrite, Moïse aurait reçu au Sinaï une Torah orale, transmise de maître à disciple, qui en donne le sens. Le texte n’est donc jamais clos, il appelle un commentaire sans fin, et l’étude elle-même devient un acte religieux. « La Torah a soixante-dix visages », dit un adage rabbinique.&lt;/p&gt; &lt;p&gt;Cette tradition prend forme avec les sages de l’époque du Second Temple. Hillel, vers le début de notre ère, formule sept règles d’interprétation, que Rabbi Ishmaël porte à treize au IIe siècle, tandis que Rabbi Akiva cherche un sens à chaque lettre. Le &lt;a href="https://fr.wikipedia.org/wiki/Midrash" title=" Wikipedia"&gt;midrash&lt;/a&gt; commente les versets pour en tirer soit des lois (&lt;em&gt;halakha&lt;/em&gt;), soit des récits et des leçons morales (&lt;em&gt;aggada&lt;/em&gt;). La Mishna, mise par écrit vers 200, puis les Talmuds de Jérusalem et de Babylone, achevés vers 400 et 500, consignent des débats où l’opinion minoritaire est conservée à côté de celle qui l’emporte. Au Moyen Âge, on distingue quatre niveaux de sens, résumés par le mot PaRDeS : &lt;em&gt;peshat&lt;/em&gt;, le sens littéral, &lt;em&gt;remez&lt;/em&gt;, l’allusion, &lt;em&gt;derash&lt;/em&gt;, l’interprétation, et &lt;em&gt;sod&lt;/em&gt;, le secret mystique de la Kabbale.&lt;/p&gt; &lt;p&gt;Rachi de Troyes, Maïmonide et Nahmanide en sont les grands commentateurs. Au XXe siècle, Emmanuel Levinas renouvelle la lecture du Talmud, et cette tradition a nourri les théories modernes de l’interprétation.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F9" s="1" t="s">
         <v>55</v>
@@ -2707,8 +2709,10 @@
       <c r="D12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>72</v>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9sychasme" title=" Wikipedia"&gt;L’Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme orthodoxe. Son nom vient du grec &lt;em&gt;hésychia&lt;/em&gt;, « silence, tranquillité » : il s’agit de faire taire les pensées pour s’unir à Dieu dans le calme du cœur. Ses racines remontent aux moines et ermites d’Égypte et de Syrie, les Pères du désert, aux IVe et Ve siècles, puis à des maîtres comme Jean Climaque, auteur de &lt;em&gt;L’Échelle sainte&lt;/em&gt; au VIIe siècle, et Syméon le Nouveau Théologien vers l’an mil.&lt;/p&gt; &lt;p&gt;Sa pratique centrale est la &lt;a href="https://fr.wikipedia.org/wiki/Pri%C3%A8re_du_c%C5%93ur" title=" Wikipedia"&gt;prière de Jésus&lt;/a&gt; : le moine répète sans cesse « Seigneur Jésus-Christ, Fils de Dieu, aie pitié de moi », au rythme de sa respiration, la tête inclinée vers la poitrine, pour que la prière descende de l’intelligence dans le cœur. Au XIVe siècle, des moines du mont Athos disent voir ainsi la lumière divine, celle qui entoura le Christ lors de sa Transfiguration sur le mont Thabor. Le moine calabrais Barlaam les accuse de superstition : Dieu ne peut pas être vu. &lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas" title=" Wikipedia"&gt;Grégoire Palamas&lt;/a&gt;, futur archevêque de Thessalonique, répond en distinguant l’essence de Dieu, à jamais inaccessible, et ses énergies, qui se communiquent réellement à l’homme et rendent possible sa « divinisation ». Des conciles réunis à Constantinople lui donnent raison en 1341 et en 1351.&lt;/p&gt; &lt;p&gt;En 1782 paraît la &lt;em&gt;Philocalie&lt;/em&gt;, recueil de textes hésychastes bientôt traduit en slavon. L’hésychasme inspire alors les « startsy », les maîtres spirituels de Russie, et les &lt;em&gt;Récits d’un pèlerin russe&lt;/em&gt; ; il reste au cœur de la spiritualité orthodoxe.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F12" s="1" t="s">
         <v>73</v>
@@ -4013,8 +4017,10 @@
       <c r="D54" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>314</v>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Silhak" title=" Wikipedia"&gt;Le Silhak&lt;/a&gt;, ou « savoir pratique », est un mouvement de réforme intellectuelle né en Corée au XVIIe siècle, sous la dynastie Joseon, et qui s’épanouit au XVIIIe. Il naît d’un pays ruiné par les invasions japonaises (1592-1598) puis mandchoues (1627 et 1636) : des lettrés reprochent alors au néoconfucianisme officiel de s’enfermer dans des querelles métaphysiques sur le principe et l’énergie, pendant que les paysans meurent de faim. Leur mot d’ordre, venu de Chine, est de « chercher la vérité dans les faits ».&lt;/p&gt; &lt;p&gt;Le premier grand nom en est Yu Hyeongwon (1622-1673), qui propose de redistribuer les terres à ceux qui les cultivent. Yi Ik (1681-1763) poursuit cette école du « bon gouvernement du monde » en critiquant l’esclavage, les privilèges héréditaires et le mépris du travail manuel. Une seconde branche, l’école des « études du Nord », autour de Pak Ji-won (1737-1805) et de Pak Je-ga, veut plutôt développer le commerce, les routes et les techniques, à l’exemple de la Chine des Qing. Le Silhak s’ouvre aussi aux sciences occidentales introduites en Chine par les jésuites : astronomie, cartographie, mathématiques.&lt;/p&gt; &lt;p&gt;Il culmine avec &lt;a href="https://fr.wikipedia.org/wiki/Jeong_Yak-yong" title=" Wikipedia"&gt;Jeong Yak-yong&lt;/a&gt; (1762-1836), dit Dasan, qui réunit les deux branches. Exilé dix-huit ans après la persécution des catholiques de 1801, il y écrit près de cinq cents volumes, dont un manuel pour bien administrer le peuple. Le calligraphe Kim Jeong-hui (1786-1856) en est l’un des derniers représentants. Marginalisé en son temps, le Silhak est aujourd’hui vu comme l’un des ferments de la modernité coréenne.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F54" s="1" t="s">
         <v>315</v>
@@ -4043,8 +4049,10 @@
       <c r="D55" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="E55" s="11" t="s">
-        <v>320</v>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martinisme" title=" Wikipedia"&gt;Le Martinisme&lt;/a&gt; est un courant ésotérique et mystique d’inspiration judéo-chrétienne, né en France au XVIIIe siècle dans les milieux de la franc-maçonnerie. Il doit son nom à deux hommes que l’on confond souvent : Martinès de Pasqually (vers 1727-1774), théurge à l’origine mal connue, et son disciple &lt;a href="https://fr.wikipedia.org/wiki/Louis-Claude_de_Saint-Martin" title=" Wikipedia"&gt;Louis-Claude de Saint-Martin&lt;/a&gt; (1743-1803), dit le « Philosophe inconnu ». Son thème central est la « réintégration » : le retour de l’être humain à la dignité spirituelle qu’il avait avant la chute.&lt;/p&gt; &lt;p&gt;Vers 1761, Martinès fonde l’ordre des Élus Coëns, dont les loges s’établissent à Bordeaux, Lyon et Paris. Dans son &lt;em&gt;Traité de la réintégration des êtres&lt;/em&gt;, il enseigne que l’homme, créé pour servir d’intermédiaire entre Dieu et le monde, a chuté par orgueil, comme Adam, et se trouve exilé dans la matière. Pour se racheter, il doit pratiquer l’ascèse, la prière et la théurgie, des rites destinés à entrer en contact avec les esprits bienfaisants. Saint-Martin, d’abord son secrétaire, délaisse ces rites pour une « voie intérieure », celle du cœur, nourrie par le mystique allemand Jacob Böhme. À Lyon, Jean-Baptiste Willermoz transmet leur doctrine au Rite écossais rectifié, une branche de la franc-maçonnerie qui existe toujours.&lt;/p&gt; &lt;p&gt;À la fin du XIXe siècle, l’occultiste Papus fonde un Ordre martiniste, et au XXe siècle Robert Ambelain fait renaître les Élus Coëns. On distingue depuis le « martinésisme », théurgique, et le « saint-martinisme », mystique. Joseph de Maistre, Balzac ou Franz von Baader ont lu Saint-Martin.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F55" s="9" t="s">
         <v>321</v>
@@ -4266,8 +4274,10 @@
       <c r="D62" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>359</v>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt;Le Donghak&lt;/a&gt;, ou « savoir de l’Orient », est un mouvement religieux et social fondé en Corée en 1860 par Choe Je-u (1824-1864), un lettré déclassé. Il naît dans une société Joseon minée par la corruption, les épidémies et la misère paysanne, et inquiète devant l’Occident : la Chine vient d’être humiliée par la seconde guerre de l’opium, et le catholicisme, appelé « savoir de l’Occident » (&lt;em&gt;seohak&lt;/em&gt;), progresse malgré les persécutions. Choe Je-u dit avoir reçu une révélation du « Seigneur du Ciel » et veut opposer au savoir étranger une voie coréenne.&lt;/p&gt; &lt;p&gt;Sa doctrine mêle le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale est que chaque être humain « porte en lui le Ciel » (&lt;em&gt;si cheonju&lt;/em&gt;) : il faut donc « servir l’homme comme le Ciel », enseigne son successeur Choe Si-hyeong, et le mouvement finira par dire que « l’homme est le Ciel » (&lt;em&gt;in nae cheon&lt;/em&gt;). Il en découle une égalité radicale entre les nobles et les serviteurs, les hommes et les femmes, les riches et les pauvres. Les fidèles récitent une formule sacrée de vingt et un caractères et attendent l’« ouverture » d’un monde nouveau.&lt;/p&gt; &lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement gagne les campagnes et inspire en 1894 la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_paysanne_Donghak" title=" Wikipedia"&gt;révolution paysanne du Donghak&lt;/a&gt;, menée par Jeon Bong-jun ; l’arrivée de troupes chinoises et japonaises pour l’écraser déclenche la guerre sino-japonaise. Rebaptisé Cheondogyo, « religion de la Voie céleste », en 1905, il joue un grand rôle dans le mouvement d’indépendance du 1er mars 1919.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F62" s="1" t="s">
         <v>360</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2834,8 +2834,10 @@
       <c r="D16" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>97</v>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme"  title=" Wikipedia"&gt;Le Confucianisme&lt;/a&gt; est la tradition de pensée issue de &lt;a href="https://fr.wikipedia.org/wiki/Confucius" title=" Wikipedia"&gt;Confucius&lt;/a&gt; (551-479 av. J.-C.), lettré de l’État de Lu, en Chine, qui chercha en vain un prince prêt à appliquer ses idées. Ses paroles, recueillies par ses disciples dans les &lt;em&gt;Entretiens&lt;/em&gt;, proposent de restaurer l’harmonie d’une société en crise non par la force ou par la loi, mais par la vertu, l’éducation et le respect des rites.&lt;/p&gt; &lt;p&gt;Son idéal est l’« homme de bien » (&lt;em&gt;junzi&lt;/em&gt;), qui se perfectionne sans cesse par l’étude. Les vertus cardinales sont l’humanité ou bienveillance (&lt;em&gt;ren&lt;/em&gt;), la droiture (&lt;em&gt;yi&lt;/em&gt;), les rites (&lt;em&gt;li&lt;/em&gt;), qui règlent avec justesse les relations humaines, la sagesse (&lt;em&gt;zhi&lt;/em&gt;) et la fidélité à la parole donnée (&lt;em&gt;xin&lt;/em&gt;). La société repose sur la famille et la piété filiale : chacun doit tenir son rôle dans les relations entre souverain et sujet, père et fils, époux, aînés et cadets, amis. Le prince gouverne par l’exemple, et les mots doivent correspondre aux choses : c’est la « rectification des noms ». Après Confucius, &lt;a href="https://fr.wikipedia.org/wiki/Mencius" title=" Wikipedia"&gt;Mencius&lt;/a&gt; affirme que la nature humaine est bonne, Xunzi qu’elle doit être redressée par l’éducation. Sous les Han, le confucianisme devient la doctrine officielle de l’empire, et les concours de recrutement des fonctionnaires, fondés sur ses classiques, durent jusqu’en 1905. Au XIIe siècle, Zhu Xi le renouvelle par une métaphysique : c’est le néoconfucianisme.&lt;/p&gt; &lt;p&gt;Il s’étend à la Corée, au Japon et au Viêt Nam. Combattu au XXe siècle comme cause du retard chinois, il connaît aujourd’hui un renouveau en Chine.&lt;/p&gt;  &lt;audio controls title="Le Confucianisme et les valeurs asiatiques par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-14.05.2019-ITEMA_22061347-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F16" s="9" t="s">
         <v>98</v>
@@ -3863,8 +3865,10 @@
       <c r="D49" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>287</v>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_vietnamienne" title=" Wikipedia"&gt;La Philosophie vietnamienne&lt;/a&gt; se caractérise par le Tam Giáo, les « trois enseignements » : une alliance durable entre le confucianisme, le bouddhisme et le taoïsme, à laquelle s’ajoutent le culte des ancêtres et celui des génies protecteurs des villages. Un adage vietnamien dit que « les trois enseignements ont une même source ». Chacun a son domaine : le confucianisme règle la famille et l’État, le bouddhisme la vie spirituelle, le taoïsme la médecine, la divination et les rites du quotidien.&lt;/p&gt; &lt;p&gt;Le bouddhisme arrive très tôt, dès les premiers siècles de notre ère, par la mer et par la Chine. Après l’indépendance, en 939, les dynasties Lý et Trần le favorisent : le roi &lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;Trần Nhân Tông&lt;/a&gt;, vainqueur des invasions mongoles, abdique en 1293 pour se faire moine et fonde l’école zen de Trúc Lâm, la « Forêt de bambous », proprement vietnamienne. Le confucianisme s’impose ensuite comme doctrine de l’État : le Temple de la Littérature est fondé à Hanoï en 1070, et les concours mandarinaux recrutent les fonctionnaires jusqu’en 1919. Mais les lettrés formés aux classiques confucéens pratiquaient souvent le bouddhisme dans leur vie personnelle et se retiraient volontiers en ermites taoïstes : les trois voies se complètent plus qu’elles ne s’opposent. &lt;a href="https://fr.wikipedia.org/wiki/Nguy%E1%BB%85n_Tr%C3%A3i" title=" Wikipedia"&gt;Nguyễn Trãi&lt;/a&gt; au XVe siècle, Nguyễn Bỉnh Khiêm au XVIe ou Lê Quý Đôn au XVIIIe illustrent cette sagesse composite.&lt;/p&gt; &lt;p&gt;Au XXe siècle, ce syncrétisme inspire de nouvelles religions comme le caodaïsme, tandis que le marxisme devient la doctrine officielle. L’empreinte du Tam Giáo demeure dans les rites familiaux et la morale.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F49" s="1" t="s">
         <v>288</v>
@@ -4306,8 +4310,10 @@
       <c r="D63" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>365</v>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_(art)"  title=" Wikipedia"&gt;Le Symbolisme&lt;/a&gt; est un courant littéraire, artistique et philosophique né en France dans les années 1880 et qui s’épanouit en Russie au tournant du XXe siècle. Il prend pour modèle le sonnet « Correspondances » de &lt;a href="https://fr.wikipedia.org/wiki/Charles_Baudelaire" title=" Wikipedia"&gt;Baudelaire&lt;/a&gt;, où la nature est une « forêt de symboles » : derrière le monde visible se cache une réalité spirituelle que le poète peut faire pressentir. Le manifeste de Jean Moréas paraît en 1886 ; Mallarmé, Verlaine, et en peinture Gustave Moreau ou Odilon Redon, incarnent le mouvement.&lt;/p&gt; &lt;p&gt;En Russie, il naît dans les années 1890 avec Dmitri Merejkovski, Valéri Brioussov et Constantin Balmont, puis prend une dimension métaphysique et religieuse avec une seconde génération, nourrie de la philosophie de &lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir Soloviev&lt;/a&gt; et de sa figure de la Sophia, la Sagesse divine. Pour Viatcheslav Ivanov, dont l’appartement de Saint-Pétersbourg, la « Tour », est le grand salon de l’époque, l’art doit aller « du réel au plus réel ». Pour Andreï Biély, le symbole unit la connaissance et la création, et le symbolisme devient une véritable vision du monde. Alexandre Blok chante la « Belle Dame », figure mystique de la Sophia, avant d’écrire en 1918 &lt;em&gt;Les Douze&lt;/em&gt;, poème de la révolution. Ces poètes-philosophes conçoivent l’art comme une « théurgie », une action capable de transformer le monde et de préparer sa transfiguration. Le symbolisme russe mêle la mystique orthodoxe, l’idéalisme allemand et Nietzsche.&lt;/p&gt; &lt;p&gt;Vers 1910, il entre en crise et laisse place à l’acméisme et au futurisme. Il a profondément marqué la philosophie religieuse russe de l’âge d’argent.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F63" s="1" t="s">
         <v>366</v>
@@ -4550,8 +4556,10 @@
       <c r="D71" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>410</v>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Logique_paracoh%C3%A9rente"  title=" Wikipedia"&gt;La Logique paraconsistante&lt;/a&gt; désigne les systèmes logiques qui peuvent contenir des contradictions sans s’effondrer. En logique classique, en effet, une seule contradiction suffit à tout démontrer : de « A et non-A », on peut déduire n’importe quelle proposition. C’est le &lt;a href="https://fr.wikipedia.org/wiki/Principe_d%27explosion" title=" Wikipedia"&gt;principe d’explosion&lt;/a&gt;, connu depuis le Moyen Âge sous la formule « du contradictoire suit n’importe quoi ». Une logique paraconsistante bloque cette explosion : une contradiction locale y reste locale, sans contaminer tout le reste.&lt;/p&gt; &lt;p&gt;L’idée apparaît en 1910, à Kazan, chez le philosophe russe Nikolaï Vassiliev (1880-1940). Il imagine une « logique imaginaire » où la loi de non-contradiction n’est plus un axiome nécessaire, de même que les géométries non euclidiennes, nées à Kazan avec Lobatchevski, avaient abandonné le postulat des parallèles. La même année, le Polonais Jan Łukasiewicz critique le principe de non-contradiction d’Aristote. Son élève Stanisław Jaśkowski construit en 1948 le premier système formel paraconsistant, et le Brésilien Newton da Costa développe à partir de 1963 toute une famille de ces logiques. Le mot « paraconsistant » est forgé en 1976 par le philosophe péruvien Francisco Miró Quesada. Certains vont plus loin, comme l’Australien &lt;a href="https://fr.wikipedia.org/wiki/Graham_Priest" title=" Wikipedia"&gt;Graham Priest&lt;/a&gt; : selon son « dialéthéisme », certaines contradictions sont vraies, par exemple le paradoxe du menteur, « cette phrase est fausse ».&lt;/p&gt; &lt;p&gt;Ces logiques servent en informatique, pour raisonner avec des bases de données incohérentes, en droit, face à des normes contradictoires, et en philosophie des sciences, quand des théories en conflit doivent coexister.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F71" s="1" t="s">
         <v>411</v>
@@ -4701,8 +4709,10 @@
       <c r="D76" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>439</v>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nkrumaism" title=" Wikipedia (en)"&gt;Le Consciencisme&lt;/a&gt; est la philosophie politique de &lt;a href="https://fr.wikipedia.org/wiki/Kwame_Nkrumah" title=" Wikipedia"&gt;Kwame Nkrumah&lt;/a&gt; (1909-1972), qui conduit la Gold Coast britannique à l’indépendance en 1957 sous le nom de Ghana, premier pays d’Afrique subsaharienne à se libérer de la colonisation. Il l’expose dans &lt;em&gt;Consciencism : Philosophy and Ideology for Decolonization&lt;/em&gt; (1964). Pour Nkrumah, la décolonisation ne sera achevée que si elle s’accompagne d’une libération des consciences : l’Afrique doit penser par elle-même la société qu’elle veut construire.&lt;/p&gt; &lt;p&gt;Il part d’un constat : la conscience africaine est désormais faite de trois héritages, la tradition africaine, l’islam et le christianisme européen, qui coexistent en conflit. Le consciencisme veut les réunir en une synthèse cohérente, guidée par les valeurs humanistes et égalitaires de l’Afrique traditionnelle. Selon Nkrumah, les sociétés africaines précoloniales étaient « communalistes » : la terre appartenait à tous et nul ne vivait du travail d’autrui. Le socialisme n’est donc pas, pour l’Afrique, une importation, mais la forme moderne de ses propres valeurs ; il peut s’y construire sans passer par la lutte des classes. Sur le plan philosophique, Nkrumah défend un matérialisme dans lequel l’esprit naît de la matière, tout en affirmant l’égale dignité de chaque être humain. Son projet politique est le &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; : une Afrique unie, seule capable de résister au néocolonialisme.&lt;/p&gt; &lt;p&gt;Renversé par un coup d’État en 1966, Nkrumah meurt en exil. Le consciencisme reste une référence des philosophies africaines de la décolonisation ; Kwame Gyekye en a critiqué l’idéalisation du passé.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F76" s="1" t="s">
         <v>440</v>
@@ -4730,8 +4740,10 @@
       <c r="D77" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>444</v>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Minjung" title=" Wikipedia"&gt;La pensée Minjung&lt;/a&gt;, du coréen &lt;em&gt;minjung&lt;/em&gt;, « le peuple » au sens des masses opprimées, est un courant théologique et philosophique né en Corée du Sud dans les années 1970, sous la dictature de Park Chung-hee. Elle naît parmi les chrétiens engagés aux côtés des ouvriers et des étudiants en lutte pour la démocratie, après l’immolation en 1970 de l’ouvrier du textile Jeon Tae-il, qui réclamait l’application du droit du travail.&lt;/p&gt; &lt;p&gt;Le &lt;em&gt;minjung&lt;/em&gt;, ce sont ceux qui sont opprimés politiquement, exploités économiquement et tenus à l’écart de la culture. Pour le bibliste Ahn Byung-mu, qui relit l’Évangile de Marc à partir de la foule qui suit Jésus, et pour le théologien Suh Nam-dong, ce peuple souffrant n’est pas seulement l’objet de la compassion : il est le véritable sujet de l’histoire, et c’est dans ses luttes que se révèle le sens des Écritures. La pensée Minjung s’appuie sur une notion coréenne, le &lt;em&gt;han&lt;/em&gt;, ce sentiment de souffrance et de ressentiment accumulés au fil des générations ; le poète Kim Chi-ha cherche comment en briser le cercle sans tomber dans la vengeance. Elle valorise aussi les formes de la culture populaire, comme la danse masquée ou le chant épique du &lt;em&gt;pansori&lt;/em&gt;. Elle a pour précurseur la philosophie de la « graine » (&lt;em&gt;ssial&lt;/em&gt;) de Ham Seok-heon, qui voyait dans le peuple le germe vivant de l’histoire.&lt;/p&gt; &lt;p&gt;Proche des théologies de la libération d’Amérique latine, la pensée Minjung a nourri la résistance au régime militaire, du &lt;a href="https://fr.wikipedia.org/wiki/Soul%C3%A8vement_de_Gwangju" title=" Wikipedia"&gt;soulèvement de Gwangju&lt;/a&gt; en 1980 à la démocratisation de 1987.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F77" s="1" t="s">
         <v>445</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2355,7 +2355,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N103"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.53"/>
@@ -2443,6 +2443,21 @@
       <c r="N3" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nature</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Famille</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Issu_de</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="n">
@@ -2475,6 +2490,16 @@
       <c r="M4" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="269.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -2507,6 +2532,16 @@
       <c r="M5" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="226.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -2536,6 +2571,16 @@
       <c r="M6" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
+        </is>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="211.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -2564,6 +2609,16 @@
       </c>
       <c r="M7" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védas et brahmanisme</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2600,6 +2655,21 @@
       <c r="N8" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christianisme antique et médiéval</t>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoplatonisme</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -2634,6 +2704,16 @@
       <c r="N9" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -2662,6 +2742,16 @@
       </c>
       <c r="M10" s="2" t="s">
         <v>64</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
       </c>
     </row>
     <row r="11" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2698,6 +2788,21 @@
       <c r="N11" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ésotérismes et gnoses</t>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique;Platonisme</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -2731,6 +2836,21 @@
       </c>
       <c r="N12" s="1" t="s">
         <v>76</v>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christianisme antique et médiéval</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
       </c>
     </row>
     <row r="13" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2764,6 +2884,16 @@
       <c r="M13" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
@@ -2793,6 +2923,16 @@
       <c r="M14" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
@@ -2821,6 +2961,21 @@
       </c>
       <c r="M15" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védas et brahmanisme</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védisme</t>
+        </is>
       </c>
     </row>
     <row r="16" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2856,6 +3011,16 @@
       <c r="M16" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="n">
@@ -2888,6 +3053,16 @@
       <c r="M17" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées africaines</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -2917,6 +3092,16 @@
       <c r="M18" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -2945,6 +3130,21 @@
       </c>
       <c r="M19" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sâmkhya</t>
+        </is>
       </c>
     </row>
     <row r="20" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2978,6 +3178,21 @@
       <c r="M20" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védas et brahmanisme</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="n">
@@ -3013,6 +3228,16 @@
       <c r="N21" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="n">
@@ -3045,6 +3270,21 @@
       <c r="M22" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="n">
@@ -3077,6 +3317,16 @@
       <c r="M23" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="n">
@@ -3109,6 +3359,16 @@
       <c r="M24" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
@@ -3137,6 +3397,16 @@
       </c>
       <c r="M25" s="2" t="s">
         <v>101</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+        </is>
       </c>
     </row>
     <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3170,6 +3440,21 @@
       <c r="M26" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
@@ -3199,6 +3484,21 @@
       <c r="M27" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
@@ -3227,6 +3527,21 @@
       </c>
       <c r="M28" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
       </c>
     </row>
     <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3260,6 +3575,21 @@
       <c r="M29" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="n">
@@ -3292,6 +3622,21 @@
       <c r="M30" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
@@ -3323,6 +3668,21 @@
       </c>
       <c r="N31" s="1" t="s">
         <v>101</v>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
       </c>
     </row>
     <row r="32" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3358,6 +3718,21 @@
       <c r="M32" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védisme</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="n">
@@ -3390,6 +3765,21 @@
       <c r="M33" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zoroastrisme</t>
+        </is>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
@@ -3419,6 +3809,21 @@
       <c r="M34" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
@@ -3451,6 +3856,21 @@
       <c r="N35" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="353.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
@@ -3479,6 +3899,16 @@
       </c>
       <c r="M36" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
       </c>
     </row>
     <row r="37" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3512,6 +3942,21 @@
       <c r="M37" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kalâm</t>
+        </is>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="n">
@@ -3544,6 +3989,21 @@
       <c r="M38" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
@@ -3572,6 +4032,21 @@
       </c>
       <c r="M39" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védanta</t>
+        </is>
       </c>
     </row>
     <row r="40" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3608,6 +4083,16 @@
       <c r="N40" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
@@ -3636,6 +4121,21 @@
       </c>
       <c r="M41" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aristotélisme;Néoplatonisme</t>
+        </is>
       </c>
     </row>
     <row r="42" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3669,6 +4169,21 @@
       <c r="M42" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mutazilisme</t>
+        </is>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
@@ -3701,6 +4216,21 @@
       <c r="M43" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique juive;Falsafa</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
@@ -3732,6 +4262,21 @@
       <c r="M44" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
@@ -3743,8 +4288,10 @@
       <c r="D45" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>265</v>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_azt%C3%A8que" title=" Wikipedia"&gt;La Pensée nahua&lt;/a&gt; désigne la réflexion philosophique des peuples de langue nahuatl, dont les Aztèques ou Mexicas, dans le Mexique central avant la conquête espagnole de 1521. Elle était portée par les &lt;em&gt;tlamatinime&lt;/em&gt;, « ceux qui savent quelque chose », sages et maîtres du &lt;em&gt;calmecac&lt;/em&gt;, l’école où l’on formait les jeunes nobles. Nous la connaissons par des codex, des chants et des discours recueillis après la conquête, notamment par le franciscain Bernardino de Sahagún.&lt;/p&gt; &lt;p&gt;L’historien mexicain &lt;a href="https://fr.wikipedia.org/wiki/Miguel_Le%C3%B3n-Portilla" title=" Wikipedia"&gt;Miguel León-Portilla&lt;/a&gt; l’a fait connaître dans &lt;em&gt;La filosofía náhuatl estudiada en sus fuentes&lt;/em&gt; (1956). Les sages s’interrogent sur la fragilité de l’existence : sur terre tout est passager, comme les fleurs qui se fanent, et l’on se demande si quelque chose est vrai, enraciné. Leur réponse est &lt;em&gt;in xochitl in cuicatl&lt;/em&gt;, « la fleur et le chant », c’est-à-dire la poésie, seule capable peut-être de dire le vrai. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Nezahualc%C3%B3yotl" title=" Wikipedia"&gt;Nezahualcóyotl&lt;/a&gt;, souverain de Texcoco au XVe siècle, auquel on attribue de nombreux poèmes, en est la grande figure. Le principe suprême, Ometeotl, « dieu de la dualité », unit le masculin et le féminin ; le monde est fait de couples complémentaires, vie et mort, ordre et désordre, en équilibre instable. Le temps est cyclique : quatre « soleils », quatre âges du monde, ont déjà été détruits, et nous vivons sous le cinquième.&lt;/p&gt; &lt;p&gt;Plus récemment, le philosophe James Maffie a lu dans le &lt;em&gt;teotl&lt;/em&gt; une énergie sacrée, unique et toujours en mouvement, dont toutes choses sont des aspects. Cette pensée est aujourd’hui étudiée comme une véritable tradition philosophique.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F45" s="1" t="s">
         <v>266</v>
@@ -3760,6 +4307,21 @@
       </c>
       <c r="M45" s="2" t="s">
         <v>64</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme mésoaméricain</t>
+        </is>
       </c>
     </row>
     <row r="46" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3792,6 +4354,21 @@
       </c>
       <c r="N46" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
+      <c r="Q46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsafa;Soufisme</t>
+        </is>
       </c>
     </row>
     <row r="47" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3825,6 +4402,21 @@
       <c r="M47" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
@@ -3854,6 +4446,21 @@
       <c r="M48" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen;Shintoïsme</t>
+        </is>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
@@ -3885,6 +4492,21 @@
       <c r="M49" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme;Bouddhisme Mahayana</t>
+        </is>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="366" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
@@ -3914,6 +4536,16 @@
       <c r="M50" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
@@ -3945,6 +4577,21 @@
       </c>
       <c r="M51" s="2" t="s">
         <v>101</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
       </c>
     </row>
     <row r="52" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3978,6 +4625,21 @@
       <c r="M52" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shintoïsme</t>
+        </is>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="n">
@@ -4010,6 +4672,16 @@
       <c r="M53" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réveils de l’islam moderne</t>
+        </is>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
@@ -4040,6 +4712,21 @@
       </c>
       <c r="M54" s="2" t="s">
         <v>101</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme coréen</t>
+        </is>
       </c>
     </row>
     <row r="55" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4075,6 +4762,21 @@
       <c r="M55" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ésotérismes et gnoses</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="n">
@@ -4107,6 +4809,21 @@
       <c r="M56" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Romantisme;Idéalisme allemand</t>
+        </is>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
@@ -4139,6 +4856,21 @@
       <c r="M57" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réveils de l’islam moderne</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumières</t>
+        </is>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
@@ -4150,8 +4882,10 @@
       <c r="D58" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>339</v>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9osophie" title=" Wikipedia"&gt;La Théosophie&lt;/a&gt; est un courant ésotérique et spirituel fondé par &lt;a href="https://fr.wikipedia.org/wiki/Helena_Blavatsky" title=" Wikipedia"&gt;Helena Blavatsky&lt;/a&gt; (1831-1891), née dans l’Empire russe, qui crée à New York en 1875, avec le colonel américain Henry Steel Olcott et William Quan Judge, la &lt;a href="https://fr.wikipedia.org/wiki/Soci%C3%A9t%C3%A9_th%C3%A9osophique" title=" Wikipedia"&gt;Société théosophique&lt;/a&gt;. Le mot, du grec &lt;em&gt;theos&lt;/em&gt;, « dieu », et &lt;em&gt;sophia&lt;/em&gt;, « sagesse », signifie « sagesse divine » : la Théosophie se veut la redécouverte d’une sagesse universelle et cachée, dont les religions, les sciences et les philosophies ne seraient que des expressions partielles.&lt;/p&gt; &lt;p&gt;La Société se donne trois buts : former le noyau d’une fraternité universelle de l’humanité, sans distinction de race, de croyance, de sexe ou de caste ; encourager l’étude comparée des religions, des philosophies et des sciences ; étudier les lois inexpliquées de la nature et les pouvoirs latents de l’homme. Blavatsky expose sa doctrine dans &lt;em&gt;Isis dévoilée&lt;/em&gt; (1877) et &lt;em&gt;La Doctrine secrète&lt;/em&gt; (1888), où elle mêle le bouddhisme, l’hindouisme, la Kabbale et le néoplatonisme : l’univers procède d’un principe unique, l’humanité traverse de longs cycles d’évolution et l’âme progresse par réincarnations successives selon la loi du karma. Elle dit tenir ces enseignements de « Maîtres » vivant au Tibet. Les fondateurs s’installent en Inde en 1879, et le siège est fixé à Adyar, près de Madras, en 1882.&lt;/p&gt; &lt;p&gt;Annie Besant, présidente à partir de 1907, présente le jeune Jiddu Krishnamurti comme un futur instructeur du monde, rôle qu’il refuse en 1929. Rudolf Steiner s’en sépare pour fonder l’anthroposophie. La Théosophie a marqué des artistes comme Kandinsky et Mondrian, le mouvement New Age et la diffusion en Occident de l’hindouisme et du bouddhisme.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F58" s="1" t="s">
         <v>340</v>
@@ -4167,6 +4901,21 @@
       </c>
       <c r="M58" s="2" t="s">
         <v>76</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ésotérismes et gnoses</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hermétisme;Hindouisme</t>
+        </is>
       </c>
     </row>
     <row r="59" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4203,6 +4952,21 @@
       <c r="N59" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="O59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
+        </is>
+      </c>
+      <c r="Q59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idéalisme allemand</t>
+        </is>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="n">
@@ -4235,6 +4999,21 @@
       <c r="M60" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme;Lumières</t>
+        </is>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="n">
@@ -4267,6 +5046,21 @@
       <c r="M61" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophilisme</t>
+        </is>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
@@ -4299,6 +5093,21 @@
       <c r="M62" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme coréen;Taoïsme</t>
+        </is>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
@@ -4329,6 +5138,21 @@
       </c>
       <c r="M63" s="2" t="s">
         <v>76</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophiologie</t>
+        </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4362,6 +5186,21 @@
       <c r="M64" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réveils de l’islam moderne</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nahda</t>
+        </is>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="n">
@@ -4394,6 +5233,16 @@
       <c r="M65" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
+        </is>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
@@ -4426,6 +5275,21 @@
       <c r="N66" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="O66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
+        </is>
+      </c>
+      <c r="Q66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
@@ -4455,6 +5319,21 @@
       <c r="M67" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaïnisme;Néo-védanta</t>
+        </is>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
@@ -4484,6 +5363,21 @@
       <c r="M68" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme</t>
+        </is>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
@@ -4516,6 +5410,21 @@
       <c r="M69" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen;Idéalisme allemand</t>
+        </is>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
@@ -4545,6 +5454,21 @@
       <c r="M70" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
@@ -4576,6 +5500,16 @@
       <c r="M71" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie analytique et pragmatisme</t>
+        </is>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="n">
@@ -4587,8 +5521,10 @@
       <c r="D72" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>416</v>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nouveau_confucianisme"  title=" Wikipedia"&gt;Le nouveau confucianisme&lt;/a&gt; est un courant philosophique chinois du XXe siècle qui veut renouveler la tradition confucéenne pour l’accorder à la modernité. Il naît en réaction au mouvement du 4 Mai 1919 et à la Nouvelle Culture, qui rejetaient le confucianisme comme responsable du retard de la Chine et en appelaient à « Monsieur Science » et à « Monsieur Démocratie ». Ses penseurs veulent montrer qu’un confucianisme repensé peut accueillir la science et la démocratie sans perdre sa sagesse morale.&lt;/p&gt; &lt;p&gt;Le point de départ est l’ouvrage de &lt;a href="https://fr.wikipedia.org/wiki/Liang_Shuming" title=" Wikipedia"&gt;Liang Shuming&lt;/a&gt;, &lt;em&gt;Les Cultures d’Orient et d’Occident et leurs philosophies&lt;/em&gt; (1921), qui compare les voies de l’Occident, de la Chine et de l’Inde. &lt;a href="https://fr.wikipedia.org/wiki/Xiong_Shili" title=" Wikipedia"&gt;Xiong Shili&lt;/a&gt; donne au courant une métaphysique dans son &lt;em&gt;Nouveau traité de la conscience seule&lt;/em&gt; (1932) : s’inspirant du &lt;em&gt;Livre des mutations&lt;/em&gt;, il critique le bouddhisme pour qui le monde est illusion, et pense la réalité comme un mouvement créateur continu. Feng Youlan, dans son &lt;em&gt;Nouvel enseignement du principe&lt;/em&gt; (1939), relit Zhu Xi à l’aide de la logique moderne.&lt;/p&gt; &lt;p&gt;Après 1949, le courant se poursuit surtout à Hong Kong et à Taïwan. En 1958, Mou Zongsan, Tang Junyi, Xu Fuguan et Zhang Junmai publient un manifeste adressé au monde sur la culture chinoise. Mou Zongsan, traducteur des trois &lt;em&gt;Critiques&lt;/em&gt; de Kant, dialogue avec lui pour fonder une « métaphysique morale ». Une troisième génération, avec &lt;a href="https://fr.wikipedia.org/wiki/Tu_Weiming" title=" Wikipedia"&gt;Tu Weiming&lt;/a&gt; ou Liu Shu-hsien, a porté ce courant dans les universités américaines ; il connaît depuis les années 1980 un important renouveau en Chine continentale.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F72" s="1" t="s">
         <v>417</v>
@@ -4607,6 +5543,21 @@
       </c>
       <c r="M72" s="2" t="s">
         <v>101</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
       </c>
     </row>
     <row r="73" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4640,6 +5591,21 @@
       <c r="M73" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan-africanisme</t>
+        </is>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
@@ -4669,6 +5635,21 @@
       <c r="M74" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme</t>
+        </is>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
@@ -4680,8 +5661,10 @@
       <c r="D75" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>434</v>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;La Philosophie africaine&lt;/a&gt; désigne la réflexion philosophique menée en Afrique ou par des penseurs africains, mais aussi le débat sur ce que peut être une telle philosophie. Les traditions de pensée du continent sont anciennes, des sagesses de l’Égypte pharaonique au &lt;em&gt;Hatata&lt;/em&gt; éthiopien du XVIIe siècle attribué à Zera Yacob ; mais la discipline moderne prend son essor en 1945, avec &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Tempels reconstruit, à partir de l’observation des Luba du Congo, une « vision du monde » cohérente centrée sur la force vitale : être, c’est être force, et le bien consiste à accroître la vie. Le prêtre rwandais Alexis Kagame prolonge cette démarche en étudiant les catégories de la langue kinyarwanda. Ce courant, appelé ethnophilosophie, est vivement critiqué par le Béninois &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976) : décrire une pensée collective et anonyme, que personne ne discute, ce n’est pas faire de la philosophie, qui suppose des auteurs, des textes et la critique.&lt;/p&gt; &lt;p&gt;Entre ces deux pôles, d’autres voies se sont ouvertes. Le Kényan Henry Odera Oruka recueille auprès des sages des villages une « philosophie de la sagesse » (&lt;em&gt;sage philosophy&lt;/em&gt;) personnelle et critique. Le Ghanéen &lt;a href="https://fr.wikipedia.org/wiki/Kwasi_Wiredu" title=" Wikipedia"&gt;Kwasi Wiredu&lt;/a&gt; appelle à une « décolonisation conceptuelle » qui examine les notions héritées de l’Occident à la lumière des langues africaines. Le Congolais Valentin-Yves Mudimbe étudie la manière dont l’Afrique a été « inventée » par le regard colonial. Le débat porte encore sur l’universalité de la raison.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F75" s="1" t="s">
         <v>435</v>
@@ -4697,6 +5680,16 @@
       </c>
       <c r="M75" s="2" t="s">
         <v>64</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées africaines</t>
+        </is>
       </c>
     </row>
     <row r="76" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4729,6 +5722,21 @@
       <c r="M76" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées africaines</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socialisme africain</t>
+        </is>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
@@ -4761,6 +5769,16 @@
       <c r="M77" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologies et philosophies de la libération</t>
+        </is>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
@@ -4772,8 +5790,10 @@
       <c r="D78" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>450</v>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buen_vivir" title=" Wikipedia"&gt;Le Buen Vivir&lt;/a&gt;, « bien vivre » en espagnol, traduit le &lt;em&gt;sumak kawsay&lt;/em&gt; des Quechuas et le &lt;em&gt;suma qamaña&lt;/em&gt; des Aymaras. C’est une philosophie issue des cosmovisions autochtones des Andes, formulée en termes contemporains à partir des années 1990 par des intellectuels et des mouvements indigènes d’Équateur et de Bolivie, rejoints par des penseurs critiques du développement.&lt;/p&gt; &lt;p&gt;Il s’oppose à l’idée occidentale du développement, mesuré par la croissance économique et l’accumulation de biens. Bien vivre, ce n’est pas vivre mieux, c’est-à-dire toujours plus, aux dépens des autres et de la nature : c’est vivre en harmonie au sein de la communauté et avec la &lt;a href="https://fr.wikipedia.org/wiki/Pachamama" title=" Wikipedia"&gt;Pachamama&lt;/a&gt;, la Terre-Mère. L’être humain n’y est ni séparé de la nature ni placé au-dessus d’elle : il fait partie d’un tout vivant tissé de relations, de réciprocité et de complémentarité, où les montagnes, les eaux et les êtres vivants ont leur place. La richesse tient à la qualité des liens plutôt qu’à l’abondance des choses. Ses défenseurs, comme l’économiste équatorien Alberto Acosta ou l’Uruguayen Eduardo Gudynas, y voient une alternative au modèle extractiviste.&lt;/p&gt; &lt;p&gt;La Constitution de l’Équateur de 2008 inscrit le &lt;em&gt;sumak kawsay&lt;/em&gt; parmi ses principes et reconnaît des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_la_nature" title=" Wikipedia"&gt;droits à la nature&lt;/a&gt; elle-même, une première mondiale. La Constitution bolivienne de 2009 en fait un principe éthique de l’État, et des lois de 2010 et 2012 y consacrent les droits de la Terre-Mère. Mais ces deux pays ont continué d’exploiter pétrole et minerais, ce qui nourrit le débat entre l’idéal et son usage politique.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F78" s="1" t="s">
         <v>451</v>
@@ -4789,6 +5809,16 @@
       </c>
       <c r="M78" s="2" t="s">
         <v>64</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
       </c>
     </row>
     <row r="79" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4817,6 +5847,21 @@
       <c r="M79" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouismes de dévotion</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bhakti;Soufisme</t>
+        </is>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1">
@@ -4863,6 +5908,21 @@
           <t xml:space="preserve">asie-est</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1">
@@ -4908,6 +5968,21 @@
           <t xml:space="preserve">asie-est</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1">
@@ -4949,6 +6024,21 @@
         </is>
       </c>
       <c r="N82"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1">
@@ -4990,6 +6080,21 @@
         </is>
       </c>
       <c r="N83"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana;Madhyamaka</t>
+        </is>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1">
@@ -5031,6 +6136,21 @@
         </is>
       </c>
       <c r="N84"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana;Yogācāra</t>
+        </is>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1">
@@ -5072,6 +6192,21 @@
         </is>
       </c>
       <c r="N85"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouismes de dévotion</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme</t>
+        </is>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1">
@@ -5113,6 +6248,21 @@
         </is>
       </c>
       <c r="N86"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouismes de dévotion</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme</t>
+        </is>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1">
@@ -5154,6 +6304,21 @@
         </is>
       </c>
       <c r="N87"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Advaïta Védanta;Brahmoïsme</t>
+        </is>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1">
@@ -5195,6 +6360,16 @@
         </is>
       </c>
       <c r="N88"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1">
@@ -5236,6 +6411,21 @@
         </is>
       </c>
       <c r="N89"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kalâm</t>
+        </is>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1">
@@ -5281,6 +6471,21 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique juive;Néoplatonisme</t>
+        </is>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1">
@@ -5322,6 +6527,21 @@
         </is>
       </c>
       <c r="N91"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1">
@@ -5367,6 +6587,21 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumières</t>
+        </is>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1">
@@ -5408,6 +6643,21 @@
         </is>
       </c>
       <c r="N93"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ishraqisme;Soufisme</t>
+        </is>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1">
@@ -5449,6 +6699,21 @@
         </is>
       </c>
       <c r="N94"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophilisme;Néoplatonisme</t>
+        </is>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1">
@@ -5494,6 +6759,21 @@
           <t xml:space="preserve">asie-est</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophilisme</t>
+        </is>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1">
@@ -5535,6 +6815,21 @@
         </is>
       </c>
       <c r="N96"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées africaines</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Négritude</t>
+        </is>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1">
@@ -5576,6 +6871,21 @@
         </is>
       </c>
       <c r="N97"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées africaines</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pan-africanisme;Marxisme</t>
+        </is>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1">
@@ -5621,6 +6931,21 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologies et philosophies de la libération</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme</t>
+        </is>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1">
@@ -5662,6 +6987,21 @@
         </is>
       </c>
       <c r="N99"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologies et philosophies de la libération</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de la libération</t>
+        </is>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1">
@@ -5703,6 +7043,21 @@
         </is>
       </c>
       <c r="N100"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Négritude</t>
+        </is>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1">
@@ -5744,6 +7099,21 @@
         </is>
       </c>
       <c r="N101"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie de la libération;Anticolonialisme</t>
+        </is>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1">
@@ -5785,6 +7155,16 @@
         </is>
       </c>
       <c r="N102"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+        </is>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1">
@@ -5826,6 +7206,21 @@
         </is>
       </c>
       <c r="N103"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme;Confucianisme</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2621,88 +2621,80 @@
         </is>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="n">
-        <v>1090</v>
-      </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="2" t="s">
-        <v>49</v>
+    <row r="8" customFormat="false" ht="353.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>720</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>720</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le kalâm musulman par ikarim</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>216</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Christianisme antique et médiéval</t>
-        </is>
-      </c>
-      <c r="Q8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Néoplatonisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9neutique_biblique" title=" Wikipedia"&gt;L’Herméneutique juive&lt;/a&gt; désigne l’ensemble des méthodes d’interprétation des textes sacrés du judaïsme : la Torah et la Bible hébraïque, puis la Mishna et le &lt;a href="https://fr.wikipedia.org/wiki/Talmud" title=" Wikipedia"&gt;Talmud&lt;/a&gt;. Elle repose sur une idée fondatrice : à côté de la Torah écrite, Moïse aurait reçu au Sinaï une Torah orale, transmise de maître à disciple, qui en donne le sens. Le texte n’est donc jamais clos, il appelle un commentaire sans fin, et l’étude elle-même devient un acte religieux. « La Torah a soixante-dix visages », dit un adage rabbinique.&lt;/p&gt; &lt;p&gt;Cette tradition prend forme avec les sages de l’époque du Second Temple. Hillel, vers le début de notre ère, formule sept règles d’interprétation, que Rabbi Ishmaël porte à treize au IIe siècle, tandis que Rabbi Akiva cherche un sens à chaque lettre. Le &lt;a href="https://fr.wikipedia.org/wiki/Midrash" title=" Wikipedia"&gt;midrash&lt;/a&gt; commente les versets pour en tirer soit des lois (&lt;em&gt;halakha&lt;/em&gt;), soit des récits et des leçons morales (&lt;em&gt;aggada&lt;/em&gt;). La Mishna, mise par écrit vers 200, puis les Talmuds de Jérusalem et de Babylone, achevés vers 400 et 500, consignent des débats où l’opinion minoritaire est conservée à côté de celle qui l’emporte. Au Moyen Âge, on distingue quatre niveaux de sens, résumés par le mot PaRDeS : &lt;em&gt;peshat&lt;/em&gt;, le sens littéral, &lt;em&gt;remez&lt;/em&gt;, l’allusion, &lt;em&gt;derash&lt;/em&gt;, l’interprétation, et &lt;em&gt;sod&lt;/em&gt;, le secret mystique de la Kabbale.&lt;/p&gt; &lt;p&gt;Rachi de Troyes, Maïmonide et Nahmanide en sont les grands commentateurs. Au XXe siècle, Emmanuel Levinas renouvelle la lecture du Talmud, et cette tradition a nourri les théories modernes de l’interprétation.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>56</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
       <c r="J9" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
@@ -2711,11 +2703,16 @@
       </c>
       <c r="P9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée juive</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Christianisme antique et médiéval</t>
+        </is>
+      </c>
+      <c r="Q9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoplatonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>-1000</v>
       </c>
@@ -2723,119 +2720,114 @@
         <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9neutique_biblique" title=" Wikipedia"&gt;L’Herméneutique juive&lt;/a&gt; désigne l’ensemble des méthodes d’interprétation des textes sacrés du judaïsme : la Torah et la Bible hébraïque, puis la Mishna et le &lt;a href="https://fr.wikipedia.org/wiki/Talmud" title=" Wikipedia"&gt;Talmud&lt;/a&gt;. Elle repose sur une idée fondatrice : à côté de la Torah écrite, Moïse aurait reçu au Sinaï une Torah orale, transmise de maître à disciple, qui en donne le sens. Le texte n’est donc jamais clos, il appelle un commentaire sans fin, et l’étude elle-même devient un acte religieux. « La Torah a soixante-dix visages », dit un adage rabbinique.&lt;/p&gt; &lt;p&gt;Cette tradition prend forme avec les sages de l’époque du Second Temple. Hillel, vers le début de notre ère, formule sept règles d’interprétation, que Rabbi Ishmaël porte à treize au IIe siècle, tandis que Rabbi Akiva cherche un sens à chaque lettre. Le &lt;a href="https://fr.wikipedia.org/wiki/Midrash" title=" Wikipedia"&gt;midrash&lt;/a&gt; commente les versets pour en tirer soit des lois (&lt;em&gt;halakha&lt;/em&gt;), soit des récits et des leçons morales (&lt;em&gt;aggada&lt;/em&gt;). La Mishna, mise par écrit vers 200, puis les Talmuds de Jérusalem et de Babylone, achevés vers 400 et 500, consignent des débats où l’opinion minoritaire est conservée à côté de celle qui l’emporte. Au Moyen Âge, on distingue quatre niveaux de sens, résumés par le mot PaRDeS : &lt;em&gt;peshat&lt;/em&gt;, le sens littéral, &lt;em&gt;remez&lt;/em&gt;, l’allusion, &lt;em&gt;derash&lt;/em&gt;, l’interprétation, et &lt;em&gt;sod&lt;/em&gt;, le secret mystique de la Kabbale.&lt;/p&gt; &lt;p&gt;Rachi de Troyes, Maïmonide et Nahmanide en sont les grands commentateurs. Au XXe siècle, Emmanuel Levinas renouvelle la lecture du Talmud, et cette tradition a nourri les théories modernes de l’interprétation.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F10" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="n">
-        <v>-700</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
+        <v>58</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="J11" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ésotérismes et gnoses</t>
-        </is>
-      </c>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Egypte antique;Platonisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>1340</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>1340</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9sychasme" title=" Wikipedia"&gt;L’Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme orthodoxe. Son nom vient du grec &lt;em&gt;hésychia&lt;/em&gt;, « silence, tranquillité » : il s’agit de faire taire les pensées pour s’unir à Dieu dans le calme du cœur. Ses racines remontent aux moines et ermites d’Égypte et de Syrie, les Pères du désert, aux IVe et Ve siècles, puis à des maîtres comme Jean Climaque, auteur de &lt;em&gt;L’Échelle sainte&lt;/em&gt; au VIIe siècle, et Syméon le Nouveau Théologien vers l’an mil.&lt;/p&gt; &lt;p&gt;Sa pratique centrale est la &lt;a href="https://fr.wikipedia.org/wiki/Pri%C3%A8re_du_c%C5%93ur" title=" Wikipedia"&gt;prière de Jésus&lt;/a&gt; : le moine répète sans cesse « Seigneur Jésus-Christ, Fils de Dieu, aie pitié de moi », au rythme de sa respiration, la tête inclinée vers la poitrine, pour que la prière descende de l’intelligence dans le cœur. Au XIVe siècle, des moines du mont Athos disent voir ainsi la lumière divine, celle qui entoura le Christ lors de sa Transfiguration sur le mont Thabor. Le moine calabrais Barlaam les accuse de superstition : Dieu ne peut pas être vu. &lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas" title=" Wikipedia"&gt;Grégoire Palamas&lt;/a&gt;, futur archevêque de Thessalonique, répond en distinguant l’essence de Dieu, à jamais inaccessible, et ses énergies, qui se communiquent réellement à l’homme et rendent possible sa « divinisation ». Des conciles réunis à Constantinople lui donnent raison en 1341 et en 1351.&lt;/p&gt; &lt;p&gt;En 1782 paraît la &lt;em&gt;Philocalie&lt;/em&gt;, recueil de textes hésychastes bientôt traduit en slavon. L’hésychasme inspire alors les « startsy », les maîtres spirituels de Russie, et les &lt;em&gt;Récits d’un pèlerin russe&lt;/em&gt; ; il reste au cœur de la spiritualité orthodoxe.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="n">
+        <v>-700</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
       <c r="J12" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
@@ -2844,81 +2836,91 @@
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christianisme antique et médiéval</t>
+          <t xml:space="preserve">Ésotérismes et gnoses</t>
         </is>
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patristique</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="n">
-        <v>-600</v>
-      </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
+          <t xml:space="preserve">Egypte antique;Platonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9sychasme" title=" Wikipedia"&gt;L’Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme orthodoxe. Son nom vient du grec &lt;em&gt;hésychia&lt;/em&gt;, « silence, tranquillité » : il s’agit de faire taire les pensées pour s’unir à Dieu dans le calme du cœur. Ses racines remontent aux moines et ermites d’Égypte et de Syrie, les Pères du désert, aux IVe et Ve siècles, puis à des maîtres comme Jean Climaque, auteur de &lt;em&gt;L’Échelle sainte&lt;/em&gt; au VIIe siècle, et Syméon le Nouveau Théologien vers l’an mil.&lt;/p&gt; &lt;p&gt;Sa pratique centrale est la &lt;a href="https://fr.wikipedia.org/wiki/Pri%C3%A8re_du_c%C5%93ur" title=" Wikipedia"&gt;prière de Jésus&lt;/a&gt; : le moine répète sans cesse « Seigneur Jésus-Christ, Fils de Dieu, aie pitié de moi », au rythme de sa respiration, la tête inclinée vers la poitrine, pour que la prière descende de l’intelligence dans le cœur. Au XIVe siècle, des moines du mont Athos disent voir ainsi la lumière divine, celle qui entoura le Christ lors de sa Transfiguration sur le mont Thabor. Le moine calabrais Barlaam les accuse de superstition : Dieu ne peut pas être vu. &lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas" title=" Wikipedia"&gt;Grégoire Palamas&lt;/a&gt;, futur archevêque de Thessalonique, répond en distinguant l’essence de Dieu, à jamais inaccessible, et ses énergies, qui se communiquent réellement à l’homme et rendent possible sa « divinisation ». Des conciles réunis à Constantinople lui donnent raison en 1341 et en 1351.&lt;/p&gt; &lt;p&gt;En 1782 paraît la &lt;em&gt;Philocalie&lt;/em&gt;, recueil de textes hésychastes bientôt traduit en slavon. L’hésychasme inspire alors les « startsy », les maîtres spirituels de Russie, et les &lt;em&gt;Récits d’un pèlerin russe&lt;/em&gt; ; il reste au cœur de la spiritualité orthodoxe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="J13" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christianisme antique et médiéval</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="n">
         <v>-600</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="D14" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
       <c r="J14" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>43</v>
@@ -2934,30 +2936,30 @@
         </is>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>-550</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>89</v>
+        <v>-600</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>91</v>
+        <v>83</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>94</v>
+        <v>86</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>43</v>
@@ -2969,141 +2971,141 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védas et brahmanisme</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Védisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="n">
-        <v>-520</v>
-      </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme"  title=" Wikipedia"&gt;Le Confucianisme&lt;/a&gt; est la tradition de pensée issue de &lt;a href="https://fr.wikipedia.org/wiki/Confucius" title=" Wikipedia"&gt;Confucius&lt;/a&gt; (551-479 av. J.-C.), lettré de l’État de Lu, en Chine, qui chercha en vain un prince prêt à appliquer ses idées. Ses paroles, recueillies par ses disciples dans les &lt;em&gt;Entretiens&lt;/em&gt;, proposent de restaurer l’harmonie d’une société en crise non par la force ou par la loi, mais par la vertu, l’éducation et le respect des rites.&lt;/p&gt; &lt;p&gt;Son idéal est l’« homme de bien » (&lt;em&gt;junzi&lt;/em&gt;), qui se perfectionne sans cesse par l’étude. Les vertus cardinales sont l’humanité ou bienveillance (&lt;em&gt;ren&lt;/em&gt;), la droiture (&lt;em&gt;yi&lt;/em&gt;), les rites (&lt;em&gt;li&lt;/em&gt;), qui règlent avec justesse les relations humaines, la sagesse (&lt;em&gt;zhi&lt;/em&gt;) et la fidélité à la parole donnée (&lt;em&gt;xin&lt;/em&gt;). La société repose sur la famille et la piété filiale : chacun doit tenir son rôle dans les relations entre souverain et sujet, père et fils, époux, aînés et cadets, amis. Le prince gouverne par l’exemple, et les mots doivent correspondre aux choses : c’est la « rectification des noms ». Après Confucius, &lt;a href="https://fr.wikipedia.org/wiki/Mencius" title=" Wikipedia"&gt;Mencius&lt;/a&gt; affirme que la nature humaine est bonne, Xunzi qu’elle doit être redressée par l’éducation. Sous les Han, le confucianisme devient la doctrine officielle de l’empire, et les concours de recrutement des fonctionnaires, fondés sur ses classiques, durent jusqu’en 1905. Au XIIe siècle, Zhu Xi le renouvelle par une métaphysique : c’est le néoconfucianisme.&lt;/p&gt; &lt;p&gt;Il s’étend à la Corée, au Japon et au Viêt Nam. Combattu au XXe siècle comme cause du retard chinois, il connaît aujourd’hui un renouveau en Chine.&lt;/p&gt;  &lt;audio controls title="Le Confucianisme et les valeurs asiatiques par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-14.05.2019-ITEMA_22061347-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="2" t="s">
-        <v>100</v>
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>-550</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védas et brahmanisme</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
+        <v>-520</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme"  title=" Wikipedia"&gt;Le Confucianisme&lt;/a&gt; est la tradition de pensée issue de &lt;a href="https://fr.wikipedia.org/wiki/Confucius" title=" Wikipedia"&gt;Confucius&lt;/a&gt; (551-479 av. J.-C.), lettré de l’État de Lu, en Chine, qui chercha en vain un prince prêt à appliquer ses idées. Ses paroles, recueillies par ses disciples dans les &lt;em&gt;Entretiens&lt;/em&gt;, proposent de restaurer l’harmonie d’une société en crise non par la force ou par la loi, mais par la vertu, l’éducation et le respect des rites.&lt;/p&gt; &lt;p&gt;Son idéal est l’« homme de bien » (&lt;em&gt;junzi&lt;/em&gt;), qui se perfectionne sans cesse par l’étude. Les vertus cardinales sont l’humanité ou bienveillance (&lt;em&gt;ren&lt;/em&gt;), la droiture (&lt;em&gt;yi&lt;/em&gt;), les rites (&lt;em&gt;li&lt;/em&gt;), qui règlent avec justesse les relations humaines, la sagesse (&lt;em&gt;zhi&lt;/em&gt;) et la fidélité à la parole donnée (&lt;em&gt;xin&lt;/em&gt;). La société repose sur la famille et la piété filiale : chacun doit tenir son rôle dans les relations entre souverain et sujet, père et fils, époux, aînés et cadets, amis. Le prince gouverne par l’exemple, et les mots doivent correspondre aux choses : c’est la « rectification des noms ». Après Confucius, &lt;a href="https://fr.wikipedia.org/wiki/Mencius" title=" Wikipedia"&gt;Mencius&lt;/a&gt; affirme que la nature humaine est bonne, Xunzi qu’elle doit être redressée par l’éducation. Sous les Han, le confucianisme devient la doctrine officielle de l’empire, et les concours de recrutement des fonctionnaires, fondés sur ses classiques, durent jusqu’en 1905. Au XIIe siècle, Zhu Xi le renouvelle par une métaphysique : c’est le néoconfucianisme.&lt;/p&gt; &lt;p&gt;Il s’étend à la Corée, au Japon et au Viêt Nam. Combattu au XXe siècle comme cause du retard chinois, il connaît aujourd’hui un renouveau en Chine.&lt;/p&gt;  &lt;audio controls title="Le Confucianisme et les valeurs asiatiques par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-14.05.2019-ITEMA_22061347-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="n">
+    <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="n">
         <v>-510</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14" t="s">
+      <c r="B18" s="14"/>
+      <c r="C18" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D18" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E18" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F18" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G18" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="2" t="s">
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>-500</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>-500</v>
       </c>
@@ -3111,22 +3113,22 @@
         <v>109</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>43</v>
@@ -3138,42 +3140,34 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sâmkhya</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="n">
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>-500</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="D20" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="J20" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>43</v>
@@ -3185,39 +3179,39 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védas et brahmanisme</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Sâmkhya</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="n">
-        <v>-470</v>
+        <v>-500</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>22</v>
@@ -3225,94 +3219,94 @@
       <c r="M21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védas et brahmanisme</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="n">
+        <v>-470</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P21" s="1" t="inlineStr">
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P22" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="n">
+    <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="n">
         <v>-450</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D23" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E23" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F23" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G23" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="2" t="s">
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="n">
-        <v>-410</v>
-      </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>101</v>
@@ -3324,34 +3318,39 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme</t>
         </is>
       </c>
     </row>
     <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="n">
-        <v>-400</v>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
+      <c r="A24" s="9" t="n">
+        <v>-410</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
       <c r="J24" s="2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>22</v>
@@ -3366,34 +3365,37 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="n">
         <v>-400</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>153</v>
-      </c>
+      <c r="D25" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
       <c r="J25" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>101</v>
@@ -3405,172 +3407,164 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>-400</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="n">
+    <row r="27" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
         <v>-350</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9" t="s">
+      <c r="B27" s="9"/>
+      <c r="C27" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D27" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E27" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G27" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="2" t="s">
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t xml:space="preserve">Brahmanisme</t>
         </is>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
+    <row r="28" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="n">
         <v>-350</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D28" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianisme</t>
         </is>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
+    <row r="29" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="n">
         <v>-250</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D29" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="n">
-        <v>-150</v>
-      </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>43</v>
@@ -3582,42 +3576,42 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brahmanisme</t>
+          <t xml:space="preserve">Bouddhisme</t>
         </is>
       </c>
     </row>
     <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
+      <c r="A30" s="14" t="n">
+        <v>-150</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
       <c r="J30" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>43</v>
@@ -3638,176 +3632,179 @@
         </is>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>188</v>
-      </c>
+    <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N31" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="E32" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="J32" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Védisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="B33" s="14"/>
-      <c r="C33" s="14" t="n">
-        <v>450</v>
+      <c r="C33" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>198</v>
+        <v>191</v>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F33" s="14" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zoroastrisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3816,98 +3813,103 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Zoroastrisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N35" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P35" s="1" t="inlineStr">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
-      <c r="Q35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="353.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>213</v>
+        <v>207</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J36" s="21" t="s">
-        <v>216</v>
+        <v>210</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        <v>43</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
         </is>
       </c>
     </row>
@@ -7228,18 +7230,18 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E10" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines&quot;  title=&quot; Wikipedia&quot;&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les traditions philosophiques et spirituelles des civilisations précolombiennes d'Amérique centrale, en particulier les Aztèques, les Mayas et les Toltèques. Ces pensées forment un univers conceptuel original, structuré autour de la relation entre l'homme, le cosmos et les forces divines.&lt;/p&gt;&lt;p&gt;Au cœur de ces traditions se trouve la notion de &lt;em&gt;teotl&lt;/em&gt; (divinité, énergie sacrée) chez les Aztèques, ou de &lt;em&gt;k'ul&lt;/em&gt; (force vitale sacrée) chez les Mayas. La cosmologie mésoaméricaine conçoit l'univers comme un système de cycles temporels, où les dieux et les hommes sont liés par des obligations réciproques. Le sacrifice rituel, loin d'être une simple pratique violente, est pensé comme une nécessité cosmique pour maintenir l'équilibre du monde.&lt;/p&gt;&lt;p&gt;Des figures comme Quetzalcóatl (le Serpent à plumes) incarnent une sagesse éthique et philosophique : tempérance, connaissance, opposition au sacrifice humain selon certaines traditions. Les philosophes aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s'interrogeaient sur la nature du vrai, du beau, du bien, et sur la condition humaine — une tradition philosophique autonome redécouverte par des chercheurs comme Miguel León-Portilla.&lt;/p&gt;"/>
-    <hyperlink ref="E12" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9sychasme&quot; title=&quot; Wikipedia&quot;&gt;L'Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme oriental, dont le nom vient du grec &lt;em&gt;hésychia&lt;/em&gt; (silence, tranquillité). Il désigne une pratique spirituelle visant à atteindre l'union avec Dieu par la prière continue, le silence intérieur et la maîtrise du souffle.&lt;/p&gt;&lt;p&gt;Ses origines remontent aux Pères du désert des IVe-Ve siècles, mais c'est au XIVe siècle que l'hésychasme devient un courant théologique et philosophique structuré, notamment grâce à Grégoire Palamas, archevêque de Thessalonique, qui en formule la doctrine dans ses &lt;em&gt;Triades&lt;/em&gt;. Palamas distingue l'essence divine (inaccessible) des énergies divines (accessibles à l'expérience mystique), permettant de fonder théologiquement la possibilité d'une véritable union de l'homme avec Dieu.&lt;/p&gt;&lt;p&gt;Cette distinction essence-énergies est l'une des contributions philosophiques les plus originales de la pensée byzantine. L'hésychasme a profondément marqué la spiritualité orthodoxe russe, grecque et serbe, et continue d'irriguer la théologie et la philosophie orthodoxes contemporaines.&lt;/p&gt;"/>
-    <hyperlink ref="E14" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka&quot;  title=&quot;Wikipedia&quot;&gt;Le Lokayata&lt;/a&gt;, également connu sous le nom de Carvaka, est la seule école philosophique de l'Inde ancienne à avoir défendu un matérialisme radical et un athéisme déclaré. Fondée vers le VIe siècle avant notre ère, elle rejette tout ce qui ne peut être appréhendé par les sens : pas d'âme immortelle, pas d'au-delà, pas de loi karmique.&lt;/p&gt;&lt;p&gt;Sa devise pourrait se résumer ainsi : ce que l'on voit existe ; ce que l'on ne peut percevoir n'est qu'invention. Les Carvakas refusent les Védas et leur autorité, les rituels brahmaniques, et toute forme de spéculation métaphysique. L'univers est composé des quatre éléments — terre, eau, feu et air — sans qu'intervienne aucune divinité créatrice.&lt;/p&gt;&lt;p&gt;En matière d'éthique, la philosophie Carvaka est franchement hédoniste : le plaisir est le seul bien réel, la souffrance le seul mal. Mieux vaut jouir de la vie maintenant plutôt qu'espérer une récompense illusoire après la mort. Ce réalisme sans concession en fait une voix singulière, souvent persécutée, de la pensée indienne classique.&lt;/p&gt;&lt;p&gt;Bien que ses textes originaux aient presque tous disparu — connus surtout par les réfutations de ses adversaires — son influence demeure dans les courants matérialistes et rationalistes qui traversent la philosophie indienne jusqu'à aujourd'hui.&lt;/p&gt;"/>
-    <hyperlink ref="E19" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra&quot; title=&quot; Wikipedia&quot;&gt; Le Yoga&lt;/a&gt; en tant qu’école philosophique (darshana) est distinct de la pratique physique popularisée en Occident. Systématisé par Patanjali dans les Yoga Sutra (entre 200 av. J.-C. et 500 apr. J.-C.), il partage la métaphysique dualiste du Samkhya — Purusha (conscience) et Prakriti (matière) — mais y ajoute une méthode pratique précise pour la libération.&lt;/p&gt;&lt;p&gt;Les huit membres (ashtanga) du Yoga structurent ce chemin : discipline éthique (yama, niyama), posture (asana), maîtrise du souffle (pranayama), retrait des sens (pratyahara), concentration (dharana), méditation (dhyana) et absorption (samadhi). Chaque étape prépare la suivante dans une progression méthodique vers l’arrêt des fluctuations du mental (chitta vritti nirodha).&lt;/p&gt;&lt;p&gt;Contrairement au Samkhya, purement théorique, le Yoga de Patanjali introduit îshvara (un principe divin, seigneur particulier parmi les âmes) comme objet de concentration facultatif — une nuance théiste absente du Samkhya classique. Cette différence a nourri des siècles de commentaires et de débats entre les deux écoles sœurs.&lt;/p&gt;&lt;p&gt;Aujourd’hui mondialement diffusée, la dimension physique du yoga occulte souvent sa profondeur philosophique originelle : une discipline rigoureuse de la conscience, visant non le bien-être mais la discrimination (viveka) entre le Soi éternel et les fluctuations passagères du mental.&lt;/p&gt;"/>
-    <hyperlink ref="E21" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme&quot;  title=&quot; Wikipedia&quot;&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt;    &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title=&quot;Le Taoïsme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E25" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/École_des_Noms&quot;  title=&quot;Wikipedia&quot;&gt;L'École des Noms&lt;/a&gt; (ming jia, 名家) est une école de philosophie chinoise qui s'est développée pendant la période des Royaumes combattants. Sa préoccupation centrale : la relation entre les mots et les choses, entre les noms et la réalité qu'ils désignent.&lt;/p&gt;&lt;p&gt;Ses représentants les plus célèbres, Gongsun Long et Hui Shi, sont connus pour leurs paradoxes vertigineux. Gongsun Long affirmait que &quot;le cheval blanc n'est pas un cheval&quot; — non par provocation, mais pour distinguer le concept général (cheval) du particulier concret (ce cheval blanc). Hui Shi proclamait que &quot;le ciel et la terre sont d'une même hauteur&quot;, explorant les limites relatives de toute catégorisation.&lt;/p&gt;&lt;p&gt;Ces réflexions sur le langage anticipent certaines problématiques de la logique et de la philosophie analytique moderne. Comment les mots nous permettent-ils — ou nous empêchent-ils — de saisir la réalité ? Toute classification n'implique-t-elle pas une distorsion du monde ?&lt;/p&gt;&lt;p&gt;Peu influente politiquement, l'École des Noms fut souvent moquée par ses contemporains confu céens et taoïstes. Mais elle constitue une contribution unique à la logique asiatique et à la philosophie du langage dans la pensée mondiale.&lt;/p&gt;"/>
-    <hyperlink ref="E26" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A2mkhya&quot;  title=&quot; Wikipedia&quot;&gt;Le Sâmkhya&lt;/a&gt; est l'une des plus anciennes écoles philosophiques de l'Inde, considérée comme un darshana orthodoxe de l'hindouisme. Il propose une analyse rationnelle de la réalité pour libérer l'individu du cycle des renaissances et de la souffrance. Ce système dualiste distingue deux réalités ultimes : Purusha, la conscience pure et passive (esprit, principe masculin), et Prakriti, la matière primordiale active (énergie universelle, principe féminin). Prakriti évolue sous l'influence des trois guṇas (sattva : harmonie ; rajas : activité ; tamas : inertie), générant le monde manifesté à travers 23 tattvas (principes), comme buddhi (intelligence), ahaṃkāra (ego) et les sens. &lt;/p&gt; &lt;p&gt; Il explique la création comme une transformation de Prakriti, sans recours à un dieu créateur : de l'état non manifesté (avyakta) naît le manifesté (vyakta), incluant le corps subtil qui transmigre. L'ignorance (avidyā) cause l'identification erronée du Purusha à la matière, source de souffrance (duḥkha). &lt;/p&gt; &lt;p&gt; Fondement théorique du Yoga de Patañjali, le Sâmkhya met l'accent sur la discrimination (viveka) entre Purusha et Prakriti pour atteindre la libération (kaivalya). Il influence largement la philosophie indienne, des Puranas au Vedānta. &lt;/p&gt;"/>
-    <hyperlink ref="E28" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Therav%C4%81da&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Theravada&lt;/a&gt; (« École des Anciens ») est la plus ancienne forme du bouddhisme conservée jusqu'à nos jours. Héritière directe des enseignements du Bouddha historique, elle s'enracina progressivement en Asie du Sud-Est : Sri Lanka, Thaïlande, Myanmar, Cambodge, Laos.&lt;/p&gt;&lt;p&gt;Au cœur du Theravada se trouve le Pali Canon (Tipitaka), le corpus scripturaire le plus ancien du bouddhisme. Sa philosophie insiste sur la voie individuelle vers l'éveil : chaque être doit parcourir lui-même le Noble Sentier Octuple — juste compréhension, juste intention, juste parole, juste action, juste mode de vie, juste effort, juste attention, juste concentration.&lt;/p&gt;&lt;p&gt;L'idéal du Theravada est l'Arhat : le sage qui, par sa propre pratique, a éteint les &quot;feux&quot; de l'attachement, de la haine et de l'illusion, et atteint le Nirvana. Cette voie solitaire et rigoureuse contraste avec l'idéal du bodhisattva du Mahayana, qui renonce à son propre éveil pour sauver tous les êtres.&lt;/p&gt;&lt;p&gt;La méditation de pleine conscience (sati), aujourd'hui mondialement répandue, trouve ses racines dans les pratiques contemplatives du Theravada, notamment la méditation vipassana qui vise à observer directement l'impermanence, la souffrance et l'absence de soi.&lt;/p&gt;"/>
-    <hyperlink ref="E30" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vaisheshika&quot;  title=&quot; Wikipedia&quot;&gt;Le Vaisheshika&lt;/a&gt;  est une école philosophique orthodoxe hindoue, fondée par le sage Kaṇāda, qui se distingue par son atomisme et son réalisme ontologique. Exposée dans les Vaiśeṣika Sūtra (non antérieurs à l'ère chrétienne), elle vise la libération (mokṣa) par la connaissance des catégories fondamentales de la réalité. Le système repose sur six ou sept padārthas (catégories) : dravya (substance), guṇa (qualité), karma (action/mouvement), sāmānya (universalité), viśeṣa (particularité) et samavāya (inhérence). Parmi les neuf substances, quatre sont atomiques (terre, eau, feu, air) : les paramāṇu (atomes éternels, indivisibles) s'assemblent en dyades puis en objets composites non éternels. &lt;/p&gt; &lt;p&gt; Sans dieu créateur direct, l'univers émerge de combinaisons atomiques influencées par une cause efficiente (adrisṭa, karma résiduel). Ākāśa (espace), kāla (temps), dik (direction) et cit (âme) complètent les substances ; les atomes sphériques se lient par forces intrinsèques, formant un monde discontinu mais perceptible. &lt;/p&gt; &lt;p&gt; Souvent fusionné avec le Nyâya (logique), il postule un Īśvara ordonnateur. La délivrance est un état pur de l'âme (sans qualités, conscience ou douleur), libérée des agrégats par la gnose discriminante. &lt;/p&gt;"/>
-    <hyperlink ref="E31" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_mah%C4%81y%C4%81na&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Mahayana&lt;/a&gt; (« Grand Véhicule ») est apparu en Inde au tournant de l'ère chrétienne, s'étendant progressivement vers la Chine, le Japon, la Corée et le Vietnam. Par rapport au Theravada, il représente une transformation profonde de la vision bouddhiste : l'éveil n'est plus un idéal solitaire mais une aspiration collective.&lt;/p&gt;&lt;p&gt;L'idéal central du Mahayana est le bodhisattva : l'être qui, sur le point d'atteindre le Nirvana, choisit de demeurer dans le cycle des renaissances (samsara) pour guider et libérer tous les êtres sensibles. Cette compassion universelle (karuna) devient le moteur de la voie spirituelle, indissociable de la sagesse (prajna).&lt;/p&gt;&lt;p&gt;Le Mahayana introduit également la notion révolutionnaire de sunyata (vacuité) : toutes choses sont dénues d'existence propre et intrinsèque — elles n'existent que de façon interdependante. Nagarjuna, au IIe siècle, en développa la philosophie dans ses Stances du Milieu, fondant l'école Madhyamaka qui influencça toute la pensée bouddhiste ultérieure.&lt;/p&gt;&lt;p&gt;C'est sur le sol du Mahayana que fleuriront le bouddhisme Zen, le bouddhisme tibétain Vajrayana, et l'École de la Terre Pure. Avec ses sutras nouveaux (Lotus, Vimalakirti, Prajnaparamita), le Mahayana offre une vision du monde d'une richesse philosophique et spirituelle sans équivalent.&lt;/p&gt;"/>
-    <hyperlink ref="E33" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mazdakisme&quot; title=&quot;Wikipedia&quot;&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse sous l’Empire sassanide. Fondé par le réformateur Mazdak, ce courant tire ses origines à la fois du mazdéisme et du manichéisme, en proposant une relecture dualiste du monde axée sur la lumière et les ténèbres. &lt;/p&gt; &lt;p&gt; Contrairement aux structures sociales hiérarchisées de l’époque, le mazdakisme prônait une égalité radicale entre les individus. Mazdak soutenait que les causes des conflits humains résidaient dans la soif de richesses et de pouvoir, ce qui l'a conduit à prôner la mise en commun des biens matériels et, selon certaines sources, des femmes. &lt;/p&gt; &lt;p&gt; Cette doctrine a été perçue comme une menace par l’aristocratie et le clergé zoroastrien traditionnel, qui y voyaient une hérésie dangereuse pour l'ordre établi. Après avoir initialement bénéficié de l'intérêt de l'empereur Kavadh Ier, le mouvement fut sévèrement réprimé lors de grandes purges organisées entre 524 et 529. &lt;/p&gt; &lt;p&gt; Bien que le mazdakisme ait été marginalisé après ces persécutions, il a laissé une trace durable dans la pensée iranienne. Parfois qualifié, de manière anachronique, de mouvement proto-socialiste, son idéal de justice sociale a influencé certains courants contestataires qui se sont manifestés en Iran jusqu'au XIVe siècle environ. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E35" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_vajrayana&quot;  title=&quot;Wikipedia&quot;&gt;Le Vajrayana&lt;/a&gt; (« Véhicule de Diamant ») est la troisième grande forme du bouddhisme, développée en Inde entre le VIIe et le Xe siècle, puis transmise au Tibet, en Mongolie et dans l'Himalaya. Il représente la voie tantrique du bouddhisme, utilisant des pratiques ésotériques pour accélérer le chemin vers l'éveil.&lt;/p&gt;&lt;p&gt;Là où le Theravada vise l'éveil en de nombreuses vies et le Mahayana en d'innombrables éons, le Vajrayana affirme qu'il est possible d'atteindre l'éveil en une seule vie — voire en un seul instant. Pour cela, il mobilise un arsenal de techniques : mantras, mandalas, mudras, visualisations de divinités, pratiques yogiques subtiles sur les énergies intérieures du corps.&lt;/p&gt;&lt;p&gt;Le Bouddhisme tibétain, la forme la plus répandue du Vajrayana, s'est développé dès le VIIe siècle sous le règne du roi Songtsen Gampo. Il intègre des éléments de la religion Bön préexistante et du Mahayana indien. Ses figures tutlaires — Padmasambhava, Milarepa, Tsongkhapa — sont au cœur d'une tradition d'une richesse philosophique et rituelle incomparable.&lt;/p&gt;&lt;p&gt;La notion de &quot;nature de bouddha&quot; (tathagatagarbha) — l'idée que chaque être possède en lui la graine de l'éveil — est centrale dans le Vajrayana. La pratique vise à reconnaître directement cette nature lumineuse originelle, au-delà des voiles de l'ignorance et de l'égo.&lt;/p&gt;"/>
+    <hyperlink ref="E11" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines&quot;  title=&quot; Wikipedia&quot;&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les traditions philosophiques et spirituelles des civilisations précolombiennes d'Amérique centrale, en particulier les Aztèques, les Mayas et les Toltèques. Ces pensées forment un univers conceptuel original, structuré autour de la relation entre l'homme, le cosmos et les forces divines.&lt;/p&gt;&lt;p&gt;Au cœur de ces traditions se trouve la notion de &lt;em&gt;teotl&lt;/em&gt; (divinité, énergie sacrée) chez les Aztèques, ou de &lt;em&gt;k'ul&lt;/em&gt; (force vitale sacrée) chez les Mayas. La cosmologie mésoaméricaine conçoit l'univers comme un système de cycles temporels, où les dieux et les hommes sont liés par des obligations réciproques. Le sacrifice rituel, loin d'être une simple pratique violente, est pensé comme une nécessité cosmique pour maintenir l'équilibre du monde.&lt;/p&gt;&lt;p&gt;Des figures comme Quetzalcóatl (le Serpent à plumes) incarnent une sagesse éthique et philosophique : tempérance, connaissance, opposition au sacrifice humain selon certaines traditions. Les philosophes aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s'interrogeaient sur la nature du vrai, du beau, du bien, et sur la condition humaine — une tradition philosophique autonome redécouverte par des chercheurs comme Miguel León-Portilla.&lt;/p&gt;"/>
+    <hyperlink ref="E13" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9sychasme&quot; title=&quot; Wikipedia&quot;&gt;L'Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme oriental, dont le nom vient du grec &lt;em&gt;hésychia&lt;/em&gt; (silence, tranquillité). Il désigne une pratique spirituelle visant à atteindre l'union avec Dieu par la prière continue, le silence intérieur et la maîtrise du souffle.&lt;/p&gt;&lt;p&gt;Ses origines remontent aux Pères du désert des IVe-Ve siècles, mais c'est au XIVe siècle que l'hésychasme devient un courant théologique et philosophique structuré, notamment grâce à Grégoire Palamas, archevêque de Thessalonique, qui en formule la doctrine dans ses &lt;em&gt;Triades&lt;/em&gt;. Palamas distingue l'essence divine (inaccessible) des énergies divines (accessibles à l'expérience mystique), permettant de fonder théologiquement la possibilité d'une véritable union de l'homme avec Dieu.&lt;/p&gt;&lt;p&gt;Cette distinction essence-énergies est l'une des contributions philosophiques les plus originales de la pensée byzantine. L'hésychasme a profondément marqué la spiritualité orthodoxe russe, grecque et serbe, et continue d'irriguer la théologie et la philosophie orthodoxes contemporaines.&lt;/p&gt;"/>
+    <hyperlink ref="E15" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka&quot;  title=&quot;Wikipedia&quot;&gt;Le Lokayata&lt;/a&gt;, également connu sous le nom de Carvaka, est la seule école philosophique de l'Inde ancienne à avoir défendu un matérialisme radical et un athéisme déclaré. Fondée vers le VIe siècle avant notre ère, elle rejette tout ce qui ne peut être appréhendé par les sens : pas d'âme immortelle, pas d'au-delà, pas de loi karmique.&lt;/p&gt;&lt;p&gt;Sa devise pourrait se résumer ainsi : ce que l'on voit existe ; ce que l'on ne peut percevoir n'est qu'invention. Les Carvakas refusent les Védas et leur autorité, les rituels brahmaniques, et toute forme de spéculation métaphysique. L'univers est composé des quatre éléments — terre, eau, feu et air — sans qu'intervienne aucune divinité créatrice.&lt;/p&gt;&lt;p&gt;En matière d'éthique, la philosophie Carvaka est franchement hédoniste : le plaisir est le seul bien réel, la souffrance le seul mal. Mieux vaut jouir de la vie maintenant plutôt qu'espérer une récompense illusoire après la mort. Ce réalisme sans concession en fait une voix singulière, souvent persécutée, de la pensée indienne classique.&lt;/p&gt;&lt;p&gt;Bien que ses textes originaux aient presque tous disparu — connus surtout par les réfutations de ses adversaires — son influence demeure dans les courants matérialistes et rationalistes qui traversent la philosophie indienne jusqu'à aujourd'hui.&lt;/p&gt;"/>
+    <hyperlink ref="E20" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra&quot; title=&quot; Wikipedia&quot;&gt; Le Yoga&lt;/a&gt; en tant qu’école philosophique (darshana) est distinct de la pratique physique popularisée en Occident. Systématisé par Patanjali dans les Yoga Sutra (entre 200 av. J.-C. et 500 apr. J.-C.), il partage la métaphysique dualiste du Samkhya — Purusha (conscience) et Prakriti (matière) — mais y ajoute une méthode pratique précise pour la libération.&lt;/p&gt;&lt;p&gt;Les huit membres (ashtanga) du Yoga structurent ce chemin : discipline éthique (yama, niyama), posture (asana), maîtrise du souffle (pranayama), retrait des sens (pratyahara), concentration (dharana), méditation (dhyana) et absorption (samadhi). Chaque étape prépare la suivante dans une progression méthodique vers l’arrêt des fluctuations du mental (chitta vritti nirodha).&lt;/p&gt;&lt;p&gt;Contrairement au Samkhya, purement théorique, le Yoga de Patanjali introduit îshvara (un principe divin, seigneur particulier parmi les âmes) comme objet de concentration facultatif — une nuance théiste absente du Samkhya classique. Cette différence a nourri des siècles de commentaires et de débats entre les deux écoles sœurs.&lt;/p&gt;&lt;p&gt;Aujourd’hui mondialement diffusée, la dimension physique du yoga occulte souvent sa profondeur philosophique originelle : une discipline rigoureuse de la conscience, visant non le bien-être mais la discrimination (viveka) entre le Soi éternel et les fluctuations passagères du mental.&lt;/p&gt;"/>
+    <hyperlink ref="E22" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme&quot;  title=&quot; Wikipedia&quot;&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt;    &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title=&quot;Le Taoïsme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E26" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/École_des_Noms&quot;  title=&quot;Wikipedia&quot;&gt;L'École des Noms&lt;/a&gt; (ming jia, 名家) est une école de philosophie chinoise qui s'est développée pendant la période des Royaumes combattants. Sa préoccupation centrale : la relation entre les mots et les choses, entre les noms et la réalité qu'ils désignent.&lt;/p&gt;&lt;p&gt;Ses représentants les plus célèbres, Gongsun Long et Hui Shi, sont connus pour leurs paradoxes vertigineux. Gongsun Long affirmait que &quot;le cheval blanc n'est pas un cheval&quot; — non par provocation, mais pour distinguer le concept général (cheval) du particulier concret (ce cheval blanc). Hui Shi proclamait que &quot;le ciel et la terre sont d'une même hauteur&quot;, explorant les limites relatives de toute catégorisation.&lt;/p&gt;&lt;p&gt;Ces réflexions sur le langage anticipent certaines problématiques de la logique et de la philosophie analytique moderne. Comment les mots nous permettent-ils — ou nous empêchent-ils — de saisir la réalité ? Toute classification n'implique-t-elle pas une distorsion du monde ?&lt;/p&gt;&lt;p&gt;Peu influente politiquement, l'École des Noms fut souvent moquée par ses contemporains confu céens et taoïstes. Mais elle constitue une contribution unique à la logique asiatique et à la philosophie du langage dans la pensée mondiale.&lt;/p&gt;"/>
+    <hyperlink ref="E27" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A2mkhya&quot;  title=&quot; Wikipedia&quot;&gt;Le Sâmkhya&lt;/a&gt; est l'une des plus anciennes écoles philosophiques de l'Inde, considérée comme un darshana orthodoxe de l'hindouisme. Il propose une analyse rationnelle de la réalité pour libérer l'individu du cycle des renaissances et de la souffrance. Ce système dualiste distingue deux réalités ultimes : Purusha, la conscience pure et passive (esprit, principe masculin), et Prakriti, la matière primordiale active (énergie universelle, principe féminin). Prakriti évolue sous l'influence des trois guṇas (sattva : harmonie ; rajas : activité ; tamas : inertie), générant le monde manifesté à travers 23 tattvas (principes), comme buddhi (intelligence), ahaṃkāra (ego) et les sens. &lt;/p&gt; &lt;p&gt; Il explique la création comme une transformation de Prakriti, sans recours à un dieu créateur : de l'état non manifesté (avyakta) naît le manifesté (vyakta), incluant le corps subtil qui transmigre. L'ignorance (avidyā) cause l'identification erronée du Purusha à la matière, source de souffrance (duḥkha). &lt;/p&gt; &lt;p&gt; Fondement théorique du Yoga de Patañjali, le Sâmkhya met l'accent sur la discrimination (viveka) entre Purusha et Prakriti pour atteindre la libération (kaivalya). Il influence largement la philosophie indienne, des Puranas au Vedānta. &lt;/p&gt;"/>
+    <hyperlink ref="E29" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Therav%C4%81da&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Theravada&lt;/a&gt; (« École des Anciens ») est la plus ancienne forme du bouddhisme conservée jusqu'à nos jours. Héritière directe des enseignements du Bouddha historique, elle s'enracina progressivement en Asie du Sud-Est : Sri Lanka, Thaïlande, Myanmar, Cambodge, Laos.&lt;/p&gt;&lt;p&gt;Au cœur du Theravada se trouve le Pali Canon (Tipitaka), le corpus scripturaire le plus ancien du bouddhisme. Sa philosophie insiste sur la voie individuelle vers l'éveil : chaque être doit parcourir lui-même le Noble Sentier Octuple — juste compréhension, juste intention, juste parole, juste action, juste mode de vie, juste effort, juste attention, juste concentration.&lt;/p&gt;&lt;p&gt;L'idéal du Theravada est l'Arhat : le sage qui, par sa propre pratique, a éteint les &quot;feux&quot; de l'attachement, de la haine et de l'illusion, et atteint le Nirvana. Cette voie solitaire et rigoureuse contraste avec l'idéal du bodhisattva du Mahayana, qui renonce à son propre éveil pour sauver tous les êtres.&lt;/p&gt;&lt;p&gt;La méditation de pleine conscience (sati), aujourd'hui mondialement répandue, trouve ses racines dans les pratiques contemplatives du Theravada, notamment la méditation vipassana qui vise à observer directement l'impermanence, la souffrance et l'absence de soi.&lt;/p&gt;"/>
+    <hyperlink ref="E31" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vaisheshika&quot;  title=&quot; Wikipedia&quot;&gt;Le Vaisheshika&lt;/a&gt;  est une école philosophique orthodoxe hindoue, fondée par le sage Kaṇāda, qui se distingue par son atomisme et son réalisme ontologique. Exposée dans les Vaiśeṣika Sūtra (non antérieurs à l'ère chrétienne), elle vise la libération (mokṣa) par la connaissance des catégories fondamentales de la réalité. Le système repose sur six ou sept padārthas (catégories) : dravya (substance), guṇa (qualité), karma (action/mouvement), sāmānya (universalité), viśeṣa (particularité) et samavāya (inhérence). Parmi les neuf substances, quatre sont atomiques (terre, eau, feu, air) : les paramāṇu (atomes éternels, indivisibles) s'assemblent en dyades puis en objets composites non éternels. &lt;/p&gt; &lt;p&gt; Sans dieu créateur direct, l'univers émerge de combinaisons atomiques influencées par une cause efficiente (adrisṭa, karma résiduel). Ākāśa (espace), kāla (temps), dik (direction) et cit (âme) complètent les substances ; les atomes sphériques se lient par forces intrinsèques, formant un monde discontinu mais perceptible. &lt;/p&gt; &lt;p&gt; Souvent fusionné avec le Nyâya (logique), il postule un Īśvara ordonnateur. La délivrance est un état pur de l'âme (sans qualités, conscience ou douleur), libérée des agrégats par la gnose discriminante. &lt;/p&gt;"/>
+    <hyperlink ref="E32" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_mah%C4%81y%C4%81na&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Mahayana&lt;/a&gt; (« Grand Véhicule ») est apparu en Inde au tournant de l'ère chrétienne, s'étendant progressivement vers la Chine, le Japon, la Corée et le Vietnam. Par rapport au Theravada, il représente une transformation profonde de la vision bouddhiste : l'éveil n'est plus un idéal solitaire mais une aspiration collective.&lt;/p&gt;&lt;p&gt;L'idéal central du Mahayana est le bodhisattva : l'être qui, sur le point d'atteindre le Nirvana, choisit de demeurer dans le cycle des renaissances (samsara) pour guider et libérer tous les êtres sensibles. Cette compassion universelle (karuna) devient le moteur de la voie spirituelle, indissociable de la sagesse (prajna).&lt;/p&gt;&lt;p&gt;Le Mahayana introduit également la notion révolutionnaire de sunyata (vacuité) : toutes choses sont dénues d'existence propre et intrinsèque — elles n'existent que de façon interdependante. Nagarjuna, au IIe siècle, en développa la philosophie dans ses Stances du Milieu, fondant l'école Madhyamaka qui influencça toute la pensée bouddhiste ultérieure.&lt;/p&gt;&lt;p&gt;C'est sur le sol du Mahayana que fleuriront le bouddhisme Zen, le bouddhisme tibétain Vajrayana, et l'École de la Terre Pure. Avec ses sutras nouveaux (Lotus, Vimalakirti, Prajnaparamita), le Mahayana offre une vision du monde d'une richesse philosophique et spirituelle sans équivalent.&lt;/p&gt;"/>
+    <hyperlink ref="E34" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mazdakisme&quot; title=&quot;Wikipedia&quot;&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse sous l’Empire sassanide. Fondé par le réformateur Mazdak, ce courant tire ses origines à la fois du mazdéisme et du manichéisme, en proposant une relecture dualiste du monde axée sur la lumière et les ténèbres. &lt;/p&gt; &lt;p&gt; Contrairement aux structures sociales hiérarchisées de l’époque, le mazdakisme prônait une égalité radicale entre les individus. Mazdak soutenait que les causes des conflits humains résidaient dans la soif de richesses et de pouvoir, ce qui l'a conduit à prôner la mise en commun des biens matériels et, selon certaines sources, des femmes. &lt;/p&gt; &lt;p&gt; Cette doctrine a été perçue comme une menace par l’aristocratie et le clergé zoroastrien traditionnel, qui y voyaient une hérésie dangereuse pour l'ordre établi. Après avoir initialement bénéficié de l'intérêt de l'empereur Kavadh Ier, le mouvement fut sévèrement réprimé lors de grandes purges organisées entre 524 et 529. &lt;/p&gt; &lt;p&gt; Bien que le mazdakisme ait été marginalisé après ces persécutions, il a laissé une trace durable dans la pensée iranienne. Parfois qualifié, de manière anachronique, de mouvement proto-socialiste, son idéal de justice sociale a influencé certains courants contestataires qui se sont manifestés en Iran jusqu'au XIVe siècle environ. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E36" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_vajrayana&quot;  title=&quot;Wikipedia&quot;&gt;Le Vajrayana&lt;/a&gt; (« Véhicule de Diamant ») est la troisième grande forme du bouddhisme, développée en Inde entre le VIIe et le Xe siècle, puis transmise au Tibet, en Mongolie et dans l'Himalaya. Il représente la voie tantrique du bouddhisme, utilisant des pratiques ésotériques pour accélérer le chemin vers l'éveil.&lt;/p&gt;&lt;p&gt;Là où le Theravada vise l'éveil en de nombreuses vies et le Mahayana en d'innombrables éons, le Vajrayana affirme qu'il est possible d'atteindre l'éveil en une seule vie — voire en un seul instant. Pour cela, il mobilise un arsenal de techniques : mantras, mandalas, mudras, visualisations de divinités, pratiques yogiques subtiles sur les énergies intérieures du corps.&lt;/p&gt;&lt;p&gt;Le Bouddhisme tibétain, la forme la plus répandue du Vajrayana, s'est développé dès le VIIe siècle sous le règne du roi Songtsen Gampo. Il intègre des éléments de la religion Bön préexistante et du Mahayana indien. Ses figures tutlaires — Padmasambhava, Milarepa, Tsongkhapa — sont au cœur d'une tradition d'une richesse philosophique et rituelle incomparable.&lt;/p&gt;&lt;p&gt;La notion de &quot;nature de bouddha&quot; (tathagatagarbha) — l'idée que chaque être possède en lui la graine de l'éveil — est centrale dans le Vajrayana. La pratique vise à reconnaître directement cette nature lumineuse originelle, au-delà des voiles de l'ignorance et de l'égo.&lt;/p&gt;"/>
     <hyperlink ref="E38" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/V%C3%A9danta&quot;  title=&quot; Wikipedia&quot;&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).https://fr.wikipedia.org/wiki/Védanta&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;&#10;&#10;"/>
     <hyperlink ref="E40" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
     <hyperlink ref="E44" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2621,168 +2621,232 @@
         </is>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="353.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1">
+        <v>-300</v>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-300</t>
+        </is>
+      </c>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">École du Yin-Yang</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_du_Yin-Yang" title=" Wikipedia"&gt;L’école du Yin-Yang&lt;/a&gt; est l’un des grands courants de la pensée chinoise de l’Antiquité, né à la fin de la période des Royaumes combattants, au IVe et au IIIe siècle avant notre ère. Son maître est &lt;a href="https://fr.wikipedia.org/wiki/Zou_Yan" title=" Wikipedia"&gt;Zou Yan&lt;/a&gt;, savant de l’État de Qi, dont les œuvres sont perdues, mais que l’historien Sima Qian présente comme l’un des penseurs les plus écoutés de son temps par les princes.&lt;/p&gt; &lt;p&gt;Elle explique toute la réalité par deux principes complémentaires, le &lt;a href="https://fr.wikipedia.org/wiki/Yin_et_yang" title=" Wikipedia"&gt;yin et le yang&lt;/a&gt; : le sombre et le lumineux, le froid et le chaud, le repos et le mouvement, le féminin et le masculin. Aucun n’existe sans l’autre, chacun contient le germe de son contraire et le monde naît de leur alternance, comme le jour succède à la nuit. Zou Yan y joint la théorie des &lt;a href="https://fr.wikipedia.org/wiki/Wuxing_%28cosmologie%29" title=" Wikipedia"&gt;cinq phases&lt;/a&gt; ou cinq éléments, le bois, le feu, la terre, le métal et l’eau, qui s’engendrent et se dominent les uns les autres selon des cycles réguliers. Il en tire une philosophie de l’histoire : chaque dynastie règne sous le signe d’une phase et sera remplacée par celle qui la domine. Le premier empereur de Chine, Qin Shi Huangdi, place ainsi son règne sous le signe de l’eau. L’école décrit aussi la géographie du monde, qui compterait neuf grands continents, dont la Chine ne serait qu’une partie.&lt;/p&gt; &lt;p&gt;Elle disparaît comme école indépendante sous les Han, mais ses idées se fondent dans toute la culture chinoise. Dong Zhongshu les intègre au confucianisme officiel, en faisant correspondre l’ordre du ciel et celui de la société. Elles fondent aussi la médecine chinoise, l’astrologie, la géomancie et la lecture du &lt;em&gt;Yijing&lt;/em&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6lyMvRf3sZ0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"En 5 Minutes • Comprendre la symbolique YIN &amp; YANG #yinyang #médecinetraditionnelle #energie" par Margaux Bussière</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école chinoise de Zou Yan qui explique la nature et l’histoire par le yin et le yang et les cinq phases.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Philosophie des sciences et du vivant</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zou YAN;Dong ZHONGSHU</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N8"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1">
+        <v>150</v>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Madhyamaka</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Madhyamaka" title=" Wikipedia"&gt;Le Madhyamaka&lt;/a&gt;, ou « école de la Voie du milieu », est l’une des deux grandes écoles philosophiques du bouddhisme mahāyāna. Il naît en Inde vers le IIe siècle avec Nāgārjuna, dont les &lt;a href="https://fr.wikipedia.org/wiki/Mulamadhyamakakarika" title=" Wikipedia"&gt;&lt;em&gt;Stances de la Voie du milieu&lt;/em&gt;&lt;/a&gt; sont le texte fondateur, et son disciple Āryadeva. Le « milieu » qu’il cherche se tient entre deux extrêmes : croire que les choses existent en elles-mêmes, ou croire qu’elles n’existent pas du tout.&lt;/p&gt; &lt;p&gt;Sa thèse centrale est la &lt;a href="https://fr.wikipedia.org/wiki/%C5%9A%C5%ABnyat%C4%81" title=" Wikipedia"&gt;vacuité&lt;/a&gt; (&lt;em&gt;śūnyatā&lt;/em&gt;) : aucune chose n’a d’existence propre, car toute chose dépend d’autre chose, de ses causes, de ses parties et de l’esprit qui la nomme. La vacuité n’est donc pas le néant, mais l’autre nom de la « production conditionnée » enseignée par le Bouddha. Nāgārjuna procède par réfutation : il montre que toute thèse sur l’être, le mouvement, le temps ou la causalité aboutit à des contradictions dès qu’on la tient pour absolue. Il distingue la vérité conventionnelle, celle du langage et de la vie ordinaire, de la vérité ultime, qui échappe aux concepts ; et la vacuité est elle-même vide : ce n’est pas une nouvelle doctrine à laquelle s’accrocher.&lt;/p&gt; &lt;p&gt;L’école se divise ensuite entre ceux qui admettent des raisonnements autonomes et les « Prāsaṅgika » de Candrakīrti, qui se contentent de montrer l’absurdité des thèses adverses. Śāntideva en tire une éthique de la compassion. Transmis au Tibet par Atiśa et systématisé par Tsongkhapa, le Madhyamaka reste la philosophie de référence du bouddhisme tibétain. On l’a souvent rapproché, au XXe siècle, de la critique du langage chez Wittgenstein.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wpDH0vawatA</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Tsongkhapa's Madhyamaka—Five Texts" par Wisdom Publications Inc.</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école bouddhiste de la Voie du milieu fondée par Nāgārjuna : rien n’existe en soi, tout est vide parce qu’interdépendant.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Épistémologie</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAGARJUNA;SHANTIDEVA;Je TSONGKHAPA</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1">
+        <v>240</v>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xuanxue</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Xuanxue" title=" Wikipedia"&gt;Xuanxue&lt;/a&gt;, « étude du mystère », parfois appelé néotaoïsme, est un grand courant de la philosophie chinoise des IIIe et IVe siècles, né après la chute de la dynastie Han, dans une période de guerres et de désordres où le confucianisme officiel a perdu son crédit. Les lettrés se tournent alors vers les « trois livres du mystère » : le &lt;em&gt;Laozi&lt;/em&gt;, le &lt;em&gt;Zhuangzi&lt;/em&gt; et le &lt;em&gt;Yijing&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Le jeune Wang Bi, mort à vingt-trois ans, en est le génie. Dans ses commentaires du &lt;em&gt;Laozi&lt;/em&gt; et du &lt;em&gt;Yijing&lt;/em&gt;, il affirme que toutes les choses ont pour fondement le « non-être » (&lt;em&gt;wu&lt;/em&gt;), réalité sans forme ni nom, que l’on ne peut pas dire mais d’où tout procède. Le sage n’est pas celui qui en parle le plus, mais celui qui l’incarne : c’est pourquoi Confucius, qui n’en parlait jamais, était plus sage que Laozi. Un demi-siècle plus tard, &lt;a href="https://fr.wikipedia.org/wiki/Guo_Xiang" title=" Wikipedia"&gt;Guo Xiang&lt;/a&gt;, éditeur et commentateur du &lt;em&gt;Zhuangzi&lt;/em&gt;, soutient au contraire que le non-être n’est rien et ne peut rien produire : chaque chose « advient d’elle-même », spontanément, sans créateur ni cause extérieure, et trouve son bonheur à suivre sa propre nature. Ces débats se poursuivent dans les « &lt;a href="https://fr.wikipedia.org/wiki/Qingtan" title=" Wikipedia"&gt;pures conversations&lt;/a&gt; », joutes philosophiques raffinées de l’aristocratie.&lt;/p&gt; &lt;p&gt;Les &lt;a href="https://fr.wikipedia.org/wiki/Sept_Sages_de_la_for%C3%AAt_de_bambous" title=" Wikipedia"&gt;Sept Sages de la forêt de bambous&lt;/a&gt;, poètes et musiciens comme Ji Kang et Ruan Ji, en vivent l’idéal de liberté, en marge des rites et des honneurs. Le Xuanxue prépare surtout l’accueil du bouddhisme en Chine : les premiers traducteurs expriment la vacuité bouddhique dans son vocabulaire du non-être.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lL9obWNAniA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Xuanxue  The Architecture of Nothingness" par Bert Chan (陳信宏)</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">« étude du mystère » : renouveau taoïste des IIIe et IVe siècles chinois, autour de Wang Bi et de Guo Xiang.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wang BI;Guo XIANG;Ji KANG</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N10"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme;Confucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="353.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C11" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D11" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E11" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">le kalâm musulman par ikarim</t>
         </is>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J11" s="21" t="s">
         <v>216</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="n">
-        <v>1090</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Christianisme antique et médiéval</t>
-        </is>
-      </c>
-      <c r="Q9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Néoplatonisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9neutique_biblique" title=" Wikipedia"&gt;L’Herméneutique juive&lt;/a&gt; désigne l’ensemble des méthodes d’interprétation des textes sacrés du judaïsme : la Torah et la Bible hébraïque, puis la Mishna et le &lt;a href="https://fr.wikipedia.org/wiki/Talmud" title=" Wikipedia"&gt;Talmud&lt;/a&gt;. Elle repose sur une idée fondatrice : à côté de la Torah écrite, Moïse aurait reçu au Sinaï une Torah orale, transmise de maître à disciple, qui en donne le sens. Le texte n’est donc jamais clos, il appelle un commentaire sans fin, et l’étude elle-même devient un acte religieux. « La Torah a soixante-dix visages », dit un adage rabbinique.&lt;/p&gt; &lt;p&gt;Cette tradition prend forme avec les sages de l’époque du Second Temple. Hillel, vers le début de notre ère, formule sept règles d’interprétation, que Rabbi Ishmaël porte à treize au IIe siècle, tandis que Rabbi Akiva cherche un sens à chaque lettre. Le &lt;a href="https://fr.wikipedia.org/wiki/Midrash" title=" Wikipedia"&gt;midrash&lt;/a&gt; commente les versets pour en tirer soit des lois (&lt;em&gt;halakha&lt;/em&gt;), soit des récits et des leçons morales (&lt;em&gt;aggada&lt;/em&gt;). La Mishna, mise par écrit vers 200, puis les Talmuds de Jérusalem et de Babylone, achevés vers 400 et 500, consignent des débats où l’opinion minoritaire est conservée à côté de celle qui l’emporte. Au Moyen Âge, on distingue quatre niveaux de sens, résumés par le mot PaRDeS : &lt;em&gt;peshat&lt;/em&gt;, le sens littéral, &lt;em&gt;remez&lt;/em&gt;, l’allusion, &lt;em&gt;derash&lt;/em&gt;, l’interprétation, et &lt;em&gt;sod&lt;/em&gt;, le secret mystique de la Kabbale.&lt;/p&gt; &lt;p&gt;Rachi de Troyes, Maïmonide et Nahmanide en sont les grands commentateurs. Au XXe siècle, Emmanuel Levinas renouvelle la lecture du Talmud, et cette tradition a nourri les théories modernes de l’interprétation.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensée juive</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -2791,43 +2855,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="n">
-        <v>-700</v>
-      </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
       <c r="J12" s="2" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
@@ -2836,47 +2900,47 @@
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ésotérismes et gnoses</t>
+          <t xml:space="preserve">Christianisme antique et médiéval</t>
         </is>
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egypte antique;Platonisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Néoplatonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>1340</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>1340</v>
+        <v>-1000</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9sychasme" title=" Wikipedia"&gt;L’Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme orthodoxe. Son nom vient du grec &lt;em&gt;hésychia&lt;/em&gt;, « silence, tranquillité » : il s’agit de faire taire les pensées pour s’unir à Dieu dans le calme du cœur. Ses racines remontent aux moines et ermites d’Égypte et de Syrie, les Pères du désert, aux IVe et Ve siècles, puis à des maîtres comme Jean Climaque, auteur de &lt;em&gt;L’Échelle sainte&lt;/em&gt; au VIIe siècle, et Syméon le Nouveau Théologien vers l’an mil.&lt;/p&gt; &lt;p&gt;Sa pratique centrale est la &lt;a href="https://fr.wikipedia.org/wiki/Pri%C3%A8re_du_c%C5%93ur" title=" Wikipedia"&gt;prière de Jésus&lt;/a&gt; : le moine répète sans cesse « Seigneur Jésus-Christ, Fils de Dieu, aie pitié de moi », au rythme de sa respiration, la tête inclinée vers la poitrine, pour que la prière descende de l’intelligence dans le cœur. Au XIVe siècle, des moines du mont Athos disent voir ainsi la lumière divine, celle qui entoura le Christ lors de sa Transfiguration sur le mont Thabor. Le moine calabrais Barlaam les accuse de superstition : Dieu ne peut pas être vu. &lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas" title=" Wikipedia"&gt;Grégoire Palamas&lt;/a&gt;, futur archevêque de Thessalonique, répond en distinguant l’essence de Dieu, à jamais inaccessible, et ses énergies, qui se communiquent réellement à l’homme et rendent possible sa « divinisation ». Des conciles réunis à Constantinople lui donnent raison en 1341 et en 1351.&lt;/p&gt; &lt;p&gt;En 1782 paraît la &lt;em&gt;Philocalie&lt;/em&gt;, recueil de textes hésychastes bientôt traduit en slavon. L’hésychasme inspire alors les « startsy », les maîtres spirituels de Russie, et les &lt;em&gt;Récits d’un pèlerin russe&lt;/em&gt; ; il reste au cœur de la spiritualité orthodoxe.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9neutique_biblique" title=" Wikipedia"&gt;L’Herméneutique juive&lt;/a&gt; désigne l’ensemble des méthodes d’interprétation des textes sacrés du judaïsme : la Torah et la Bible hébraïque, puis la Mishna et le &lt;a href="https://fr.wikipedia.org/wiki/Talmud" title=" Wikipedia"&gt;Talmud&lt;/a&gt;. Elle repose sur une idée fondatrice : à côté de la Torah écrite, Moïse aurait reçu au Sinaï une Torah orale, transmise de maître à disciple, qui en donne le sens. Le texte n’est donc jamais clos, il appelle un commentaire sans fin, et l’étude elle-même devient un acte religieux. « La Torah a soixante-dix visages », dit un adage rabbinique.&lt;/p&gt; &lt;p&gt;Cette tradition prend forme avec les sages de l’époque du Second Temple. Hillel, vers le début de notre ère, formule sept règles d’interprétation, que Rabbi Ishmaël porte à treize au IIe siècle, tandis que Rabbi Akiva cherche un sens à chaque lettre. Le &lt;a href="https://fr.wikipedia.org/wiki/Midrash" title=" Wikipedia"&gt;midrash&lt;/a&gt; commente les versets pour en tirer soit des lois (&lt;em&gt;halakha&lt;/em&gt;), soit des récits et des leçons morales (&lt;em&gt;aggada&lt;/em&gt;). La Mishna, mise par écrit vers 200, puis les Talmuds de Jérusalem et de Babylone, achevés vers 400 et 500, consignent des débats où l’opinion minoritaire est conservée à côté de celle qui l’emporte. Au Moyen Âge, on distingue quatre niveaux de sens, résumés par le mot PaRDeS : &lt;em&gt;peshat&lt;/em&gt;, le sens littéral, &lt;em&gt;remez&lt;/em&gt;, l’allusion, &lt;em&gt;derash&lt;/em&gt;, l’interprétation, et &lt;em&gt;sod&lt;/em&gt;, le secret mystique de la Kabbale.&lt;/p&gt; &lt;p&gt;Rachi de Troyes, Maïmonide et Nahmanide en sont les grands commentateurs. Au XXe siècle, Emmanuel Levinas renouvelle la lecture du Talmud, et cette tradition a nourri les théories modernes de l’interprétation.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F13" s="1" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
@@ -2885,45 +2949,37 @@
       </c>
       <c r="P13" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christianisme antique et médiéval</t>
-        </is>
-      </c>
-      <c r="Q13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Patristique</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="n">
-        <v>-600</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="J14" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2932,76 +2988,113 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>-600</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>86</v>
-      </c>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="n">
+        <v>-700</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
       <c r="J15" s="2" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>-550</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ésotérismes et gnoses</t>
+        </is>
+      </c>
+      <c r="Q15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique;Platonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1">
+        <v>1200</v>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200</t>
+        </is>
+      </c>
+      <c r="D16" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kabbale" title=" Wikipedia"&gt;La Kabbale&lt;/a&gt;, la « tradition reçue », est la grande tradition mystique et ésotérique du judaïsme. Elle apparaît à la fin du XIIe siècle en Provence, puis en Catalogne, où Nahmanide, à Gérone, lui donne son autorité, et en Castille, où &lt;a href="https://fr.wikipedia.org/wiki/Mo%C3%AFse_de_Le%C3%B3n" title=" Wikipedia"&gt;Moïse de León&lt;/a&gt; compose vers 1280 le &lt;em&gt;Zohar&lt;/em&gt;, « livre de la Splendeur », qui en devient le texte majeur.&lt;/p&gt; &lt;p&gt;Elle distingue en Dieu l’&lt;em&gt;En Sof&lt;/em&gt;, « l’Infini », absolument caché, et les dix &lt;a href="https://fr.wikipedia.org/wiki/Sephiroth_%28Kabbale%29" title=" Wikipedia"&gt;&lt;em&gt;sefirot&lt;/em&gt;&lt;/a&gt;, émanations par lesquelles il se manifeste : sagesse, intelligence, amour, rigueur, beauté, jusqu’à la &lt;a href="https://fr.wikipedia.org/wiki/Shekhina" title=" Wikipedia"&gt;&lt;em&gt;Shekhina&lt;/em&gt;&lt;/a&gt;, la présence divine dans le monde, que la Kabbale conçoit comme féminine et exilée avec le peuple. Chaque mot de la Torah, chaque commandement accompli, agit sur l’harmonie de ces puissances. Après l’expulsion des Juifs d’Espagne, en 1492, la Kabbale se renouvelle à Safed, en Galilée, autour d’&lt;a href="https://fr.wikipedia.org/wiki/Isaac_Louria" title=" Wikipedia"&gt;Isaac Louria&lt;/a&gt;. Pour faire place au monde, l’Infini a dû se retirer en lui-même : c’est le &lt;a href="https://fr.wikipedia.org/wiki/Tsimtsoum" title=" Wikipedia"&gt;&lt;em&gt;tsimtsoum&lt;/em&gt;&lt;/a&gt;. Puis les « vases » qui devaient recevoir sa lumière se sont brisés, et des étincelles divines sont tombées dans la matière. La tâche de l’être humain est le &lt;a href="https://fr.wikipedia.org/wiki/Tikkoun_Olam" title=" Wikipedia"&gt;&lt;em&gt;tikkoun&lt;/em&gt;&lt;/a&gt;, la réparation du monde, en relevant ces étincelles par la prière et les actes justes. Ce messianisme intérieur nourrit au XVIIe siècle l’aventure de Sabbataï Tsevi, puis, au XVIIIe, le hassidisme.&lt;/p&gt; &lt;p&gt;À la Renaissance, Pic de la Mirandole fonde une « Kabbale chrétienne ». Longtemps méprisée par les historiens, la Kabbale a été réhabilitée au XXe siècle par les travaux de Gershom Scholem, qui en a fait un objet d’étude majeur.&lt;/p&gt;  &lt;audio controls title="La kabbale par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14512-03.03.2016-ITEMA_20927570-2016F23912S0063-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TR8zo52EzWI</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La kabbale, c'est quoi?" par Banque spirituelle</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tradition mystique du judaïsme qui contemple les dix émanations de Dieu et appelle l’être humain à réparer le monde.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac LOURIA;Moïse de LEÓN;NAHMANIDE;Abraham ABOULAFIA</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3010,89 +3103,94 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védas et brahmanisme</t>
+          <t xml:space="preserve">Pensée juive</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="n">
-        <v>-520</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme"  title=" Wikipedia"&gt;Le Confucianisme&lt;/a&gt; est la tradition de pensée issue de &lt;a href="https://fr.wikipedia.org/wiki/Confucius" title=" Wikipedia"&gt;Confucius&lt;/a&gt; (551-479 av. J.-C.), lettré de l’État de Lu, en Chine, qui chercha en vain un prince prêt à appliquer ses idées. Ses paroles, recueillies par ses disciples dans les &lt;em&gt;Entretiens&lt;/em&gt;, proposent de restaurer l’harmonie d’une société en crise non par la force ou par la loi, mais par la vertu, l’éducation et le respect des rites.&lt;/p&gt; &lt;p&gt;Son idéal est l’« homme de bien » (&lt;em&gt;junzi&lt;/em&gt;), qui se perfectionne sans cesse par l’étude. Les vertus cardinales sont l’humanité ou bienveillance (&lt;em&gt;ren&lt;/em&gt;), la droiture (&lt;em&gt;yi&lt;/em&gt;), les rites (&lt;em&gt;li&lt;/em&gt;), qui règlent avec justesse les relations humaines, la sagesse (&lt;em&gt;zhi&lt;/em&gt;) et la fidélité à la parole donnée (&lt;em&gt;xin&lt;/em&gt;). La société repose sur la famille et la piété filiale : chacun doit tenir son rôle dans les relations entre souverain et sujet, père et fils, époux, aînés et cadets, amis. Le prince gouverne par l’exemple, et les mots doivent correspondre aux choses : c’est la « rectification des noms ». Après Confucius, &lt;a href="https://fr.wikipedia.org/wiki/Mencius" title=" Wikipedia"&gt;Mencius&lt;/a&gt; affirme que la nature humaine est bonne, Xunzi qu’elle doit être redressée par l’éducation. Sous les Han, le confucianisme devient la doctrine officielle de l’empire, et les concours de recrutement des fonctionnaires, fondés sur ses classiques, durent jusqu’en 1905. Au XIIe siècle, Zhu Xi le renouvelle par une métaphysique : c’est le néoconfucianisme.&lt;/p&gt; &lt;p&gt;Il s’étend à la Corée, au Japon et au Viêt Nam. Combattu au XXe siècle comme cause du retard chinois, il connaît aujourd’hui un renouveau en Chine.&lt;/p&gt;  &lt;audio controls title="Le Confucianisme et les valeurs asiatiques par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-14.05.2019-ITEMA_22061347-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+          <t xml:space="preserve">Herméneutique juive;Néoplatonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9sychasme" title=" Wikipedia"&gt;L’Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme orthodoxe. Son nom vient du grec &lt;em&gt;hésychia&lt;/em&gt;, « silence, tranquillité » : il s’agit de faire taire les pensées pour s’unir à Dieu dans le calme du cœur. Ses racines remontent aux moines et ermites d’Égypte et de Syrie, les Pères du désert, aux IVe et Ve siècles, puis à des maîtres comme Jean Climaque, auteur de &lt;em&gt;L’Échelle sainte&lt;/em&gt; au VIIe siècle, et Syméon le Nouveau Théologien vers l’an mil.&lt;/p&gt; &lt;p&gt;Sa pratique centrale est la &lt;a href="https://fr.wikipedia.org/wiki/Pri%C3%A8re_du_c%C5%93ur" title=" Wikipedia"&gt;prière de Jésus&lt;/a&gt; : le moine répète sans cesse « Seigneur Jésus-Christ, Fils de Dieu, aie pitié de moi », au rythme de sa respiration, la tête inclinée vers la poitrine, pour que la prière descende de l’intelligence dans le cœur. Au XIVe siècle, des moines du mont Athos disent voir ainsi la lumière divine, celle qui entoura le Christ lors de sa Transfiguration sur le mont Thabor. Le moine calabrais Barlaam les accuse de superstition : Dieu ne peut pas être vu. &lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas" title=" Wikipedia"&gt;Grégoire Palamas&lt;/a&gt;, futur archevêque de Thessalonique, répond en distinguant l’essence de Dieu, à jamais inaccessible, et ses énergies, qui se communiquent réellement à l’homme et rendent possible sa « divinisation ». Des conciles réunis à Constantinople lui donnent raison en 1341 et en 1351.&lt;/p&gt; &lt;p&gt;En 1782 paraît la &lt;em&gt;Philocalie&lt;/em&gt;, recueil de textes hésychastes bientôt traduit en slavon. L’hésychasme inspire alors les « startsy », les maîtres spirituels de Russie, et les &lt;em&gt;Récits d’un pèlerin russe&lt;/em&gt; ; il reste au cœur de la spiritualité orthodoxe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="J17" s="2" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christianisme antique et médiéval</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="n">
-        <v>-510</v>
+        <v>-600</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="2" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3101,34 +3199,34 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensées africaines</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>43</v>
@@ -3144,30 +3242,30 @@
         </is>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>-500</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>109</v>
+        <v>-550</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>116</v>
+        <v>90</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>119</v>
+        <v>93</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>43</v>
@@ -3179,185 +3277,168 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+          <t xml:space="preserve">Védas et brahmanisme</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sâmkhya</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Védisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="n">
-        <v>-500</v>
+        <v>-520</v>
       </c>
       <c r="B21" s="9"/>
       <c r="C21" s="9" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>122</v>
+        <v>96</v>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme"  title=" Wikipedia"&gt;Le Confucianisme&lt;/a&gt; est la tradition de pensée issue de &lt;a href="https://fr.wikipedia.org/wiki/Confucius" title=" Wikipedia"&gt;Confucius&lt;/a&gt; (551-479 av. J.-C.), lettré de l’État de Lu, en Chine, qui chercha en vain un prince prêt à appliquer ses idées. Ses paroles, recueillies par ses disciples dans les &lt;em&gt;Entretiens&lt;/em&gt;, proposent de restaurer l’harmonie d’une société en crise non par la force ou par la loi, mais par la vertu, l’éducation et le respect des rites.&lt;/p&gt; &lt;p&gt;Son idéal est l’« homme de bien » (&lt;em&gt;junzi&lt;/em&gt;), qui se perfectionne sans cesse par l’étude. Les vertus cardinales sont l’humanité ou bienveillance (&lt;em&gt;ren&lt;/em&gt;), la droiture (&lt;em&gt;yi&lt;/em&gt;), les rites (&lt;em&gt;li&lt;/em&gt;), qui règlent avec justesse les relations humaines, la sagesse (&lt;em&gt;zhi&lt;/em&gt;) et la fidélité à la parole donnée (&lt;em&gt;xin&lt;/em&gt;). La société repose sur la famille et la piété filiale : chacun doit tenir son rôle dans les relations entre souverain et sujet, père et fils, époux, aînés et cadets, amis. Le prince gouverne par l’exemple, et les mots doivent correspondre aux choses : c’est la « rectification des noms ». Après Confucius, &lt;a href="https://fr.wikipedia.org/wiki/Mencius" title=" Wikipedia"&gt;Mencius&lt;/a&gt; affirme que la nature humaine est bonne, Xunzi qu’elle doit être redressée par l’éducation. Sous les Han, le confucianisme devient la doctrine officielle de l’empire, et les concours de recrutement des fonctionnaires, fondés sur ses classiques, durent jusqu’en 1905. Au XIIe siècle, Zhu Xi le renouvelle par une métaphysique : c’est le néoconfucianisme.&lt;/p&gt; &lt;p&gt;Il s’étend à la Corée, au Japon et au Viêt Nam. Combattu au XXe siècle comme cause du retard chinois, il connaît aujourd’hui un renouveau en Chine.&lt;/p&gt;  &lt;audio controls title="Le Confucianisme et les valeurs asiatiques par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-14.05.2019-ITEMA_22061347-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F21" s="9" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="2" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M21" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="n">
+        <v>-510</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées africaines</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>-500</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Védas et brahmanisme</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="n">
-        <v>-470</v>
-      </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M22" s="2" t="s">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>-500</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="n">
-        <v>-450</v>
-      </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="n">
-        <v>-410</v>
-      </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -3365,162 +3446,181 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japon : shintō et voies nationales</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="n">
-        <v>-400</v>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sâmkhya</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
       <c r="J25" s="2" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védas et brahmanisme</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="n">
+        <v>-470</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>-400</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="M26" s="2" t="s">
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="n">
+        <v>-450</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M27" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="n">
-        <v>-350</v>
-      </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>-350</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>165</v>
-      </c>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="n">
+        <v>-410</v>
+      </c>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
       <c r="J28" s="2" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>101</v>
@@ -3532,42 +3632,40 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>-250</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>171</v>
-      </c>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="n">
+        <v>-400</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
       <c r="J29" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3576,45 +3674,37 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="n">
-        <v>-150</v>
-      </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="n">
+        <v>-400</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="J30" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>155</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -3623,39 +3713,34 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brahmanisme</t>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="n">
-        <v>-100</v>
+        <v>-350</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="9" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
       <c r="J31" s="2" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>88</v>
@@ -3679,82 +3764,74 @@
         </is>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>100</v>
+        <v>-350</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="K32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
+        <v>-250</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="K33" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="G33" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>43</v>
@@ -3766,45 +3843,45 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="n">
-        <v>450</v>
+        <v>-150</v>
       </c>
       <c r="B34" s="14"/>
-      <c r="C34" s="14" t="n">
-        <v>450</v>
+      <c r="C34" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>198</v>
+        <v>174</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="14"/>
       <c r="J34" s="2" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3813,42 +3890,45 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zoroastrisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>205</v>
-      </c>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
       <c r="J35" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3857,36 +3937,36 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>22</v>
@@ -3909,40 +3989,42 @@
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="2" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3951,45 +4033,45 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalâm</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Védisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="n">
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="B38" s="14"/>
-      <c r="C38" s="14" t="s">
-        <v>217</v>
+      <c r="C38" s="14" t="n">
+        <v>450</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>224</v>
+        <v>197</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>198</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
       <c r="J38" s="2" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3998,42 +4080,42 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brahmanisme</t>
+          <t xml:space="preserve">Zoroastrisme</t>
         </is>
       </c>
     </row>
     <row r="39" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4042,48 +4124,45 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védanta</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9" t="n">
-        <v>820</v>
-      </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
+          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="J40" s="2" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>239</v>
+        <v>101</v>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
@@ -4092,31 +4171,39 @@
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>850</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>850</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>243</v>
-      </c>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="n">
+        <v>750</v>
+      </c>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
       <c r="J41" s="2" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>22</v>
@@ -4131,45 +4218,45 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aristotélisme;Néoplatonisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Kalâm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="n">
-        <v>890</v>
+        <v>750</v>
       </c>
       <c r="B42" s="14"/>
       <c r="C42" s="14" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>247</v>
+        <v>223</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>224</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="14"/>
       <c r="J42" s="2" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4178,45 +4265,42 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mutazilisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>251</v>
+        <v>800</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>800</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>258</v>
+        <v>88</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4225,90 +4309,87 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée juive</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herméneutique juive;Falsafa</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e" title=" Wikipedia"&gt;Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement de la pensée confucéenne dans la péninsule coréenne. Arrivé dès l’époque des Trois Royaumes, le confucianisme inspire sous la dynastie Goryeo l’organisation de l’État, avec l’instauration en 958 d’examens pour recruter les fonctionnaires. À la fin du XIIIe siècle, le néoconfucianisme de Zhu Xi est introduit depuis la Chine. Il devient la doctrine officielle de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9riode_Joseon" title=" Wikipedia"&gt;dynastie Joseon&lt;/a&gt; (1392-1910), dont les fondateurs s’appuient sur des lettrés qui veulent réformer l’État et réduire l’influence du bouddhisme.&lt;/p&gt; &lt;p&gt;Deux figures dominent ce courant au XVIe siècle. &lt;a href="https://fr.wikipedia.org/wiki/Yi_Hwang" title=" Wikipedia"&gt;Yi Hwang&lt;/a&gt;, dit Toegye (1501-1570), affirme la primauté du principe (&lt;em&gt;li&lt;/em&gt;), réalité immatérielle et morale, sur l’énergie matérielle (&lt;em&gt;gi&lt;/em&gt;). Il en sort une célèbre controverse, le « débat des quatre et des sept » : les quatre sentiments moraux, comme la compassion, naissent-ils du principe, et les sept émotions ordinaires, comme la colère ou la joie, de l’énergie ? &lt;a href="https://fr.wikipedia.org/wiki/Yi_I" title=" Wikipedia"&gt;Yi I&lt;/a&gt;, dit Yulgok (1536-1584), défend au contraire leur unité dynamique : le principe n’agit jamais sans l’énergie. Ce débat, qui oppose ensuite des écoles rivales, structure la philosophie coréenne pendant des siècles.&lt;/p&gt; &lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (&lt;em&gt;seonbi&lt;/em&gt;) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (&lt;em&gt;seowon&lt;/em&gt;) diffusent cet idéal dans tout le pays. Au XVIIIe siècle, le mouvement Silhak, le « savoir pratique », le tourne vers les réformes concrètes. Son empreinte demeure profonde dans la Corée d’aujourd’hui : respect des aînés, valorisation de l’éducation, rites familiaux et éthique du travail.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>262</v>
-      </c>
+          <t xml:space="preserve">Védanta</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="n">
+        <v>820</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
       <c r="J44" s="2" t="s">
-        <v>263</v>
+        <v>238</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Néoconfucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>58</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_azt%C3%A8que" title=" Wikipedia"&gt;La Pensée nahua&lt;/a&gt; désigne la réflexion philosophique des peuples de langue nahuatl, dont les Aztèques ou Mexicas, dans le Mexique central avant la conquête espagnole de 1521. Elle était portée par les &lt;em&gt;tlamatinime&lt;/em&gt;, « ceux qui savent quelque chose », sages et maîtres du &lt;em&gt;calmecac&lt;/em&gt;, l’école où l’on formait les jeunes nobles. Nous la connaissons par des codex, des chants et des discours recueillis après la conquête, notamment par le franciscain Bernardino de Sahagún.&lt;/p&gt; &lt;p&gt;L’historien mexicain &lt;a href="https://fr.wikipedia.org/wiki/Miguel_Le%C3%B3n-Portilla" title=" Wikipedia"&gt;Miguel León-Portilla&lt;/a&gt; l’a fait connaître dans &lt;em&gt;La filosofía náhuatl estudiada en sus fuentes&lt;/em&gt; (1956). Les sages s’interrogent sur la fragilité de l’existence : sur terre tout est passager, comme les fleurs qui se fanent, et l’on se demande si quelque chose est vrai, enraciné. Leur réponse est &lt;em&gt;in xochitl in cuicatl&lt;/em&gt;, « la fleur et le chant », c’est-à-dire la poésie, seule capable peut-être de dire le vrai. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Nezahualc%C3%B3yotl" title=" Wikipedia"&gt;Nezahualcóyotl&lt;/a&gt;, souverain de Texcoco au XVe siècle, auquel on attribue de nombreux poèmes, en est la grande figure. Le principe suprême, Ometeotl, « dieu de la dualité », unit le masculin et le féminin ; le monde est fait de couples complémentaires, vie et mort, ordre et désordre, en équilibre instable. Le temps est cyclique : quatre « soleils », quatre âges du monde, ont déjà été détruits, et nous vivons sous le cinquième.&lt;/p&gt; &lt;p&gt;Plus récemment, le philosophe James Maffie a lu dans le &lt;em&gt;teotl&lt;/em&gt; une énergie sacrée, unique et toujours en mouvement, dont toutes choses sont des aspects. Cette pensée est aujourd’hui étudiée comme une véritable tradition philosophique.&lt;/p&gt;</t>
-        </is>
+        <v>240</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4317,36 +4398,39 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensées autochtones</t>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mysticisme mésoaméricain</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>1150</v>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>1150</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>272</v>
-      </c>
+          <t xml:space="preserve">Aristotélisme;Néoplatonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="n">
+        <v>890</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
       <c r="J46" s="2" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>22</v>
@@ -4354,96 +4438,95 @@
       <c r="M46" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N46" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
-        </is>
-      </c>
-      <c r="Q46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Falsafa;Soufisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9" t="n">
-        <v>1150</v>
-      </c>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mutazilisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
+        <v>900</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="J47" s="2" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="K47" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique juive;Falsafa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e" title=" Wikipedia"&gt;Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement de la pensée confucéenne dans la péninsule coréenne. Arrivé dès l’époque des Trois Royaumes, le confucianisme inspire sous la dynastie Goryeo l’organisation de l’État, avec l’instauration en 958 d’examens pour recruter les fonctionnaires. À la fin du XIIIe siècle, le néoconfucianisme de Zhu Xi est introduit depuis la Chine. Il devient la doctrine officielle de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9riode_Joseon" title=" Wikipedia"&gt;dynastie Joseon&lt;/a&gt; (1392-1910), dont les fondateurs s’appuient sur des lettrés qui veulent réformer l’État et réduire l’influence du bouddhisme.&lt;/p&gt; &lt;p&gt;Deux figures dominent ce courant au XVIe siècle. &lt;a href="https://fr.wikipedia.org/wiki/Yi_Hwang" title=" Wikipedia"&gt;Yi Hwang&lt;/a&gt;, dit Toegye (1501-1570), affirme la primauté du principe (&lt;em&gt;li&lt;/em&gt;), réalité immatérielle et morale, sur l’énergie matérielle (&lt;em&gt;gi&lt;/em&gt;). Il en sort une célèbre controverse, le « débat des quatre et des sept » : les quatre sentiments moraux, comme la compassion, naissent-ils du principe, et les sept émotions ordinaires, comme la colère ou la joie, de l’énergie ? &lt;a href="https://fr.wikipedia.org/wiki/Yi_I" title=" Wikipedia"&gt;Yi I&lt;/a&gt;, dit Yulgok (1536-1584), défend au contraire leur unité dynamique : le principe n’agit jamais sans l’énergie. Ce débat, qui oppose ensuite des écoles rivales, structure la philosophie coréenne pendant des siècles.&lt;/p&gt; &lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (&lt;em&gt;seonbi&lt;/em&gt;) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (&lt;em&gt;seowon&lt;/em&gt;) diffusent cet idéal dans tout le pays. Au XVIIIe siècle, le mouvement Silhak, le « savoir pratique », le tourne vers les réformes concrètes. Son empreinte demeure profonde dans la Corée d’aujourd’hui : respect des aînés, valorisation de l’éducation, rites familiaux et éthique du travail.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K48" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>101</v>
@@ -4455,44 +4538,44 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+          <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Zen;Shintoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_vietnamienne" title=" Wikipedia"&gt;La Philosophie vietnamienne&lt;/a&gt; se caractérise par le Tam Giáo, les « trois enseignements » : une alliance durable entre le confucianisme, le bouddhisme et le taoïsme, à laquelle s’ajoutent le culte des ancêtres et celui des génies protecteurs des villages. Un adage vietnamien dit que « les trois enseignements ont une même source ». Chacun a son domaine : le confucianisme règle la famille et l’État, le bouddhisme la vie spirituelle, le taoïsme la médecine, la divination et les rites du quotidien.&lt;/p&gt; &lt;p&gt;Le bouddhisme arrive très tôt, dès les premiers siècles de notre ère, par la mer et par la Chine. Après l’indépendance, en 939, les dynasties Lý et Trần le favorisent : le roi &lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;Trần Nhân Tông&lt;/a&gt;, vainqueur des invasions mongoles, abdique en 1293 pour se faire moine et fonde l’école zen de Trúc Lâm, la « Forêt de bambous », proprement vietnamienne. Le confucianisme s’impose ensuite comme doctrine de l’État : le Temple de la Littérature est fondé à Hanoï en 1070, et les concours mandarinaux recrutent les fonctionnaires jusqu’en 1919. Mais les lettrés formés aux classiques confucéens pratiquaient souvent le bouddhisme dans leur vie personnelle et se retiraient volontiers en ermites taoïstes : les trois voies se complètent plus qu’elles ne s’opposent. &lt;a href="https://fr.wikipedia.org/wiki/Nguy%E1%BB%85n_Tr%C3%A3i" title=" Wikipedia"&gt;Nguyễn Trãi&lt;/a&gt; au XVe siècle, Nguyễn Bỉnh Khiêm au XVIe ou Lê Quý Đôn au XVIIIe illustrent cette sagesse composite.&lt;/p&gt; &lt;p&gt;Au XXe siècle, ce syncrétisme inspire de nouvelles religions comme le caodaïsme, tandis que le marxisme devient la doctrine officielle. L’empreinte du Tam Giáo demeure dans les rites familiaux et la morale.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_azt%C3%A8que" title=" Wikipedia"&gt;La Pensée nahua&lt;/a&gt; désigne la réflexion philosophique des peuples de langue nahuatl, dont les Aztèques ou Mexicas, dans le Mexique central avant la conquête espagnole de 1521. Elle était portée par les &lt;em&gt;tlamatinime&lt;/em&gt;, « ceux qui savent quelque chose », sages et maîtres du &lt;em&gt;calmecac&lt;/em&gt;, l’école où l’on formait les jeunes nobles. Nous la connaissons par des codex, des chants et des discours recueillis après la conquête, notamment par le franciscain Bernardino de Sahagún.&lt;/p&gt; &lt;p&gt;L’historien mexicain &lt;a href="https://fr.wikipedia.org/wiki/Miguel_Le%C3%B3n-Portilla" title=" Wikipedia"&gt;Miguel León-Portilla&lt;/a&gt; l’a fait connaître dans &lt;em&gt;La filosofía náhuatl estudiada en sus fuentes&lt;/em&gt; (1956). Les sages s’interrogent sur la fragilité de l’existence : sur terre tout est passager, comme les fleurs qui se fanent, et l’on se demande si quelque chose est vrai, enraciné. Leur réponse est &lt;em&gt;in xochitl in cuicatl&lt;/em&gt;, « la fleur et le chant », c’est-à-dire la poésie, seule capable peut-être de dire le vrai. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Nezahualc%C3%B3yotl" title=" Wikipedia"&gt;Nezahualcóyotl&lt;/a&gt;, souverain de Texcoco au XVe siècle, auquel on attribue de nombreux poèmes, en est la grande figure. Le principe suprême, Ometeotl, « dieu de la dualité », unit le masculin et le féminin ; le monde est fait de couples complémentaires, vie et mort, ordre et désordre, en équilibre instable. Le temps est cyclique : quatre « soleils », quatre âges du monde, ont déjà été détruits, et nous vivons sous le cinquième.&lt;/p&gt; &lt;p&gt;Plus récemment, le philosophe James Maffie a lu dans le &lt;em&gt;teotl&lt;/em&gt; une énergie sacrée, unique et toujours en mouvement, dont toutes choses sont des aspects. Cette pensée est aujourd’hui étudiée comme une véritable tradition philosophique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F49" s="1" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4501,81 +4584,89 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+          <t xml:space="preserve">Pensées autochtones</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianisme;Bouddhisme Mahayana</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="366" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Mysticisme mésoaméricain</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
-        <v>1650</v>
+        <v>1150</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>1650</v>
+        <v>1150</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>292</v>
+        <v>269</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>270</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J50" s="23" t="s">
-        <v>295</v>
+        <v>272</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>1650</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>297</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
+      <c r="Q50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsafa;Soufisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
       <c r="J51" s="2" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>301</v>
+        <v>22</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>101</v>
@@ -4592,37 +4683,34 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Néoconfucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="14" t="n">
-        <v>1680</v>
-      </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>283</v>
+      </c>
       <c r="J52" s="2" t="s">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>22</v>
+        <v>285</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>101</v>
@@ -4639,40 +4727,39 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shintoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="14" t="n">
-        <v>1720</v>
-      </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14" t="n">
-        <v>1720</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>308</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="23" t="s">
-        <v>312</v>
+          <t xml:space="preserve">Bouddhisme Zen;Shintoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_vietnamienne" title=" Wikipedia"&gt;La Philosophie vietnamienne&lt;/a&gt; se caractérise par le Tam Giáo, les « trois enseignements » : une alliance durable entre le confucianisme, le bouddhisme et le taoïsme, à laquelle s’ajoutent le culte des ancêtres et celui des génies protecteurs des villages. Un adage vietnamien dit que « les trois enseignements ont une même source ». Chacun a son domaine : le confucianisme règle la famille et l’État, le bouddhisme la vie spirituelle, le taoïsme la médecine, la divination et les rites du quotidien.&lt;/p&gt; &lt;p&gt;Le bouddhisme arrive très tôt, dès les premiers siècles de notre ère, par la mer et par la Chine. Après l’indépendance, en 939, les dynasties Lý et Trần le favorisent : le roi &lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;Trần Nhân Tông&lt;/a&gt;, vainqueur des invasions mongoles, abdique en 1293 pour se faire moine et fonde l’école zen de Trúc Lâm, la « Forêt de bambous », proprement vietnamienne. Le confucianisme s’impose ensuite comme doctrine de l’État : le Temple de la Littérature est fondé à Hanoï en 1070, et les concours mandarinaux recrutent les fonctionnaires jusqu’en 1919. Mais les lettrés formés aux classiques confucéens pratiquaient souvent le bouddhisme dans leur vie personnelle et se retiraient volontiers en ermites taoïstes : les trois voies se complètent plus qu’elles ne s’opposent. &lt;a href="https://fr.wikipedia.org/wiki/Nguy%E1%BB%85n_Tr%C3%A3i" title=" Wikipedia"&gt;Nguyễn Trãi&lt;/a&gt; au XVe siècle, Nguyễn Bỉnh Khiêm au XVIe ou Lê Quý Đôn au XVIIIe illustrent cette sagesse composite.&lt;/p&gt; &lt;p&gt;Au XXe siècle, ce syncrétisme inspire de nouvelles religions comme le caodaïsme, tandis que le marxisme devient la doctrine officielle. L’empreinte du Tam Giáo demeure dans les rites familiaux et la morale.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>290</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4681,39 +4768,49 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Réveils de l’islam moderne</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme;Bouddhisme Mahayana</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
-        <v>1750</v>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>1750</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Silhak" title=" Wikipedia"&gt;Le Silhak&lt;/a&gt;, ou « savoir pratique », est un mouvement de réforme intellectuelle né en Corée au XVIIe siècle, sous la dynastie Joseon, et qui s’épanouit au XVIIIe. Il naît d’un pays ruiné par les invasions japonaises (1592-1598) puis mandchoues (1627 et 1636) : des lettrés reprochent alors au néoconfucianisme officiel de s’enfermer dans des querelles métaphysiques sur le principe et l’énergie, pendant que les paysans meurent de faim. Leur mot d’ordre, venu de Chine, est de « chercher la vérité dans les faits ».&lt;/p&gt; &lt;p&gt;Le premier grand nom en est Yu Hyeongwon (1622-1673), qui propose de redistribuer les terres à ceux qui les cultivent. Yi Ik (1681-1763) poursuit cette école du « bon gouvernement du monde » en critiquant l’esclavage, les privilèges héréditaires et le mépris du travail manuel. Une seconde branche, l’école des « études du Nord », autour de Pak Ji-won (1737-1805) et de Pak Je-ga, veut plutôt développer le commerce, les routes et les techniques, à l’exemple de la Chine des Qing. Le Silhak s’ouvre aussi aux sciences occidentales introduites en Chine par les jésuites : astronomie, cartographie, mathématiques.&lt;/p&gt; &lt;p&gt;Il culmine avec &lt;a href="https://fr.wikipedia.org/wiki/Jeong_Yak-yong" title=" Wikipedia"&gt;Jeong Yak-yong&lt;/a&gt; (1762-1836), dit Dasan, qui réunit les deux branches. Exilé dix-huit ans après la persécution des catholiques de 1801, il y écrit près de cinq cents volumes, dont un manuel pour bien administrer le peuple. Le calligraphe Kim Jeong-hui (1786-1856) en est l’un des derniers représentants. Marginalisé en son temps, le Silhak est aujourd’hui vu comme l’un des ferments de la modernité coréenne.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>317</v>
+        <v>1500</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EqO4cPcG4KY</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Le SIKHISME : La religion qui affirme que "DIEU N'A PAS DE RELIGION" (Le message de l'Unité)" par MYSTICA</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>101</v>
+        <v>458</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -4722,47 +4819,42 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianismes</t>
+          <t xml:space="preserve">Hindouismes de dévotion</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianisme coréen</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9" t="n">
-        <v>1760</v>
-      </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martinisme" title=" Wikipedia"&gt;Le Martinisme&lt;/a&gt; est un courant ésotérique et mystique d’inspiration judéo-chrétienne, né en France au XVIIIe siècle dans les milieux de la franc-maçonnerie. Il doit son nom à deux hommes que l’on confond souvent : Martinès de Pasqually (vers 1727-1774), théurge à l’origine mal connue, et son disciple &lt;a href="https://fr.wikipedia.org/wiki/Louis-Claude_de_Saint-Martin" title=" Wikipedia"&gt;Louis-Claude de Saint-Martin&lt;/a&gt; (1743-1803), dit le « Philosophe inconnu ». Son thème central est la « réintégration » : le retour de l’être humain à la dignité spirituelle qu’il avait avant la chute.&lt;/p&gt; &lt;p&gt;Vers 1761, Martinès fonde l’ordre des Élus Coëns, dont les loges s’établissent à Bordeaux, Lyon et Paris. Dans son &lt;em&gt;Traité de la réintégration des êtres&lt;/em&gt;, il enseigne que l’homme, créé pour servir d’intermédiaire entre Dieu et le monde, a chuté par orgueil, comme Adam, et se trouve exilé dans la matière. Pour se racheter, il doit pratiquer l’ascèse, la prière et la théurgie, des rites destinés à entrer en contact avec les esprits bienfaisants. Saint-Martin, d’abord son secrétaire, délaisse ces rites pour une « voie intérieure », celle du cœur, nourrie par le mystique allemand Jacob Böhme. À Lyon, Jean-Baptiste Willermoz transmet leur doctrine au Rite écossais rectifié, une branche de la franc-maçonnerie qui existe toujours.&lt;/p&gt; &lt;p&gt;À la fin du XIXe siècle, l’occultiste Papus fonde un Ordre martiniste, et au XXe siècle Robert Ambelain fait renaître les Élus Coëns. On distingue depuis le « martinésisme », théurgique, et le « saint-martinisme », mystique. Joseph de Maistre, Balzac ou Franz von Baader ont lu Saint-Martin.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="2" t="s">
-        <v>323</v>
+          <t xml:space="preserve">Bhakti;Soufisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="366" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E55" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J55" s="23" t="s">
+        <v>295</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4771,45 +4863,40 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ésotérismes et gnoses</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kabbale</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="14" t="n">
-        <v>1820</v>
-      </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14" t="n">
-        <v>1820</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>324</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="F56" s="14" t="s">
-        <v>326</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="H56" s="14"/>
-      <c r="I56" s="16"/>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>297</v>
+      </c>
       <c r="J56" s="2" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>108</v>
+        <v>196</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -4818,45 +4905,45 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
+          <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Romantisme;Idéalisme allemand</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
-        <v>1830</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>333</v>
-      </c>
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="14" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="F57" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
       <c r="J57" s="2" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="L57" s="2" t="s">
-        <v>336</v>
+        <v>22</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -4865,44 +4952,45 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Réveils de l’islam moderne</t>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lumières</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
-        <v>1840</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9osophie" title=" Wikipedia"&gt;La Théosophie&lt;/a&gt; est un courant ésotérique et spirituel fondé par &lt;a href="https://fr.wikipedia.org/wiki/Helena_Blavatsky" title=" Wikipedia"&gt;Helena Blavatsky&lt;/a&gt; (1831-1891), née dans l’Empire russe, qui crée à New York en 1875, avec le colonel américain Henry Steel Olcott et William Quan Judge, la &lt;a href="https://fr.wikipedia.org/wiki/Soci%C3%A9t%C3%A9_th%C3%A9osophique" title=" Wikipedia"&gt;Société théosophique&lt;/a&gt;. Le mot, du grec &lt;em&gt;theos&lt;/em&gt;, « dieu », et &lt;em&gt;sophia&lt;/em&gt;, « sagesse », signifie « sagesse divine » : la Théosophie se veut la redécouverte d’une sagesse universelle et cachée, dont les religions, les sciences et les philosophies ne seraient que des expressions partielles.&lt;/p&gt; &lt;p&gt;La Société se donne trois buts : former le noyau d’une fraternité universelle de l’humanité, sans distinction de race, de croyance, de sexe ou de caste ; encourager l’étude comparée des religions, des philosophies et des sciences ; étudier les lois inexpliquées de la nature et les pouvoirs latents de l’homme. Blavatsky expose sa doctrine dans &lt;em&gt;Isis dévoilée&lt;/em&gt; (1877) et &lt;em&gt;La Doctrine secrète&lt;/em&gt; (1888), où elle mêle le bouddhisme, l’hindouisme, la Kabbale et le néoplatonisme : l’univers procède d’un principe unique, l’humanité traverse de longs cycles d’évolution et l’âme progresse par réincarnations successives selon la loi du karma. Elle dit tenir ces enseignements de « Maîtres » vivant au Tibet. Les fondateurs s’installent en Inde en 1879, et le siège est fixé à Adyar, près de Madras, en 1882.&lt;/p&gt; &lt;p&gt;Annie Besant, présidente à partir de 1907, présente le jeune Jiddu Krishnamurti comme un futur instructeur du monde, rôle qu’il refuse en 1929. Rudolf Steiner s’en sépare pour fonder l’anthroposophie. La Théosophie a marqué des artistes comme Kandinsky et Mondrian, le mouvement New Age et la diffusion en Occident de l’hindouisme et du bouddhisme.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>342</v>
+          <t xml:space="preserve">Shintoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="14" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14" t="n">
+        <v>1720</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="F58" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="23" t="s">
+        <v>312</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4911,95 +4999,105 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ésotérismes et gnoses</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hermétisme;Hindouisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="14" t="n">
-        <v>1845</v>
-      </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14" t="n">
-        <v>1845</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="H59" s="14"/>
-      <c r="I59" s="16"/>
-      <c r="J59" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
-        </is>
-      </c>
-      <c r="Q59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Idéalisme allemand</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D60" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="F60" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="G60" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="16"/>
+          <t xml:space="preserve">Réveils de l’islam moderne</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1">
+        <v>1740</v>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1740</t>
+        </is>
+      </c>
+      <c r="D59" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hassidisme</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;Le hassidisme&lt;/a&gt;, de l’hébreu &lt;em&gt;hassid&lt;/em&gt;, « pieux », est un mouvement de renouveau mystique du judaïsme né au XVIIIe siècle en Podolie, dans l’actuelle Ukraine, alors polonaise, autour du Baal Shem Tov, le « Maître du Bon Nom ». Il paraît dans des communautés juives pauvres et éprouvées par les massacres et par la faillite du faux messie Sabbataï Tsevi, où le savoir talmudique est réservé à une élite.&lt;/p&gt; &lt;p&gt;Reprenant les idées de la Kabbale, le hassidisme les met à la portée de tous. Dieu est présent partout, jusque dans les choses les plus humbles : on peut donc le servir non seulement par l’étude, mais par la prière fervente, le chant, la danse et chaque geste du quotidien, accompli avec attention. La joie est une forme de piété, la tristesse un obstacle. La ferveur du cœur compte plus que l’érudition, et le plus simple des fidèles peut s’unir à Dieu. Au centre de chaque communauté se tient le &lt;a href="https://fr.wikipedia.org/wiki/Tsadik" title=" Wikipedia"&gt;&lt;em&gt;tsaddik&lt;/em&gt;&lt;/a&gt;, le « juste », maître spirituel qui guide ses disciples et intercède pour eux. Les maîtres hassidiques enseignent par des récits et des paraboles, comme ceux de &lt;a href="https://fr.wikipedia.org/wiki/Nahman_de_Bratslav" title=" Wikipedia"&gt;Nahman de Bratslav&lt;/a&gt;, arrière-petit-fils du Baal Shem Tov.&lt;/p&gt; &lt;p&gt;Combattu d’abord par les rabbins traditionnels, les &lt;a href="https://fr.wikipedia.org/wiki/Mitnagdim" title=" Wikipedia"&gt;Mitnagdim&lt;/a&gt;, le mouvement gagne une grande partie des Juifs d’Europe de l’Est. Presque anéanti par la Shoah, il renaît aux États-Unis et en Israël, où ses communautés, comme celle de Loubavitch, sont aujourd’hui très vivantes. Martin Buber a fait connaître ses récits en Occident ; Abraham Heschel et Elie Wiesel, issus de familles hassidiques, en ont transmis l’esprit.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ph9ZTOd6E54</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"C'est quoi le hassidisme ?" par Hugo Brdl</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement mystique juif né en Ukraine autour du Baal Shem Tov : servir Dieu dans la joie, l’humilité et chaque geste du quotidien.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAAL SHEM TOV;Martin BUBER</t>
+        </is>
+      </c>
+      <c r="M59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N59"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Silhak" title=" Wikipedia"&gt;Le Silhak&lt;/a&gt;, ou « savoir pratique », est un mouvement de réforme intellectuelle né en Corée au XVIIe siècle, sous la dynastie Joseon, et qui s’épanouit au XVIIIe. Il naît d’un pays ruiné par les invasions japonaises (1592-1598) puis mandchoues (1627 et 1636) : des lettrés reprochent alors au néoconfucianisme officiel de s’enfermer dans des querelles métaphysiques sur le principe et l’énergie, pendant que les paysans meurent de faim. Leur mot d’ordre, venu de Chine, est de « chercher la vérité dans les faits ».&lt;/p&gt; &lt;p&gt;Le premier grand nom en est Yu Hyeongwon (1622-1673), qui propose de redistribuer les terres à ceux qui les cultivent. Yi Ik (1681-1763) poursuit cette école du « bon gouvernement du monde » en critiquant l’esclavage, les privilèges héréditaires et le mépris du travail manuel. Une seconde branche, l’école des « études du Nord », autour de Pak Ji-won (1737-1805) et de Pak Je-ga, veut plutôt développer le commerce, les routes et les techniques, à l’exemple de la Chine des Qing. Le Silhak s’ouvre aussi aux sciences occidentales introduites en Chine par les jésuites : astronomie, cartographie, mathématiques.&lt;/p&gt; &lt;p&gt;Il culmine avec &lt;a href="https://fr.wikipedia.org/wiki/Jeong_Yak-yong" title=" Wikipedia"&gt;Jeong Yak-yong&lt;/a&gt; (1762-1836), dit Dasan, qui réunit les deux branches. Exilé dix-huit ans après la persécution des catholiques de 1801, il y écrit près de cinq cents volumes, dont un manuel pour bien administrer le peuple. Le calligraphe Kim Jeong-hui (1786-1856) en est l’un des derniers représentants. Marginalisé en son temps, le Silhak est aujourd’hui vu comme l’un des ferments de la modernité coréenne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>316</v>
+      </c>
       <c r="J60" s="2" t="s">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5008,45 +5106,47 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">L’Inde moderne</t>
+          <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindouisme;Lumières</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="H61" s="14"/>
-      <c r="I61" s="16"/>
+          <t xml:space="preserve">Confucianisme coréen</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="9" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martinisme" title=" Wikipedia"&gt;Le Martinisme&lt;/a&gt; est un courant ésotérique et mystique d’inspiration judéo-chrétienne, né en France au XVIIIe siècle dans les milieux de la franc-maçonnerie. Il doit son nom à deux hommes que l’on confond souvent : Martinès de Pasqually (vers 1727-1774), théurge à l’origine mal connue, et son disciple &lt;a href="https://fr.wikipedia.org/wiki/Louis-Claude_de_Saint-Martin" title=" Wikipedia"&gt;Louis-Claude de Saint-Martin&lt;/a&gt; (1743-1803), dit le « Philosophe inconnu ». Son thème central est la « réintégration » : le retour de l’être humain à la dignité spirituelle qu’il avait avant la chute.&lt;/p&gt; &lt;p&gt;Vers 1761, Martinès fonde l’ordre des Élus Coëns, dont les loges s’établissent à Bordeaux, Lyon et Paris. Dans son &lt;em&gt;Traité de la réintégration des êtres&lt;/em&gt;, il enseigne que l’homme, créé pour servir d’intermédiaire entre Dieu et le monde, a chuté par orgueil, comme Adam, et se trouve exilé dans la matière. Pour se racheter, il doit pratiquer l’ascèse, la prière et la théurgie, des rites destinés à entrer en contact avec les esprits bienfaisants. Saint-Martin, d’abord son secrétaire, délaisse ces rites pour une « voie intérieure », celle du cœur, nourrie par le mystique allemand Jacob Böhme. À Lyon, Jean-Baptiste Willermoz transmet leur doctrine au Rite écossais rectifié, une branche de la franc-maçonnerie qui existe toujours.&lt;/p&gt; &lt;p&gt;À la fin du XIXe siècle, l’occultiste Papus fonde un Ordre martiniste, et au XXe siècle Robert Ambelain fait renaître les Élus Coëns. On distingue depuis le « martinésisme », théurgique, et le « saint-martinisme », mystique. Joseph de Maistre, Balzac ou Franz von Baader ont lu Saint-Martin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
       <c r="J61" s="2" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5055,45 +5155,68 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie religieuse russe</t>
+          <t xml:space="preserve">Ésotérismes et gnoses</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slavophilisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
-        <v>1860</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>1860</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>358</v>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1">
+        <v>1770</v>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1770</t>
+        </is>
+      </c>
+      <c r="D62" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haskala</t>
+        </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt;Le Donghak&lt;/a&gt;, ou « savoir de l’Orient », est un mouvement religieux et social fondé en Corée en 1860 par Choe Je-u (1824-1864), un lettré déclassé. Il naît dans une société Joseon minée par la corruption, les épidémies et la misère paysanne, et inquiète devant l’Occident : la Chine vient d’être humiliée par la seconde guerre de l’opium, et le catholicisme, appelé « savoir de l’Occident » (&lt;em&gt;seohak&lt;/em&gt;), progresse malgré les persécutions. Choe Je-u dit avoir reçu une révélation du « Seigneur du Ciel » et veut opposer au savoir étranger une voie coréenne.&lt;/p&gt; &lt;p&gt;Sa doctrine mêle le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale est que chaque être humain « porte en lui le Ciel » (&lt;em&gt;si cheonju&lt;/em&gt;) : il faut donc « servir l’homme comme le Ciel », enseigne son successeur Choe Si-hyeong, et le mouvement finira par dire que « l’homme est le Ciel » (&lt;em&gt;in nae cheon&lt;/em&gt;). Il en découle une égalité radicale entre les nobles et les serviteurs, les hommes et les femmes, les riches et les pauvres. Les fidèles récitent une formule sacrée de vingt et un caractères et attendent l’« ouverture » d’un monde nouveau.&lt;/p&gt; &lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement gagne les campagnes et inspire en 1894 la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_paysanne_Donghak" title=" Wikipedia"&gt;révolution paysanne du Donghak&lt;/a&gt;, menée par Jeon Bong-jun ; l’arrivée de troupes chinoises et japonaises pour l’écraser déclenche la guerre sino-japonaise. Rebaptisé Cheondogyo, « religion de la Voie céleste », en 1905, il joue un grand rôle dans le mouvement d’indépendance du 1er mars 1919.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="G62" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1" t="s">
-        <v>101</v>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Haskala" title=" Wikipedia"&gt;La Haskala&lt;/a&gt;, de l’hébreu &lt;em&gt;sekhel&lt;/em&gt;, « intelligence », est le mouvement des Lumières juives, né à Berlin dans les années 1770. Ses partisans, les &lt;em&gt;maskilim&lt;/em&gt;, veulent faire sortir les Juifs du ghetto culturel où les ont enfermés des siècles de discriminations, en les ouvrant aux sciences, à la philosophie et aux langues de l’Europe, sans qu’ils renoncent pour autant à leur foi.&lt;/p&gt; &lt;p&gt;Son inspirateur est Moses Mendelssohn, surnommé le « Socrate de Berlin », admiré de Kant et ami de &lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing" title=" Wikipedia"&gt;Lessing&lt;/a&gt;, qui fait de lui le modèle de son &lt;em&gt;Nathan le Sage&lt;/em&gt;. Il traduit la Torah en allemand, imprimée en caractères hébraïques, pour que les Juifs apprennent la langue du pays. Dans &lt;em&gt;Jérusalem&lt;/em&gt; (1783), il défend la liberté de conscience et la séparation de l’État et de la religion : le judaïsme, dit-il, n’impose pas de croyances, il prescrit des pratiques, et ses vérités sont celles de la raison, accessibles à tous les hommes. Autour de lui, le médecin Marcus Herz, élève de Kant, et David Friedländer, qui plaide pour l’émancipation civile des Juifs de Prusse, poursuivent son œuvre. La Haskala fonde des écoles modernes, une presse et fait renaître l’hébreu comme langue littéraire profane.&lt;/p&gt; &lt;p&gt;Au XIXe siècle, elle gagne la Galicie et l’Empire russe. Elle prépare le &lt;a href="https://fr.wikipedia.org/wiki/Juda%C3%AFsme_r%C3%A9form%C3%A9" title=" Wikipedia"&gt;judaïsme libéral&lt;/a&gt;, la &lt;a href="https://fr.wikipedia.org/wiki/Wissenschaft_des_Judentums" title=" Wikipedia"&gt;« science du judaïsme »&lt;/a&gt;, l’étude historique de sa tradition, et indirectement le sionisme. Ses adversaires lui ont reproché d’ouvrir la voie à l’assimilation ; ses héritiers y voient l’entrée du judaïsme dans la modernité.&lt;/p&gt;  &lt;audio controls title="le jadudaîsme de la modernité par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13094-09.11.2014-ITEMA_20688848-2014C21364E0044-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">itIIrC5jvFM</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">""La Haskala : Des "Lumières" Qui Ont Éteint la Torah !" 🇰 Kitsour." par Torah-Box</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">les « Lumières juives » de Mendelssohn : unir la fidélité au judaïsme, la raison et la culture européenne.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie politique;Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moses MENDELSSOHN</t>
+        </is>
+      </c>
+      <c r="M62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5102,41 +5225,42 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+          <t xml:space="preserve">Pensée juive</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianisme coréen;Taoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
-        <v>1865</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_(art)"  title=" Wikipedia"&gt;Le Symbolisme&lt;/a&gt; est un courant littéraire, artistique et philosophique né en France dans les années 1880 et qui s’épanouit en Russie au tournant du XXe siècle. Il prend pour modèle le sonnet « Correspondances » de &lt;a href="https://fr.wikipedia.org/wiki/Charles_Baudelaire" title=" Wikipedia"&gt;Baudelaire&lt;/a&gt;, où la nature est une « forêt de symboles » : derrière le monde visible se cache une réalité spirituelle que le poète peut faire pressentir. Le manifeste de Jean Moréas paraît en 1886 ; Mallarmé, Verlaine, et en peinture Gustave Moreau ou Odilon Redon, incarnent le mouvement.&lt;/p&gt; &lt;p&gt;En Russie, il naît dans les années 1890 avec Dmitri Merejkovski, Valéri Brioussov et Constantin Balmont, puis prend une dimension métaphysique et religieuse avec une seconde génération, nourrie de la philosophie de &lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir Soloviev&lt;/a&gt; et de sa figure de la Sophia, la Sagesse divine. Pour Viatcheslav Ivanov, dont l’appartement de Saint-Pétersbourg, la « Tour », est le grand salon de l’époque, l’art doit aller « du réel au plus réel ». Pour Andreï Biély, le symbole unit la connaissance et la création, et le symbolisme devient une véritable vision du monde. Alexandre Blok chante la « Belle Dame », figure mystique de la Sophia, avant d’écrire en 1918 &lt;em&gt;Les Douze&lt;/em&gt;, poème de la révolution. Ces poètes-philosophes conçoivent l’art comme une « théurgie », une action capable de transformer le monde et de préparer sa transfiguration. Le symbolisme russe mêle la mystique orthodoxe, l’idéalisme allemand et Nietzsche.&lt;/p&gt; &lt;p&gt;Vers 1910, il entre en crise et laisse place à l’acméisme et au futurisme. Il a profondément marqué la philosophie religieuse russe de l’âge d’argent.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>367</v>
-      </c>
+          <t xml:space="preserve">Lumières</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="14" t="n">
+        <v>1820</v>
+      </c>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14" t="n">
+        <v>1820</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="F63" s="14" t="s">
+        <v>326</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="H63" s="14"/>
+      <c r="I63" s="16"/>
       <c r="J63" s="2" t="s">
-        <v>368</v>
+        <v>328</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>76</v>
@@ -5148,42 +5272,42 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie religieuse russe</t>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophiologie</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="G64" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="H64" s="9"/>
-      <c r="I64" s="9"/>
+          <t xml:space="preserve">Romantisme;Idéalisme allemand</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="n">
+        <v>1830</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>333</v>
+      </c>
       <c r="J64" s="2" t="s">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>108</v>
+        <v>335</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>58</v>
@@ -5200,37 +5324,36 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nahda</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14" t="n">
-        <v>1878</v>
-      </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14" t="n">
-        <v>1878</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="H65" s="14"/>
-      <c r="I65" s="16"/>
+          <t xml:space="preserve">Lumières</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9osophie" title=" Wikipedia"&gt;La Théosophie&lt;/a&gt; est un courant ésotérique et spirituel fondé par &lt;a href="https://fr.wikipedia.org/wiki/Helena_Blavatsky" title=" Wikipedia"&gt;Helena Blavatsky&lt;/a&gt; (1831-1891), née dans l’Empire russe, qui crée à New York en 1875, avec le colonel américain Henry Steel Olcott et William Quan Judge, la &lt;a href="https://fr.wikipedia.org/wiki/Soci%C3%A9t%C3%A9_th%C3%A9osophique" title=" Wikipedia"&gt;Société théosophique&lt;/a&gt;. Le mot, du grec &lt;em&gt;theos&lt;/em&gt;, « dieu », et &lt;em&gt;sophia&lt;/em&gt;, « sagesse », signifie « sagesse divine » : la Théosophie se veut la redécouverte d’une sagesse universelle et cachée, dont les religions, les sciences et les philosophies ne seraient que des expressions partielles.&lt;/p&gt; &lt;p&gt;La Société se donne trois buts : former le noyau d’une fraternité universelle de l’humanité, sans distinction de race, de croyance, de sexe ou de caste ; encourager l’étude comparée des religions, des philosophies et des sciences ; étudier les lois inexpliquées de la nature et les pouvoirs latents de l’homme. Blavatsky expose sa doctrine dans &lt;em&gt;Isis dévoilée&lt;/em&gt; (1877) et &lt;em&gt;La Doctrine secrète&lt;/em&gt; (1888), où elle mêle le bouddhisme, l’hindouisme, la Kabbale et le néoplatonisme : l’univers procède d’un principe unique, l’humanité traverse de longs cycles d’évolution et l’âme progresse par réincarnations successives selon la loi du karma. Elle dit tenir ces enseignements de « Maîtres » vivant au Tibet. Les fondateurs s’installent en Inde en 1879, et le siège est fixé à Adyar, près de Madras, en 1882.&lt;/p&gt; &lt;p&gt;Annie Besant, présidente à partir de 1907, présente le jeune Jiddu Krishnamurti comme un futur instructeur du monde, rôle qu’il refuse en 1929. Rudolf Steiner s’en sépare pour fonder l’anthroposophie. La Théosophie a marqué des artistes comme Kandinsky et Mondrian, le mouvement New Age et la diffusion en Occident de l’hindouisme et du bouddhisme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="J65" s="2" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>379</v>
+        <v>22</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>76</v>
@@ -5242,40 +5365,48 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie religieuse russe</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>383</v>
-      </c>
+          <t xml:space="preserve">Ésotérismes et gnoses</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hermétisme;Hindouisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="14" t="n">
+        <v>1845</v>
+      </c>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14" t="n">
+        <v>1845</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="F66" s="14" t="s">
+        <v>345</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="H66" s="14"/>
+      <c r="I66" s="16"/>
       <c r="J66" s="2" t="s">
-        <v>384</v>
+        <v>347</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>108</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
@@ -5284,39 +5415,42 @@
       </c>
       <c r="P66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
         </is>
       </c>
       <c r="Q66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="C67" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>388</v>
-      </c>
+          <t xml:space="preserve">Idéalisme allemand</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="F67" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="H67" s="14"/>
+      <c r="I67" s="16"/>
       <c r="J67" s="2" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="M67" s="2" t="s">
         <v>43</v>
@@ -5333,34 +5467,37 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jaïnisme;Néo-védanta</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="C68" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="E68" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="J68" s="21" t="s">
-        <v>394</v>
+          <t xml:space="preserve">Hindouisme;Lumières</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B68" s="14"/>
+      <c r="C68" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="H68" s="14"/>
+      <c r="I68" s="16"/>
+      <c r="J68" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>76</v>
@@ -5372,44 +5509,44 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marxisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Slavophilisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
-        <v>1911</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>395</v>
+        <v>1860</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>1860</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>397</v>
+        <v>358</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt;Le Donghak&lt;/a&gt;, ou « savoir de l’Orient », est un mouvement religieux et social fondé en Corée en 1860 par Choe Je-u (1824-1864), un lettré déclassé. Il naît dans une société Joseon minée par la corruption, les épidémies et la misère paysanne, et inquiète devant l’Occident : la Chine vient d’être humiliée par la seconde guerre de l’opium, et le catholicisme, appelé « savoir de l’Occident » (&lt;em&gt;seohak&lt;/em&gt;), progresse malgré les persécutions. Choe Je-u dit avoir reçu une révélation du « Seigneur du Ciel » et veut opposer au savoir étranger une voie coréenne.&lt;/p&gt; &lt;p&gt;Sa doctrine mêle le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale est que chaque être humain « porte en lui le Ciel » (&lt;em&gt;si cheonju&lt;/em&gt;) : il faut donc « servir l’homme comme le Ciel », enseigne son successeur Choe Si-hyeong, et le mouvement finira par dire que « l’homme est le Ciel » (&lt;em&gt;in nae cheon&lt;/em&gt;). Il en découle une égalité radicale entre les nobles et les serviteurs, les hommes et les femmes, les riches et les pauvres. Les fidèles récitent une formule sacrée de vingt et un caractères et attendent l’« ouverture » d’un monde nouveau.&lt;/p&gt; &lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement gagne les campagnes et inspire en 1894 la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_paysanne_Donghak" title=" Wikipedia"&gt;révolution paysanne du Donghak&lt;/a&gt;, menée par Jeon Bong-jun ; l’arrivée de troupes chinoises et japonaises pour l’écraser déclenche la guerre sino-japonaise. Rebaptisé Cheondogyo, « religion de la Voie céleste », en 1905, il joue un grand rôle dans le mouvement d’indépendance du 1er mars 1919.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F69" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>400</v>
+        <v>360</v>
+      </c>
+      <c r="G69" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="M69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1" t="s">
         <v>101</v>
       </c>
       <c r="O69" t="inlineStr">
@@ -5419,88 +5556,91 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Zen;Idéalisme allemand</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Confucianisme coréen;Taoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
-        <v>1920</v>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>1920</v>
+        <v>1865</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>404</v>
+        <v>364</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_(art)"  title=" Wikipedia"&gt;Le Symbolisme&lt;/a&gt; est un courant littéraire, artistique et philosophique né en France dans les années 1880 et qui s’épanouit en Russie au tournant du XXe siècle. Il prend pour modèle le sonnet « Correspondances » de &lt;a href="https://fr.wikipedia.org/wiki/Charles_Baudelaire" title=" Wikipedia"&gt;Baudelaire&lt;/a&gt;, où la nature est une « forêt de symboles » : derrière le monde visible se cache une réalité spirituelle que le poète peut faire pressentir. Le manifeste de Jean Moréas paraît en 1886 ; Mallarmé, Verlaine, et en peinture Gustave Moreau ou Odilon Redon, incarnent le mouvement.&lt;/p&gt; &lt;p&gt;En Russie, il naît dans les années 1890 avec Dmitri Merejkovski, Valéri Brioussov et Constantin Balmont, puis prend une dimension métaphysique et religieuse avec une seconde génération, nourrie de la philosophie de &lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir Soloviev&lt;/a&gt; et de sa figure de la Sophia, la Sagesse divine. Pour Viatcheslav Ivanov, dont l’appartement de Saint-Pétersbourg, la « Tour », est le grand salon de l’époque, l’art doit aller « du réel au plus réel ». Pour Andreï Biély, le symbole unit la connaissance et la création, et le symbolisme devient une véritable vision du monde. Alexandre Blok chante la « Belle Dame », figure mystique de la Sophia, avant d’écrire en 1918 &lt;em&gt;Les Douze&lt;/em&gt;, poème de la révolution. Ces poètes-philosophes conçoivent l’art comme une « théurgie », une action capable de transformer le monde et de préparer sa transfiguration. Le symbolisme russe mêle la mystique orthodoxe, l’idéalisme allemand et Nietzsche.&lt;/p&gt; &lt;p&gt;Vers 1910, il entre en crise et laisse place à l’acméisme et au futurisme. Il a profondément marqué la philosophie religieuse russe de l’âge d’argent.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F70" s="1" t="s">
-        <v>405</v>
+        <v>366</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>406</v>
+        <v>367</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>407</v>
+        <v>368</v>
       </c>
       <c r="K70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophiologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="E71" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="K71" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M70" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Inde moderne</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>1920</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Logique_paracoh%C3%A9rente"  title=" Wikipedia"&gt;La Logique paraconsistante&lt;/a&gt; désigne les systèmes logiques qui peuvent contenir des contradictions sans s’effondrer. En logique classique, en effet, une seule contradiction suffit à tout démontrer : de « A et non-A », on peut déduire n’importe quelle proposition. C’est le &lt;a href="https://fr.wikipedia.org/wiki/Principe_d%27explosion" title=" Wikipedia"&gt;principe d’explosion&lt;/a&gt;, connu depuis le Moyen Âge sous la formule « du contradictoire suit n’importe quoi ». Une logique paraconsistante bloque cette explosion : une contradiction locale y reste locale, sans contaminer tout le reste.&lt;/p&gt; &lt;p&gt;L’idée apparaît en 1910, à Kazan, chez le philosophe russe Nikolaï Vassiliev (1880-1940). Il imagine une « logique imaginaire » où la loi de non-contradiction n’est plus un axiome nécessaire, de même que les géométries non euclidiennes, nées à Kazan avec Lobatchevski, avaient abandonné le postulat des parallèles. La même année, le Polonais Jan Łukasiewicz critique le principe de non-contradiction d’Aristote. Son élève Stanisław Jaśkowski construit en 1948 le premier système formel paraconsistant, et le Brésilien Newton da Costa développe à partir de 1963 toute une famille de ces logiques. Le mot « paraconsistant » est forgé en 1976 par le philosophe péruvien Francisco Miró Quesada. Certains vont plus loin, comme l’Australien &lt;a href="https://fr.wikipedia.org/wiki/Graham_Priest" title=" Wikipedia"&gt;Graham Priest&lt;/a&gt; : selon son « dialéthéisme », certaines contradictions sont vraies, par exemple le paradoxe du menteur, « cette phrase est fausse ».&lt;/p&gt; &lt;p&gt;Ces logiques servent en informatique, pour raisonner avec des bases de données incohérentes, en droit, face à des normes contradictoires, et en philosophie des sciences, quand des théories en conflit doivent coexister.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="M71" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5509,42 +5649,45 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie analytique et pragmatisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>1921</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nouveau_confucianisme"  title=" Wikipedia"&gt;Le nouveau confucianisme&lt;/a&gt; est un courant philosophique chinois du XXe siècle qui veut renouveler la tradition confucéenne pour l’accorder à la modernité. Il naît en réaction au mouvement du 4 Mai 1919 et à la Nouvelle Culture, qui rejetaient le confucianisme comme responsable du retard de la Chine et en appelaient à « Monsieur Science » et à « Monsieur Démocratie ». Ses penseurs veulent montrer qu’un confucianisme repensé peut accueillir la science et la démocratie sans perdre sa sagesse morale.&lt;/p&gt; &lt;p&gt;Le point de départ est l’ouvrage de &lt;a href="https://fr.wikipedia.org/wiki/Liang_Shuming" title=" Wikipedia"&gt;Liang Shuming&lt;/a&gt;, &lt;em&gt;Les Cultures d’Orient et d’Occident et leurs philosophies&lt;/em&gt; (1921), qui compare les voies de l’Occident, de la Chine et de l’Inde. &lt;a href="https://fr.wikipedia.org/wiki/Xiong_Shili" title=" Wikipedia"&gt;Xiong Shili&lt;/a&gt; donne au courant une métaphysique dans son &lt;em&gt;Nouveau traité de la conscience seule&lt;/em&gt; (1932) : s’inspirant du &lt;em&gt;Livre des mutations&lt;/em&gt;, il critique le bouddhisme pour qui le monde est illusion, et pense la réalité comme un mouvement créateur continu. Feng Youlan, dans son &lt;em&gt;Nouvel enseignement du principe&lt;/em&gt; (1939), relit Zhu Xi à l’aide de la logique moderne.&lt;/p&gt; &lt;p&gt;Après 1949, le courant se poursuit surtout à Hong Kong et à Taïwan. En 1958, Mou Zongsan, Tang Junyi, Xu Fuguan et Zhang Junmai publient un manifeste adressé au monde sur la culture chinoise. Mou Zongsan, traducteur des trois &lt;em&gt;Critiques&lt;/em&gt; de Kant, dialogue avec lui pour fonder une « métaphysique morale ». Une troisième génération, avec &lt;a href="https://fr.wikipedia.org/wiki/Tu_Weiming" title=" Wikipedia"&gt;Tu Weiming&lt;/a&gt; ou Liu Shu-hsien, a porté ce courant dans les universités américaines ; il connaît depuis les années 1980 un important renouveau en Chine continentale.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>418</v>
-      </c>
+          <t xml:space="preserve">Réveils de l’islam moderne</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nahda</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B72" s="14"/>
+      <c r="C72" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="F72" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="H72" s="14"/>
+      <c r="I72" s="16"/>
       <c r="J72" s="2" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>421</v>
+        <v>379</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -5553,39 +5696,31 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Néoconfucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="14" t="n">
-        <v>1935</v>
-      </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14" t="s">
-        <v>422</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="E73" s="16" t="s">
-        <v>424</v>
-      </c>
-      <c r="F73" s="14" t="s">
-        <v>425</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>426</v>
-      </c>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>383</v>
+      </c>
       <c r="J73" s="2" t="s">
-        <v>427</v>
+        <v>384</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>108</v>
@@ -5593,262 +5728,278 @@
       <c r="M73" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
+      <c r="N73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P73" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pan-africanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Q73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
-        <v>1940</v>
+        <v>1905</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>1940</v>
+        <v>1905</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>428</v>
-      </c>
-      <c r="E74" s="23" t="s">
-        <v>429</v>
+        <v>385</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>386</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>430</v>
+        <v>387</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="J74" s="23" t="s">
-        <v>432</v>
+        <v>388</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>108</v>
       </c>
       <c r="M74" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaïnisme;Néo-védanta</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J75" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M75" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t xml:space="preserve">Marxisme</t>
         </is>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="C75" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="D75" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;La Philosophie africaine&lt;/a&gt; désigne la réflexion philosophique menée en Afrique ou par des penseurs africains, mais aussi le débat sur ce que peut être une telle philosophie. Les traditions de pensée du continent sont anciennes, des sagesses de l’Égypte pharaonique au &lt;em&gt;Hatata&lt;/em&gt; éthiopien du XVIIe siècle attribué à Zera Yacob ; mais la discipline moderne prend son essor en 1945, avec &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Tempels reconstruit, à partir de l’observation des Luba du Congo, une « vision du monde » cohérente centrée sur la force vitale : être, c’est être force, et le bien consiste à accroître la vie. Le prêtre rwandais Alexis Kagame prolonge cette démarche en étudiant les catégories de la langue kinyarwanda. Ce courant, appelé ethnophilosophie, est vivement critiqué par le Béninois &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976) : décrire une pensée collective et anonyme, que personne ne discute, ce n’est pas faire de la philosophie, qui suppose des auteurs, des textes et la critique.&lt;/p&gt; &lt;p&gt;Entre ces deux pôles, d’autres voies se sont ouvertes. Le Kényan Henry Odera Oruka recueille auprès des sages des villages une « philosophie de la sagesse » (&lt;em&gt;sage philosophy&lt;/em&gt;) personnelle et critique. Le Ghanéen &lt;a href="https://fr.wikipedia.org/wiki/Kwasi_Wiredu" title=" Wikipedia"&gt;Kwasi Wiredu&lt;/a&gt; appelle à une « décolonisation conceptuelle » qui examine les notions héritées de l’Occident à la lumière des langues africaines. Le Congolais Valentin-Yves Mudimbe étudie la manière dont l’Afrique a été « inventée » par le regard colonial. Le débat porte encore sur l’universalité de la raison.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="K75" s="2" t="s">
+    <row r="76" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
+        <v>1911</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen;Idéalisme allemand</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="K77" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M75" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées africaines</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>1964</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>1964</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nkrumaism" title=" Wikipedia (en)"&gt;Le Consciencisme&lt;/a&gt; est la philosophie politique de &lt;a href="https://fr.wikipedia.org/wiki/Kwame_Nkrumah" title=" Wikipedia"&gt;Kwame Nkrumah&lt;/a&gt; (1909-1972), qui conduit la Gold Coast britannique à l’indépendance en 1957 sous le nom de Ghana, premier pays d’Afrique subsaharienne à se libérer de la colonisation. Il l’expose dans &lt;em&gt;Consciencism : Philosophy and Ideology for Decolonization&lt;/em&gt; (1964). Pour Nkrumah, la décolonisation ne sera achevée que si elle s’accompagne d’une libération des consciences : l’Afrique doit penser par elle-même la société qu’elle veut construire.&lt;/p&gt; &lt;p&gt;Il part d’un constat : la conscience africaine est désormais faite de trois héritages, la tradition africaine, l’islam et le christianisme européen, qui coexistent en conflit. Le consciencisme veut les réunir en une synthèse cohérente, guidée par les valeurs humanistes et égalitaires de l’Afrique traditionnelle. Selon Nkrumah, les sociétés africaines précoloniales étaient « communalistes » : la terre appartenait à tous et nul ne vivait du travail d’autrui. Le socialisme n’est donc pas, pour l’Afrique, une importation, mais la forme moderne de ses propres valeurs ; il peut s’y construire sans passer par la lutte des classes. Sur le plan philosophique, Nkrumah défend un matérialisme dans lequel l’esprit naît de la matière, tout en affirmant l’égale dignité de chaque être humain. Son projet politique est le &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; : une Afrique unie, seule capable de résister au néocolonialisme.&lt;/p&gt; &lt;p&gt;Renversé par un coup d’État en 1966, Nkrumah meurt en exil. Le consciencisme reste une référence des philosophies africaines de la décolonisation ; Kwame Gyekye en a critiqué l’idéalisation du passé.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées africaines</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Socialisme africain</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
-        <v>1970</v>
-      </c>
-      <c r="C77" s="1" t="n">
-        <v>1970</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Minjung" title=" Wikipedia"&gt;La pensée Minjung&lt;/a&gt;, du coréen &lt;em&gt;minjung&lt;/em&gt;, « le peuple » au sens des masses opprimées, est un courant théologique et philosophique né en Corée du Sud dans les années 1970, sous la dictature de Park Chung-hee. Elle naît parmi les chrétiens engagés aux côtés des ouvriers et des étudiants en lutte pour la démocratie, après l’immolation en 1970 de l’ouvrier du textile Jeon Tae-il, qui réclamait l’application du droit du travail.&lt;/p&gt; &lt;p&gt;Le &lt;em&gt;minjung&lt;/em&gt;, ce sont ceux qui sont opprimés politiquement, exploités économiquement et tenus à l’écart de la culture. Pour le bibliste Ahn Byung-mu, qui relit l’Évangile de Marc à partir de la foule qui suit Jésus, et pour le théologien Suh Nam-dong, ce peuple souffrant n’est pas seulement l’objet de la compassion : il est le véritable sujet de l’histoire, et c’est dans ses luttes que se révèle le sens des Écritures. La pensée Minjung s’appuie sur une notion coréenne, le &lt;em&gt;han&lt;/em&gt;, ce sentiment de souffrance et de ressentiment accumulés au fil des générations ; le poète Kim Chi-ha cherche comment en briser le cercle sans tomber dans la vengeance. Elle valorise aussi les formes de la culture populaire, comme la danse masquée ou le chant épique du &lt;em&gt;pansori&lt;/em&gt;. Elle a pour précurseur la philosophie de la « graine » (&lt;em&gt;ssial&lt;/em&gt;) de Ham Seok-heon, qui voyait dans le peuple le germe vivant de l’histoire.&lt;/p&gt; &lt;p&gt;Proche des théologies de la libération d’Amérique latine, la pensée Minjung a nourri la résistance au régime militaire, du &lt;a href="https://fr.wikipedia.org/wiki/Soul%C3%A8vement_de_Gwangju" title=" Wikipedia"&gt;soulèvement de Gwangju&lt;/a&gt; en 1980 à la démocratisation de 1987.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="L77" s="1"/>
       <c r="M77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Logique_paracoh%C3%A9rente"  title=" Wikipedia"&gt;La Logique paraconsistante&lt;/a&gt; désigne les systèmes logiques qui peuvent contenir des contradictions sans s’effondrer. En logique classique, en effet, une seule contradiction suffit à tout démontrer : de « A et non-A », on peut déduire n’importe quelle proposition. C’est le &lt;a href="https://fr.wikipedia.org/wiki/Principe_d%27explosion" title=" Wikipedia"&gt;principe d’explosion&lt;/a&gt;, connu depuis le Moyen Âge sous la formule « du contradictoire suit n’importe quoi ». Une logique paraconsistante bloque cette explosion : une contradiction locale y reste locale, sans contaminer tout le reste.&lt;/p&gt; &lt;p&gt;L’idée apparaît en 1910, à Kazan, chez le philosophe russe Nikolaï Vassiliev (1880-1940). Il imagine une « logique imaginaire » où la loi de non-contradiction n’est plus un axiome nécessaire, de même que les géométries non euclidiennes, nées à Kazan avec Lobatchevski, avaient abandonné le postulat des parallèles. La même année, le Polonais Jan Łukasiewicz critique le principe de non-contradiction d’Aristote. Son élève Stanisław Jaśkowski construit en 1948 le premier système formel paraconsistant, et le Brésilien Newton da Costa développe à partir de 1963 toute une famille de ces logiques. Le mot « paraconsistant » est forgé en 1976 par le philosophe péruvien Francisco Miró Quesada. Certains vont plus loin, comme l’Australien &lt;a href="https://fr.wikipedia.org/wiki/Graham_Priest" title=" Wikipedia"&gt;Graham Priest&lt;/a&gt; : selon son « dialéthéisme », certaines contradictions sont vraies, par exemple le paradoxe du menteur, « cette phrase est fausse ».&lt;/p&gt; &lt;p&gt;Ces logiques servent en informatique, pour raisonner avec des bases de données incohérentes, en droit, face à des normes contradictoires, et en philosophie des sciences, quand des théories en conflit doivent coexister.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie analytique et pragmatisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
+        <v>1921</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nouveau_confucianisme"  title=" Wikipedia"&gt;Le nouveau confucianisme&lt;/a&gt; est un courant philosophique chinois du XXe siècle qui veut renouveler la tradition confucéenne pour l’accorder à la modernité. Il naît en réaction au mouvement du 4 Mai 1919 et à la Nouvelle Culture, qui rejetaient le confucianisme comme responsable du retard de la Chine et en appelaient à « Monsieur Science » et à « Monsieur Démocratie ». Ses penseurs veulent montrer qu’un confucianisme repensé peut accueillir la science et la démocratie sans perdre sa sagesse morale.&lt;/p&gt; &lt;p&gt;Le point de départ est l’ouvrage de &lt;a href="https://fr.wikipedia.org/wiki/Liang_Shuming" title=" Wikipedia"&gt;Liang Shuming&lt;/a&gt;, &lt;em&gt;Les Cultures d’Orient et d’Occident et leurs philosophies&lt;/em&gt; (1921), qui compare les voies de l’Occident, de la Chine et de l’Inde. &lt;a href="https://fr.wikipedia.org/wiki/Xiong_Shili" title=" Wikipedia"&gt;Xiong Shili&lt;/a&gt; donne au courant une métaphysique dans son &lt;em&gt;Nouveau traité de la conscience seule&lt;/em&gt; (1932) : s’inspirant du &lt;em&gt;Livre des mutations&lt;/em&gt;, il critique le bouddhisme pour qui le monde est illusion, et pense la réalité comme un mouvement créateur continu. Feng Youlan, dans son &lt;em&gt;Nouvel enseignement du principe&lt;/em&gt; (1939), relit Zhu Xi à l’aide de la logique moderne.&lt;/p&gt; &lt;p&gt;Après 1949, le courant se poursuit surtout à Hong Kong et à Taïwan. En 1958, Mou Zongsan, Tang Junyi, Xu Fuguan et Zhang Junmai publient un manifeste adressé au monde sur la culture chinoise. Mou Zongsan, traducteur des trois &lt;em&gt;Critiques&lt;/em&gt; de Kant, dialogue avec lui pour fonder une « métaphysique morale ». Une troisième génération, avec &lt;a href="https://fr.wikipedia.org/wiki/Tu_Weiming" title=" Wikipedia"&gt;Tu Weiming&lt;/a&gt; ou Liu Shu-hsien, a porté ce courant dans les universités américaines ; il connaît depuis les années 1980 un important renouveau en Chine continentale.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="M79" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologies et philosophies de la libération</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buen_vivir" title=" Wikipedia"&gt;Le Buen Vivir&lt;/a&gt;, « bien vivre » en espagnol, traduit le &lt;em&gt;sumak kawsay&lt;/em&gt; des Quechuas et le &lt;em&gt;suma qamaña&lt;/em&gt; des Aymaras. C’est une philosophie issue des cosmovisions autochtones des Andes, formulée en termes contemporains à partir des années 1990 par des intellectuels et des mouvements indigènes d’Équateur et de Bolivie, rejoints par des penseurs critiques du développement.&lt;/p&gt; &lt;p&gt;Il s’oppose à l’idée occidentale du développement, mesuré par la croissance économique et l’accumulation de biens. Bien vivre, ce n’est pas vivre mieux, c’est-à-dire toujours plus, aux dépens des autres et de la nature : c’est vivre en harmonie au sein de la communauté et avec la &lt;a href="https://fr.wikipedia.org/wiki/Pachamama" title=" Wikipedia"&gt;Pachamama&lt;/a&gt;, la Terre-Mère. L’être humain n’y est ni séparé de la nature ni placé au-dessus d’elle : il fait partie d’un tout vivant tissé de relations, de réciprocité et de complémentarité, où les montagnes, les eaux et les êtres vivants ont leur place. La richesse tient à la qualité des liens plutôt qu’à l’abondance des choses. Ses défenseurs, comme l’économiste équatorien Alberto Acosta ou l’Uruguayen Eduardo Gudynas, y voient une alternative au modèle extractiviste.&lt;/p&gt; &lt;p&gt;La Constitution de l’Équateur de 2008 inscrit le &lt;em&gt;sumak kawsay&lt;/em&gt; parmi ses principes et reconnaît des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_la_nature" title=" Wikipedia"&gt;droits à la nature&lt;/a&gt; elle-même, une première mondiale. La Constitution bolivienne de 2009 en fait un principe éthique de l’État, et des lois de 2010 et 2012 y consacrent les droits de la Terre-Mère. Mais ces deux pays ont continué d’exploiter pétrole et minerais, ce qui nourrit le débat entre l’idéal et son usage politique.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M78" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="D79" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="G79" s="1"/>
-      <c r="J79" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="M79" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -5856,53 +6007,52 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindouismes de dévotion</t>
+          <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhakti;Soufisme</t>
+          <t xml:space="preserve">Néoconfucianisme</t>
         </is>
       </c>
     </row>
     <row r="80" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1">
-        <v>150</v>
+        <v>1921</v>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">150</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Madhyamaka</t>
+          <t xml:space="preserve">1921</t>
+        </is>
+      </c>
+      <c r="D80" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eurasisme</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Madhyamaka" title=" Wikipedia"&gt;Le Madhyamaka&lt;/a&gt;, ou « école de la Voie du milieu », est l’une des deux grandes écoles philosophiques du bouddhisme mahāyāna. Il naît en Inde vers le IIe siècle avec Nāgārjuna, dont les &lt;a href="https://fr.wikipedia.org/wiki/Mulamadhyamakakarika" title=" Wikipedia"&gt;&lt;em&gt;Stances de la Voie du milieu&lt;/em&gt;&lt;/a&gt; sont le texte fondateur, et son disciple Āryadeva. Le « milieu » qu’il cherche se tient entre deux extrêmes : croire que les choses existent en elles-mêmes, ou croire qu’elles n’existent pas du tout.&lt;/p&gt; &lt;p&gt;Sa thèse centrale est la &lt;a href="https://fr.wikipedia.org/wiki/%C5%9A%C5%ABnyat%C4%81" title=" Wikipedia"&gt;vacuité&lt;/a&gt; (&lt;em&gt;śūnyatā&lt;/em&gt;) : aucune chose n’a d’existence propre, car toute chose dépend d’autre chose, de ses causes, de ses parties et de l’esprit qui la nomme. La vacuité n’est donc pas le néant, mais l’autre nom de la « production conditionnée » enseignée par le Bouddha. Nāgārjuna procède par réfutation : il montre que toute thèse sur l’être, le mouvement, le temps ou la causalité aboutit à des contradictions dès qu’on la tient pour absolue. Il distingue la vérité conventionnelle, celle du langage et de la vie ordinaire, de la vérité ultime, qui échappe aux concepts ; et la vacuité est elle-même vide : ce n’est pas une nouvelle doctrine à laquelle s’accrocher.&lt;/p&gt; &lt;p&gt;L’école se divise ensuite entre ceux qui admettent des raisonnements autonomes et les « Prāsaṅgika » de Candrakīrti, qui se contentent de montrer l’absurdité des thèses adverses. Śāntideva en tire une éthique de la compassion. Transmis au Tibet par Atiśa et systématisé par Tsongkhapa, le Madhyamaka reste la philosophie de référence du bouddhisme tibétain. On l’a souvent rapproché, au XXe siècle, de la critique du langage chez Wittgenstein.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="G80" s="1"/>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;L’eurasisme&lt;/a&gt; est un courant de pensée né en 1921 dans l’émigration russe, après la révolution bolchevique, avec le recueil &lt;em&gt;L’Exode vers l’Orient&lt;/em&gt;, publié à Sofia par un petit groupe de jeunes intellectuels exilés : le linguiste &lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Sergue%C3%AFevitch_Troubetsko%C3%AF" title=" Wikipedia"&gt;Nikolaï Troubetskoï&lt;/a&gt;, le géographe Piotr Savitski, le musicologue Pierre Souvtchinski et le théologien Georges Florovsky.&lt;/p&gt; &lt;p&gt;Leur thèse est que la Russie n’est ni une partie de l’Europe ni une partie de l’Asie, mais un monde à part, l’« Eurasie », dont la grande plaine, des Carpates au Pacifique, a façonné l’unité des peuples slaves, turcs et finno-ougriens. Contre les occidentalistes, ils refusent l’idée d’une civilisation européenne universelle : dans &lt;em&gt;L’Europe et l’humanité&lt;/em&gt; (1920), Troubetskoï y voit l’égoïsme d’une culture « romano-germanique » qui s’impose aux autres. Contre les slavophiles, ils réhabilitent l’héritage asiatique de la Russie, et jusqu’à l’empire de Gengis Khan, qui aurait le premier unifié cet espace. Ils rêvent d’un État fondé sur une idéologie commune et sur l’orthodoxie, distinct à la fois de la démocratie libérale et du communisme. Florovsky s’en éloigne vite et critique en 1928 ce qu’il appelle une « vérité des questions » devenue une « erreur des réponses ». Le mouvement se divise à la fin des années 1920, une partie se rapprochant du régime soviétique.&lt;/p&gt; &lt;p&gt;Prolongé en URSS par l’historien &lt;a href="https://fr.wikipedia.org/wiki/Lev_Goumilev" title=" Wikipedia"&gt;Lev Goumilev&lt;/a&gt;, l’eurasisme renaît après 1991 sous la forme d’un « néo-eurasisme » porté par &lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Douguine" title=" Wikipedia"&gt;Alexandre Douguine&lt;/a&gt;, idéologue d’extrême droite, et influence aujourd’hui la géopolitique nationaliste et impériale de la Russie.&lt;/p&gt;  &lt;audio controls title="De l'idée à l'action : 4 doctrines géopolitiques . Eurasie : la Russie au centre du jeu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18720-25.03.2021-ITEMA_22614994-2021C16756S0084.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">école bouddhiste de la Voie du milieu fondée par Nāgārjuna : rien n’existe en soi, tout est vide parce qu’interdépendant.</t>
+          <t xml:space="preserve">doctrine née dans l’émigration russe : la Russie ne serait ni l’Europe ni l’Asie, mais une civilisation à part, l’« Eurasie ».</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métaphysique;Épistémologie</t>
+          <t xml:space="preserve">Philosophie politique</t>
         </is>
       </c>
       <c r="L80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAGARJUNA;SHANTIDEVA;Je TSONGKHAPA</t>
+          <t xml:space="preserve">Nikolaï TROUBETSKOÏ;Georges FLOROVSKY</t>
         </is>
       </c>
       <c r="M80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inde</t>
+          <t xml:space="preserve">russe</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5917,58 +6067,45 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1">
-        <v>350</v>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350</t>
-        </is>
-      </c>
-      <c r="D81" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yogācāra</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chittamatra" title=" Wikipedia"&gt;Le Yogācāra&lt;/a&gt;, « pratique du yoga », appelé aussi Cittamātra, « esprit seul », est avec le Madhyamaka l’une des deux grandes écoles philosophiques du bouddhisme mahāyāna. Il se forme en Inde au IVe siècle autour de deux frères, Asaṅga et Vasubandhu, à partir de l’expérience des méditants : ce que l’on observe en méditation montre combien le monde vécu est façonné par l’esprit. On doit à Vasubandhu deux courts traités, les &lt;em&gt;Vingt stances&lt;/em&gt; et les &lt;em&gt;Trente stances&lt;/em&gt;, qui résument la doctrine.&lt;/p&gt; &lt;p&gt;Sa thèse est que nous ne connaissons jamais que des représentations : les objets que nous croyons extérieurs sont des apparitions de la conscience, comme dans un rêve. Pour l’expliquer, il ajoute aux six consciences reconnues par le bouddhisme une conscience souillée, qui produit l’illusion d’un moi, et surtout une &lt;a href="https://fr.wikipedia.org/wiki/%C4%80layavij%C3%B1%C4%81na" title=" Wikipedia"&gt;conscience-réceptacle&lt;/a&gt; (&lt;em&gt;ālayavijñāna&lt;/em&gt;), sorte d’inconscient où les actes passés déposent des traces, comme des graines qui germeront plus tard. Il décrit aussi « trois natures » des choses : imaginaire, dépendante et parfaitement accomplie. L’éveil consiste à transformer ce fond de la conscience, jusqu’à ce que cesse le partage entre un sujet qui saisit et un objet saisi.&lt;/p&gt; &lt;p&gt;Ses logiciens, Dignāga puis Dharmakīrti, fondent la grande épistémologie bouddhique. Le pèlerin chinois &lt;a href="https://fr.wikipedia.org/wiki/Xuanzang" title=" Wikipedia"&gt;Xuanzang&lt;/a&gt; rapporte ses textes d’Inde au VIIe siècle et fonde en Chine l’école de la « conscience seule ». Le Yogācāra a nourri le zen, le bouddhisme tibétain et, aujourd’hui, le dialogue avec la phénoménologie et les sciences cognitives.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J81" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">école bouddhiste de « l’esprit seul » : le monde que nous percevons est une construction de la conscience.</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Philosophie de l'esprit;Métaphysique;Épistémologie</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ASANGA;VASUBANDHU;XUANZANG</t>
-        </is>
-      </c>
-      <c r="M81" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inde</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
+          <t xml:space="preserve">Slavophilisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="14" t="n">
+        <v>1935</v>
+      </c>
+      <c r="B81" s="14"/>
+      <c r="C81" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="F81" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -5977,55 +6114,43 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1">
-        <v>402</v>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">402</t>
-        </is>
-      </c>
-      <c r="D82" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme de la Terre pure</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;Le bouddhisme de la &lt;a href="https://fr.wikipedia.org/wiki/Terre_pure" title=" Wikipedia"&gt;Terre pure&lt;/a&gt; est le courant du bouddhisme mahāyāna centré sur la dévotion au bouddha Amitābha (Amida en japonais) qui, selon les sūtras, a fait le vœu d’accueillir dans sa « Terre pure », un paradis situé à l’Occident, tous ceux qui l’invoquent avec foi. Né en Chine, il remonte à Huiyuan, qui réunit en 402 au mont Lu une communauté vouée à Amitābha, puis à &lt;a href="https://fr.wikipedia.org/wiki/Tanluan" title=" Wikipedia"&gt;Tanluan&lt;/a&gt; et à Shandao, qui en font une école.&lt;/p&gt; &lt;p&gt;Sa philosophie part d’un constat : en cette époque de « déclin de la Loi », les êtres humains ne peuvent plus atteindre l’éveil par leurs propres forces, par la méditation ou l’ascèse. Il faut s’en remettre à la « force de l’autre », la compassion d’Amitābha. La pratique principale devient la récitation de son nom, le &lt;em&gt;nembutsu&lt;/em&gt; : « Namu Amida Butsu ». Au Japon, Hōnen fonde en 1175 l’école &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_sh%C5%AB" title=" Wikipedia"&gt;Jōdo shū&lt;/a&gt; et affirme que cette seule récitation suffit au salut, ce qui ouvre le bouddhisme aux gens simples, aux paysans et aux femmes. Son disciple Shinran va plus loin avec le &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_shinsh%C5%AB" title=" Wikipedia"&gt;Jōdo shinshū&lt;/a&gt; : le salut est entièrement un don reçu dans la foi, et c’est le « méchant » conscient de ses fautes, plus encore que le juste, que le Bouddha veut sauver. Shinran se marie, quitte la vie monastique et vit parmi le peuple.&lt;/p&gt; &lt;p&gt;Devenue l’une des formes du bouddhisme les plus pratiquées d’Asie de l’Est, la Terre pure évoque la doctrine chrétienne de la grâce, rapprochement qui a fasciné bien des théologiens occidentaux. Elle compte aujourd’hui des dizaines de millions de fidèles au Japon, en Chine, en Corée et au Viêt Nam.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bouddhisme de la foi en Amitābha : le salut par la récitation de son nom et la « force de l’autre ».</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie et spiritualité</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HŌNEN;SHINRAN</t>
-        </is>
-      </c>
-      <c r="M82" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="N82"/>
+          <t xml:space="preserve">Pan-africanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>1940</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="E82" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J82" s="23" t="s">
+        <v>432</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6033,55 +6158,45 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1">
-        <v>575</v>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">575</t>
-        </is>
-      </c>
-      <c r="D83" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiantai</t>
-        </is>
+          <t xml:space="preserve">Marxisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>433</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tiantai" title=" Wikipedia"&gt;Le Tiantai&lt;/a&gt; est la première grande école du bouddhisme née en Chine plutôt qu’importée d’Inde. Elle tire son nom du mont Tiantai, dans le Zhejiang, où le moine Zhiyi (538-597) s’installe en 575 et élabore sa doctrine. Face à la masse des sūtras traduits en chinois, souvent contradictoires, Zhiyi les classe en périodes et en méthodes d’enseignement : le Bouddha aurait adapté sa parole à ses auditeurs, et le &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_du_Lotus" title=" Wikipedia"&gt;&lt;em&gt;Sūtra du Lotus&lt;/em&gt;&lt;/a&gt; en serait le sommet, qui révèle que tous les êtres peuvent devenir bouddhas.&lt;/p&gt; &lt;p&gt;Sa philosophie repose sur la doctrine des « trois vérités » : toute chose est vide, car sans existence propre ; elle existe pourtant provisoirement, comme apparence ; et elle est le « milieu », qui unit les deux sans les séparer. Zhiyi en tire l’idée qu’« un instant de pensée contient trois mille mondes » : chaque moment de conscience renferme la totalité des états possibles de l’existence, des enfers jusqu’à l’éveil. Le salut n’est donc pas ailleurs : il se découvre au cœur même du monde ordinaire. Zhiyi va jusqu’à soutenir que la nature de bouddha contient aussi le mal, ce qui fait l’originalité de l’école. Il unit étroitement l’étude des textes et la méditation, qu’il expose dans de grands traités sur « l’arrêt et la contemplation ».&lt;/p&gt; &lt;p&gt;Introduite au Japon en 805 par Saichō sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Tendai" title=" Wikipedia"&gt;Tendai&lt;/a&gt;, l’école fait du monastère du mont Hiei le grand centre du bouddhisme japonais. Elle y forme la plupart des fondateurs des écoles ultérieures, dont Hōnen, Shinran, Dōgen et Nichiren, qui en reprend la dévotion au Lotus.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J83" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">école bouddhiste chinoise fondée par Zhiyi sur le Sūtra du Lotus : trois vérités et trois mille mondes dans un instant de pensée.</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZHIYI;SAICHŌ</t>
-        </is>
-      </c>
-      <c r="M83" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="N83"/>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;La Philosophie africaine&lt;/a&gt; désigne la réflexion philosophique menée en Afrique ou par des penseurs africains, mais aussi le débat sur ce que peut être une telle philosophie. Les traditions de pensée du continent sont anciennes, des sagesses de l’Égypte pharaonique au &lt;em&gt;Hatata&lt;/em&gt; éthiopien du XVIIe siècle attribué à Zera Yacob ; mais la discipline moderne prend son essor en 1945, avec &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Tempels reconstruit, à partir de l’observation des Luba du Congo, une « vision du monde » cohérente centrée sur la force vitale : être, c’est être force, et le bien consiste à accroître la vie. Le prêtre rwandais Alexis Kagame prolonge cette démarche en étudiant les catégories de la langue kinyarwanda. Ce courant, appelé ethnophilosophie, est vivement critiqué par le Béninois &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976) : décrire une pensée collective et anonyme, que personne ne discute, ce n’est pas faire de la philosophie, qui suppose des auteurs, des textes et la critique.&lt;/p&gt; &lt;p&gt;Entre ces deux pôles, d’autres voies se sont ouvertes. Le Kényan Henry Odera Oruka recueille auprès des sages des villages une « philosophie de la sagesse » (&lt;em&gt;sage philosophy&lt;/em&gt;) personnelle et critique. Le Ghanéen &lt;a href="https://fr.wikipedia.org/wiki/Kwasi_Wiredu" title=" Wikipedia"&gt;Kwasi Wiredu&lt;/a&gt; appelle à une « décolonisation conceptuelle » qui examine les notions héritées de l’Occident à la lumière des langues africaines. Le Congolais Valentin-Yves Mudimbe étudie la manière dont l’Afrique a été « inventée » par le regard colonial. Le débat porte encore sur l’universalité de la raison.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6089,52 +6204,57 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme Mahayana;Madhyamaka</t>
+          <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
     </row>
     <row r="84" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1">
-        <v>600</v>
+        <v>1945</v>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">1945</t>
         </is>
       </c>
       <c r="D84" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huayan</t>
+          <t xml:space="preserve">Ethnophilosophie</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Huayan" title=" Wikipedia"&gt;Le Huayan&lt;/a&gt;, ou « école de l’Ornementation fleurie », est une école du bouddhisme chinois fondée sur l’&lt;a href="https://fr.wikipedia.org/wiki/Avata%E1%B9%83saka_s%C5%ABtra" title=" Wikipedia"&gt;&lt;em&gt;Avataṃsaka sūtra&lt;/em&gt;&lt;/a&gt;, immense texte qui décrit l’univers tel que le voit un bouddha éveillé. Elle se forme aux VIe et VIIe siècles autour de &lt;a href="https://fr.wikipedia.org/wiki/Dushun" title=" Wikipedia"&gt;Dushun&lt;/a&gt;, son premier patriarche, puis de Zhiyan, et trouve son grand systématicien en Fazang (643-712), qui l’expose à la cour de l’impératrice Wu Zetian.&lt;/p&gt; &lt;p&gt;Sa philosophie est celle de l’interdépendance totale : chaque chose contient toutes les autres et se trouve contenue en elles, sans que leurs différences soient abolies. Pour le faire comprendre à l’impératrice, Fazang prend l’image d’un lion d’or : l’or est la nature unique et vide, le lion la forme qu’elle prend, et chaque poil du lion contient le lion tout entier. Il reprend aussi celle du filet d’Indra, filet céleste dont chaque nœud porte une perle qui reflète toutes les autres perles, à l’infini. Le Huayan distingue quatre plans de réalité : celui des phénomènes, celui du principe, celui de leur non-obstruction mutuelle, et enfin celui de la non-obstruction de tous les phénomènes entre eux, qui est la vision de l’éveil.&lt;/p&gt; &lt;p&gt;En Chine, &lt;a href="https://fr.wikipedia.org/wiki/Zongmi" title=" Wikipedia"&gt;Zongmi&lt;/a&gt; (780-841) le concilie avec le chan. Ŭisang l’apporte en Corée, où il devient l’école Hwaeom, que Chinul unira plus tard à la méditation seon ; au Japon, il prend le nom de &lt;a href="https://fr.wikipedia.org/wiki/Kegon" title=" Wikipedia"&gt;Kegon&lt;/a&gt; et c’est à lui que se rattache le grand Bouddha de Nara. Le Huayan a profondément marqué le zen et le néoconfucianisme. On rapproche parfois aujourd’hui sa vision d’un monde entièrement relié de la pensée écologique.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ethnophilosophy" title=" Wikipedia (en)"&gt;L’ethnophilosophie&lt;/a&gt; désigne la démarche qui cherche la philosophie d’un peuple dans ses langues, ses proverbes, ses mythes et ses croyances, plutôt que dans les œuvres de penseurs individuels. Elle naît en 1945 avec &lt;a href="https://fr.wikipedia.org/wiki/La_Philosophie_bantoue" title=" Wikipedia"&gt;&lt;em&gt;La Philosophie bantoue&lt;/em&gt;&lt;/a&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;, qui veut montrer, contre le préjugé colonial, que les Africains ont une pensée cohérente, fondée sur l’idée de « force vitale » : pour les Bantous, l’être est force, et toute chose est une force qui peut croître ou décroître.&lt;/p&gt; &lt;p&gt;Des penseurs africains reprennent cette démarche en la retournant contre le regard colonial. Le prêtre rwandais Alexis Kagame, dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), dégage les catégories de la pensée à partir de la grammaire du kinyarwanda, comme Aristote l’avait fait, selon lui, à partir du grec. Le théologien kényan John Mbiti décrit dans &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969) une conception du temps tournée vers le passé plus que vers l’avenir. Dans l’esprit de la Négritude, il s’agit d’affirmer la dignité des cultures africaines.&lt;/p&gt; &lt;p&gt;À partir des années 1970, cette démarche est vivement critiquée par d’autres philosophes africains. Paulin Hountondji, dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976), dénonce le « mythe de l’unanimité » : une philosophie n’est pas une vision du monde collective et figée, mais un discours critique, signé, argumenté et ouvert à la discussion. Marcien Towa et Fabien Eboussi Boulaga vont dans le même sens. Le débat sur l’ethnophilosophie a structuré toute la philosophie africaine contemporaine.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WdgKfF8Ghn0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Révision BAC: La Philosophie Africaine Existe -t - Elle?" par Ibrahima Ngom - Attitude</t>
         </is>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">école bouddhiste chinoise de l’interdépendance totale, où chaque chose contient toutes les autres.</t>
+          <t xml:space="preserve">recherche d’une philosophie africaine dans les langues, les croyances et les traditions des peuples, et débat qu’elle a suscité.</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+          <t xml:space="preserve">Métaphysique;Épistémologie</t>
         </is>
       </c>
       <c r="L84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAZANG;UISANG</t>
+          <t xml:space="preserve">Placide TEMPELS;Alexis KAGAME;John MBITI</t>
         </is>
       </c>
       <c r="M84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">asie-est</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="N84"/>
@@ -6145,55 +6265,45 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana;Yogācāra</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1">
-        <v>600</v>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">600</t>
-        </is>
-      </c>
-      <c r="D85" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bhakti</t>
-        </is>
+          <t xml:space="preserve">Négritude</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>438</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bhakti" title=" Wikipedia"&gt;La bhakti&lt;/a&gt;, la « dévotion » ou « l’amour de Dieu », est une voie spirituelle de l’hindouisme qui place l’amour personnel d’une divinité au-dessus des rites, des sacrifices et du savoir. Annoncée dans la &lt;em&gt;Bhagavad-Gītā&lt;/em&gt;, où Krishna enseigne que l’abandon aimant à Dieu est le plus sûr chemin vers la délivrance, elle devient un grand mouvement dans l’Inde du Sud entre le VIe et le IXe siècle, avec les poètes tamouls : les &lt;a href="https://fr.wikipedia.org/wiki/Alvar" title=" Wikipedia"&gt;Alvars&lt;/a&gt;, dévots de Vishnou, et les &lt;a href="https://fr.wikipedia.org/wiki/Nayanar" title=" Wikipedia"&gt;Nayanars&lt;/a&gt;, dévots de Shiva.&lt;/p&gt; &lt;p&gt;Ces saints chantent leur dieu dans la langue du peuple et non en sanskrit, et beaucoup viennent de basses castes : la bhakti affirme que l’amour de Dieu est ouvert à tous, sans distinction de naissance ni de sexe. Elle reçoit une base philosophique avec Rāmānuja, au XIe siècle, qui défend contre Shankara la réalité de l’âme et du monde, distincts de Dieu tout en dépendant de lui ; Madhva va plus loin dans le dualisme. L’âme ne se fond pas dans l’absolu : elle demeure, pour aimer. Du XIIIe au XVIIe siècle, la bhakti gagne l’Inde du Nord : Kabir, tisserand de Bénarès, unit hindous et musulmans dans le culte d’un Dieu sans forme ; la princesse Mīrābāī chante Krishna en bravant les conventions ; Chaitanya, au Bengale, fait du chant et de la danse une prière extatique ; &lt;a href="https://fr.wikipedia.org/wiki/Tuls%C3%AEd%C3%A2s" title=" Wikipedia"&gt;Tulsîdâs&lt;/a&gt; écrit le &lt;em&gt;Ramcharitmanas&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Mouvement de réforme autant que de piété, la bhakti a façonné l’hindouisme populaire, inspiré le sikhisme et nourri, jusqu’à Gandhi, l’idée que la religion se vit d’abord dans le cœur.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J85" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voie hindoue de la dévotion amoureuse à Dieu, ouverte à tous sans distinction de caste ni de sexe.</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RAMANUJA;KABIR;MIRABAI</t>
-        </is>
-      </c>
-      <c r="M85" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inde</t>
-        </is>
-      </c>
-      <c r="N85"/>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nkrumaism" title=" Wikipedia (en)"&gt;Le Consciencisme&lt;/a&gt; est la philosophie politique de &lt;a href="https://fr.wikipedia.org/wiki/Kwame_Nkrumah" title=" Wikipedia"&gt;Kwame Nkrumah&lt;/a&gt; (1909-1972), qui conduit la Gold Coast britannique à l’indépendance en 1957 sous le nom de Ghana, premier pays d’Afrique subsaharienne à se libérer de la colonisation. Il l’expose dans &lt;em&gt;Consciencism : Philosophy and Ideology for Decolonization&lt;/em&gt; (1964). Pour Nkrumah, la décolonisation ne sera achevée que si elle s’accompagne d’une libération des consciences : l’Afrique doit penser par elle-même la société qu’elle veut construire.&lt;/p&gt; &lt;p&gt;Il part d’un constat : la conscience africaine est désormais faite de trois héritages, la tradition africaine, l’islam et le christianisme européen, qui coexistent en conflit. Le consciencisme veut les réunir en une synthèse cohérente, guidée par les valeurs humanistes et égalitaires de l’Afrique traditionnelle. Selon Nkrumah, les sociétés africaines précoloniales étaient « communalistes » : la terre appartenait à tous et nul ne vivait du travail d’autrui. Le socialisme n’est donc pas, pour l’Afrique, une importation, mais la forme moderne de ses propres valeurs ; il peut s’y construire sans passer par la lutte des classes. Sur le plan philosophique, Nkrumah défend un matérialisme dans lequel l’esprit naît de la matière, tout en affirmant l’égale dignité de chaque être humain. Son projet politique est le &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; : une Afrique unie, seule capable de résister au néocolonialisme.&lt;/p&gt; &lt;p&gt;Renversé par un coup d’État en 1966, Nkrumah meurt en exil. Le consciencisme reste une référence des philosophies africaines de la décolonisation ; Kwame Gyekye en a critiqué l’idéalisation du passé.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6201,55 +6311,46 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindouismes de dévotion</t>
+          <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindouisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1">
-        <v>850</v>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">850</t>
-        </is>
-      </c>
-      <c r="D86" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shivaïsme du Cachemire</t>
-        </is>
+          <t xml:space="preserve">Socialisme africain</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="n">
+        <v>1970</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>1970</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>443</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shiva%C3%AFsme_du_Cachemire" title=" Wikipedia"&gt;Le shivaïsme du Cachemire&lt;/a&gt; est une école philosophique et mystique hindoue qui s’épanouit dans la vallée du Cachemire entre le IXe et le XIe siècle. Il naît, selon la tradition, des &lt;em&gt;Śiva Sūtra&lt;/em&gt; que &lt;a href="https://fr.wikipedia.org/wiki/Vasugupta" title=" Wikipedia"&gt;Vasugupta&lt;/a&gt; aurait reçus en rêve. À la différence du shivaïsme dualiste du Sud, il est résolument non dualiste : il n’existe qu’une seule réalité, Shiva, conscience absolue, libre et lumineuse, dont l’univers entier est la manifestation. Il appartient au monde des tantras, qui valorise le corps, l’énergie et la vie dans le monde plutôt que le renoncement.&lt;/p&gt; &lt;p&gt;Là où l’Advaita Védanta de Shankara voit dans le monde une illusion, le shivaïsme du Cachemire y voit le jeu bien réel de la liberté divine. La conscience n’est pas seulement une lumière immobile ; elle est aussi &lt;a href="https://fr.wikipedia.org/wiki/Spanda" title=" Wikipedia"&gt;&lt;em&gt;spanda&lt;/em&gt;&lt;/a&gt;, « vibration », énergie créatrice qui se déploie sous la forme des choses. Utpaladeva fonde l’école de la « Reconnaissance » (&lt;em&gt;Pratyabhijñā&lt;/em&gt;) : l’être humain n’a pas à devenir Shiva, il l’est déjà, et la libération consiste à le reconnaître, comme on reconnaît soudain un ami qu’on avait sous les yeux. Le grand penseur de l’école, Abhinavagupta, en fait la synthèse dans son immense &lt;em&gt;Tantrāloka&lt;/em&gt;, « Lumière sur les tantras ». Il pense aussi l’art : l’émotion esthétique (&lt;em&gt;rasa&lt;/em&gt;) éprouvée au théâtre ou devant un poème est un avant-goût de la joie de la conscience libérée.&lt;/p&gt; &lt;p&gt;Presque oublié après le XIIe siècle, il a été redécouvert au XXe siècle, notamment grâce à l’indianiste &lt;a href="https://fr.wikipedia.org/wiki/Lilian_Silburn" title=" Wikipedia"&gt;Lilian Silburn&lt;/a&gt; en France et au maître cachemirien Swami Lakshman Joo.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J86" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">non-dualisme hindou pour qui le monde est le libre jeu de la conscience divine, Shiva, que l’être humain doit reconnaître en lui.</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ABHINAVAGUPTA;UTPALADEVA</t>
-        </is>
-      </c>
-      <c r="M86" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inde</t>
-        </is>
-      </c>
-      <c r="N86"/>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Minjung" title=" Wikipedia"&gt;La pensée Minjung&lt;/a&gt;, du coréen &lt;em&gt;minjung&lt;/em&gt;, « le peuple » au sens des masses opprimées, est un courant théologique et philosophique né en Corée du Sud dans les années 1970, sous la dictature de Park Chung-hee. Elle naît parmi les chrétiens engagés aux côtés des ouvriers et des étudiants en lutte pour la démocratie, après l’immolation en 1970 de l’ouvrier du textile Jeon Tae-il, qui réclamait l’application du droit du travail.&lt;/p&gt; &lt;p&gt;Le &lt;em&gt;minjung&lt;/em&gt;, ce sont ceux qui sont opprimés politiquement, exploités économiquement et tenus à l’écart de la culture. Pour le bibliste Ahn Byung-mu, qui relit l’Évangile de Marc à partir de la foule qui suit Jésus, et pour le théologien Suh Nam-dong, ce peuple souffrant n’est pas seulement l’objet de la compassion : il est le véritable sujet de l’histoire, et c’est dans ses luttes que se révèle le sens des Écritures. La pensée Minjung s’appuie sur une notion coréenne, le &lt;em&gt;han&lt;/em&gt;, ce sentiment de souffrance et de ressentiment accumulés au fil des générations ; le poète Kim Chi-ha cherche comment en briser le cercle sans tomber dans la vengeance. Elle valorise aussi les formes de la culture populaire, comme la danse masquée ou le chant épique du &lt;em&gt;pansori&lt;/em&gt;. Elle a pour précurseur la philosophie de la « graine » (&lt;em&gt;ssial&lt;/em&gt;) de Ham Seok-heon, qui voyait dans le peuple le germe vivant de l’histoire.&lt;/p&gt; &lt;p&gt;Proche des théologies de la libération d’Amérique latine, la pensée Minjung a nourri la résistance au régime militaire, du &lt;a href="https://fr.wikipedia.org/wiki/Soul%C3%A8vement_de_Gwangju" title=" Wikipedia"&gt;soulèvement de Gwangju&lt;/a&gt; en 1980 à la démocratisation de 1987.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="L86" s="1"/>
+      <c r="M86" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6257,52 +6358,57 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindouismes de dévotion</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hindouisme</t>
+          <t xml:space="preserve">Théologies et philosophies de la libération</t>
         </is>
       </c>
     </row>
     <row r="87" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1">
-        <v>1890</v>
+        <v>1981</v>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890</t>
+          <t xml:space="preserve">1981</t>
         </is>
       </c>
       <c r="D87" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Néo-védanta</t>
+          <t xml:space="preserve">Créolisation</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9o-v%C3%A9danta" title=" Wikipedia"&gt;néo-védanta&lt;/a&gt; la forme moderne du Védanta qui se développe en Inde à partir du XIXe siècle, en anglais plutôt qu’en sanskrit, au contact de l’Occident et de la domination britannique. Elle renouvelle la philosophie non dualiste de Shankara pour en faire une réponse aux critiques des missionnaires et un fondement de la fierté indienne.&lt;/p&gt; &lt;p&gt;Son point de départ est le mystique bengali &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A2makrishna" title=" Wikipedia"&gt;Râmakrishna&lt;/a&gt; (1836-1886), qui affirme, après avoir pratiqué plusieurs religions, que toutes mènent au même but. Son disciple Vivekananda porte ce message au &lt;a href="https://fr.wikipedia.org/wiki/Parlement_des_religions" title=" Wikipedia"&gt;Parlement des religions&lt;/a&gt; de Chicago, en 1893 : le Védanta y devient une religion universelle et rationnelle, compatible avec la science, qui reconnaît la divinité présente en chaque être humain. Il en découle une éthique de l’action : servir les pauvres, c’est servir Dieu ; Vivekananda fonde à cette fin la Mission Ramakrishna, vouée à l’enseignement et aux soins. Au XXe siècle, Sri Aurobindo en propose, depuis son ashram de Pondichéry, une version évolutionniste, où la conscience divine descend dans la matière et où l’humanité doit s’élever vers un « supramental ». Sarvepalli Radhakrishnan, professeur à Oxford devenu président de l’Inde, en donne l’exposé savant et le présente comme la synthèse de l’expérience religieuse de l’humanité.&lt;/p&gt; &lt;p&gt;Le néo-védanta a façonné l’image de l’hindouisme dans le monde et nourri le nationalisme indien. Des historiens lui reprochent cependant d’avoir unifié une tradition très diverse en la lisant à travers des catégories occidentales.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;La &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olisation_%28concept%29" title=" Wikipedia"&gt;créolisation&lt;/a&gt; est un courant de pensée né aux Antilles autour de l’œuvre d’Édouard Glissant. Le mot désigne d’abord la naissance des langues et des cultures créoles dans les sociétés de plantation des Caraïbes, où des peuples arrachés à l’Afrique, des colons européens, des Amérindiens et plus tard des travailleurs venus d’Inde ont dû inventer ensemble un monde nouveau. Glissant en fait un concept philosophique pour penser le monde entier.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Discours_antillais" title=" Wikipedia"&gt;&lt;em&gt;Le Discours antillais&lt;/em&gt;&lt;/a&gt; (1981), il développe d’abord l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : l’identité des Antilles ne se trouve ni dans un retour à l’Afrique, comme le voulait la Négritude, ni dans l’imitation de la France, mais dans l’archipel caribéen lui-même. Avec la créolisation, il montre que la rencontre des cultures ne produit pas un simple mélange prévisible, mais de l’inédit. Reprenant une image de Deleuze et Guattari, il oppose l’« identité-racine », unique, qui exclut l’autre, à l’« identité-rhizome », qui se construit dans la relation. Dans &lt;em&gt;Poétique de la Relation&lt;/em&gt; (1990), il défend le « droit à l’opacité » : comprendre l’autre ne signifie pas le réduire à soi. Il appelle &lt;a href="https://fr.wikipedia.org/wiki/Tout-monde" title=" Wikipedia"&gt;« Tout-Monde »&lt;/a&gt; ce monde où toutes les cultures sont désormais en contact, pour le meilleur et pour le pire, et où nul ne peut plus vivre à l’écart des autres.&lt;/p&gt; &lt;p&gt;En 1989, les écrivains martiniquais Jean Bernabé, &lt;a href="https://fr.wikipedia.org/wiki/Patrick_Chamoiseau" title=" Wikipedia"&gt;Patrick Chamoiseau&lt;/a&gt; et Raphaël Confiant prolongent ce mouvement dans leur &lt;em&gt;Éloge de la &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olit%C3%A9" title=" Wikipedia"&gt;créolité&lt;/a&gt;&lt;/em&gt;. La pensée de Glissant est aujourd’hui l’une des grandes références de la réflexion sur la mondialisation et les identités.&lt;/p&gt;  &lt;audio controls title="La Créolisation : un concept passé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/20904-30.04.2026-ITEMA_24494160-2026F49089S0120-NET_MFI_5FD251D7-5286-4ED2-85CC-C785E6DDF90E-27-205638c71d84a7236a4f197db5a2f1f9.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mLZ9uprUARg</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Edouard Glissant : penser la créolisation" par France Culture</t>
         </is>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">relecture moderne du Védanta par Vivekananda, Aurobindo et Radhakrishnan : une religion universelle et rationnelle.</t>
+          <t xml:space="preserve">pensée antillaise de Glissant : les cultures en contact créent de l’imprévisible ; à l’identité-racine s’oppose l’identité-relation.</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+          <t xml:space="preserve">Métaphysique;Philosophie politique</t>
         </is>
       </c>
       <c r="L87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIVEKANANDA;Sri AUROBINDO;Sarvepalli RADHAKRISHNAN</t>
+          <t xml:space="preserve">Édouard GLISSANT</t>
         </is>
       </c>
       <c r="M87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inde</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="N87"/>
@@ -6313,55 +6419,45 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t xml:space="preserve">L’Inde moderne</t>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Advaïta Védanta;Brahmoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1">
-        <v>765</v>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">765</t>
-        </is>
-      </c>
-      <c r="D88" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ismaélisme</t>
-        </is>
+          <t xml:space="preserve">Négritude</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>449</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isma%C3%A9lisme" title=" Wikipedia"&gt;L’ismaélisme&lt;/a&gt; est une branche du chiisme née au VIIIe siècle d’une querelle de succession : à la mort de l’imam Ja’far al-Sadiq, en 765, ses fidèles reconnaissent pour héritier son fils Ismaïl, et non son frère. Pour les ismaéliens, l’imam vivant, descendant du Prophète, est le guide qui détient le sens véritable de la révélation.&lt;/p&gt; &lt;p&gt;Leur pensée repose sur la distinction entre l’apparent (&lt;em&gt;zâhir&lt;/em&gt;), la lettre de la Loi et les rites, et le caché (&lt;em&gt;bâtin&lt;/em&gt;), la vérité spirituelle qu’ils contiennent. L’interprétation (&lt;em&gt;ta’wîl&lt;/em&gt;) consiste à remonter de l’un à l’autre. Pour exprimer ce sens caché, les penseurs ismaéliens des Xe et XIe siècles bâtissent une grande philosophie inspirée du néoplatonisme : Dieu, au-delà de tout attribut, fait émaner un premier Intellect, dont procèdent l’Âme et l’univers ; &lt;a href="https://fr.wikipedia.org/wiki/Hamid_al-Din_al-Kirmani" title=" Wikipedia"&gt;al-Kirmani&lt;/a&gt; décrit ainsi une hiérarchie de dix intelligences. On rattache souvent à ce milieu les &lt;a href="https://fr.wikipedia.org/wiki/Ikhwan_al-Safa" title=" Wikipedia"&gt;Frères de la Pureté&lt;/a&gt;, auteurs d’une encyclopédie des sciences. Le califat des &lt;a href="https://fr.wikipedia.org/wiki/Fatimides" title=" Wikipedia"&gt;Fatimides&lt;/a&gt;, qui règne sur l’Égypte de 969 à 1171 et fonde Le Caire et la mosquée al-Azhar, en fait une doctrine d’État.&lt;/p&gt; &lt;p&gt;Le poète persan Nasir Khusraw en est l’un des grands maîtres ; la branche nizârite s’établit en Iran dans la forteresse d’&lt;a href="https://fr.wikipedia.org/wiki/Alamut" title=" Wikipedia"&gt;Alamut&lt;/a&gt;, où le savant Nasir al-Din al-Tusi travaille de longues années, jusqu’à sa prise par les Mongols en 1256. Dépeints à tort par leurs ennemis comme une secte d’« Assassins », les ismaéliens sont aujourd’hui plusieurs millions dans le monde, et la branche nizârite reconnaît pour imam l’&lt;a href="https://fr.wikipedia.org/wiki/Aga_Khan" title=" Wikipedia"&gt;Aga Khan&lt;/a&gt;.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">branche du chiisme qui cherche le sens caché du Coran et l’exprime dans une grande philosophie néoplatonicienne.</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hamid al-Din AL-KIRMANI;NASIR KHUSRAW;Nasir AL-DIN AL-TUSI</t>
-        </is>
-      </c>
-      <c r="M88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="N88"/>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buen_vivir" title=" Wikipedia"&gt;Le Buen Vivir&lt;/a&gt;, « bien vivre » en espagnol, traduit le &lt;em&gt;sumak kawsay&lt;/em&gt; des Quechuas et le &lt;em&gt;suma qamaña&lt;/em&gt; des Aymaras. C’est une philosophie issue des cosmovisions autochtones des Andes, formulée en termes contemporains à partir des années 1990 par des intellectuels et des mouvements indigènes d’Équateur et de Bolivie, rejoints par des penseurs critiques du développement.&lt;/p&gt; &lt;p&gt;Il s’oppose à l’idée occidentale du développement, mesuré par la croissance économique et l’accumulation de biens. Bien vivre, ce n’est pas vivre mieux, c’est-à-dire toujours plus, aux dépens des autres et de la nature : c’est vivre en harmonie au sein de la communauté et avec la &lt;a href="https://fr.wikipedia.org/wiki/Pachamama" title=" Wikipedia"&gt;Pachamama&lt;/a&gt;, la Terre-Mère. L’être humain n’y est ni séparé de la nature ni placé au-dessus d’elle : il fait partie d’un tout vivant tissé de relations, de réciprocité et de complémentarité, où les montagnes, les eaux et les êtres vivants ont leur place. La richesse tient à la qualité des liens plutôt qu’à l’abondance des choses. Ses défenseurs, comme l’économiste équatorien Alberto Acosta ou l’Uruguayen Eduardo Gudynas, y voient une alternative au modèle extractiviste.&lt;/p&gt; &lt;p&gt;La Constitution de l’Équateur de 2008 inscrit le &lt;em&gt;sumak kawsay&lt;/em&gt; parmi ses principes et reconnaît des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_la_nature" title=" Wikipedia"&gt;droits à la nature&lt;/a&gt; elle-même, une première mondiale. La Constitution bolivienne de 2009 en fait un principe éthique de l’État, et des lois de 2010 et 2012 y consacrent les droits de la Terre-Mère. Mais ces deux pays ont continué d’exploiter pétrole et minerais, ce qui nourrit le débat entre l’idéal et son usage politique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6369,50 +6465,54 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+          <t xml:space="preserve">Pensées autochtones</t>
         </is>
       </c>
     </row>
     <row r="89" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1">
-        <v>900</v>
+        <v>350</v>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">900</t>
+          <t xml:space="preserve">350</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maturidisme</t>
+          <t xml:space="preserve">Yogācāra</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maturidisme" title=" Wikipedia"&gt;Le maturidisme&lt;/a&gt; est l’une des deux grandes écoles de théologie rationnelle (&lt;em&gt;kalâm&lt;/em&gt;) de l’islam sunnite, avec l’acharisme. Il est fondé au Xe siècle à Samarcande, en Asie centrale, par Abu Mansur al-Maturidi, qui se réclame de l’héritage de l’imam &lt;a href="https://fr.wikipedia.org/wiki/Ab%C3%BB_Han%C3%AEfa" title=" Wikipedia"&gt;Abû Hanîfa&lt;/a&gt;, fondateur de l’école juridique &lt;a href="https://fr.wikipedia.org/wiki/Hanafisme" title=" Wikipedia"&gt;hanafite&lt;/a&gt;. Comme son contemporain al-Ash’ari, al-Maturidi cherche une voie moyenne entre les mutazilites, qui soumettaient la foi à la raison, et les traditionalistes, qui refusaient tout raisonnement sur Dieu.&lt;/p&gt; &lt;p&gt;Mais il fait une plus grande place à la raison. Pour les maturidites, l’être humain peut savoir par sa seule intelligence que Dieu existe et distinguer le bien du mal, même sans avoir reçu de révélation : le bien et le mal sont inscrits dans les choses, et la révélation vient confirmer et préciser ce que la raison entrevoit. Ils défendent aussi plus nettement la liberté humaine : Dieu crée les actes, mais l’être humain les choisit réellement et en porte la responsabilité. La foi, enfin, est l’adhésion du cœur, confirmée par la parole ; elle ne grandit ni ne diminue avec les œuvres. Les différences avec l’acharisme sont subtiles, et les deux écoles finissent par se reconnaître mutuellement comme orthodoxes.&lt;/p&gt; &lt;p&gt;Porté par les dynasties turques, le maturidisme devient la théologie dominante de l’Asie centrale, de l’Empire ottoman et du monde indien. Le petit credo d’al-Nasafi, au XIIe siècle, commenté par al-Taftazani, est étudié dans les écoles jusqu’à nos jours. Il reste aujourd’hui la théologie de référence d’une grande partie des musulmans sunnites, de la Turquie au Pakistan.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chittamatra" title=" Wikipedia"&gt;Le Yogācāra&lt;/a&gt;, « pratique du yoga », appelé aussi Cittamātra, « esprit seul », est avec le Madhyamaka l’une des deux grandes écoles philosophiques du bouddhisme mahāyāna. Il se forme en Inde au IVe siècle autour de deux frères, Asaṅga et Vasubandhu, à partir de l’expérience des méditants : ce que l’on observe en méditation montre combien le monde vécu est façonné par l’esprit. On doit à Vasubandhu deux courts traités, les &lt;em&gt;Vingt stances&lt;/em&gt; et les &lt;em&gt;Trente stances&lt;/em&gt;, qui résument la doctrine.&lt;/p&gt; &lt;p&gt;Sa thèse est que nous ne connaissons jamais que des représentations : les objets que nous croyons extérieurs sont des apparitions de la conscience, comme dans un rêve. Pour l’expliquer, il ajoute aux six consciences reconnues par le bouddhisme une conscience souillée, qui produit l’illusion d’un moi, et surtout une &lt;a href="https://fr.wikipedia.org/wiki/%C4%80layavij%C3%B1%C4%81na" title=" Wikipedia"&gt;conscience-réceptacle&lt;/a&gt; (&lt;em&gt;ālayavijñāna&lt;/em&gt;), sorte d’inconscient où les actes passés déposent des traces, comme des graines qui germeront plus tard. Il décrit aussi « trois natures » des choses : imaginaire, dépendante et parfaitement accomplie. L’éveil consiste à transformer ce fond de la conscience, jusqu’à ce que cesse le partage entre un sujet qui saisit et un objet saisi.&lt;/p&gt; &lt;p&gt;Ses logiciens, Dignāga puis Dharmakīrti, fondent la grande épistémologie bouddhique. Le pèlerin chinois &lt;a href="https://fr.wikipedia.org/wiki/Xuanzang" title=" Wikipedia"&gt;Xuanzang&lt;/a&gt; rapporte ses textes d’Inde au VIIe siècle et fonde en Chine l’école de la « conscience seule ». Le Yogācāra a nourri le zen, le bouddhisme tibétain et, aujourd’hui, le dialogue avec la phénoménologie et les sciences cognitives.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">école de théologie sunnite fondée à Samarcande par al-Maturidi : la raison peut connaître Dieu et le bien avant toute révélation.</t>
+          <t xml:space="preserve">école bouddhiste de « l’esprit seul » : le monde que nous percevons est une construction de la conscience.</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie et spiritualité;Épistémologie</t>
+          <t xml:space="preserve">Philosophie de l'esprit;Métaphysique;Épistémologie</t>
         </is>
       </c>
       <c r="L89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abu Mansur AL-MATURIDI;Abu Hafs AL-NASAFI</t>
+          <t xml:space="preserve">ASANGA;VASUBANDHU;XUANZANG</t>
         </is>
       </c>
       <c r="M89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="N89"/>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6420,59 +6520,55 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalâm</t>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
         </is>
       </c>
     </row>
     <row r="90" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1">
-        <v>1200</v>
+        <v>402</v>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200</t>
+          <t xml:space="preserve">402</t>
         </is>
       </c>
       <c r="D90" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kabbale</t>
+          <t xml:space="preserve">Bouddhisme de la Terre pure</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kabbale" title=" Wikipedia"&gt;La Kabbale&lt;/a&gt;, la « tradition reçue », est la grande tradition mystique et ésotérique du judaïsme. Elle apparaît à la fin du XIIe siècle en Provence, puis en Catalogne, où Nahmanide, à Gérone, lui donne son autorité, et en Castille, où &lt;a href="https://fr.wikipedia.org/wiki/Mo%C3%AFse_de_Le%C3%B3n" title=" Wikipedia"&gt;Moïse de León&lt;/a&gt; compose vers 1280 le &lt;em&gt;Zohar&lt;/em&gt;, « livre de la Splendeur », qui en devient le texte majeur.&lt;/p&gt; &lt;p&gt;Elle distingue en Dieu l’&lt;em&gt;En Sof&lt;/em&gt;, « l’Infini », absolument caché, et les dix &lt;a href="https://fr.wikipedia.org/wiki/Sephiroth_%28Kabbale%29" title=" Wikipedia"&gt;&lt;em&gt;sefirot&lt;/em&gt;&lt;/a&gt;, émanations par lesquelles il se manifeste : sagesse, intelligence, amour, rigueur, beauté, jusqu’à la &lt;a href="https://fr.wikipedia.org/wiki/Shekhina" title=" Wikipedia"&gt;&lt;em&gt;Shekhina&lt;/em&gt;&lt;/a&gt;, la présence divine dans le monde, que la Kabbale conçoit comme féminine et exilée avec le peuple. Chaque mot de la Torah, chaque commandement accompli, agit sur l’harmonie de ces puissances. Après l’expulsion des Juifs d’Espagne, en 1492, la Kabbale se renouvelle à Safed, en Galilée, autour d’&lt;a href="https://fr.wikipedia.org/wiki/Isaac_Louria" title=" Wikipedia"&gt;Isaac Louria&lt;/a&gt;. Pour faire place au monde, l’Infini a dû se retirer en lui-même : c’est le &lt;a href="https://fr.wikipedia.org/wiki/Tsimtsoum" title=" Wikipedia"&gt;&lt;em&gt;tsimtsoum&lt;/em&gt;&lt;/a&gt;. Puis les « vases » qui devaient recevoir sa lumière se sont brisés, et des étincelles divines sont tombées dans la matière. La tâche de l’être humain est le &lt;a href="https://fr.wikipedia.org/wiki/Tikkoun_Olam" title=" Wikipedia"&gt;&lt;em&gt;tikkoun&lt;/em&gt;&lt;/a&gt;, la réparation du monde, en relevant ces étincelles par la prière et les actes justes. Ce messianisme intérieur nourrit au XVIIe siècle l’aventure de Sabbataï Tsevi, puis, au XVIIIe, le hassidisme.&lt;/p&gt; &lt;p&gt;À la Renaissance, Pic de la Mirandole fonde une « Kabbale chrétienne ». Longtemps méprisée par les historiens, la Kabbale a été réhabilitée au XXe siècle par les travaux de Gershom Scholem, qui en a fait un objet d’étude majeur.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;Le bouddhisme de la &lt;a href="https://fr.wikipedia.org/wiki/Terre_pure" title=" Wikipedia"&gt;Terre pure&lt;/a&gt; est le courant du bouddhisme mahāyāna centré sur la dévotion au bouddha Amitābha (Amida en japonais) qui, selon les sūtras, a fait le vœu d’accueillir dans sa « Terre pure », un paradis situé à l’Occident, tous ceux qui l’invoquent avec foi. Né en Chine, il remonte à Huiyuan, qui réunit en 402 au mont Lu une communauté vouée à Amitābha, puis à &lt;a href="https://fr.wikipedia.org/wiki/Tanluan" title=" Wikipedia"&gt;Tanluan&lt;/a&gt; et à Shandao, qui en font une école.&lt;/p&gt; &lt;p&gt;Sa philosophie part d’un constat : en cette époque de « déclin de la Loi », les êtres humains ne peuvent plus atteindre l’éveil par leurs propres forces, par la méditation ou l’ascèse. Il faut s’en remettre à la « force de l’autre », la compassion d’Amitābha. La pratique principale devient la récitation de son nom, le &lt;em&gt;nembutsu&lt;/em&gt; : « Namu Amida Butsu ». Au Japon, Hōnen fonde en 1175 l’école &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_sh%C5%AB" title=" Wikipedia"&gt;Jōdo shū&lt;/a&gt; et affirme que cette seule récitation suffit au salut, ce qui ouvre le bouddhisme aux gens simples, aux paysans et aux femmes. Son disciple Shinran va plus loin avec le &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_shinsh%C5%AB" title=" Wikipedia"&gt;Jōdo shinshū&lt;/a&gt; : le salut est entièrement un don reçu dans la foi, et c’est le « méchant » conscient de ses fautes, plus encore que le juste, que le Bouddha veut sauver. Shinran se marie, quitte la vie monastique et vit parmi le peuple.&lt;/p&gt; &lt;p&gt;Devenue l’une des formes du bouddhisme les plus pratiquées d’Asie de l’Est, la Terre pure évoque la doctrine chrétienne de la grâce, rapprochement qui a fasciné bien des théologiens occidentaux. Elle compte aujourd’hui des dizaines de millions de fidèles au Japon, en Chine, en Corée et au Viêt Nam.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tradition mystique du judaïsme qui contemple les dix émanations de Dieu et appelle l’être humain à réparer le monde.</t>
+          <t xml:space="preserve">bouddhisme de la foi en Amitābha : le salut par la récitation de son nom et la « force de l’autre ».</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
+          <t xml:space="preserve">Théologie et spiritualité</t>
         </is>
       </c>
       <c r="L90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isaac LOURIA;Moïse de LEÓN;NAHMANIDE;Abraham ABOULAFIA</t>
+          <t xml:space="preserve">HŌNEN;SHINRAN</t>
         </is>
       </c>
       <c r="M90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N90"/>
       <c r="O90" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6480,52 +6576,52 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée juive</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herméneutique juive;Néoplatonisme</t>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
         </is>
       </c>
     </row>
     <row r="91" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1">
-        <v>1740</v>
+        <v>575</v>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740</t>
+          <t xml:space="preserve">575</t>
         </is>
       </c>
       <c r="D91" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hassidisme</t>
+          <t xml:space="preserve">Tiantai</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;Le hassidisme&lt;/a&gt;, de l’hébreu &lt;em&gt;hassid&lt;/em&gt;, « pieux », est un mouvement de renouveau mystique du judaïsme né au XVIIIe siècle en Podolie, dans l’actuelle Ukraine, alors polonaise, autour du Baal Shem Tov, le « Maître du Bon Nom ». Il paraît dans des communautés juives pauvres et éprouvées par les massacres et par la faillite du faux messie Sabbataï Tsevi, où le savoir talmudique est réservé à une élite.&lt;/p&gt; &lt;p&gt;Reprenant les idées de la Kabbale, le hassidisme les met à la portée de tous. Dieu est présent partout, jusque dans les choses les plus humbles : on peut donc le servir non seulement par l’étude, mais par la prière fervente, le chant, la danse et chaque geste du quotidien, accompli avec attention. La joie est une forme de piété, la tristesse un obstacle. La ferveur du cœur compte plus que l’érudition, et le plus simple des fidèles peut s’unir à Dieu. Au centre de chaque communauté se tient le &lt;a href="https://fr.wikipedia.org/wiki/Tsadik" title=" Wikipedia"&gt;&lt;em&gt;tsaddik&lt;/em&gt;&lt;/a&gt;, le « juste », maître spirituel qui guide ses disciples et intercède pour eux. Les maîtres hassidiques enseignent par des récits et des paraboles, comme ceux de &lt;a href="https://fr.wikipedia.org/wiki/Nahman_de_Bratslav" title=" Wikipedia"&gt;Nahman de Bratslav&lt;/a&gt;, arrière-petit-fils du Baal Shem Tov.&lt;/p&gt; &lt;p&gt;Combattu d’abord par les rabbins traditionnels, les &lt;a href="https://fr.wikipedia.org/wiki/Mitnagdim" title=" Wikipedia"&gt;Mitnagdim&lt;/a&gt;, le mouvement gagne une grande partie des Juifs d’Europe de l’Est. Presque anéanti par la Shoah, il renaît aux États-Unis et en Israël, où ses communautés, comme celle de Loubavitch, sont aujourd’hui très vivantes. Martin Buber a fait connaître ses récits en Occident ; Abraham Heschel et Elie Wiesel, issus de familles hassidiques, en ont transmis l’esprit.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tiantai" title=" Wikipedia"&gt;Le Tiantai&lt;/a&gt; est la première grande école du bouddhisme née en Chine plutôt qu’importée d’Inde. Elle tire son nom du mont Tiantai, dans le Zhejiang, où le moine Zhiyi (538-597) s’installe en 575 et élabore sa doctrine. Face à la masse des sūtras traduits en chinois, souvent contradictoires, Zhiyi les classe en périodes et en méthodes d’enseignement : le Bouddha aurait adapté sa parole à ses auditeurs, et le &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_du_Lotus" title=" Wikipedia"&gt;&lt;em&gt;Sūtra du Lotus&lt;/em&gt;&lt;/a&gt; en serait le sommet, qui révèle que tous les êtres peuvent devenir bouddhas.&lt;/p&gt; &lt;p&gt;Sa philosophie repose sur la doctrine des « trois vérités » : toute chose est vide, car sans existence propre ; elle existe pourtant provisoirement, comme apparence ; et elle est le « milieu », qui unit les deux sans les séparer. Zhiyi en tire l’idée qu’« un instant de pensée contient trois mille mondes » : chaque moment de conscience renferme la totalité des états possibles de l’existence, des enfers jusqu’à l’éveil. Le salut n’est donc pas ailleurs : il se découvre au cœur même du monde ordinaire. Zhiyi va jusqu’à soutenir que la nature de bouddha contient aussi le mal, ce qui fait l’originalité de l’école. Il unit étroitement l’étude des textes et la méditation, qu’il expose dans de grands traités sur « l’arrêt et la contemplation ».&lt;/p&gt; &lt;p&gt;Introduite au Japon en 805 par Saichō sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Tendai" title=" Wikipedia"&gt;Tendai&lt;/a&gt;, l’école fait du monastère du mont Hiei le grand centre du bouddhisme japonais. Elle y forme la plupart des fondateurs des écoles ultérieures, dont Hōnen, Shinran, Dōgen et Nichiren, qui en reprend la dévotion au Lotus.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mouvement mystique juif né en Ukraine autour du Baal Shem Tov : servir Dieu dans la joie, l’humilité et chaque geste du quotidien.</t>
+          <t xml:space="preserve">école bouddhiste chinoise fondée par Zhiyi sur le Sūtra du Lotus : trois vérités et trois mille mondes dans un instant de pensée.</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
         </is>
       </c>
       <c r="L91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAAL SHEM TOV;Martin BUBER</t>
+          <t xml:space="preserve">ZHIYI;SAICHŌ</t>
         </is>
       </c>
       <c r="M91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
+          <t xml:space="preserve">asie-est</t>
         </is>
       </c>
       <c r="N91"/>
@@ -6536,59 +6632,55 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée juive</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kabbale</t>
+          <t xml:space="preserve">Bouddhisme Mahayana;Madhyamaka</t>
         </is>
       </c>
     </row>
     <row r="92" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1">
-        <v>1770</v>
+        <v>600</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1770</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haskala</t>
+          <t xml:space="preserve">Huayan</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Haskala" title=" Wikipedia"&gt;La Haskala&lt;/a&gt;, de l’hébreu &lt;em&gt;sekhel&lt;/em&gt;, « intelligence », est le mouvement des Lumières juives, né à Berlin dans les années 1770. Ses partisans, les &lt;em&gt;maskilim&lt;/em&gt;, veulent faire sortir les Juifs du ghetto culturel où les ont enfermés des siècles de discriminations, en les ouvrant aux sciences, à la philosophie et aux langues de l’Europe, sans qu’ils renoncent pour autant à leur foi.&lt;/p&gt; &lt;p&gt;Son inspirateur est Moses Mendelssohn, surnommé le « Socrate de Berlin », admiré de Kant et ami de &lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing" title=" Wikipedia"&gt;Lessing&lt;/a&gt;, qui fait de lui le modèle de son &lt;em&gt;Nathan le Sage&lt;/em&gt;. Il traduit la Torah en allemand, imprimée en caractères hébraïques, pour que les Juifs apprennent la langue du pays. Dans &lt;em&gt;Jérusalem&lt;/em&gt; (1783), il défend la liberté de conscience et la séparation de l’État et de la religion : le judaïsme, dit-il, n’impose pas de croyances, il prescrit des pratiques, et ses vérités sont celles de la raison, accessibles à tous les hommes. Autour de lui, le médecin Marcus Herz, élève de Kant, et David Friedländer, qui plaide pour l’émancipation civile des Juifs de Prusse, poursuivent son œuvre. La Haskala fonde des écoles modernes, une presse et fait renaître l’hébreu comme langue littéraire profane.&lt;/p&gt; &lt;p&gt;Au XIXe siècle, elle gagne la Galicie et l’Empire russe. Elle prépare le &lt;a href="https://fr.wikipedia.org/wiki/Juda%C3%AFsme_r%C3%A9form%C3%A9" title=" Wikipedia"&gt;judaïsme libéral&lt;/a&gt;, la &lt;a href="https://fr.wikipedia.org/wiki/Wissenschaft_des_Judentums" title=" Wikipedia"&gt;« science du judaïsme »&lt;/a&gt;, l’étude historique de sa tradition, et indirectement le sionisme. Ses adversaires lui ont reproché d’ouvrir la voie à l’assimilation ; ses héritiers y voient l’entrée du judaïsme dans la modernité.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Huayan" title=" Wikipedia"&gt;Le Huayan&lt;/a&gt;, ou « école de l’Ornementation fleurie », est une école du bouddhisme chinois fondée sur l’&lt;a href="https://fr.wikipedia.org/wiki/Avata%E1%B9%83saka_s%C5%ABtra" title=" Wikipedia"&gt;&lt;em&gt;Avataṃsaka sūtra&lt;/em&gt;&lt;/a&gt;, immense texte qui décrit l’univers tel que le voit un bouddha éveillé. Elle se forme aux VIe et VIIe siècles autour de &lt;a href="https://fr.wikipedia.org/wiki/Dushun" title=" Wikipedia"&gt;Dushun&lt;/a&gt;, son premier patriarche, puis de Zhiyan, et trouve son grand systématicien en Fazang (643-712), qui l’expose à la cour de l’impératrice Wu Zetian.&lt;/p&gt; &lt;p&gt;Sa philosophie est celle de l’interdépendance totale : chaque chose contient toutes les autres et se trouve contenue en elles, sans que leurs différences soient abolies. Pour le faire comprendre à l’impératrice, Fazang prend l’image d’un lion d’or : l’or est la nature unique et vide, le lion la forme qu’elle prend, et chaque poil du lion contient le lion tout entier. Il reprend aussi celle du filet d’Indra, filet céleste dont chaque nœud porte une perle qui reflète toutes les autres perles, à l’infini. Le Huayan distingue quatre plans de réalité : celui des phénomènes, celui du principe, celui de leur non-obstruction mutuelle, et enfin celui de la non-obstruction de tous les phénomènes entre eux, qui est la vision de l’éveil.&lt;/p&gt; &lt;p&gt;En Chine, &lt;a href="https://fr.wikipedia.org/wiki/Zongmi" title=" Wikipedia"&gt;Zongmi&lt;/a&gt; (780-841) le concilie avec le chan. Ŭisang l’apporte en Corée, où il devient l’école Hwaeom, que Chinul unira plus tard à la méditation seon ; au Japon, il prend le nom de &lt;a href="https://fr.wikipedia.org/wiki/Kegon" title=" Wikipedia"&gt;Kegon&lt;/a&gt; et c’est à lui que se rattache le grand Bouddha de Nara. Le Huayan a profondément marqué le zen et le néoconfucianisme. On rapproche parfois aujourd’hui sa vision d’un monde entièrement relié de la pensée écologique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">les « Lumières juives » de Mendelssohn : unir la fidélité au judaïsme, la raison et la culture européenne.</t>
+          <t xml:space="preserve">école bouddhiste chinoise de l’interdépendance totale, où chaque chose contient toutes les autres.</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie politique;Théologie et spiritualité</t>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
         </is>
       </c>
       <c r="L92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moses MENDELSSOHN</t>
+          <t xml:space="preserve">FAZANG;UISANG</t>
         </is>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N92"/>
       <c r="O92" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6596,52 +6688,52 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée juive</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lumières</t>
+          <t xml:space="preserve">Bouddhisme Mahayana;Yogācāra</t>
         </is>
       </c>
     </row>
     <row r="93" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1">
-        <v>1600</v>
+        <v>600</v>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600</t>
+          <t xml:space="preserve">600</t>
         </is>
       </c>
       <c r="D93" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">École d'Ispahan</t>
+          <t xml:space="preserve">Bhakti</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_d%27Ispahan" title=" Wikipedia"&gt;École d’Ispahan&lt;/a&gt; le grand renouveau philosophique qui se produit en Iran au XVIIe siècle, à Ispahan, capitale de la dynastie &lt;a href="https://fr.wikipedia.org/wiki/Dynastie_des_S%C3%A9f%C3%A9vides" title=" Wikipedia"&gt;safavide&lt;/a&gt; qui a fait du chiisme la religion d’État. Alors que l’on a longtemps cru la philosophie islamique morte après Averroès, elle connaît là une nouvelle floraison, qui unit l’héritage d’Avicenne, la sagesse de l’illumination de Sohrawardi, la mystique d’Ibn Arabî et la théologie chiite.&lt;/p&gt; &lt;p&gt;Son premier maître est &lt;a href="https://fr.wikipedia.org/wiki/Mir_Damad" title=" Wikipedia"&gt;Mir Damad&lt;/a&gt;, philosophe et théologien, qui réfléchit sur le rapport entre l’éternité et le temps et signe ses poèmes du nom d’« Ishrâq », l’illumination. Son disciple Molla Sadra en est le génie. Dans ses &lt;em&gt;Quatre voyages de l’intellect&lt;/em&gt;, il fonde la « sagesse transcendante » (&lt;em&gt;al-hikma al-muta’aliya&lt;/em&gt;), qui veut unir la démonstration rationnelle, l’expérience spirituelle et la révélation. Sa thèse centrale est la primauté de l’existence : ce qui est réel, ce n’est pas l’essence, la définition des choses, mais l’acte d’exister, unique et présent en toutes choses à des degrés différents, comme une même lumière plus ou moins intense. Il affirme aussi le « mouvement substantiel » : l’être des choses n’est pas fixe, il est lui-même en devenir, si bien que le monde tout entier est en marche vers sa perfection.&lt;/p&gt; &lt;p&gt;Prolongée en Iran jusqu’à nos jours, par Sabzevari au XIXe siècle puis par Allameh Tabatabaï et Morteza Motahhari, cette école a été révélée au public occidental par &lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin" title=" Wikipedia"&gt;Henry Corbin&lt;/a&gt;, qui lui a donné son nom. Elle a aussi profondément marqué le clergé chiite iranien du XXe siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bhakti" title=" Wikipedia"&gt;La bhakti&lt;/a&gt;, la « dévotion » ou « l’amour de Dieu », est une voie spirituelle de l’hindouisme qui place l’amour personnel d’une divinité au-dessus des rites, des sacrifices et du savoir. Annoncée dans la &lt;em&gt;Bhagavad-Gītā&lt;/em&gt;, où Krishna enseigne que l’abandon aimant à Dieu est le plus sûr chemin vers la délivrance, elle devient un grand mouvement dans l’Inde du Sud entre le VIe et le IXe siècle, avec les poètes tamouls : les &lt;a href="https://fr.wikipedia.org/wiki/Alvar" title=" Wikipedia"&gt;Alvars&lt;/a&gt;, dévots de Vishnou, et les &lt;a href="https://fr.wikipedia.org/wiki/Nayanar" title=" Wikipedia"&gt;Nayanars&lt;/a&gt;, dévots de Shiva.&lt;/p&gt; &lt;p&gt;Ces saints chantent leur dieu dans la langue du peuple et non en sanskrit, et beaucoup viennent de basses castes : la bhakti affirme que l’amour de Dieu est ouvert à tous, sans distinction de naissance ni de sexe. Elle reçoit une base philosophique avec Rāmānuja, au XIe siècle, qui défend contre Shankara la réalité de l’âme et du monde, distincts de Dieu tout en dépendant de lui ; Madhva va plus loin dans le dualisme. L’âme ne se fond pas dans l’absolu : elle demeure, pour aimer. Du XIIIe au XVIIe siècle, la bhakti gagne l’Inde du Nord : Kabir, tisserand de Bénarès, unit hindous et musulmans dans le culte d’un Dieu sans forme ; la princesse Mīrābāī chante Krishna en bravant les conventions ; Chaitanya, au Bengale, fait du chant et de la danse une prière extatique ; &lt;a href="https://fr.wikipedia.org/wiki/Tuls%C3%AEd%C3%A2s" title=" Wikipedia"&gt;Tulsîdâs&lt;/a&gt; écrit le &lt;em&gt;Ramcharitmanas&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Mouvement de réforme autant que de piété, la bhakti a façonné l’hindouisme populaire, inspiré le sikhisme et nourri, jusqu’à Gandhi, l’idée que la religion se vit d’abord dans le cœur.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">renaissance de la philosophie dans l’Iran chiite des Safavides, dont Molla Sadra est le sommet avec sa « sagesse transcendante ».</t>
+          <t xml:space="preserve">voie hindoue de la dévotion amoureuse à Dieu, ouverte à tous sans distinction de caste ni de sexe.</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+          <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
         </is>
       </c>
       <c r="L93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molla SADRA;MIR DAMAD;Allameh TABATABAÏ</t>
+          <t xml:space="preserve">RAMANUJA;KABIR;MIRABAI</t>
         </is>
       </c>
       <c r="M93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">islam-juif</t>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
       <c r="N93"/>
@@ -6652,52 +6744,52 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+          <t xml:space="preserve">Hindouismes de dévotion</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ishraqisme;Soufisme</t>
+          <t xml:space="preserve">Hindouisme</t>
         </is>
       </c>
     </row>
     <row r="94" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1">
-        <v>1878</v>
+        <v>850</v>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878</t>
+          <t xml:space="preserve">850</t>
         </is>
       </c>
       <c r="D94" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophiologie</t>
+          <t xml:space="preserve">Shivaïsme du Cachemire</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sophiologie" title=" Wikipedia"&gt;La sophiologie&lt;/a&gt; est un courant de la philosophie religieuse russe, né à la fin du XIXe siècle, qui fait de la &lt;a href="https://fr.wikipedia.org/wiki/Sophia_%28philosophie%29" title=" Wikipedia"&gt;Sagesse divine&lt;/a&gt;, Sophia, le cœur de sa réflexion. Elle reprend une figure de la Bible, où la Sagesse est présentée comme la compagne de Dieu lors de la création, et une longue tradition mystique, du platonisme à Jacob Boehme. Son fondateur est Vladimir Soloviev, qui raconte avoir eu trois visions de Sophia, la dernière dans le désert d’Égypte, en 1875.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Leçons sur la divino-humanité&lt;/em&gt; (1878), Soloviev décrit Sophia comme l’âme du monde, l’unité idéale de toutes les créatures en Dieu : elle est le lien entre le Créateur et la création, ce par quoi le monde n’est pas étranger à Dieu. L’histoire a pour sens la réunion progressive de l’humanité et du divin, dont le Christ, Dieu fait homme, est le modèle. Le prêtre et savant Pavel Florensky reprend cette intuition dans &lt;em&gt;La Colonne et le Fondement de la vérité&lt;/em&gt; (1914), en y mêlant mathématiques, théologie et histoire de l’art. Mais c’est Sergueï Boulgakov, économiste marxiste devenu prêtre orthodoxe, qui en fait un vaste système théologique dans son exil parisien, à l’&lt;a href="https://fr.wikipedia.org/wiki/Institut_Saint-Serge" title=" Wikipedia"&gt;Institut Saint-Serge&lt;/a&gt; : la Sagesse est la nature même de Dieu, qui se révèle dans le monde créé, si bien que la création tout entière est appelée à être transfigurée.&lt;/p&gt; &lt;p&gt;En 1935, l’Église orthodoxe russe condamne les thèses de Boulgakov, et les théologiens Vladimir Lossky et Georges Florovsky les critiquent sévèrement. La sophiologie a pourtant marqué les poètes symbolistes, comme Alexandre Blok et Andreï Biély, et elle inspire aujourd’hui une théologie de la création attentive à l’écologie.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shiva%C3%AFsme_du_Cachemire" title=" Wikipedia"&gt;Le shivaïsme du Cachemire&lt;/a&gt; est une école philosophique et mystique hindoue qui s’épanouit dans la vallée du Cachemire entre le IXe et le XIe siècle. Il naît, selon la tradition, des &lt;em&gt;Śiva Sūtra&lt;/em&gt; que &lt;a href="https://fr.wikipedia.org/wiki/Vasugupta" title=" Wikipedia"&gt;Vasugupta&lt;/a&gt; aurait reçus en rêve. À la différence du shivaïsme dualiste du Sud, il est résolument non dualiste : il n’existe qu’une seule réalité, Shiva, conscience absolue, libre et lumineuse, dont l’univers entier est la manifestation. Il appartient au monde des tantras, qui valorise le corps, l’énergie et la vie dans le monde plutôt que le renoncement.&lt;/p&gt; &lt;p&gt;Là où l’Advaita Védanta de Shankara voit dans le monde une illusion, le shivaïsme du Cachemire y voit le jeu bien réel de la liberté divine. La conscience n’est pas seulement une lumière immobile ; elle est aussi &lt;a href="https://fr.wikipedia.org/wiki/Spanda" title=" Wikipedia"&gt;&lt;em&gt;spanda&lt;/em&gt;&lt;/a&gt;, « vibration », énergie créatrice qui se déploie sous la forme des choses. Utpaladeva fonde l’école de la « Reconnaissance » (&lt;em&gt;Pratyabhijñā&lt;/em&gt;) : l’être humain n’a pas à devenir Shiva, il l’est déjà, et la libération consiste à le reconnaître, comme on reconnaît soudain un ami qu’on avait sous les yeux. Le grand penseur de l’école, Abhinavagupta, en fait la synthèse dans son immense &lt;em&gt;Tantrāloka&lt;/em&gt;, « Lumière sur les tantras ». Il pense aussi l’art : l’émotion esthétique (&lt;em&gt;rasa&lt;/em&gt;) éprouvée au théâtre ou devant un poème est un avant-goût de la joie de la conscience libérée.&lt;/p&gt; &lt;p&gt;Presque oublié après le XIIe siècle, il a été redécouvert au XXe siècle, notamment grâce à l’indianiste &lt;a href="https://fr.wikipedia.org/wiki/Lilian_Silburn" title=" Wikipedia"&gt;Lilian Silburn&lt;/a&gt; en France et au maître cachemirien Swami Lakshman Joo.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophie religieuse russe de la Sagesse divine, Sophia, qui unit Dieu et le monde : Soloviev, Florensky, Boulgakov.</t>
+          <t xml:space="preserve">non-dualisme hindou pour qui le monde est le libre jeu de la conscience divine, Shiva, que l’être humain doit reconnaître en lui.</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
         </is>
       </c>
       <c r="L94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vladimir SOLOVIEV;Sergueï BOULGAKOV;Pavel FLORENSKY</t>
+          <t xml:space="preserve">ABHINAVAGUPTA;UTPALADEVA</t>
         </is>
       </c>
       <c r="M94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">russe</t>
+          <t xml:space="preserve">inde</t>
         </is>
       </c>
       <c r="N94"/>
@@ -6708,59 +6800,55 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie religieuse russe</t>
+          <t xml:space="preserve">Hindouismes de dévotion</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slavophilisme;Néoplatonisme</t>
+          <t xml:space="preserve">Hindouisme</t>
         </is>
       </c>
     </row>
     <row r="95" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1">
-        <v>1921</v>
+        <v>1890</v>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921</t>
+          <t xml:space="preserve">1890</t>
         </is>
       </c>
       <c r="D95" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eurasisme</t>
+          <t xml:space="preserve">Néo-védanta</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;L’eurasisme&lt;/a&gt; est un courant de pensée né en 1921 dans l’émigration russe, après la révolution bolchevique, avec le recueil &lt;em&gt;L’Exode vers l’Orient&lt;/em&gt;, publié à Sofia par un petit groupe de jeunes intellectuels exilés : le linguiste &lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Sergue%C3%AFevitch_Troubetsko%C3%AF" title=" Wikipedia"&gt;Nikolaï Troubetskoï&lt;/a&gt;, le géographe Piotr Savitski, le musicologue Pierre Souvtchinski et le théologien Georges Florovsky.&lt;/p&gt; &lt;p&gt;Leur thèse est que la Russie n’est ni une partie de l’Europe ni une partie de l’Asie, mais un monde à part, l’« Eurasie », dont la grande plaine, des Carpates au Pacifique, a façonné l’unité des peuples slaves, turcs et finno-ougriens. Contre les occidentalistes, ils refusent l’idée d’une civilisation européenne universelle : dans &lt;em&gt;L’Europe et l’humanité&lt;/em&gt; (1920), Troubetskoï y voit l’égoïsme d’une culture « romano-germanique » qui s’impose aux autres. Contre les slavophiles, ils réhabilitent l’héritage asiatique de la Russie, et jusqu’à l’empire de Gengis Khan, qui aurait le premier unifié cet espace. Ils rêvent d’un État fondé sur une idéologie commune et sur l’orthodoxie, distinct à la fois de la démocratie libérale et du communisme. Florovsky s’en éloigne vite et critique en 1928 ce qu’il appelle une « vérité des questions » devenue une « erreur des réponses ». Le mouvement se divise à la fin des années 1920, une partie se rapprochant du régime soviétique.&lt;/p&gt; &lt;p&gt;Prolongé en URSS par l’historien &lt;a href="https://fr.wikipedia.org/wiki/Lev_Goumilev" title=" Wikipedia"&gt;Lev Goumilev&lt;/a&gt;, l’eurasisme renaît après 1991 sous la forme d’un « néo-eurasisme » porté par &lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Douguine" title=" Wikipedia"&gt;Alexandre Douguine&lt;/a&gt;, idéologue d’extrême droite, et influence aujourd’hui la géopolitique nationaliste et impériale de la Russie.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9o-v%C3%A9danta" title=" Wikipedia"&gt;néo-védanta&lt;/a&gt; la forme moderne du Védanta qui se développe en Inde à partir du XIXe siècle, en anglais plutôt qu’en sanskrit, au contact de l’Occident et de la domination britannique. Elle renouvelle la philosophie non dualiste de Shankara pour en faire une réponse aux critiques des missionnaires et un fondement de la fierté indienne.&lt;/p&gt; &lt;p&gt;Son point de départ est le mystique bengali &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A2makrishna" title=" Wikipedia"&gt;Râmakrishna&lt;/a&gt; (1836-1886), qui affirme, après avoir pratiqué plusieurs religions, que toutes mènent au même but. Son disciple Vivekananda porte ce message au &lt;a href="https://fr.wikipedia.org/wiki/Parlement_des_religions" title=" Wikipedia"&gt;Parlement des religions&lt;/a&gt; de Chicago, en 1893 : le Védanta y devient une religion universelle et rationnelle, compatible avec la science, qui reconnaît la divinité présente en chaque être humain. Il en découle une éthique de l’action : servir les pauvres, c’est servir Dieu ; Vivekananda fonde à cette fin la Mission Ramakrishna, vouée à l’enseignement et aux soins. Au XXe siècle, Sri Aurobindo en propose, depuis son ashram de Pondichéry, une version évolutionniste, où la conscience divine descend dans la matière et où l’humanité doit s’élever vers un « supramental ». Sarvepalli Radhakrishnan, professeur à Oxford devenu président de l’Inde, en donne l’exposé savant et le présente comme la synthèse de l’expérience religieuse de l’humanité.&lt;/p&gt; &lt;p&gt;Le néo-védanta a façonné l’image de l’hindouisme dans le monde et nourri le nationalisme indien. Des historiens lui reprochent cependant d’avoir unifié une tradition très diverse en la lisant à travers des catégories occidentales.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">doctrine née dans l’émigration russe : la Russie ne serait ni l’Europe ni l’Asie, mais une civilisation à part, l’« Eurasie ».</t>
+          <t xml:space="preserve">relecture moderne du Védanta par Vivekananda, Aurobindo et Radhakrishnan : une religion universelle et rationnelle.</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie politique</t>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
         </is>
       </c>
       <c r="L95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nikolaï TROUBETSKOÏ;Georges FLOROVSKY</t>
+          <t xml:space="preserve">VIVEKANANDA;Sri AUROBINDO;Sarvepalli RADHAKRISHNAN</t>
         </is>
       </c>
       <c r="M95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">russe</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N95"/>
       <c r="O95" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6768,52 +6856,52 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
+          <t xml:space="preserve">L’Inde moderne</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slavophilisme</t>
+          <t xml:space="preserve">Advaïta Védanta;Brahmoïsme</t>
         </is>
       </c>
     </row>
     <row r="96" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1">
-        <v>1945</v>
+        <v>765</v>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1945</t>
+          <t xml:space="preserve">765</t>
         </is>
       </c>
       <c r="D96" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ethnophilosophie</t>
+          <t xml:space="preserve">Ismaélisme</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ethnophilosophy" title=" Wikipedia (en)"&gt;L’ethnophilosophie&lt;/a&gt; désigne la démarche qui cherche la philosophie d’un peuple dans ses langues, ses proverbes, ses mythes et ses croyances, plutôt que dans les œuvres de penseurs individuels. Elle naît en 1945 avec &lt;a href="https://fr.wikipedia.org/wiki/La_Philosophie_bantoue" title=" Wikipedia"&gt;&lt;em&gt;La Philosophie bantoue&lt;/em&gt;&lt;/a&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;, qui veut montrer, contre le préjugé colonial, que les Africains ont une pensée cohérente, fondée sur l’idée de « force vitale » : pour les Bantous, l’être est force, et toute chose est une force qui peut croître ou décroître.&lt;/p&gt; &lt;p&gt;Des penseurs africains reprennent cette démarche en la retournant contre le regard colonial. Le prêtre rwandais Alexis Kagame, dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), dégage les catégories de la pensée à partir de la grammaire du kinyarwanda, comme Aristote l’avait fait, selon lui, à partir du grec. Le théologien kényan John Mbiti décrit dans &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969) une conception du temps tournée vers le passé plus que vers l’avenir. Dans l’esprit de la Négritude, il s’agit d’affirmer la dignité des cultures africaines.&lt;/p&gt; &lt;p&gt;À partir des années 1970, cette démarche est vivement critiquée par d’autres philosophes africains. Paulin Hountondji, dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976), dénonce le « mythe de l’unanimité » : une philosophie n’est pas une vision du monde collective et figée, mais un discours critique, signé, argumenté et ouvert à la discussion. Marcien Towa et Fabien Eboussi Boulaga vont dans le même sens. Le débat sur l’ethnophilosophie a structuré toute la philosophie africaine contemporaine.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Isma%C3%A9lisme" title=" Wikipedia"&gt;L’ismaélisme&lt;/a&gt; est une branche du chiisme née au VIIIe siècle d’une querelle de succession : à la mort de l’imam Ja’far al-Sadiq, en 765, ses fidèles reconnaissent pour héritier son fils Ismaïl, et non son frère. Pour les ismaéliens, l’imam vivant, descendant du Prophète, est le guide qui détient le sens véritable de la révélation.&lt;/p&gt; &lt;p&gt;Leur pensée repose sur la distinction entre l’apparent (&lt;em&gt;zâhir&lt;/em&gt;), la lettre de la Loi et les rites, et le caché (&lt;em&gt;bâtin&lt;/em&gt;), la vérité spirituelle qu’ils contiennent. L’interprétation (&lt;em&gt;ta’wîl&lt;/em&gt;) consiste à remonter de l’un à l’autre. Pour exprimer ce sens caché, les penseurs ismaéliens des Xe et XIe siècles bâtissent une grande philosophie inspirée du néoplatonisme : Dieu, au-delà de tout attribut, fait émaner un premier Intellect, dont procèdent l’Âme et l’univers ; &lt;a href="https://fr.wikipedia.org/wiki/Hamid_al-Din_al-Kirmani" title=" Wikipedia"&gt;al-Kirmani&lt;/a&gt; décrit ainsi une hiérarchie de dix intelligences. On rattache souvent à ce milieu les &lt;a href="https://fr.wikipedia.org/wiki/Ikhwan_al-Safa" title=" Wikipedia"&gt;Frères de la Pureté&lt;/a&gt;, auteurs d’une encyclopédie des sciences. Le califat des &lt;a href="https://fr.wikipedia.org/wiki/Fatimides" title=" Wikipedia"&gt;Fatimides&lt;/a&gt;, qui règne sur l’Égypte de 969 à 1171 et fonde Le Caire et la mosquée al-Azhar, en fait une doctrine d’État.&lt;/p&gt; &lt;p&gt;Le poète persan Nasir Khusraw en est l’un des grands maîtres ; la branche nizârite s’établit en Iran dans la forteresse d’&lt;a href="https://fr.wikipedia.org/wiki/Alamut" title=" Wikipedia"&gt;Alamut&lt;/a&gt;, où le savant Nasir al-Din al-Tusi travaille de longues années, jusqu’à sa prise par les Mongols en 1256. Dépeints à tort par leurs ennemis comme une secte d’« Assassins », les ismaéliens sont aujourd’hui plusieurs millions dans le monde, et la branche nizârite reconnaît pour imam l’&lt;a href="https://fr.wikipedia.org/wiki/Aga_Khan" title=" Wikipedia"&gt;Aga Khan&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">recherche d’une philosophie africaine dans les langues, les croyances et les traditions des peuples, et débat qu’elle a suscité.</t>
+          <t xml:space="preserve">branche du chiisme qui cherche le sens caché du Coran et l’exprime dans une grande philosophie néoplatonicienne.</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métaphysique;Épistémologie</t>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
         </is>
       </c>
       <c r="L96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Placide TEMPELS;Alexis KAGAME;John MBITI</t>
+          <t xml:space="preserve">Hamid al-Din AL-KIRMANI;NASIR KHUSRAW;Nasir AL-DIN AL-TUSI</t>
         </is>
       </c>
       <c r="M96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="N96"/>
@@ -6824,52 +6912,47 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensées africaines</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Négritude</t>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
         </is>
       </c>
     </row>
     <row r="97" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1">
-        <v>1960</v>
+        <v>900</v>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960</t>
+          <t xml:space="preserve">900</t>
         </is>
       </c>
       <c r="D97" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Socialisme africain</t>
+          <t xml:space="preserve">Maturidisme</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/Socialisme_africain" title=" Wikipedia"&gt;socialisme africain&lt;/a&gt; l’ensemble des doctrines par lesquelles plusieurs dirigeants des indépendances africaines, autour de 1960, ont voulu définir une voie propre de développement, distincte à la fois du capitalisme des anciennes puissances coloniales et du communisme soviétique.&lt;/p&gt; &lt;p&gt;Leur idée commune est que l’Afrique n’a pas besoin d’importer le socialisme, car elle le porte déjà dans ses traditions : la solidarité de la famille élargie et du village, la propriété commune de la terre, le partage des biens. Il ne s’agit donc pas de mener une lutte des classes, que les sociétés africaines n’auraient pas connue, mais de moderniser ces solidarités. Au Sénégal, Léopold Sédar Senghor défend un socialisme humaniste et spirituel, nourri de la Négritude et de la pensée de Teilhard de Chardin, qui refuse l’athéisme marxiste. Au Ghana, Kwame Nkrumah, plus proche du marxisme, cherche dans son « consciencisme » une synthèse entre la tradition africaine, l’islam et le christianisme. En Tanzanie, Julius Nyerere en donne la version la plus élaborée avec l’&lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt;, mot swahili qui signifie « esprit de famille » : la nation doit vivre comme une grande famille où chacun travaille et où personne n’exploite personne. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;déclaration d’Arusha&lt;/a&gt; (1967) en fait le programme du pays.&lt;/p&gt; &lt;p&gt;Dans les faits, ces politiques ont souvent abouti à des partis uniques et, en Tanzanie, au regroupement forcé des paysans dans des villages collectifs, qui fut un échec économique, reconnu par Nyerere lui-même. Elles restent pourtant une tentative originale de penser le développement à partir des valeurs africaines.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maturidisme" title=" Wikipedia"&gt;Le maturidisme&lt;/a&gt; est l’une des deux grandes écoles de théologie rationnelle (&lt;em&gt;kalâm&lt;/em&gt;) de l’islam sunnite, avec l’acharisme. Il est fondé au Xe siècle à Samarcande, en Asie centrale, par Abu Mansur al-Maturidi, qui se réclame de l’héritage de l’imam &lt;a href="https://fr.wikipedia.org/wiki/Ab%C3%BB_Han%C3%AEfa" title=" Wikipedia"&gt;Abû Hanîfa&lt;/a&gt;, fondateur de l’école juridique &lt;a href="https://fr.wikipedia.org/wiki/Hanafisme" title=" Wikipedia"&gt;hanafite&lt;/a&gt;. Comme son contemporain al-Ash’ari, al-Maturidi cherche une voie moyenne entre les mutazilites, qui soumettaient la foi à la raison, et les traditionalistes, qui refusaient tout raisonnement sur Dieu.&lt;/p&gt; &lt;p&gt;Mais il fait une plus grande place à la raison. Pour les maturidites, l’être humain peut savoir par sa seule intelligence que Dieu existe et distinguer le bien du mal, même sans avoir reçu de révélation : le bien et le mal sont inscrits dans les choses, et la révélation vient confirmer et préciser ce que la raison entrevoit. Ils défendent aussi plus nettement la liberté humaine : Dieu crée les actes, mais l’être humain les choisit réellement et en porte la responsabilité. La foi, enfin, est l’adhésion du cœur, confirmée par la parole ; elle ne grandit ni ne diminue avec les œuvres. Les différences avec l’acharisme sont subtiles, et les deux écoles finissent par se reconnaître mutuellement comme orthodoxes.&lt;/p&gt; &lt;p&gt;Porté par les dynasties turques, le maturidisme devient la théologie dominante de l’Asie centrale, de l’Empire ottoman et du monde indien. Le petit credo d’al-Nasafi, au XIIe siècle, commenté par al-Taftazani, est étudié dans les écoles jusqu’à nos jours. Il reste aujourd’hui la théologie de référence d’une grande partie des musulmans sunnites, de la Turquie au Pakistan.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">socialisme des indépendances fondé sur les solidarités communautaires africaines plutôt que sur la lutte des classes.</t>
+          <t xml:space="preserve">école de théologie sunnite fondée à Samarcande par al-Maturidi : la raison peut connaître Dieu et le bien avant toute révélation.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie politique;Éthique</t>
+          <t xml:space="preserve">Théologie et spiritualité;Épistémologie</t>
         </is>
       </c>
       <c r="L97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Julius NYERERE;Léopold Sédar SENGHOR;Kwame NKRUMAH</t>
+          <t xml:space="preserve">Abu Mansur AL-MATURIDI;Abu Hafs AL-NASAFI</t>
         </is>
       </c>
       <c r="M97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
       <c r="N97"/>
@@ -6880,59 +6963,55 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensées africaines</t>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pan-africanisme;Marxisme</t>
+          <t xml:space="preserve">Kalâm</t>
         </is>
       </c>
     </row>
     <row r="98" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1">
-        <v>1968</v>
+        <v>1600</v>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968</t>
+          <t xml:space="preserve">1600</t>
         </is>
       </c>
       <c r="D98" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de la libération</t>
+          <t xml:space="preserve">École d'Ispahan</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;La théologie de la libération&lt;/a&gt; est un courant de pensée chrétien, surtout catholique, né en Amérique latine à la fin des années 1960, dans un continent marqué par la misère, les inégalités et les dictatures. Elle s’appuie sur le renouveau du concile Vatican II et sur la &lt;a href="https://fr.wikipedia.org/wiki/Conf%C3%A9rence_de_Medell%C3%ADn" title=" Wikipedia"&gt;conférence des évêques latino-américains de Medellín&lt;/a&gt;, en 1968, qui dénonce la « violence institutionnalisée » de l’injustice sociale.&lt;/p&gt; &lt;p&gt;Son texte fondateur est &lt;em&gt;Théologie de la libération&lt;/em&gt; (1971) du prêtre péruvien &lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo Gutiérrez&lt;/a&gt;. La théologie n’y est plus seulement une réflexion abstraite sur Dieu, mais une « réflexion critique sur la pratique » : elle part de la situation concrète des pauvres et de leur lutte pour leur dignité. Dieu prend parti pour les opprimés, comme il a libéré Israël de l’esclavage en Égypte ; le salut ne concerne pas seulement l’au-delà, il commence par la libération de toutes les servitudes. D’où l’« option préférentielle pour les pauvres ». Pour comprendre les causes de la pauvreté, ces théologiens utilisent les sciences sociales, y compris l’analyse marxiste. La foi se vit dans les &lt;a href="https://fr.wikipedia.org/wiki/Communaut%C3%A9_eccl%C3%A9siale_de_base" title=" Wikipedia"&gt;communautés ecclésiales de base&lt;/a&gt;, où les pauvres lisent eux-mêmes la Bible à la lumière de leur vie. Le Brésilien Leonardo Boff, le jésuite Ignacio Ellacuría, assassiné au Salvador en 1989, et les réflexions de Paulo Freire et d’Enrique Dussel lui sont proches.&lt;/p&gt; &lt;p&gt;Rome, sous Jean-Paul II, critique dans les années 1980 son usage du marxisme et impose le silence à Boff. Sa reconnaissance vient avec le pape François, et l’option pour les pauvres est aujourd’hui reprise par toute l’Église catholique.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_d%27Ispahan" title=" Wikipedia"&gt;École d’Ispahan&lt;/a&gt; le grand renouveau philosophique qui se produit en Iran au XVIIe siècle, à Ispahan, capitale de la dynastie &lt;a href="https://fr.wikipedia.org/wiki/Dynastie_des_S%C3%A9f%C3%A9vides" title=" Wikipedia"&gt;safavide&lt;/a&gt; qui a fait du chiisme la religion d’État. Alors que l’on a longtemps cru la philosophie islamique morte après Averroès, elle connaît là une nouvelle floraison, qui unit l’héritage d’Avicenne, la sagesse de l’illumination de Sohrawardi, la mystique d’Ibn Arabî et la théologie chiite.&lt;/p&gt; &lt;p&gt;Son premier maître est &lt;a href="https://fr.wikipedia.org/wiki/Mir_Damad" title=" Wikipedia"&gt;Mir Damad&lt;/a&gt;, philosophe et théologien, qui réfléchit sur le rapport entre l’éternité et le temps et signe ses poèmes du nom d’« Ishrâq », l’illumination. Son disciple Molla Sadra en est le génie. Dans ses &lt;em&gt;Quatre voyages de l’intellect&lt;/em&gt;, il fonde la « sagesse transcendante » (&lt;em&gt;al-hikma al-muta’aliya&lt;/em&gt;), qui veut unir la démonstration rationnelle, l’expérience spirituelle et la révélation. Sa thèse centrale est la primauté de l’existence : ce qui est réel, ce n’est pas l’essence, la définition des choses, mais l’acte d’exister, unique et présent en toutes choses à des degrés différents, comme une même lumière plus ou moins intense. Il affirme aussi le « mouvement substantiel » : l’être des choses n’est pas fixe, il est lui-même en devenir, si bien que le monde tout entier est en marche vers sa perfection.&lt;/p&gt; &lt;p&gt;Prolongée en Iran jusqu’à nos jours, par Sabzevari au XIXe siècle puis par Allameh Tabatabaï et Morteza Motahhari, cette école a été révélée au public occidental par &lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin" title=" Wikipedia"&gt;Henry Corbin&lt;/a&gt;, qui lui a donné son nom. Elle a aussi profondément marqué le clergé chiite iranien du XXe siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">courant chrétien latino-américain qui place au cœur de la foi l’engagement aux côtés des pauvres et contre l’injustice.</t>
+          <t xml:space="preserve">renaissance de la philosophie dans l’Iran chiite des Safavides, dont Molla Sadra est le sommet avec sa « sagesse transcendante ».</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie et spiritualité;Philosophie politique</t>
+          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
         </is>
       </c>
       <c r="L98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gustavo GUTIÉRREZ;Leonardo BOFF;Enrique DUSSEL;Paulo FREIRE</t>
+          <t xml:space="preserve">Molla SADRA;MIR DAMAD;Allameh TABATABAÏ</t>
         </is>
       </c>
       <c r="M98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N98"/>
       <c r="O98" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6940,52 +7019,52 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologies et philosophies de la libération</t>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marxisme</t>
+          <t xml:space="preserve">Ishraqisme;Soufisme</t>
         </is>
       </c>
     </row>
     <row r="99" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1">
-        <v>1971</v>
+        <v>1878</v>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971</t>
+          <t xml:space="preserve">1878</t>
         </is>
       </c>
       <c r="D99" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie de la libération</t>
+          <t xml:space="preserve">Sophiologie</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;La philosophie de la libération&lt;/a&gt; est un mouvement philosophique latino-américain apparu au début des années 1970, en Argentine surtout, autour du congrès national de philosophie de Córdoba en 1971. Il veut faire de la philosophie un instrument d’émancipation pour les peuples d’Amérique latine, dominés économiquement et culturellement, en écho à la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt; des économistes.&lt;/p&gt; &lt;p&gt;Il naît d’un débat. En 1968, le Péruvien Augusto Salazar Bondy demande « Existe-t-il une philosophie de notre Amérique ? » et répond qu’une culture dépendante ne peut produire qu’une pensée imitée, inauthentique, tant que dure la domination. Le Mexicain Leopoldo Zea lui répond que la pensée latino-américaine est déjà une philosophie à part entière, qui réfléchit sur sa propre histoire. L’Argentin Enrique Dussel en devient la figure majeure. S’inspirant d’&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Levinas" title=" Wikipedia"&gt;Emmanuel Levinas&lt;/a&gt;, il fait de l’Autre, le pauvre, l’Indien, le colonisé, la femme, le point de départ de l’éthique : la philosophie doit écouter la parole de celui que le système exclut. Pour lui, la modernité ne commence pas avec le « je pense » de Descartes, mais en 1492, avec le « je conquiers » des conquistadors. Rodolfo Kusch, de son côté, cherche dans la pensée des peuples andins une autre manière d’être au monde, celle de l’« être là » plutôt que de l’« être quelqu’un ».&lt;/p&gt; &lt;p&gt;Persécutés par la dictature militaire, Dussel et plusieurs autres partent en exil en 1975. Le mouvement a nourri la théologie de la libération, puis la pensée décoloniale, et reste une référence des philosophies du Sud.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sophiologie" title=" Wikipedia"&gt;La sophiologie&lt;/a&gt; est un courant de la philosophie religieuse russe, né à la fin du XIXe siècle, qui fait de la &lt;a href="https://fr.wikipedia.org/wiki/Sophia_%28philosophie%29" title=" Wikipedia"&gt;Sagesse divine&lt;/a&gt;, Sophia, le cœur de sa réflexion. Elle reprend une figure de la Bible, où la Sagesse est présentée comme la compagne de Dieu lors de la création, et une longue tradition mystique, du platonisme à Jacob Boehme. Son fondateur est Vladimir Soloviev, qui raconte avoir eu trois visions de Sophia, la dernière dans le désert d’Égypte, en 1875.&lt;/p&gt; &lt;p&gt;Dans ses &lt;em&gt;Leçons sur la divino-humanité&lt;/em&gt; (1878), Soloviev décrit Sophia comme l’âme du monde, l’unité idéale de toutes les créatures en Dieu : elle est le lien entre le Créateur et la création, ce par quoi le monde n’est pas étranger à Dieu. L’histoire a pour sens la réunion progressive de l’humanité et du divin, dont le Christ, Dieu fait homme, est le modèle. Le prêtre et savant Pavel Florensky reprend cette intuition dans &lt;em&gt;La Colonne et le Fondement de la vérité&lt;/em&gt; (1914), en y mêlant mathématiques, théologie et histoire de l’art. Mais c’est Sergueï Boulgakov, économiste marxiste devenu prêtre orthodoxe, qui en fait un vaste système théologique dans son exil parisien, à l’&lt;a href="https://fr.wikipedia.org/wiki/Institut_Saint-Serge" title=" Wikipedia"&gt;Institut Saint-Serge&lt;/a&gt; : la Sagesse est la nature même de Dieu, qui se révèle dans le monde créé, si bien que la création tout entière est appelée à être transfigurée.&lt;/p&gt; &lt;p&gt;En 1935, l’Église orthodoxe russe condamne les thèses de Boulgakov, et les théologiens Vladimir Lossky et Georges Florovsky les critiquent sévèrement. La sophiologie a pourtant marqué les poètes symbolistes, comme Alexandre Blok et Andreï Biély, et elle inspire aujourd’hui une théologie de la création attentive à l’écologie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophie latino-américaine qui pense à partir des peuples dominés et dénonce la dépendance culturelle envers l’Europe.</t>
+          <t xml:space="preserve">philosophie religieuse russe de la Sagesse divine, Sophia, qui unit Dieu et le monde : Soloviev, Florensky, Boulgakov.</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Éthique;Philosophie politique</t>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
         </is>
       </c>
       <c r="L99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enrique DUSSEL;Augusto SALAZAR BONDY;Leopoldo ZEA-AGUILAR</t>
+          <t xml:space="preserve">Vladimir SOLOVIEV;Sergueï BOULGAKOV;Pavel FLORENSKY</t>
         </is>
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sud</t>
+          <t xml:space="preserve">russe</t>
         </is>
       </c>
       <c r="N99"/>
@@ -6996,47 +7075,47 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologies et philosophies de la libération</t>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Théologie de la libération</t>
+          <t xml:space="preserve">Slavophilisme;Néoplatonisme</t>
         </is>
       </c>
     </row>
     <row r="100" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1">
-        <v>1981</v>
+        <v>1960</v>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981</t>
+          <t xml:space="preserve">1960</t>
         </is>
       </c>
       <c r="D100" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Créolisation</t>
+          <t xml:space="preserve">Socialisme africain</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;La &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olisation_%28concept%29" title=" Wikipedia"&gt;créolisation&lt;/a&gt; est un courant de pensée né aux Antilles autour de l’œuvre d’Édouard Glissant. Le mot désigne d’abord la naissance des langues et des cultures créoles dans les sociétés de plantation des Caraïbes, où des peuples arrachés à l’Afrique, des colons européens, des Amérindiens et plus tard des travailleurs venus d’Inde ont dû inventer ensemble un monde nouveau. Glissant en fait un concept philosophique pour penser le monde entier.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Discours_antillais" title=" Wikipedia"&gt;&lt;em&gt;Le Discours antillais&lt;/em&gt;&lt;/a&gt; (1981), il développe d’abord l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : l’identité des Antilles ne se trouve ni dans un retour à l’Afrique, comme le voulait la Négritude, ni dans l’imitation de la France, mais dans l’archipel caribéen lui-même. Avec la créolisation, il montre que la rencontre des cultures ne produit pas un simple mélange prévisible, mais de l’inédit. Reprenant une image de Deleuze et Guattari, il oppose l’« identité-racine », unique, qui exclut l’autre, à l’« identité-rhizome », qui se construit dans la relation. Dans &lt;em&gt;Poétique de la Relation&lt;/em&gt; (1990), il défend le « droit à l’opacité » : comprendre l’autre ne signifie pas le réduire à soi. Il appelle &lt;a href="https://fr.wikipedia.org/wiki/Tout-monde" title=" Wikipedia"&gt;« Tout-Monde »&lt;/a&gt; ce monde où toutes les cultures sont désormais en contact, pour le meilleur et pour le pire, et où nul ne peut plus vivre à l’écart des autres.&lt;/p&gt; &lt;p&gt;En 1989, les écrivains martiniquais Jean Bernabé, &lt;a href="https://fr.wikipedia.org/wiki/Patrick_Chamoiseau" title=" Wikipedia"&gt;Patrick Chamoiseau&lt;/a&gt; et Raphaël Confiant prolongent ce mouvement dans leur &lt;em&gt;Éloge de la &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olit%C3%A9" title=" Wikipedia"&gt;créolité&lt;/a&gt;&lt;/em&gt;. La pensée de Glissant est aujourd’hui l’une des grandes références de la réflexion sur la mondialisation et les identités.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;On appelle &lt;a href="https://fr.wikipedia.org/wiki/Socialisme_africain" title=" Wikipedia"&gt;socialisme africain&lt;/a&gt; l’ensemble des doctrines par lesquelles plusieurs dirigeants des indépendances africaines, autour de 1960, ont voulu définir une voie propre de développement, distincte à la fois du capitalisme des anciennes puissances coloniales et du communisme soviétique.&lt;/p&gt; &lt;p&gt;Leur idée commune est que l’Afrique n’a pas besoin d’importer le socialisme, car elle le porte déjà dans ses traditions : la solidarité de la famille élargie et du village, la propriété commune de la terre, le partage des biens. Il ne s’agit donc pas de mener une lutte des classes, que les sociétés africaines n’auraient pas connue, mais de moderniser ces solidarités. Au Sénégal, Léopold Sédar Senghor défend un socialisme humaniste et spirituel, nourri de la Négritude et de la pensée de Teilhard de Chardin, qui refuse l’athéisme marxiste. Au Ghana, Kwame Nkrumah, plus proche du marxisme, cherche dans son « consciencisme » une synthèse entre la tradition africaine, l’islam et le christianisme. En Tanzanie, Julius Nyerere en donne la version la plus élaborée avec l’&lt;a href="https://fr.wikipedia.org/wiki/Ujamaa" title=" Wikipedia"&gt;&lt;em&gt;ujamaa&lt;/em&gt;&lt;/a&gt;, mot swahili qui signifie « esprit de famille » : la nation doit vivre comme une grande famille où chacun travaille et où personne n’exploite personne. La &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9claration_d%27Arusha" title=" Wikipedia"&gt;déclaration d’Arusha&lt;/a&gt; (1967) en fait le programme du pays.&lt;/p&gt; &lt;p&gt;Dans les faits, ces politiques ont souvent abouti à des partis uniques et, en Tanzanie, au regroupement forcé des paysans dans des villages collectifs, qui fut un échec économique, reconnu par Nyerere lui-même. Elles restent pourtant une tentative originale de penser le développement à partir des valeurs africaines.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pensée antillaise de Glissant : les cultures en contact créent de l’imprévisible ; à l’identité-racine s’oppose l’identité-relation.</t>
+          <t xml:space="preserve">socialisme des indépendances fondé sur les solidarités communautaires africaines plutôt que sur la lutte des classes.</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métaphysique;Philosophie politique</t>
+          <t xml:space="preserve">Philosophie politique;Éthique</t>
         </is>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Édouard GLISSANT</t>
+          <t xml:space="preserve">Julius NYERERE;Léopold Sédar SENGHOR;Kwame NKRUMAH</t>
         </is>
       </c>
       <c r="M100" s="1" t="inlineStr">
@@ -7052,47 +7131,47 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
+          <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Négritude</t>
+          <t xml:space="preserve">Pan-africanisme;Marxisme</t>
         </is>
       </c>
     </row>
     <row r="101" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1">
-        <v>1992</v>
+        <v>1968</v>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1992</t>
+          <t xml:space="preserve">1968</t>
         </is>
       </c>
       <c r="D101" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée décoloniale</t>
+          <t xml:space="preserve">Théologie de la libération</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;La pensée décoloniale, ou &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;études décoloniales&lt;/a&gt;, est un courant né en Amérique latine dans les années 1990. Son point de départ est un article de 1992 du sociologue péruvien &lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal Quijano&lt;/a&gt;, qui forge la notion de « colonialité du pouvoir » : le colonialisme, comme domination politique directe, a pris fin, mais la colonialité, elle, a survécu.&lt;/p&gt; &lt;p&gt;Pour ces penseurs, la modernité européenne et la colonisation des Amériques, à partir de 1492, sont les deux faces d’un même processus. La colonisation a installé une hiérarchie des êtres humains fondée sur la race, une division du travail mondiale et une hiérarchie des savoirs, qui présente la science et la philosophie européennes comme universelles et relègue les autres savoirs au rang de croyances ou de folklore. Cette colonialité continue d’organiser le monde après les indépendances. Le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt;, qui réunit autour de Quijano l’Argentin &lt;a href="https://fr.wikipedia.org/wiki/Walter_Mignolo" title=" Wikipedia"&gt;Walter Mignolo&lt;/a&gt;, Enrique Dussel et d’autres, appelle à une « désobéissance épistémique » : penser à partir des expériences et des savoirs des peuples colonisés, pour un monde où plusieurs mondes seraient possibles. Sylvia Wynter et Lewis Gordon prolongent cette réflexion dans la Caraïbe et chez les Afro-Américains.&lt;/p&gt; &lt;p&gt;Le courant se distingue des études postcoloniales anglophones d’Edward Saïd ou de &lt;a href="https://fr.wikipedia.org/wiki/Gayatri_Chakravorty_Spivak" title=" Wikipedia"&gt;Gayatri Spivak&lt;/a&gt;, nées de la critique littéraire et centrées sur l’Asie et le Moyen-Orient. Il suscite aussi des critiques, y compris en Amérique latine, où Silvia Rivera Cusicanqui lui reproche d’être devenu une mode universitaire du Nord.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;La théologie de la libération&lt;/a&gt; est un courant de pensée chrétien, surtout catholique, né en Amérique latine à la fin des années 1960, dans un continent marqué par la misère, les inégalités et les dictatures. Elle s’appuie sur le renouveau du concile Vatican II et sur la &lt;a href="https://fr.wikipedia.org/wiki/Conf%C3%A9rence_de_Medell%C3%ADn" title=" Wikipedia"&gt;conférence des évêques latino-américains de Medellín&lt;/a&gt;, en 1968, qui dénonce la « violence institutionnalisée » de l’injustice sociale.&lt;/p&gt; &lt;p&gt;Son texte fondateur est &lt;em&gt;Théologie de la libération&lt;/em&gt; (1971) du prêtre péruvien &lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo Gutiérrez&lt;/a&gt;. La théologie n’y est plus seulement une réflexion abstraite sur Dieu, mais une « réflexion critique sur la pratique » : elle part de la situation concrète des pauvres et de leur lutte pour leur dignité. Dieu prend parti pour les opprimés, comme il a libéré Israël de l’esclavage en Égypte ; le salut ne concerne pas seulement l’au-delà, il commence par la libération de toutes les servitudes. D’où l’« option préférentielle pour les pauvres ». Pour comprendre les causes de la pauvreté, ces théologiens utilisent les sciences sociales, y compris l’analyse marxiste. La foi se vit dans les &lt;a href="https://fr.wikipedia.org/wiki/Communaut%C3%A9_eccl%C3%A9siale_de_base" title=" Wikipedia"&gt;communautés ecclésiales de base&lt;/a&gt;, où les pauvres lisent eux-mêmes la Bible à la lumière de leur vie. Le Brésilien Leonardo Boff, le jésuite Ignacio Ellacuría, assassiné au Salvador en 1989, et les réflexions de Paulo Freire et d’Enrique Dussel lui sont proches.&lt;/p&gt; &lt;p&gt;Rome, sous Jean-Paul II, critique dans les années 1980 son usage du marxisme et impose le silence à Boff. Sa reconnaissance vient avec le pape François, et l’option pour les pauvres est aujourd’hui reprise par toute l’Église catholique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">courant latino-américain pour qui la colonialité du pouvoir et du savoir a survécu à la fin des colonies.</t>
+          <t xml:space="preserve">courant chrétien latino-américain qui place au cœur de la foi l’engagement aux côtés des pauvres et contre l’injustice.</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie politique;Épistémologie</t>
+          <t xml:space="preserve">Théologie et spiritualité;Philosophie politique</t>
         </is>
       </c>
       <c r="L101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aníbal QUIJANO;Walter MIGNOLO;Enrique DUSSEL;Sylvia WYNTER</t>
+          <t xml:space="preserve">Gustavo GUTIÉRREZ;Leonardo BOFF;Enrique DUSSEL;Paulo FREIRE</t>
         </is>
       </c>
       <c r="M101" s="1" t="inlineStr">
@@ -7100,7 +7179,11 @@
           <t xml:space="preserve">sud</t>
         </is>
       </c>
-      <c r="N101"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -7108,52 +7191,52 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
+          <t xml:space="preserve">Théologies et philosophies de la libération</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie de la libération;Anticolonialisme</t>
+          <t xml:space="preserve">Marxisme</t>
         </is>
       </c>
     </row>
     <row r="102" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1">
-        <v>-300</v>
+        <v>1971</v>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">-300</t>
+          <t xml:space="preserve">1971</t>
         </is>
       </c>
       <c r="D102" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">École du Yin-Yang</t>
+          <t xml:space="preserve">Philosophie de la libération</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_du_Yin-Yang" title=" Wikipedia"&gt;L’école du Yin-Yang&lt;/a&gt; est l’un des grands courants de la pensée chinoise de l’Antiquité, né à la fin de la période des Royaumes combattants, au IVe et au IIIe siècle avant notre ère. Son maître est &lt;a href="https://fr.wikipedia.org/wiki/Zou_Yan" title=" Wikipedia"&gt;Zou Yan&lt;/a&gt;, savant de l’État de Qi, dont les œuvres sont perdues, mais que l’historien Sima Qian présente comme l’un des penseurs les plus écoutés de son temps par les princes.&lt;/p&gt; &lt;p&gt;Elle explique toute la réalité par deux principes complémentaires, le &lt;a href="https://fr.wikipedia.org/wiki/Yin_et_yang" title=" Wikipedia"&gt;yin et le yang&lt;/a&gt; : le sombre et le lumineux, le froid et le chaud, le repos et le mouvement, le féminin et le masculin. Aucun n’existe sans l’autre, chacun contient le germe de son contraire et le monde naît de leur alternance, comme le jour succède à la nuit. Zou Yan y joint la théorie des &lt;a href="https://fr.wikipedia.org/wiki/Wuxing_%28cosmologie%29" title=" Wikipedia"&gt;cinq phases&lt;/a&gt; ou cinq éléments, le bois, le feu, la terre, le métal et l’eau, qui s’engendrent et se dominent les uns les autres selon des cycles réguliers. Il en tire une philosophie de l’histoire : chaque dynastie règne sous le signe d’une phase et sera remplacée par celle qui la domine. Le premier empereur de Chine, Qin Shi Huangdi, place ainsi son règne sous le signe de l’eau. L’école décrit aussi la géographie du monde, qui compterait neuf grands continents, dont la Chine ne serait qu’une partie.&lt;/p&gt; &lt;p&gt;Elle disparaît comme école indépendante sous les Han, mais ses idées se fondent dans toute la culture chinoise. Dong Zhongshu les intègre au confucianisme officiel, en faisant correspondre l’ordre du ciel et celui de la société. Elles fondent aussi la médecine chinoise, l’astrologie, la géomancie et la lecture du &lt;em&gt;Yijing&lt;/em&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;La philosophie de la libération&lt;/a&gt; est un mouvement philosophique latino-américain apparu au début des années 1970, en Argentine surtout, autour du congrès national de philosophie de Córdoba en 1971. Il veut faire de la philosophie un instrument d’émancipation pour les peuples d’Amérique latine, dominés économiquement et culturellement, en écho à la &lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9orie_de_la_d%C3%A9pendance" title=" Wikipedia"&gt;théorie de la dépendance&lt;/a&gt; des économistes.&lt;/p&gt; &lt;p&gt;Il naît d’un débat. En 1968, le Péruvien Augusto Salazar Bondy demande « Existe-t-il une philosophie de notre Amérique ? » et répond qu’une culture dépendante ne peut produire qu’une pensée imitée, inauthentique, tant que dure la domination. Le Mexicain Leopoldo Zea lui répond que la pensée latino-américaine est déjà une philosophie à part entière, qui réfléchit sur sa propre histoire. L’Argentin Enrique Dussel en devient la figure majeure. S’inspirant d’&lt;a href="https://fr.wikipedia.org/wiki/Emmanuel_Levinas" title=" Wikipedia"&gt;Emmanuel Levinas&lt;/a&gt;, il fait de l’Autre, le pauvre, l’Indien, le colonisé, la femme, le point de départ de l’éthique : la philosophie doit écouter la parole de celui que le système exclut. Pour lui, la modernité ne commence pas avec le « je pense » de Descartes, mais en 1492, avec le « je conquiers » des conquistadors. Rodolfo Kusch, de son côté, cherche dans la pensée des peuples andins une autre manière d’être au monde, celle de l’« être là » plutôt que de l’« être quelqu’un ».&lt;/p&gt; &lt;p&gt;Persécutés par la dictature militaire, Dussel et plusieurs autres partent en exil en 1975. Le mouvement a nourri la théologie de la libération, puis la pensée décoloniale, et reste une référence des philosophies du Sud.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">école chinoise de Zou Yan qui explique la nature et l’histoire par le yin et le yang et les cinq phases.</t>
+          <t xml:space="preserve">philosophie latino-américaine qui pense à partir des peuples dominés et dénonce la dépendance culturelle envers l’Europe.</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métaphysique;Philosophie des sciences et du vivant</t>
+          <t xml:space="preserve">Éthique;Philosophie politique</t>
         </is>
       </c>
       <c r="L102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zou YAN;Dong ZHONGSHU</t>
+          <t xml:space="preserve">Enrique DUSSEL;Augusto SALAZAR BONDY;Leopoldo ZEA-AGUILAR</t>
         </is>
       </c>
       <c r="M102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">asie-est</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="N102"/>
@@ -7164,47 +7247,52 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+          <t xml:space="preserve">Théologies et philosophies de la libération</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de la libération</t>
         </is>
       </c>
     </row>
     <row r="103" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1">
-        <v>240</v>
+        <v>1992</v>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">240</t>
+          <t xml:space="preserve">1992</t>
         </is>
       </c>
       <c r="D103" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xuanxue</t>
+          <t xml:space="preserve">Pensée décoloniale</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;Le &lt;a href="https://fr.wikipedia.org/wiki/Xuanxue" title=" Wikipedia"&gt;Xuanxue&lt;/a&gt;, « étude du mystère », parfois appelé néotaoïsme, est un grand courant de la philosophie chinoise des IIIe et IVe siècles, né après la chute de la dynastie Han, dans une période de guerres et de désordres où le confucianisme officiel a perdu son crédit. Les lettrés se tournent alors vers les « trois livres du mystère » : le &lt;em&gt;Laozi&lt;/em&gt;, le &lt;em&gt;Zhuangzi&lt;/em&gt; et le &lt;em&gt;Yijing&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Le jeune Wang Bi, mort à vingt-trois ans, en est le génie. Dans ses commentaires du &lt;em&gt;Laozi&lt;/em&gt; et du &lt;em&gt;Yijing&lt;/em&gt;, il affirme que toutes les choses ont pour fondement le « non-être » (&lt;em&gt;wu&lt;/em&gt;), réalité sans forme ni nom, que l’on ne peut pas dire mais d’où tout procède. Le sage n’est pas celui qui en parle le plus, mais celui qui l’incarne : c’est pourquoi Confucius, qui n’en parlait jamais, était plus sage que Laozi. Un demi-siècle plus tard, &lt;a href="https://fr.wikipedia.org/wiki/Guo_Xiang" title=" Wikipedia"&gt;Guo Xiang&lt;/a&gt;, éditeur et commentateur du &lt;em&gt;Zhuangzi&lt;/em&gt;, soutient au contraire que le non-être n’est rien et ne peut rien produire : chaque chose « advient d’elle-même », spontanément, sans créateur ni cause extérieure, et trouve son bonheur à suivre sa propre nature. Ces débats se poursuivent dans les « &lt;a href="https://fr.wikipedia.org/wiki/Qingtan" title=" Wikipedia"&gt;pures conversations&lt;/a&gt; », joutes philosophiques raffinées de l’aristocratie.&lt;/p&gt; &lt;p&gt;Les &lt;a href="https://fr.wikipedia.org/wiki/Sept_Sages_de_la_for%C3%AAt_de_bambous" title=" Wikipedia"&gt;Sept Sages de la forêt de bambous&lt;/a&gt;, poètes et musiciens comme Ji Kang et Ruan Ji, en vivent l’idéal de liberté, en marge des rites et des honneurs. Le Xuanxue prépare surtout l’accueil du bouddhisme en Chine : les premiers traducteurs expriment la vacuité bouddhique dans son vocabulaire du non-être.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;La pensée décoloniale, ou &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;études décoloniales&lt;/a&gt;, est un courant né en Amérique latine dans les années 1990. Son point de départ est un article de 1992 du sociologue péruvien &lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal Quijano&lt;/a&gt;, qui forge la notion de « colonialité du pouvoir » : le colonialisme, comme domination politique directe, a pris fin, mais la colonialité, elle, a survécu.&lt;/p&gt; &lt;p&gt;Pour ces penseurs, la modernité européenne et la colonisation des Amériques, à partir de 1492, sont les deux faces d’un même processus. La colonisation a installé une hiérarchie des êtres humains fondée sur la race, une division du travail mondiale et une hiérarchie des savoirs, qui présente la science et la philosophie européennes comme universelles et relègue les autres savoirs au rang de croyances ou de folklore. Cette colonialité continue d’organiser le monde après les indépendances. Le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt;, qui réunit autour de Quijano l’Argentin &lt;a href="https://fr.wikipedia.org/wiki/Walter_Mignolo" title=" Wikipedia"&gt;Walter Mignolo&lt;/a&gt;, Enrique Dussel et d’autres, appelle à une « désobéissance épistémique » : penser à partir des expériences et des savoirs des peuples colonisés, pour un monde où plusieurs mondes seraient possibles. Sylvia Wynter et Lewis Gordon prolongent cette réflexion dans la Caraïbe et chez les Afro-Américains.&lt;/p&gt; &lt;p&gt;Le courant se distingue des études postcoloniales anglophones d’Edward Saïd ou de &lt;a href="https://fr.wikipedia.org/wiki/Gayatri_Chakravorty_Spivak" title=" Wikipedia"&gt;Gayatri Spivak&lt;/a&gt;, nées de la critique littéraire et centrées sur l’Asie et le Moyen-Orient. Il suscite aussi des critiques, y compris en Amérique latine, où Silvia Rivera Cusicanqui lui reproche d’être devenu une mode universitaire du Nord.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">« étude du mystère » : renouveau taoïste des IIIe et IVe siècles chinois, autour de Wang Bi et de Guo Xiang.</t>
+          <t xml:space="preserve">courant latino-américain pour qui la colonialité du pouvoir et du savoir a survécu à la fin des colonies.</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Métaphysique;Théologie et spiritualité</t>
+          <t xml:space="preserve">Philosophie politique;Épistémologie</t>
         </is>
       </c>
       <c r="L103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wang BI;Guo XIANG;Ji KANG</t>
+          <t xml:space="preserve">Aníbal QUIJANO;Walter MIGNOLO;Enrique DUSSEL;Sylvia WYNTER</t>
         </is>
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">asie-est</t>
+          <t xml:space="preserve">sud</t>
         </is>
       </c>
       <c r="N103"/>
@@ -7215,12 +7303,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme;Confucianisme</t>
+          <t xml:space="preserve">Philosophie de la libération;Anticolonialisme</t>
         </is>
       </c>
     </row>
@@ -7230,29 +7318,29 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines&quot;  title=&quot; Wikipedia&quot;&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les traditions philosophiques et spirituelles des civilisations précolombiennes d'Amérique centrale, en particulier les Aztèques, les Mayas et les Toltèques. Ces pensées forment un univers conceptuel original, structuré autour de la relation entre l'homme, le cosmos et les forces divines.&lt;/p&gt;&lt;p&gt;Au cœur de ces traditions se trouve la notion de &lt;em&gt;teotl&lt;/em&gt; (divinité, énergie sacrée) chez les Aztèques, ou de &lt;em&gt;k'ul&lt;/em&gt; (force vitale sacrée) chez les Mayas. La cosmologie mésoaméricaine conçoit l'univers comme un système de cycles temporels, où les dieux et les hommes sont liés par des obligations réciproques. Le sacrifice rituel, loin d'être une simple pratique violente, est pensé comme une nécessité cosmique pour maintenir l'équilibre du monde.&lt;/p&gt;&lt;p&gt;Des figures comme Quetzalcóatl (le Serpent à plumes) incarnent une sagesse éthique et philosophique : tempérance, connaissance, opposition au sacrifice humain selon certaines traditions. Les philosophes aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s'interrogeaient sur la nature du vrai, du beau, du bien, et sur la condition humaine — une tradition philosophique autonome redécouverte par des chercheurs comme Miguel León-Portilla.&lt;/p&gt;"/>
-    <hyperlink ref="E13" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9sychasme&quot; title=&quot; Wikipedia&quot;&gt;L'Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme oriental, dont le nom vient du grec &lt;em&gt;hésychia&lt;/em&gt; (silence, tranquillité). Il désigne une pratique spirituelle visant à atteindre l'union avec Dieu par la prière continue, le silence intérieur et la maîtrise du souffle.&lt;/p&gt;&lt;p&gt;Ses origines remontent aux Pères du désert des IVe-Ve siècles, mais c'est au XIVe siècle que l'hésychasme devient un courant théologique et philosophique structuré, notamment grâce à Grégoire Palamas, archevêque de Thessalonique, qui en formule la doctrine dans ses &lt;em&gt;Triades&lt;/em&gt;. Palamas distingue l'essence divine (inaccessible) des énergies divines (accessibles à l'expérience mystique), permettant de fonder théologiquement la possibilité d'une véritable union de l'homme avec Dieu.&lt;/p&gt;&lt;p&gt;Cette distinction essence-énergies est l'une des contributions philosophiques les plus originales de la pensée byzantine. L'hésychasme a profondément marqué la spiritualité orthodoxe russe, grecque et serbe, et continue d'irriguer la théologie et la philosophie orthodoxes contemporaines.&lt;/p&gt;"/>
-    <hyperlink ref="E15" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka&quot;  title=&quot;Wikipedia&quot;&gt;Le Lokayata&lt;/a&gt;, également connu sous le nom de Carvaka, est la seule école philosophique de l'Inde ancienne à avoir défendu un matérialisme radical et un athéisme déclaré. Fondée vers le VIe siècle avant notre ère, elle rejette tout ce qui ne peut être appréhendé par les sens : pas d'âme immortelle, pas d'au-delà, pas de loi karmique.&lt;/p&gt;&lt;p&gt;Sa devise pourrait se résumer ainsi : ce que l'on voit existe ; ce que l'on ne peut percevoir n'est qu'invention. Les Carvakas refusent les Védas et leur autorité, les rituels brahmaniques, et toute forme de spéculation métaphysique. L'univers est composé des quatre éléments — terre, eau, feu et air — sans qu'intervienne aucune divinité créatrice.&lt;/p&gt;&lt;p&gt;En matière d'éthique, la philosophie Carvaka est franchement hédoniste : le plaisir est le seul bien réel, la souffrance le seul mal. Mieux vaut jouir de la vie maintenant plutôt qu'espérer une récompense illusoire après la mort. Ce réalisme sans concession en fait une voix singulière, souvent persécutée, de la pensée indienne classique.&lt;/p&gt;&lt;p&gt;Bien que ses textes originaux aient presque tous disparu — connus surtout par les réfutations de ses adversaires — son influence demeure dans les courants matérialistes et rationalistes qui traversent la philosophie indienne jusqu'à aujourd'hui.&lt;/p&gt;"/>
-    <hyperlink ref="E20" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra&quot; title=&quot; Wikipedia&quot;&gt; Le Yoga&lt;/a&gt; en tant qu’école philosophique (darshana) est distinct de la pratique physique popularisée en Occident. Systématisé par Patanjali dans les Yoga Sutra (entre 200 av. J.-C. et 500 apr. J.-C.), il partage la métaphysique dualiste du Samkhya — Purusha (conscience) et Prakriti (matière) — mais y ajoute une méthode pratique précise pour la libération.&lt;/p&gt;&lt;p&gt;Les huit membres (ashtanga) du Yoga structurent ce chemin : discipline éthique (yama, niyama), posture (asana), maîtrise du souffle (pranayama), retrait des sens (pratyahara), concentration (dharana), méditation (dhyana) et absorption (samadhi). Chaque étape prépare la suivante dans une progression méthodique vers l’arrêt des fluctuations du mental (chitta vritti nirodha).&lt;/p&gt;&lt;p&gt;Contrairement au Samkhya, purement théorique, le Yoga de Patanjali introduit îshvara (un principe divin, seigneur particulier parmi les âmes) comme objet de concentration facultatif — une nuance théiste absente du Samkhya classique. Cette différence a nourri des siècles de commentaires et de débats entre les deux écoles sœurs.&lt;/p&gt;&lt;p&gt;Aujourd’hui mondialement diffusée, la dimension physique du yoga occulte souvent sa profondeur philosophique originelle : une discipline rigoureuse de la conscience, visant non le bien-être mais la discrimination (viveka) entre le Soi éternel et les fluctuations passagères du mental.&lt;/p&gt;"/>
-    <hyperlink ref="E22" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme&quot;  title=&quot; Wikipedia&quot;&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt;    &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title=&quot;Le Taoïsme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E26" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/École_des_Noms&quot;  title=&quot;Wikipedia&quot;&gt;L'École des Noms&lt;/a&gt; (ming jia, 名家) est une école de philosophie chinoise qui s'est développée pendant la période des Royaumes combattants. Sa préoccupation centrale : la relation entre les mots et les choses, entre les noms et la réalité qu'ils désignent.&lt;/p&gt;&lt;p&gt;Ses représentants les plus célèbres, Gongsun Long et Hui Shi, sont connus pour leurs paradoxes vertigineux. Gongsun Long affirmait que &quot;le cheval blanc n'est pas un cheval&quot; — non par provocation, mais pour distinguer le concept général (cheval) du particulier concret (ce cheval blanc). Hui Shi proclamait que &quot;le ciel et la terre sont d'une même hauteur&quot;, explorant les limites relatives de toute catégorisation.&lt;/p&gt;&lt;p&gt;Ces réflexions sur le langage anticipent certaines problématiques de la logique et de la philosophie analytique moderne. Comment les mots nous permettent-ils — ou nous empêchent-ils — de saisir la réalité ? Toute classification n'implique-t-elle pas une distorsion du monde ?&lt;/p&gt;&lt;p&gt;Peu influente politiquement, l'École des Noms fut souvent moquée par ses contemporains confu céens et taoïstes. Mais elle constitue une contribution unique à la logique asiatique et à la philosophie du langage dans la pensée mondiale.&lt;/p&gt;"/>
-    <hyperlink ref="E27" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A2mkhya&quot;  title=&quot; Wikipedia&quot;&gt;Le Sâmkhya&lt;/a&gt; est l'une des plus anciennes écoles philosophiques de l'Inde, considérée comme un darshana orthodoxe de l'hindouisme. Il propose une analyse rationnelle de la réalité pour libérer l'individu du cycle des renaissances et de la souffrance. Ce système dualiste distingue deux réalités ultimes : Purusha, la conscience pure et passive (esprit, principe masculin), et Prakriti, la matière primordiale active (énergie universelle, principe féminin). Prakriti évolue sous l'influence des trois guṇas (sattva : harmonie ; rajas : activité ; tamas : inertie), générant le monde manifesté à travers 23 tattvas (principes), comme buddhi (intelligence), ahaṃkāra (ego) et les sens. &lt;/p&gt; &lt;p&gt; Il explique la création comme une transformation de Prakriti, sans recours à un dieu créateur : de l'état non manifesté (avyakta) naît le manifesté (vyakta), incluant le corps subtil qui transmigre. L'ignorance (avidyā) cause l'identification erronée du Purusha à la matière, source de souffrance (duḥkha). &lt;/p&gt; &lt;p&gt; Fondement théorique du Yoga de Patañjali, le Sâmkhya met l'accent sur la discrimination (viveka) entre Purusha et Prakriti pour atteindre la libération (kaivalya). Il influence largement la philosophie indienne, des Puranas au Vedānta. &lt;/p&gt;"/>
-    <hyperlink ref="E29" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Therav%C4%81da&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Theravada&lt;/a&gt; (« École des Anciens ») est la plus ancienne forme du bouddhisme conservée jusqu'à nos jours. Héritière directe des enseignements du Bouddha historique, elle s'enracina progressivement en Asie du Sud-Est : Sri Lanka, Thaïlande, Myanmar, Cambodge, Laos.&lt;/p&gt;&lt;p&gt;Au cœur du Theravada se trouve le Pali Canon (Tipitaka), le corpus scripturaire le plus ancien du bouddhisme. Sa philosophie insiste sur la voie individuelle vers l'éveil : chaque être doit parcourir lui-même le Noble Sentier Octuple — juste compréhension, juste intention, juste parole, juste action, juste mode de vie, juste effort, juste attention, juste concentration.&lt;/p&gt;&lt;p&gt;L'idéal du Theravada est l'Arhat : le sage qui, par sa propre pratique, a éteint les &quot;feux&quot; de l'attachement, de la haine et de l'illusion, et atteint le Nirvana. Cette voie solitaire et rigoureuse contraste avec l'idéal du bodhisattva du Mahayana, qui renonce à son propre éveil pour sauver tous les êtres.&lt;/p&gt;&lt;p&gt;La méditation de pleine conscience (sati), aujourd'hui mondialement répandue, trouve ses racines dans les pratiques contemplatives du Theravada, notamment la méditation vipassana qui vise à observer directement l'impermanence, la souffrance et l'absence de soi.&lt;/p&gt;"/>
-    <hyperlink ref="E31" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vaisheshika&quot;  title=&quot; Wikipedia&quot;&gt;Le Vaisheshika&lt;/a&gt;  est une école philosophique orthodoxe hindoue, fondée par le sage Kaṇāda, qui se distingue par son atomisme et son réalisme ontologique. Exposée dans les Vaiśeṣika Sūtra (non antérieurs à l'ère chrétienne), elle vise la libération (mokṣa) par la connaissance des catégories fondamentales de la réalité. Le système repose sur six ou sept padārthas (catégories) : dravya (substance), guṇa (qualité), karma (action/mouvement), sāmānya (universalité), viśeṣa (particularité) et samavāya (inhérence). Parmi les neuf substances, quatre sont atomiques (terre, eau, feu, air) : les paramāṇu (atomes éternels, indivisibles) s'assemblent en dyades puis en objets composites non éternels. &lt;/p&gt; &lt;p&gt; Sans dieu créateur direct, l'univers émerge de combinaisons atomiques influencées par une cause efficiente (adrisṭa, karma résiduel). Ākāśa (espace), kāla (temps), dik (direction) et cit (âme) complètent les substances ; les atomes sphériques se lient par forces intrinsèques, formant un monde discontinu mais perceptible. &lt;/p&gt; &lt;p&gt; Souvent fusionné avec le Nyâya (logique), il postule un Īśvara ordonnateur. La délivrance est un état pur de l'âme (sans qualités, conscience ou douleur), libérée des agrégats par la gnose discriminante. &lt;/p&gt;"/>
-    <hyperlink ref="E32" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_mah%C4%81y%C4%81na&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Mahayana&lt;/a&gt; (« Grand Véhicule ») est apparu en Inde au tournant de l'ère chrétienne, s'étendant progressivement vers la Chine, le Japon, la Corée et le Vietnam. Par rapport au Theravada, il représente une transformation profonde de la vision bouddhiste : l'éveil n'est plus un idéal solitaire mais une aspiration collective.&lt;/p&gt;&lt;p&gt;L'idéal central du Mahayana est le bodhisattva : l'être qui, sur le point d'atteindre le Nirvana, choisit de demeurer dans le cycle des renaissances (samsara) pour guider et libérer tous les êtres sensibles. Cette compassion universelle (karuna) devient le moteur de la voie spirituelle, indissociable de la sagesse (prajna).&lt;/p&gt;&lt;p&gt;Le Mahayana introduit également la notion révolutionnaire de sunyata (vacuité) : toutes choses sont dénues d'existence propre et intrinsèque — elles n'existent que de façon interdependante. Nagarjuna, au IIe siècle, en développa la philosophie dans ses Stances du Milieu, fondant l'école Madhyamaka qui influencça toute la pensée bouddhiste ultérieure.&lt;/p&gt;&lt;p&gt;C'est sur le sol du Mahayana que fleuriront le bouddhisme Zen, le bouddhisme tibétain Vajrayana, et l'École de la Terre Pure. Avec ses sutras nouveaux (Lotus, Vimalakirti, Prajnaparamita), le Mahayana offre une vision du monde d'une richesse philosophique et spirituelle sans équivalent.&lt;/p&gt;"/>
-    <hyperlink ref="E34" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mazdakisme&quot; title=&quot;Wikipedia&quot;&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse sous l’Empire sassanide. Fondé par le réformateur Mazdak, ce courant tire ses origines à la fois du mazdéisme et du manichéisme, en proposant une relecture dualiste du monde axée sur la lumière et les ténèbres. &lt;/p&gt; &lt;p&gt; Contrairement aux structures sociales hiérarchisées de l’époque, le mazdakisme prônait une égalité radicale entre les individus. Mazdak soutenait que les causes des conflits humains résidaient dans la soif de richesses et de pouvoir, ce qui l'a conduit à prôner la mise en commun des biens matériels et, selon certaines sources, des femmes. &lt;/p&gt; &lt;p&gt; Cette doctrine a été perçue comme une menace par l’aristocratie et le clergé zoroastrien traditionnel, qui y voyaient une hérésie dangereuse pour l'ordre établi. Après avoir initialement bénéficié de l'intérêt de l'empereur Kavadh Ier, le mouvement fut sévèrement réprimé lors de grandes purges organisées entre 524 et 529. &lt;/p&gt; &lt;p&gt; Bien que le mazdakisme ait été marginalisé après ces persécutions, il a laissé une trace durable dans la pensée iranienne. Parfois qualifié, de manière anachronique, de mouvement proto-socialiste, son idéal de justice sociale a influencé certains courants contestataires qui se sont manifestés en Iran jusqu'au XIVe siècle environ. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E36" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_vajrayana&quot;  title=&quot;Wikipedia&quot;&gt;Le Vajrayana&lt;/a&gt; (« Véhicule de Diamant ») est la troisième grande forme du bouddhisme, développée en Inde entre le VIIe et le Xe siècle, puis transmise au Tibet, en Mongolie et dans l'Himalaya. Il représente la voie tantrique du bouddhisme, utilisant des pratiques ésotériques pour accélérer le chemin vers l'éveil.&lt;/p&gt;&lt;p&gt;Là où le Theravada vise l'éveil en de nombreuses vies et le Mahayana en d'innombrables éons, le Vajrayana affirme qu'il est possible d'atteindre l'éveil en une seule vie — voire en un seul instant. Pour cela, il mobilise un arsenal de techniques : mantras, mandalas, mudras, visualisations de divinités, pratiques yogiques subtiles sur les énergies intérieures du corps.&lt;/p&gt;&lt;p&gt;Le Bouddhisme tibétain, la forme la plus répandue du Vajrayana, s'est développé dès le VIIe siècle sous le règne du roi Songtsen Gampo. Il intègre des éléments de la religion Bön préexistante et du Mahayana indien. Ses figures tutlaires — Padmasambhava, Milarepa, Tsongkhapa — sont au cœur d'une tradition d'une richesse philosophique et rituelle incomparable.&lt;/p&gt;&lt;p&gt;La notion de &quot;nature de bouddha&quot; (tathagatagarbha) — l'idée que chaque être possède en lui la graine de l'éveil — est centrale dans le Vajrayana. La pratique vise à reconnaître directement cette nature lumineuse originelle, au-delà des voiles de l'ignorance et de l'égo.&lt;/p&gt;"/>
-    <hyperlink ref="E38" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/V%C3%A9danta&quot;  title=&quot; Wikipedia&quot;&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).https://fr.wikipedia.org/wiki/Védanta&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="E40" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E44" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>
-    <hyperlink ref="E48" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bushido&quot; title=&quot;Wikipedia&quot;&gt;Le Bushido&lt;/a&gt; (« Voie du Guerrier ») est le code éthique de la classe des samouraïs du Japon féodal, progressivement formalisé entre l'époque Kamakura (XIIe siècle) et la période Edo. Il synthétise en une philosophie de vie cohérente des valeurs empruntées au bouddhisme zen, au shintoïsme et au confucianisme.&lt;/p&gt;&lt;p&gt;Les sept vertus cardinales du Bushido sont : la rectitude (gi), le courage (yu), la bienveillance (jin), le respect (rei), la sincérité (makoto), l'honneur (meiyo) et la loyauté (chugi). À celles-ci s'ajoute la maîtrise de soi, la frugalité et l'acceptation stoïque de la mort — le samouraï doit &quot;vivre comme s'il était déjà mort&quot; pour agir sans attachement ni peur.&lt;/p&gt;&lt;p&gt;La pratique de seppuku (suicide rituel) illustre à l'extrême cette philosophie : la mort honorable vaut mieux qu'une vie dans la honte. Cette acceptation de la mort comme acte ultime de liberté et de dignité a fasciné les philosophes — de Nitobe Inazo, qui codafia le Bushido en 1900, à ceux qui y voient une forme de stoïcisme oriental.&lt;/p&gt;&lt;p&gt;Après la fin de l'ère des samouraïs au XIXe siècle, le Bushido survit dans les arts martiaux japonais (kendo, judo, aïkido), dans la culture d'entreprise japonaise et dans une vision de l'excellence par la maîtrise de soi qui continue d'inspirer bien au-delà du Japon.&lt;/p&gt;"/>
-    <hyperlink ref="E53" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fondamentalisme&quot;   title=&quot; Wikipedia&quot;&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient , principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les religions ; le fondamentalisme chrétien par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E59" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E64" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E65" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E66" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
-    <hyperlink ref="E73" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E74" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E14" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines&quot;  title=&quot; Wikipedia&quot;&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les traditions philosophiques et spirituelles des civilisations précolombiennes d'Amérique centrale, en particulier les Aztèques, les Mayas et les Toltèques. Ces pensées forment un univers conceptuel original, structuré autour de la relation entre l'homme, le cosmos et les forces divines.&lt;/p&gt;&lt;p&gt;Au cœur de ces traditions se trouve la notion de &lt;em&gt;teotl&lt;/em&gt; (divinité, énergie sacrée) chez les Aztèques, ou de &lt;em&gt;k'ul&lt;/em&gt; (force vitale sacrée) chez les Mayas. La cosmologie mésoaméricaine conçoit l'univers comme un système de cycles temporels, où les dieux et les hommes sont liés par des obligations réciproques. Le sacrifice rituel, loin d'être une simple pratique violente, est pensé comme une nécessité cosmique pour maintenir l'équilibre du monde.&lt;/p&gt;&lt;p&gt;Des figures comme Quetzalcóatl (le Serpent à plumes) incarnent une sagesse éthique et philosophique : tempérance, connaissance, opposition au sacrifice humain selon certaines traditions. Les philosophes aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s'interrogeaient sur la nature du vrai, du beau, du bien, et sur la condition humaine — une tradition philosophique autonome redécouverte par des chercheurs comme Miguel León-Portilla.&lt;/p&gt;"/>
+    <hyperlink ref="E17" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9sychasme&quot; title=&quot; Wikipedia&quot;&gt;L'Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme oriental, dont le nom vient du grec &lt;em&gt;hésychia&lt;/em&gt; (silence, tranquillité). Il désigne une pratique spirituelle visant à atteindre l'union avec Dieu par la prière continue, le silence intérieur et la maîtrise du souffle.&lt;/p&gt;&lt;p&gt;Ses origines remontent aux Pères du désert des IVe-Ve siècles, mais c'est au XIVe siècle que l'hésychasme devient un courant théologique et philosophique structuré, notamment grâce à Grégoire Palamas, archevêque de Thessalonique, qui en formule la doctrine dans ses &lt;em&gt;Triades&lt;/em&gt;. Palamas distingue l'essence divine (inaccessible) des énergies divines (accessibles à l'expérience mystique), permettant de fonder théologiquement la possibilité d'une véritable union de l'homme avec Dieu.&lt;/p&gt;&lt;p&gt;Cette distinction essence-énergies est l'une des contributions philosophiques les plus originales de la pensée byzantine. L'hésychasme a profondément marqué la spiritualité orthodoxe russe, grecque et serbe, et continue d'irriguer la théologie et la philosophie orthodoxes contemporaines.&lt;/p&gt;"/>
+    <hyperlink ref="E19" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka&quot;  title=&quot;Wikipedia&quot;&gt;Le Lokayata&lt;/a&gt;, également connu sous le nom de Carvaka, est la seule école philosophique de l'Inde ancienne à avoir défendu un matérialisme radical et un athéisme déclaré. Fondée vers le VIe siècle avant notre ère, elle rejette tout ce qui ne peut être appréhendé par les sens : pas d'âme immortelle, pas d'au-delà, pas de loi karmique.&lt;/p&gt;&lt;p&gt;Sa devise pourrait se résumer ainsi : ce que l'on voit existe ; ce que l'on ne peut percevoir n'est qu'invention. Les Carvakas refusent les Védas et leur autorité, les rituels brahmaniques, et toute forme de spéculation métaphysique. L'univers est composé des quatre éléments — terre, eau, feu et air — sans qu'intervienne aucune divinité créatrice.&lt;/p&gt;&lt;p&gt;En matière d'éthique, la philosophie Carvaka est franchement hédoniste : le plaisir est le seul bien réel, la souffrance le seul mal. Mieux vaut jouir de la vie maintenant plutôt qu'espérer une récompense illusoire après la mort. Ce réalisme sans concession en fait une voix singulière, souvent persécutée, de la pensée indienne classique.&lt;/p&gt;&lt;p&gt;Bien que ses textes originaux aient presque tous disparu — connus surtout par les réfutations de ses adversaires — son influence demeure dans les courants matérialistes et rationalistes qui traversent la philosophie indienne jusqu'à aujourd'hui.&lt;/p&gt;"/>
+    <hyperlink ref="E24" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra&quot; title=&quot; Wikipedia&quot;&gt; Le Yoga&lt;/a&gt; en tant qu’école philosophique (darshana) est distinct de la pratique physique popularisée en Occident. Systématisé par Patanjali dans les Yoga Sutra (entre 200 av. J.-C. et 500 apr. J.-C.), il partage la métaphysique dualiste du Samkhya — Purusha (conscience) et Prakriti (matière) — mais y ajoute une méthode pratique précise pour la libération.&lt;/p&gt;&lt;p&gt;Les huit membres (ashtanga) du Yoga structurent ce chemin : discipline éthique (yama, niyama), posture (asana), maîtrise du souffle (pranayama), retrait des sens (pratyahara), concentration (dharana), méditation (dhyana) et absorption (samadhi). Chaque étape prépare la suivante dans une progression méthodique vers l’arrêt des fluctuations du mental (chitta vritti nirodha).&lt;/p&gt;&lt;p&gt;Contrairement au Samkhya, purement théorique, le Yoga de Patanjali introduit îshvara (un principe divin, seigneur particulier parmi les âmes) comme objet de concentration facultatif — une nuance théiste absente du Samkhya classique. Cette différence a nourri des siècles de commentaires et de débats entre les deux écoles sœurs.&lt;/p&gt;&lt;p&gt;Aujourd’hui mondialement diffusée, la dimension physique du yoga occulte souvent sa profondeur philosophique originelle : une discipline rigoureuse de la conscience, visant non le bien-être mais la discrimination (viveka) entre le Soi éternel et les fluctuations passagères du mental.&lt;/p&gt;"/>
+    <hyperlink ref="E26" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme&quot;  title=&quot; Wikipedia&quot;&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt;    &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title=&quot;Le Taoïsme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E30" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/École_des_Noms&quot;  title=&quot;Wikipedia&quot;&gt;L'École des Noms&lt;/a&gt; (ming jia, 名家) est une école de philosophie chinoise qui s'est développée pendant la période des Royaumes combattants. Sa préoccupation centrale : la relation entre les mots et les choses, entre les noms et la réalité qu'ils désignent.&lt;/p&gt;&lt;p&gt;Ses représentants les plus célèbres, Gongsun Long et Hui Shi, sont connus pour leurs paradoxes vertigineux. Gongsun Long affirmait que &quot;le cheval blanc n'est pas un cheval&quot; — non par provocation, mais pour distinguer le concept général (cheval) du particulier concret (ce cheval blanc). Hui Shi proclamait que &quot;le ciel et la terre sont d'une même hauteur&quot;, explorant les limites relatives de toute catégorisation.&lt;/p&gt;&lt;p&gt;Ces réflexions sur le langage anticipent certaines problématiques de la logique et de la philosophie analytique moderne. Comment les mots nous permettent-ils — ou nous empêchent-ils — de saisir la réalité ? Toute classification n'implique-t-elle pas une distorsion du monde ?&lt;/p&gt;&lt;p&gt;Peu influente politiquement, l'École des Noms fut souvent moquée par ses contemporains confu céens et taoïstes. Mais elle constitue une contribution unique à la logique asiatique et à la philosophie du langage dans la pensée mondiale.&lt;/p&gt;"/>
+    <hyperlink ref="E31" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A2mkhya&quot;  title=&quot; Wikipedia&quot;&gt;Le Sâmkhya&lt;/a&gt; est l'une des plus anciennes écoles philosophiques de l'Inde, considérée comme un darshana orthodoxe de l'hindouisme. Il propose une analyse rationnelle de la réalité pour libérer l'individu du cycle des renaissances et de la souffrance. Ce système dualiste distingue deux réalités ultimes : Purusha, la conscience pure et passive (esprit, principe masculin), et Prakriti, la matière primordiale active (énergie universelle, principe féminin). Prakriti évolue sous l'influence des trois guṇas (sattva : harmonie ; rajas : activité ; tamas : inertie), générant le monde manifesté à travers 23 tattvas (principes), comme buddhi (intelligence), ahaṃkāra (ego) et les sens. &lt;/p&gt; &lt;p&gt; Il explique la création comme une transformation de Prakriti, sans recours à un dieu créateur : de l'état non manifesté (avyakta) naît le manifesté (vyakta), incluant le corps subtil qui transmigre. L'ignorance (avidyā) cause l'identification erronée du Purusha à la matière, source de souffrance (duḥkha). &lt;/p&gt; &lt;p&gt; Fondement théorique du Yoga de Patañjali, le Sâmkhya met l'accent sur la discrimination (viveka) entre Purusha et Prakriti pour atteindre la libération (kaivalya). Il influence largement la philosophie indienne, des Puranas au Vedānta. &lt;/p&gt;"/>
+    <hyperlink ref="E33" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Therav%C4%81da&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Theravada&lt;/a&gt; (« École des Anciens ») est la plus ancienne forme du bouddhisme conservée jusqu'à nos jours. Héritière directe des enseignements du Bouddha historique, elle s'enracina progressivement en Asie du Sud-Est : Sri Lanka, Thaïlande, Myanmar, Cambodge, Laos.&lt;/p&gt;&lt;p&gt;Au cœur du Theravada se trouve le Pali Canon (Tipitaka), le corpus scripturaire le plus ancien du bouddhisme. Sa philosophie insiste sur la voie individuelle vers l'éveil : chaque être doit parcourir lui-même le Noble Sentier Octuple — juste compréhension, juste intention, juste parole, juste action, juste mode de vie, juste effort, juste attention, juste concentration.&lt;/p&gt;&lt;p&gt;L'idéal du Theravada est l'Arhat : le sage qui, par sa propre pratique, a éteint les &quot;feux&quot; de l'attachement, de la haine et de l'illusion, et atteint le Nirvana. Cette voie solitaire et rigoureuse contraste avec l'idéal du bodhisattva du Mahayana, qui renonce à son propre éveil pour sauver tous les êtres.&lt;/p&gt;&lt;p&gt;La méditation de pleine conscience (sati), aujourd'hui mondialement répandue, trouve ses racines dans les pratiques contemplatives du Theravada, notamment la méditation vipassana qui vise à observer directement l'impermanence, la souffrance et l'absence de soi.&lt;/p&gt;"/>
+    <hyperlink ref="E35" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vaisheshika&quot;  title=&quot; Wikipedia&quot;&gt;Le Vaisheshika&lt;/a&gt;  est une école philosophique orthodoxe hindoue, fondée par le sage Kaṇāda, qui se distingue par son atomisme et son réalisme ontologique. Exposée dans les Vaiśeṣika Sūtra (non antérieurs à l'ère chrétienne), elle vise la libération (mokṣa) par la connaissance des catégories fondamentales de la réalité. Le système repose sur six ou sept padārthas (catégories) : dravya (substance), guṇa (qualité), karma (action/mouvement), sāmānya (universalité), viśeṣa (particularité) et samavāya (inhérence). Parmi les neuf substances, quatre sont atomiques (terre, eau, feu, air) : les paramāṇu (atomes éternels, indivisibles) s'assemblent en dyades puis en objets composites non éternels. &lt;/p&gt; &lt;p&gt; Sans dieu créateur direct, l'univers émerge de combinaisons atomiques influencées par une cause efficiente (adrisṭa, karma résiduel). Ākāśa (espace), kāla (temps), dik (direction) et cit (âme) complètent les substances ; les atomes sphériques se lient par forces intrinsèques, formant un monde discontinu mais perceptible. &lt;/p&gt; &lt;p&gt; Souvent fusionné avec le Nyâya (logique), il postule un Īśvara ordonnateur. La délivrance est un état pur de l'âme (sans qualités, conscience ou douleur), libérée des agrégats par la gnose discriminante. &lt;/p&gt;"/>
+    <hyperlink ref="E36" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_mah%C4%81y%C4%81na&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Mahayana&lt;/a&gt; (« Grand Véhicule ») est apparu en Inde au tournant de l'ère chrétienne, s'étendant progressivement vers la Chine, le Japon, la Corée et le Vietnam. Par rapport au Theravada, il représente une transformation profonde de la vision bouddhiste : l'éveil n'est plus un idéal solitaire mais une aspiration collective.&lt;/p&gt;&lt;p&gt;L'idéal central du Mahayana est le bodhisattva : l'être qui, sur le point d'atteindre le Nirvana, choisit de demeurer dans le cycle des renaissances (samsara) pour guider et libérer tous les êtres sensibles. Cette compassion universelle (karuna) devient le moteur de la voie spirituelle, indissociable de la sagesse (prajna).&lt;/p&gt;&lt;p&gt;Le Mahayana introduit également la notion révolutionnaire de sunyata (vacuité) : toutes choses sont dénues d'existence propre et intrinsèque — elles n'existent que de façon interdependante. Nagarjuna, au IIe siècle, en développa la philosophie dans ses Stances du Milieu, fondant l'école Madhyamaka qui influencça toute la pensée bouddhiste ultérieure.&lt;/p&gt;&lt;p&gt;C'est sur le sol du Mahayana que fleuriront le bouddhisme Zen, le bouddhisme tibétain Vajrayana, et l'École de la Terre Pure. Avec ses sutras nouveaux (Lotus, Vimalakirti, Prajnaparamita), le Mahayana offre une vision du monde d'une richesse philosophique et spirituelle sans équivalent.&lt;/p&gt;"/>
+    <hyperlink ref="E38" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mazdakisme&quot; title=&quot;Wikipedia&quot;&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse sous l’Empire sassanide. Fondé par le réformateur Mazdak, ce courant tire ses origines à la fois du mazdéisme et du manichéisme, en proposant une relecture dualiste du monde axée sur la lumière et les ténèbres. &lt;/p&gt; &lt;p&gt; Contrairement aux structures sociales hiérarchisées de l’époque, le mazdakisme prônait une égalité radicale entre les individus. Mazdak soutenait que les causes des conflits humains résidaient dans la soif de richesses et de pouvoir, ce qui l'a conduit à prôner la mise en commun des biens matériels et, selon certaines sources, des femmes. &lt;/p&gt; &lt;p&gt; Cette doctrine a été perçue comme une menace par l’aristocratie et le clergé zoroastrien traditionnel, qui y voyaient une hérésie dangereuse pour l'ordre établi. Après avoir initialement bénéficié de l'intérêt de l'empereur Kavadh Ier, le mouvement fut sévèrement réprimé lors de grandes purges organisées entre 524 et 529. &lt;/p&gt; &lt;p&gt; Bien que le mazdakisme ait été marginalisé après ces persécutions, il a laissé une trace durable dans la pensée iranienne. Parfois qualifié, de manière anachronique, de mouvement proto-socialiste, son idéal de justice sociale a influencé certains courants contestataires qui se sont manifestés en Iran jusqu'au XIVe siècle environ. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E40" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_vajrayana&quot;  title=&quot;Wikipedia&quot;&gt;Le Vajrayana&lt;/a&gt; (« Véhicule de Diamant ») est la troisième grande forme du bouddhisme, développée en Inde entre le VIIe et le Xe siècle, puis transmise au Tibet, en Mongolie et dans l'Himalaya. Il représente la voie tantrique du bouddhisme, utilisant des pratiques ésotériques pour accélérer le chemin vers l'éveil.&lt;/p&gt;&lt;p&gt;Là où le Theravada vise l'éveil en de nombreuses vies et le Mahayana en d'innombrables éons, le Vajrayana affirme qu'il est possible d'atteindre l'éveil en une seule vie — voire en un seul instant. Pour cela, il mobilise un arsenal de techniques : mantras, mandalas, mudras, visualisations de divinités, pratiques yogiques subtiles sur les énergies intérieures du corps.&lt;/p&gt;&lt;p&gt;Le Bouddhisme tibétain, la forme la plus répandue du Vajrayana, s'est développé dès le VIIe siècle sous le règne du roi Songtsen Gampo. Il intègre des éléments de la religion Bön préexistante et du Mahayana indien. Ses figures tutlaires — Padmasambhava, Milarepa, Tsongkhapa — sont au cœur d'une tradition d'une richesse philosophique et rituelle incomparable.&lt;/p&gt;&lt;p&gt;La notion de &quot;nature de bouddha&quot; (tathagatagarbha) — l'idée que chaque être possède en lui la graine de l'éveil — est centrale dans le Vajrayana. La pratique vise à reconnaître directement cette nature lumineuse originelle, au-delà des voiles de l'ignorance et de l'égo.&lt;/p&gt;"/>
+    <hyperlink ref="E42" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/V%C3%A9danta&quot;  title=&quot; Wikipedia&quot;&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).https://fr.wikipedia.org/wiki/Védanta&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="E44" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E48" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>
+    <hyperlink ref="E52" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bushido&quot; title=&quot;Wikipedia&quot;&gt;Le Bushido&lt;/a&gt; (« Voie du Guerrier ») est le code éthique de la classe des samouraïs du Japon féodal, progressivement formalisé entre l'époque Kamakura (XIIe siècle) et la période Edo. Il synthétise en une philosophie de vie cohérente des valeurs empruntées au bouddhisme zen, au shintoïsme et au confucianisme.&lt;/p&gt;&lt;p&gt;Les sept vertus cardinales du Bushido sont : la rectitude (gi), le courage (yu), la bienveillance (jin), le respect (rei), la sincérité (makoto), l'honneur (meiyo) et la loyauté (chugi). À celles-ci s'ajoute la maîtrise de soi, la frugalité et l'acceptation stoïque de la mort — le samouraï doit &quot;vivre comme s'il était déjà mort&quot; pour agir sans attachement ni peur.&lt;/p&gt;&lt;p&gt;La pratique de seppuku (suicide rituel) illustre à l'extrême cette philosophie : la mort honorable vaut mieux qu'une vie dans la honte. Cette acceptation de la mort comme acte ultime de liberté et de dignité a fasciné les philosophes — de Nitobe Inazo, qui codafia le Bushido en 1900, à ceux qui y voient une forme de stoïcisme oriental.&lt;/p&gt;&lt;p&gt;Après la fin de l'ère des samouraïs au XIXe siècle, le Bushido survit dans les arts martiaux japonais (kendo, judo, aïkido), dans la culture d'entreprise japonaise et dans une vision de l'excellence par la maîtrise de soi qui continue d'inspirer bien au-delà du Japon.&lt;/p&gt;"/>
+    <hyperlink ref="E58" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fondamentalisme&quot;   title=&quot; Wikipedia&quot;&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient , principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les religions ; le fondamentalisme chrétien par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E66" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E71" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E72" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E73" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
+    <hyperlink ref="E81" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E82" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2476,8 +2476,10 @@
       <c r="F4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>20</v>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La Philosophie Egyptienne" par Le Précepteur</t>
+        </is>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
@@ -2598,8 +2600,10 @@
       <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>41</v>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mythologie Hindoue Védisme à Hindouisme par Arcana Mystères du Monde</t>
+        </is>
       </c>
       <c r="J7" s="13" t="s">
         <v>42</v>
@@ -2963,8 +2967,10 @@
       <c r="D14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>60</v>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines"  title=" Wikipedia"&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les conceptions religieuses et philosophiques des civilisations de Mésoamérique, du Mexique central au Guatemala : les Olmèques dès le IIe millénaire avant notre ère, puis les Mayas, les Toltèques et les Aztèques. Malgré leur diversité, elles partagent la vision d’un monde sacré, cyclique et fragile, dont l’équilibre dépend de l’action des humains. Elles nous sont connues par les codex peints, les inscriptions mayas, l’architecture des cités et les récits recueillis après la conquête espagnole.&lt;/p&gt; &lt;p&gt;Le temps y est pensé en cycles : le calendrier rituel de 260 jours et l’année solaire de 365 jours se combinent en un « siècle » de 52 ans, et les Mayas datent aussi les événements sur de très longues périodes, le « compte long », depuis une origine mythique fixée en 3114 av. J.-C. Pour les Aztèques, le monde actuel est le cinquième « Soleil », après quatre créations détruites ; les dieux se sont sacrifiés pour mettre ce soleil en mouvement, et les humains leur doivent en retour leur propre sang. Le sacrifice est ainsi pensé comme une dette cosmique, nécessaire pour que le soleil poursuive sa course. Le &lt;em&gt;Popol Vuh&lt;/em&gt;, livre sacré des Mayas quichés, raconte la création des humains, façonnés dans le maïs après plusieurs essais manqués. La figure de &lt;a href="https://fr.wikipedia.org/wiki/Quetzalc%C3%B3atl" title=" Wikipedia"&gt;Quetzalcóatl&lt;/a&gt;, le Serpent à plumes, est associée au savoir, aux arts et au calendrier.&lt;/p&gt; &lt;p&gt;Les sages aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s’interrogeaient sur la vérité et la fragilité de l’existence. Leur pensée a été étudiée comme une véritable philosophie par Miguel León-Portilla.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F14" s="1" t="s">
         <v>61</v>
@@ -3130,8 +3136,10 @@
       <c r="F17" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>74</v>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L'hésychasme prière sacrée par Mystica</t>
+        </is>
       </c>
       <c r="J17" s="2" t="s">
         <v>75</v>
@@ -3305,8 +3313,10 @@
       <c r="F21" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>99</v>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Les enseignemants de Confucius" par Film 25 Production</t>
+        </is>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
@@ -3688,8 +3698,10 @@
       <c r="D30" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>151</v>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/École_des_Noms"  title="Wikipedia"&gt;L’École des Noms&lt;/a&gt;, en chinois &lt;em&gt;mingjia&lt;/em&gt;, est une école de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.) qui s’intéresse au rapport entre les noms et les choses, c’est-à-dire entre le langage et la réalité. À une époque où les Cent Écoles débattent sans cesse, ses penseurs, appelés aussi « disputeurs », cultivent l’art de l’argumentation et du paradoxe, au point de passer pour des sophistes aux yeux de leurs adversaires. Ils prolongent à leur manière une exigence de Confucius, la « rectification des noms », qui veut que les mots s’accordent avec la réalité.&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hui_Shi" title=" Wikipedia"&gt;Hui Shi&lt;/a&gt; (IVe siècle av. J.-C.), ami et contradicteur de Zhuangzi, avance dix paradoxes sur l’espace, le temps et l’unité du monde : « le ciel est aussi bas que la terre », « je pars aujourd’hui pour Yue et j’y suis arrivé hier », ou encore « aimez tous les êtres, car le ciel et la terre ne font qu’un corps ». Ils montrent que toute distinction, grand et petit, haut et bas, dépend du point de vue. Son cadet &lt;a href="https://fr.wikipedia.org/wiki/Gongsun_Long" title=" Wikipedia"&gt;Gongsun Long&lt;/a&gt; (vers 320-250 av. J.-C.) est célèbre pour sa thèse « un cheval blanc n’est pas un cheval » : le nom « cheval blanc » désigne à la fois une forme et une couleur, il ne se confond donc pas avec le nom « cheval ». Il distingue ainsi le concept général des choses particulières, et le nom de ce qu’il désigne.&lt;/p&gt; &lt;p&gt;Raillée par les confucéens et les taoïstes, l’école disparaît avec l’empire Qin. Redécouverte au XXe siècle, elle est vue comme l’un des rares foyers de logique et de philosophie du langage de la Chine ancienne, aux côtés des logiciens moïstes. Un seul de ses livres, le &lt;em&gt;Gongsun Longzi&lt;/em&gt;, nous est parvenu, en partie.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F30" s="1" t="s">
         <v>152</v>
@@ -3863,8 +3875,10 @@
       <c r="D34" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="E34" s="19" t="s">
-        <v>175</v>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ny%C3%A2ya" title=" Wikipedia"&gt;Le Nyâya&lt;/a&gt;, « la règle » ou « la méthode », est l’une des six écoles orthodoxes de la philosophie indienne, celle qui s’est consacrée à la logique et à la théorie de la connaissance. Ses textes fondateurs, les &lt;em&gt;Nyāya Sūtra&lt;/em&gt;, attribués à Akṣapāda Gautama, sont composés entre le IIe siècle avant et le IIe siècle de notre ère, à partir de traditions de débat plus anciennes. Leur but reste spirituel : seule la connaissance juste délivre de la souffrance et du cycle des renaissances.&lt;/p&gt; &lt;p&gt;Le Nyâya reconnaît quatre moyens de connaissance valide (&lt;em&gt;pramāṇa&lt;/em&gt;) : la perception, l’inférence, la comparaison et le témoignage digne de foi. Il codifie l’inférence en un raisonnement à cinq membres, illustré par un exemple célèbre : la colline est en feu, parce qu’elle fume ; tout ce qui fume est en feu, comme un foyer de cuisine ; or la colline fume ; donc elle est en feu. Il dresse aussi la liste des sophismes et des ruses de la discussion. Réaliste, il soutient que le monde extérieur existe tel que nous le percevons, contre les bouddhistes. Il défend l’existence d’un Soi permanent et d’un Dieu cause du monde, notamment avec Udayana vers l’an mil. Associé à l’école &lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika" title=" Wikipedia"&gt;Vaiśeṣika&lt;/a&gt;, qui lui apporte sa théorie des atomes et des catégories, il forme avec elle le Nyāya-Vaiśeṣika.&lt;/p&gt; &lt;p&gt;Au XIVe siècle, Gaṅgeśa fonde le « nouveau Nyâya » (&lt;em&gt;Navya-Nyāya&lt;/em&gt;), dont le langage technique devient l’outil commun de toute la philosophie indienne. Ses analyses de l’inférence et du témoignage ont souvent été comparées à la logique d’Aristote.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F34" s="14" t="s">
         <v>176</v>
@@ -4797,7 +4811,7 @@
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Le SIKHISME : La religion qui affirme que "DIEU N'A PAS DE RELIGION" (Le message de l'Unité)" par MYSTICA</t>
+          <t xml:space="preserve">"Le SIKHISME : La religion qui affirme que "DIEU N'A PAS DE RELIGION" (Le message de l'Unité)" par Mystica</t>
         </is>
       </c>
       <c r="J54" s="1" t="s">
@@ -4978,8 +4992,10 @@
       <c r="F58" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="G58" s="16" t="s">
-        <v>311</v>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fondamentalisme par Le Savoir Partagé</t>
+        </is>
       </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
@@ -6035,6 +6051,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;L’eurasisme&lt;/a&gt; est un courant de pensée né en 1921 dans l’émigration russe, après la révolution bolchevique, avec le recueil &lt;em&gt;L’Exode vers l’Orient&lt;/em&gt;, publié à Sofia par un petit groupe de jeunes intellectuels exilés : le linguiste &lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Sergue%C3%AFevitch_Troubetsko%C3%AF" title=" Wikipedia"&gt;Nikolaï Troubetskoï&lt;/a&gt;, le géographe Piotr Savitski, le musicologue Pierre Souvtchinski et le théologien Georges Florovsky.&lt;/p&gt; &lt;p&gt;Leur thèse est que la Russie n’est ni une partie de l’Europe ni une partie de l’Asie, mais un monde à part, l’« Eurasie », dont la grande plaine, des Carpates au Pacifique, a façonné l’unité des peuples slaves, turcs et finno-ougriens. Contre les occidentalistes, ils refusent l’idée d’une civilisation européenne universelle : dans &lt;em&gt;L’Europe et l’humanité&lt;/em&gt; (1920), Troubetskoï y voit l’égoïsme d’une culture « romano-germanique » qui s’impose aux autres. Contre les slavophiles, ils réhabilitent l’héritage asiatique de la Russie, et jusqu’à l’empire de Gengis Khan, qui aurait le premier unifié cet espace. Ils rêvent d’un État fondé sur une idéologie commune et sur l’orthodoxie, distinct à la fois de la démocratie libérale et du communisme. Florovsky s’en éloigne vite et critique en 1928 ce qu’il appelle une « vérité des questions » devenue une « erreur des réponses ». Le mouvement se divise à la fin des années 1920, une partie se rapprochant du régime soviétique.&lt;/p&gt; &lt;p&gt;Prolongé en URSS par l’historien &lt;a href="https://fr.wikipedia.org/wiki/Lev_Goumilev" title=" Wikipedia"&gt;Lev Goumilev&lt;/a&gt;, l’eurasisme renaît après 1991 sous la forme d’un « néo-eurasisme » porté par &lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Douguine" title=" Wikipedia"&gt;Alexandre Douguine&lt;/a&gt;, idéologue d’extrême droite, et influence aujourd’hui la géopolitique nationaliste et impériale de la Russie.&lt;/p&gt;  &lt;audio controls title="De l'idée à l'action : 4 doctrines géopolitiques . Eurasie : la Russie au centre du jeu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18720-25.03.2021-ITEMA_22614994-2021C16756S0084.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QodQ2ORmtKg</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L'EURASISME : le projet géopolitique de la Russie ? - C Ce soir du 24 février 2022" par C Ce Soir - France Télévisions</t>
+        </is>
+      </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">doctrine née dans l’émigration russe : la Russie ne serait ni l’Europe ni l’Asie, mais une civilisation à part, l’« Eurasie ».</t>
@@ -6292,8 +6318,10 @@
       <c r="F85" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>441</v>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le consciencisme de Kwane Nkrumah par Renaissance Africaine</t>
+        </is>
       </c>
       <c r="J85" s="2" t="s">
         <v>442</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -3341,18 +3341,26 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="n">
-        <v>-510</v>
+      <c r="A22" s="14">
+        <v>1980</v>
       </c>
       <c r="B22" s="14"/>
-      <c r="C22" s="14" t="s">
-        <v>102</v>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980</t>
+        </is>
       </c>
       <c r="D22" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>104</v>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_(philosophie)"   title=" Wikipedia"&gt; L'Ubuntu&lt;/a&gt; trouve ses origines en Afrique subsaharienne, principalement chez les peuples bantous. Ubuntu est un mot en langue zouloue qui peut être traduit approximativement par « humanité envers les autres » ou « je suis parce que nous sommes ». Il s'agit d'une philosophie qui met l'accent sur l'interconnexion, l'interdépendance et la bienveillance mutuelle entre les êtres humains. &lt;/p&gt; &lt;p&gt;
+Dans la philosophie Ubuntu, chaque individu est considéré comme étant en relation avec les autres et le monde qui l'entoure. Les relations humaines sont au cœur de cette philosophie, et l'identité d'une personne est déterminée en grande partie par sa relation avec les autres membres de sa communauté. Selon Ubuntu, nous sommes tous liés et notre bien-être individuel est intrinsèquement lié au bien-être collectif. &lt;/p&gt; &lt;p&gt;
+Un proverbe couramment cité pour illustrer cette philosophie est : « Umuntu ngumuntu ngabantu », ce qui signifie « Je suis ce que je suis grâce à ce que nous sommes tous ». Cela souligne l'idée que notre humanité commune se manifeste dans nos interactions et nos relations avec les autres. La philosophie Ubuntu encourage donc l'empathie, la solidarité et le respect mutuel. &lt;/p&gt; &lt;p&gt;
+Elle a également des implications politiques et sociales et met l'accent sur l'importance de la justice, de la réconciliation et de la coopération dans la construction de sociétés harmonieuses et est souvent invoqué comme une base éthique pour guider les décisions politiques et promouvoir la tolérance, la compréhension et la paix. &lt;/p&gt; &lt;p&gt;
+Il convient de noter que la philosophie Ubuntu ne se limite pas à l'Afrique subsaharienne. Elle a inspiré des penseurs et des leaders du monde entier qui reconnaissent l'importance des relations humaines et de la solidarité pour créer des sociétés justes et inclusives. &lt;/p&gt; &lt;p&gt;Ce n’est qu’au XXe siècle que l’Ubuntu devient une philosophie écrite. En 1980, au Zimbabwe, Stanlake et Tommie Marie Samkange publient &lt;em&gt;Hunhuism or Ubuntuism&lt;/em&gt;, qui en fait le fondement d’une pensée politique africaine. En Afrique du Sud, la Constitution provisoire de 1993 invoque « un besoin d’ubuntu, et non de victimisation » pour sortir de l’apartheid. L’archevêque &lt;a href="https://fr.wikipedia.org/wiki/Desmond_Tutu" title=" Wikipedia"&gt;Desmond Tutu&lt;/a&gt; en fait l’esprit de la Commission vérité et réconciliation, qu’il préside à partir de 1995, et le défend dans &lt;em&gt;Il n’y a pas d’avenir sans pardon&lt;/em&gt; (1999). La même année, le philosophe Mogobe Ramose publie &lt;em&gt;African Philosophy through Ubuntu&lt;/em&gt;, qui en propose une lecture métaphysique : l’être n’est pas une chose figée, mais un mouvement de relations.&lt;/p&gt;  &lt;audio controls title="Ubuntu ou l'histoire, les valeurs et la mémoire par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/08/s32/RF_DF1DF1B4-FF64-438F-BC47-78A44A7FA537_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F22" s="14" t="s">
         <v>105</v>
@@ -4432,8 +4440,15 @@
       <c r="D46" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="E46" s="16" t="s">
-        <v>247</v>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Acharisme"   title=" Wikipedia"&gt;L'Acharisme&lt;/a&gt; est une école théologique sunnite de l'islam, fondée par Abu al-Hasan al-Ash'ari. Il était à l'origine un théologien mutazilite, mais il a finalement rejeté leurs idées et a développé sa propre doctrine théologique qui est devenue connue sous le nom d'acharisme. &lt;/p&gt; &lt;p&gt;
+L'acharisme est basé sur la croyance en l'unicité de Dieu (tawhid) et l'acceptation de la révélation coranique et de la sunna (les enseignements et pratiques du prophète Mahomet). La principale préoccupation de l'acharisme est de défendre et de rationaliser les croyances islamiques face à diverses idées philosophiques et théologiques en circulation à l'époque. &lt;/p&gt; &lt;p&gt;
+Il met l'accent sur la prédestination (al-qadr) et la volonté divine. Selon les acharites, Dieu est le créateur de toutes choses et détient un contrôle absolu sur le destin de chaque individu. Cependant, ils affirment également que les humains ont une certaine responsabilité dans leurs actions, même si ces actions sont prédestinées par Dieu. Ils rejettent l'idée du libre arbitre absolu et soutiennent que les humains ont une volonté limitée. &lt;/p&gt; &lt;p&gt;
+En ce qui concerne la compréhension des attributs de Dieu, les acharites adoptent une position dite "intermédiaire". Ils affirment que Dieu possède des attributs, tels que la connaissance, la puissance et la volonté, mais ils rejettent l'idée d'une ressemblance entre les attributs divins et les attributs humains. Ils soutiennent que les attributs de Dieu sont uniques et ne peuvent pas être comparés à ceux des créatures. &lt;/p&gt; &lt;p&gt;
+L'acharisme a également une position particulière sur la foi (iman). Les acharites affirment que la foi est une combinaison de croyance dans le cœur, affirmation avec la langue et actes avec les membres. Ils soutiennent que la foi augmente et diminue en fonction des actions et des croyances de l'individu. 
+ &lt;/p&gt;   &lt;audio controls title="La doctrine acharite par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-23.04.2023-ITEMA_23356900-2023C26163E0013-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F46" s="14" t="s">
         <v>248</v>
@@ -4986,8 +5001,11 @@
       <c r="D58" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="E58" s="19" t="s">
-        <v>309</v>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fondamentalisme"   title=" Wikipedia"&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient, principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; 
+ &lt;audio controls title="les religions ; le fondamentalisme chrétien par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F58" s="14" t="s">
         <v>310</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -4591,11 +4591,15 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_azt%C3%A8que" title=" Wikipedia"&gt;La Pensée nahua&lt;/a&gt; désigne la réflexion philosophique des peuples de langue nahuatl, dont les Aztèques ou Mexicas, dans le Mexique central avant la conquête espagnole de 1521. Elle était portée par les &lt;em&gt;tlamatinime&lt;/em&gt;, « ceux qui savent quelque chose », sages et maîtres du &lt;em&gt;calmecac&lt;/em&gt;, l’école où l’on formait les jeunes nobles. Nous la connaissons par des codex, des chants et des discours recueillis après la conquête, notamment par le franciscain Bernardino de Sahagún.&lt;/p&gt; &lt;p&gt;L’historien mexicain &lt;a href="https://fr.wikipedia.org/wiki/Miguel_Le%C3%B3n-Portilla" title=" Wikipedia"&gt;Miguel León-Portilla&lt;/a&gt; l’a fait connaître dans &lt;em&gt;La filosofía náhuatl estudiada en sus fuentes&lt;/em&gt; (1956). Les sages s’interrogent sur la fragilité de l’existence : sur terre tout est passager, comme les fleurs qui se fanent, et l’on se demande si quelque chose est vrai, enraciné. Leur réponse est &lt;em&gt;in xochitl in cuicatl&lt;/em&gt;, « la fleur et le chant », c’est-à-dire la poésie, seule capable peut-être de dire le vrai. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Nezahualc%C3%B3yotl" title=" Wikipedia"&gt;Nezahualcóyotl&lt;/a&gt;, souverain de Texcoco au XVe siècle, auquel on attribue de nombreux poèmes, en est la grande figure. Le principe suprême, Ometeotl, « dieu de la dualité », unit le masculin et le féminin ; le monde est fait de couples complémentaires, vie et mort, ordre et désordre, en équilibre instable. Le temps est cyclique : quatre « soleils », quatre âges du monde, ont déjà été détruits, et nous vivons sous le cinquième.&lt;/p&gt; &lt;p&gt;Plus récemment, le philosophe James Maffie a lu dans le &lt;em&gt;teotl&lt;/em&gt; une énergie sacrée, unique et toujours en mouvement, dont toutes choses sont des aspects. Cette pensée est aujourd’hui étudiée comme une véritable tradition philosophique.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>267</v>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mLi2f452GNo</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Aztec Philosophy with James Maffie" par Hermitix Podcast</t>
+        </is>
       </c>
       <c r="J49" s="2" t="s">
         <v>268</v>
@@ -4775,11 +4779,15 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_vietnamienne" title=" Wikipedia"&gt;La Philosophie vietnamienne&lt;/a&gt; se caractérise par le Tam Giáo, les « trois enseignements » : une alliance durable entre le confucianisme, le bouddhisme et le taoïsme, à laquelle s’ajoutent le culte des ancêtres et celui des génies protecteurs des villages. Un adage vietnamien dit que « les trois enseignements ont une même source ». Chacun a son domaine : le confucianisme règle la famille et l’État, le bouddhisme la vie spirituelle, le taoïsme la médecine, la divination et les rites du quotidien.&lt;/p&gt; &lt;p&gt;Le bouddhisme arrive très tôt, dès les premiers siècles de notre ère, par la mer et par la Chine. Après l’indépendance, en 939, les dynasties Lý et Trần le favorisent : le roi &lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;Trần Nhân Tông&lt;/a&gt;, vainqueur des invasions mongoles, abdique en 1293 pour se faire moine et fonde l’école zen de Trúc Lâm, la « Forêt de bambous », proprement vietnamienne. Le confucianisme s’impose ensuite comme doctrine de l’État : le Temple de la Littérature est fondé à Hanoï en 1070, et les concours mandarinaux recrutent les fonctionnaires jusqu’en 1919. Mais les lettrés formés aux classiques confucéens pratiquaient souvent le bouddhisme dans leur vie personnelle et se retiraient volontiers en ermites taoïstes : les trois voies se complètent plus qu’elles ne s’opposent. &lt;a href="https://fr.wikipedia.org/wiki/Nguy%E1%BB%85n_Tr%C3%A3i" title=" Wikipedia"&gt;Nguyễn Trãi&lt;/a&gt; au XVe siècle, Nguyễn Bỉnh Khiêm au XVIe ou Lê Quý Đôn au XVIIIe illustrent cette sagesse composite.&lt;/p&gt; &lt;p&gt;Au XXe siècle, ce syncrétisme inspire de nouvelles religions comme le caodaïsme, tandis que le marxisme devient la doctrine officielle. L’empreinte du Tam Giáo demeure dans les rites familiaux et la morale.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>289</v>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOWcduKGZYI</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Sự khác nhau của Nho giáo, Đạo giáo và Phật giáo - Tam Giáo Đồng Nguyên là gì?" par Radio Suy Ngẫm</t>
+        </is>
       </c>
       <c r="J53" s="2" t="s">
         <v>290</v>
@@ -5929,11 +5937,15 @@
       <c r="E77" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>406</v>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imzO0eNziD4</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"B.R. Ambedkar: The Life of the Mind &amp; a Life in Politics" par Library of Congress</t>
+        </is>
       </c>
       <c r="J77" s="2" t="s">
         <v>407</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2835,12 +2835,14 @@
       <c r="E11" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>214</v>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jnuSRt72dqw</t>
+        </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">le kalâm musulman par ikarim</t>
+          <t xml:space="preserve">"Introduction à la philosophie juive : le Kalām musulman" par Ikarim</t>
         </is>
       </c>
       <c r="J11" s="21" t="s">
@@ -5227,12 +5229,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">itIIrC5jvFM</t>
+          <t xml:space="preserve">0a3g3J3rIQc</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">""La Haskala : Des "Lumières" Qui Ont Éteint la Torah !" 🇰 Kitsour." par Torah-Box</t>
+          <t xml:space="preserve">"The Haskalah (Essential Lectures in Jewish History)" par Henry Abramson</t>
         </is>
       </c>
       <c r="J62" s="1" t="inlineStr">

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2555,8 +2555,10 @@
       <c r="D6" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>34</v>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zoroastrisme" title="Wikipedia"&gt;Le Zoroastrisme&lt;/a&gt; est la religion fondée en Iran par le prophète &lt;a href="https://fr.wikipedia.org/wiki/Zarathoustra" title=" Wikipedia"&gt;Zarathoustra&lt;/a&gt;, dont on situe la vie, selon les auteurs, entre 1500 et 600 av. J.-C. Ses hymnes, les &lt;em&gt;Gâthâs&lt;/em&gt;, forment la partie la plus ancienne de l’&lt;a href="https://fr.wikipedia.org/wiki/Avesta" title=" Wikipedia"&gt;Avesta&lt;/a&gt;, le livre sacré. Religion des empires perses, des Achéménides aux Sassanides, il est aussi l’une des premières grandes pensées du bien et du mal.&lt;/p&gt; &lt;p&gt;Zarathoustra rompt avec le polythéisme de son temps pour célébrer un dieu suprême, Ahura Mazda, le « Seigneur Sage ». Le monde est le théâtre d’un combat entre deux esprits : l’Esprit saint, du côté de la vérité et de l’ordre (&lt;em&gt;asha&lt;/em&gt;), et l’Esprit destructeur, Angra Mainyu, du côté du mensonge. Chaque être humain doit choisir son camp ; sa liberté morale est au cœur de la doctrine, résumée par la triade « bonnes pensées, bonnes paroles, bonnes actions ». Après la mort, l’âme est jugée au pont Chinvat ; à la fin des temps, un sauveur viendra, les morts ressusciteront et le mal sera vaincu. Ces idées de jugement, de résurrection et de fin des temps ont pu influencer le judaïsme tardif, puis le christianisme et l’islam.&lt;/p&gt; &lt;p&gt;Après la conquête arabe, une partie des fidèles émigre en Inde, où elle forme la communauté des Parsis. Les zoroastriens, quelques centaines de milliers aujourd’hui, entretiennent toujours le feu sacré, symbole de la lumière divine. Le manichéisme et le mazdakisme en sont issus, et Nietzsche a fait de Zarathoustra le porte-parole de sa propre pensée.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F6" s="1" t="s">
         <v>35</v>
@@ -3402,8 +3404,10 @@
       <c r="D23" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>111</v>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ajivika"  title="Wikipedia"&gt;L’Ajīvika&lt;/a&gt; est une école ascétique de l’Inde ancienne, fondée ou réorganisée au Ve siècle av. J.-C. par Makkhali Gosala, contemporain du Bouddha et de &lt;a href="https://fr.wikipedia.org/wiki/Mahavira" title=" Wikipedia"&gt;Mahavira&lt;/a&gt;, le fondateur du jaïnisme, dont il fut un temps le compagnon. Ses textes sont perdus : nous ne la connaissons que par ses adversaires bouddhistes et jaïns, qui en font un portrait hostile. Le nom viendrait d’&lt;em&gt;ājīva&lt;/em&gt;, « mode de vie », allusion à leur règle d’existence.&lt;/p&gt; &lt;p&gt;Sa thèse centrale est un déterminisme radical, la doctrine de la &lt;em&gt;niyati&lt;/em&gt;, le destin. Tout ce qui arrive est fixé d’avance ; l’effort, la vertu ou les rites ne changent rien. Chaque être traverse un nombre immense de renaissances, 8 400 000 grands cycles selon les sources, puis atteint la fin de la souffrance au terme prévu, comme une pelote de fil qui se déroule jusqu’au bout. Le libre arbitre est une illusion. Cette position heurte de front le bouddhisme et le jaïnisme, pour qui les actes, le karma, déterminent l’avenir et l’effort moral conduit à la délivrance. Les Ajīvikas étaient pourtant de rigoureux ascètes, souvent nus, qui pratiquaient parfois le jeûne jusqu’à la mort. Selon les textes jaïns, Gosala mourut peu après une violente querelle avec Mahavira.&lt;/p&gt; &lt;p&gt;Ils connaissent un grand rayonnement sous l’empire Maurya : &lt;a href="https://fr.wikipedia.org/wiki/Ashoka" title=" Wikipedia"&gt;Ashoka&lt;/a&gt; leur fait creuser des &lt;a href="https://fr.wikipedia.org/wiki/Grottes_de_Barabar" title=" Wikipedia"&gt;grottes dans les collines de Barabar&lt;/a&gt;. L’école décline ensuite et disparaît vers le XIVe siècle dans le sud de l’Inde. On y voit l’une des premières formes de fatalisme philosophique, comparable à certaines thèses des stoïciens.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F23" s="1" t="s">
         <v>112</v>
@@ -3750,8 +3754,10 @@
       <c r="D31" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>158</v>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A2mkhya"  title=" Wikipedia"&gt;Le Sâmkhya&lt;/a&gt;, « dénombrement », est l’une des six écoles orthodoxes de la philosophie indienne, et sans doute la plus ancienne. On l’attribue au sage légendaire &lt;a href="https://fr.wikipedia.org/wiki/Kapila" title=" Wikipedia"&gt;Kapila&lt;/a&gt;, mais son texte de référence, les &lt;em&gt;Sāṃkhya-kārikā&lt;/em&gt; d’Īśvarakṛṣṇa, date des environs du IVe siècle de notre ère. Comme les autres écoles, il cherche à délivrer l’homme de la souffrance et du cycle des renaissances par la connaissance.&lt;/p&gt; &lt;p&gt;Le Sâmkhya est un dualisme : il distingue deux principes éternels. Le &lt;em&gt;puruṣa&lt;/em&gt; est la conscience pure, immobile, simple témoin ; il y en a une infinité, une par être. La &lt;em&gt;prakṛti&lt;/em&gt; est la nature, matière première active, faite de trois qualités (&lt;em&gt;guṇa&lt;/em&gt;) : la clarté (&lt;em&gt;sattva&lt;/em&gt;), l’énergie (&lt;em&gt;rajas&lt;/em&gt;) et l’inertie (&lt;em&gt;tamas&lt;/em&gt;). Quand leur équilibre se rompt, la nature se déploie en 23 principes : l’intellect, le sens du moi, l’esprit, les sens, puis les éléments subtils et grossiers. Tout effet préexiste dans sa cause, comme l’huile dans la graine, et le monde se forme sans dieu créateur. La souffrance vient de ce que la conscience se confond avec les opérations de la nature, qu’elle ne fait que regarder ; la délivrance, l’« isolement » (&lt;em&gt;kaivalya&lt;/em&gt;), vient du discernement qui les sépare.&lt;/p&gt; &lt;p&gt;Le Sâmkhya fournit sa métaphysique au Yoga de &lt;a href="https://fr.wikipedia.org/wiki/Patanjali" title=" Wikipedia"&gt;Patañjali&lt;/a&gt;, qui en est comme la pratique, et imprègne la &lt;em&gt;Bhagavad-Gîtâ&lt;/em&gt;, la médecine āyurvédique et une grande partie de la pensée hindoue. Le Vedânta lui reproche de séparer la nature de l’Absolu, mais reprend beaucoup de ses notions.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F31" s="9" t="s">
         <v>159</v>
@@ -3796,8 +3802,10 @@
       <c r="D32" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>163</v>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9gisme" title="Wikipedia"&gt;Le Légisme&lt;/a&gt;, en chinois &lt;em&gt;fajia&lt;/em&gt;, « école de la loi », est une philosophie politique de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.). À une époque de guerres incessantes, ses penseurs, souvent ministres, cherchent comment rendre un État riche et puissant. Contre les confucéens, qui veulent gouverner par la vertu et les rites, ils affirment que seule la loi, écrite, publique et appliquée à tous, peut assurer l’ordre.&lt;/p&gt; &lt;p&gt;Au IVe siècle av. J.-C., &lt;a href="https://fr.wikipedia.org/wiki/Shang_Yang" title=" Wikipedia"&gt;Shang Yang&lt;/a&gt; réforme le royaume de Qin : il encourage l’agriculture et la guerre, supprime les privilèges de la noblesse héréditaire et instaure des récompenses et des châtiments rigoureux, avec une responsabilité collective des familles. Shen Buhai insiste sur l’art de contrôler les fonctionnaires, Shen Dao sur la position de pouvoir. &lt;a href="https://fr.wikipedia.org/wiki/Han_Fei" title=" Wikipedia"&gt;Han Fei&lt;/a&gt; (vers 280-233 av. J.-C.), disciple du confucéen Xunzi, réunit la loi, la technique et la position en une doctrine complète. Puisque les hommes recherchent leur intérêt, inutile d’en appeler à leur bonté : le souverain doit les gouverner par la crainte et l’intérêt, rester secret et impénétrable, et faire fonctionner l’État comme une machine qui marche seule.&lt;/p&gt; &lt;p&gt;Le légisme triomphe quand &lt;a href="https://fr.wikipedia.org/wiki/Qin_Shi_Huang" title=" Wikipedia"&gt;Qin Shi Huang&lt;/a&gt; unifie la Chine en 221 av. J.-C. et fait brûler les livres des autres écoles. Discrédité par la chute rapide des Qin, il survit en pratique dans l’administration impériale, sous un vernis confucéen. Dans les années 1970, la campagne maoïste « contre Lin Biao et Confucius » en fait encore l’éloge.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F32" s="1" t="s">
         <v>164</v>
@@ -3840,8 +3848,10 @@
       <c r="D33" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>169</v>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Therav%C4%81da" title="Wikipedia"&gt;Le Bouddhisme Theravada&lt;/a&gt;, « l’enseignement des Anciens », est la plus ancienne forme du bouddhisme encore vivante. Il se réclame des premiers disciples du Bouddha et se transmet en pali. Sous le règne d’&lt;a href="https://fr.wikipedia.org/wiki/Ashoka" title=" Wikipedia"&gt;Ashoka&lt;/a&gt;, au IIIe siècle av. J.-C., le moine Mahinda l’introduit à Sri Lanka, d’où il gagne la Birmanie, la Thaïlande, le Cambodge et le Laos, où il reste majoritaire.&lt;/p&gt; &lt;p&gt;Ses textes forment le Canon pali, ou &lt;em&gt;Tipitaka&lt;/em&gt; (« trois corbeilles ») : la discipline monastique, les discours du Bouddha et l’&lt;em&gt;Abhidhamma&lt;/em&gt;, analyse philosophique des phénomènes, mis par écrit à Sri Lanka au Ier siècle av. J.-C. Au Ve siècle, &lt;a href="https://fr.wikipedia.org/wiki/Buddhaghosa" title=" Wikipedia"&gt;Buddhaghosa&lt;/a&gt; en donne la synthèse dans le &lt;em&gt;Chemin de la pureté&lt;/em&gt;. L’enseignement repose sur les quatre nobles vérités : la souffrance, son origine dans le désir, sa cessation et le Noble Sentier octuple qui y mène. Tout ce qui existe est impermanent, insatisfaisant et dépourvu de soi : la personne n’est qu’un assemblage changeant de cinq agrégats. L’idéal est l’&lt;em&gt;arhat&lt;/em&gt;, qui a éteint par sa propre pratique les feux du désir, de la haine et de l’illusion, alors que le Mahayana met en avant le bodhisattva, qui se consacre au salut de tous les êtres.&lt;/p&gt; &lt;p&gt;La méditation vipassana, « vision pénétrante », qui observe l’apparition et la disparition des phénomènes, a été remise à l’honneur en Birmanie au XXe siècle par des maîtres comme Mahasi Sayadaw ; elle a inspiré la « pleine conscience » répandue en Occident.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F33" s="1" t="s">
         <v>170</v>
@@ -3934,8 +3944,10 @@
       <c r="D35" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>181</v>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika"  title=" Wikipedia"&gt;Le Vaisheshika&lt;/a&gt;, de &lt;em&gt;viśeṣa&lt;/em&gt;, « particularité », est l’une des six écoles orthodoxes de la philosophie indienne. Ses &lt;em&gt;Vaiśeṣika Sūtra&lt;/em&gt; sont attribués au sage Kaṇāda, dont le nom signifierait « mangeur de grains », et datent sans doute des débuts de notre ère. Son but est la délivrance (&lt;em&gt;mokṣa&lt;/em&gt;), que procure la connaissance exacte des catégories du réel. Le système est surtout connu par le traité de Praśastapāda (VIe siècle), qui l’organise et le complète.&lt;/p&gt; &lt;p&gt;Le Vaisheshika classe tout ce qui existe en six catégories (&lt;em&gt;padārtha&lt;/em&gt;), auxquelles on ajoute plus tard la non-existence : la substance, la qualité, l’action, l’universel, la particularité et l’inhérence, relation qui unit par exemple une qualité à sa substance. Il compte neuf substances : la terre, l’eau, le feu et l’air, faits d’atomes éternels et indivisibles (&lt;em&gt;paramāṇu&lt;/em&gt;), puis l’éther, le temps, l’espace, l’âme et le sens interne. Les atomes s’assemblent par deux, puis par trois, pour former les objets visibles, qui eux sont périssables. Leurs mouvements sont guidés par l’&lt;em&gt;adṛṣṭa&lt;/em&gt;, la force invisible des actes passés ; les auteurs plus tardifs y ajoutent un Dieu ordonnateur, Īśvara. L’âme délivrée retrouve un état pur, sans plaisir ni douleur, car toute qualité liée au corps a cessé.&lt;/p&gt; &lt;p&gt;Très tôt associé au Nyâya, qui lui apporte sa logique, il forme avec lui le Nyāya-Vaiśeṣika. Son atomisme a souvent été comparé à celui de &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9mocrite" title=" Wikipedia"&gt;Démocrite&lt;/a&gt; ; mais là où Démocrite voyait le hasard, le Vaisheshika voit un ordre moral.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F35" s="9" t="s">
         <v>182</v>
@@ -4638,8 +4650,10 @@
       <c r="D50" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>270</v>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ishraqisme"  title="Wikipedia"&gt;L’Ishraqisme&lt;/a&gt;, ou philosophie de l’Illumination (&lt;em&gt;ishrâq&lt;/em&gt;, le lever du soleil), est le courant fondé par le penseur persan &lt;a href="https://fr.wikipedia.org/wiki/Sohrawardi" title=" Wikipedia"&gt;Sohrawardi&lt;/a&gt; (1154-1191). Dans son &lt;em&gt;Livre de la sagesse orientale&lt;/em&gt;, où l’« Orient » désigne la source de la lumière plutôt qu’un lieu, il veut unir la philosophie grecque, en particulier Platon et le néoplatonisme, la sagesse de l’ancienne Perse et la mystique soufie en une vision fondée sur la lumière.&lt;/p&gt; &lt;p&gt;Pour Sohrawardi, toute la réalité est un déploiement de la Lumière des lumières, qui est Dieu. Les êtres s’ordonnent selon leur degré de lumière, des intelligences angéliques jusqu’aux ténèbres de la matière, qui n’est que lumière absente. La connaissance véritable n’est pas d’abord un raisonnement : c’est une « connaissance par présence », immédiate, comme celle que l’âme a d’elle-même. Elle s’acquiert par la purification et l’expérience spirituelle autant que par la logique, et Sohrawardi critique sur ce point Avicenne. Il décrit aussi un monde intermédiaire entre l’esprit et le corps, le monde des images, où se situent les visions des prophètes et des mystiques. Ses récits symboliques, comme &lt;em&gt;Le Bruissement des ailes de Gabriel&lt;/em&gt;, racontent l’exil de l’âme et son retour vers l’Orient de la lumière.&lt;/p&gt; &lt;p&gt;Accusé d’hérésie par les juristes, il est exécuté à Alep avec l’accord de Saladin, d’où son surnom de « maître tué » (&lt;em&gt;al-maqtûl&lt;/em&gt;). Sa pensée nourrit pourtant l’école d’Ispahan et &lt;a href="https://fr.wikipedia.org/wiki/Molla_Sadra_Chirazi" title=" Wikipedia"&gt;Mollâ Sadrâ&lt;/a&gt;. &lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin" title=" Wikipedia"&gt;Henry Corbin&lt;/a&gt; l’a fait connaître en Occident au XXe siècle, en le traduisant et en le commentant.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F50" s="1" t="s">
         <v>271</v>
@@ -4686,8 +4700,10 @@
       <c r="D51" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="E51" s="22" t="s">
-        <v>276</v>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oconfucianisme"  title=" Wikipedia"&gt;Le Néoconfucianisme&lt;/a&gt; est le renouveau du confucianisme qui s’épanouit en Chine sous la dynastie Song (960-1279). Face au bouddhisme et au taoïsme, qui offraient une métaphysique et une spiritualité plus riches, des lettrés relisent les Classiques pour donner à la morale confucéenne un fondement cosmique. Devenu orthodoxie d’État, il domine la Chine jusqu’en 1905, ainsi que la Corée, le Japon et le Vietnam.&lt;/p&gt; &lt;p&gt;Zhou Dunyi médite sur le « Faîte suprême » d’où naissent le yin et le yang ; les frères Cheng distinguent en toute chose le &lt;em&gt;li&lt;/em&gt;, principe ou ordre rationnel, et le &lt;em&gt;qi&lt;/em&gt;, souffle ou énergie matérielle. &lt;a href="https://fr.wikipedia.org/wiki/Zhu_Xi" title=" Wikipedia"&gt;Zhu Xi&lt;/a&gt; (1130-1200) fait la synthèse de cette « école du Principe » : chaque être porte en lui le principe universel, et la nature humaine est bonne, comme le disait Mencius, mais obscurcie par un souffle impur. On se perfectionne par l’« investigation des choses », l’étude et la méditation assise. Ses commentaires des Quatre Livres servent de base aux examens impériaux de 1313 à 1905. Contre lui, Lu Jiuyuan puis &lt;a href="https://fr.wikipedia.org/wiki/Wang_Yangming" title=" Wikipedia"&gt;Wang Yangming&lt;/a&gt; (1472-1529) fondent l’« école du Cœur » : le principe n’est pas à chercher dans les choses mais dans le cœur, et la connaissance est inséparable de l’action.&lt;/p&gt; &lt;p&gt;Critiqué au XVIIIe siècle par l’école des études critiques, le &lt;em&gt;kaozheng&lt;/em&gt;, puis par la modernisation, il inspire encore au XXe siècle le « nouveau confucianisme ». En Corée, Yi Hwang et Yi I en débattent au XVIe siècle, et au Japon la doctrine de Zhu Xi devient celle du shogunat Tokugawa.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F51" s="9" t="s">
         <v>277</v>
@@ -5889,8 +5905,10 @@
       <c r="D76" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>397</v>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Ky%C5%8Dto"  title=" Wikipedia"&gt;L’école de Kyōto&lt;/a&gt; désigne le premier grand courant de philosophie moderne né au Japon, autour de &lt;a href="https://fr.wikipedia.org/wiki/Kitar%C5%8D_Nishida" title=" Wikipedia"&gt;Kitarō Nishida&lt;/a&gt; (1870-1945) et de ses successeurs à l’université impériale de Kyōto. On en fixe souvent le point de départ à 1911, date de la &lt;em&gt;Recherche sur le bien&lt;/em&gt;, où Nishida part de l’« expérience pure », antérieure à la séparation du sujet et de l’objet.&lt;/p&gt; &lt;p&gt;Ses penseurs, formés à la philosophie allemande, de Kant et Hegel à Husserl et Heidegger, veulent exprimer dans le langage de la philosophie occidentale l’expérience spirituelle de l’Asie, en particulier celle du bouddhisme zen et de la Terre pure. Au centre de leur réflexion se trouve la notion de « néant absolu » : non pas un simple manque, mais le fond ouvert d’où tout surgit, que Nishida pense comme le « lieu » (&lt;em&gt;basho&lt;/em&gt;) de toute réalité. Tanabe Hajime en tire une « philosophie de la repentance », et &lt;a href="https://fr.wikipedia.org/wiki/Keiji_Nishitani" title=" Wikipedia"&gt;Nishitani Keiji&lt;/a&gt; affronte le nihilisme européen : on ne le surmonte qu’en le traversant jusqu’à la vacuité. Watsuji Tetsurō et Kuki Shūzō, proches du groupe, l’ouvrent à l’éthique et à l’esthétique.&lt;/p&gt; &lt;p&gt;Plusieurs de ses membres furent compromis dans la justification idéologique de la guerre du Pacifique, ce qui a longtemps pesé sur sa réception. Depuis les années 1980, l’école est étudiée dans le monde entier comme le lieu d’un dialogue majeur entre la philosophie occidentale et les traditions spirituelles d’Asie. Ueda Shizuteru, mort en 2019, en a prolongé la pensée jusqu’à notre siècle.&lt;/p&gt;  &lt;audio controls title="Philosophie japonaise: l’école de Kyôto par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.11.2013-ITEMA_20549374-2013C12410E0320-NET_FC_EE7092B3-7D80-40AA-947D-AFAD338FBA01-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F76" s="1" t="s">
         <v>398</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -3225,8 +3225,10 @@
       <c r="D19" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>84</v>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka"  title="Wikipedia"&gt;Le Lokayata&lt;/a&gt;, « ce qui est répandu dans le monde », ou Chârvâka, est l’école &lt;a href="https://fr.wikipedia.org/wiki/Mat%C3%A9rialisme" title=" Wikipedia"&gt;matérialiste&lt;/a&gt; de l’Inde ancienne, la seule à rejeter à la fois les Védas, les dieux, l’âme immortelle et la loi du karma. Ses origines sont anciennes : des thèses matérialistes apparaissent dès le VIe siècle av. J.-C., et la tradition attribue ses premiers aphorismes, aujourd’hui perdus, au sage Brihaspati.&lt;/p&gt; &lt;p&gt;Pour le Lokayata, la perception est le seul moyen de connaissance valide. L’inférence est incertaine : de ce que la fumée a toujours accompagné le feu, on ne peut conclure qu’il en sera toujours ainsi, car on n’a pas observé tous les cas. Ce qui ne se perçoit pas, l’au-delà, l’âme ou le karma, n’est qu’invention. Le monde est fait de quatre éléments, la terre, l’eau, le feu et l’air ; la conscience naît de leur combinaison dans le corps, comme le pouvoir enivrant naît du mélange de certains ingrédients, et disparaît avec lui. Il n’y a donc ni renaissance ni délivrance. La morale qui en découle est hédoniste : le plaisir est le seul but, et les rites des brahmanes ne sont qu’un moyen pour les prêtres de gagner leur vie.&lt;/p&gt; &lt;p&gt;Ses textes ont disparu ; on le connaît par ses adversaires, qui le réfutent longuement, et par le traité sceptique de Jayarashi Bhatta (VIIIe siècle). Il a été redécouvert au XXe siècle comme un témoin de la pensée rationaliste indienne, notamment par Debiprasad Chattopadhyaya, qui y voit l’expression d’une culture populaire opposée aux brahmanes.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F19" s="1" t="s">
         <v>85</v>
@@ -3671,8 +3673,10 @@
       <c r="D29" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E29" s="16" t="s">
-        <v>146</v>
+      <c r="E29" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tao%C3%AFsme"  style="color:#d35400"  title=" Wikipedia"&gt;Le Taoïsme&lt;/a&gt; est, avec le confucianisme, l’une des deux grandes traditions de pensée nées en Chine. Il se réclame de &lt;a href="https://fr.wikipedia.org/wiki/Laozi" title=" Wikipedia"&gt;Laozi&lt;/a&gt;, sage peut-être légendaire du VIe siècle av. J.-C., auquel on attribue le &lt;em&gt;Daodejing&lt;/em&gt;, le « Livre de la Voie et de la Vertu », composé sans doute vers le IVe siècle av. J.-C., et de &lt;a href="https://fr.wikipedia.org/wiki/Tchouang-tseu" title=" Wikipedia"&gt;Zhuangzi&lt;/a&gt; (vers 370-287 av. J.-C.), dont le livre mêle fables, dialogues et paradoxes.&lt;/p&gt; &lt;p&gt;Au cœur du taoïsme se trouve le &lt;em&gt;dao&lt;/em&gt;, la Voie : l’origine sans forme de toutes choses et l’ordre spontané selon lequel elles se transforment. « La Voie qui peut être dite n’est pas la Voie constante » : elle échappe aux mots. Elle agit comme l’eau, souple et humble, qui finit par user la pierre. Le sage l’imite par le &lt;em&gt;wuwei&lt;/em&gt;, le « non-agir » : non pas l’inaction, mais une action sans effort ni contrainte, accordée au cours naturel des choses. Contre les confucéens, qui veulent régler la société par les rites et la morale, le taoïsme prône la simplicité, le retour à la nature et un gouvernement aussi discret que possible. Zhuangzi y ajoute un relativisme plein d’humour : ayant rêvé qu’il était papillon, il ne sait plus, au réveil, s’il est Zhuangzi qui a rêvé d’être papillon, ou un papillon qui rêve d’être Zhuangzi.&lt;/p&gt; &lt;p&gt;À partir du IIe siècle se forme aussi une religion taoïste, avec ses temples, ses rites et sa quête de longévité. Le taoïsme a inspiré la peinture, la médecine et les arts martiaux chinois, ainsi que le bouddhisme chan.&lt;/p&gt;  &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/10/s44/NET_FC_43660d0e-6519-4ba7-84a5-c6390767f7da.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F29" s="14" t="s">
         <v>147</v>
@@ -4089,8 +4093,10 @@
       <c r="D38" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="E38" s="20" t="s">
-        <v>198</v>
+      <c r="E38" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mazdakisme" title="Wikipedia"&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse à la fin du Ve siècle, sous l’Empire sassanide. Il tire son nom de Mazdak, prêtre réformateur dont la doctrine s’inspire d’un prédicateur plus ancien, Zaradusht de Fasa, et emprunte à la fois au zoroastrisme et au &lt;a href="https://fr.wikipedia.org/wiki/Manich%C3%A9isme_%28religion%29" title=" Wikipedia"&gt;manichéisme&lt;/a&gt;. Nous le connaissons surtout par ses adversaires, chroniqueurs perses, arabes et byzantins.&lt;/p&gt; &lt;p&gt;Comme les manichéens, Mazdak voit le monde comme un mélange de lumière et de ténèbres ; mais pour lui, la lumière agit librement et sciemment, tandis que les ténèbres agissent au hasard, ce qui rend la victoire du bien probable. Le mal humain vient surtout de cinq démons : l’envie, la colère, la vengeance, le besoin et la cupidité. Puisque l’inégalité des richesses nourrit ces passions, il faut partager les biens et, selon ses ennemis, les femmes, ce qui visait sans doute les vastes harems de l’aristocratie. Il prêche aussi la non-violence, le refus de tuer et un régime végétarien. Dans une période de famine, ce message rencontre un large écho populaire. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Kavadh_Ier" title=" Wikipedia"&gt;Kavadh Ier&lt;/a&gt; le soutient d’abord, peut-être pour affaiblir la noblesse et le clergé.&lt;/p&gt; &lt;p&gt;Mais vers 528, son fils, le futur &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, fait massacrer Mazdak et ses partisans. Le mouvement survit dans la clandestinité et inspire des révoltes en Iran à l’époque islamique. On l’a parfois présenté, de façon anachronique, comme un « communisme » avant la lettre.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F38" s="14" t="s">
         <v>199</v>
@@ -4320,8 +4326,10 @@
       <c r="D43" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>229</v>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adva%C3%AFta_v%C3%A9danta" title="Wikipedia"&gt;L’Advaïta Védanta&lt;/a&gt;, le « Védânta non dualiste », est la plus influente des écoles issues du Védânta, la réflexion sur les Upanishad, textes qui forment la « fin des Védas ». Sa thèse tient en une formule : le Soi individuel (&lt;em&gt;ātman&lt;/em&gt;) et l’Absolu (&lt;em&gt;brahman&lt;/em&gt;) ne font qu’un. Il est systématisé au VIIIe siècle par &lt;a href="https://fr.wikipedia.org/wiki/Adi_Shankara" title=" Wikipedia"&gt;Shankara&lt;/a&gt;, à la suite de Gaudapada.&lt;/p&gt; &lt;p&gt;Pour Shankara, seul le &lt;em&gt;brahman&lt;/em&gt; est pleinement réel : conscience pure, infinie et sans qualités, il est l’être même de toute chose. Le monde multiple que nous percevons n’est pas un pur néant, mais une apparence, &lt;em&gt;māyā&lt;/em&gt;, comparable à la corde que l’on prend dans la pénombre pour un serpent. Notre sentiment d’être un individu séparé vient de l’ignorance (&lt;em&gt;avidyā&lt;/em&gt;), qui attribue au Soi des caractères qui ne sont pas les siens : le corps, les sens, le moi. La délivrance (&lt;em&gt;mokṣa&lt;/em&gt;) n’est donc ni un lieu à atteindre ni le fruit d’actions ou de rites : elle est la connaissance directe de cette identité, exprimée par les grandes paroles des Upanishad, « Tu es Cela » ou « Je suis brahman ». Shankara fonde aussi des monastères aux quatre coins de l’Inde.&lt;/p&gt; &lt;p&gt;Contesté par Ramanuja et Madhva, qui défendent un Dieu personnel, l’Advaïta devient au XIXe siècle, avec &lt;a href="https://fr.wikipedia.org/wiki/Vivekananda" title=" Wikipedia"&gt;Vivekananda&lt;/a&gt;, le visage de l’hindouisme en Occident. Ramana Maharshi en a été au XXe siècle un maître célèbre, enseignant à ses visiteurs une seule question : « Qui suis-je ? ». On a souvent rapproché sa doctrine de Parménide, de Plotin ou de Spinoza.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F43" s="1" t="s">
         <v>230</v>
@@ -4748,8 +4756,10 @@
       <c r="D52" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>281</v>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bushido" title="Wikipedia"&gt;Le Bushido&lt;/a&gt;, la « voie du guerrier », désigne l’éthique des samouraïs, la classe militaire qui domine le Japon de l’époque de Kamakura (1185-1333) jusqu’au milieu du XIXe siècle. Ce n’est pas un code écrit unique, mais un ensemble de valeurs qui se forment peu à peu et ne sont mises en forme qu’à l’époque d’Edo (1603-1868), quand les guerriers, en temps de paix, deviennent administrateurs.&lt;/p&gt; &lt;p&gt;Le bushido mêle plusieurs sources : du confucianisme, il retient la loyauté envers le seigneur, la piété filiale et le sens du devoir ; du bouddhisme zen, la maîtrise de soi et le détachement face à la mort ; du shintō, le respect des ancêtres. Le guerrier doit être droit, courageux, bienveillant, poli, sincère, et préférer l’honneur à la vie : le suicide rituel, le &lt;em&gt;seppuku&lt;/em&gt;, permet d’effacer une faute ou d’échapper à la honte. Au XVIIe siècle, Yamaga Sokō définit le rôle moral du samouraï en temps de paix, et Miyamoto Musashi, dans le &lt;em&gt;Traité des cinq roues&lt;/em&gt;, fait de l’art du sabre une voie de perfection. Le &lt;a href="https://fr.wikipedia.org/wiki/Hagakure" title=" Wikipedia"&gt;&lt;em&gt;Hagakure&lt;/em&gt;&lt;/a&gt;, recueil des propos de Yamamoto Tsunetomo, affirme : « la voie du samouraï, je l’ai trouvée dans la mort ».&lt;/p&gt; &lt;p&gt;L’image moderne du bushido doit beaucoup à &lt;a href="https://fr.wikipedia.org/wiki/Inaz%C5%8D_Nitobe" title=" Wikipedia"&gt;Nitobe Inazō&lt;/a&gt;, dont le livre &lt;em&gt;Bushido, l’âme du Japon&lt;/em&gt; (1900), écrit en anglais, le présente comme une morale nationale comparable à la chevalerie. Exalté par le militarisme japonais jusqu’en 1945, il survit dans les arts martiaux et nourrit encore l’image que le monde se fait du Japon.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F52" s="1" t="s">
         <v>282</v>
@@ -6163,8 +6173,10 @@
       <c r="D81" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="E81" s="16" t="s">
-        <v>424</v>
+      <c r="E81" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9gritude"  title=" Wikipedia"&gt;La Négritude&lt;/a&gt; est un mouvement littéraire, culturel et politique né à Paris dans les années 1930 parmi les étudiants noirs venus d’Afrique et des Antilles. Le mot apparaît sous la plume du Martiniquais &lt;a href="https://fr.wikipedia.org/wiki/Aim%C3%A9_C%C3%A9saire" title=" Wikipedia"&gt;Aimé Césaire&lt;/a&gt; en 1935, dans la revue &lt;em&gt;L’Étudiant noir&lt;/em&gt;, puis dans son &lt;em&gt;Cahier d’un retour au pays natal&lt;/em&gt; (1939). Il retourne fièrement une insulte coloniale pour en faire l’affirmation d’une identité.&lt;/p&gt; &lt;p&gt;Avec le Sénégalais &lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9opold_S%C3%A9dar_Senghor" title=" Wikipedia"&gt;Léopold Sédar Senghor&lt;/a&gt; et le Guyanais &lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on-Gontran_Damas" title=" Wikipedia"&gt;Léon-Gontran Damas&lt;/a&gt;, Césaire refuse l’assimilation que propose la France coloniale, qui demande aux colonisés de renoncer à leur culture pour adopter celle de l’Europe. Ils revendiquent l’héritage des civilisations africaines, leurs arts, leurs langues et leurs valeurs. Pour Senghor, la négritude est « l’ensemble des valeurs culturelles du monde noir » ; il oppose parfois une raison africaine intuitive à la raison européenne analytique. Pour Césaire, elle est d’abord une révolte contre l’oppression : son &lt;em&gt;Discours sur le colonialisme&lt;/em&gt; (1950) dénonce la barbarie de l’Europe coloniale. En 1948, l’&lt;em&gt;Anthologie&lt;/em&gt; de Senghor, préfacée par Sartre sous le titre « Orphée noir », donne au mouvement un retentissement mondial.&lt;/p&gt; &lt;p&gt;Senghor devient en 1960 le premier président du Sénégal. La négritude a été critiquée pour son essentialisme, par Frantz Fanon, par Wole Soyinka (« le tigre ne proclame pas sa tigritude ») ou par les auteurs de la créolité, mais elle a ouvert la voie aux pensées postcoloniales.&lt;/p&gt;  &lt;audio controls title="Bonjour et adieu à la Négritude par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
       </c>
       <c r="F81" s="14" t="s">
         <v>425</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2470,8 +2470,15 @@
       <c r="D4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>18</v>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mythologie_%C3%A9gyptienne"  title=" Wikipedia"&gt; La Philosophie Egyptienne&lt;/a&gt;  (et la Mythologie Egyptienne) est l'une des plus anciennes traditions philosophiques du monde. Elle s'est développée en Égypte ancienne, principalement à partir de l'époque de l'Ancien Empire (vers 2700-2200 av. J.-C.) jusqu'à la période ptolémaïque (323-30 av. J.-C.), avec la domination des rois grecs. &lt;/p&gt; &lt;p&gt;
+La philosophie égyptienne était profondément influencée par les croyances religieuses et la spiritualité qui imprégnaient la société égyptienne. Les anciens Égyptiens avaient une vision du monde centrée sur la notion de maât, qui se traduit approximativement par l'ordre, l'équilibre et l'harmonie. La maât était considérée comme la force qui maintenait l'univers en ordre et qui devait également être préservée dans la société humaine. &lt;/p&gt; &lt;p&gt;
+Les textes sacrés, tels que les Textes des Pyramides et les Textes des Sarcophages, contiennent des éléments philosophiques importants. Ils abordent des sujets tels que l'existence de Dieu, la nature de l'âme, la vie après la mort et la moralité. Ces textes étaient destinés à guider les pharaons et les défunts dans leur voyage vers l'au-delà. &lt;/p&gt; &lt;p&gt;
+L'un des concepts centraux est la croyance en l'immortalité de l'âme. Les anciens Égyptiens pensaient que l'âme humaine était composée de plusieurs parties, notamment le ka (la force vitale), le ba (l'aspect personnel de l'âme) et le akh (l'aspect spirituel et immortel de l'âme). Ils croyaient que l'âme pouvait continuer à exister après la mort, à condition qu'elle puisse passer les différentes épreuves et jugements dans l'au-delà. &lt;/p&gt; &lt;p&gt;
+Elle accordait également une grande importance à la moralité et à la justice. Les Égyptiens croyaient en un système de rétribution après la mort, où les bonnes actions étaient récompensées et les mauvaises actions étaient punies. Ils pensaient que chaque individu était responsable de ses actes et qu'il devait vivre en accord avec les principes de maât pour atteindre une existence heureuse et équilibrée. &lt;/p&gt; &lt;p&gt;
+la plupart des textes philosophiques égyptiens ont été perdus au fil du temps. Les noms de quelques penseurs, comme Ptahhotep et Amenemopet, sont parvenus jusqu'à nous grâce à leurs écrits sur la moralité et la sagesse. Cependant, notre compréhension de la philosophie égyptienne repose principalement sur l'interprétation des textes religieux et funéraires.  &lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F4" s="9" t="s">
         <v>19</v>
@@ -2878,8 +2885,14 @@
       <c r="D12" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="16" t="s">
-        <v>46</v>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mystique#:~:text=La%20mystique%20a%20commenc%C3%A9%20%C3%A0,d%C3%A9bordant%20largement%20son%20tropisme%20chr%C3%A9tien."  title=" Wikipedia"&gt; Le Mysticisme &lt;/a&gt;  est un courant de pensée qui considère que l'expérience directe et personnelle de la réalité spirituelle est plus importante que la connaissance intellectuelle ou rationnelle. &lt;/p&gt; &lt;p&gt; Il désigne une quête de l'expérience de l'absolu, de l'union avec Dieu ou l'univers, qui dépasse les limites de la raison et de la perception sensorielle. Les mystiques cherchent à atteindre une expérience de l'unité avec la réalité ultime ou divine, souvent par le biais de pratiques spirituelles telles que la méditation, la prière, le jeûne, ou la contemplation. &lt;/p&gt; &lt;p&gt; 
+Historiquement, le mysticisme a été présent dans de nombreuses cultures et religions, telles que le christianisme, l'islam, le judaïsme, l'hindouisme, le bouddhisme et le taoïsme. Les mystiques, qu'ils soient des saints, des moines, des soufis, des yogis ou des chamans, ont cherché à transcender la condition humaine, à découvrir la réalité ultime et à vivre une expérience spirituelle intense. &lt;/p&gt; &lt;p&gt;
+Il est souvent considéré comme un domaine de la métaphysique, qui traite des questions de la réalité ultime, de l'existence de Dieu, de l'âme et de la nature de la conscience. Les mystiques affirment souvent que la réalité ultime est inconnaissable ou ineffable, et que la seule façon de la comprendre est par l'expérience directe.&lt;/p&gt; &lt;p&gt; 
+Cependant, le mysticisme a également été critiqué par certains philosophes, qui ont affirmé que les expériences mystiques ne sont pas fiables ou vérifiables par la méthode scientifique ou rationnelle. Ils ont également souligné que le mysticisme peut être sujet à des interprétations erronées ou à des pratiques dangereuses. &lt;/p&gt;    &lt;audio controls title="Capitalisme et mysticisme par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/09/s38/Frontieres--PODCAST--NET_2a264117-0835-4f8f-8e8c-c672a19641ab_FC.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F12" s="14" t="s">
         <v>47</v>
@@ -3365,7 +3378,7 @@
 Dans la philosophie Ubuntu, chaque individu est considéré comme étant en relation avec les autres et le monde qui l'entoure. Les relations humaines sont au cœur de cette philosophie, et l'identité d'une personne est déterminée en grande partie par sa relation avec les autres membres de sa communauté. Selon Ubuntu, nous sommes tous liés et notre bien-être individuel est intrinsèquement lié au bien-être collectif. &lt;/p&gt; &lt;p&gt;
 Un proverbe couramment cité pour illustrer cette philosophie est : « Umuntu ngumuntu ngabantu », ce qui signifie « Je suis ce que je suis grâce à ce que nous sommes tous ». Cela souligne l'idée que notre humanité commune se manifeste dans nos interactions et nos relations avec les autres. La philosophie Ubuntu encourage donc l'empathie, la solidarité et le respect mutuel. &lt;/p&gt; &lt;p&gt;
 Elle a également des implications politiques et sociales et met l'accent sur l'importance de la justice, de la réconciliation et de la coopération dans la construction de sociétés harmonieuses et est souvent invoqué comme une base éthique pour guider les décisions politiques et promouvoir la tolérance, la compréhension et la paix. &lt;/p&gt; &lt;p&gt;
-Il convient de noter que la philosophie Ubuntu ne se limite pas à l'Afrique subsaharienne. Elle a inspiré des penseurs et des leaders du monde entier qui reconnaissent l'importance des relations humaines et de la solidarité pour créer des sociétés justes et inclusives. &lt;/p&gt; &lt;p&gt;Ce n’est qu’au XXe siècle que l’Ubuntu devient une philosophie écrite. En 1980, au Zimbabwe, Stanlake et Tommie Marie Samkange publient &lt;em&gt;Hunhuism or Ubuntuism&lt;/em&gt;, qui en fait le fondement d’une pensée politique africaine. En Afrique du Sud, la Constitution provisoire de 1993 invoque « un besoin d’ubuntu, et non de victimisation » pour sortir de l’apartheid. L’archevêque &lt;a href="https://fr.wikipedia.org/wiki/Desmond_Tutu" title=" Wikipedia"&gt;Desmond Tutu&lt;/a&gt; en fait l’esprit de la Commission vérité et réconciliation, qu’il préside à partir de 1995, et le défend dans &lt;em&gt;Il n’y a pas d’avenir sans pardon&lt;/em&gt; (1999). La même année, le philosophe Mogobe Ramose publie &lt;em&gt;African Philosophy through Ubuntu&lt;/em&gt;, qui en propose une lecture métaphysique : l’être n’est pas une chose figée, mais un mouvement de relations.&lt;/p&gt;  &lt;audio controls title="Ubuntu ou l'histoire, les valeurs et la mémoire par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/08/s32/RF_DF1DF1B4-FF64-438F-BC47-78A44A7FA537_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+Il convient de noter que la philosophie Ubuntu ne se limite pas à l'Afrique subsaharienne. Elle a inspiré des penseurs et des leaders du monde entier qui reconnaissent l'importance des relations humaines et de la solidarité pour créer des sociétés justes et inclusives. &lt;/p&gt; &lt;p&gt;Ce n’est qu’au XXe siècle que l’Ubuntu devient une philosophie écrite. En 1980, au Zimbabwe, Stanlake et Tommie Marie Samkange publient &lt;em&gt;Hunhuism or Ubuntuism&lt;/em&gt;, qui en fait le fondement d’une pensée politique africaine. En Afrique du Sud, la Constitution provisoire de 1993 invoque « un besoin d’ubuntu, et non de victimisation » pour sortir de l’apartheid. L’archevêque &lt;a href="https://fr.wikipedia.org/wiki/Desmond_Tutu" title=" Wikipedia"&gt;Desmond Tutu&lt;/a&gt; en fait l’esprit de la Commission vérité et réconciliation, qu’il préside à partir de 1995, et le défend dans &lt;em&gt;Il n’y a pas d’avenir sans pardon&lt;/em&gt; (1999). La même année, le philosophe Mogobe Ramose publie &lt;em&gt;African Philosophy through Ubuntu&lt;/em&gt;, qui en propose une lecture métaphysique : l’être n’est pas une chose figée, mais un mouvement de relations.&lt;/p&gt;  &lt;audio controls title="Ubuntu ou l'histoire, les valeurs et la mémoire par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/08/s32/RF_DF1DF1B4-FF64-438F-BC47-78A44A7FA537_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F22" s="14" t="s">
@@ -3539,8 +3552,10 @@
       <c r="D26" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>128</v>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bouddhisme"  title=" Wikipedia"&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt; &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F26" s="9" t="s">
         <v>129</v>
@@ -3631,8 +3646,13 @@
       <c r="D28" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>140</v>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shinto%C3%AFsme"  style="color:#d35400"  title=" Wikipedia"&gt;Le Shintoïsme&lt;/a&gt; est une religion philosophique autochtone du Japon. Le mot "shinto" signifie littéralement "la voie des dieux" ou "la voie des kami". Les kami sont des esprits ou des divinités vénérées dans la tradition shintoïste. &lt;/p&gt; &lt;p&gt;
+Le shintoïsme est souvent considéré comme une religion animiste, car il accorde une grande importance à la nature et aux phénomènes naturels. Les montagnes, les rivières, les arbres et autres éléments naturels sont vus comme abritant des kami, et ces kami sont vénérés et respectés. Les humains, en tant qu'êtres vivants, sont également considérés comme ayant une âme, et ils sont connectés aux kami et à la nature qui les entoure. Une caractéristique importante du shintoïsme est le culte des ancêtres. Les ancêtres décédés sont également considérés comme des kami et sont vénérés dans les sanctuaires shintoïstes familiaux.  &lt;/p&gt; &lt;p&gt;
+Le shintoïsme n'a pas de texte sacré, il se compose d'une multitude de mythes, de récits et de traditions transmises oralement de génération en génération. Les sanctuaires shintoïstes sont des lieux importants de pratique religieuse. Ils sont souvent situés au milieu de la nature et comprennent des bâtiments sacrés, des autels et des torii (portails d'entrée). &lt;/p&gt; &lt;p&gt;
+Le shintoïsme a une forte influence sur la culture japonaise. De nombreux festivals et cérémonies au Japon sont de nature shintoïste. Par exemple, le festival du Nouvel An, appelé "Hatsumode", est une célébration importante où les gens se rendent dans les sanctuaires pour prier, faire des offrandes et purifier leur esprit pour la nouvelle année. &lt;/p&gt; &lt;p&gt; Bien que ce ne soit pas une religion qui développe une philosophie systématique comme le bouddhisme ou le confucianisme, il offre une perspective favorisant l'harmonie avec la nature, le respect des ancêtres et la recherche de la pureté spirituelle. Ces idées peuvent être explorées et interprétées dans un contexte philosophique plus large. &lt;/p&gt;  &lt;audio controls title="Le shinto n'est pas une religion à système, c'est un ensemble de croyance très ancienne par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-13.08.2020-ITEMA_22401465-2018C3372E0676-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F28" s="9" t="s">
         <v>141</v>
@@ -4233,8 +4253,15 @@
       <c r="D41" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E41" s="11" t="s">
-        <v>219</v>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mutazilisme"  title=" Wikipedia"&gt;Le Mutazilisme&lt;/a&gt;  était un courant théologique et philosophique qui a émergé au sein de l'islam sunnite. Le terme "mutazilisme" dérive du mot arabe "itizal", qui signifie "se séparer" ou "se retirer".  Il est considéré comme l'une des premières écoles théologiques islamiques rationalistes, cherchant à combiner la foi et la raison. Ils croyaient que la raison humaine était une source importante de connaissances et qu'elle devait être utilisée pour interpréter les enseignements religieux. Les mutazilites rejetaient l'idée que le Coran était la parole incréée de Dieu, affirmant plutôt que le Coran était créé et qu'il devait être interprété à la lumière de la raison. &lt;/p&gt; &lt;p&gt;
+Un des principaux enseignements du mutazilisme était la doctrine de la "Justice divine" (Al-'Adl wa al-Tawhid). Selon cette doctrine, Dieu était juste et ne pouvait pas ordonner ou commettre des actes injustes. Ils soutenaient également le concept de libre arbitre humain, affirmant que les humains étaient responsables de leurs propres actes et qu'ils devaient être récompensés ou punis en fonction de leurs actions. &lt;/p&gt; &lt;p&gt; Les principes fondamentaux du mutazilisme comprennent : &lt;/p&gt;
+&lt;p&gt;Tawhid : l'unicité de Dieu, affirmant qu'il n'y a qu'un seul Dieu et qu'il est indivisible. &lt;/p&gt;
+&lt;p&gt;Adl : la justice de Dieu, soutenant que Dieu est juste et ne peut commettre d'injustice. &lt;/p&gt;
+&lt;p&gt; Al-'Aql wa al-Naql : affirmant que la raison et la révélation divine doivent être en harmonie. &lt;/p&gt;
+&lt;p&gt;A partir du IXe siècle, le courant a perdu de son influence en raison de l'opposition des théologiens conservateurs et de l'arrivée au pouvoir de califes plus traditionalistes et a graduellement décliné en tant que courant théologique distinct, bien qu'il ait laissé une empreinte durable sur le développement de la pensée islamique. &lt;/p&gt; &lt;audio controls title="Le néo mutazilisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-13.10.2019-ITEMA_22174473-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F41" s="9" t="s">
         <v>220</v>
@@ -4280,8 +4307,11 @@
       <c r="D42" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E42" s="19" t="s">
-        <v>224</v>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/V%C3%A9danta"  title=" Wikipedia"&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;
+</t>
+        </is>
       </c>
       <c r="F42" s="14" t="s">
         <v>225</v>
@@ -4373,8 +4403,14 @@
       <c r="D44" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="E44" s="11" t="s">
-        <v>235</v>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Soufisme" title=" Wikipedia"&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;
+Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou "soufis") qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; 
+Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;
+Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;
+Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title="Qu'est ce que le Soufisme ? par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
       </c>
       <c r="F44" s="9" t="s">
         <v>236</v>
@@ -5039,7 +5075,7 @@
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fondamentalisme"   title=" Wikipedia"&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient, principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fondamentalisme"   title=" Wikipedia"&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient, principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : la contestation des lois civiles au nom de la loi divine ; la mobilisation électorale ou militante de groupes religieux ; parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; 
  &lt;audio controls title="les religions ; le fondamentalisme chrétien par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
@@ -5455,8 +5491,12 @@
       <c r="D66" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="E66" s="16" t="s">
-        <v>344</v>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Occidentalisme"  title=" Wikipedia"&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; 
+ &lt;audio controls title="l’Occidentalisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
+</t>
+        </is>
       </c>
       <c r="F66" s="14" t="s">
         <v>345</v>
@@ -5552,8 +5592,11 @@
       <c r="D68" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="E68" s="16" t="s">
-        <v>354</v>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Intuitivisme"  title=" Wikipedia"&gt; L’Intuitivisme&lt;/a&gt;  est un courant philosophique russe qui privilégie la connaissance immédiate par l'intuition plutôt que par la médiation des sens ou des concepts. Il s'inscrit dans une tradition mystique orthodoxe où philosophie et religion fusionnent, rejetant le dualisme sujet-objet propre à la pensée occidentale. Ses figures emblématiques, comme Nicolas Lossky et Siméon Frank, en font un pilier de la philosophie russe spiritualiste. &lt;/p&gt; &lt;p&gt; Ce courant repose sur le principe d'une saisie directe de la réalité, où l'être se présente originairement dans la conscience sans voile ni intermédiaire. Lossky, par exemple, critique le kantisme en affirmant que les objets de la connaissance sont les "choses en soi" et non des phénomènes construits, grâce à une intuition qui transcende les sensations. Vrai et être y sont identiques, garantissant une vérité objective par la présence même de l'objet dans l'esprit. &lt;/p&gt; &lt;p&gt; Lossky distingue trois formes d'intuition : sensible (sur le monde et le corps), intellectuelle (sur les lois idéales) et mystique (sur Dieu et les sphères métalogiques). Cette triade permet une connaissance intégrale, incluant le religieux sans justification épistémologique séparée. Elle surmonte ainsi le "dédoublement artificiel" du monde opéré par les sensations, vues comme trans-subjectives et objectives. &lt;/p&gt; &lt;p&gt; L'intuitivisme s'oppose à l'épistémologie occidentale, valorisant l'ontologisme où l'être prime sur le savoir. Il prolonge les slavophiles et Soloviev, dans un climat de tension entre Logos mystique et ratio discursive. Sous l'ère soviétique, des penseurs comme B. N. Babynine l'adaptent à un réalisme matérialiste, via des recueils comme Les voies du réalisme. &lt;/p&gt; &lt;p&gt; Malgré la révolution bolchevique, l'intuitivisme persiste en émigration et influence la pensée religieuse russe, affirmant une union possible entre l'esprit humain et le divin sur Terre. Il incarne le refus russe d'une connaissance fragmentée, au profit d'une vision unitaire et vivante de la réalité. Ce courant reste une clé pour comprendre la spécificité philosophique russe. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F68" s="14" t="s">
         <v>355</v>
@@ -5871,8 +5914,11 @@
       <c r="D75" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="E75" s="21" t="s">
-        <v>391</v>
+      <c r="E75" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Empiriomonisme"  title="Wikipedia"&gt;L’Empiriomonisme&lt;/a&gt; est une doctrine philosophique développée par Alexandre Bogdanov qui cherche à penser la réalité comme une expérience unique et organisée, en refusant le dualisme strict entre matière et esprit. Bogdanov veut réunir l’empirisme et le monisme. Autrement dit, il affirme que toute connaissance vient de l’expérience, mais que cette expérience forme un tout cohérent, sans séparation fondamentale entre le monde physique et le monde psychique.&lt;/p&gt; &lt;p&gt; Les sources résument souvent sa pensée en trois grands points : le réalisme naïf, selon lequel nous percevons les choses telles qu’elles sont ; la primauté de la nature, qui signifie que les formes simples de la réalité sont premières ; le caractère secondaire de l’esprit, vu comme un produit de formes plus complexes d’organisation de l’expérience. &lt;/p&gt; &lt;p&gt; Dans cette perspective, la connaissance n’est pas une copie passive du monde : elle est une manière d’ordonner l’expérience. Bogdanov insiste sur des notions comme l’expérience et l’organisation, qui annoncent aussi sa future théorie de la tектologie, une science générale de l’organisation. &lt;/p&gt; &lt;p&gt; Il a été vivement critiqué par Lénine et Plekhanov, qui l’accusaient de dérive idéaliste et de révision du marxisme. Aujourd’hui, on le lit surtout comme un moment important des débats philosophiques du marxisme russe. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F75" s="1" t="s">
         <v>392</v>
@@ -6221,8 +6267,11 @@
       <c r="D82" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="E82" s="23" t="s">
-        <v>429</v>
+      <c r="E82" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Doctrine_Jdanov"  title=" Wikipedia"&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; 
+</t>
+        </is>
       </c>
       <c r="F82" s="1" t="s">
         <v>430</v>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -2831,61 +2831,197 @@
         </is>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="353.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+    <row r="11" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1">
+        <v>350</v>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">350</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yogācāra</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Yogachara" title=" Wikipedia (en)"&gt;Le Yogācāra&lt;/a&gt;, « pratique du yoga », appelé aussi Cittamātra, « esprit seul », est avec le Madhyamaka l’une des deux grandes écoles philosophiques du bouddhisme mahāyāna. Il se forme en Inde au IVe siècle autour de deux frères, Asaṅga et Vasubandhu, à partir de l’expérience des méditants : ce que l’on observe en méditation montre combien le monde vécu est façonné par l’esprit. On doit à Vasubandhu deux courts traités, les &lt;em&gt;Vingt stances&lt;/em&gt; et les &lt;em&gt;Trente stances&lt;/em&gt;, qui résument la doctrine.&lt;/p&gt; &lt;p&gt;Sa thèse est que nous ne connaissons jamais que des représentations : les objets que nous croyons extérieurs sont des apparitions de la conscience, comme dans un rêve. Pour l’expliquer, il ajoute aux six consciences reconnues par le bouddhisme une conscience souillée, qui produit l’illusion d’un moi, et surtout une &lt;a href="https://fr.wikipedia.org/wiki/%C4%80layavij%C3%B1%C4%81na" title=" Wikipedia"&gt;conscience-réceptacle&lt;/a&gt; (&lt;em&gt;ālayavijñāna&lt;/em&gt;), sorte d’inconscient où les actes passés déposent des traces, comme des graines qui germeront plus tard. Il décrit aussi « trois natures » des choses : imaginaire, dépendante et parfaitement accomplie. L’éveil consiste à transformer ce fond de la conscience, jusqu’à ce que cesse le partage entre un sujet qui saisit et un objet saisi.&lt;/p&gt; &lt;p&gt;Ses logiciens, Dignāga puis Dharmakīrti, fondent la grande épistémologie bouddhique. Le pèlerin chinois &lt;a href="https://fr.wikipedia.org/wiki/Xuanzang" title=" Wikipedia"&gt;Xuanzang&lt;/a&gt; rapporte ses textes d’Inde au VIIe siècle et fonde en Chine l’école de la « conscience seule ». Le Yogācāra a nourri le zen, le bouddhisme tibétain et, aujourd’hui, le dialogue avec la phénoménologie et les sciences cognitives.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z51s7i1YZi0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Yogacara: consciousness is the final boss." par Boddhisattvas108</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">école bouddhiste de « l’esprit seul » : le monde que nous percevons est une construction de la conscience.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie de l'esprit;Métaphysique;Épistémologie</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASANGA;VASUBANDHU;XUANZANG</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1">
+        <v>402</v>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">402</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme de la Terre pure</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;Le bouddhisme de la &lt;a href="https://fr.wikipedia.org/wiki/Terre_pure" title=" Wikipedia"&gt;Terre pure&lt;/a&gt; est le courant du bouddhisme mahāyāna centré sur la dévotion au bouddha Amitābha (Amida en japonais) qui, selon les sūtras, a fait le vœu d’accueillir dans sa « Terre pure », un paradis situé à l’Occident, tous ceux qui l’invoquent avec foi. Né en Chine, il remonte à Huiyuan, qui réunit en 402 au mont Lu une communauté vouée à Amitābha, puis à &lt;a href="https://fr.wikipedia.org/wiki/Tanluan" title=" Wikipedia"&gt;Tanluan&lt;/a&gt; et à Shandao, qui en font une école.&lt;/p&gt; &lt;p&gt;Sa philosophie part d’un constat : en cette époque de « déclin de la Loi », les êtres humains ne peuvent plus atteindre l’éveil par leurs propres forces, par la méditation ou l’ascèse. Il faut s’en remettre à la « force de l’autre », la compassion d’Amitābha. La pratique principale devient la récitation de son nom, le &lt;em&gt;nembutsu&lt;/em&gt; : « Namu Amida Butsu ». Au Japon, Hōnen fonde en 1175 l’école &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_sh%C5%AB" title=" Wikipedia"&gt;Jōdo shū&lt;/a&gt; et affirme que cette seule récitation suffit au salut, ce qui ouvre le bouddhisme aux gens simples, aux paysans et aux femmes. Son disciple Shinran va plus loin avec le &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_shinsh%C5%AB" title=" Wikipedia"&gt;Jōdo shinshū&lt;/a&gt; : le salut est entièrement un don reçu dans la foi, et c’est le « méchant » conscient de ses fautes, plus encore que le juste, que le Bouddha veut sauver. Shinran se marie, quitte la vie monastique et vit parmi le peuple.&lt;/p&gt; &lt;p&gt;Devenue l’une des formes du bouddhisme les plus pratiquées d’Asie de l’Est, la Terre pure évoque la doctrine chrétienne de la grâce, rapprochement qui a fasciné bien des théologiens occidentaux. Elle compte aujourd’hui des dizaines de millions de fidèles au Japon, en Chine, en Corée et au Viêt Nam.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7mR5e1LZOTA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Comprendre la Terre Pure du Bouddha Amida" par Greg le Bonze - Bouddhisme Jôdo Shinshû</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bouddhisme de la foi en Amitābha : le salut par la récitation de son nom et la « force de l’autre ».</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HŌNEN;SHINRAN</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">asie-est</t>
+        </is>
+      </c>
+      <c r="N12"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="353.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C13" s="1" t="n">
         <v>720</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D13" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E13" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">jnuSRt72dqw</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"Introduction à la philosophie juive : le Kalām musulman" par Ikarim</t>
         </is>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J13" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
         </is>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="n">
+    <row r="14" customFormat="false" ht="132.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="n">
         <v>1090</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mystique#:~:text=La%20mystique%20a%20commenc%C3%A9%20%C3%A0,d%C3%A9bordant%20largement%20son%20tropisme%20chr%C3%A9tien."  title=" Wikipedia"&gt; Le Mysticisme &lt;/a&gt;  est un courant de pensée qui considère que l'expérience directe et personnelle de la réalité spirituelle est plus importante que la connaissance intellectuelle ou rationnelle. &lt;/p&gt; &lt;p&gt; Il désigne une quête de l'expérience de l'absolu, de l'union avec Dieu ou l'univers, qui dépasse les limites de la raison et de la perception sensorielle. Les mystiques cherchent à atteindre une expérience de l'unité avec la réalité ultime ou divine, souvent par le biais de pratiques spirituelles telles que la méditation, la prière, le jeûne, ou la contemplation. &lt;/p&gt; &lt;p&gt; 
 Historiquement, le mysticisme a été présent dans de nombreuses cultures et religions, telles que le christianisme, l'islam, le judaïsme, l'hindouisme, le bouddhisme et le taoïsme. Les mystiques, qu'ils soient des saints, des moines, des soufis, des yogis ou des chamans, ont cherché à transcender la condition humaine, à découvrir la réalité ultime et à vivre une expérience spirituelle intense. &lt;/p&gt; &lt;p&gt;
@@ -2894,161 +3030,75 @@
 </t>
         </is>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G14" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="2" t="s">
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Christianisme antique et médiéval</t>
-        </is>
-      </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Néoplatonisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9neutique_biblique" title=" Wikipedia"&gt;L’Herméneutique juive&lt;/a&gt; désigne l’ensemble des méthodes d’interprétation des textes sacrés du judaïsme : la Torah et la Bible hébraïque, puis la Mishna et le &lt;a href="https://fr.wikipedia.org/wiki/Talmud" title=" Wikipedia"&gt;Talmud&lt;/a&gt;. Elle repose sur une idée fondatrice : à côté de la Torah écrite, Moïse aurait reçu au Sinaï une Torah orale, transmise de maître à disciple, qui en donne le sens. Le texte n’est donc jamais clos, il appelle un commentaire sans fin, et l’étude elle-même devient un acte religieux. « La Torah a soixante-dix visages », dit un adage rabbinique.&lt;/p&gt; &lt;p&gt;Cette tradition prend forme avec les sages de l’époque du Second Temple. Hillel, vers le début de notre ère, formule sept règles d’interprétation, que Rabbi Ishmaël porte à treize au IIe siècle, tandis que Rabbi Akiva cherche un sens à chaque lettre. Le &lt;a href="https://fr.wikipedia.org/wiki/Midrash" title=" Wikipedia"&gt;midrash&lt;/a&gt; commente les versets pour en tirer soit des lois (&lt;em&gt;halakha&lt;/em&gt;), soit des récits et des leçons morales (&lt;em&gt;aggada&lt;/em&gt;). La Mishna, mise par écrit vers 200, puis les Talmuds de Jérusalem et de Babylone, achevés vers 400 et 500, consignent des débats où l’opinion minoritaire est conservée à côté de celle qui l’emporte. Au Moyen Âge, on distingue quatre niveaux de sens, résumés par le mot PaRDeS : &lt;em&gt;peshat&lt;/em&gt;, le sens littéral, &lt;em&gt;remez&lt;/em&gt;, l’allusion, &lt;em&gt;derash&lt;/em&gt;, l’interprétation, et &lt;em&gt;sod&lt;/em&gt;, le secret mystique de la Kabbale.&lt;/p&gt; &lt;p&gt;Rachi de Troyes, Maïmonide et Nahmanide en sont les grands commentateurs. Au XXe siècle, Emmanuel Levinas renouvelle la lecture du Talmud, et cette tradition a nourri les théories modernes de l’interprétation.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensée juive</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines"  title=" Wikipedia"&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les conceptions religieuses et philosophiques des civilisations de Mésoamérique, du Mexique central au Guatemala : les Olmèques dès le IIe millénaire avant notre ère, puis les Mayas, les Toltèques et les Aztèques. Malgré leur diversité, elles partagent la vision d’un monde sacré, cyclique et fragile, dont l’équilibre dépend de l’action des humains. Elles nous sont connues par les codex peints, les inscriptions mayas, l’architecture des cités et les récits recueillis après la conquête espagnole.&lt;/p&gt; &lt;p&gt;Le temps y est pensé en cycles : le calendrier rituel de 260 jours et l’année solaire de 365 jours se combinent en un « siècle » de 52 ans, et les Mayas datent aussi les événements sur de très longues périodes, le « compte long », depuis une origine mythique fixée en 3114 av. J.-C. Pour les Aztèques, le monde actuel est le cinquième « Soleil », après quatre créations détruites ; les dieux se sont sacrifiés pour mettre ce soleil en mouvement, et les humains leur doivent en retour leur propre sang. Le sacrifice est ainsi pensé comme une dette cosmique, nécessaire pour que le soleil poursuive sa course. Le &lt;em&gt;Popol Vuh&lt;/em&gt;, livre sacré des Mayas quichés, raconte la création des humains, façonnés dans le maïs après plusieurs essais manqués. La figure de &lt;a href="https://fr.wikipedia.org/wiki/Quetzalc%C3%B3atl" title=" Wikipedia"&gt;Quetzalcóatl&lt;/a&gt;, le Serpent à plumes, est associée au savoir, aux arts et au calendrier.&lt;/p&gt; &lt;p&gt;Les sages aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s’interrogeaient sur la vérité et la fragilité de l’existence. Leur pensée a été étudiée comme une véritable philosophie par Miguel León-Portilla.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="n">
-        <v>-700</v>
-      </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+        <v>50</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Christianisme antique et médiéval</t>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoplatonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herm%C3%A9neutique_biblique" title=" Wikipedia"&gt;L’Herméneutique juive&lt;/a&gt; désigne l’ensemble des méthodes d’interprétation des textes sacrés du judaïsme : la Torah et la Bible hébraïque, puis la Mishna et le &lt;a href="https://fr.wikipedia.org/wiki/Talmud" title=" Wikipedia"&gt;Talmud&lt;/a&gt;. Elle repose sur une idée fondatrice : à côté de la Torah écrite, Moïse aurait reçu au Sinaï une Torah orale, transmise de maître à disciple, qui en donne le sens. Le texte n’est donc jamais clos, il appelle un commentaire sans fin, et l’étude elle-même devient un acte religieux. « La Torah a soixante-dix visages », dit un adage rabbinique.&lt;/p&gt; &lt;p&gt;Cette tradition prend forme avec les sages de l’époque du Second Temple. Hillel, vers le début de notre ère, formule sept règles d’interprétation, que Rabbi Ishmaël porte à treize au IIe siècle, tandis que Rabbi Akiva cherche un sens à chaque lettre. Le &lt;a href="https://fr.wikipedia.org/wiki/Midrash" title=" Wikipedia"&gt;midrash&lt;/a&gt; commente les versets pour en tirer soit des lois (&lt;em&gt;halakha&lt;/em&gt;), soit des récits et des leçons morales (&lt;em&gt;aggada&lt;/em&gt;). La Mishna, mise par écrit vers 200, puis les Talmuds de Jérusalem et de Babylone, achevés vers 400 et 500, consignent des débats où l’opinion minoritaire est conservée à côté de celle qui l’emporte. Au Moyen Âge, on distingue quatre niveaux de sens, résumés par le mot PaRDeS : &lt;em&gt;peshat&lt;/em&gt;, le sens littéral, &lt;em&gt;remez&lt;/em&gt;, l’allusion, &lt;em&gt;derash&lt;/em&gt;, l’interprétation, et &lt;em&gt;sod&lt;/em&gt;, le secret mystique de la Kabbale.&lt;/p&gt; &lt;p&gt;Rachi de Troyes, Maïmonide et Nahmanide en sont les grands commentateurs. Au XXe siècle, Emmanuel Levinas renouvelle la lecture du Talmud, et cette tradition a nourri les théories modernes de l’interprétation.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="J15" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -3056,68 +3106,39 @@
       </c>
       <c r="P15" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ésotérismes et gnoses</t>
-        </is>
-      </c>
-      <c r="Q15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Egypte antique;Platonisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1">
-        <v>1200</v>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1200</t>
-        </is>
-      </c>
-      <c r="D16" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kabbale</t>
-        </is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kabbale" title=" Wikipedia"&gt;La Kabbale&lt;/a&gt;, la « tradition reçue », est la grande tradition mystique et ésotérique du judaïsme. Elle apparaît à la fin du XIIe siècle en Provence, puis en Catalogne, où Nahmanide, à Gérone, lui donne son autorité, et en Castille, où &lt;a href="https://fr.wikipedia.org/wiki/Mo%C3%AFse_de_Le%C3%B3n" title=" Wikipedia"&gt;Moïse de León&lt;/a&gt; compose vers 1280 le &lt;em&gt;Zohar&lt;/em&gt;, « livre de la Splendeur », qui en devient le texte majeur.&lt;/p&gt; &lt;p&gt;Elle distingue en Dieu l’&lt;em&gt;En Sof&lt;/em&gt;, « l’Infini », absolument caché, et les dix &lt;a href="https://fr.wikipedia.org/wiki/Sephiroth_%28Kabbale%29" title=" Wikipedia"&gt;&lt;em&gt;sefirot&lt;/em&gt;&lt;/a&gt;, émanations par lesquelles il se manifeste : sagesse, intelligence, amour, rigueur, beauté, jusqu’à la &lt;a href="https://fr.wikipedia.org/wiki/Shekhina" title=" Wikipedia"&gt;&lt;em&gt;Shekhina&lt;/em&gt;&lt;/a&gt;, la présence divine dans le monde, que la Kabbale conçoit comme féminine et exilée avec le peuple. Chaque mot de la Torah, chaque commandement accompli, agit sur l’harmonie de ces puissances. Après l’expulsion des Juifs d’Espagne, en 1492, la Kabbale se renouvelle à Safed, en Galilée, autour d’&lt;a href="https://fr.wikipedia.org/wiki/Isaac_Louria" title=" Wikipedia"&gt;Isaac Louria&lt;/a&gt;. Pour faire place au monde, l’Infini a dû se retirer en lui-même : c’est le &lt;a href="https://fr.wikipedia.org/wiki/Tsimtsoum" title=" Wikipedia"&gt;&lt;em&gt;tsimtsoum&lt;/em&gt;&lt;/a&gt;. Puis les « vases » qui devaient recevoir sa lumière se sont brisés, et des étincelles divines sont tombées dans la matière. La tâche de l’être humain est le &lt;a href="https://fr.wikipedia.org/wiki/Tikkoun_Olam" title=" Wikipedia"&gt;&lt;em&gt;tikkoun&lt;/em&gt;&lt;/a&gt;, la réparation du monde, en relevant ces étincelles par la prière et les actes justes. Ce messianisme intérieur nourrit au XVIIe siècle l’aventure de Sabbataï Tsevi, puis, au XVIIIe, le hassidisme.&lt;/p&gt; &lt;p&gt;À la Renaissance, Pic de la Mirandole fonde une « Kabbale chrétienne ». Longtemps méprisée par les historiens, la Kabbale a été réhabilitée au XXe siècle par les travaux de Gershom Scholem, qui en a fait un objet d’étude majeur.&lt;/p&gt;  &lt;audio controls title="La kabbale par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14512-03.03.2016-ITEMA_20927570-2016F23912S0063-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TR8zo52EzWI</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"La kabbale, c'est quoi?" par Banque spirituelle</t>
-        </is>
-      </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tradition mystique du judaïsme qui contemple les dix émanations de Dieu et appelle l’être humain à réparer le monde.</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
-        </is>
-      </c>
-      <c r="L16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Isaac LOURIA;Moïse de LEÓN;NAHMANIDE;Abraham ABOULAFIA</t>
-        </is>
-      </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines"  title=" Wikipedia"&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les conceptions religieuses et philosophiques des civilisations de Mésoamérique, du Mexique central au Guatemala : les Olmèques dès le IIe millénaire avant notre ère, puis les Mayas, les Toltèques et les Aztèques. Malgré leur diversité, elles partagent la vision d’un monde sacré, cyclique et fragile, dont l’équilibre dépend de l’action des humains. Elles nous sont connues par les codex peints, les inscriptions mayas, l’architecture des cités et les récits recueillis après la conquête espagnole.&lt;/p&gt; &lt;p&gt;Le temps y est pensé en cycles : le calendrier rituel de 260 jours et l’année solaire de 365 jours se combinent en un « siècle » de 52 ans, et les Mayas datent aussi les événements sur de très longues périodes, le « compte long », depuis une origine mythique fixée en 3114 av. J.-C. Pour les Aztèques, le monde actuel est le cinquième « Soleil », après quatre créations détruites ; les dieux se sont sacrifiés pour mettre ce soleil en mouvement, et les humains leur doivent en retour leur propre sang. Le sacrifice est ainsi pensé comme une dette cosmique, nécessaire pour que le soleil poursuive sa course. Le &lt;em&gt;Popol Vuh&lt;/em&gt;, livre sacré des Mayas quichés, raconte la création des humains, façonnés dans le maïs après plusieurs essais manqués. La figure de &lt;a href="https://fr.wikipedia.org/wiki/Quetzalc%C3%B3atl" title=" Wikipedia"&gt;Quetzalcóatl&lt;/a&gt;, le Serpent à plumes, est associée au savoir, aux arts et au calendrier.&lt;/p&gt; &lt;p&gt;Les sages aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s’interrogeaient sur la vérité et la fragilité de l’existence. Leur pensée a été étudiée comme une véritable philosophie par Miguel León-Portilla.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3126,170 +3147,205 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensée juive</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Herméneutique juive;Néoplatonisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>1340</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>1340</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9sychasme" title=" Wikipedia"&gt;L’Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme orthodoxe. Son nom vient du grec &lt;em&gt;hésychia&lt;/em&gt;, « silence, tranquillité » : il s’agit de faire taire les pensées pour s’unir à Dieu dans le calme du cœur. Ses racines remontent aux moines et ermites d’Égypte et de Syrie, les Pères du désert, aux IVe et Ve siècles, puis à des maîtres comme Jean Climaque, auteur de &lt;em&gt;L’Échelle sainte&lt;/em&gt; au VIIe siècle, et Syméon le Nouveau Théologien vers l’an mil.&lt;/p&gt; &lt;p&gt;Sa pratique centrale est la &lt;a href="https://fr.wikipedia.org/wiki/Pri%C3%A8re_du_c%C5%93ur" title=" Wikipedia"&gt;prière de Jésus&lt;/a&gt; : le moine répète sans cesse « Seigneur Jésus-Christ, Fils de Dieu, aie pitié de moi », au rythme de sa respiration, la tête inclinée vers la poitrine, pour que la prière descende de l’intelligence dans le cœur. Au XIVe siècle, des moines du mont Athos disent voir ainsi la lumière divine, celle qui entoura le Christ lors de sa Transfiguration sur le mont Thabor. Le moine calabrais Barlaam les accuse de superstition : Dieu ne peut pas être vu. &lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas" title=" Wikipedia"&gt;Grégoire Palamas&lt;/a&gt;, futur archevêque de Thessalonique, répond en distinguant l’essence de Dieu, à jamais inaccessible, et ses énergies, qui se communiquent réellement à l’homme et rendent possible sa « divinisation ». Des conciles réunis à Constantinople lui donnent raison en 1341 et en 1351.&lt;/p&gt; &lt;p&gt;En 1782 paraît la &lt;em&gt;Philocalie&lt;/em&gt;, recueil de textes hésychastes bientôt traduit en slavon. L’hésychasme inspire alors les « startsy », les maîtres spirituels de Russie, et les &lt;em&gt;Récits d’un pèlerin russe&lt;/em&gt; ; il reste au cœur de la spiritualité orthodoxe.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"L'hésychasme prière sacrée par Mystica</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="144.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="n">
+        <v>-700</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
       <c r="J17" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ésotérismes et gnoses</t>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egypte antique;Platonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1">
+        <v>1200</v>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200</t>
+        </is>
+      </c>
+      <c r="D18" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Kabbale" title=" Wikipedia"&gt;La Kabbale&lt;/a&gt;, la « tradition reçue », est la grande tradition mystique et ésotérique du judaïsme. Elle apparaît à la fin du XIIe siècle en Provence, puis en Catalogne, où Nahmanide, à Gérone, lui donne son autorité, et en Castille, où &lt;a href="https://fr.wikipedia.org/wiki/Mo%C3%AFse_de_Le%C3%B3n" title=" Wikipedia"&gt;Moïse de León&lt;/a&gt; compose vers 1280 le &lt;em&gt;Zohar&lt;/em&gt;, « livre de la Splendeur », qui en devient le texte majeur.&lt;/p&gt; &lt;p&gt;Elle distingue en Dieu l’&lt;em&gt;En Sof&lt;/em&gt;, « l’Infini », absolument caché, et les dix &lt;a href="https://fr.wikipedia.org/wiki/Sephiroth_%28Kabbale%29" title=" Wikipedia"&gt;&lt;em&gt;sefirot&lt;/em&gt;&lt;/a&gt;, émanations par lesquelles il se manifeste : sagesse, intelligence, amour, rigueur, beauté, jusqu’à la &lt;a href="https://fr.wikipedia.org/wiki/Shekhina" title=" Wikipedia"&gt;&lt;em&gt;Shekhina&lt;/em&gt;&lt;/a&gt;, la présence divine dans le monde, que la Kabbale conçoit comme féminine et exilée avec le peuple. Chaque mot de la Torah, chaque commandement accompli, agit sur l’harmonie de ces puissances. Après l’expulsion des Juifs d’Espagne, en 1492, la Kabbale se renouvelle à Safed, en Galilée, autour d’&lt;a href="https://fr.wikipedia.org/wiki/Isaac_Louria" title=" Wikipedia"&gt;Isaac Louria&lt;/a&gt;. Pour faire place au monde, l’Infini a dû se retirer en lui-même : c’est le &lt;a href="https://fr.wikipedia.org/wiki/Tsimtsoum" title=" Wikipedia"&gt;&lt;em&gt;tsimtsoum&lt;/em&gt;&lt;/a&gt;. Puis les « vases » qui devaient recevoir sa lumière se sont brisés, et des étincelles divines sont tombées dans la matière. La tâche de l’être humain est le &lt;a href="https://fr.wikipedia.org/wiki/Tikkoun_Olam" title=" Wikipedia"&gt;&lt;em&gt;tikkoun&lt;/em&gt;&lt;/a&gt;, la réparation du monde, en relevant ces étincelles par la prière et les actes justes. Ce messianisme intérieur nourrit au XVIIe siècle l’aventure de Sabbataï Tsevi, puis, au XVIIIe, le hassidisme.&lt;/p&gt; &lt;p&gt;À la Renaissance, Pic de la Mirandole fonde une « Kabbale chrétienne ». Longtemps méprisée par les historiens, la Kabbale a été réhabilitée au XXe siècle par les travaux de Gershom Scholem, qui en a fait un objet d’étude majeur.&lt;/p&gt;  &lt;audio controls title="La kabbale par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14512-03.03.2016-ITEMA_20927570-2016F23912S0063-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TR8zo52EzWI</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"La kabbale, c'est quoi?" par Banque spirituelle</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tradition mystique du judaïsme qui contemple les dix émanations de Dieu et appelle l’être humain à réparer le monde.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isaac LOURIA;Moïse de LEÓN;NAHMANIDE;Abraham ABOULAFIA</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique juive;Néoplatonisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="50.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>1340</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9sychasme" title=" Wikipedia"&gt;L’Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme orthodoxe. Son nom vient du grec &lt;em&gt;hésychia&lt;/em&gt;, « silence, tranquillité » : il s’agit de faire taire les pensées pour s’unir à Dieu dans le calme du cœur. Ses racines remontent aux moines et ermites d’Égypte et de Syrie, les Pères du désert, aux IVe et Ve siècles, puis à des maîtres comme Jean Climaque, auteur de &lt;em&gt;L’Échelle sainte&lt;/em&gt; au VIIe siècle, et Syméon le Nouveau Théologien vers l’an mil.&lt;/p&gt; &lt;p&gt;Sa pratique centrale est la &lt;a href="https://fr.wikipedia.org/wiki/Pri%C3%A8re_du_c%C5%93ur" title=" Wikipedia"&gt;prière de Jésus&lt;/a&gt; : le moine répète sans cesse « Seigneur Jésus-Christ, Fils de Dieu, aie pitié de moi », au rythme de sa respiration, la tête inclinée vers la poitrine, pour que la prière descende de l’intelligence dans le cœur. Au XIVe siècle, des moines du mont Athos disent voir ainsi la lumière divine, celle qui entoura le Christ lors de sa Transfiguration sur le mont Thabor. Le moine calabrais Barlaam les accuse de superstition : Dieu ne peut pas être vu. &lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_Palamas" title=" Wikipedia"&gt;Grégoire Palamas&lt;/a&gt;, futur archevêque de Thessalonique, répond en distinguant l’essence de Dieu, à jamais inaccessible, et ses énergies, qui se communiquent réellement à l’homme et rendent possible sa « divinisation ». Des conciles réunis à Constantinople lui donnent raison en 1341 et en 1351.&lt;/p&gt; &lt;p&gt;En 1782 paraît la &lt;em&gt;Philocalie&lt;/em&gt;, recueil de textes hésychastes bientôt traduit en slavon. L’hésychasme inspire alors les « startsy », les maîtres spirituels de Russie, et les &lt;em&gt;Récits d’un pèlerin russe&lt;/em&gt; ; il reste au cœur de la spiritualité orthodoxe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"L'hésychasme prière sacrée par Mystica</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="O17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P17" s="1" t="inlineStr">
+      <c r="O19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P19" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Christianisme antique et médiéval</t>
         </is>
       </c>
-      <c r="Q17" s="1" t="inlineStr">
+      <c r="Q19" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Patristique</t>
         </is>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="n">
+    <row r="20" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="n">
         <v>-600</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14" t="s">
+      <c r="B20" s="14"/>
+      <c r="C20" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E20" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F20" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G20" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="2" t="s">
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>-600</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka"  title="Wikipedia"&gt;Le Lokayata&lt;/a&gt;, « ce qui est répandu dans le monde », ou Chârvâka, est l’école &lt;a href="https://fr.wikipedia.org/wiki/Mat%C3%A9rialisme" title=" Wikipedia"&gt;matérialiste&lt;/a&gt; de l’Inde ancienne, la seule à rejeter à la fois les Védas, les dieux, l’âme immortelle et la loi du karma. Ses origines sont anciennes : des thèses matérialistes apparaissent dès le VIe siècle av. J.-C., et la tradition attribue ses premiers aphorismes, aujourd’hui perdus, au sage Brihaspati.&lt;/p&gt; &lt;p&gt;Pour le Lokayata, la perception est le seul moyen de connaissance valide. L’inférence est incertaine : de ce que la fumée a toujours accompagné le feu, on ne peut conclure qu’il en sera toujours ainsi, car on n’a pas observé tous les cas. Ce qui ne se perçoit pas, l’au-delà, l’âme ou le karma, n’est qu’invention. Le monde est fait de quatre éléments, la terre, l’eau, le feu et l’air ; la conscience naît de leur combinaison dans le corps, comme le pouvoir enivrant naît du mélange de certains ingrédients, et disparaît avec lui. Il n’y a donc ni renaissance ni délivrance. La morale qui en découle est hédoniste : le plaisir est le seul but, et les rites des brahmanes ne sont qu’un moyen pour les prêtres de gagner leur vie.&lt;/p&gt; &lt;p&gt;Ses textes ont disparu ; on le connaît par ses adversaires, qui le réfutent longuement, et par le traité sceptique de Jayarashi Bhatta (VIIIe siècle). Il a été redécouvert au XXe siècle comme un témoin de la pensée rationaliste indienne, notamment par Debiprasad Chattopadhyaya, qui y voit l’expression d’une culture populaire opposée aux brahmanes.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>-550</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>94</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>22</v>
@@ -3304,75 +3360,155 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>-600</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka"  title="Wikipedia"&gt;Le Lokayata&lt;/a&gt;, « ce qui est répandu dans le monde », ou Chârvâka, est l’école &lt;a href="https://fr.wikipedia.org/wiki/Mat%C3%A9rialisme" title=" Wikipedia"&gt;matérialiste&lt;/a&gt; de l’Inde ancienne, la seule à rejeter à la fois les Védas, les dieux, l’âme immortelle et la loi du karma. Ses origines sont anciennes : des thèses matérialistes apparaissent dès le VIe siècle av. J.-C., et la tradition attribue ses premiers aphorismes, aujourd’hui perdus, au sage Brihaspati.&lt;/p&gt; &lt;p&gt;Pour le Lokayata, la perception est le seul moyen de connaissance valide. L’inférence est incertaine : de ce que la fumée a toujours accompagné le feu, on ne peut conclure qu’il en sera toujours ainsi, car on n’a pas observé tous les cas. Ce qui ne se perçoit pas, l’au-delà, l’âme ou le karma, n’est qu’invention. Le monde est fait de quatre éléments, la terre, l’eau, le feu et l’air ; la conscience naît de leur combinaison dans le corps, comme le pouvoir enivrant naît du mélange de certains ingrédients, et disparaît avec lui. Il n’y a donc ni renaissance ni délivrance. La morale qui en découle est hédoniste : le plaisir est le seul but, et les rites des brahmanes ne sont qu’un moyen pour les prêtres de gagner leur vie.&lt;/p&gt; &lt;p&gt;Ses textes ont disparu ; on le connaît par ses adversaires, qui le réfutent longuement, et par le traité sceptique de Jayarashi Bhatta (VIIIe siècle). Il a été redécouvert au XXe siècle comme un témoin de la pensée rationaliste indienne, notamment par Debiprasad Chattopadhyaya, qui y voit l’expression d’une culture populaire opposée aux brahmanes.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="164.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>-550</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Védas et brahmanisme</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t xml:space="preserve">Védisme</t>
         </is>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="n">
+    <row r="23" customFormat="false" ht="174" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="n">
         <v>-520</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9" t="s">
+      <c r="B23" s="9"/>
+      <c r="C23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D23" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme"  title=" Wikipedia"&gt;Le Confucianisme&lt;/a&gt; est la tradition de pensée issue de &lt;a href="https://fr.wikipedia.org/wiki/Confucius" title=" Wikipedia"&gt;Confucius&lt;/a&gt; (551-479 av. J.-C.), lettré de l’État de Lu, en Chine, qui chercha en vain un prince prêt à appliquer ses idées. Ses paroles, recueillies par ses disciples dans les &lt;em&gt;Entretiens&lt;/em&gt;, proposent de restaurer l’harmonie d’une société en crise non par la force ou par la loi, mais par la vertu, l’éducation et le respect des rites.&lt;/p&gt; &lt;p&gt;Son idéal est l’« homme de bien » (&lt;em&gt;junzi&lt;/em&gt;), qui se perfectionne sans cesse par l’étude. Les vertus cardinales sont l’humanité ou bienveillance (&lt;em&gt;ren&lt;/em&gt;), la droiture (&lt;em&gt;yi&lt;/em&gt;), les rites (&lt;em&gt;li&lt;/em&gt;), qui règlent avec justesse les relations humaines, la sagesse (&lt;em&gt;zhi&lt;/em&gt;) et la fidélité à la parole donnée (&lt;em&gt;xin&lt;/em&gt;). La société repose sur la famille et la piété filiale : chacun doit tenir son rôle dans les relations entre souverain et sujet, père et fils, époux, aînés et cadets, amis. Le prince gouverne par l’exemple, et les mots doivent correspondre aux choses : c’est la « rectification des noms ». Après Confucius, &lt;a href="https://fr.wikipedia.org/wiki/Mencius" title=" Wikipedia"&gt;Mencius&lt;/a&gt; affirme que la nature humaine est bonne, Xunzi qu’elle doit être redressée par l’éducation. Sous les Han, le confucianisme devient la doctrine officielle de l’empire, et les concours de recrutement des fonctionnaires, fondés sur ses classiques, durent jusqu’en 1905. Au XIIe siècle, Zhu Xi le renouvelle par une métaphysique : c’est le néoconfucianisme.&lt;/p&gt; &lt;p&gt;Il s’étend à la Corée, au Japon et au Viêt Nam. Combattu au XXe siècle comme cause du retard chinois, il connaît aujourd’hui un renouveau en Chine.&lt;/p&gt;  &lt;audio controls title="Le Confucianisme et les valeurs asiatiques par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-14.05.2019-ITEMA_22061347-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F23" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">"Les enseignemants de Confucius" par Film 25 Production</t>
         </is>
       </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="2" t="s">
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14">
+    <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14">
         <v>1980</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="B24" s="14"/>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">1980</t>
         </is>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D24" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_(philosophie)"   title=" Wikipedia"&gt; L'Ubuntu&lt;/a&gt; trouve ses origines en Afrique subsaharienne, principalement chez les peuples bantous. Ubuntu est un mot en langue zouloue qui peut être traduit approximativement par « humanité envers les autres » ou « je suis parce que nous sommes ». Il s'agit d'une philosophie qui met l'accent sur l'interconnexion, l'interdépendance et la bienveillance mutuelle entre les êtres humains. &lt;/p&gt; &lt;p&gt;
 Dans la philosophie Ubuntu, chaque individu est considéré comme étant en relation avec les autres et le monde qui l'entoure. Les relations humaines sont au cœur de cette philosophie, et l'identité d'une personne est déterminée en grande partie par sa relation avec les autres membres de sa communauté. Selon Ubuntu, nous sommes tous liés et notre bien-être individuel est intrinsèquement lié au bien-être collectif. &lt;/p&gt; &lt;p&gt;
@@ -3381,143 +3517,57 @@
 Il convient de noter que la philosophie Ubuntu ne se limite pas à l'Afrique subsaharienne. Elle a inspiré des penseurs et des leaders du monde entier qui reconnaissent l'importance des relations humaines et de la solidarité pour créer des sociétés justes et inclusives. &lt;/p&gt; &lt;p&gt;Ce n’est qu’au XXe siècle que l’Ubuntu devient une philosophie écrite. En 1980, au Zimbabwe, Stanlake et Tommie Marie Samkange publient &lt;em&gt;Hunhuism or Ubuntuism&lt;/em&gt;, qui en fait le fondement d’une pensée politique africaine. En Afrique du Sud, la Constitution provisoire de 1993 invoque « un besoin d’ubuntu, et non de victimisation » pour sortir de l’apartheid. L’archevêque &lt;a href="https://fr.wikipedia.org/wiki/Desmond_Tutu" title=" Wikipedia"&gt;Desmond Tutu&lt;/a&gt; en fait l’esprit de la Commission vérité et réconciliation, qu’il préside à partir de 1995, et le défend dans &lt;em&gt;Il n’y a pas d’avenir sans pardon&lt;/em&gt; (1999). La même année, le philosophe Mogobe Ramose publie &lt;em&gt;African Philosophy through Ubuntu&lt;/em&gt;, qui en propose une lecture métaphysique : l’être n’est pas une chose figée, mais un mouvement de relations.&lt;/p&gt;  &lt;audio controls title="Ubuntu ou l'histoire, les valeurs et la mémoire par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/08/s32/RF_DF1DF1B4-FF64-438F-BC47-78A44A7FA537_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F24" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G24" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="2" t="s">
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+    <row r="25" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
         <v>-500</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ajivika"  title="Wikipedia"&gt;L’Ajīvika&lt;/a&gt; est une école ascétique de l’Inde ancienne, fondée ou réorganisée au Ve siècle av. J.-C. par Makkhali Gosala, contemporain du Bouddha et de &lt;a href="https://fr.wikipedia.org/wiki/Mahavira" title=" Wikipedia"&gt;Mahavira&lt;/a&gt;, le fondateur du jaïnisme, dont il fut un temps le compagnon. Ses textes sont perdus : nous ne la connaissons que par ses adversaires bouddhistes et jaïns, qui en font un portrait hostile. Le nom viendrait d’&lt;em&gt;ājīva&lt;/em&gt;, « mode de vie », allusion à leur règle d’existence.&lt;/p&gt; &lt;p&gt;Sa thèse centrale est un déterminisme radical, la doctrine de la &lt;em&gt;niyati&lt;/em&gt;, le destin. Tout ce qui arrive est fixé d’avance ; l’effort, la vertu ou les rites ne changent rien. Chaque être traverse un nombre immense de renaissances, 8 400 000 grands cycles selon les sources, puis atteint la fin de la souffrance au terme prévu, comme une pelote de fil qui se déroule jusqu’au bout. Le libre arbitre est une illusion. Cette position heurte de front le bouddhisme et le jaïnisme, pour qui les actes, le karma, déterminent l’avenir et l’effort moral conduit à la délivrance. Les Ajīvikas étaient pourtant de rigoureux ascètes, souvent nus, qui pratiquaient parfois le jeûne jusqu’à la mort. Selon les textes jaïns, Gosala mourut peu après une violente querelle avec Mahavira.&lt;/p&gt; &lt;p&gt;Ils connaissent un grand rayonnement sous l’empire Maurya : &lt;a href="https://fr.wikipedia.org/wiki/Ashoka" title=" Wikipedia"&gt;Ashoka&lt;/a&gt; leur fait creuser des &lt;a href="https://fr.wikipedia.org/wiki/Grottes_de_Barabar" title=" Wikipedia"&gt;grottes dans les collines de Barabar&lt;/a&gt;. L’école décline ensuite et disparaît vers le XIVe siècle dans le sud de l’Inde. On y voit l’une des premières formes de fatalisme philosophique, comparable à certaines thèses des stoïciens.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>-500</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sâmkhya</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="n">
-        <v>-500</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>22</v>
@@ -3532,92 +3582,84 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védas et brahmanisme</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="n">
-        <v>-470</v>
-      </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bouddhisme"  title=" Wikipedia"&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt; &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>-500</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="J26" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="n">
-        <v>-450</v>
-      </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sâmkhya</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="n">
+        <v>-500</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
       <c r="J27" s="2" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -3626,27 +3668,121 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+          <t xml:space="preserve">Védas et brahmanisme</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianisme</t>
+          <t xml:space="preserve">Brahmanisme</t>
         </is>
       </c>
     </row>
     <row r="28" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="n">
-        <v>-410</v>
+        <v>-470</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bouddhisme"  title=" Wikipedia"&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt; &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="n">
+        <v>-450</v>
+      </c>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="n">
+        <v>-410</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D30" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shinto%C3%AFsme"  style="color:#d35400"  title=" Wikipedia"&gt;Le Shintoïsme&lt;/a&gt; est une religion philosophique autochtone du Japon. Le mot "shinto" signifie littéralement "la voie des dieux" ou "la voie des kami". Les kami sont des esprits ou des divinités vénérées dans la tradition shintoïste. &lt;/p&gt; &lt;p&gt;
 Le shintoïsme est souvent considéré comme une religion animiste, car il accorde une grande importance à la nature et aux phénomènes naturels. Les montagnes, les rivières, les arbres et autres éléments naturels sont vus comme abritant des kami, et ces kami sont vénérés et respectés. Les humains, en tant qu'êtres vivants, sont également considérés comme ayant une âme, et ils sont connectés aux kami et à la nature qui les entoure. Une caractéristique importante du shintoïsme est le culte des ancêtres. Les ancêtres décédés sont également considérés comme des kami et sont vénérés dans les sanctuaires shintoïstes familiaux.  &lt;/p&gt; &lt;p&gt;
@@ -3654,104 +3790,19 @@
 Le shintoïsme a une forte influence sur la culture japonaise. De nombreux festivals et cérémonies au Japon sont de nature shintoïste. Par exemple, le festival du Nouvel An, appelé "Hatsumode", est une célébration importante où les gens se rendent dans les sanctuaires pour prier, faire des offrandes et purifier leur esprit pour la nouvelle année. &lt;/p&gt; &lt;p&gt; Bien que ce ne soit pas une religion qui développe une philosophie systématique comme le bouddhisme ou le confucianisme, il offre une perspective favorisant l'harmonie avec la nature, le respect des ancêtres et la recherche de la pureté spirituelle. Ces idées peuvent être explorées et interprétées dans un contexte philosophique plus large. &lt;/p&gt;  &lt;audio controls title="Le shinto n'est pas une religion à système, c'est un ensemble de croyance très ancienne par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-13.08.2020-ITEMA_22401465-2018C3372E0676-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F30" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G30" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="2" t="s">
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Japon : shintō et voies nationales</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="n">
-        <v>-400</v>
-      </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tao%C3%AFsme"  style="color:#d35400"  title=" Wikipedia"&gt;Le Taoïsme&lt;/a&gt; est, avec le confucianisme, l’une des deux grandes traditions de pensée nées en Chine. Il se réclame de &lt;a href="https://fr.wikipedia.org/wiki/Laozi" title=" Wikipedia"&gt;Laozi&lt;/a&gt;, sage peut-être légendaire du VIe siècle av. J.-C., auquel on attribue le &lt;em&gt;Daodejing&lt;/em&gt;, le « Livre de la Voie et de la Vertu », composé sans doute vers le IVe siècle av. J.-C., et de &lt;a href="https://fr.wikipedia.org/wiki/Tchouang-tseu" title=" Wikipedia"&gt;Zhuangzi&lt;/a&gt; (vers 370-287 av. J.-C.), dont le livre mêle fables, dialogues et paradoxes.&lt;/p&gt; &lt;p&gt;Au cœur du taoïsme se trouve le &lt;em&gt;dao&lt;/em&gt;, la Voie : l’origine sans forme de toutes choses et l’ordre spontané selon lequel elles se transforment. « La Voie qui peut être dite n’est pas la Voie constante » : elle échappe aux mots. Elle agit comme l’eau, souple et humble, qui finit par user la pierre. Le sage l’imite par le &lt;em&gt;wuwei&lt;/em&gt;, le « non-agir » : non pas l’inaction, mais une action sans effort ni contrainte, accordée au cours naturel des choses. Contre les confucéens, qui veulent régler la société par les rites et la morale, le taoïsme prône la simplicité, le retour à la nature et un gouvernement aussi discret que possible. Zhuangzi y ajoute un relativisme plein d’humour : ayant rêvé qu’il était papillon, il ne sait plus, au réveil, s’il est Zhuangzi qui a rêvé d’être papillon, ou un papillon qui rêve d’être Zhuangzi.&lt;/p&gt; &lt;p&gt;À partir du IIe siècle se forme aussi une religion taoïste, avec ses temples, ses rites et sa quête de longévité. Le taoïsme a inspiré la peinture, la médecine et les arts martiaux chinois, ainsi que le bouddhisme chan.&lt;/p&gt;  &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/10/s44/NET_FC_43660d0e-6519-4ba7-84a5-c6390767f7da.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>-400</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/École_des_Noms"  title="Wikipedia"&gt;L’École des Noms&lt;/a&gt;, en chinois &lt;em&gt;mingjia&lt;/em&gt;, est une école de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.) qui s’intéresse au rapport entre les noms et les choses, c’est-à-dire entre le langage et la réalité. À une époque où les Cent Écoles débattent sans cesse, ses penseurs, appelés aussi « disputeurs », cultivent l’art de l’argumentation et du paradoxe, au point de passer pour des sophistes aux yeux de leurs adversaires. Ils prolongent à leur manière une exigence de Confucius, la « rectification des noms », qui veut que les mots s’accordent avec la réalité.&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hui_Shi" title=" Wikipedia"&gt;Hui Shi&lt;/a&gt; (IVe siècle av. J.-C.), ami et contradicteur de Zhuangzi, avance dix paradoxes sur l’espace, le temps et l’unité du monde : « le ciel est aussi bas que la terre », « je pars aujourd’hui pour Yue et j’y suis arrivé hier », ou encore « aimez tous les êtres, car le ciel et la terre ne font qu’un corps ». Ils montrent que toute distinction, grand et petit, haut et bas, dépend du point de vue. Son cadet &lt;a href="https://fr.wikipedia.org/wiki/Gongsun_Long" title=" Wikipedia"&gt;Gongsun Long&lt;/a&gt; (vers 320-250 av. J.-C.) est célèbre pour sa thèse « un cheval blanc n’est pas un cheval » : le nom « cheval blanc » désigne à la fois une forme et une couleur, il ne se confond donc pas avec le nom « cheval ». Il distingue ainsi le concept général des choses particulières, et le nom de ce qu’il désigne.&lt;/p&gt; &lt;p&gt;Raillée par les confucéens et les taoïstes, l’école disparaît avec l’empire Qin. Redécouverte au XXe siècle, elle est vue comme l’un des rares foyers de logique et de philosophie du langage de la Chine ancienne, aux côtés des logiciens moïstes. Un seul de ses livres, le &lt;em&gt;Gongsun Longzi&lt;/em&gt;, nous est parvenu, en partie.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>101</v>
@@ -3763,42 +3814,42 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="n">
-        <v>-350</v>
-      </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A2mkhya"  title=" Wikipedia"&gt;Le Sâmkhya&lt;/a&gt;, « dénombrement », est l’une des six écoles orthodoxes de la philosophie indienne, et sans doute la plus ancienne. On l’attribue au sage légendaire &lt;a href="https://fr.wikipedia.org/wiki/Kapila" title=" Wikipedia"&gt;Kapila&lt;/a&gt;, mais son texte de référence, les &lt;em&gt;Sāṃkhya-kārikā&lt;/em&gt; d’Īśvarakṛṣṇa, date des environs du IVe siècle de notre ère. Comme les autres écoles, il cherche à délivrer l’homme de la souffrance et du cycle des renaissances par la connaissance.&lt;/p&gt; &lt;p&gt;Le Sâmkhya est un dualisme : il distingue deux principes éternels. Le &lt;em&gt;puruṣa&lt;/em&gt; est la conscience pure, immobile, simple témoin ; il y en a une infinité, une par être. La &lt;em&gt;prakṛti&lt;/em&gt; est la nature, matière première active, faite de trois qualités (&lt;em&gt;guṇa&lt;/em&gt;) : la clarté (&lt;em&gt;sattva&lt;/em&gt;), l’énergie (&lt;em&gt;rajas&lt;/em&gt;) et l’inertie (&lt;em&gt;tamas&lt;/em&gt;). Quand leur équilibre se rompt, la nature se déploie en 23 principes : l’intellect, le sens du moi, l’esprit, les sens, puis les éléments subtils et grossiers. Tout effet préexiste dans sa cause, comme l’huile dans la graine, et le monde se forme sans dieu créateur. La souffrance vient de ce que la conscience se confond avec les opérations de la nature, qu’elle ne fait que regarder ; la délivrance, l’« isolement » (&lt;em&gt;kaivalya&lt;/em&gt;), vient du discernement qui les sépare.&lt;/p&gt; &lt;p&gt;Le Sâmkhya fournit sa métaphysique au Yoga de &lt;a href="https://fr.wikipedia.org/wiki/Patanjali" title=" Wikipedia"&gt;Patañjali&lt;/a&gt;, qui en est comme la pratique, et imprègne la &lt;em&gt;Bhagavad-Gîtâ&lt;/em&gt;, la médecine āyurvédique et une grande partie de la pensée hindoue. Le Vedânta lui reproche de séparer la nature de l’Absolu, mais reprend beaucoup de ses notions.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
+      <c r="A31" s="14" t="n">
+        <v>-400</v>
+      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tao%C3%AFsme"  style="color:#d35400"  title=" Wikipedia"&gt;Le Taoïsme&lt;/a&gt; est, avec le confucianisme, l’une des deux grandes traditions de pensée nées en Chine. Il se réclame de &lt;a href="https://fr.wikipedia.org/wiki/Laozi" title=" Wikipedia"&gt;Laozi&lt;/a&gt;, sage peut-être légendaire du VIe siècle av. J.-C., auquel on attribue le &lt;em&gt;Daodejing&lt;/em&gt;, le « Livre de la Voie et de la Vertu », composé sans doute vers le IVe siècle av. J.-C., et de &lt;a href="https://fr.wikipedia.org/wiki/Tchouang-tseu" title=" Wikipedia"&gt;Zhuangzi&lt;/a&gt; (vers 370-287 av. J.-C.), dont le livre mêle fables, dialogues et paradoxes.&lt;/p&gt; &lt;p&gt;Au cœur du taoïsme se trouve le &lt;em&gt;dao&lt;/em&gt;, la Voie : l’origine sans forme de toutes choses et l’ordre spontané selon lequel elles se transforment. « La Voie qui peut être dite n’est pas la Voie constante » : elle échappe aux mots. Elle agit comme l’eau, souple et humble, qui finit par user la pierre. Le sage l’imite par le &lt;em&gt;wuwei&lt;/em&gt;, le « non-agir » : non pas l’inaction, mais une action sans effort ni contrainte, accordée au cours naturel des choses. Contre les confucéens, qui veulent régler la société par les rites et la morale, le taoïsme prône la simplicité, le retour à la nature et un gouvernement aussi discret que possible. Zhuangzi y ajoute un relativisme plein d’humour : ayant rêvé qu’il était papillon, il ne sait plus, au réveil, s’il est Zhuangzi qui a rêvé d’être papillon, ou un papillon qui rêve d’être Zhuangzi.&lt;/p&gt; &lt;p&gt;À partir du IIe siècle se forme aussi une religion taoïste, avec ses temples, ses rites et sa quête de longévité. Le taoïsme a inspiré la peinture, la médecine et les arts martiaux chinois, ainsi que le bouddhisme chan.&lt;/p&gt;  &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/10/s44/NET_FC_43660d0e-6519-4ba7-84a5-c6390767f7da.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -3807,41 +3858,36 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
-        <v>-350</v>
+        <v>-400</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9gisme" title="Wikipedia"&gt;Le Légisme&lt;/a&gt;, en chinois &lt;em&gt;fajia&lt;/em&gt;, « école de la loi », est une philosophie politique de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.). À une époque de guerres incessantes, ses penseurs, souvent ministres, cherchent comment rendre un État riche et puissant. Contre les confucéens, qui veulent gouverner par la vertu et les rites, ils affirment que seule la loi, écrite, publique et appliquée à tous, peut assurer l’ordre.&lt;/p&gt; &lt;p&gt;Au IVe siècle av. J.-C., &lt;a href="https://fr.wikipedia.org/wiki/Shang_Yang" title=" Wikipedia"&gt;Shang Yang&lt;/a&gt; réforme le royaume de Qin : il encourage l’agriculture et la guerre, supprime les privilèges de la noblesse héréditaire et instaure des récompenses et des châtiments rigoureux, avec une responsabilité collective des familles. Shen Buhai insiste sur l’art de contrôler les fonctionnaires, Shen Dao sur la position de pouvoir. &lt;a href="https://fr.wikipedia.org/wiki/Han_Fei" title=" Wikipedia"&gt;Han Fei&lt;/a&gt; (vers 280-233 av. J.-C.), disciple du confucéen Xunzi, réunit la loi, la technique et la position en une doctrine complète. Puisque les hommes recherchent leur intérêt, inutile d’en appeler à leur bonté : le souverain doit les gouverner par la crainte et l’intérêt, rester secret et impénétrable, et faire fonctionner l’État comme une machine qui marche seule.&lt;/p&gt; &lt;p&gt;Le légisme triomphe quand &lt;a href="https://fr.wikipedia.org/wiki/Qin_Shi_Huang" title=" Wikipedia"&gt;Qin Shi Huang&lt;/a&gt; unifie la Chine en 221 av. J.-C. et fait brûler les livres des autres écoles. Discrédité par la chute rapide des Qin, il survit en pratique dans l’administration impériale, sous un vernis confucéen. Dans les années 1970, la campagne maoïste « contre Lin Biao et Confucius » en fait encore l’éloge.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/École_des_Noms"  title="Wikipedia"&gt;L’École des Noms&lt;/a&gt;, en chinois &lt;em&gt;mingjia&lt;/em&gt;, est une école de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.) qui s’intéresse au rapport entre les noms et les choses, c’est-à-dire entre le langage et la réalité. À une époque où les Cent Écoles débattent sans cesse, ses penseurs, appelés aussi « disputeurs », cultivent l’art de l’argumentation et du paradoxe, au point de passer pour des sophistes aux yeux de leurs adversaires. Ils prolongent à leur manière une exigence de Confucius, la « rectification des noms », qui veut que les mots s’accordent avec la réalité.&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hui_Shi" title=" Wikipedia"&gt;Hui Shi&lt;/a&gt; (IVe siècle av. J.-C.), ami et contradicteur de Zhuangzi, avance dix paradoxes sur l’espace, le temps et l’unité du monde : « le ciel est aussi bas que la terre », « je pars aujourd’hui pour Yue et j’y suis arrivé hier », ou encore « aimez tous les êtres, car le ciel et la terre ne font qu’un corps ». Ils montrent que toute distinction, grand et petit, haut et bas, dépend du point de vue. Son cadet &lt;a href="https://fr.wikipedia.org/wiki/Gongsun_Long" title=" Wikipedia"&gt;Gongsun Long&lt;/a&gt; (vers 320-250 av. J.-C.) est célèbre pour sa thèse « un cheval blanc n’est pas un cheval » : le nom « cheval blanc » désigne à la fois une forme et une couleur, il ne se confond donc pas avec le nom « cheval ». Il distingue ainsi le concept général des choses particulières, et le nom de ce qu’il désigne.&lt;/p&gt; &lt;p&gt;Raillée par les confucéens et les taoïstes, l’école disparaît avec l’empire Qin. Redécouverte au XXe siècle, elle est vue comme l’un des rares foyers de logique et de philosophie du langage de la Chine ancienne, aux côtés des logiciens moïstes. Un seul de ses livres, le &lt;em&gt;Gongsun Longzi&lt;/em&gt;, nous est parvenu, en partie.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F32" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>101</v>
@@ -3856,38 +3902,36 @@
           <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>-250</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Therav%C4%81da" title="Wikipedia"&gt;Le Bouddhisme Theravada&lt;/a&gt;, « l’enseignement des Anciens », est la plus ancienne forme du bouddhisme encore vivante. Il se réclame des premiers disciples du Bouddha et se transmet en pali. Sous le règne d’&lt;a href="https://fr.wikipedia.org/wiki/Ashoka" title=" Wikipedia"&gt;Ashoka&lt;/a&gt;, au IIIe siècle av. J.-C., le moine Mahinda l’introduit à Sri Lanka, d’où il gagne la Birmanie, la Thaïlande, le Cambodge et le Laos, où il reste majoritaire.&lt;/p&gt; &lt;p&gt;Ses textes forment le Canon pali, ou &lt;em&gt;Tipitaka&lt;/em&gt; (« trois corbeilles ») : la discipline monastique, les discours du Bouddha et l’&lt;em&gt;Abhidhamma&lt;/em&gt;, analyse philosophique des phénomènes, mis par écrit à Sri Lanka au Ier siècle av. J.-C. Au Ve siècle, &lt;a href="https://fr.wikipedia.org/wiki/Buddhaghosa" title=" Wikipedia"&gt;Buddhaghosa&lt;/a&gt; en donne la synthèse dans le &lt;em&gt;Chemin de la pureté&lt;/em&gt;. L’enseignement repose sur les quatre nobles vérités : la souffrance, son origine dans le désir, sa cessation et le Noble Sentier octuple qui y mène. Tout ce qui existe est impermanent, insatisfaisant et dépourvu de soi : la personne n’est qu’un assemblage changeant de cinq agrégats. L’idéal est l’&lt;em&gt;arhat&lt;/em&gt;, qui a éteint par sa propre pratique les feux du désir, de la haine et de l’illusion, alors que le Mahayana met en avant le bodhisattva, qui se consacre au salut de tous les êtres.&lt;/p&gt; &lt;p&gt;La méditation vipassana, « vision pénétrante », qui observe l’apparition et la disparition des phénomènes, a été remise à l’honneur en Birmanie au XXe siècle par des maîtres comme Mahasi Sayadaw ; elle a inspiré la « pleine conscience » répandue en Occident.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>171</v>
-      </c>
+    </row>
+    <row r="33" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="n">
+        <v>-350</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A2mkhya"  title=" Wikipedia"&gt;Le Sâmkhya&lt;/a&gt;, « dénombrement », est l’une des six écoles orthodoxes de la philosophie indienne, et sans doute la plus ancienne. On l’attribue au sage légendaire &lt;a href="https://fr.wikipedia.org/wiki/Kapila" title=" Wikipedia"&gt;Kapila&lt;/a&gt;, mais son texte de référence, les &lt;em&gt;Sāṃkhya-kārikā&lt;/em&gt; d’Īśvarakṛṣṇa, date des environs du IVe siècle de notre ère. Comme les autres écoles, il cherche à délivrer l’homme de la souffrance et du cycle des renaissances par la connaissance.&lt;/p&gt; &lt;p&gt;Le Sâmkhya est un dualisme : il distingue deux principes éternels. Le &lt;em&gt;puruṣa&lt;/em&gt; est la conscience pure, immobile, simple témoin ; il y en a une infinité, une par être. La &lt;em&gt;prakṛti&lt;/em&gt; est la nature, matière première active, faite de trois qualités (&lt;em&gt;guṇa&lt;/em&gt;) : la clarté (&lt;em&gt;sattva&lt;/em&gt;), l’énergie (&lt;em&gt;rajas&lt;/em&gt;) et l’inertie (&lt;em&gt;tamas&lt;/em&gt;). Quand leur équilibre se rompt, la nature se déploie en 23 principes : l’intellect, le sens du moi, l’esprit, les sens, puis les éléments subtils et grossiers. Tout effet préexiste dans sa cause, comme l’huile dans la graine, et le monde se forme sans dieu créateur. La souffrance vient de ce que la conscience se confond avec les opérations de la nature, qu’elle ne fait que regarder ; la délivrance, l’« isolement » (&lt;em&gt;kaivalya&lt;/em&gt;), vient du discernement qui les sépare.&lt;/p&gt; &lt;p&gt;Le Sâmkhya fournit sa métaphysique au Yoga de &lt;a href="https://fr.wikipedia.org/wiki/Patanjali" title=" Wikipedia"&gt;Patañjali&lt;/a&gt;, qui en est comme la pratique, et imprègne la &lt;em&gt;Bhagavad-Gîtâ&lt;/em&gt;, la médecine āyurvédique et une grande partie de la pensée hindoue. Le Vedânta lui reproche de séparer la nature de l’Absolu, mais reprend beaucoup de ses notions.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
       <c r="J33" s="2" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>43</v>
@@ -3899,47 +3943,44 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="n">
-        <v>-150</v>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ny%C3%A2ya" title=" Wikipedia"&gt;Le Nyâya&lt;/a&gt;, « la règle » ou « la méthode », est l’une des six écoles orthodoxes de la philosophie indienne, celle qui s’est consacrée à la logique et à la théorie de la connaissance. Ses textes fondateurs, les &lt;em&gt;Nyāya Sūtra&lt;/em&gt;, attribués à Akṣapāda Gautama, sont composés entre le IIe siècle avant et le IIe siècle de notre ère, à partir de traditions de débat plus anciennes. Leur but reste spirituel : seule la connaissance juste délivre de la souffrance et du cycle des renaissances.&lt;/p&gt; &lt;p&gt;Le Nyâya reconnaît quatre moyens de connaissance valide (&lt;em&gt;pramāṇa&lt;/em&gt;) : la perception, l’inférence, la comparaison et le témoignage digne de foi. Il codifie l’inférence en un raisonnement à cinq membres, illustré par un exemple célèbre : la colline est en feu, parce qu’elle fume ; tout ce qui fume est en feu, comme un foyer de cuisine ; or la colline fume ; donc elle est en feu. Il dresse aussi la liste des sophismes et des ruses de la discussion. Réaliste, il soutient que le monde extérieur existe tel que nous le percevons, contre les bouddhistes. Il défend l’existence d’un Soi permanent et d’un Dieu cause du monde, notamment avec Udayana vers l’an mil. Associé à l’école &lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika" title=" Wikipedia"&gt;Vaiśeṣika&lt;/a&gt;, qui lui apporte sa théorie des atomes et des catégories, il forme avec elle le Nyāya-Vaiśeṣika.&lt;/p&gt; &lt;p&gt;Au XIVe siècle, Gaṅgeśa fonde le « nouveau Nyâya » (&lt;em&gt;Navya-Nyāya&lt;/em&gt;), dont le langage technique devient l’outil commun de toute la philosophie indienne. Ses analyses de l’inférence et du témoignage ont souvent été comparées à la logique d’Aristote.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="n">
+        <v>-350</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9gisme" title="Wikipedia"&gt;Le Légisme&lt;/a&gt;, en chinois &lt;em&gt;fajia&lt;/em&gt;, « école de la loi », est une philosophie politique de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.). À une époque de guerres incessantes, ses penseurs, souvent ministres, cherchent comment rendre un État riche et puissant. Contre les confucéens, qui veulent gouverner par la vertu et les rites, ils affirment que seule la loi, écrite, publique et appliquée à tous, peut assurer l’ordre.&lt;/p&gt; &lt;p&gt;Au IVe siècle av. J.-C., &lt;a href="https://fr.wikipedia.org/wiki/Shang_Yang" title=" Wikipedia"&gt;Shang Yang&lt;/a&gt; réforme le royaume de Qin : il encourage l’agriculture et la guerre, supprime les privilèges de la noblesse héréditaire et instaure des récompenses et des châtiments rigoureux, avec une responsabilité collective des familles. Shen Buhai insiste sur l’art de contrôler les fonctionnaires, Shen Dao sur la position de pouvoir. &lt;a href="https://fr.wikipedia.org/wiki/Han_Fei" title=" Wikipedia"&gt;Han Fei&lt;/a&gt; (vers 280-233 av. J.-C.), disciple du confucéen Xunzi, réunit la loi, la technique et la position en une doctrine complète. Puisque les hommes recherchent leur intérêt, inutile d’en appeler à leur bonté : le souverain doit les gouverner par la crainte et l’intérêt, rester secret et impénétrable, et faire fonctionner l’État comme une machine qui marche seule.&lt;/p&gt; &lt;p&gt;Le légisme triomphe quand &lt;a href="https://fr.wikipedia.org/wiki/Qin_Shi_Huang" title=" Wikipedia"&gt;Qin Shi Huang&lt;/a&gt; unifie la Chine en 221 av. J.-C. et fait brûler les livres des autres écoles. Discrédité par la chute rapide des Qin, il survit en pratique dans l’administration impériale, sous un vernis confucéen. Dans les années 1970, la campagne maoïste « contre Lin Biao et Confucius » en fait encore l’éloge.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="J34" s="2" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3948,44 +3989,41 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+          <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika"  title=" Wikipedia"&gt;Le Vaisheshika&lt;/a&gt;, de &lt;em&gt;viśeṣa&lt;/em&gt;, « particularité », est l’une des six écoles orthodoxes de la philosophie indienne. Ses &lt;em&gt;Vaiśeṣika Sūtra&lt;/em&gt; sont attribués au sage Kaṇāda, dont le nom signifierait « mangeur de grains », et datent sans doute des débuts de notre ère. Son but est la délivrance (&lt;em&gt;mokṣa&lt;/em&gt;), que procure la connaissance exacte des catégories du réel. Le système est surtout connu par le traité de Praśastapāda (VIe siècle), qui l’organise et le complète.&lt;/p&gt; &lt;p&gt;Le Vaisheshika classe tout ce qui existe en six catégories (&lt;em&gt;padārtha&lt;/em&gt;), auxquelles on ajoute plus tard la non-existence : la substance, la qualité, l’action, l’universel, la particularité et l’inhérence, relation qui unit par exemple une qualité à sa substance. Il compte neuf substances : la terre, l’eau, le feu et l’air, faits d’atomes éternels et indivisibles (&lt;em&gt;paramāṇu&lt;/em&gt;), puis l’éther, le temps, l’espace, l’âme et le sens interne. Les atomes s’assemblent par deux, puis par trois, pour former les objets visibles, qui eux sont périssables. Leurs mouvements sont guidés par l’&lt;em&gt;adṛṣṭa&lt;/em&gt;, la force invisible des actes passés ; les auteurs plus tardifs y ajoutent un Dieu ordonnateur, Īśvara. L’âme délivrée retrouve un état pur, sans plaisir ni douleur, car toute qualité liée au corps a cessé.&lt;/p&gt; &lt;p&gt;Très tôt associé au Nyâya, qui lui apporte sa logique, il forme avec lui le Nyāya-Vaiśeṣika. Son atomisme a souvent été comparé à celui de &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9mocrite" title=" Wikipedia"&gt;Démocrite&lt;/a&gt; ; mais là où Démocrite voyait le hasard, le Vaisheshika voit un ordre moral.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
+        <v>-250</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Therav%C4%81da" title="Wikipedia"&gt;Le Bouddhisme Theravada&lt;/a&gt;, « l’enseignement des Anciens », est la plus ancienne forme du bouddhisme encore vivante. Il se réclame des premiers disciples du Bouddha et se transmet en pali. Sous le règne d’&lt;a href="https://fr.wikipedia.org/wiki/Ashoka" title=" Wikipedia"&gt;Ashoka&lt;/a&gt;, au IIIe siècle av. J.-C., le moine Mahinda l’introduit à Sri Lanka, d’où il gagne la Birmanie, la Thaïlande, le Cambodge et le Laos, où il reste majoritaire.&lt;/p&gt; &lt;p&gt;Ses textes forment le Canon pali, ou &lt;em&gt;Tipitaka&lt;/em&gt; (« trois corbeilles ») : la discipline monastique, les discours du Bouddha et l’&lt;em&gt;Abhidhamma&lt;/em&gt;, analyse philosophique des phénomènes, mis par écrit à Sri Lanka au Ier siècle av. J.-C. Au Ve siècle, &lt;a href="https://fr.wikipedia.org/wiki/Buddhaghosa" title=" Wikipedia"&gt;Buddhaghosa&lt;/a&gt; en donne la synthèse dans le &lt;em&gt;Chemin de la pureté&lt;/em&gt;. L’enseignement repose sur les quatre nobles vérités : la souffrance, son origine dans le désir, sa cessation et le Noble Sentier octuple qui y mène. Tout ce qui existe est impermanent, insatisfaisant et dépourvu de soi : la personne n’est qu’un assemblage changeant de cinq agrégats. L’idéal est l’&lt;em&gt;arhat&lt;/em&gt;, qui a éteint par sa propre pratique les feux du désir, de la haine et de l’illusion, alors que le Mahayana met en avant le bodhisattva, qui se consacre au salut de tous les êtres.&lt;/p&gt; &lt;p&gt;La méditation vipassana, « vision pénétrante », qui observe l’apparition et la disparition des phénomènes, a été remise à l’honneur en Birmanie au XXe siècle par des maîtres comme Mahasi Sayadaw ; elle a inspiré la « pleine conscience » répandue en Occident.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="J35" s="2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>43</v>
@@ -3997,91 +4035,93 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>188</v>
-      </c>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="n">
+        <v>-150</v>
+      </c>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ny%C3%A2ya" title=" Wikipedia"&gt;Le Nyâya&lt;/a&gt;, « la règle » ou « la méthode », est l’une des six écoles orthodoxes de la philosophie indienne, celle qui s’est consacrée à la logique et à la théorie de la connaissance. Ses textes fondateurs, les &lt;em&gt;Nyāya Sūtra&lt;/em&gt;, attribués à Akṣapāda Gautama, sont composés entre le IIe siècle avant et le IIe siècle de notre ère, à partir de traditions de débat plus anciennes. Leur but reste spirituel : seule la connaissance juste délivre de la souffrance et du cycle des renaissances.&lt;/p&gt; &lt;p&gt;Le Nyâya reconnaît quatre moyens de connaissance valide (&lt;em&gt;pramāṇa&lt;/em&gt;) : la perception, l’inférence, la comparaison et le témoignage digne de foi. Il codifie l’inférence en un raisonnement à cinq membres, illustré par un exemple célèbre : la colline est en feu, parce qu’elle fume ; tout ce qui fume est en feu, comme un foyer de cuisine ; or la colline fume ; donc elle est en feu. Il dresse aussi la liste des sophismes et des ruses de la discussion. Réaliste, il soutient que le monde extérieur existe tel que nous le percevons, contre les bouddhistes. Il défend l’existence d’un Soi permanent et d’un Dieu cause du monde, notamment avec Udayana vers l’an mil. Associé à l’école &lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika" title=" Wikipedia"&gt;Vaiśeṣika&lt;/a&gt;, qui lui apporte sa théorie des atomes et des catégories, il forme avec elle le Nyāya-Vaiśeṣika.&lt;/p&gt; &lt;p&gt;Au XIVe siècle, Gaṅgeśa fonde le « nouveau Nyâya » (&lt;em&gt;Navya-Nyāya&lt;/em&gt;), dont le langage technique devient l’outil commun de toute la philosophie indienne. Ses analyses de l’inférence et du témoignage ont souvent été comparées à la logique d’Aristote.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
       <c r="J36" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N36" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
         </is>
       </c>
     </row>
     <row r="37" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
+      <c r="A37" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika"  title=" Wikipedia"&gt;Le Vaisheshika&lt;/a&gt;, de &lt;em&gt;viśeṣa&lt;/em&gt;, « particularité », est l’une des six écoles orthodoxes de la philosophie indienne. Ses &lt;em&gt;Vaiśeṣika Sūtra&lt;/em&gt; sont attribués au sage Kaṇāda, dont le nom signifierait « mangeur de grains », et datent sans doute des débuts de notre ère. Son but est la délivrance (&lt;em&gt;mokṣa&lt;/em&gt;), que procure la connaissance exacte des catégories du réel. Le système est surtout connu par le traité de Praśastapāda (VIe siècle), qui l’organise et le complète.&lt;/p&gt; &lt;p&gt;Le Vaisheshika classe tout ce qui existe en six catégories (&lt;em&gt;padārtha&lt;/em&gt;), auxquelles on ajoute plus tard la non-existence : la substance, la qualité, l’action, l’universel, la particularité et l’inhérence, relation qui unit par exemple une qualité à sa substance. Il compte neuf substances : la terre, l’eau, le feu et l’air, faits d’atomes éternels et indivisibles (&lt;em&gt;paramāṇu&lt;/em&gt;), puis l’éther, le temps, l’espace, l’âme et le sens interne. Les atomes s’assemblent par deux, puis par trois, pour former les objets visibles, qui eux sont périssables. Leurs mouvements sont guidés par l’&lt;em&gt;adṛṣṭa&lt;/em&gt;, la force invisible des actes passés ; les auteurs plus tardifs y ajoutent un Dieu ordonnateur, Īśvara. L’âme délivrée retrouve un état pur, sans plaisir ni douleur, car toute qualité liée au corps a cessé.&lt;/p&gt; &lt;p&gt;Très tôt associé au Nyâya, qui lui apporte sa logique, il forme avec lui le Nyāya-Vaiśeṣika. Son atomisme a souvent été comparé à celui de &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9mocrite" title=" Wikipedia"&gt;Démocrite&lt;/a&gt; ; mais là où Démocrite voyait le hasard, le Vaisheshika voit un ordre moral.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
       <c r="J37" s="2" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>43</v>
@@ -4098,86 +4138,89 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="n">
-        <v>450</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14" t="n">
-        <v>450</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E38" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mazdakisme" title="Wikipedia"&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse à la fin du Ve siècle, sous l’Empire sassanide. Il tire son nom de Mazdak, prêtre réformateur dont la doctrine s’inspire d’un prédicateur plus ancien, Zaradusht de Fasa, et emprunte à la fois au zoroastrisme et au &lt;a href="https://fr.wikipedia.org/wiki/Manich%C3%A9isme_%28religion%29" title=" Wikipedia"&gt;manichéisme&lt;/a&gt;. Nous le connaissons surtout par ses adversaires, chroniqueurs perses, arabes et byzantins.&lt;/p&gt; &lt;p&gt;Comme les manichéens, Mazdak voit le monde comme un mélange de lumière et de ténèbres ; mais pour lui, la lumière agit librement et sciemment, tandis que les ténèbres agissent au hasard, ce qui rend la victoire du bien probable. Le mal humain vient surtout de cinq démons : l’envie, la colère, la vengeance, le besoin et la cupidité. Puisque l’inégalité des richesses nourrit ces passions, il faut partager les biens et, selon ses ennemis, les femmes, ce qui visait sans doute les vastes harems de l’aristocratie. Il prêche aussi la non-violence, le refus de tuer et un régime végétarien. Dans une période de famine, ce message rencontre un large écho populaire. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Kavadh_Ier" title=" Wikipedia"&gt;Kavadh Ier&lt;/a&gt; le soutient d’abord, peut-être pour affaiblir la noblesse et le clergé.&lt;/p&gt; &lt;p&gt;Mais vers 528, son fils, le futur &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, fait massacrer Mazdak et ses partisans. Le mouvement survit dans la clandestinité et inspire des révoltes en Iran à l’époque islamique. On l’a parfois présenté, de façon anachronique, comme un « communisme » avant la lettre.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>200</v>
-      </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="J38" s="2" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zoroastrisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
       <c r="J39" s="2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4186,74 +4229,167 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>700</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>700</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>210</v>
-      </c>
+          <t xml:space="preserve">Védisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mazdakisme" title="Wikipedia"&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse à la fin du Ve siècle, sous l’Empire sassanide. Il tire son nom de Mazdak, prêtre réformateur dont la doctrine s’inspire d’un prédicateur plus ancien, Zaradusht de Fasa, et emprunte à la fois au zoroastrisme et au &lt;a href="https://fr.wikipedia.org/wiki/Manich%C3%A9isme_%28religion%29" title=" Wikipedia"&gt;manichéisme&lt;/a&gt;. Nous le connaissons surtout par ses adversaires, chroniqueurs perses, arabes et byzantins.&lt;/p&gt; &lt;p&gt;Comme les manichéens, Mazdak voit le monde comme un mélange de lumière et de ténèbres ; mais pour lui, la lumière agit librement et sciemment, tandis que les ténèbres agissent au hasard, ce qui rend la victoire du bien probable. Le mal humain vient surtout de cinq démons : l’envie, la colère, la vengeance, le besoin et la cupidité. Puisque l’inégalité des richesses nourrit ces passions, il faut partager les biens et, selon ses ennemis, les femmes, ce qui visait sans doute les vastes harems de l’aristocratie. Il prêche aussi la non-violence, le refus de tuer et un régime végétarien. Dans une période de famine, ce message rencontre un large écho populaire. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Kavadh_Ier" title=" Wikipedia"&gt;Kavadh Ier&lt;/a&gt; le soutient d’abord, peut-être pour affaiblir la noblesse et le clergé.&lt;/p&gt; &lt;p&gt;Mais vers 528, son fils, le futur &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, fait massacrer Mazdak et ses partisans. Le mouvement survit dans la clandestinité et inspire des révoltes en Iran à l’époque islamique. On l’a parfois présenté, de façon anachronique, comme un « communisme » avant la lettre.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
       <c r="J40" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M40" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zoroastrisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="N42" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P42" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
+      <c r="Q42" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhisme Mahayana</t>
         </is>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9" t="n">
+    <row r="43" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="n">
         <v>750</v>
       </c>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9" t="s">
+      <c r="B43" s="9"/>
+      <c r="C43" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D43" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mutazilisme"  title=" Wikipedia"&gt;Le Mutazilisme&lt;/a&gt;  était un courant théologique et philosophique qui a émergé au sein de l'islam sunnite. Le terme "mutazilisme" dérive du mot arabe "itizal", qui signifie "se séparer" ou "se retirer".  Il est considéré comme l'une des premières écoles théologiques islamiques rationalistes, cherchant à combiner la foi et la raison. Ils croyaient que la raison humaine était une source importante de connaissances et qu'elle devait être utilisée pour interpréter les enseignements religieux. Les mutazilites rejetaient l'idée que le Coran était la parole incréée de Dieu, affirmant plutôt que le Coran était créé et qu'il devait être interprété à la lumière de la raison. &lt;/p&gt; &lt;p&gt;
 Un des principaux enseignements du mutazilisme était la doctrine de la "Justice divine" (Al-'Adl wa al-Tawhid). Selon cette doctrine, Dieu était juste et ne pouvait pas ordonner ou commettre des actes injustes. Ils soutenaient également le concept de libre arbitre humain, affirmant que les humains étaient responsables de leurs propres actes et qu'ils devaient être récompensés ou punis en fonction de leurs actions. &lt;/p&gt; &lt;p&gt; Les principes fondamentaux du mutazilisme comprennent : &lt;/p&gt;
@@ -4263,147 +4399,147 @@
 &lt;p&gt;A partir du IXe siècle, le courant a perdu de son influence en raison de l'opposition des théologiens conservateurs et de l'arrivée au pouvoir de califes plus traditionalistes et a graduellement décliné en tant que courant théologique distinct, bien qu'il ait laissé une empreinte durable sur le développement de la pensée islamique. &lt;/p&gt; &lt;audio controls title="Le néo mutazilisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-13.10.2019-ITEMA_22174473-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F43" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="G41" s="11" t="s">
+      <c r="G43" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="2" t="s">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="M43" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t xml:space="preserve">Kalâm</t>
         </is>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14" t="n">
+    <row r="44" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="n">
         <v>750</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14" t="s">
+      <c r="B44" s="14"/>
+      <c r="C44" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D44" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E42" s="19" t="inlineStr">
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/V%C3%A9danta"  title=" Wikipedia"&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;
 </t>
         </is>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F44" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="G44" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="2" t="s">
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t xml:space="preserve">Brahmanisme</t>
         </is>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
+    <row r="45" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C45" s="1" t="n">
         <v>800</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D45" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adva%C3%AFta_v%C3%A9danta" title="Wikipedia"&gt;L’Advaïta Védanta&lt;/a&gt;, le « Védânta non dualiste », est la plus influente des écoles issues du Védânta, la réflexion sur les Upanishad, textes qui forment la « fin des Védas ». Sa thèse tient en une formule : le Soi individuel (&lt;em&gt;ātman&lt;/em&gt;) et l’Absolu (&lt;em&gt;brahman&lt;/em&gt;) ne font qu’un. Il est systématisé au VIIIe siècle par &lt;a href="https://fr.wikipedia.org/wiki/Adi_Shankara" title=" Wikipedia"&gt;Shankara&lt;/a&gt;, à la suite de Gaudapada.&lt;/p&gt; &lt;p&gt;Pour Shankara, seul le &lt;em&gt;brahman&lt;/em&gt; est pleinement réel : conscience pure, infinie et sans qualités, il est l’être même de toute chose. Le monde multiple que nous percevons n’est pas un pur néant, mais une apparence, &lt;em&gt;māyā&lt;/em&gt;, comparable à la corde que l’on prend dans la pénombre pour un serpent. Notre sentiment d’être un individu séparé vient de l’ignorance (&lt;em&gt;avidyā&lt;/em&gt;), qui attribue au Soi des caractères qui ne sont pas les siens : le corps, les sens, le moi. La délivrance (&lt;em&gt;mokṣa&lt;/em&gt;) n’est donc ni un lieu à atteindre ni le fruit d’actions ou de rites : elle est la connaissance directe de cette identité, exprimée par les grandes paroles des Upanishad, « Tu es Cela » ou « Je suis brahman ». Shankara fonde aussi des monastères aux quatre coins de l’Inde.&lt;/p&gt; &lt;p&gt;Contesté par Ramanuja et Madhva, qui défendent un Dieu personnel, l’Advaïta devient au XIXe siècle, avec &lt;a href="https://fr.wikipedia.org/wiki/Vivekananda" title=" Wikipedia"&gt;Vivekananda&lt;/a&gt;, le visage de l’hindouisme en Occident. Ramana Maharshi en a été au XXe siècle un maître célèbre, enseignant à ses visiteurs une seule question : « Qui suis-je ? ». On a souvent rapproché sa doctrine de Parménide, de Plotin ou de Spinoza.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="J45" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="K45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t xml:space="preserve">Védanta</t>
         </is>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="n">
+    <row r="46" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="n">
         <v>820</v>
       </c>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9" t="s">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D46" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Soufisme" title=" Wikipedia"&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;
 Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou "soufis") qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; 
@@ -4412,93 +4548,95 @@
 Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title="Qu'est ce que le Soufisme ? par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F46" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="G44" s="11" t="s">
+      <c r="G46" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="2" t="s">
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N44" s="1" t="s">
+      <c r="N46" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="O44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P44" s="1" t="inlineStr">
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P46" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie et mystique de l’islam</t>
         </is>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
+    <row r="47" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C47" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D47" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F45" s="1" t="s">
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_islamique"   title=" Wikipedia"&gt;Falsafa&lt;/a&gt; est le nom donné à la philosophie rationnelle pratique  dans le monde arabo-islamique médiéval, de Bagdad à Cordoue, entre le IXe et le XIIe siècle. Née du grand mouvement de traduction des textes grecs (Aristote, Platon, Plotin) en arabe, elle tente d'harmoniser la raison grecque avec la révélation islamique.&lt;/p&gt;&lt;p&gt;Al-Kindi (801–873), considéré comme le "père de la Falsafa", fut le premier à introduire la philosophie grecque dans la pensée islamique. Al-Farabi (872–950) construisit une cité idéale philosophique inspirée de Platon. Avicenne (Ibn Sina, 980–1037) synthétisa Aristote et le néoplatonisme dans une vision de l'être, de l'âme et de l'intellect d'une portée immense.&lt;/p&gt;&lt;p&gt;Ces philosophes furent confrontés à une tension fondamentale : la raison peut-elle contredire la foi ? Al-Ghazali répondit par un "oui" dévastateur dans son Incohérence des philosophes. Averroès (Ibn Rushd, 1126–1198) répondit à son tour dans l'Incohérence de l'incohérence, défendant la compatibilité de la philosophie et de l'islam.&lt;/p&gt;&lt;p&gt;La Falsafa transmit aux philosophes chrétiens du Moyen Âge (Thomas d'Aquin, Albert le Grand) l'Aristote qui leur était inconnu. Sans elle, la scolastique européenne n'aurait pas existé sous la forme que nous lui connaissons. Elle reste l'un des grands carrefours de l'histoire intellectuelle de l'humanité.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="J47" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="K47" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie et mystique de l’islam</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t xml:space="preserve">Aristotélisme;Néoplatonisme</t>
         </is>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="14" t="n">
+    <row r="48" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="n">
         <v>890</v>
       </c>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14" t="s">
+      <c r="B48" s="14"/>
+      <c r="C48" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D48" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Acharisme"   title=" Wikipedia"&gt;L'Acharisme&lt;/a&gt; est une école théologique sunnite de l'islam, fondée par Abu al-Hasan al-Ash'ari. Il était à l'origine un théologien mutazilite, mais il a finalement rejeté leurs idées et a développé sa propre doctrine théologique qui est devenue connue sous le nom d'acharisme. &lt;/p&gt; &lt;p&gt;
 L'acharisme est basé sur la croyance en l'unicité de Dieu (tawhid) et l'acceptation de la révélation coranique et de la sunna (les enseignements et pratiques du prophète Mahomet). La principale préoccupation de l'acharisme est de défendre et de rationaliser les croyances islamiques face à diverses idées philosophiques et théologiques en circulation à l'époque. &lt;/p&gt; &lt;p&gt;
@@ -4508,115 +4646,22 @@
  &lt;/p&gt;   &lt;audio controls title="La doctrine acharite par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-23.04.2023-ITEMA_23356900-2023C26163E0013-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F48" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="G46" s="16" t="s">
+      <c r="G48" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="2" t="s">
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mutazilisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensée juive</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Herméneutique juive;Falsafa</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e" title=" Wikipedia"&gt;Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement de la pensée confucéenne dans la péninsule coréenne. Arrivé dès l’époque des Trois Royaumes, le confucianisme inspire sous la dynastie Goryeo l’organisation de l’État, avec l’instauration en 958 d’examens pour recruter les fonctionnaires. À la fin du XIIIe siècle, le néoconfucianisme de Zhu Xi est introduit depuis la Chine. Il devient la doctrine officielle de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9riode_Joseon" title=" Wikipedia"&gt;dynastie Joseon&lt;/a&gt; (1392-1910), dont les fondateurs s’appuient sur des lettrés qui veulent réformer l’État et réduire l’influence du bouddhisme.&lt;/p&gt; &lt;p&gt;Deux figures dominent ce courant au XVIe siècle. &lt;a href="https://fr.wikipedia.org/wiki/Yi_Hwang" title=" Wikipedia"&gt;Yi Hwang&lt;/a&gt;, dit Toegye (1501-1570), affirme la primauté du principe (&lt;em&gt;li&lt;/em&gt;), réalité immatérielle et morale, sur l’énergie matérielle (&lt;em&gt;gi&lt;/em&gt;). Il en sort une célèbre controverse, le « débat des quatre et des sept » : les quatre sentiments moraux, comme la compassion, naissent-ils du principe, et les sept émotions ordinaires, comme la colère ou la joie, de l’énergie ? &lt;a href="https://fr.wikipedia.org/wiki/Yi_I" title=" Wikipedia"&gt;Yi I&lt;/a&gt;, dit Yulgok (1536-1584), défend au contraire leur unité dynamique : le principe n’agit jamais sans l’énergie. Ce débat, qui oppose ensuite des écoles rivales, structure la philosophie coréenne pendant des siècles.&lt;/p&gt; &lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (&lt;em&gt;seonbi&lt;/em&gt;) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (&lt;em&gt;seowon&lt;/em&gt;) diffusent cet idéal dans tout le pays. Au XVIIIe siècle, le mouvement Silhak, le « savoir pratique », le tourne vers les réformes concrètes. Son empreinte demeure profonde dans la Corée d’aujourd’hui : respect des aînés, valorisation de l’éducation, rites familiaux et éthique du travail.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4625,146 +4670,141 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianismes</t>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Néoconfucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Mutazilisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
+        <v>900</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herméneutique juive;Falsafa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C50" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_azt%C3%A8que" title=" Wikipedia"&gt;La Pensée nahua&lt;/a&gt; désigne la réflexion philosophique des peuples de langue nahuatl, dont les Aztèques ou Mexicas, dans le Mexique central avant la conquête espagnole de 1521. Elle était portée par les &lt;em&gt;tlamatinime&lt;/em&gt;, « ceux qui savent quelque chose », sages et maîtres du &lt;em&gt;calmecac&lt;/em&gt;, l’école où l’on formait les jeunes nobles. Nous la connaissons par des codex, des chants et des discours recueillis après la conquête, notamment par le franciscain Bernardino de Sahagún.&lt;/p&gt; &lt;p&gt;L’historien mexicain &lt;a href="https://fr.wikipedia.org/wiki/Miguel_Le%C3%B3n-Portilla" title=" Wikipedia"&gt;Miguel León-Portilla&lt;/a&gt; l’a fait connaître dans &lt;em&gt;La filosofía náhuatl estudiada en sus fuentes&lt;/em&gt; (1956). Les sages s’interrogent sur la fragilité de l’existence : sur terre tout est passager, comme les fleurs qui se fanent, et l’on se demande si quelque chose est vrai, enraciné. Leur réponse est &lt;em&gt;in xochitl in cuicatl&lt;/em&gt;, « la fleur et le chant », c’est-à-dire la poésie, seule capable peut-être de dire le vrai. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Nezahualc%C3%B3yotl" title=" Wikipedia"&gt;Nezahualcóyotl&lt;/a&gt;, souverain de Texcoco au XVe siècle, auquel on attribue de nombreux poèmes, en est la grande figure. Le principe suprême, Ometeotl, « dieu de la dualité », unit le masculin et le féminin ; le monde est fait de couples complémentaires, vie et mort, ordre et désordre, en équilibre instable. Le temps est cyclique : quatre « soleils », quatre âges du monde, ont déjà été détruits, et nous vivons sous le cinquième.&lt;/p&gt; &lt;p&gt;Plus récemment, le philosophe James Maffie a lu dans le &lt;em&gt;teotl&lt;/em&gt; une énergie sacrée, unique et toujours en mouvement, dont toutes choses sont des aspects. Cette pensée est aujourd’hui étudiée comme une véritable tradition philosophique.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mLi2f452GNo</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Aztec Philosophy with James Maffie" par Hermitix Podcast</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mysticisme mésoaméricain</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>1150</v>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>1150</v>
-      </c>
       <c r="D50" s="12" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ishraqisme"  title="Wikipedia"&gt;L’Ishraqisme&lt;/a&gt;, ou philosophie de l’Illumination (&lt;em&gt;ishrâq&lt;/em&gt;, le lever du soleil), est le courant fondé par le penseur persan &lt;a href="https://fr.wikipedia.org/wiki/Sohrawardi" title=" Wikipedia"&gt;Sohrawardi&lt;/a&gt; (1154-1191). Dans son &lt;em&gt;Livre de la sagesse orientale&lt;/em&gt;, où l’« Orient » désigne la source de la lumière plutôt qu’un lieu, il veut unir la philosophie grecque, en particulier Platon et le néoplatonisme, la sagesse de l’ancienne Perse et la mystique soufie en une vision fondée sur la lumière.&lt;/p&gt; &lt;p&gt;Pour Sohrawardi, toute la réalité est un déploiement de la Lumière des lumières, qui est Dieu. Les êtres s’ordonnent selon leur degré de lumière, des intelligences angéliques jusqu’aux ténèbres de la matière, qui n’est que lumière absente. La connaissance véritable n’est pas d’abord un raisonnement : c’est une « connaissance par présence », immédiate, comme celle que l’âme a d’elle-même. Elle s’acquiert par la purification et l’expérience spirituelle autant que par la logique, et Sohrawardi critique sur ce point Avicenne. Il décrit aussi un monde intermédiaire entre l’esprit et le corps, le monde des images, où se situent les visions des prophètes et des mystiques. Ses récits symboliques, comme &lt;em&gt;Le Bruissement des ailes de Gabriel&lt;/em&gt;, racontent l’exil de l’âme et son retour vers l’Orient de la lumière.&lt;/p&gt; &lt;p&gt;Accusé d’hérésie par les juristes, il est exécuté à Alep avec l’accord de Saladin, d’où son surnom de « maître tué » (&lt;em&gt;al-maqtûl&lt;/em&gt;). Sa pensée nourrit pourtant l’école d’Ispahan et &lt;a href="https://fr.wikipedia.org/wiki/Molla_Sadra_Chirazi" title=" Wikipedia"&gt;Mollâ Sadrâ&lt;/a&gt;. &lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin" title=" Wikipedia"&gt;Henry Corbin&lt;/a&gt; l’a fait connaître en Occident au XXe siècle, en le traduisant et en le commentant.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e" title=" Wikipedia"&gt;Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement de la pensée confucéenne dans la péninsule coréenne. Arrivé dès l’époque des Trois Royaumes, le confucianisme inspire sous la dynastie Goryeo l’organisation de l’État, avec l’instauration en 958 d’examens pour recruter les fonctionnaires. À la fin du XIIIe siècle, le néoconfucianisme de Zhu Xi est introduit depuis la Chine. Il devient la doctrine officielle de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9riode_Joseon" title=" Wikipedia"&gt;dynastie Joseon&lt;/a&gt; (1392-1910), dont les fondateurs s’appuient sur des lettrés qui veulent réformer l’État et réduire l’influence du bouddhisme.&lt;/p&gt; &lt;p&gt;Deux figures dominent ce courant au XVIe siècle. &lt;a href="https://fr.wikipedia.org/wiki/Yi_Hwang" title=" Wikipedia"&gt;Yi Hwang&lt;/a&gt;, dit Toegye (1501-1570), affirme la primauté du principe (&lt;em&gt;li&lt;/em&gt;), réalité immatérielle et morale, sur l’énergie matérielle (&lt;em&gt;gi&lt;/em&gt;). Il en sort une célèbre controverse, le « débat des quatre et des sept » : les quatre sentiments moraux, comme la compassion, naissent-ils du principe, et les sept émotions ordinaires, comme la colère ou la joie, de l’énergie ? &lt;a href="https://fr.wikipedia.org/wiki/Yi_I" title=" Wikipedia"&gt;Yi I&lt;/a&gt;, dit Yulgok (1536-1584), défend au contraire leur unité dynamique : le principe n’agit jamais sans l’énergie. Ce débat, qui oppose ensuite des écoles rivales, structure la philosophie coréenne pendant des siècles.&lt;/p&gt; &lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (&lt;em&gt;seonbi&lt;/em&gt;) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (&lt;em&gt;seowon&lt;/em&gt;) diffusent cet idéal dans tout le pays. Au XVIIIe siècle, le mouvement Silhak, le « savoir pratique », le tourne vers les réformes concrètes. Son empreinte demeure profonde dans la Corée d’aujourd’hui : respect des aînés, valorisation de l’éducation, rites familiaux et éthique du travail.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F50" s="1" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
-        </is>
-      </c>
-      <c r="Q50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Falsafa;Soufisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="n">
-        <v>1150</v>
-      </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="E51" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oconfucianisme"  title=" Wikipedia"&gt;Le Néoconfucianisme&lt;/a&gt; est le renouveau du confucianisme qui s’épanouit en Chine sous la dynastie Song (960-1279). Face au bouddhisme et au taoïsme, qui offraient une métaphysique et une spiritualité plus riches, des lettrés relisent les Classiques pour donner à la morale confucéenne un fondement cosmique. Devenu orthodoxie d’État, il domine la Chine jusqu’en 1905, ainsi que la Corée, le Japon et le Vietnam.&lt;/p&gt; &lt;p&gt;Zhou Dunyi médite sur le « Faîte suprême » d’où naissent le yin et le yang ; les frères Cheng distinguent en toute chose le &lt;em&gt;li&lt;/em&gt;, principe ou ordre rationnel, et le &lt;em&gt;qi&lt;/em&gt;, souffle ou énergie matérielle. &lt;a href="https://fr.wikipedia.org/wiki/Zhu_Xi" title=" Wikipedia"&gt;Zhu Xi&lt;/a&gt; (1130-1200) fait la synthèse de cette « école du Principe » : chaque être porte en lui le principe universel, et la nature humaine est bonne, comme le disait Mencius, mais obscurcie par un souffle impur. On se perfectionne par l’« investigation des choses », l’étude et la méditation assise. Ses commentaires des Quatre Livres servent de base aux examens impériaux de 1313 à 1905. Contre lui, Lu Jiuyuan puis &lt;a href="https://fr.wikipedia.org/wiki/Wang_Yangming" title=" Wikipedia"&gt;Wang Yangming&lt;/a&gt; (1472-1529) fondent l’« école du Cœur » : le principe n’est pas à chercher dans les choses mais dans le cœur, et la connaissance est inséparable de l’action.&lt;/p&gt; &lt;p&gt;Critiqué au XVIIIe siècle par l’école des études critiques, le &lt;em&gt;kaozheng&lt;/em&gt;, puis par la modernisation, il inspire encore au XXe siècle le « nouveau confucianisme ». En Corée, Yi Hwang et Yi I en débattent au XVIe siècle, et au Japon la doctrine de Zhu Xi devient celle du shogunat Tokugawa.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_azt%C3%A8que" title=" Wikipedia"&gt;La Pensée nahua&lt;/a&gt; désigne la réflexion philosophique des peuples de langue nahuatl, dont les Aztèques ou Mexicas, dans le Mexique central avant la conquête espagnole de 1521. Elle était portée par les &lt;em&gt;tlamatinime&lt;/em&gt;, « ceux qui savent quelque chose », sages et maîtres du &lt;em&gt;calmecac&lt;/em&gt;, l’école où l’on formait les jeunes nobles. Nous la connaissons par des codex, des chants et des discours recueillis après la conquête, notamment par le franciscain Bernardino de Sahagún.&lt;/p&gt; &lt;p&gt;L’historien mexicain &lt;a href="https://fr.wikipedia.org/wiki/Miguel_Le%C3%B3n-Portilla" title=" Wikipedia"&gt;Miguel León-Portilla&lt;/a&gt; l’a fait connaître dans &lt;em&gt;La filosofía náhuatl estudiada en sus fuentes&lt;/em&gt; (1956). Les sages s’interrogent sur la fragilité de l’existence : sur terre tout est passager, comme les fleurs qui se fanent, et l’on se demande si quelque chose est vrai, enraciné. Leur réponse est &lt;em&gt;in xochitl in cuicatl&lt;/em&gt;, « la fleur et le chant », c’est-à-dire la poésie, seule capable peut-être de dire le vrai. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Nezahualc%C3%B3yotl" title=" Wikipedia"&gt;Nezahualcóyotl&lt;/a&gt;, souverain de Texcoco au XVe siècle, auquel on attribue de nombreux poèmes, en est la grande figure. Le principe suprême, Ometeotl, « dieu de la dualité », unit le masculin et le féminin ; le monde est fait de couples complémentaires, vie et mort, ordre et désordre, en équilibre instable. Le temps est cyclique : quatre « soleils », quatre âges du monde, ont déjà été détruits, et nous vivons sous le cinquième.&lt;/p&gt; &lt;p&gt;Plus récemment, le philosophe James Maffie a lu dans le &lt;em&gt;teotl&lt;/em&gt; une énergie sacrée, unique et toujours en mouvement, dont toutes choses sont des aspects. Cette pensée est aujourd’hui étudiée comme une véritable tradition philosophique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mLi2f452GNo</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Aztec Philosophy with James Maffie" par Hermitix Podcast</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4773,88 +4813,90 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianismes</t>
+          <t xml:space="preserve">Pensées autochtones</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Mysticisme mésoaméricain</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bushido" title="Wikipedia"&gt;Le Bushido&lt;/a&gt;, la « voie du guerrier », désigne l’éthique des samouraïs, la classe militaire qui domine le Japon de l’époque de Kamakura (1185-1333) jusqu’au milieu du XIXe siècle. Ce n’est pas un code écrit unique, mais un ensemble de valeurs qui se forment peu à peu et ne sont mises en forme qu’à l’époque d’Edo (1603-1868), quand les guerriers, en temps de paix, deviennent administrateurs.&lt;/p&gt; &lt;p&gt;Le bushido mêle plusieurs sources : du confucianisme, il retient la loyauté envers le seigneur, la piété filiale et le sens du devoir ; du bouddhisme zen, la maîtrise de soi et le détachement face à la mort ; du shintō, le respect des ancêtres. Le guerrier doit être droit, courageux, bienveillant, poli, sincère, et préférer l’honneur à la vie : le suicide rituel, le &lt;em&gt;seppuku&lt;/em&gt;, permet d’effacer une faute ou d’échapper à la honte. Au XVIIe siècle, Yamaga Sokō définit le rôle moral du samouraï en temps de paix, et Miyamoto Musashi, dans le &lt;em&gt;Traité des cinq roues&lt;/em&gt;, fait de l’art du sabre une voie de perfection. Le &lt;a href="https://fr.wikipedia.org/wiki/Hagakure" title=" Wikipedia"&gt;&lt;em&gt;Hagakure&lt;/em&gt;&lt;/a&gt;, recueil des propos de Yamamoto Tsunetomo, affirme : « la voie du samouraï, je l’ai trouvée dans la mort ».&lt;/p&gt; &lt;p&gt;L’image moderne du bushido doit beaucoup à &lt;a href="https://fr.wikipedia.org/wiki/Inaz%C5%8D_Nitobe" title=" Wikipedia"&gt;Nitobe Inazō&lt;/a&gt;, dont le livre &lt;em&gt;Bushido, l’âme du Japon&lt;/em&gt; (1900), écrit en anglais, le présente comme une morale nationale comparable à la chevalerie. Exalté par le militarisme japonais jusqu’en 1945, il survit dans les arts martiaux et nourrit encore l’image que le monde se fait du Japon.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Illuminationism"  title="Wikipedia"&gt;L’Ishraqisme&lt;/a&gt;, ou philosophie de l’Illumination (&lt;em&gt;ishrâq&lt;/em&gt;, le lever du soleil), est le courant fondé par le penseur persan &lt;a href="https://fr.wikipedia.org/wiki/Sohrawardi" title=" Wikipedia"&gt;Sohrawardi&lt;/a&gt; (1154-1191). Dans son &lt;em&gt;Livre de la sagesse orientale&lt;/em&gt;, où l’« Orient » désigne la source de la lumière plutôt qu’un lieu, il veut unir la philosophie grecque, en particulier Platon et le néoplatonisme, la sagesse de l’ancienne Perse et la mystique soufie en une vision fondée sur la lumière.&lt;/p&gt; &lt;p&gt;Pour Sohrawardi, toute la réalité est un déploiement de la Lumière des lumières, qui est Dieu. Les êtres s’ordonnent selon leur degré de lumière, des intelligences angéliques jusqu’aux ténèbres de la matière, qui n’est que lumière absente. La connaissance véritable n’est pas d’abord un raisonnement : c’est une « connaissance par présence », immédiate, comme celle que l’âme a d’elle-même. Elle s’acquiert par la purification et l’expérience spirituelle autant que par la logique, et Sohrawardi critique sur ce point Avicenne. Il décrit aussi un monde intermédiaire entre l’esprit et le corps, le monde des images, où se situent les visions des prophètes et des mystiques. Ses récits symboliques, comme &lt;em&gt;Le Bruissement des ailes de Gabriel&lt;/em&gt;, racontent l’exil de l’âme et son retour vers l’Orient de la lumière.&lt;/p&gt; &lt;p&gt;Accusé d’hérésie par les juristes, il est exécuté à Alep avec l’accord de Saladin, d’où son surnom de « maître tué » (&lt;em&gt;al-maqtûl&lt;/em&gt;). Sa pensée nourrit pourtant l’école d’Ispahan et &lt;a href="https://fr.wikipedia.org/wiki/Molla_Sadra_Chirazi" title=" Wikipedia"&gt;Mollâ Sadrâ&lt;/a&gt;. &lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin" title=" Wikipedia"&gt;Henry Corbin&lt;/a&gt; l’a fait connaître en Occident au XXe siècle, en le traduisant et en le commentant.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F52" s="1" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Japon : shintō et voies nationales</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme Zen;Shintoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_vietnamienne" title=" Wikipedia"&gt;La Philosophie vietnamienne&lt;/a&gt; se caractérise par le Tam Giáo, les « trois enseignements » : une alliance durable entre le confucianisme, le bouddhisme et le taoïsme, à laquelle s’ajoutent le culte des ancêtres et celui des génies protecteurs des villages. Un adage vietnamien dit que « les trois enseignements ont une même source ». Chacun a son domaine : le confucianisme règle la famille et l’État, le bouddhisme la vie spirituelle, le taoïsme la médecine, la divination et les rites du quotidien.&lt;/p&gt; &lt;p&gt;Le bouddhisme arrive très tôt, dès les premiers siècles de notre ère, par la mer et par la Chine. Après l’indépendance, en 939, les dynasties Lý et Trần le favorisent : le roi &lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;Trần Nhân Tông&lt;/a&gt;, vainqueur des invasions mongoles, abdique en 1293 pour se faire moine et fonde l’école zen de Trúc Lâm, la « Forêt de bambous », proprement vietnamienne. Le confucianisme s’impose ensuite comme doctrine de l’État : le Temple de la Littérature est fondé à Hanoï en 1070, et les concours mandarinaux recrutent les fonctionnaires jusqu’en 1919. Mais les lettrés formés aux classiques confucéens pratiquaient souvent le bouddhisme dans leur vie personnelle et se retiraient volontiers en ermites taoïstes : les trois voies se complètent plus qu’elles ne s’opposent. &lt;a href="https://fr.wikipedia.org/wiki/Nguy%E1%BB%85n_Tr%C3%A3i" title=" Wikipedia"&gt;Nguyễn Trãi&lt;/a&gt; au XVe siècle, Nguyễn Bỉnh Khiêm au XVIe ou Lê Quý Đôn au XVIIIe illustrent cette sagesse composite.&lt;/p&gt; &lt;p&gt;Au XXe siècle, ce syncrétisme inspire de nouvelles religions comme le caodaïsme, tandis que le marxisme devient la doctrine officielle. L’empreinte du Tam Giáo demeure dans les rites familiaux et la morale.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOWcduKGZYI</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Sự khác nhau của Nho giáo, Đạo giáo và Phật giáo - Tam Giáo Đồng Nguyên là gì?" par Radio Suy Ngẫm</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
+      <c r="Q52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsafa;Soufisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oconfucianisme"  title=" Wikipedia"&gt;Le Néoconfucianisme&lt;/a&gt; est le renouveau du confucianisme qui s’épanouit en Chine sous la dynastie Song (960-1279). Face au bouddhisme et au taoïsme, qui offraient une métaphysique et une spiritualité plus riches, des lettrés relisent les Classiques pour donner à la morale confucéenne un fondement cosmique. Devenu orthodoxie d’État, il domine la Chine jusqu’en 1905, ainsi que la Corée, le Japon et le Vietnam.&lt;/p&gt; &lt;p&gt;Zhou Dunyi médite sur le « Faîte suprême » d’où naissent le yin et le yang ; les frères Cheng distinguent en toute chose le &lt;em&gt;li&lt;/em&gt;, principe ou ordre rationnel, et le &lt;em&gt;qi&lt;/em&gt;, souffle ou énergie matérielle. &lt;a href="https://fr.wikipedia.org/wiki/Zhu_Xi" title=" Wikipedia"&gt;Zhu Xi&lt;/a&gt; (1130-1200) fait la synthèse de cette « école du Principe » : chaque être porte en lui le principe universel, et la nature humaine est bonne, comme le disait Mencius, mais obscurcie par un souffle impur. On se perfectionne par l’« investigation des choses », l’étude et la méditation assise. Ses commentaires des Quatre Livres servent de base aux examens impériaux de 1313 à 1905. Contre lui, Lu Jiuyuan puis &lt;a href="https://fr.wikipedia.org/wiki/Wang_Yangming" title=" Wikipedia"&gt;Wang Yangming&lt;/a&gt; (1472-1529) fondent l’« école du Cœur » : le principe n’est pas à chercher dans les choses mais dans le cœur, et la connaissance est inséparable de l’action.&lt;/p&gt; &lt;p&gt;Critiqué au XVIIIe siècle par l’école des études critiques, le &lt;em&gt;kaozheng&lt;/em&gt;, puis par la modernisation, il inspire encore au XXe siècle le « nouveau confucianisme ». En Corée, Yi Hwang et Yi I en débattent au XVIe siècle, et au Japon la doctrine de Zhu Xi devient celle du shogunat Tokugawa.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G53" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
       <c r="J53" s="2" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>22</v>
@@ -4869,49 +4911,44 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+          <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianisme;Bouddhisme Mahayana</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="D54" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EqO4cPcG4KY</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Le SIKHISME : La religion qui affirme que "DIEU N'A PAS DE RELIGION" (Le message de l'Unité)" par Mystica</t>
-        </is>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>457</v>
+        <v>1200</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bushido" title="Wikipedia"&gt;Le Bushido&lt;/a&gt;, la « voie du guerrier », désigne l’éthique des samouraïs, la classe militaire qui domine le Japon de l’époque de Kamakura (1185-1333) jusqu’au milieu du XIXe siècle. Ce n’est pas un code écrit unique, mais un ensemble de valeurs qui se forment peu à peu et ne sont mises en forme qu’à l’époque d’Edo (1603-1868), quand les guerriers, en temps de paix, deviennent administrateurs.&lt;/p&gt; &lt;p&gt;Le bushido mêle plusieurs sources : du confucianisme, il retient la loyauté envers le seigneur, la piété filiale et le sens du devoir ; du bouddhisme zen, la maîtrise de soi et le détachement face à la mort ; du shintō, le respect des ancêtres. Le guerrier doit être droit, courageux, bienveillant, poli, sincère, et préférer l’honneur à la vie : le suicide rituel, le &lt;em&gt;seppuku&lt;/em&gt;, permet d’effacer une faute ou d’échapper à la honte. Au XVIIe siècle, Yamaga Sokō définit le rôle moral du samouraï en temps de paix, et Miyamoto Musashi, dans le &lt;em&gt;Traité des cinq roues&lt;/em&gt;, fait de l’art du sabre une voie de perfection. Le &lt;a href="https://fr.wikipedia.org/wiki/Hagakure" title=" Wikipedia"&gt;&lt;em&gt;Hagakure&lt;/em&gt;&lt;/a&gt;, recueil des propos de Yamamoto Tsunetomo, affirme : « la voie du samouraï, je l’ai trouvée dans la mort ».&lt;/p&gt; &lt;p&gt;L’image moderne du bushido doit beaucoup à &lt;a href="https://fr.wikipedia.org/wiki/Inaz%C5%8D_Nitobe" title=" Wikipedia"&gt;Nitobe Inazō&lt;/a&gt;, dont le livre &lt;em&gt;Bushido, l’âme du Japon&lt;/em&gt; (1900), écrit en anglais, le présente comme une morale nationale comparable à la chevalerie. Exalté par le militarisme japonais jusqu’en 1945, il survit dans les arts martiaux et nourrit encore l’image que le monde se fait du Japon.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>43</v>
+        <v>285</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -4920,42 +4957,48 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hindouismes de dévotion</t>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bhakti;Soufisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="366" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Bouddhisme Zen;Shintoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
-        <v>1650</v>
+        <v>1300</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>1650</v>
+        <v>1300</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J55" s="23" t="s">
-        <v>295</v>
+        <v>286</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_vietnamienne" title=" Wikipedia"&gt;La Philosophie vietnamienne&lt;/a&gt; se caractérise par le Tam Giáo, les « trois enseignements » : une alliance durable entre le confucianisme, le bouddhisme et le taoïsme, à laquelle s’ajoutent le culte des ancêtres et celui des génies protecteurs des villages. Un adage vietnamien dit que « les trois enseignements ont une même source ». Chacun a son domaine : le confucianisme règle la famille et l’État, le bouddhisme la vie spirituelle, le taoïsme la médecine, la divination et les rites du quotidien.&lt;/p&gt; &lt;p&gt;Le bouddhisme arrive très tôt, dès les premiers siècles de notre ère, par la mer et par la Chine. Après l’indépendance, en 939, les dynasties Lý et Trần le favorisent : le roi &lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;Trần Nhân Tông&lt;/a&gt;, vainqueur des invasions mongoles, abdique en 1293 pour se faire moine et fonde l’école zen de Trúc Lâm, la « Forêt de bambous », proprement vietnamienne. Le confucianisme s’impose ensuite comme doctrine de l’État : le Temple de la Littérature est fondé à Hanoï en 1070, et les concours mandarinaux recrutent les fonctionnaires jusqu’en 1919. Mais les lettrés formés aux classiques confucéens pratiquaient souvent le bouddhisme dans leur vie personnelle et se retiraient volontiers en ermites taoïstes : les trois voies se complètent plus qu’elles ne s’opposent. &lt;a href="https://fr.wikipedia.org/wiki/Nguy%E1%BB%85n_Tr%C3%A3i" title=" Wikipedia"&gt;Nguyễn Trãi&lt;/a&gt; au XVe siècle, Nguyễn Bỉnh Khiêm au XVIe ou Lê Quý Đôn au XVIIIe illustrent cette sagesse composite.&lt;/p&gt; &lt;p&gt;Au XXe siècle, ce syncrétisme inspire de nouvelles religions comme le caodaïsme, tandis que le marxisme devient la doctrine officielle. L’empreinte du Tam Giáo demeure dans les rites familiaux et la morale.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOWcduKGZYI</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Sự khác nhau của Nho giáo, Đạo giáo và Phật giáo - Tam Giáo Đồng Nguyên là gì?" par Radio Suy Ngẫm</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>290</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -4964,502 +5007,504 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme;Bouddhisme Mahayana</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EqO4cPcG4KY</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Le SIKHISME : La religion qui affirme que "DIEU N'A PAS DE RELIGION" (Le message de l'Unité)" par Mystica</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouismes de dévotion</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bhakti;Soufisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="366" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
         <v>1650</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Néoconfucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="14" t="n">
-        <v>1680</v>
-      </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="F57" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="2" t="s">
-        <v>307</v>
+      <c r="C57" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J57" s="23" t="s">
+        <v>295</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="M58" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="14" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="F59" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t xml:space="preserve">Japon : shintō et voies nationales</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t xml:space="preserve">Shintoïsme</t>
         </is>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="14" t="n">
+    <row r="60" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="14" t="n">
         <v>1720</v>
       </c>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14" t="n">
+      <c r="B60" s="14"/>
+      <c r="C60" s="14" t="n">
         <v>1720</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D60" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="E58" s="19" t="inlineStr">
+      <c r="E60" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fondamentalisme"   title=" Wikipedia"&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient, principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : la contestation des lois civiles au nom de la loi divine ; la mobilisation électorale ou militante de groupes religieux ; parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; 
  &lt;audio controls title="les religions ; le fondamentalisme chrétien par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F60" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="G60" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Fondamentalisme par Le Savoir Partagé</t>
         </is>
       </c>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="23" t="s">
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="23" t="s">
         <v>312</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Réveils de l’islam moderne</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1">
-        <v>1740</v>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1740</t>
-        </is>
-      </c>
-      <c r="D59" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hassidisme</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;Le hassidisme&lt;/a&gt;, de l’hébreu &lt;em&gt;hassid&lt;/em&gt;, « pieux », est un mouvement de renouveau mystique du judaïsme né au XVIIIe siècle en Podolie, dans l’actuelle Ukraine, alors polonaise, autour du Baal Shem Tov, le « Maître du Bon Nom ». Il paraît dans des communautés juives pauvres et éprouvées par les massacres et par la faillite du faux messie Sabbataï Tsevi, où le savoir talmudique est réservé à une élite.&lt;/p&gt; &lt;p&gt;Reprenant les idées de la Kabbale, le hassidisme les met à la portée de tous. Dieu est présent partout, jusque dans les choses les plus humbles : on peut donc le servir non seulement par l’étude, mais par la prière fervente, le chant, la danse et chaque geste du quotidien, accompli avec attention. La joie est une forme de piété, la tristesse un obstacle. La ferveur du cœur compte plus que l’érudition, et le plus simple des fidèles peut s’unir à Dieu. Au centre de chaque communauté se tient le &lt;a href="https://fr.wikipedia.org/wiki/Tsadik" title=" Wikipedia"&gt;&lt;em&gt;tsaddik&lt;/em&gt;&lt;/a&gt;, le « juste », maître spirituel qui guide ses disciples et intercède pour eux. Les maîtres hassidiques enseignent par des récits et des paraboles, comme ceux de &lt;a href="https://fr.wikipedia.org/wiki/Nahman_de_Bratslav" title=" Wikipedia"&gt;Nahman de Bratslav&lt;/a&gt;, arrière-petit-fils du Baal Shem Tov.&lt;/p&gt; &lt;p&gt;Combattu d’abord par les rabbins traditionnels, les &lt;a href="https://fr.wikipedia.org/wiki/Mitnagdim" title=" Wikipedia"&gt;Mitnagdim&lt;/a&gt;, le mouvement gagne une grande partie des Juifs d’Europe de l’Est. Presque anéanti par la Shoah, il renaît aux États-Unis et en Israël, où ses communautés, comme celle de Loubavitch, sont aujourd’hui très vivantes. Martin Buber a fait connaître ses récits en Occident ; Abraham Heschel et Elie Wiesel, issus de familles hassidiques, en ont transmis l’esprit.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ph9ZTOd6E54</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"C'est quoi le hassidisme ?" par Hugo Brdl</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement mystique juif né en Ukraine autour du Baal Shem Tov : servir Dieu dans la joie, l’humilité et chaque geste du quotidien.</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAAL SHEM TOV;Martin BUBER</t>
-        </is>
-      </c>
-      <c r="M59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">islam-juif</t>
-        </is>
-      </c>
-      <c r="N59"/>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensée juive</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kabbale</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
-        <v>1750</v>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>1750</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Silhak" title=" Wikipedia"&gt;Le Silhak&lt;/a&gt;, ou « savoir pratique », est un mouvement de réforme intellectuelle né en Corée au XVIIe siècle, sous la dynastie Joseon, et qui s’épanouit au XVIIIe. Il naît d’un pays ruiné par les invasions japonaises (1592-1598) puis mandchoues (1627 et 1636) : des lettrés reprochent alors au néoconfucianisme officiel de s’enfermer dans des querelles métaphysiques sur le principe et l’énergie, pendant que les paysans meurent de faim. Leur mot d’ordre, venu de Chine, est de « chercher la vérité dans les faits ».&lt;/p&gt; &lt;p&gt;Le premier grand nom en est Yu Hyeongwon (1622-1673), qui propose de redistribuer les terres à ceux qui les cultivent. Yi Ik (1681-1763) poursuit cette école du « bon gouvernement du monde » en critiquant l’esclavage, les privilèges héréditaires et le mépris du travail manuel. Une seconde branche, l’école des « études du Nord », autour de Pak Ji-won (1737-1805) et de Pak Je-ga, veut plutôt développer le commerce, les routes et les techniques, à l’exemple de la Chine des Qing. Le Silhak s’ouvre aussi aux sciences occidentales introduites en Chine par les jésuites : astronomie, cartographie, mathématiques.&lt;/p&gt; &lt;p&gt;Il culmine avec &lt;a href="https://fr.wikipedia.org/wiki/Jeong_Yak-yong" title=" Wikipedia"&gt;Jeong Yak-yong&lt;/a&gt; (1762-1836), dit Dasan, qui réunit les deux branches. Exilé dix-huit ans après la persécution des catholiques de 1801, il y écrit près de cinq cents volumes, dont un manuel pour bien administrer le peuple. Le calligraphe Kim Jeong-hui (1786-1856) en est l’un des derniers représentants. Marginalisé en son temps, le Silhak est aujourd’hui vu comme l’un des ferments de la modernité coréenne.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M60" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réveils de l’islam moderne</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1">
+        <v>1740</v>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1740</t>
+        </is>
+      </c>
+      <c r="D61" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hassidisme</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;Le hassidisme&lt;/a&gt;, de l’hébreu &lt;em&gt;hassid&lt;/em&gt;, « pieux », est un mouvement de renouveau mystique du judaïsme né au XVIIIe siècle en Podolie, dans l’actuelle Ukraine, alors polonaise, autour du Baal Shem Tov, le « Maître du Bon Nom ». Il paraît dans des communautés juives pauvres et éprouvées par les massacres et par la faillite du faux messie Sabbataï Tsevi, où le savoir talmudique est réservé à une élite.&lt;/p&gt; &lt;p&gt;Reprenant les idées de la Kabbale, le hassidisme les met à la portée de tous. Dieu est présent partout, jusque dans les choses les plus humbles : on peut donc le servir non seulement par l’étude, mais par la prière fervente, le chant, la danse et chaque geste du quotidien, accompli avec attention. La joie est une forme de piété, la tristesse un obstacle. La ferveur du cœur compte plus que l’érudition, et le plus simple des fidèles peut s’unir à Dieu. Au centre de chaque communauté se tient le &lt;a href="https://fr.wikipedia.org/wiki/Tsadik" title=" Wikipedia"&gt;&lt;em&gt;tsaddik&lt;/em&gt;&lt;/a&gt;, le « juste », maître spirituel qui guide ses disciples et intercède pour eux. Les maîtres hassidiques enseignent par des récits et des paraboles, comme ceux de &lt;a href="https://fr.wikipedia.org/wiki/Nahman_de_Bratslav" title=" Wikipedia"&gt;Nahman de Bratslav&lt;/a&gt;, arrière-petit-fils du Baal Shem Tov.&lt;/p&gt; &lt;p&gt;Combattu d’abord par les rabbins traditionnels, les &lt;a href="https://fr.wikipedia.org/wiki/Mitnagdim" title=" Wikipedia"&gt;Mitnagdim&lt;/a&gt;, le mouvement gagne une grande partie des Juifs d’Europe de l’Est. Presque anéanti par la Shoah, il renaît aux États-Unis et en Israël, où ses communautés, comme celle de Loubavitch, sont aujourd’hui très vivantes. Martin Buber a fait connaître ses récits en Occident ; Abraham Heschel et Elie Wiesel, issus de familles hassidiques, en ont transmis l’esprit.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ph9ZTOd6E54</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"C'est quoi le hassidisme ?" par Hugo Brdl</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement mystique juif né en Ukraine autour du Baal Shem Tov : servir Dieu dans la joie, l’humilité et chaque geste du quotidien.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
+        </is>
+      </c>
+      <c r="L61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAAL SHEM TOV;Martin BUBER</t>
+        </is>
+      </c>
+      <c r="M61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
+        </is>
+      </c>
+      <c r="N61"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensée juive</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kabbale</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Silhak" title=" Wikipedia"&gt;Le Silhak&lt;/a&gt;, ou « savoir pratique », est un mouvement de réforme intellectuelle né en Corée au XVIIe siècle, sous la dynastie Joseon, et qui s’épanouit au XVIIIe. Il naît d’un pays ruiné par les invasions japonaises (1592-1598) puis mandchoues (1627 et 1636) : des lettrés reprochent alors au néoconfucianisme officiel de s’enfermer dans des querelles métaphysiques sur le principe et l’énergie, pendant que les paysans meurent de faim. Leur mot d’ordre, venu de Chine, est de « chercher la vérité dans les faits ».&lt;/p&gt; &lt;p&gt;Le premier grand nom en est Yu Hyeongwon (1622-1673), qui propose de redistribuer les terres à ceux qui les cultivent. Yi Ik (1681-1763) poursuit cette école du « bon gouvernement du monde » en critiquant l’esclavage, les privilèges héréditaires et le mépris du travail manuel. Une seconde branche, l’école des « études du Nord », autour de Pak Ji-won (1737-1805) et de Pak Je-ga, veut plutôt développer le commerce, les routes et les techniques, à l’exemple de la Chine des Qing. Le Silhak s’ouvre aussi aux sciences occidentales introduites en Chine par les jésuites : astronomie, cartographie, mathématiques.&lt;/p&gt; &lt;p&gt;Il culmine avec &lt;a href="https://fr.wikipedia.org/wiki/Jeong_Yak-yong" title=" Wikipedia"&gt;Jeong Yak-yong&lt;/a&gt; (1762-1836), dit Dasan, qui réunit les deux branches. Exilé dix-huit ans après la persécution des catholiques de 1801, il y écrit près de cinq cents volumes, dont un manuel pour bien administrer le peuple. Le calligraphe Kim Jeong-hui (1786-1856) en est l’un des derniers représentants. Marginalisé en son temps, le Silhak est aujourd’hui vu comme l’un des ferments de la modernité coréenne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M62" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianisme coréen</t>
         </is>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="9" t="n">
+    <row r="63" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="n">
         <v>1760</v>
       </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9" t="s">
+      <c r="B63" s="9"/>
+      <c r="C63" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D63" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martinisme" title=" Wikipedia"&gt;Le Martinisme&lt;/a&gt; est un courant ésotérique et mystique d’inspiration judéo-chrétienne, né en France au XVIIIe siècle dans les milieux de la franc-maçonnerie. Il doit son nom à deux hommes que l’on confond souvent : Martinès de Pasqually (vers 1727-1774), théurge à l’origine mal connue, et son disciple &lt;a href="https://fr.wikipedia.org/wiki/Louis-Claude_de_Saint-Martin" title=" Wikipedia"&gt;Louis-Claude de Saint-Martin&lt;/a&gt; (1743-1803), dit le « Philosophe inconnu ». Son thème central est la « réintégration » : le retour de l’être humain à la dignité spirituelle qu’il avait avant la chute.&lt;/p&gt; &lt;p&gt;Vers 1761, Martinès fonde l’ordre des Élus Coëns, dont les loges s’établissent à Bordeaux, Lyon et Paris. Dans son &lt;em&gt;Traité de la réintégration des êtres&lt;/em&gt;, il enseigne que l’homme, créé pour servir d’intermédiaire entre Dieu et le monde, a chuté par orgueil, comme Adam, et se trouve exilé dans la matière. Pour se racheter, il doit pratiquer l’ascèse, la prière et la théurgie, des rites destinés à entrer en contact avec les esprits bienfaisants. Saint-Martin, d’abord son secrétaire, délaisse ces rites pour une « voie intérieure », celle du cœur, nourrie par le mystique allemand Jacob Böhme. À Lyon, Jean-Baptiste Willermoz transmet leur doctrine au Rite écossais rectifié, une branche de la franc-maçonnerie qui existe toujours.&lt;/p&gt; &lt;p&gt;À la fin du XIXe siècle, l’occultiste Papus fonde un Ordre martiniste, et au XXe siècle Robert Ambelain fait renaître les Élus Coëns. On distingue depuis le « martinésisme », théurgique, et le « saint-martinisme », mystique. Joseph de Maistre, Balzac ou Franz von Baader ont lu Saint-Martin.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F63" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="G61" s="11" t="s">
+      <c r="G63" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="2" t="s">
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="K61" s="2" t="s">
+      <c r="K63" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M61" s="2" t="s">
+      <c r="M63" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ésotérismes et gnoses</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t xml:space="preserve">Kabbale</t>
         </is>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1">
+    <row r="64" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1">
         <v>1770</v>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1770</t>
         </is>
       </c>
-      <c r="D62" s="28" t="inlineStr">
+      <c r="D64" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Haskala</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Haskala" title=" Wikipedia"&gt;La Haskala&lt;/a&gt;, de l’hébreu &lt;em&gt;sekhel&lt;/em&gt;, « intelligence », est le mouvement des Lumières juives, né à Berlin dans les années 1770. Ses partisans, les &lt;em&gt;maskilim&lt;/em&gt;, veulent faire sortir les Juifs du ghetto culturel où les ont enfermés des siècles de discriminations, en les ouvrant aux sciences, à la philosophie et aux langues de l’Europe, sans qu’ils renoncent pour autant à leur foi.&lt;/p&gt; &lt;p&gt;Son inspirateur est Moses Mendelssohn, surnommé le « Socrate de Berlin », admiré de Kant et ami de &lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing" title=" Wikipedia"&gt;Lessing&lt;/a&gt;, qui fait de lui le modèle de son &lt;em&gt;Nathan le Sage&lt;/em&gt;. Il traduit la Torah en allemand, imprimée en caractères hébraïques, pour que les Juifs apprennent la langue du pays. Dans &lt;em&gt;Jérusalem&lt;/em&gt; (1783), il défend la liberté de conscience et la séparation de l’État et de la religion : le judaïsme, dit-il, n’impose pas de croyances, il prescrit des pratiques, et ses vérités sont celles de la raison, accessibles à tous les hommes. Autour de lui, le médecin Marcus Herz, élève de Kant, et David Friedländer, qui plaide pour l’émancipation civile des Juifs de Prusse, poursuivent son œuvre. La Haskala fonde des écoles modernes, une presse et fait renaître l’hébreu comme langue littéraire profane.&lt;/p&gt; &lt;p&gt;Au XIXe siècle, elle gagne la Galicie et l’Empire russe. Elle prépare le &lt;a href="https://fr.wikipedia.org/wiki/Juda%C3%AFsme_r%C3%A9form%C3%A9" title=" Wikipedia"&gt;judaïsme libéral&lt;/a&gt;, la &lt;a href="https://fr.wikipedia.org/wiki/Wissenschaft_des_Judentums" title=" Wikipedia"&gt;« science du judaïsme »&lt;/a&gt;, l’étude historique de sa tradition, et indirectement le sionisme. Ses adversaires lui ont reproché d’ouvrir la voie à l’assimilation ; ses héritiers y voient l’entrée du judaïsme dans la modernité.&lt;/p&gt;  &lt;audio controls title="le jadudaîsme de la modernité par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13094-09.11.2014-ITEMA_20688848-2014C21364E0044-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t xml:space="preserve">0a3g3J3rIQc</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">"The Haskalah (Essential Lectures in Jewish History)" par Henry Abramson</t>
         </is>
       </c>
-      <c r="J62" s="1" t="inlineStr">
+      <c r="J64" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">les « Lumières juives » de Mendelssohn : unir la fidélité au judaïsme, la raison et la culture européenne.</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie politique;Théologie et spiritualité</t>
         </is>
       </c>
-      <c r="L62" s="1" t="inlineStr">
+      <c r="L64" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Moses MENDELSSOHN</t>
         </is>
       </c>
-      <c r="M62" s="1" t="inlineStr">
+      <c r="M64" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensée juive</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t xml:space="preserve">Lumières</t>
         </is>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="14" t="n">
+    <row r="65" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="14" t="n">
         <v>1820</v>
       </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14" t="n">
+      <c r="B65" s="14"/>
+      <c r="C65" s="14" t="n">
         <v>1820</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D65" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="E63" s="16" t="s">
+      <c r="E65" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F65" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="G63" s="16" t="s">
+      <c r="G65" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="H63" s="14"/>
-      <c r="I63" s="16"/>
-      <c r="J63" s="2" t="s">
+      <c r="H65" s="14"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="K65" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Romantisme;Idéalisme allemand</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
-        <v>1830</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Réveils de l’islam moderne</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lumières</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>1840</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9osophie" title=" Wikipedia"&gt;La Théosophie&lt;/a&gt; est un courant ésotérique et spirituel fondé par &lt;a href="https://fr.wikipedia.org/wiki/Helena_Blavatsky" title=" Wikipedia"&gt;Helena Blavatsky&lt;/a&gt; (1831-1891), née dans l’Empire russe, qui crée à New York en 1875, avec le colonel américain Henry Steel Olcott et William Quan Judge, la &lt;a href="https://fr.wikipedia.org/wiki/Soci%C3%A9t%C3%A9_th%C3%A9osophique" title=" Wikipedia"&gt;Société théosophique&lt;/a&gt;. Le mot, du grec &lt;em&gt;theos&lt;/em&gt;, « dieu », et &lt;em&gt;sophia&lt;/em&gt;, « sagesse », signifie « sagesse divine » : la Théosophie se veut la redécouverte d’une sagesse universelle et cachée, dont les religions, les sciences et les philosophies ne seraient que des expressions partielles.&lt;/p&gt; &lt;p&gt;La Société se donne trois buts : former le noyau d’une fraternité universelle de l’humanité, sans distinction de race, de croyance, de sexe ou de caste ; encourager l’étude comparée des religions, des philosophies et des sciences ; étudier les lois inexpliquées de la nature et les pouvoirs latents de l’homme. Blavatsky expose sa doctrine dans &lt;em&gt;Isis dévoilée&lt;/em&gt; (1877) et &lt;em&gt;La Doctrine secrète&lt;/em&gt; (1888), où elle mêle le bouddhisme, l’hindouisme, la Kabbale et le néoplatonisme : l’univers procède d’un principe unique, l’humanité traverse de longs cycles d’évolution et l’âme progresse par réincarnations successives selon la loi du karma. Elle dit tenir ces enseignements de « Maîtres » vivant au Tibet. Les fondateurs s’installent en Inde en 1879, et le siège est fixé à Adyar, près de Madras, en 1882.&lt;/p&gt; &lt;p&gt;Annie Besant, présidente à partir de 1907, présente le jeune Jiddu Krishnamurti comme un futur instructeur du monde, rôle qu’il refuse en 1929. Rudolf Steiner s’en sépare pour fonder l’anthroposophie. La Théosophie a marqué des artistes comme Kandinsky et Mondrian, le mouvement New Age et la diffusion en Occident de l’hindouisme et du bouddhisme.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>76</v>
@@ -5471,196 +5516,192 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Romantisme;Idéalisme allemand</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="n">
+        <v>1830</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réveils de l’islam moderne</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lumières</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9osophie" title=" Wikipedia"&gt;La Théosophie&lt;/a&gt; est un courant ésotérique et spirituel fondé par &lt;a href="https://fr.wikipedia.org/wiki/Helena_Blavatsky" title=" Wikipedia"&gt;Helena Blavatsky&lt;/a&gt; (1831-1891), née dans l’Empire russe, qui crée à New York en 1875, avec le colonel américain Henry Steel Olcott et William Quan Judge, la &lt;a href="https://fr.wikipedia.org/wiki/Soci%C3%A9t%C3%A9_th%C3%A9osophique" title=" Wikipedia"&gt;Société théosophique&lt;/a&gt;. Le mot, du grec &lt;em&gt;theos&lt;/em&gt;, « dieu », et &lt;em&gt;sophia&lt;/em&gt;, « sagesse », signifie « sagesse divine » : la Théosophie se veut la redécouverte d’une sagesse universelle et cachée, dont les religions, les sciences et les philosophies ne seraient que des expressions partielles.&lt;/p&gt; &lt;p&gt;La Société se donne trois buts : former le noyau d’une fraternité universelle de l’humanité, sans distinction de race, de croyance, de sexe ou de caste ; encourager l’étude comparée des religions, des philosophies et des sciences ; étudier les lois inexpliquées de la nature et les pouvoirs latents de l’homme. Blavatsky expose sa doctrine dans &lt;em&gt;Isis dévoilée&lt;/em&gt; (1877) et &lt;em&gt;La Doctrine secrète&lt;/em&gt; (1888), où elle mêle le bouddhisme, l’hindouisme, la Kabbale et le néoplatonisme : l’univers procède d’un principe unique, l’humanité traverse de longs cycles d’évolution et l’âme progresse par réincarnations successives selon la loi du karma. Elle dit tenir ces enseignements de « Maîtres » vivant au Tibet. Les fondateurs s’installent en Inde en 1879, et le siège est fixé à Adyar, près de Madras, en 1882.&lt;/p&gt; &lt;p&gt;Annie Besant, présidente à partir de 1907, présente le jeune Jiddu Krishnamurti comme un futur instructeur du monde, rôle qu’il refuse en 1929. Rudolf Steiner s’en sépare pour fonder l’anthroposophie. La Théosophie a marqué des artistes comme Kandinsky et Mondrian, le mouvement New Age et la diffusion en Occident de l’hindouisme et du bouddhisme.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ésotérismes et gnoses</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t xml:space="preserve">Hermétisme;Hindouisme</t>
         </is>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="14" t="n">
+    <row r="68" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="14" t="n">
         <v>1845</v>
       </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14" t="n">
+      <c r="B68" s="14"/>
+      <c r="C68" s="14" t="n">
         <v>1845</v>
       </c>
-      <c r="D66" s="15" t="s">
+      <c r="D68" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E68" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Occidentalisme"  title=" Wikipedia"&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; 
  &lt;audio controls title="l’Occidentalisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="F68" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="G66" s="16" t="s">
+      <c r="G68" s="16" t="s">
         <v>346</v>
-      </c>
-      <c r="H66" s="14"/>
-      <c r="I66" s="16"/>
-      <c r="J66" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
-        </is>
-      </c>
-      <c r="Q66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Idéalisme allemand</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="F67" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="H67" s="14"/>
-      <c r="I67" s="16"/>
-      <c r="J67" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Inde moderne</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hindouisme;Lumières</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Intuitivisme"  title=" Wikipedia"&gt; L’Intuitivisme&lt;/a&gt;  est un courant philosophique russe qui privilégie la connaissance immédiate par l'intuition plutôt que par la médiation des sens ou des concepts. Il s'inscrit dans une tradition mystique orthodoxe où philosophie et religion fusionnent, rejetant le dualisme sujet-objet propre à la pensée occidentale. Ses figures emblématiques, comme Nicolas Lossky et Siméon Frank, en font un pilier de la philosophie russe spiritualiste. &lt;/p&gt; &lt;p&gt; Ce courant repose sur le principe d'une saisie directe de la réalité, où l'être se présente originairement dans la conscience sans voile ni intermédiaire. Lossky, par exemple, critique le kantisme en affirmant que les objets de la connaissance sont les "choses en soi" et non des phénomènes construits, grâce à une intuition qui transcende les sensations. Vrai et être y sont identiques, garantissant une vérité objective par la présence même de l'objet dans l'esprit. &lt;/p&gt; &lt;p&gt; Lossky distingue trois formes d'intuition : sensible (sur le monde et le corps), intellectuelle (sur les lois idéales) et mystique (sur Dieu et les sphères métalogiques). Cette triade permet une connaissance intégrale, incluant le religieux sans justification épistémologique séparée. Elle surmonte ainsi le "dédoublement artificiel" du monde opéré par les sensations, vues comme trans-subjectives et objectives. &lt;/p&gt; &lt;p&gt; L'intuitivisme s'oppose à l'épistémologie occidentale, valorisant l'ontologisme où l'être prime sur le savoir. Il prolonge les slavophiles et Soloviev, dans un climat de tension entre Logos mystique et ratio discursive. Sous l'ère soviétique, des penseurs comme B. N. Babynine l'adaptent à un réalisme matérialiste, via des recueils comme Les voies du réalisme. &lt;/p&gt; &lt;p&gt; Malgré la révolution bolchevique, l'intuitivisme persiste en émigration et influence la pensée religieuse russe, affirmant une union possible entre l'esprit humain et le divin sur Terre. Il incarne le refus russe d'une connaissance fragmentée, au profit d'une vision unitaire et vivante de la réalité. Ce courant reste une clé pour comprendre la spécificité philosophique russe. &lt;/p&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="s">
-        <v>355</v>
-      </c>
-      <c r="G68" s="16" t="s">
-        <v>356</v>
       </c>
       <c r="H68" s="14"/>
       <c r="I68" s="16"/>
       <c r="J68" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Philosophie religieuse russe</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Slavophilisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
-        <v>1860</v>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>1860</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt;Le Donghak&lt;/a&gt;, ou « savoir de l’Orient », est un mouvement religieux et social fondé en Corée en 1860 par Choe Je-u (1824-1864), un lettré déclassé. Il naît dans une société Joseon minée par la corruption, les épidémies et la misère paysanne, et inquiète devant l’Occident : la Chine vient d’être humiliée par la seconde guerre de l’opium, et le catholicisme, appelé « savoir de l’Occident » (&lt;em&gt;seohak&lt;/em&gt;), progresse malgré les persécutions. Choe Je-u dit avoir reçu une révélation du « Seigneur du Ciel » et veut opposer au savoir étranger une voie coréenne.&lt;/p&gt; &lt;p&gt;Sa doctrine mêle le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale est que chaque être humain « porte en lui le Ciel » (&lt;em&gt;si cheonju&lt;/em&gt;) : il faut donc « servir l’homme comme le Ciel », enseigne son successeur Choe Si-hyeong, et le mouvement finira par dire que « l’homme est le Ciel » (&lt;em&gt;in nae cheon&lt;/em&gt;). Il en découle une égalité radicale entre les nobles et les serviteurs, les hommes et les femmes, les riches et les pauvres. Les fidèles récitent une formule sacrée de vingt et un caractères et attendent l’« ouverture » d’un monde nouveau.&lt;/p&gt; &lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement gagne les campagnes et inspire en 1894 la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_paysanne_Donghak" title=" Wikipedia"&gt;révolution paysanne du Donghak&lt;/a&gt;, menée par Jeon Bong-jun ; l’arrivée de troupes chinoises et japonaises pour l’écraser déclenche la guerre sino-japonaise. Rebaptisé Cheondogyo, « religion de la Voie céleste », en 1905, il joue un grand rôle dans le mouvement d’indépendance du 1er mars 1919.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="G69" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>362</v>
+      <c r="N68" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
+        </is>
+      </c>
+      <c r="Q68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idéalisme allemand</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B69" s="14"/>
+      <c r="C69" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>349</v>
+      </c>
+      <c r="F69" s="14" t="s">
+        <v>350</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="H69" s="14"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="2" t="s">
+        <v>352</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1" t="s">
-        <v>101</v>
+      <c r="M69" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -5669,41 +5710,45 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+          <t xml:space="preserve">L’Inde moderne</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confucianisme coréen;Taoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
-        <v>1865</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_(art)"  title=" Wikipedia"&gt;Le Symbolisme&lt;/a&gt; est un courant littéraire, artistique et philosophique né en France dans les années 1880 et qui s’épanouit en Russie au tournant du XXe siècle. Il prend pour modèle le sonnet « Correspondances » de &lt;a href="https://fr.wikipedia.org/wiki/Charles_Baudelaire" title=" Wikipedia"&gt;Baudelaire&lt;/a&gt;, où la nature est une « forêt de symboles » : derrière le monde visible se cache une réalité spirituelle que le poète peut faire pressentir. Le manifeste de Jean Moréas paraît en 1886 ; Mallarmé, Verlaine, et en peinture Gustave Moreau ou Odilon Redon, incarnent le mouvement.&lt;/p&gt; &lt;p&gt;En Russie, il naît dans les années 1890 avec Dmitri Merejkovski, Valéri Brioussov et Constantin Balmont, puis prend une dimension métaphysique et religieuse avec une seconde génération, nourrie de la philosophie de &lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir Soloviev&lt;/a&gt; et de sa figure de la Sophia, la Sagesse divine. Pour Viatcheslav Ivanov, dont l’appartement de Saint-Pétersbourg, la « Tour », est le grand salon de l’époque, l’art doit aller « du réel au plus réel ». Pour Andreï Biély, le symbole unit la connaissance et la création, et le symbolisme devient une véritable vision du monde. Alexandre Blok chante la « Belle Dame », figure mystique de la Sophia, avant d’écrire en 1918 &lt;em&gt;Les Douze&lt;/em&gt;, poème de la révolution. Ces poètes-philosophes conçoivent l’art comme une « théurgie », une action capable de transformer le monde et de préparer sa transfiguration. Le symbolisme russe mêle la mystique orthodoxe, l’idéalisme allemand et Nietzsche.&lt;/p&gt; &lt;p&gt;Vers 1910, il entre en crise et laisse place à l’acméisme et au futurisme. Il a profondément marqué la philosophie religieuse russe de l’âge d’argent.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>367</v>
-      </c>
+          <t xml:space="preserve">Hindouisme;Lumières</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B70" s="14"/>
+      <c r="C70" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Intuitivisme"  title=" Wikipedia"&gt; L’Intuitivisme&lt;/a&gt;  est un courant philosophique russe qui privilégie la connaissance immédiate par l'intuition plutôt que par la médiation des sens ou des concepts. Il s'inscrit dans une tradition mystique orthodoxe où philosophie et religion fusionnent, rejetant le dualisme sujet-objet propre à la pensée occidentale. Ses figures emblématiques, comme Nicolas Lossky et Siméon Frank, en font un pilier de la philosophie russe spiritualiste. &lt;/p&gt; &lt;p&gt; Ce courant repose sur le principe d'une saisie directe de la réalité, où l'être se présente originairement dans la conscience sans voile ni intermédiaire. Lossky, par exemple, critique le kantisme en affirmant que les objets de la connaissance sont les "choses en soi" et non des phénomènes construits, grâce à une intuition qui transcende les sensations. Vrai et être y sont identiques, garantissant une vérité objective par la présence même de l'objet dans l'esprit. &lt;/p&gt; &lt;p&gt; Lossky distingue trois formes d'intuition : sensible (sur le monde et le corps), intellectuelle (sur les lois idéales) et mystique (sur Dieu et les sphères métalogiques). Cette triade permet une connaissance intégrale, incluant le religieux sans justification épistémologique séparée. Elle surmonte ainsi le "dédoublement artificiel" du monde opéré par les sensations, vues comme trans-subjectives et objectives. &lt;/p&gt; &lt;p&gt; L'intuitivisme s'oppose à l'épistémologie occidentale, valorisant l'ontologisme où l'être prime sur le savoir. Il prolonge les slavophiles et Soloviev, dans un climat de tension entre Logos mystique et ratio discursive. Sous l'ère soviétique, des penseurs comme B. N. Babynine l'adaptent à un réalisme matérialiste, via des recueils comme Les voies du réalisme. &lt;/p&gt; &lt;p&gt; Malgré la révolution bolchevique, l'intuitivisme persiste en émigration et influence la pensée religieuse russe, affirmant une union possible entre l'esprit humain et le divin sur Terre. Il incarne le refus russe d'une connaissance fragmentée, au profit d'une vision unitaire et vivante de la réalité. Ce courant reste une clé pour comprendre la spécificité philosophique russe. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="H70" s="14"/>
+      <c r="I70" s="16"/>
       <c r="J70" s="2" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>76</v>
@@ -5720,40 +5765,40 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophiologie</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9" t="n">
-        <v>1870</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="E71" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="G71" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="H71" s="9"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="2" t="s">
-        <v>373</v>
+          <t xml:space="preserve">Slavophilisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>1860</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt;Le Donghak&lt;/a&gt;, ou « savoir de l’Orient », est un mouvement religieux et social fondé en Corée en 1860 par Choe Je-u (1824-1864), un lettré déclassé. Il naît dans une société Joseon minée par la corruption, les épidémies et la misère paysanne, et inquiète devant l’Occident : la Chine vient d’être humiliée par la seconde guerre de l’opium, et le catholicisme, appelé « savoir de l’Occident » (&lt;em&gt;seohak&lt;/em&gt;), progresse malgré les persécutions. Choe Je-u dit avoir reçu une révélation du « Seigneur du Ciel » et veut opposer au savoir étranger une voie coréenne.&lt;/p&gt; &lt;p&gt;Sa doctrine mêle le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale est que chaque être humain « porte en lui le Ciel » (&lt;em&gt;si cheonju&lt;/em&gt;) : il faut donc « servir l’homme comme le Ciel », enseigne son successeur Choe Si-hyeong, et le mouvement finira par dire que « l’homme est le Ciel » (&lt;em&gt;in nae cheon&lt;/em&gt;). Il en découle une égalité radicale entre les nobles et les serviteurs, les hommes et les femmes, les riches et les pauvres. Les fidèles récitent une formule sacrée de vingt et un caractères et attendent l’« ouverture » d’un monde nouveau.&lt;/p&gt; &lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement gagne les campagnes et inspire en 1894 la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_paysanne_Donghak" title=" Wikipedia"&gt;révolution paysanne du Donghak&lt;/a&gt;, menée par Jeon Bong-jun ; l’arrivée de troupes chinoises et japonaises pour l’écraser déclenche la guerre sino-japonaise. Rebaptisé Cheondogyo, « religion de la Voie céleste », en 1905, il joue un grand rôle dans le mouvement d’indépendance du 1er mars 1919.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G71" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>58</v>
+        <v>22</v>
+      </c>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -5762,42 +5807,41 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Réveils de l’islam moderne</t>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nahda</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="14" t="n">
-        <v>1878</v>
-      </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14" t="n">
-        <v>1878</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="E72" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="F72" s="14" t="s">
-        <v>376</v>
-      </c>
-      <c r="G72" s="16" t="s">
-        <v>377</v>
-      </c>
-      <c r="H72" s="14"/>
-      <c r="I72" s="16"/>
+          <t xml:space="preserve">Confucianisme coréen;Taoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
+        <v>1865</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_(art)"  title=" Wikipedia"&gt;Le Symbolisme&lt;/a&gt; est un courant littéraire, artistique et philosophique né en France dans les années 1880 et qui s’épanouit en Russie au tournant du XXe siècle. Il prend pour modèle le sonnet « Correspondances » de &lt;a href="https://fr.wikipedia.org/wiki/Charles_Baudelaire" title=" Wikipedia"&gt;Baudelaire&lt;/a&gt;, où la nature est une « forêt de symboles » : derrière le monde visible se cache une réalité spirituelle que le poète peut faire pressentir. Le manifeste de Jean Moréas paraît en 1886 ; Mallarmé, Verlaine, et en peinture Gustave Moreau ou Odilon Redon, incarnent le mouvement.&lt;/p&gt; &lt;p&gt;En Russie, il naît dans les années 1890 avec Dmitri Merejkovski, Valéri Brioussov et Constantin Balmont, puis prend une dimension métaphysique et religieuse avec une seconde génération, nourrie de la philosophie de &lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir Soloviev&lt;/a&gt; et de sa figure de la Sophia, la Sagesse divine. Pour Viatcheslav Ivanov, dont l’appartement de Saint-Pétersbourg, la « Tour », est le grand salon de l’époque, l’art doit aller « du réel au plus réel ». Pour Andreï Biély, le symbole unit la connaissance et la création, et le symbolisme devient une véritable vision du monde. Alexandre Blok chante la « Belle Dame », figure mystique de la Sophia, avant d’écrire en 1918 &lt;em&gt;Les Douze&lt;/em&gt;, poème de la révolution. Ces poètes-philosophes conçoivent l’art comme une « théurgie », une action capable de transformer le monde et de préparer sa transfiguration. Le symbolisme russe mêle la mystique orthodoxe, l’idéalisme allemand et Nietzsche.&lt;/p&gt; &lt;p&gt;Vers 1910, il entre en crise et laisse place à l’acméisme et au futurisme. Il a profondément marqué la philosophie religieuse russe de l’âge d’argent.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>367</v>
+      </c>
       <c r="J72" s="2" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>379</v>
+        <v>22</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>76</v>
@@ -5812,630 +5856,615 @@
           <t xml:space="preserve">Philosophie religieuse russe</t>
         </is>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>1900</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>383</v>
-      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophiologie</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="B73" s="9"/>
+      <c r="C73" s="9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="E73" s="27" t="s">
+        <v>370</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="G73" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
       <c r="J73" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>108</v>
       </c>
       <c r="M73" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réveils de l’islam moderne</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nahda</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="B74" s="14"/>
+      <c r="C74" s="14" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="F74" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="H74" s="14"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie religieuse russe</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M75" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="N73" s="1" t="s">
+      <c r="N75" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="O73" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P73" s="1" t="inlineStr">
+      <c r="O75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P75" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
-      <c r="Q73" s="1" t="inlineStr">
+      <c r="Q75" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme</t>
         </is>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
+    <row r="76" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
         <v>1905</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C76" s="1" t="n">
         <v>1905</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D76" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="J74" s="2" t="s">
+      <c r="J76" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="K74" s="2" t="s">
+      <c r="K76" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M74" s="2" t="s">
+      <c r="M76" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t xml:space="preserve">L’Inde moderne</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t xml:space="preserve">Jaïnisme;Néo-védanta</t>
         </is>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
+    <row r="77" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="n">
         <v>1905</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C77" s="1" t="n">
         <v>1905</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D77" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="E75" s="21" t="inlineStr">
+      <c r="E77" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Empiriomonisme"  title="Wikipedia"&gt;L’Empiriomonisme&lt;/a&gt; est une doctrine philosophique développée par Alexandre Bogdanov qui cherche à penser la réalité comme une expérience unique et organisée, en refusant le dualisme strict entre matière et esprit. Bogdanov veut réunir l’empirisme et le monisme. Autrement dit, il affirme que toute connaissance vient de l’expérience, mais que cette expérience forme un tout cohérent, sans séparation fondamentale entre le monde physique et le monde psychique.&lt;/p&gt; &lt;p&gt; Les sources résument souvent sa pensée en trois grands points : le réalisme naïf, selon lequel nous percevons les choses telles qu’elles sont ; la primauté de la nature, qui signifie que les formes simples de la réalité sont premières ; le caractère secondaire de l’esprit, vu comme un produit de formes plus complexes d’organisation de l’expérience. &lt;/p&gt; &lt;p&gt; Dans cette perspective, la connaissance n’est pas une copie passive du monde : elle est une manière d’ordonner l’expérience. Bogdanov insiste sur des notions comme l’expérience et l’organisation, qui annoncent aussi sa future théorie de la tектologie, une science générale de l’organisation. &lt;/p&gt; &lt;p&gt; Il a été vivement critiqué par Lénine et Plekhanov, qui l’accusaient de dérive idéaliste et de révision du marxisme. Aujourd’hui, on le lit surtout comme un moment important des débats philosophiques du marxisme russe. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G77" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="J75" s="21" t="s">
+      <c r="J77" s="21" t="s">
         <v>394</v>
       </c>
-      <c r="K75" s="2" t="s">
+      <c r="K77" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M75" s="2" t="s">
+      <c r="M77" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t xml:space="preserve">Marxisme</t>
         </is>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
+    <row r="78" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
         <v>1911</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D78" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Ky%C5%8Dto"  title=" Wikipedia"&gt;L’école de Kyōto&lt;/a&gt; désigne le premier grand courant de philosophie moderne né au Japon, autour de &lt;a href="https://fr.wikipedia.org/wiki/Kitar%C5%8D_Nishida" title=" Wikipedia"&gt;Kitarō Nishida&lt;/a&gt; (1870-1945) et de ses successeurs à l’université impériale de Kyōto. On en fixe souvent le point de départ à 1911, date de la &lt;em&gt;Recherche sur le bien&lt;/em&gt;, où Nishida part de l’« expérience pure », antérieure à la séparation du sujet et de l’objet.&lt;/p&gt; &lt;p&gt;Ses penseurs, formés à la philosophie allemande, de Kant et Hegel à Husserl et Heidegger, veulent exprimer dans le langage de la philosophie occidentale l’expérience spirituelle de l’Asie, en particulier celle du bouddhisme zen et de la Terre pure. Au centre de leur réflexion se trouve la notion de « néant absolu » : non pas un simple manque, mais le fond ouvert d’où tout surgit, que Nishida pense comme le « lieu » (&lt;em&gt;basho&lt;/em&gt;) de toute réalité. Tanabe Hajime en tire une « philosophie de la repentance », et &lt;a href="https://fr.wikipedia.org/wiki/Keiji_Nishitani" title=" Wikipedia"&gt;Nishitani Keiji&lt;/a&gt; affronte le nihilisme européen : on ne le surmonte qu’en le traversant jusqu’à la vacuité. Watsuji Tetsurō et Kuki Shūzō, proches du groupe, l’ouvrent à l’éthique et à l’esthétique.&lt;/p&gt; &lt;p&gt;Plusieurs de ses membres furent compromis dans la justification idéologique de la guerre du Pacifique, ce qui a longtemps pesé sur sa réception. Depuis les années 1980, l’école est étudiée dans le monde entier comme le lieu d’un dialogue majeur entre la philosophie occidentale et les traditions spirituelles d’Asie. Ueda Shizuteru, mort en 2019, en a prolongé la pensée jusqu’à notre siècle.&lt;/p&gt;  &lt;audio controls title="Philosophie japonaise: l’école de Kyôto par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.11.2013-ITEMA_20549374-2013C12410E0320-NET_FC_EE7092B3-7D80-40AA-947D-AFAD338FBA01-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F78" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G78" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="J76" s="2" t="s">
+      <c r="J78" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="L78" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="M76" s="2" t="s">
+      <c r="M78" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
         <is>
           <t xml:space="preserve">Japon : shintō et voies nationales</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhisme Zen;Idéalisme allemand</t>
         </is>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
+    <row r="79" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="C77" s="1" t="n">
+      <c r="C79" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D79" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="F77" s="1" t="inlineStr">
+      <c r="F79" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">imzO0eNziD4</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">"B.R. Ambedkar: The Life of the Mind &amp; a Life in Politics" par Library of Congress</t>
         </is>
       </c>
-      <c r="J77" s="2" t="s">
+      <c r="J79" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="K79" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M77" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t xml:space="preserve">L’Inde moderne</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhisme</t>
         </is>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
+    <row r="80" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C80" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D80" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Logique_paracoh%C3%A9rente"  title=" Wikipedia"&gt;La Logique paraconsistante&lt;/a&gt; désigne les systèmes logiques qui peuvent contenir des contradictions sans s’effondrer. En logique classique, en effet, une seule contradiction suffit à tout démontrer : de « A et non-A », on peut déduire n’importe quelle proposition. C’est le &lt;a href="https://fr.wikipedia.org/wiki/Principe_d%27explosion" title=" Wikipedia"&gt;principe d’explosion&lt;/a&gt;, connu depuis le Moyen Âge sous la formule « du contradictoire suit n’importe quoi ». Une logique paraconsistante bloque cette explosion : une contradiction locale y reste locale, sans contaminer tout le reste.&lt;/p&gt; &lt;p&gt;L’idée apparaît en 1910, à Kazan, chez le philosophe russe Nikolaï Vassiliev (1880-1940). Il imagine une « logique imaginaire » où la loi de non-contradiction n’est plus un axiome nécessaire, de même que les géométries non euclidiennes, nées à Kazan avec Lobatchevski, avaient abandonné le postulat des parallèles. La même année, le Polonais Jan Łukasiewicz critique le principe de non-contradiction d’Aristote. Son élève Stanisław Jaśkowski construit en 1948 le premier système formel paraconsistant, et le Brésilien Newton da Costa développe à partir de 1963 toute une famille de ces logiques. Le mot « paraconsistant » est forgé en 1976 par le philosophe péruvien Francisco Miró Quesada. Certains vont plus loin, comme l’Australien &lt;a href="https://fr.wikipedia.org/wiki/Graham_Priest" title=" Wikipedia"&gt;Graham Priest&lt;/a&gt; : selon son « dialéthéisme », certaines contradictions sont vraies, par exemple le paradoxe du menteur, « cette phrase est fausse ».&lt;/p&gt; &lt;p&gt;Ces logiques servent en informatique, pour raisonner avec des bases de données incohérentes, en droit, face à des normes contradictoires, et en philosophie des sciences, quand des théories en conflit doivent coexister.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G80" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="J78" s="2" t="s">
+      <c r="J80" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="K80" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="M78" s="2" t="s">
+      <c r="M80" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie analytique et pragmatisme</t>
         </is>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
+    <row r="81" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="n">
         <v>1921</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C81" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D81" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nouveau_confucianisme"  title=" Wikipedia"&gt;Le nouveau confucianisme&lt;/a&gt; est un courant philosophique chinois du XXe siècle qui veut renouveler la tradition confucéenne pour l’accorder à la modernité. Il naît en réaction au mouvement du 4 Mai 1919 et à la Nouvelle Culture, qui rejetaient le confucianisme comme responsable du retard de la Chine et en appelaient à « Monsieur Science » et à « Monsieur Démocratie ». Ses penseurs veulent montrer qu’un confucianisme repensé peut accueillir la science et la démocratie sans perdre sa sagesse morale.&lt;/p&gt; &lt;p&gt;Le point de départ est l’ouvrage de &lt;a href="https://fr.wikipedia.org/wiki/Liang_Shuming" title=" Wikipedia"&gt;Liang Shuming&lt;/a&gt;, &lt;em&gt;Les Cultures d’Orient et d’Occident et leurs philosophies&lt;/em&gt; (1921), qui compare les voies de l’Occident, de la Chine et de l’Inde. &lt;a href="https://fr.wikipedia.org/wiki/Xiong_Shili" title=" Wikipedia"&gt;Xiong Shili&lt;/a&gt; donne au courant une métaphysique dans son &lt;em&gt;Nouveau traité de la conscience seule&lt;/em&gt; (1932) : s’inspirant du &lt;em&gt;Livre des mutations&lt;/em&gt;, il critique le bouddhisme pour qui le monde est illusion, et pense la réalité comme un mouvement créateur continu. Feng Youlan, dans son &lt;em&gt;Nouvel enseignement du principe&lt;/em&gt; (1939), relit Zhu Xi à l’aide de la logique moderne.&lt;/p&gt; &lt;p&gt;Après 1949, le courant se poursuit surtout à Hong Kong et à Taïwan. En 1958, Mou Zongsan, Tang Junyi, Xu Fuguan et Zhang Junmai publient un manifeste adressé au monde sur la culture chinoise. Mou Zongsan, traducteur des trois &lt;em&gt;Critiques&lt;/em&gt; de Kant, dialogue avec lui pour fonder une « métaphysique morale ». Une troisième génération, avec &lt;a href="https://fr.wikipedia.org/wiki/Tu_Weiming" title=" Wikipedia"&gt;Tu Weiming&lt;/a&gt; ou Liu Shu-hsien, a porté ce courant dans les universités américaines ; il connaît depuis les années 1980 un important renouveau en Chine continentale.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G81" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="J79" s="2" t="s">
+      <c r="J81" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="K79" s="2" t="s">
+      <c r="K81" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="L79" s="1" t="s">
+      <c r="L81" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="M81" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t xml:space="preserve">Néoconfucianisme</t>
         </is>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1">
+    <row r="82" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1">
         <v>1921</v>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1921</t>
         </is>
       </c>
-      <c r="D80" s="28" t="inlineStr">
+      <c r="D82" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Eurasisme</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;L’eurasisme&lt;/a&gt; est un courant de pensée né en 1921 dans l’émigration russe, après la révolution bolchevique, avec le recueil &lt;em&gt;L’Exode vers l’Orient&lt;/em&gt;, publié à Sofia par un petit groupe de jeunes intellectuels exilés : le linguiste &lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Sergue%C3%AFevitch_Troubetsko%C3%AF" title=" Wikipedia"&gt;Nikolaï Troubetskoï&lt;/a&gt;, le géographe Piotr Savitski, le musicologue Pierre Souvtchinski et le théologien Georges Florovsky.&lt;/p&gt; &lt;p&gt;Leur thèse est que la Russie n’est ni une partie de l’Europe ni une partie de l’Asie, mais un monde à part, l’« Eurasie », dont la grande plaine, des Carpates au Pacifique, a façonné l’unité des peuples slaves, turcs et finno-ougriens. Contre les occidentalistes, ils refusent l’idée d’une civilisation européenne universelle : dans &lt;em&gt;L’Europe et l’humanité&lt;/em&gt; (1920), Troubetskoï y voit l’égoïsme d’une culture « romano-germanique » qui s’impose aux autres. Contre les slavophiles, ils réhabilitent l’héritage asiatique de la Russie, et jusqu’à l’empire de Gengis Khan, qui aurait le premier unifié cet espace. Ils rêvent d’un État fondé sur une idéologie commune et sur l’orthodoxie, distinct à la fois de la démocratie libérale et du communisme. Florovsky s’en éloigne vite et critique en 1928 ce qu’il appelle une « vérité des questions » devenue une « erreur des réponses ». Le mouvement se divise à la fin des années 1920, une partie se rapprochant du régime soviétique.&lt;/p&gt; &lt;p&gt;Prolongé en URSS par l’historien &lt;a href="https://fr.wikipedia.org/wiki/Lev_Goumilev" title=" Wikipedia"&gt;Lev Goumilev&lt;/a&gt;, l’eurasisme renaît après 1991 sous la forme d’un « néo-eurasisme » porté par &lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Douguine" title=" Wikipedia"&gt;Alexandre Douguine&lt;/a&gt;, idéologue d’extrême droite, et influence aujourd’hui la géopolitique nationaliste et impériale de la Russie.&lt;/p&gt;  &lt;audio controls title="De l'idée à l'action : 4 doctrines géopolitiques . Eurasie : la Russie au centre du jeu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18720-25.03.2021-ITEMA_22614994-2021C16756S0084.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t xml:space="preserve">QodQ2ORmtKg</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t xml:space="preserve">"L'EURASISME : le projet géopolitique de la Russie ? - C Ce soir du 24 février 2022" par C Ce Soir - France Télévisions</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
+      <c r="J82" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">doctrine née dans l’émigration russe : la Russie ne serait ni l’Europe ni l’Asie, mais une civilisation à part, l’« Eurasie ».</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie politique</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
+      <c r="L82" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nikolaï TROUBETSKOÏ;Georges FLOROVSKY</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
+      <c r="M82" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">russe</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t xml:space="preserve">asie-est</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t xml:space="preserve">Slavophilisme</t>
         </is>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="14" t="n">
+    <row r="83" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="14" t="n">
         <v>1935</v>
       </c>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14" t="s">
+      <c r="B83" s="14"/>
+      <c r="C83" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="D81" s="15" t="s">
+      <c r="D83" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="E81" s="16" t="inlineStr">
+      <c r="E83" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9gritude"  title=" Wikipedia"&gt;La Négritude&lt;/a&gt; est un mouvement littéraire, culturel et politique né à Paris dans les années 1930 parmi les étudiants noirs venus d’Afrique et des Antilles. Le mot apparaît sous la plume du Martiniquais &lt;a href="https://fr.wikipedia.org/wiki/Aim%C3%A9_C%C3%A9saire" title=" Wikipedia"&gt;Aimé Césaire&lt;/a&gt; en 1935, dans la revue &lt;em&gt;L’Étudiant noir&lt;/em&gt;, puis dans son &lt;em&gt;Cahier d’un retour au pays natal&lt;/em&gt; (1939). Il retourne fièrement une insulte coloniale pour en faire l’affirmation d’une identité.&lt;/p&gt; &lt;p&gt;Avec le Sénégalais &lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9opold_S%C3%A9dar_Senghor" title=" Wikipedia"&gt;Léopold Sédar Senghor&lt;/a&gt; et le Guyanais &lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on-Gontran_Damas" title=" Wikipedia"&gt;Léon-Gontran Damas&lt;/a&gt;, Césaire refuse l’assimilation que propose la France coloniale, qui demande aux colonisés de renoncer à leur culture pour adopter celle de l’Europe. Ils revendiquent l’héritage des civilisations africaines, leurs arts, leurs langues et leurs valeurs. Pour Senghor, la négritude est « l’ensemble des valeurs culturelles du monde noir » ; il oppose parfois une raison africaine intuitive à la raison européenne analytique. Pour Césaire, elle est d’abord une révolte contre l’oppression : son &lt;em&gt;Discours sur le colonialisme&lt;/em&gt; (1950) dénonce la barbarie de l’Europe coloniale. En 1948, l’&lt;em&gt;Anthologie&lt;/em&gt; de Senghor, préfacée par Sartre sous le titre « Orphée noir », donne au mouvement un retentissement mondial.&lt;/p&gt; &lt;p&gt;Senghor devient en 1960 le premier président du Sénégal. La négritude a été critiquée pour son essentialisme, par Frantz Fanon, par Wole Soyinka (« le tigre ne proclame pas sa tigritude ») ou par les auteurs de la créolité, mais elle a ouvert la voie aux pensées postcoloniales.&lt;/p&gt;  &lt;audio controls title="Bonjour et adieu à la Négritude par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F81" s="14" t="s">
+      <c r="F83" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="G81" s="16" t="s">
+      <c r="G83" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="2" t="s">
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="K81" s="2" t="s">
+      <c r="K83" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M81" s="2" t="s">
+      <c r="M83" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t xml:space="preserve">Pan-africanisme</t>
         </is>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="n">
+    <row r="84" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="n">
         <v>1940</v>
       </c>
-      <c r="C82" s="1" t="n">
+      <c r="C84" s="1" t="n">
         <v>1940</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D84" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="E82" s="23" t="inlineStr">
+      <c r="E84" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Doctrine_Jdanov"  title=" Wikipedia"&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F84" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G84" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="J82" s="23" t="s">
+      <c r="J84" s="23" t="s">
         <v>432</v>
       </c>
-      <c r="K82" s="2" t="s">
+      <c r="K84" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M82" s="2" t="s">
+      <c r="M84" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
         <is>
           <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t xml:space="preserve">Marxisme</t>
         </is>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
+    <row r="85" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
         <v>1945</v>
       </c>
-      <c r="C83" s="1" t="n">
+      <c r="C85" s="1" t="n">
         <v>1945</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D85" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;La Philosophie africaine&lt;/a&gt; désigne la réflexion philosophique menée en Afrique ou par des penseurs africains, mais aussi le débat sur ce que peut être une telle philosophie. Les traditions de pensée du continent sont anciennes, des sagesses de l’Égypte pharaonique au &lt;em&gt;Hatata&lt;/em&gt; éthiopien du XVIIe siècle attribué à Zera Yacob ; mais la discipline moderne prend son essor en 1945, avec &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Tempels reconstruit, à partir de l’observation des Luba du Congo, une « vision du monde » cohérente centrée sur la force vitale : être, c’est être force, et le bien consiste à accroître la vie. Le prêtre rwandais Alexis Kagame prolonge cette démarche en étudiant les catégories de la langue kinyarwanda. Ce courant, appelé ethnophilosophie, est vivement critiqué par le Béninois &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976) : décrire une pensée collective et anonyme, que personne ne discute, ce n’est pas faire de la philosophie, qui suppose des auteurs, des textes et la critique.&lt;/p&gt; &lt;p&gt;Entre ces deux pôles, d’autres voies se sont ouvertes. Le Kényan Henry Odera Oruka recueille auprès des sages des villages une « philosophie de la sagesse » (&lt;em&gt;sage philosophy&lt;/em&gt;) personnelle et critique. Le Ghanéen &lt;a href="https://fr.wikipedia.org/wiki/Kwasi_Wiredu" title=" Wikipedia"&gt;Kwasi Wiredu&lt;/a&gt; appelle à une « décolonisation conceptuelle » qui examine les notions héritées de l’Occident à la lumière des langues africaines. Le Congolais Valentin-Yves Mudimbe étudie la manière dont l’Afrique a été « inventée » par le regard colonial. Le débat porte encore sur l’universalité de la raison.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="G83" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="J83" s="2" t="s">
+      <c r="J85" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées africaines</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1">
-        <v>1945</v>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1945</t>
-        </is>
-      </c>
-      <c r="D84" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ethnophilosophie</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ethnophilosophy" title=" Wikipedia (en)"&gt;L’ethnophilosophie&lt;/a&gt; désigne la démarche qui cherche la philosophie d’un peuple dans ses langues, ses proverbes, ses mythes et ses croyances, plutôt que dans les œuvres de penseurs individuels. Elle naît en 1945 avec &lt;a href="https://fr.wikipedia.org/wiki/La_Philosophie_bantoue" title=" Wikipedia"&gt;&lt;em&gt;La Philosophie bantoue&lt;/em&gt;&lt;/a&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;, qui veut montrer, contre le préjugé colonial, que les Africains ont une pensée cohérente, fondée sur l’idée de « force vitale » : pour les Bantous, l’être est force, et toute chose est une force qui peut croître ou décroître.&lt;/p&gt; &lt;p&gt;Des penseurs africains reprennent cette démarche en la retournant contre le regard colonial. Le prêtre rwandais Alexis Kagame, dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), dégage les catégories de la pensée à partir de la grammaire du kinyarwanda, comme Aristote l’avait fait, selon lui, à partir du grec. Le théologien kényan John Mbiti décrit dans &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969) une conception du temps tournée vers le passé plus que vers l’avenir. Dans l’esprit de la Négritude, il s’agit d’affirmer la dignité des cultures africaines.&lt;/p&gt; &lt;p&gt;À partir des années 1970, cette démarche est vivement critiquée par d’autres philosophes africains. Paulin Hountondji, dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976), dénonce le « mythe de l’unanimité » : une philosophie n’est pas une vision du monde collective et figée, mais un discours critique, signé, argumenté et ouvert à la discussion. Marcien Towa et Fabien Eboussi Boulaga vont dans le même sens. Le débat sur l’ethnophilosophie a structuré toute la philosophie africaine contemporaine.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WdgKfF8Ghn0</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Révision BAC: La Philosophie Africaine Existe -t - Elle?" par Ibrahima Ngom - Attitude</t>
-        </is>
-      </c>
-      <c r="J84" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">recherche d’une philosophie africaine dans les langues, les croyances et les traditions des peuples, et débat qu’elle a suscité.</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Métaphysique;Épistémologie</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Placide TEMPELS;Alexis KAGAME;John MBITI</t>
-        </is>
-      </c>
-      <c r="M84" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="N84"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées africaines</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Négritude</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
-        <v>1964</v>
-      </c>
-      <c r="C85" s="1" t="n">
-        <v>1964</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nkrumaism" title=" Wikipedia (en)"&gt;Le Consciencisme&lt;/a&gt; est la philosophie politique de &lt;a href="https://fr.wikipedia.org/wiki/Kwame_Nkrumah" title=" Wikipedia"&gt;Kwame Nkrumah&lt;/a&gt; (1909-1972), qui conduit la Gold Coast britannique à l’indépendance en 1957 sous le nom de Ghana, premier pays d’Afrique subsaharienne à se libérer de la colonisation. Il l’expose dans &lt;em&gt;Consciencism : Philosophy and Ideology for Decolonization&lt;/em&gt; (1964). Pour Nkrumah, la décolonisation ne sera achevée que si elle s’accompagne d’une libération des consciences : l’Afrique doit penser par elle-même la société qu’elle veut construire.&lt;/p&gt; &lt;p&gt;Il part d’un constat : la conscience africaine est désormais faite de trois héritages, la tradition africaine, l’islam et le christianisme européen, qui coexistent en conflit. Le consciencisme veut les réunir en une synthèse cohérente, guidée par les valeurs humanistes et égalitaires de l’Afrique traditionnelle. Selon Nkrumah, les sociétés africaines précoloniales étaient « communalistes » : la terre appartenait à tous et nul ne vivait du travail d’autrui. Le socialisme n’est donc pas, pour l’Afrique, une importation, mais la forme moderne de ses propres valeurs ; il peut s’y construire sans passer par la lutte des classes. Sur le plan philosophique, Nkrumah défend un matérialisme dans lequel l’esprit naît de la matière, tout en affirmant l’égale dignité de chaque être humain. Son projet politique est le &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; : une Afrique unie, seule capable de résister au néocolonialisme.&lt;/p&gt; &lt;p&gt;Renversé par un coup d’État en 1966, Nkrumah meurt en exil. Le consciencisme reste une référence des philosophies africaines de la décolonisation ; Kwame Gyekye en a critiqué l’idéalisation du passé.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">le consciencisme de Kwane Nkrumah par Renaissance Africaine</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>108</v>
@@ -6453,205 +6482,213 @@
           <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+    </row>
+    <row r="86" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1">
+        <v>1945</v>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1945</t>
+        </is>
+      </c>
+      <c r="D86" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ethnophilosophie</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ethnophilosophy" title=" Wikipedia (en)"&gt;L’ethnophilosophie&lt;/a&gt; désigne la démarche qui cherche la philosophie d’un peuple dans ses langues, ses proverbes, ses mythes et ses croyances, plutôt que dans les œuvres de penseurs individuels. Elle naît en 1945 avec &lt;a href="https://fr.wikipedia.org/wiki/La_Philosophie_bantoue" title=" Wikipedia"&gt;&lt;em&gt;La Philosophie bantoue&lt;/em&gt;&lt;/a&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;, qui veut montrer, contre le préjugé colonial, que les Africains ont une pensée cohérente, fondée sur l’idée de « force vitale » : pour les Bantous, l’être est force, et toute chose est une force qui peut croître ou décroître.&lt;/p&gt; &lt;p&gt;Des penseurs africains reprennent cette démarche en la retournant contre le regard colonial. Le prêtre rwandais Alexis Kagame, dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), dégage les catégories de la pensée à partir de la grammaire du kinyarwanda, comme Aristote l’avait fait, selon lui, à partir du grec. Le théologien kényan John Mbiti décrit dans &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969) une conception du temps tournée vers le passé plus que vers l’avenir. Dans l’esprit de la Négritude, il s’agit d’affirmer la dignité des cultures africaines.&lt;/p&gt; &lt;p&gt;À partir des années 1970, cette démarche est vivement critiquée par d’autres philosophes africains. Paulin Hountondji, dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976), dénonce le « mythe de l’unanimité » : une philosophie n’est pas une vision du monde collective et figée, mais un discours critique, signé, argumenté et ouvert à la discussion. Marcien Towa et Fabien Eboussi Boulaga vont dans le même sens. Le débat sur l’ethnophilosophie a structuré toute la philosophie africaine contemporaine.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WdgKfF8Ghn0</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Révision BAC: La Philosophie Africaine Existe -t - Elle?" par Ibrahima Ngom - Attitude</t>
+        </is>
+      </c>
+      <c r="J86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recherche d’une philosophie africaine dans les langues, les croyances et les traditions des peuples, et débat qu’elle a suscité.</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Métaphysique;Épistémologie</t>
+        </is>
+      </c>
+      <c r="L86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Placide TEMPELS;Alexis KAGAME;John MBITI</t>
+        </is>
+      </c>
+      <c r="M86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N86"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées africaines</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Négritude</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>1964</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nkrumaism" title=" Wikipedia (en)"&gt;Le Consciencisme&lt;/a&gt; est la philosophie politique de &lt;a href="https://fr.wikipedia.org/wiki/Kwame_Nkrumah" title=" Wikipedia"&gt;Kwame Nkrumah&lt;/a&gt; (1909-1972), qui conduit la Gold Coast britannique à l’indépendance en 1957 sous le nom de Ghana, premier pays d’Afrique subsaharienne à se libérer de la colonisation. Il l’expose dans &lt;em&gt;Consciencism : Philosophy and Ideology for Decolonization&lt;/em&gt; (1964). Pour Nkrumah, la décolonisation ne sera achevée que si elle s’accompagne d’une libération des consciences : l’Afrique doit penser par elle-même la société qu’elle veut construire.&lt;/p&gt; &lt;p&gt;Il part d’un constat : la conscience africaine est désormais faite de trois héritages, la tradition africaine, l’islam et le christianisme européen, qui coexistent en conflit. Le consciencisme veut les réunir en une synthèse cohérente, guidée par les valeurs humanistes et égalitaires de l’Afrique traditionnelle. Selon Nkrumah, les sociétés africaines précoloniales étaient « communalistes » : la terre appartenait à tous et nul ne vivait du travail d’autrui. Le socialisme n’est donc pas, pour l’Afrique, une importation, mais la forme moderne de ses propres valeurs ; il peut s’y construire sans passer par la lutte des classes. Sur le plan philosophique, Nkrumah défend un matérialisme dans lequel l’esprit naît de la matière, tout en affirmant l’égale dignité de chaque être humain. Son projet politique est le &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; : une Afrique unie, seule capable de résister au néocolonialisme.&lt;/p&gt; &lt;p&gt;Renversé par un coup d’État en 1966, Nkrumah meurt en exil. Le consciencisme reste une référence des philosophies africaines de la décolonisation ; Kwame Gyekye en a critiqué l’idéalisation du passé.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">le consciencisme de Kwane Nkrumah par Renaissance Africaine</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées africaines</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
         <is>
           <t xml:space="preserve">Socialisme africain</t>
         </is>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
+    <row r="88" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
         <v>1970</v>
       </c>
-      <c r="C86" s="1" t="n">
+      <c r="C88" s="1" t="n">
         <v>1970</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D88" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Minjung" title=" Wikipedia"&gt;La pensée Minjung&lt;/a&gt;, du coréen &lt;em&gt;minjung&lt;/em&gt;, « le peuple » au sens des masses opprimées, est un courant théologique et philosophique né en Corée du Sud dans les années 1970, sous la dictature de Park Chung-hee. Elle naît parmi les chrétiens engagés aux côtés des ouvriers et des étudiants en lutte pour la démocratie, après l’immolation en 1970 de l’ouvrier du textile Jeon Tae-il, qui réclamait l’application du droit du travail.&lt;/p&gt; &lt;p&gt;Le &lt;em&gt;minjung&lt;/em&gt;, ce sont ceux qui sont opprimés politiquement, exploités économiquement et tenus à l’écart de la culture. Pour le bibliste Ahn Byung-mu, qui relit l’Évangile de Marc à partir de la foule qui suit Jésus, et pour le théologien Suh Nam-dong, ce peuple souffrant n’est pas seulement l’objet de la compassion : il est le véritable sujet de l’histoire, et c’est dans ses luttes que se révèle le sens des Écritures. La pensée Minjung s’appuie sur une notion coréenne, le &lt;em&gt;han&lt;/em&gt;, ce sentiment de souffrance et de ressentiment accumulés au fil des générations ; le poète Kim Chi-ha cherche comment en briser le cercle sans tomber dans la vengeance. Elle valorise aussi les formes de la culture populaire, comme la danse masquée ou le chant épique du &lt;em&gt;pansori&lt;/em&gt;. Elle a pour précurseur la philosophie de la « graine » (&lt;em&gt;ssial&lt;/em&gt;) de Ham Seok-heon, qui voyait dans le peuple le germe vivant de l’histoire.&lt;/p&gt; &lt;p&gt;Proche des théologies de la libération d’Amérique latine, la pensée Minjung a nourri la résistance au régime militaire, du &lt;a href="https://fr.wikipedia.org/wiki/Soul%C3%A8vement_de_Gwangju" title=" Wikipedia"&gt;soulèvement de Gwangju&lt;/a&gt; en 1980 à la démocratisation de 1987.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="G86" s="2" t="s">
+      <c r="G88" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J86" s="2" t="s">
+      <c r="J88" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="K86" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="L86" s="1"/>
-      <c r="M86" s="2" t="s">
+      <c r="L88" s="1"/>
+      <c r="M88" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t xml:space="preserve">Théologies et philosophies de la libération</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1">
-        <v>1981</v>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1981</t>
-        </is>
-      </c>
-      <c r="D87" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Créolisation</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;La &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olisation_%28concept%29" title=" Wikipedia"&gt;créolisation&lt;/a&gt; est un courant de pensée né aux Antilles autour de l’œuvre d’Édouard Glissant. Le mot désigne d’abord la naissance des langues et des cultures créoles dans les sociétés de plantation des Caraïbes, où des peuples arrachés à l’Afrique, des colons européens, des Amérindiens et plus tard des travailleurs venus d’Inde ont dû inventer ensemble un monde nouveau. Glissant en fait un concept philosophique pour penser le monde entier.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Discours_antillais" title=" Wikipedia"&gt;&lt;em&gt;Le Discours antillais&lt;/em&gt;&lt;/a&gt; (1981), il développe d’abord l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : l’identité des Antilles ne se trouve ni dans un retour à l’Afrique, comme le voulait la Négritude, ni dans l’imitation de la France, mais dans l’archipel caribéen lui-même. Avec la créolisation, il montre que la rencontre des cultures ne produit pas un simple mélange prévisible, mais de l’inédit. Reprenant une image de Deleuze et Guattari, il oppose l’« identité-racine », unique, qui exclut l’autre, à l’« identité-rhizome », qui se construit dans la relation. Dans &lt;em&gt;Poétique de la Relation&lt;/em&gt; (1990), il défend le « droit à l’opacité » : comprendre l’autre ne signifie pas le réduire à soi. Il appelle &lt;a href="https://fr.wikipedia.org/wiki/Tout-monde" title=" Wikipedia"&gt;« Tout-Monde »&lt;/a&gt; ce monde où toutes les cultures sont désormais en contact, pour le meilleur et pour le pire, et où nul ne peut plus vivre à l’écart des autres.&lt;/p&gt; &lt;p&gt;En 1989, les écrivains martiniquais Jean Bernabé, &lt;a href="https://fr.wikipedia.org/wiki/Patrick_Chamoiseau" title=" Wikipedia"&gt;Patrick Chamoiseau&lt;/a&gt; et Raphaël Confiant prolongent ce mouvement dans leur &lt;em&gt;Éloge de la &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olit%C3%A9" title=" Wikipedia"&gt;créolité&lt;/a&gt;&lt;/em&gt;. La pensée de Glissant est aujourd’hui l’une des grandes références de la réflexion sur la mondialisation et les identités.&lt;/p&gt;  &lt;audio controls title="La Créolisation : un concept passé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/20904-30.04.2026-ITEMA_24494160-2026F49089S0120-NET_MFI_5FD251D7-5286-4ED2-85CC-C785E6DDF90E-27-205638c71d84a7236a4f197db5a2f1f9.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mLZ9uprUARg</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Edouard Glissant : penser la créolisation" par France Culture</t>
-        </is>
-      </c>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pensée antillaise de Glissant : les cultures en contact créent de l’imprévisible ; à l’identité-racine s’oppose l’identité-relation.</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Métaphysique;Philosophie politique</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Édouard GLISSANT</t>
-        </is>
-      </c>
-      <c r="M87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sud</t>
-        </is>
-      </c>
-      <c r="N87"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Négritude</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="C88" s="1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="D88" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buen_vivir" title=" Wikipedia"&gt;Le Buen Vivir&lt;/a&gt;, « bien vivre » en espagnol, traduit le &lt;em&gt;sumak kawsay&lt;/em&gt; des Quechuas et le &lt;em&gt;suma qamaña&lt;/em&gt; des Aymaras. C’est une philosophie issue des cosmovisions autochtones des Andes, formulée en termes contemporains à partir des années 1990 par des intellectuels et des mouvements indigènes d’Équateur et de Bolivie, rejoints par des penseurs critiques du développement.&lt;/p&gt; &lt;p&gt;Il s’oppose à l’idée occidentale du développement, mesuré par la croissance économique et l’accumulation de biens. Bien vivre, ce n’est pas vivre mieux, c’est-à-dire toujours plus, aux dépens des autres et de la nature : c’est vivre en harmonie au sein de la communauté et avec la &lt;a href="https://fr.wikipedia.org/wiki/Pachamama" title=" Wikipedia"&gt;Pachamama&lt;/a&gt;, la Terre-Mère. L’être humain n’y est ni séparé de la nature ni placé au-dessus d’elle : il fait partie d’un tout vivant tissé de relations, de réciprocité et de complémentarité, où les montagnes, les eaux et les êtres vivants ont leur place. La richesse tient à la qualité des liens plutôt qu’à l’abondance des choses. Ses défenseurs, comme l’économiste équatorien Alberto Acosta ou l’Uruguayen Eduardo Gudynas, y voient une alternative au modèle extractiviste.&lt;/p&gt; &lt;p&gt;La Constitution de l’Équateur de 2008 inscrit le &lt;em&gt;sumak kawsay&lt;/em&gt; parmi ses principes et reconnaît des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_la_nature" title=" Wikipedia"&gt;droits à la nature&lt;/a&gt; elle-même, une première mondiale. La Constitution bolivienne de 2009 en fait un principe éthique de l’État, et des lois de 2010 et 2012 y consacrent les droits de la Terre-Mère. Mais ces deux pays ont continué d’exploiter pétrole et minerais, ce qui nourrit le débat entre l’idéal et son usage politique.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="J88" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées autochtones</t>
         </is>
       </c>
     </row>
     <row r="89" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1">
-        <v>350</v>
+        <v>1981</v>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">350</t>
+          <t xml:space="preserve">1981</t>
         </is>
       </c>
       <c r="D89" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yogācāra</t>
+          <t xml:space="preserve">Créolisation</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Chittamatra" title=" Wikipedia"&gt;Le Yogācāra&lt;/a&gt;, « pratique du yoga », appelé aussi Cittamātra, « esprit seul », est avec le Madhyamaka l’une des deux grandes écoles philosophiques du bouddhisme mahāyāna. Il se forme en Inde au IVe siècle autour de deux frères, Asaṅga et Vasubandhu, à partir de l’expérience des méditants : ce que l’on observe en méditation montre combien le monde vécu est façonné par l’esprit. On doit à Vasubandhu deux courts traités, les &lt;em&gt;Vingt stances&lt;/em&gt; et les &lt;em&gt;Trente stances&lt;/em&gt;, qui résument la doctrine.&lt;/p&gt; &lt;p&gt;Sa thèse est que nous ne connaissons jamais que des représentations : les objets que nous croyons extérieurs sont des apparitions de la conscience, comme dans un rêve. Pour l’expliquer, il ajoute aux six consciences reconnues par le bouddhisme une conscience souillée, qui produit l’illusion d’un moi, et surtout une &lt;a href="https://fr.wikipedia.org/wiki/%C4%80layavij%C3%B1%C4%81na" title=" Wikipedia"&gt;conscience-réceptacle&lt;/a&gt; (&lt;em&gt;ālayavijñāna&lt;/em&gt;), sorte d’inconscient où les actes passés déposent des traces, comme des graines qui germeront plus tard. Il décrit aussi « trois natures » des choses : imaginaire, dépendante et parfaitement accomplie. L’éveil consiste à transformer ce fond de la conscience, jusqu’à ce que cesse le partage entre un sujet qui saisit et un objet saisi.&lt;/p&gt; &lt;p&gt;Ses logiciens, Dignāga puis Dharmakīrti, fondent la grande épistémologie bouddhique. Le pèlerin chinois &lt;a href="https://fr.wikipedia.org/wiki/Xuanzang" title=" Wikipedia"&gt;Xuanzang&lt;/a&gt; rapporte ses textes d’Inde au VIIe siècle et fonde en Chine l’école de la « conscience seule ». Le Yogācāra a nourri le zen, le bouddhisme tibétain et, aujourd’hui, le dialogue avec la phénoménologie et les sciences cognitives.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;La &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olisation_%28concept%29" title=" Wikipedia"&gt;créolisation&lt;/a&gt; est un courant de pensée né aux Antilles autour de l’œuvre d’Édouard Glissant. Le mot désigne d’abord la naissance des langues et des cultures créoles dans les sociétés de plantation des Caraïbes, où des peuples arrachés à l’Afrique, des colons européens, des Amérindiens et plus tard des travailleurs venus d’Inde ont dû inventer ensemble un monde nouveau. Glissant en fait un concept philosophique pour penser le monde entier.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Discours_antillais" title=" Wikipedia"&gt;&lt;em&gt;Le Discours antillais&lt;/em&gt;&lt;/a&gt; (1981), il développe d’abord l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : l’identité des Antilles ne se trouve ni dans un retour à l’Afrique, comme le voulait la Négritude, ni dans l’imitation de la France, mais dans l’archipel caribéen lui-même. Avec la créolisation, il montre que la rencontre des cultures ne produit pas un simple mélange prévisible, mais de l’inédit. Reprenant une image de Deleuze et Guattari, il oppose l’« identité-racine », unique, qui exclut l’autre, à l’« identité-rhizome », qui se construit dans la relation. Dans &lt;em&gt;Poétique de la Relation&lt;/em&gt; (1990), il défend le « droit à l’opacité » : comprendre l’autre ne signifie pas le réduire à soi. Il appelle &lt;a href="https://fr.wikipedia.org/wiki/Tout-Monde" title=" Wikipedia"&gt;« Tout-Monde »&lt;/a&gt; ce monde où toutes les cultures sont désormais en contact, pour le meilleur et pour le pire, et où nul ne peut plus vivre à l’écart des autres.&lt;/p&gt; &lt;p&gt;En 1989, les écrivains martiniquais Jean Bernabé, &lt;a href="https://fr.wikipedia.org/wiki/Patrick_Chamoiseau" title=" Wikipedia"&gt;Patrick Chamoiseau&lt;/a&gt; et Raphaël Confiant prolongent ce mouvement dans leur &lt;em&gt;Éloge de la &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olit%C3%A9" title=" Wikipedia"&gt;créolité&lt;/a&gt;&lt;/em&gt;. La pensée de Glissant est aujourd’hui l’une des grandes références de la réflexion sur la mondialisation et les identités.&lt;/p&gt;  &lt;audio controls title="La Créolisation : un concept passé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/20904-30.04.2026-ITEMA_24494160-2026F49089S0120-NET_MFI_5FD251D7-5286-4ED2-85CC-C785E6DDF90E-27-205638c71d84a7236a4f197db5a2f1f9.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mLZ9uprUARg</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Edouard Glissant : penser la créolisation" par France Culture</t>
         </is>
       </c>
       <c r="J89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">école bouddhiste de « l’esprit seul » : le monde que nous percevons est une construction de la conscience.</t>
+          <t xml:space="preserve">pensée antillaise de Glissant : les cultures en contact créent de l’imprévisible ; à l’identité-racine s’oppose l’identité-relation.</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosophie de l'esprit;Métaphysique;Épistémologie</t>
+          <t xml:space="preserve">Métaphysique;Philosophie politique</t>
         </is>
       </c>
       <c r="L89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASANGA;VASUBANDHU;XUANZANG</t>
+          <t xml:space="preserve">Édouard GLISSANT</t>
         </is>
       </c>
       <c r="M89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inde</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N89"/>
       <c r="O89" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6659,55 +6696,45 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1">
-        <v>402</v>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">402</t>
-        </is>
-      </c>
-      <c r="D90" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme de la Terre pure</t>
-        </is>
+          <t xml:space="preserve">Négritude</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>449</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;Le bouddhisme de la &lt;a href="https://fr.wikipedia.org/wiki/Terre_pure" title=" Wikipedia"&gt;Terre pure&lt;/a&gt; est le courant du bouddhisme mahāyāna centré sur la dévotion au bouddha Amitābha (Amida en japonais) qui, selon les sūtras, a fait le vœu d’accueillir dans sa « Terre pure », un paradis situé à l’Occident, tous ceux qui l’invoquent avec foi. Né en Chine, il remonte à Huiyuan, qui réunit en 402 au mont Lu une communauté vouée à Amitābha, puis à &lt;a href="https://fr.wikipedia.org/wiki/Tanluan" title=" Wikipedia"&gt;Tanluan&lt;/a&gt; et à Shandao, qui en font une école.&lt;/p&gt; &lt;p&gt;Sa philosophie part d’un constat : en cette époque de « déclin de la Loi », les êtres humains ne peuvent plus atteindre l’éveil par leurs propres forces, par la méditation ou l’ascèse. Il faut s’en remettre à la « force de l’autre », la compassion d’Amitābha. La pratique principale devient la récitation de son nom, le &lt;em&gt;nembutsu&lt;/em&gt; : « Namu Amida Butsu ». Au Japon, Hōnen fonde en 1175 l’école &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_sh%C5%AB" title=" Wikipedia"&gt;Jōdo shū&lt;/a&gt; et affirme que cette seule récitation suffit au salut, ce qui ouvre le bouddhisme aux gens simples, aux paysans et aux femmes. Son disciple Shinran va plus loin avec le &lt;a href="https://fr.wikipedia.org/wiki/J%C5%8Ddo_shinsh%C5%AB" title=" Wikipedia"&gt;Jōdo shinshū&lt;/a&gt; : le salut est entièrement un don reçu dans la foi, et c’est le « méchant » conscient de ses fautes, plus encore que le juste, que le Bouddha veut sauver. Shinran se marie, quitte la vie monastique et vit parmi le peuple.&lt;/p&gt; &lt;p&gt;Devenue l’une des formes du bouddhisme les plus pratiquées d’Asie de l’Est, la Terre pure évoque la doctrine chrétienne de la grâce, rapprochement qui a fasciné bien des théologiens occidentaux. Elle compte aujourd’hui des dizaines de millions de fidèles au Japon, en Chine, en Corée et au Viêt Nam.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J90" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bouddhisme de la foi en Amitābha : le salut par la récitation de son nom et la « force de l’autre ».</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie et spiritualité</t>
-        </is>
-      </c>
-      <c r="L90" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HŌNEN;SHINRAN</t>
-        </is>
-      </c>
-      <c r="M90" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="N90"/>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buen_vivir" title=" Wikipedia"&gt;Le Buen Vivir&lt;/a&gt;, « bien vivre » en espagnol, traduit le &lt;em&gt;sumak kawsay&lt;/em&gt; des Quechuas et le &lt;em&gt;suma qamaña&lt;/em&gt; des Aymaras. C’est une philosophie issue des cosmovisions autochtones des Andes, formulée en termes contemporains à partir des années 1990 par des intellectuels et des mouvements indigènes d’Équateur et de Bolivie, rejoints par des penseurs critiques du développement.&lt;/p&gt; &lt;p&gt;Il s’oppose à l’idée occidentale du développement, mesuré par la croissance économique et l’accumulation de biens. Bien vivre, ce n’est pas vivre mieux, c’est-à-dire toujours plus, aux dépens des autres et de la nature : c’est vivre en harmonie au sein de la communauté et avec la &lt;a href="https://fr.wikipedia.org/wiki/Pachamama" title=" Wikipedia"&gt;Pachamama&lt;/a&gt;, la Terre-Mère. L’être humain n’y est ni séparé de la nature ni placé au-dessus d’elle : il fait partie d’un tout vivant tissé de relations, de réciprocité et de complémentarité, où les montagnes, les eaux et les êtres vivants ont leur place. La richesse tient à la qualité des liens plutôt qu’à l’abondance des choses. Ses défenseurs, comme l’économiste équatorien Alberto Acosta ou l’Uruguayen Eduardo Gudynas, y voient une alternative au modèle extractiviste.&lt;/p&gt; &lt;p&gt;La Constitution de l’Équateur de 2008 inscrit le &lt;em&gt;sumak kawsay&lt;/em&gt; parmi ses principes et reconnaît des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_la_nature" title=" Wikipedia"&gt;droits à la nature&lt;/a&gt; elle-même, une première mondiale. La Constitution bolivienne de 2009 en fait un principe éthique de l’État, et des lois de 2010 et 2012 y consacrent les droits de la Terre-Mère. Mais ces deux pays ont continué d’exploiter pétrole et minerais, ce qui nourrit le débat entre l’idéal et son usage politique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement</t>
@@ -6715,12 +6742,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme Mahayana</t>
+          <t xml:space="preserve">Pensées autochtones</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7433,17 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;La pensée décoloniale, ou &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;études décoloniales&lt;/a&gt;, est un courant né en Amérique latine dans les années 1990. Son point de départ est un article de 1992 du sociologue péruvien &lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal Quijano&lt;/a&gt;, qui forge la notion de « colonialité du pouvoir » : le colonialisme, comme domination politique directe, a pris fin, mais la colonialité, elle, a survécu.&lt;/p&gt; &lt;p&gt;Pour ces penseurs, la modernité européenne et la colonisation des Amériques, à partir de 1492, sont les deux faces d’un même processus. La colonisation a installé une hiérarchie des êtres humains fondée sur la race, une division du travail mondiale et une hiérarchie des savoirs, qui présente la science et la philosophie européennes comme universelles et relègue les autres savoirs au rang de croyances ou de folklore. Cette colonialité continue d’organiser le monde après les indépendances. Le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt;, qui réunit autour de Quijano l’Argentin &lt;a href="https://fr.wikipedia.org/wiki/Walter_Mignolo" title=" Wikipedia"&gt;Walter Mignolo&lt;/a&gt;, Enrique Dussel et d’autres, appelle à une « désobéissance épistémique » : penser à partir des expériences et des savoirs des peuples colonisés, pour un monde où plusieurs mondes seraient possibles. Sylvia Wynter et Lewis Gordon prolongent cette réflexion dans la Caraïbe et chez les Afro-Américains.&lt;/p&gt; &lt;p&gt;Le courant se distingue des études postcoloniales anglophones d’Edward Saïd ou de &lt;a href="https://fr.wikipedia.org/wiki/Gayatri_Chakravorty_Spivak" title=" Wikipedia"&gt;Gayatri Spivak&lt;/a&gt;, nées de la critique littéraire et centrées sur l’Asie et le Moyen-Orient. Il suscite aussi des critiques, y compris en Amérique latine, où Silvia Rivera Cusicanqui lui reproche d’être devenu une mode universitaire du Nord.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;La pensée décoloniale, ou &lt;a href="https://fr.wikipedia.org/wiki/%C3%89tudes_d%C3%A9coloniales" title=" Wikipedia"&gt;études décoloniales&lt;/a&gt;, est un courant né en Amérique latine dans les années 1990. Son point de départ est un article de 1992 du sociologue péruvien &lt;a href="https://fr.wikipedia.org/wiki/An%C3%ADbal_Quijano" title=" Wikipedia"&gt;Aníbal Quijano&lt;/a&gt;, qui forge la notion de « colonialité du pouvoir » : le colonialisme, comme domination politique directe, a pris fin, mais la colonialité, elle, a survécu.&lt;/p&gt; &lt;p&gt;Pour ces penseurs, la modernité européenne et la colonisation des Amériques, à partir de 1492, sont les deux faces d’un même processus. La colonisation a installé une hiérarchie des êtres humains fondée sur la race, une division du travail mondiale et une hiérarchie des savoirs, qui présente la science et la philosophie européennes comme universelles et relègue les autres savoirs au rang de croyances ou de folklore. Cette colonialité continue d’organiser le monde après les indépendances. Le &lt;a href="https://fr.wikipedia.org/wiki/Groupe_modernit%C3%A9/colonialit%C3%A9" title=" Wikipedia"&gt;groupe « modernité/colonialité »&lt;/a&gt;, qui réunit autour de Quijano l’Argentin &lt;a href="https://fr.wikipedia.org/wiki/Walter_Mignolo" title=" Wikipedia"&gt;Walter Mignolo&lt;/a&gt;, Enrique Dussel et d’autres, appelle à une « désobéissance épistémique » : penser à partir des expériences et des savoirs des peuples colonisés, pour un monde où plusieurs mondes seraient possibles. Sylvia Wynter et Lewis Gordon prolongent cette réflexion dans la Caraïbe et chez les Afro-Américains.&lt;/p&gt; &lt;p&gt;Le courant se distingue des études postcoloniales anglophones d’Edward Saïd ou de &lt;a href="https://fr.wikipedia.org/wiki/Gayatri_Chakravorty_Spivak" title=" Wikipedia"&gt;Gayatri Spivak&lt;/a&gt;, nées de la critique littéraire et centrées sur l’Asie et le Moyen-Orient. Il suscite aussi des critiques, y compris en Amérique latine, où Silvia Rivera Cusicanqui lui reproche d’être devenu une mode universitaire du Nord.&lt;/p&gt;  &lt;audio controls title="Qu'est ce que c'est la pensée décoloniale ? par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-08.05.2023-ITEMA_23371665-2023C48904S0128-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bYWmAMTbnyQ</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Qu'est-ce que le décolonial ? | INTERSTICE" par Contreuphorie</t>
         </is>
       </c>
       <c r="J103" s="1" t="inlineStr">
@@ -7457,29 +7489,29 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E14" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines&quot;  title=&quot; Wikipedia&quot;&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les traditions philosophiques et spirituelles des civilisations précolombiennes d'Amérique centrale, en particulier les Aztèques, les Mayas et les Toltèques. Ces pensées forment un univers conceptuel original, structuré autour de la relation entre l'homme, le cosmos et les forces divines.&lt;/p&gt;&lt;p&gt;Au cœur de ces traditions se trouve la notion de &lt;em&gt;teotl&lt;/em&gt; (divinité, énergie sacrée) chez les Aztèques, ou de &lt;em&gt;k'ul&lt;/em&gt; (force vitale sacrée) chez les Mayas. La cosmologie mésoaméricaine conçoit l'univers comme un système de cycles temporels, où les dieux et les hommes sont liés par des obligations réciproques. Le sacrifice rituel, loin d'être une simple pratique violente, est pensé comme une nécessité cosmique pour maintenir l'équilibre du monde.&lt;/p&gt;&lt;p&gt;Des figures comme Quetzalcóatl (le Serpent à plumes) incarnent une sagesse éthique et philosophique : tempérance, connaissance, opposition au sacrifice humain selon certaines traditions. Les philosophes aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s'interrogeaient sur la nature du vrai, du beau, du bien, et sur la condition humaine — une tradition philosophique autonome redécouverte par des chercheurs comme Miguel León-Portilla.&lt;/p&gt;"/>
-    <hyperlink ref="E17" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9sychasme&quot; title=&quot; Wikipedia&quot;&gt;L'Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme oriental, dont le nom vient du grec &lt;em&gt;hésychia&lt;/em&gt; (silence, tranquillité). Il désigne une pratique spirituelle visant à atteindre l'union avec Dieu par la prière continue, le silence intérieur et la maîtrise du souffle.&lt;/p&gt;&lt;p&gt;Ses origines remontent aux Pères du désert des IVe-Ve siècles, mais c'est au XIVe siècle que l'hésychasme devient un courant théologique et philosophique structuré, notamment grâce à Grégoire Palamas, archevêque de Thessalonique, qui en formule la doctrine dans ses &lt;em&gt;Triades&lt;/em&gt;. Palamas distingue l'essence divine (inaccessible) des énergies divines (accessibles à l'expérience mystique), permettant de fonder théologiquement la possibilité d'une véritable union de l'homme avec Dieu.&lt;/p&gt;&lt;p&gt;Cette distinction essence-énergies est l'une des contributions philosophiques les plus originales de la pensée byzantine. L'hésychasme a profondément marqué la spiritualité orthodoxe russe, grecque et serbe, et continue d'irriguer la théologie et la philosophie orthodoxes contemporaines.&lt;/p&gt;"/>
-    <hyperlink ref="E19" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka&quot;  title=&quot;Wikipedia&quot;&gt;Le Lokayata&lt;/a&gt;, également connu sous le nom de Carvaka, est la seule école philosophique de l'Inde ancienne à avoir défendu un matérialisme radical et un athéisme déclaré. Fondée vers le VIe siècle avant notre ère, elle rejette tout ce qui ne peut être appréhendé par les sens : pas d'âme immortelle, pas d'au-delà, pas de loi karmique.&lt;/p&gt;&lt;p&gt;Sa devise pourrait se résumer ainsi : ce que l'on voit existe ; ce que l'on ne peut percevoir n'est qu'invention. Les Carvakas refusent les Védas et leur autorité, les rituels brahmaniques, et toute forme de spéculation métaphysique. L'univers est composé des quatre éléments — terre, eau, feu et air — sans qu'intervienne aucune divinité créatrice.&lt;/p&gt;&lt;p&gt;En matière d'éthique, la philosophie Carvaka est franchement hédoniste : le plaisir est le seul bien réel, la souffrance le seul mal. Mieux vaut jouir de la vie maintenant plutôt qu'espérer une récompense illusoire après la mort. Ce réalisme sans concession en fait une voix singulière, souvent persécutée, de la pensée indienne classique.&lt;/p&gt;&lt;p&gt;Bien que ses textes originaux aient presque tous disparu — connus surtout par les réfutations de ses adversaires — son influence demeure dans les courants matérialistes et rationalistes qui traversent la philosophie indienne jusqu'à aujourd'hui.&lt;/p&gt;"/>
-    <hyperlink ref="E24" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra&quot; title=&quot; Wikipedia&quot;&gt; Le Yoga&lt;/a&gt; en tant qu’école philosophique (darshana) est distinct de la pratique physique popularisée en Occident. Systématisé par Patanjali dans les Yoga Sutra (entre 200 av. J.-C. et 500 apr. J.-C.), il partage la métaphysique dualiste du Samkhya — Purusha (conscience) et Prakriti (matière) — mais y ajoute une méthode pratique précise pour la libération.&lt;/p&gt;&lt;p&gt;Les huit membres (ashtanga) du Yoga structurent ce chemin : discipline éthique (yama, niyama), posture (asana), maîtrise du souffle (pranayama), retrait des sens (pratyahara), concentration (dharana), méditation (dhyana) et absorption (samadhi). Chaque étape prépare la suivante dans une progression méthodique vers l’arrêt des fluctuations du mental (chitta vritti nirodha).&lt;/p&gt;&lt;p&gt;Contrairement au Samkhya, purement théorique, le Yoga de Patanjali introduit îshvara (un principe divin, seigneur particulier parmi les âmes) comme objet de concentration facultatif — une nuance théiste absente du Samkhya classique. Cette différence a nourri des siècles de commentaires et de débats entre les deux écoles sœurs.&lt;/p&gt;&lt;p&gt;Aujourd’hui mondialement diffusée, la dimension physique du yoga occulte souvent sa profondeur philosophique originelle : une discipline rigoureuse de la conscience, visant non le bien-être mais la discrimination (viveka) entre le Soi éternel et les fluctuations passagères du mental.&lt;/p&gt;"/>
-    <hyperlink ref="E26" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme&quot;  title=&quot; Wikipedia&quot;&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt;    &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title=&quot;Le Taoïsme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E30" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/École_des_Noms&quot;  title=&quot;Wikipedia&quot;&gt;L'École des Noms&lt;/a&gt; (ming jia, 名家) est une école de philosophie chinoise qui s'est développée pendant la période des Royaumes combattants. Sa préoccupation centrale : la relation entre les mots et les choses, entre les noms et la réalité qu'ils désignent.&lt;/p&gt;&lt;p&gt;Ses représentants les plus célèbres, Gongsun Long et Hui Shi, sont connus pour leurs paradoxes vertigineux. Gongsun Long affirmait que &quot;le cheval blanc n'est pas un cheval&quot; — non par provocation, mais pour distinguer le concept général (cheval) du particulier concret (ce cheval blanc). Hui Shi proclamait que &quot;le ciel et la terre sont d'une même hauteur&quot;, explorant les limites relatives de toute catégorisation.&lt;/p&gt;&lt;p&gt;Ces réflexions sur le langage anticipent certaines problématiques de la logique et de la philosophie analytique moderne. Comment les mots nous permettent-ils — ou nous empêchent-ils — de saisir la réalité ? Toute classification n'implique-t-elle pas une distorsion du monde ?&lt;/p&gt;&lt;p&gt;Peu influente politiquement, l'École des Noms fut souvent moquée par ses contemporains confu céens et taoïstes. Mais elle constitue une contribution unique à la logique asiatique et à la philosophie du langage dans la pensée mondiale.&lt;/p&gt;"/>
-    <hyperlink ref="E31" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A2mkhya&quot;  title=&quot; Wikipedia&quot;&gt;Le Sâmkhya&lt;/a&gt; est l'une des plus anciennes écoles philosophiques de l'Inde, considérée comme un darshana orthodoxe de l'hindouisme. Il propose une analyse rationnelle de la réalité pour libérer l'individu du cycle des renaissances et de la souffrance. Ce système dualiste distingue deux réalités ultimes : Purusha, la conscience pure et passive (esprit, principe masculin), et Prakriti, la matière primordiale active (énergie universelle, principe féminin). Prakriti évolue sous l'influence des trois guṇas (sattva : harmonie ; rajas : activité ; tamas : inertie), générant le monde manifesté à travers 23 tattvas (principes), comme buddhi (intelligence), ahaṃkāra (ego) et les sens. &lt;/p&gt; &lt;p&gt; Il explique la création comme une transformation de Prakriti, sans recours à un dieu créateur : de l'état non manifesté (avyakta) naît le manifesté (vyakta), incluant le corps subtil qui transmigre. L'ignorance (avidyā) cause l'identification erronée du Purusha à la matière, source de souffrance (duḥkha). &lt;/p&gt; &lt;p&gt; Fondement théorique du Yoga de Patañjali, le Sâmkhya met l'accent sur la discrimination (viveka) entre Purusha et Prakriti pour atteindre la libération (kaivalya). Il influence largement la philosophie indienne, des Puranas au Vedānta. &lt;/p&gt;"/>
-    <hyperlink ref="E33" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Therav%C4%81da&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Theravada&lt;/a&gt; (« École des Anciens ») est la plus ancienne forme du bouddhisme conservée jusqu'à nos jours. Héritière directe des enseignements du Bouddha historique, elle s'enracina progressivement en Asie du Sud-Est : Sri Lanka, Thaïlande, Myanmar, Cambodge, Laos.&lt;/p&gt;&lt;p&gt;Au cœur du Theravada se trouve le Pali Canon (Tipitaka), le corpus scripturaire le plus ancien du bouddhisme. Sa philosophie insiste sur la voie individuelle vers l'éveil : chaque être doit parcourir lui-même le Noble Sentier Octuple — juste compréhension, juste intention, juste parole, juste action, juste mode de vie, juste effort, juste attention, juste concentration.&lt;/p&gt;&lt;p&gt;L'idéal du Theravada est l'Arhat : le sage qui, par sa propre pratique, a éteint les &quot;feux&quot; de l'attachement, de la haine et de l'illusion, et atteint le Nirvana. Cette voie solitaire et rigoureuse contraste avec l'idéal du bodhisattva du Mahayana, qui renonce à son propre éveil pour sauver tous les êtres.&lt;/p&gt;&lt;p&gt;La méditation de pleine conscience (sati), aujourd'hui mondialement répandue, trouve ses racines dans les pratiques contemplatives du Theravada, notamment la méditation vipassana qui vise à observer directement l'impermanence, la souffrance et l'absence de soi.&lt;/p&gt;"/>
-    <hyperlink ref="E35" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vaisheshika&quot;  title=&quot; Wikipedia&quot;&gt;Le Vaisheshika&lt;/a&gt;  est une école philosophique orthodoxe hindoue, fondée par le sage Kaṇāda, qui se distingue par son atomisme et son réalisme ontologique. Exposée dans les Vaiśeṣika Sūtra (non antérieurs à l'ère chrétienne), elle vise la libération (mokṣa) par la connaissance des catégories fondamentales de la réalité. Le système repose sur six ou sept padārthas (catégories) : dravya (substance), guṇa (qualité), karma (action/mouvement), sāmānya (universalité), viśeṣa (particularité) et samavāya (inhérence). Parmi les neuf substances, quatre sont atomiques (terre, eau, feu, air) : les paramāṇu (atomes éternels, indivisibles) s'assemblent en dyades puis en objets composites non éternels. &lt;/p&gt; &lt;p&gt; Sans dieu créateur direct, l'univers émerge de combinaisons atomiques influencées par une cause efficiente (adrisṭa, karma résiduel). Ākāśa (espace), kāla (temps), dik (direction) et cit (âme) complètent les substances ; les atomes sphériques se lient par forces intrinsèques, formant un monde discontinu mais perceptible. &lt;/p&gt; &lt;p&gt; Souvent fusionné avec le Nyâya (logique), il postule un Īśvara ordonnateur. La délivrance est un état pur de l'âme (sans qualités, conscience ou douleur), libérée des agrégats par la gnose discriminante. &lt;/p&gt;"/>
-    <hyperlink ref="E36" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_mah%C4%81y%C4%81na&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Mahayana&lt;/a&gt; (« Grand Véhicule ») est apparu en Inde au tournant de l'ère chrétienne, s'étendant progressivement vers la Chine, le Japon, la Corée et le Vietnam. Par rapport au Theravada, il représente une transformation profonde de la vision bouddhiste : l'éveil n'est plus un idéal solitaire mais une aspiration collective.&lt;/p&gt;&lt;p&gt;L'idéal central du Mahayana est le bodhisattva : l'être qui, sur le point d'atteindre le Nirvana, choisit de demeurer dans le cycle des renaissances (samsara) pour guider et libérer tous les êtres sensibles. Cette compassion universelle (karuna) devient le moteur de la voie spirituelle, indissociable de la sagesse (prajna).&lt;/p&gt;&lt;p&gt;Le Mahayana introduit également la notion révolutionnaire de sunyata (vacuité) : toutes choses sont dénues d'existence propre et intrinsèque — elles n'existent que de façon interdependante. Nagarjuna, au IIe siècle, en développa la philosophie dans ses Stances du Milieu, fondant l'école Madhyamaka qui influencça toute la pensée bouddhiste ultérieure.&lt;/p&gt;&lt;p&gt;C'est sur le sol du Mahayana que fleuriront le bouddhisme Zen, le bouddhisme tibétain Vajrayana, et l'École de la Terre Pure. Avec ses sutras nouveaux (Lotus, Vimalakirti, Prajnaparamita), le Mahayana offre une vision du monde d'une richesse philosophique et spirituelle sans équivalent.&lt;/p&gt;"/>
-    <hyperlink ref="E38" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mazdakisme&quot; title=&quot;Wikipedia&quot;&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse sous l’Empire sassanide. Fondé par le réformateur Mazdak, ce courant tire ses origines à la fois du mazdéisme et du manichéisme, en proposant une relecture dualiste du monde axée sur la lumière et les ténèbres. &lt;/p&gt; &lt;p&gt; Contrairement aux structures sociales hiérarchisées de l’époque, le mazdakisme prônait une égalité radicale entre les individus. Mazdak soutenait que les causes des conflits humains résidaient dans la soif de richesses et de pouvoir, ce qui l'a conduit à prôner la mise en commun des biens matériels et, selon certaines sources, des femmes. &lt;/p&gt; &lt;p&gt; Cette doctrine a été perçue comme une menace par l’aristocratie et le clergé zoroastrien traditionnel, qui y voyaient une hérésie dangereuse pour l'ordre établi. Après avoir initialement bénéficié de l'intérêt de l'empereur Kavadh Ier, le mouvement fut sévèrement réprimé lors de grandes purges organisées entre 524 et 529. &lt;/p&gt; &lt;p&gt; Bien que le mazdakisme ait été marginalisé après ces persécutions, il a laissé une trace durable dans la pensée iranienne. Parfois qualifié, de manière anachronique, de mouvement proto-socialiste, son idéal de justice sociale a influencé certains courants contestataires qui se sont manifestés en Iran jusqu'au XIVe siècle environ. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E40" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_vajrayana&quot;  title=&quot;Wikipedia&quot;&gt;Le Vajrayana&lt;/a&gt; (« Véhicule de Diamant ») est la troisième grande forme du bouddhisme, développée en Inde entre le VIIe et le Xe siècle, puis transmise au Tibet, en Mongolie et dans l'Himalaya. Il représente la voie tantrique du bouddhisme, utilisant des pratiques ésotériques pour accélérer le chemin vers l'éveil.&lt;/p&gt;&lt;p&gt;Là où le Theravada vise l'éveil en de nombreuses vies et le Mahayana en d'innombrables éons, le Vajrayana affirme qu'il est possible d'atteindre l'éveil en une seule vie — voire en un seul instant. Pour cela, il mobilise un arsenal de techniques : mantras, mandalas, mudras, visualisations de divinités, pratiques yogiques subtiles sur les énergies intérieures du corps.&lt;/p&gt;&lt;p&gt;Le Bouddhisme tibétain, la forme la plus répandue du Vajrayana, s'est développé dès le VIIe siècle sous le règne du roi Songtsen Gampo. Il intègre des éléments de la religion Bön préexistante et du Mahayana indien. Ses figures tutlaires — Padmasambhava, Milarepa, Tsongkhapa — sont au cœur d'une tradition d'une richesse philosophique et rituelle incomparable.&lt;/p&gt;&lt;p&gt;La notion de &quot;nature de bouddha&quot; (tathagatagarbha) — l'idée que chaque être possède en lui la graine de l'éveil — est centrale dans le Vajrayana. La pratique vise à reconnaître directement cette nature lumineuse originelle, au-delà des voiles de l'ignorance et de l'égo.&lt;/p&gt;"/>
-    <hyperlink ref="E42" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/V%C3%A9danta&quot;  title=&quot; Wikipedia&quot;&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).https://fr.wikipedia.org/wiki/Védanta&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;&#10;&#10;"/>
-    <hyperlink ref="E44" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
-    <hyperlink ref="E48" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>
-    <hyperlink ref="E52" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bushido&quot; title=&quot;Wikipedia&quot;&gt;Le Bushido&lt;/a&gt; (« Voie du Guerrier ») est le code éthique de la classe des samouraïs du Japon féodal, progressivement formalisé entre l'époque Kamakura (XIIe siècle) et la période Edo. Il synthétise en une philosophie de vie cohérente des valeurs empruntées au bouddhisme zen, au shintoïsme et au confucianisme.&lt;/p&gt;&lt;p&gt;Les sept vertus cardinales du Bushido sont : la rectitude (gi), le courage (yu), la bienveillance (jin), le respect (rei), la sincérité (makoto), l'honneur (meiyo) et la loyauté (chugi). À celles-ci s'ajoute la maîtrise de soi, la frugalité et l'acceptation stoïque de la mort — le samouraï doit &quot;vivre comme s'il était déjà mort&quot; pour agir sans attachement ni peur.&lt;/p&gt;&lt;p&gt;La pratique de seppuku (suicide rituel) illustre à l'extrême cette philosophie : la mort honorable vaut mieux qu'une vie dans la honte. Cette acceptation de la mort comme acte ultime de liberté et de dignité a fasciné les philosophes — de Nitobe Inazo, qui codafia le Bushido en 1900, à ceux qui y voient une forme de stoïcisme oriental.&lt;/p&gt;&lt;p&gt;Après la fin de l'ère des samouraïs au XIXe siècle, le Bushido survit dans les arts martiaux japonais (kendo, judo, aïkido), dans la culture d'entreprise japonaise et dans une vision de l'excellence par la maîtrise de soi qui continue d'inspirer bien au-delà du Japon.&lt;/p&gt;"/>
-    <hyperlink ref="E58" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fondamentalisme&quot;   title=&quot; Wikipedia&quot;&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient , principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les religions ; le fondamentalisme chrétien par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E66" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
-    <hyperlink ref="E71" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
-    <hyperlink ref="E72" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E73" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
-    <hyperlink ref="E81" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
-    <hyperlink ref="E82" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
+    <hyperlink ref="E16" r:id="rId1" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Religions_m%C3%A9soam%C3%A9ricaines&quot;  title=&quot; Wikipedia&quot;&gt;Le Mysticisme mésoaméricain&lt;/a&gt; désigne les traditions philosophiques et spirituelles des civilisations précolombiennes d'Amérique centrale, en particulier les Aztèques, les Mayas et les Toltèques. Ces pensées forment un univers conceptuel original, structuré autour de la relation entre l'homme, le cosmos et les forces divines.&lt;/p&gt;&lt;p&gt;Au cœur de ces traditions se trouve la notion de &lt;em&gt;teotl&lt;/em&gt; (divinité, énergie sacrée) chez les Aztèques, ou de &lt;em&gt;k'ul&lt;/em&gt; (force vitale sacrée) chez les Mayas. La cosmologie mésoaméricaine conçoit l'univers comme un système de cycles temporels, où les dieux et les hommes sont liés par des obligations réciproques. Le sacrifice rituel, loin d'être une simple pratique violente, est pensé comme une nécessité cosmique pour maintenir l'équilibre du monde.&lt;/p&gt;&lt;p&gt;Des figures comme Quetzalcóatl (le Serpent à plumes) incarnent une sagesse éthique et philosophique : tempérance, connaissance, opposition au sacrifice humain selon certaines traditions. Les philosophes aztèques, les &lt;em&gt;tlamatinime&lt;/em&gt;, s'interrogeaient sur la nature du vrai, du beau, du bien, et sur la condition humaine — une tradition philosophique autonome redécouverte par des chercheurs comme Miguel León-Portilla.&lt;/p&gt;"/>
+    <hyperlink ref="E19" r:id="rId2" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/H%C3%A9sychasme&quot; title=&quot; Wikipedia&quot;&gt;L'Hésychasme&lt;/a&gt; est une tradition mystique et contemplative du christianisme oriental, dont le nom vient du grec &lt;em&gt;hésychia&lt;/em&gt; (silence, tranquillité). Il désigne une pratique spirituelle visant à atteindre l'union avec Dieu par la prière continue, le silence intérieur et la maîtrise du souffle.&lt;/p&gt;&lt;p&gt;Ses origines remontent aux Pères du désert des IVe-Ve siècles, mais c'est au XIVe siècle que l'hésychasme devient un courant théologique et philosophique structuré, notamment grâce à Grégoire Palamas, archevêque de Thessalonique, qui en formule la doctrine dans ses &lt;em&gt;Triades&lt;/em&gt;. Palamas distingue l'essence divine (inaccessible) des énergies divines (accessibles à l'expérience mystique), permettant de fonder théologiquement la possibilité d'une véritable union de l'homme avec Dieu.&lt;/p&gt;&lt;p&gt;Cette distinction essence-énergies est l'une des contributions philosophiques les plus originales de la pensée byzantine. L'hésychasme a profondément marqué la spiritualité orthodoxe russe, grecque et serbe, et continue d'irriguer la théologie et la philosophie orthodoxes contemporaines.&lt;/p&gt;"/>
+    <hyperlink ref="E21" r:id="rId3" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Ch%C3%A2rv%C3%A2ka&quot;  title=&quot;Wikipedia&quot;&gt;Le Lokayata&lt;/a&gt;, également connu sous le nom de Carvaka, est la seule école philosophique de l'Inde ancienne à avoir défendu un matérialisme radical et un athéisme déclaré. Fondée vers le VIe siècle avant notre ère, elle rejette tout ce qui ne peut être appréhendé par les sens : pas d'âme immortelle, pas d'au-delà, pas de loi karmique.&lt;/p&gt;&lt;p&gt;Sa devise pourrait se résumer ainsi : ce que l'on voit existe ; ce que l'on ne peut percevoir n'est qu'invention. Les Carvakas refusent les Védas et leur autorité, les rituels brahmaniques, et toute forme de spéculation métaphysique. L'univers est composé des quatre éléments — terre, eau, feu et air — sans qu'intervienne aucune divinité créatrice.&lt;/p&gt;&lt;p&gt;En matière d'éthique, la philosophie Carvaka est franchement hédoniste : le plaisir est le seul bien réel, la souffrance le seul mal. Mieux vaut jouir de la vie maintenant plutôt qu'espérer une récompense illusoire après la mort. Ce réalisme sans concession en fait une voix singulière, souvent persécutée, de la pensée indienne classique.&lt;/p&gt;&lt;p&gt;Bien que ses textes originaux aient presque tous disparu — connus surtout par les réfutations de ses adversaires — son influence demeure dans les courants matérialistes et rationalistes qui traversent la philosophie indienne jusqu'à aujourd'hui.&lt;/p&gt;"/>
+    <hyperlink ref="E26" r:id="rId4" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra&quot; title=&quot; Wikipedia&quot;&gt; Le Yoga&lt;/a&gt; en tant qu’école philosophique (darshana) est distinct de la pratique physique popularisée en Occident. Systématisé par Patanjali dans les Yoga Sutra (entre 200 av. J.-C. et 500 apr. J.-C.), il partage la métaphysique dualiste du Samkhya — Purusha (conscience) et Prakriti (matière) — mais y ajoute une méthode pratique précise pour la libération.&lt;/p&gt;&lt;p&gt;Les huit membres (ashtanga) du Yoga structurent ce chemin : discipline éthique (yama, niyama), posture (asana), maîtrise du souffle (pranayama), retrait des sens (pratyahara), concentration (dharana), méditation (dhyana) et absorption (samadhi). Chaque étape prépare la suivante dans une progression méthodique vers l’arrêt des fluctuations du mental (chitta vritti nirodha).&lt;/p&gt;&lt;p&gt;Contrairement au Samkhya, purement théorique, le Yoga de Patanjali introduit îshvara (un principe divin, seigneur particulier parmi les âmes) comme objet de concentration facultatif — une nuance théiste absente du Samkhya classique. Cette différence a nourri des siècles de commentaires et de débats entre les deux écoles sœurs.&lt;/p&gt;&lt;p&gt;Aujourd’hui mondialement diffusée, la dimension physique du yoga occulte souvent sa profondeur philosophique originelle : une discipline rigoureuse de la conscience, visant non le bien-être mais la discrimination (viveka) entre le Soi éternel et les fluctuations passagères du mental.&lt;/p&gt;"/>
+    <hyperlink ref="E28" r:id="rId5" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme&quot;  title=&quot; Wikipedia&quot;&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt;    &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title=&quot;Le Taoïsme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E32" r:id="rId6" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/École_des_Noms&quot;  title=&quot;Wikipedia&quot;&gt;L'École des Noms&lt;/a&gt; (ming jia, 名家) est une école de philosophie chinoise qui s'est développée pendant la période des Royaumes combattants. Sa préoccupation centrale : la relation entre les mots et les choses, entre les noms et la réalité qu'ils désignent.&lt;/p&gt;&lt;p&gt;Ses représentants les plus célèbres, Gongsun Long et Hui Shi, sont connus pour leurs paradoxes vertigineux. Gongsun Long affirmait que &quot;le cheval blanc n'est pas un cheval&quot; — non par provocation, mais pour distinguer le concept général (cheval) du particulier concret (ce cheval blanc). Hui Shi proclamait que &quot;le ciel et la terre sont d'une même hauteur&quot;, explorant les limites relatives de toute catégorisation.&lt;/p&gt;&lt;p&gt;Ces réflexions sur le langage anticipent certaines problématiques de la logique et de la philosophie analytique moderne. Comment les mots nous permettent-ils — ou nous empêchent-ils — de saisir la réalité ? Toute classification n'implique-t-elle pas une distorsion du monde ?&lt;/p&gt;&lt;p&gt;Peu influente politiquement, l'École des Noms fut souvent moquée par ses contemporains confu céens et taoïstes. Mais elle constitue une contribution unique à la logique asiatique et à la philosophie du langage dans la pensée mondiale.&lt;/p&gt;"/>
+    <hyperlink ref="E33" r:id="rId7" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/S%C3%A2mkhya&quot;  title=&quot; Wikipedia&quot;&gt;Le Sâmkhya&lt;/a&gt; est l'une des plus anciennes écoles philosophiques de l'Inde, considérée comme un darshana orthodoxe de l'hindouisme. Il propose une analyse rationnelle de la réalité pour libérer l'individu du cycle des renaissances et de la souffrance. Ce système dualiste distingue deux réalités ultimes : Purusha, la conscience pure et passive (esprit, principe masculin), et Prakriti, la matière primordiale active (énergie universelle, principe féminin). Prakriti évolue sous l'influence des trois guṇas (sattva : harmonie ; rajas : activité ; tamas : inertie), générant le monde manifesté à travers 23 tattvas (principes), comme buddhi (intelligence), ahaṃkāra (ego) et les sens. &lt;/p&gt; &lt;p&gt; Il explique la création comme une transformation de Prakriti, sans recours à un dieu créateur : de l'état non manifesté (avyakta) naît le manifesté (vyakta), incluant le corps subtil qui transmigre. L'ignorance (avidyā) cause l'identification erronée du Purusha à la matière, source de souffrance (duḥkha). &lt;/p&gt; &lt;p&gt; Fondement théorique du Yoga de Patañjali, le Sâmkhya met l'accent sur la discrimination (viveka) entre Purusha et Prakriti pour atteindre la libération (kaivalya). Il influence largement la philosophie indienne, des Puranas au Vedānta. &lt;/p&gt;"/>
+    <hyperlink ref="E35" r:id="rId8" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Therav%C4%81da&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Theravada&lt;/a&gt; (« École des Anciens ») est la plus ancienne forme du bouddhisme conservée jusqu'à nos jours. Héritière directe des enseignements du Bouddha historique, elle s'enracina progressivement en Asie du Sud-Est : Sri Lanka, Thaïlande, Myanmar, Cambodge, Laos.&lt;/p&gt;&lt;p&gt;Au cœur du Theravada se trouve le Pali Canon (Tipitaka), le corpus scripturaire le plus ancien du bouddhisme. Sa philosophie insiste sur la voie individuelle vers l'éveil : chaque être doit parcourir lui-même le Noble Sentier Octuple — juste compréhension, juste intention, juste parole, juste action, juste mode de vie, juste effort, juste attention, juste concentration.&lt;/p&gt;&lt;p&gt;L'idéal du Theravada est l'Arhat : le sage qui, par sa propre pratique, a éteint les &quot;feux&quot; de l'attachement, de la haine et de l'illusion, et atteint le Nirvana. Cette voie solitaire et rigoureuse contraste avec l'idéal du bodhisattva du Mahayana, qui renonce à son propre éveil pour sauver tous les êtres.&lt;/p&gt;&lt;p&gt;La méditation de pleine conscience (sati), aujourd'hui mondialement répandue, trouve ses racines dans les pratiques contemplatives du Theravada, notamment la méditation vipassana qui vise à observer directement l'impermanence, la souffrance et l'absence de soi.&lt;/p&gt;"/>
+    <hyperlink ref="E37" r:id="rId9" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Vaisheshika&quot;  title=&quot; Wikipedia&quot;&gt;Le Vaisheshika&lt;/a&gt;  est une école philosophique orthodoxe hindoue, fondée par le sage Kaṇāda, qui se distingue par son atomisme et son réalisme ontologique. Exposée dans les Vaiśeṣika Sūtra (non antérieurs à l'ère chrétienne), elle vise la libération (mokṣa) par la connaissance des catégories fondamentales de la réalité. Le système repose sur six ou sept padārthas (catégories) : dravya (substance), guṇa (qualité), karma (action/mouvement), sāmānya (universalité), viśeṣa (particularité) et samavāya (inhérence). Parmi les neuf substances, quatre sont atomiques (terre, eau, feu, air) : les paramāṇu (atomes éternels, indivisibles) s'assemblent en dyades puis en objets composites non éternels. &lt;/p&gt; &lt;p&gt; Sans dieu créateur direct, l'univers émerge de combinaisons atomiques influencées par une cause efficiente (adrisṭa, karma résiduel). Ākāśa (espace), kāla (temps), dik (direction) et cit (âme) complètent les substances ; les atomes sphériques se lient par forces intrinsèques, formant un monde discontinu mais perceptible. &lt;/p&gt; &lt;p&gt; Souvent fusionné avec le Nyâya (logique), il postule un Īśvara ordonnateur. La délivrance est un état pur de l'âme (sans qualités, conscience ou douleur), libérée des agrégats par la gnose discriminante. &lt;/p&gt;"/>
+    <hyperlink ref="E38" r:id="rId10" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_mah%C4%81y%C4%81na&quot; title=&quot;Wikipedia&quot;&gt;Le Bouddhisme Mahayana&lt;/a&gt; (« Grand Véhicule ») est apparu en Inde au tournant de l'ère chrétienne, s'étendant progressivement vers la Chine, le Japon, la Corée et le Vietnam. Par rapport au Theravada, il représente une transformation profonde de la vision bouddhiste : l'éveil n'est plus un idéal solitaire mais une aspiration collective.&lt;/p&gt;&lt;p&gt;L'idéal central du Mahayana est le bodhisattva : l'être qui, sur le point d'atteindre le Nirvana, choisit de demeurer dans le cycle des renaissances (samsara) pour guider et libérer tous les êtres sensibles. Cette compassion universelle (karuna) devient le moteur de la voie spirituelle, indissociable de la sagesse (prajna).&lt;/p&gt;&lt;p&gt;Le Mahayana introduit également la notion révolutionnaire de sunyata (vacuité) : toutes choses sont dénues d'existence propre et intrinsèque — elles n'existent que de façon interdependante. Nagarjuna, au IIe siècle, en développa la philosophie dans ses Stances du Milieu, fondant l'école Madhyamaka qui influencça toute la pensée bouddhiste ultérieure.&lt;/p&gt;&lt;p&gt;C'est sur le sol du Mahayana que fleuriront le bouddhisme Zen, le bouddhisme tibétain Vajrayana, et l'École de la Terre Pure. Avec ses sutras nouveaux (Lotus, Vimalakirti, Prajnaparamita), le Mahayana offre une vision du monde d'une richesse philosophique et spirituelle sans équivalent.&lt;/p&gt;"/>
+    <hyperlink ref="E40" r:id="rId11" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Mazdakisme&quot; title=&quot;Wikipedia&quot;&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse sous l’Empire sassanide. Fondé par le réformateur Mazdak, ce courant tire ses origines à la fois du mazdéisme et du manichéisme, en proposant une relecture dualiste du monde axée sur la lumière et les ténèbres. &lt;/p&gt; &lt;p&gt; Contrairement aux structures sociales hiérarchisées de l’époque, le mazdakisme prônait une égalité radicale entre les individus. Mazdak soutenait que les causes des conflits humains résidaient dans la soif de richesses et de pouvoir, ce qui l'a conduit à prôner la mise en commun des biens matériels et, selon certaines sources, des femmes. &lt;/p&gt; &lt;p&gt; Cette doctrine a été perçue comme une menace par l’aristocratie et le clergé zoroastrien traditionnel, qui y voyaient une hérésie dangereuse pour l'ordre établi. Après avoir initialement bénéficié de l'intérêt de l'empereur Kavadh Ier, le mouvement fut sévèrement réprimé lors de grandes purges organisées entre 524 et 529. &lt;/p&gt; &lt;p&gt; Bien que le mazdakisme ait été marginalisé après ces persécutions, il a laissé une trace durable dans la pensée iranienne. Parfois qualifié, de manière anachronique, de mouvement proto-socialiste, son idéal de justice sociale a influencé certains courants contestataires qui se sont manifestés en Iran jusqu'au XIVe siècle environ. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E42" r:id="rId12" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bouddhisme_vajrayana&quot;  title=&quot;Wikipedia&quot;&gt;Le Vajrayana&lt;/a&gt; (« Véhicule de Diamant ») est la troisième grande forme du bouddhisme, développée en Inde entre le VIIe et le Xe siècle, puis transmise au Tibet, en Mongolie et dans l'Himalaya. Il représente la voie tantrique du bouddhisme, utilisant des pratiques ésotériques pour accélérer le chemin vers l'éveil.&lt;/p&gt;&lt;p&gt;Là où le Theravada vise l'éveil en de nombreuses vies et le Mahayana en d'innombrables éons, le Vajrayana affirme qu'il est possible d'atteindre l'éveil en une seule vie — voire en un seul instant. Pour cela, il mobilise un arsenal de techniques : mantras, mandalas, mudras, visualisations de divinités, pratiques yogiques subtiles sur les énergies intérieures du corps.&lt;/p&gt;&lt;p&gt;Le Bouddhisme tibétain, la forme la plus répandue du Vajrayana, s'est développé dès le VIIe siècle sous le règne du roi Songtsen Gampo. Il intègre des éléments de la religion Bön préexistante et du Mahayana indien. Ses figures tutlaires — Padmasambhava, Milarepa, Tsongkhapa — sont au cœur d'une tradition d'une richesse philosophique et rituelle incomparable.&lt;/p&gt;&lt;p&gt;La notion de &quot;nature de bouddha&quot; (tathagatagarbha) — l'idée que chaque être possède en lui la graine de l'éveil — est centrale dans le Vajrayana. La pratique vise à reconnaître directement cette nature lumineuse originelle, au-delà des voiles de l'ignorance et de l'égo.&lt;/p&gt;"/>
+    <hyperlink ref="E44" r:id="rId13" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/V%C3%A9danta&quot;  title=&quot; Wikipedia&quot;&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).https://fr.wikipedia.org/wiki/Védanta&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;&#10;&#10;"/>
+    <hyperlink ref="E46" r:id="rId14" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Soufisme&quot; title=&quot; Wikipedia&quot;&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;&#10;Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou &quot;soufis&quot;) qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; &#10;Le soufisme a connu une expansion considérable au cours des siècles suivants, en particulier en Iran, en Égypte, en Turquie, en Inde et en Asie centrale. Les soufis ont produit une riche littérature mystique, composée de poèmes, de récits et de traités qui reflètent leur quête de l'union avec Dieu. &lt;/p&gt; &lt;p&gt;&#10;Le soufisme a également été influencé par les cultures et les traditions religieuses des régions où il s'est développé, notamment le zoroastrisme, le bouddhisme, le christianisme et le judaïsme. Cette influence s'est reflétée dans la diversité des pratiques et des enseignements soufis à travers le monde musulman. &lt;/p&gt; &lt;p&gt;&#10;Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title=&quot;Qu'est ce que le Soufisme ? par France Culture&quot;&gt; &lt;source src=&quot;https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;"/>
+    <hyperlink ref="E50" r:id="rId15" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt; Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement du néo-confucianisme chinois sur la péninsule coréenne, en particulier durant la dynastie Joseon (1392–1910) où il devint la doctrine d’État.&lt;/p&gt;&lt;p&gt;Deux figures dominent ce courant : Yi Hwang (Toegye, 1501–1570), qui affirme la primauté du principe immatériel (li) sur la matière (ki) et fonde l’école de Yeongnam, et Yi I (Yulgok, 1536–1584), qui défend au contraire leur interdépendance dynamique. Ce débat li-ki structura la philosophie coréenne pendant des siècles.&lt;/p&gt;&lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (seonbi) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (seowon) diffusèrent cet idéal éducatif dans tout le pays.&lt;/p&gt;&lt;p&gt;Son empreinte demeure profonde dans la société coréenne contemporaine : hiérarchie des âges, valorisation de l’éducation, rites familiaux et éthique du travail y trouvent encore des racines directement confucéennes.&lt;/p&gt;"/>
+    <hyperlink ref="E54" r:id="rId16" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bushido&quot; title=&quot;Wikipedia&quot;&gt;Le Bushido&lt;/a&gt; (« Voie du Guerrier ») est le code éthique de la classe des samouraïs du Japon féodal, progressivement formalisé entre l'époque Kamakura (XIIe siècle) et la période Edo. Il synthétise en une philosophie de vie cohérente des valeurs empruntées au bouddhisme zen, au shintoïsme et au confucianisme.&lt;/p&gt;&lt;p&gt;Les sept vertus cardinales du Bushido sont : la rectitude (gi), le courage (yu), la bienveillance (jin), le respect (rei), la sincérité (makoto), l'honneur (meiyo) et la loyauté (chugi). À celles-ci s'ajoute la maîtrise de soi, la frugalité et l'acceptation stoïque de la mort — le samouraï doit &quot;vivre comme s'il était déjà mort&quot; pour agir sans attachement ni peur.&lt;/p&gt;&lt;p&gt;La pratique de seppuku (suicide rituel) illustre à l'extrême cette philosophie : la mort honorable vaut mieux qu'une vie dans la honte. Cette acceptation de la mort comme acte ultime de liberté et de dignité a fasciné les philosophes — de Nitobe Inazo, qui codafia le Bushido en 1900, à ceux qui y voient une forme de stoïcisme oriental.&lt;/p&gt;&lt;p&gt;Après la fin de l'ère des samouraïs au XIXe siècle, le Bushido survit dans les arts martiaux japonais (kendo, judo, aïkido), dans la culture d'entreprise japonaise et dans une vision de l'excellence par la maîtrise de soi qui continue d'inspirer bien au-delà du Japon.&lt;/p&gt;"/>
+    <hyperlink ref="E60" r:id="rId17" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Fondamentalisme&quot;   title=&quot; Wikipedia&quot;&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient , principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : - la contestation des lois civiles au nom de la loi divine ; - la mobilisation électorale ou militante de groupes religieux ; - parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; &#10; &lt;audio controls title=&quot;les religions ; le fondamentalisme chrétien par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E68" r:id="rId18" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Marxisme&quot;  title=&quot; Wikipedia&quot;&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; &#10; &lt;audio controls title=&quot;l’Occidentalisme par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; &#10;"/>
+    <hyperlink ref="E73" r:id="rId19" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panislamisme&quot; title=&quot;Wikipedia&quot;&gt;Le Panislamisme&lt;/a&gt; est un mouvement politico-religieux qui prône l’union de l’ensemble des communautés musulmanes, ou Oumma, par-delà les frontières ethniques et géographiques. Historiquement, il s’est structuré comme une réponse directe à l’expansionnisme et à l’impérialisme des puissances européennes sur les terres d’Islam. &lt;/p&gt; &lt;p&gt;  L’un des principaux théoriciens de ce mouvement, Djamal al-Din al-Afghani, voyait dans ce rassemblement sous l’autorité d’un calife unique le moyen de restaurer la puissance et la dignité du monde musulman. L’objectif central était de créer une solidarité transnationale capable de préserver l’indépendance des territoires musulmans et de renforcer la cohésion de la civilisation islamique face aux pressions extérieures. &lt;/p&gt; &lt;p&gt; Au cours du XXe siècle, il a évolué vers des formes plus institutionnelles, s'adaptant aux indépendances nationales des États musulmans. Si le projet originel visait un califat politique centralisé, les développements plus récents ont mis l'accent sur des organisations de coopération internationale, cherchant à instaurer un espace de dialogue social, économique et culturel entre les nations musulmanes. &lt;/p&gt; &lt;p&gt; Aujourd'hui, ce concept conserve une résonance importante en tant qu'idéal de fraternité et de défense des valeurs islamiques universelles. Bien qu’il ne constitue plus un mouvement politique unique et homogène, il continue d'inspirer diverses mouvances, allant de la diplomatie interétatique à des aspirations militantes prônant une restauration globale de l'unité islamique. &lt;/p&gt; &#10;"/>
+    <hyperlink ref="E74" r:id="rId20" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Cosmisme&quot; title=&quot; Wikipedia&quot;&gt;Le Cosmisme&lt;/a&gt; est un courant de pensée à la fois philosophique et religieux apparu en Russie et qui lie très étroitement l’avenir de l’humanité à l’évolution de l’univers tout entier. Contrairement aux utopies sociales ou aux spiritualités purement intérieures, il affirme que les plus hautes aspirations de l’homme – comme la recherche de l’immortalité ou du salut – ne se réalisent pas simplement par des réformes politiques ou un progrès moral, mais par une transformation active du cosmos lui‑même. &lt;/p&gt; &lt;p&gt; D’un point de vue religieux‑philosophique, il s’inspire du christianisme orthodoxe russe et de la pensée des Pères de l’Église, en voyant le cosmos comme un organisme vivant où l’humanité joue un rôle central. Il met au cœur de sa vision une forte dimension eschatologique : l’idée que le monde actuel est une phase transitoire devant mener à une fin radicale, notamment par la résurrection des morts et la transfiguration de la matière. Cette résurrection n’est pas vue comme un simple miracle divin, mais comme un projet universel que l’humanité doit accomplir grâce à sa conscience et à son travail. &lt;/p&gt; &lt;p&gt; Parallèlement, il  développe une « branche scientifique » qui articule la biologie, la géologie, l’astronomie et la technologie pour penser l’homme comme un acteur de l’évolution cosmique. Les penseurs comme Nikolaï Fiodorov (auteur de la « philosophie de l’œuvre commune ») et Vladimir Vernadski (avec l’idée de la biosphère et de la noosphère) conçoivent l’humanité comme un maillon entre la matière vivante et un stade supérieur de la conscience universelle. Dans cette perspective, la science et la technique deviennent des instruments de réalisation d’une mission quasi‑messianique : faire passer la biosphère terrestre vers une noosphère, monde de la raison maîtrisée. &lt;/p&gt; &lt;p&gt; Il  reste un courant minoritaire, mais il continue d’inspirer la pensée russe et certaines réflexions sur l’avenir de l’humanité, l’espace et la technologie. En réunissant inspirations mystiques chrétiennes, projet scientifique ambitieux et rêve de conquête spatiale, il propose une vision à la fois holistique et anthropocentrique : l’homme comme sujet actif d’une évolution cosmique orientée vers un but final, où la matière, la vie et la conscience seraient harmonieusement réunies. &lt;/p&gt; &#10;  &lt;audio controls title=&quot;Le Cosmisme, l’autre grand récit russe par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/18755-10.02.2022-ITEMA_22928837-2022C19327S0041-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E75" r:id="rId21" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Panafricanisme&quot; title=&quot;Wikipedia&quot;&gt;Le Pan-africanisme&lt;/a&gt; est un mouvement philosophique et politique qui affirme l'unité culturelle, historique et politique des peuples africains et de la diaspora africaine. Son objectif fondamental : l'émancipation collective des Africains face à la colonisation et au racisme systémique.&lt;/p&gt;&lt;p&gt;Les pères du Pan-africanisme sont W.E.B. Du Bois, intellectuel afro-américain qui organisa les premiers Congrès panafricains à partir de 1919, et Marcus Garvey, jamaïcain fondateur du mouvement &quot;Retour en Afrique&quot;. Plus tard, Kwame Nkrumah (premier président du Ghana indépendant en 1957) en fit une philosophie politique concrète, synthétisée dans son &quot;consciencisme&quot; : articuler marxisme, tradition africaine et islam pour bâtir une Afrique unie.&lt;/p&gt;&lt;p&gt;Sur le plan philosophique, le Pan-africanisme engage une critique radicale de l'eurocentrisme : il revendique la richesse des civilisations africaines antérieures à la colonisation, le droit des peuples à disposer d'eux-mêmes, et la nécessité de décoloniser non seulement les États mais aussi les esprits. Frantz Fanon, dans Les Damnés de la Terre (1961), en donne la formulation la plus révolutionnaire.&lt;/p&gt;&lt;p&gt;Aujourd'hui, le Pan-africanisme continue d'inspirer les mouvements pour la justice raciale, les revendications de réparations historiques, et les réflexions sur l'identité africaine dans un monde globalisé. L'Union Africaine, fondée en 2002, est l'héritière institutionnelle de cet idéal d'unité continentale.&lt;/p&gt;"/>
+    <hyperlink ref="E83" r:id="rId22" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;La Négritude&lt;/a&gt;  est un concept littéraire et philosophique développé par des écrivains et intellectuels francophones d'origine africaine et antillaise. Le terme &quot;négritude&quot; a été utilisé pour la première fois par le poète martiniquais Aimé Césaire dans son Cahier d'un retour au pays natal, publié en 1939. &lt;/p&gt; &lt;p&gt;  La négritude est une affirmation de l'identité noire et une critique de la colonisation et du racisme. Les auteurs de la négritude cherchaient à mettre en valeur la culture africaine et à lutter contre les stéréotypes et les préjugés raciaux. Ils revendiquaient leur fierté d'être noirs et affirmaient que la culture africaine avait une valeur intrinsèque. &lt;/p&gt; &lt;p&gt;  Parmi les principaux représentants de la négritude, on trouve Aimé Césaire, Léopold Sédar Senghor (qui deviendra plus tard le premier président du Sénégal) et Léon-Gontran Damas. Ces écrivains ont influencé la littérature et la pensée politique dans les pays francophones d'Afrique et des Caraïbes. &lt;/p&gt; &lt;p&gt;  La négritude a également été un mouvement politique et social, contribuant à l'émergence des mouvements de libération en Afrique. Elle a encouragé la prise de conscience de l'oppression coloniale et a joué un rôle important dans le développement de l'identité noire et de la lutte pour l'égalité des droits. &lt;/p&gt; &#10; &lt;audio controls title=&quot;Bonjour et adieu à la Négritude par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; "/>
+    <hyperlink ref="E84" r:id="rId23" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/N%C3%A9gritude&quot;  title=&quot; Wikipedia&quot;&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; &#10;&#10;"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/frise-courant-pensee-oriental.xlsx
+++ b/data/frise-courant-pensee-oriental.xlsx
@@ -3495,20 +3495,80 @@
         </is>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14">
+    <row r="24" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1">
+        <v>1968</v>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1968</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie de la libération</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9ologie_de_la_lib%C3%A9ration" title=" Wikipedia"&gt;La théologie de la libération&lt;/a&gt; est un courant de pensée chrétien, surtout catholique, né en Amérique latine à la fin des années 1960, dans un continent marqué par la misère, les inégalités et les dictatures. Elle s’appuie sur le renouveau du concile Vatican II et sur la &lt;a href="https://fr.wikipedia.org/wiki/Conf%C3%A9rence_de_Medell%C3%ADn" title=" Wikipedia"&gt;conférence des évêques latino-américains de Medellín&lt;/a&gt;, en 1968, qui dénonce la « violence institutionnalisée » de l’injustice sociale.&lt;/p&gt; &lt;p&gt;Son texte fondateur est &lt;em&gt;Théologie de la libération&lt;/em&gt; (1971) du prêtre péruvien &lt;a href="https://fr.wikipedia.org/wiki/Gustavo_Guti%C3%A9rrez_Merino" title=" Wikipedia"&gt;Gustavo Gutiérrez&lt;/a&gt;. La théologie n’y est plus seulement une réflexion abstraite sur Dieu, mais une « réflexion critique sur la pratique » : elle part de la situation concrète des pauvres et de leur lutte pour leur dignité. Dieu prend parti pour les opprimés, comme il a libéré Israël de l’esclavage en Égypte ; le salut ne concerne pas seulement l’au-delà, il commence par la libération de toutes les servitudes. D’où l’« option préférentielle pour les pauvres ». Pour comprendre les causes de la pauvreté, ces théologiens utilisent les sciences sociales, y compris l’analyse marxiste. La foi se vit dans les &lt;a href="https://fr.wikipedia.org/wiki/Communaut%C3%A9_eccl%C3%A9siale_de_base" title=" Wikipedia"&gt;communautés ecclésiales de base&lt;/a&gt;, où les pauvres lisent eux-mêmes la Bible à la lumière de leur vie. Le Brésilien Leonardo Boff, le jésuite Ignacio Ellacuría, assassiné au Salvador en 1989, et les réflexions de Paulo Freire et d’Enrique Dussel lui sont proches.&lt;/p&gt; &lt;p&gt;Rome, sous Jean-Paul II, critique dans les années 1980 son usage du marxisme et impose le silence à Boff. Sa reconnaissance vient avec le pape François, et l’option pour les pauvres est aujourd’hui reprise par toute l’Église catholique.&lt;/p&gt;  &lt;audio controls title="La théologie de la libération par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13940-23.03.2022-ITEMA_22971810-2022F22805S0082-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">courant chrétien latino-américain qui place au cœur de la foi l’engagement aux côtés des pauvres et contre l’injustice.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologie et spiritualité;Philosophie politique</t>
+        </is>
+      </c>
+      <c r="L24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gustavo GUTIÉRREZ;Leonardo BOFF;Enrique DUSSEL;Paulo FREIRE</t>
+        </is>
+      </c>
+      <c r="M24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sud</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théologies et philosophies de la libération</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14">
         <v>1980</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">1980</t>
         </is>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ubuntu_(philosophie)"   title=" Wikipedia"&gt; L'Ubuntu&lt;/a&gt; trouve ses origines en Afrique subsaharienne, principalement chez les peuples bantous. Ubuntu est un mot en langue zouloue qui peut être traduit approximativement par « humanité envers les autres » ou « je suis parce que nous sommes ». Il s'agit d'une philosophie qui met l'accent sur l'interconnexion, l'interdépendance et la bienveillance mutuelle entre les êtres humains. &lt;/p&gt; &lt;p&gt;
 Dans la philosophie Ubuntu, chaque individu est considéré comme étant en relation avec les autres et le monde qui l'entoure. Les relations humaines sont au cœur de cette philosophie, et l'identité d'une personne est déterminée en grande partie par sa relation avec les autres membres de sa communauté. Selon Ubuntu, nous sommes tous liés et notre bien-être individuel est intrinsèquement lié au bien-être collectif. &lt;/p&gt; &lt;p&gt;
@@ -3517,76 +3577,35 @@
 Il convient de noter que la philosophie Ubuntu ne se limite pas à l'Afrique subsaharienne. Elle a inspiré des penseurs et des leaders du monde entier qui reconnaissent l'importance des relations humaines et de la solidarité pour créer des sociétés justes et inclusives. &lt;/p&gt; &lt;p&gt;Ce n’est qu’au XXe siècle que l’Ubuntu devient une philosophie écrite. En 1980, au Zimbabwe, Stanlake et Tommie Marie Samkange publient &lt;em&gt;Hunhuism or Ubuntuism&lt;/em&gt;, qui en fait le fondement d’une pensée politique africaine. En Afrique du Sud, la Constitution provisoire de 1993 invoque « un besoin d’ubuntu, et non de victimisation » pour sortir de l’apartheid. L’archevêque &lt;a href="https://fr.wikipedia.org/wiki/Desmond_Tutu" title=" Wikipedia"&gt;Desmond Tutu&lt;/a&gt; en fait l’esprit de la Commission vérité et réconciliation, qu’il préside à partir de 1995, et le défend dans &lt;em&gt;Il n’y a pas d’avenir sans pardon&lt;/em&gt; (1999). La même année, le philosophe Mogobe Ramose publie &lt;em&gt;African Philosophy through Ubuntu&lt;/em&gt;, qui en propose une lecture métaphysique : l’être n’est pas une chose figée, mais un mouvement de relations.&lt;/p&gt;  &lt;audio controls title="Ubuntu ou l'histoire, les valeurs et la mémoire par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2012/08/s32/RF_DF1DF1B4-FF64-438F-BC47-78A44A7FA537_GENE.MP3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F25" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G25" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="2" t="s">
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>-500</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ajivika"  title="Wikipedia"&gt;L’Ajīvika&lt;/a&gt; est une école ascétique de l’Inde ancienne, fondée ou réorganisée au Ve siècle av. J.-C. par Makkhali Gosala, contemporain du Bouddha et de &lt;a href="https://fr.wikipedia.org/wiki/Mahavira" title=" Wikipedia"&gt;Mahavira&lt;/a&gt;, le fondateur du jaïnisme, dont il fut un temps le compagnon. Ses textes sont perdus : nous ne la connaissons que par ses adversaires bouddhistes et jaïns, qui en font un portrait hostile. Le nom viendrait d’&lt;em&gt;ājīva&lt;/em&gt;, « mode de vie », allusion à leur règle d’existence.&lt;/p&gt; &lt;p&gt;Sa thèse centrale est un déterminisme radical, la doctrine de la &lt;em&gt;niyati&lt;/em&gt;, le destin. Tout ce qui arrive est fixé d’avance ; l’effort, la vertu ou les rites ne changent rien. Chaque être traverse un nombre immense de renaissances, 8 400 000 grands cycles selon les sources, puis atteint la fin de la souffrance au terme prévu, comme une pelote de fil qui se déroule jusqu’au bout. Le libre arbitre est une illusion. Cette position heurte de front le bouddhisme et le jaïnisme, pour qui les actes, le karma, déterminent l’avenir et l’effort moral conduit à la délivrance. Les Ajīvikas étaient pourtant de rigoureux ascètes, souvent nus, qui pratiquaient parfois le jeûne jusqu’à la mort. Selon les textes jaïns, Gosala mourut peu après une violente querelle avec Mahavira.&lt;/p&gt; &lt;p&gt;Ils connaissent un grand rayonnement sous l’empire Maurya : &lt;a href="https://fr.wikipedia.org/wiki/Ashoka" title=" Wikipedia"&gt;Ashoka&lt;/a&gt; leur fait creuser des &lt;a href="https://fr.wikipedia.org/wiki/Grottes_de_Barabar" title=" Wikipedia"&gt;grottes dans les collines de Barabar&lt;/a&gt;. L’école décline ensuite et disparaît vers le XIVe siècle dans le sud de l’Inde. On y voit l’une des premières formes de fatalisme philosophique, comparable à certaines thèses des stoïciens.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>-500</v>
       </c>
@@ -3594,22 +3613,24 @@
         <v>109</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ajivika"  title="Wikipedia"&gt;L’Ajīvika&lt;/a&gt; est une école ascétique de l’Inde ancienne, fondée ou réorganisée au Ve siècle av. J.-C. par Makkhali Gosala, contemporain du Bouddha et de &lt;a href="https://fr.wikipedia.org/wiki/Mahavira" title=" Wikipedia"&gt;Mahavira&lt;/a&gt;, le fondateur du jaïnisme, dont il fut un temps le compagnon. Ses textes sont perdus : nous ne la connaissons que par ses adversaires bouddhistes et jaïns, qui en font un portrait hostile. Le nom viendrait d’&lt;em&gt;ājīva&lt;/em&gt;, « mode de vie », allusion à leur règle d’existence.&lt;/p&gt; &lt;p&gt;Sa thèse centrale est un déterminisme radical, la doctrine de la &lt;em&gt;niyati&lt;/em&gt;, le destin. Tout ce qui arrive est fixé d’avance ; l’effort, la vertu ou les rites ne changent rien. Chaque être traverse un nombre immense de renaissances, 8 400 000 grands cycles selon les sources, puis atteint la fin de la souffrance au terme prévu, comme une pelote de fil qui se déroule jusqu’au bout. Le libre arbitre est une illusion. Cette position heurte de front le bouddhisme et le jaïnisme, pour qui les actes, le karma, déterminent l’avenir et l’effort moral conduit à la délivrance. Les Ajīvikas étaient pourtant de rigoureux ascètes, souvent nus, qui pratiquaient parfois le jeûne jusqu’à la mort. Selon les textes jaïns, Gosala mourut peu après une violente querelle avec Mahavira.&lt;/p&gt; &lt;p&gt;Ils connaissent un grand rayonnement sous l’empire Maurya : &lt;a href="https://fr.wikipedia.org/wiki/Ashoka" title=" Wikipedia"&gt;Ashoka&lt;/a&gt; leur fait creuser des &lt;a href="https://fr.wikipedia.org/wiki/Grottes_de_Barabar" title=" Wikipedia"&gt;grottes dans les collines de Barabar&lt;/a&gt;. L’école décline ensuite et disparaît vers le XIVe siècle dans le sud de l’Inde. On y voit l’une des premières formes de fatalisme philosophique, comparable à certaines thèses des stoïciens.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F26" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>43</v>
@@ -3621,42 +3642,36 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sâmkhya</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="n">
+          <t xml:space="preserve">Les voies dissidentes de l’Inde</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="208.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
         <v>-500</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
+      <c r="D27" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Yoga_s%C5%ABtra" title=" Wikipedia"&gt; Le Yoga&lt;/a&gt; en tant qu’école philosophique (darshana) est distinct de la pratique physique popularisée en Occident. Systématisé par Patanjali dans les Yoga Sutra (entre 200 av. J.-C. et 500 apr. J.-C.), il partage la métaphysique dualiste du Samkhya — Purusha (conscience) et Prakriti (matière) — mais y ajoute une méthode pratique précise pour la libération.&lt;/p&gt;&lt;p&gt;Les huit membres (ashtanga) du Yoga structurent ce chemin : discipline éthique (yama, niyama), posture (asana), maîtrise du souffle (pranayama), retrait des sens (pratyahara), concentration (dharana), méditation (dhyana) et absorption (samadhi). Chaque étape prépare la suivante dans une progression méthodique vers l’arrêt des fluctuations du mental (chitta vritti nirodha).&lt;/p&gt;&lt;p&gt;Contrairement au Samkhya, purement théorique, le Yoga de Patanjali introduit îshvara (un principe divin, seigneur particulier parmi les âmes) comme objet de concentration facultatif — une nuance théiste absente du Samkhya classique. Cette différence a nourri des siècles de commentaires et de débats entre les deux écoles sœurs. Le commentaire attribué à Vyāsa, vers le Ve siècle, fait autorité, et le roi Bhoja en donne au XIe siècle un autre, resté célèbre.&lt;/p&gt;&lt;p&gt;Aujourd’hui mondialement diffusée, la dimension physique du yoga occulte souvent sa profondeur philosophique originelle : une discipline rigoureuse de la conscience, visant non le bien-être mais la discrimination (viveka) entre le Soi éternel et les fluctuations passagères du mental.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="J27" s="2" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>43</v>
@@ -3668,41 +3683,39 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Védas et brahmanisme</t>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Sâmkhya</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="138.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="n">
-        <v>-470</v>
+        <v>-500</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bouddhisme"  title=" Wikipedia"&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt; &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
+        <v>121</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>122</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
       <c r="J28" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>22</v>
@@ -3710,79 +3723,128 @@
       <c r="M28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védas et brahmanisme</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="n">
+        <v>-470</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bouddhisme"  title=" Wikipedia"&gt; Le Bouddhisme&lt;/a&gt; est une tradition philosophique qui s'est développée à partir des enseignements du Bouddha, un prince indien du 5ème siècle avant JC qui a atteint l'éveil spirituel en méditant sous un arbre, maintenant connu sous le nom de l'Arbre de la Bodhi. &lt;/p&gt; &lt;p&gt;La philosophie bouddhiste repose sur le principe fondamental de la cessation de la souffrance, connu sous le nom de Nirvana, et cherche à atteindre cet état par une compréhension profonde de la nature de la réalité. &lt;/p&gt; &lt;p&gt; Le Bouddhisme enseigne que la souffrance est causée par le désir et l'attachement aux choses matérielles et éphémères, et que la libération de la souffrance peut être atteinte par la compréhension de la nature de l'existence et de la réalité. Pour atteindre cet état de libération, le bouddhisme propose la pratique de la méditation et le développement de la sagesse, de la compassion et de la bienveillance envers tous les êtres vivants. &lt;/p&gt; &lt;p&gt; Il est également connu pour ses enseignements sur les Quatre Nobles Vérités et le Noble Chemin Octuple, qui sont considérés comme les fondements de la pratique bouddhiste. Les Quatre Nobles Vérités décrivent la nature de la souffrance, ses causes, sa cessation et le chemin menant à la cessation de la souffrance. Le Noble Chemin Octuple est une série d'étapes pratiques pour développer la sagesse, la moralité et la concentration, afin d'atteindre l'éveil spirituel. &lt;/p&gt; &lt;p&gt; En outre, la philosophie bouddhiste met l'accent sur l'interdépendance de tous les phénomènes, la nature impermanente de l'existence et la non-existence d'un soi permanent et autonome.&lt;/p&gt; &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18755-11.03.2019-ITEMA_22005213-1.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P28" s="1" t="inlineStr">
+      <c r="O29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P29" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="n">
+    <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="n">
         <v>-450</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14" t="s">
+      <c r="B30" s="14"/>
+      <c r="C30" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D30" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E30" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F30" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G30" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="2" t="s">
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianisme</t>
         </is>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="n">
+    <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="n">
         <v>-410</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D31" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Shinto%C3%AFsme"  style="color:#d35400"  title=" Wikipedia"&gt;Le Shintoïsme&lt;/a&gt; est une religion philosophique autochtone du Japon. Le mot "shinto" signifie littéralement "la voie des dieux" ou "la voie des kami". Les kami sont des esprits ou des divinités vénérées dans la tradition shintoïste. &lt;/p&gt; &lt;p&gt;
 Le shintoïsme est souvent considéré comme une religion animiste, car il accorde une grande importance à la nature et aux phénomènes naturels. Les montagnes, les rivières, les arbres et autres éléments naturels sont vus comme abritant des kami, et ces kami sont vénérés et respectés. Les humains, en tant qu'êtres vivants, sont également considérés comme ayant une âme, et ils sont connectés aux kami et à la nature qui les entoure. Une caractéristique importante du shintoïsme est le culte des ancêtres. Les ancêtres décédés sont également considérés comme des kami et sont vénérés dans les sanctuaires shintoïstes familiaux.  &lt;/p&gt; &lt;p&gt;
@@ -3790,60 +3852,16 @@
 Le shintoïsme a une forte influence sur la culture japonaise. De nombreux festivals et cérémonies au Japon sont de nature shintoïste. Par exemple, le festival du Nouvel An, appelé "Hatsumode", est une célébration importante où les gens se rendent dans les sanctuaires pour prier, faire des offrandes et purifier leur esprit pour la nouvelle année. &lt;/p&gt; &lt;p&gt; Bien que ce ne soit pas une religion qui développe une philosophie systématique comme le bouddhisme ou le confucianisme, il offre une perspective favorisant l'harmonie avec la nature, le respect des ancêtres et la recherche de la pureté spirituelle. Ces idées peuvent être explorées et interprétées dans un contexte philosophique plus large. &lt;/p&gt;  &lt;audio controls title="Le shinto n'est pas une religion à système, c'est un ensemble de croyance très ancienne par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-13.08.2020-ITEMA_22401465-2018C3372E0676-1779455909.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F31" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G31" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="2" t="s">
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Japon : shintō et voies nationales</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="n">
-        <v>-400</v>
-      </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tao%C3%AFsme"  style="color:#d35400"  title=" Wikipedia"&gt;Le Taoïsme&lt;/a&gt; est, avec le confucianisme, l’une des deux grandes traditions de pensée nées en Chine. Il se réclame de &lt;a href="https://fr.wikipedia.org/wiki/Laozi" title=" Wikipedia"&gt;Laozi&lt;/a&gt;, sage peut-être légendaire du VIe siècle av. J.-C., auquel on attribue le &lt;em&gt;Daodejing&lt;/em&gt;, le « Livre de la Voie et de la Vertu », composé sans doute vers le IVe siècle av. J.-C., et de &lt;a href="https://fr.wikipedia.org/wiki/Tchouang-tseu" title=" Wikipedia"&gt;Zhuangzi&lt;/a&gt; (vers 370-287 av. J.-C.), dont le livre mêle fables, dialogues et paradoxes.&lt;/p&gt; &lt;p&gt;Au cœur du taoïsme se trouve le &lt;em&gt;dao&lt;/em&gt;, la Voie : l’origine sans forme de toutes choses et l’ordre spontané selon lequel elles se transforment. « La Voie qui peut être dite n’est pas la Voie constante » : elle échappe aux mots. Elle agit comme l’eau, souple et humble, qui finit par user la pierre. Le sage l’imite par le &lt;em&gt;wuwei&lt;/em&gt;, le « non-agir » : non pas l’inaction, mais une action sans effort ni contrainte, accordée au cours naturel des choses. Contre les confucéens, qui veulent régler la société par les rites et la morale, le taoïsme prône la simplicité, le retour à la nature et un gouvernement aussi discret que possible. Zhuangzi y ajoute un relativisme plein d’humour : ayant rêvé qu’il était papillon, il ne sait plus, au réveil, s’il est Zhuangzi qui a rêvé d’être papillon, ou un papillon qui rêve d’être Zhuangzi.&lt;/p&gt; &lt;p&gt;À partir du IIe siècle se forme aussi une religion taoïste, avec ses temples, ses rites et sa quête de longévité. Le taoïsme a inspiré la peinture, la médecine et les arts martiaux chinois, ainsi que le bouddhisme chan.&lt;/p&gt;  &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/10/s44/NET_FC_43660d0e-6519-4ba7-84a5-c6390767f7da.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="G31" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>22</v>
@@ -3858,36 +3876,39 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="n">
         <v>-400</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/École_des_Noms"  title="Wikipedia"&gt;L’École des Noms&lt;/a&gt;, en chinois &lt;em&gt;mingjia&lt;/em&gt;, est une école de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.) qui s’intéresse au rapport entre les noms et les choses, c’est-à-dire entre le langage et la réalité. À une époque où les Cent Écoles débattent sans cesse, ses penseurs, appelés aussi « disputeurs », cultivent l’art de l’argumentation et du paradoxe, au point de passer pour des sophistes aux yeux de leurs adversaires. Ils prolongent à leur manière une exigence de Confucius, la « rectification des noms », qui veut que les mots s’accordent avec la réalité.&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hui_Shi" title=" Wikipedia"&gt;Hui Shi&lt;/a&gt; (IVe siècle av. J.-C.), ami et contradicteur de Zhuangzi, avance dix paradoxes sur l’espace, le temps et l’unité du monde : « le ciel est aussi bas que la terre », « je pars aujourd’hui pour Yue et j’y suis arrivé hier », ou encore « aimez tous les êtres, car le ciel et la terre ne font qu’un corps ». Ils montrent que toute distinction, grand et petit, haut et bas, dépend du point de vue. Son cadet &lt;a href="https://fr.wikipedia.org/wiki/Gongsun_Long" title=" Wikipedia"&gt;Gongsun Long&lt;/a&gt; (vers 320-250 av. J.-C.) est célèbre pour sa thèse « un cheval blanc n’est pas un cheval » : le nom « cheval blanc » désigne à la fois une forme et une couleur, il ne se confond donc pas avec le nom « cheval ». Il distingue ainsi le concept général des choses particulières, et le nom de ce qu’il désigne.&lt;/p&gt; &lt;p&gt;Raillée par les confucéens et les taoïstes, l’école disparaît avec l’empire Qin. Redécouverte au XXe siècle, elle est vue comme l’un des rares foyers de logique et de philosophie du langage de la Chine ancienne, aux côtés des logiciens moïstes. Un seul de ses livres, le &lt;em&gt;Gongsun Longzi&lt;/em&gt;, nous est parvenu, en partie.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>153</v>
-      </c>
+      <c r="D32" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tao%C3%AFsme"  style="color:#d35400"  title=" Wikipedia"&gt;Le Taoïsme&lt;/a&gt; est, avec le confucianisme, l’une des deux grandes traditions de pensée nées en Chine. Il se réclame de &lt;a href="https://fr.wikipedia.org/wiki/Laozi" title=" Wikipedia"&gt;Laozi&lt;/a&gt;, sage peut-être légendaire du VIe siècle av. J.-C., auquel on attribue le &lt;em&gt;Daodejing&lt;/em&gt;, le « Livre de la Voie et de la Vertu », composé sans doute vers le IVe siècle av. J.-C., et de &lt;a href="https://fr.wikipedia.org/wiki/Tchouang-tseu" title=" Wikipedia"&gt;Zhuangzi&lt;/a&gt; (vers 370-287 av. J.-C.), dont le livre mêle fables, dialogues et paradoxes.&lt;/p&gt; &lt;p&gt;Au cœur du taoïsme se trouve le &lt;em&gt;dao&lt;/em&gt;, la Voie : l’origine sans forme de toutes choses et l’ordre spontané selon lequel elles se transforment. « La Voie qui peut être dite n’est pas la Voie constante » : elle échappe aux mots. Elle agit comme l’eau, souple et humble, qui finit par user la pierre. Le sage l’imite par le &lt;em&gt;wuwei&lt;/em&gt;, le « non-agir » : non pas l’inaction, mais une action sans effort ni contrainte, accordée au cours naturel des choses. Contre les confucéens, qui veulent régler la société par les rites et la morale, le taoïsme prône la simplicité, le retour à la nature et un gouvernement aussi discret que possible. Zhuangzi y ajoute un relativisme plein d’humour : ayant rêvé qu’il était papillon, il ne sait plus, au réveil, s’il est Zhuangzi qui a rêvé d’être papillon, ou un papillon qui rêve d’être Zhuangzi.&lt;/p&gt; &lt;p&gt;À partir du IIe siècle se forme aussi une religion taoïste, avec ses temples, ses rites et sa quête de longévité. Le taoïsme a inspiré la peinture, la médecine et les arts martiaux chinois, ainsi que le bouddhisme chan.&lt;/p&gt;  &lt;audio controls title="Le Taoïsme par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/10/s44/NET_FC_43660d0e-6519-4ba7-84a5-c6390767f7da.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
       <c r="J32" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>101</v>
@@ -3899,180 +3920,172 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="n">
+        <v>-400</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/École_des_Noms"  title="Wikipedia"&gt;L’École des Noms&lt;/a&gt;, en chinois &lt;em&gt;mingjia&lt;/em&gt;, est une école de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.) qui s’intéresse au rapport entre les noms et les choses, c’est-à-dire entre le langage et la réalité. À une époque où les Cent Écoles débattent sans cesse, ses penseurs, appelés aussi « disputeurs », cultivent l’art de l’argumentation et du paradoxe, au point de passer pour des sophistes aux yeux de leurs adversaires. Ils prolongent à leur manière une exigence de Confucius, la « rectification des noms », qui veut que les mots s’accordent avec la réalité.&lt;/p&gt; &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hui_Shi" title=" Wikipedia"&gt;Hui Shi&lt;/a&gt; (IVe siècle av. J.-C.), ami et contradicteur de Zhuangzi, avance dix paradoxes sur l’espace, le temps et l’unité du monde : « le ciel est aussi bas que la terre », « je pars aujourd’hui pour Yue et j’y suis arrivé hier », ou encore « aimez tous les êtres, car le ciel et la terre ne font qu’un corps ». Ils montrent que toute distinction, grand et petit, haut et bas, dépend du point de vue. Son cadet &lt;a href="https://fr.wikipedia.org/wiki/Gongsun_Long" title=" Wikipedia"&gt;Gongsun Long&lt;/a&gt; (vers 320-250 av. J.-C.) est célèbre pour sa thèse « un cheval blanc n’est pas un cheval » : le nom « cheval blanc » désigne à la fois une forme et une couleur, il ne se confond donc pas avec le nom « cheval ». Il distingue ainsi le concept général des choses particulières, et le nom de ce qu’il désigne.&lt;/p&gt; &lt;p&gt;Raillée par les confucéens et les taoïstes, l’école disparaît avec l’empire Qin. Redécouverte au XXe siècle, elle est vue comme l’un des rares foyers de logique et de philosophie du langage de la Chine ancienne, aux côtés des logiciens moïstes. Un seul de ses livres, le &lt;em&gt;Gongsun Longzi&lt;/em&gt;, nous est parvenu, en partie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="n">
+    <row r="34" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="n">
         <v>-350</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9" t="s">
+      <c r="B34" s="9"/>
+      <c r="C34" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D34" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E33" s="18" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/S%C3%A2mkhya"  title=" Wikipedia"&gt;Le Sâmkhya&lt;/a&gt;, « dénombrement », est l’une des six écoles orthodoxes de la philosophie indienne, et sans doute la plus ancienne. On l’attribue au sage légendaire &lt;a href="https://fr.wikipedia.org/wiki/Kapila" title=" Wikipedia"&gt;Kapila&lt;/a&gt;, mais son texte de référence, les &lt;em&gt;Sāṃkhya-kārikā&lt;/em&gt; d’Īśvarakṛṣṇa, date des environs du IVe siècle de notre ère. Comme les autres écoles, il cherche à délivrer l’homme de la souffrance et du cycle des renaissances par la connaissance.&lt;/p&gt; &lt;p&gt;Le Sâmkhya est un dualisme : il distingue deux principes éternels. Le &lt;em&gt;puruṣa&lt;/em&gt; est la conscience pure, immobile, simple témoin ; il y en a une infinité, une par être. La &lt;em&gt;prakṛti&lt;/em&gt; est la nature, matière première active, faite de trois qualités (&lt;em&gt;guṇa&lt;/em&gt;) : la clarté (&lt;em&gt;sattva&lt;/em&gt;), l’énergie (&lt;em&gt;rajas&lt;/em&gt;) et l’inertie (&lt;em&gt;tamas&lt;/em&gt;). Quand leur équilibre se rompt, la nature se déploie en 23 principes : l’intellect, le sens du moi, l’esprit, les sens, puis les éléments subtils et grossiers. Tout effet préexiste dans sa cause, comme l’huile dans la graine, et le monde se forme sans dieu créateur. La souffrance vient de ce que la conscience se confond avec les opérations de la nature, qu’elle ne fait que regarder ; la délivrance, l’« isolement » (&lt;em&gt;kaivalya&lt;/em&gt;), vient du discernement qui les sépare.&lt;/p&gt; &lt;p&gt;Le Sâmkhya fournit sa métaphysique au Yoga de &lt;a href="https://fr.wikipedia.org/wiki/Patanjali" title=" Wikipedia"&gt;Patañjali&lt;/a&gt;, qui en est comme la pratique, et imprègne la &lt;em&gt;Bhagavad-Gîtâ&lt;/em&gt;, la médecine āyurvédique et une grande partie de la pensée hindoue. Le Vedânta lui reproche de séparer la nature de l’Absolu, mais reprend beaucoup de ses notions.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F34" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G34" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="2" t="s">
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t xml:space="preserve">Brahmanisme</t>
         </is>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
+    <row r="35" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="n">
         <v>-350</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D35" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9gisme" title="Wikipedia"&gt;Le Légisme&lt;/a&gt;, en chinois &lt;em&gt;fajia&lt;/em&gt;, « école de la loi », est une philosophie politique de la Chine des Royaumes combattants (Ve-IIIe siècle av. J.-C.). À une époque de guerres incessantes, ses penseurs, souvent ministres, cherchent comment rendre un État riche et puissant. Contre les confucéens, qui veulent gouverner par la vertu et les rites, ils affirment que seule la loi, écrite, publique et appliquée à tous, peut assurer l’ordre.&lt;/p&gt; &lt;p&gt;Au IVe siècle av. J.-C., &lt;a href="https://fr.wikipedia.org/wiki/Shang_Yang" title=" Wikipedia"&gt;Shang Yang&lt;/a&gt; réforme le royaume de Qin : il encourage l’agriculture et la guerre, supprime les privilèges de la noblesse héréditaire et instaure des récompenses et des châtiments rigoureux, avec une responsabilité collective des familles. Shen Buhai insiste sur l’art de contrôler les fonctionnaires, Shen Dao sur la position de pouvoir. &lt;a href="https://fr.wikipedia.org/wiki/Han_Fei" title=" Wikipedia"&gt;Han Fei&lt;/a&gt; (vers 280-233 av. J.-C.), disciple du confucéen Xunzi, réunit la loi, la technique et la position en une doctrine complète. Puisque les hommes recherchent leur intérêt, inutile d’en appeler à leur bonté : le souverain doit les gouverner par la crainte et l’intérêt, rester secret et impénétrable, et faire fonctionner l’État comme une machine qui marche seule.&lt;/p&gt; &lt;p&gt;Le légisme triomphe quand &lt;a href="https://fr.wikipedia.org/wiki/Qin_Shi_Huang" title=" Wikipedia"&gt;Qin Shi Huang&lt;/a&gt; unifie la Chine en 221 av. J.-C. et fait brûler les livres des autres écoles. Discrédité par la chute rapide des Qin, il survit en pratique dans l’administration impériale, sous un vernis confucéen. Dans les années 1970, la campagne maoïste « contre Lin Biao et Confucius » en fait encore l’éloge.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G35" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t xml:space="preserve">Les Cent Écoles de la Chine antique</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianisme</t>
         </is>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
+    <row r="36" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="n">
         <v>-250</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D36" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Therav%C4%81da" title="Wikipedia"&gt;Le Bouddhisme Theravada&lt;/a&gt;, « l’enseignement des Anciens », est la plus ancienne forme du bouddhisme encore vivante. Il se réclame des premiers disciples du Bouddha et se transmet en pali. Sous le règne d’&lt;a href="https://fr.wikipedia.org/wiki/Ashoka" title=" Wikipedia"&gt;Ashoka&lt;/a&gt;, au IIIe siècle av. J.-C., le moine Mahinda l’introduit à Sri Lanka, d’où il gagne la Birmanie, la Thaïlande, le Cambodge et le Laos, où il reste majoritaire.&lt;/p&gt; &lt;p&gt;Ses textes forment le Canon pali, ou &lt;em&gt;Tipitaka&lt;/em&gt; (« trois corbeilles ») : la discipline monastique, les discours du Bouddha et l’&lt;em&gt;Abhidhamma&lt;/em&gt;, analyse philosophique des phénomènes, mis par écrit à Sri Lanka au Ier siècle av. J.-C. Au Ve siècle, &lt;a href="https://fr.wikipedia.org/wiki/Buddhaghosa" title=" Wikipedia"&gt;Buddhaghosa&lt;/a&gt; en donne la synthèse dans le &lt;em&gt;Chemin de la pureté&lt;/em&gt;. L’enseignement repose sur les quatre nobles vérités : la souffrance, son origine dans le désir, sa cessation et le Noble Sentier octuple qui y mène. Tout ce qui existe est impermanent, insatisfaisant et dépourvu de soi : la personne n’est qu’un assemblage changeant de cinq agrégats. L’idéal est l’&lt;em&gt;arhat&lt;/em&gt;, qui a éteint par sa propre pratique les feux du désir, de la haine et de l’illusion, alors que le Mahayana met en avant le bodhisattva, qui se consacre au salut de tous les êtres.&lt;/p&gt; &lt;p&gt;La méditation vipassana, « vision pénétrante », qui observe l’apparition et la disparition des phénomènes, a été remise à l’honneur en Birmanie au XXe siècle par des maîtres comme Mahasi Sayadaw ; elle a inspiré la « pleine conscience » répandue en Occident.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G36" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="J36" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="n">
-        <v>-150</v>
-      </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ny%C3%A2ya" title=" Wikipedia"&gt;Le Nyâya&lt;/a&gt;, « la règle » ou « la méthode », est l’une des six écoles orthodoxes de la philosophie indienne, celle qui s’est consacrée à la logique et à la théorie de la connaissance. Ses textes fondateurs, les &lt;em&gt;Nyāya Sūtra&lt;/em&gt;, attribués à Akṣapāda Gautama, sont composés entre le IIe siècle avant et le IIe siècle de notre ère, à partir de traditions de débat plus anciennes. Leur but reste spirituel : seule la connaissance juste délivre de la souffrance et du cycle des renaissances.&lt;/p&gt; &lt;p&gt;Le Nyâya reconnaît quatre moyens de connaissance valide (&lt;em&gt;pramāṇa&lt;/em&gt;) : la perception, l’inférence, la comparaison et le témoignage digne de foi. Il codifie l’inférence en un raisonnement à cinq membres, illustré par un exemple célèbre : la colline est en feu, parce qu’elle fume ; tout ce qui fume est en feu, comme un foyer de cuisine ; or la colline fume ; donc elle est en feu. Il dresse aussi la liste des sophismes et des ruses de la discussion. Réaliste, il soutient que le monde extérieur existe tel que nous le percevons, contre les bouddhistes. Il défend l’existence d’un Soi permanent et d’un Dieu cause du monde, notamment avec Udayana vers l’an mil. Associé à l’école &lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika" title=" Wikipedia"&gt;Vaiśeṣika&lt;/a&gt;, qui lui apporte sa théorie des atomes et des catégories, il forme avec elle le Nyāya-Vaiśeṣika.&lt;/p&gt; &lt;p&gt;Au XIVe siècle, Gaṅgeśa fonde le « nouveau Nyâya » (&lt;em&gt;Navya-Nyāya&lt;/em&gt;), dont le langage technique devient l’outil commun de toute la philosophie indienne. Ses analyses de l’inférence et du témoignage ont souvent été comparées à la logique d’Aristote.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>43</v>
@@ -4084,44 +4097,44 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+          <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brahmanisme</t>
+          <t xml:space="preserve">Bouddhisme</t>
         </is>
       </c>
     </row>
     <row r="37" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="n">
-        <v>-100</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika"  title=" Wikipedia"&gt;Le Vaisheshika&lt;/a&gt;, de &lt;em&gt;viśeṣa&lt;/em&gt;, « particularité », est l’une des six écoles orthodoxes de la philosophie indienne. Ses &lt;em&gt;Vaiśeṣika Sūtra&lt;/em&gt; sont attribués au sage Kaṇāda, dont le nom signifierait « mangeur de grains », et datent sans doute des débuts de notre ère. Son but est la délivrance (&lt;em&gt;mokṣa&lt;/em&gt;), que procure la connaissance exacte des catégories du réel. Le système est surtout connu par le traité de Praśastapāda (VIe siècle), qui l’organise et le complète.&lt;/p&gt; &lt;p&gt;Le Vaisheshika classe tout ce qui existe en six catégories (&lt;em&gt;padārtha&lt;/em&gt;), auxquelles on ajoute plus tard la non-existence : la substance, la qualité, l’action, l’universel, la particularité et l’inhérence, relation qui unit par exemple une qualité à sa substance. Il compte neuf substances : la terre, l’eau, le feu et l’air, faits d’atomes éternels et indivisibles (&lt;em&gt;paramāṇu&lt;/em&gt;), puis l’éther, le temps, l’espace, l’âme et le sens interne. Les atomes s’assemblent par deux, puis par trois, pour former les objets visibles, qui eux sont périssables. Leurs mouvements sont guidés par l’&lt;em&gt;adṛṣṭa&lt;/em&gt;, la force invisible des actes passés ; les auteurs plus tardifs y ajoutent un Dieu ordonnateur, Īśvara. L’âme délivrée retrouve un état pur, sans plaisir ni douleur, car toute qualité liée au corps a cessé.&lt;/p&gt; &lt;p&gt;Très tôt associé au Nyâya, qui lui apporte sa logique, il forme avec lui le Nyāya-Vaiśeṣika. Son atomisme a souvent été comparé à celui de &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9mocrite" title=" Wikipedia"&gt;Démocrite&lt;/a&gt; ; mais là où Démocrite voyait le hasard, le Vaisheshika voit un ordre moral.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
+      <c r="A37" s="14" t="n">
+        <v>-150</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ny%C3%A2ya" title=" Wikipedia"&gt;Le Nyâya&lt;/a&gt;, « la règle » ou « la méthode », est l’une des six écoles orthodoxes de la philosophie indienne, celle qui s’est consacrée à la logique et à la théorie de la connaissance. Ses textes fondateurs, les &lt;em&gt;Nyāya Sūtra&lt;/em&gt;, attribués à Akṣapāda Gautama, sont composés entre le IIe siècle avant et le IIe siècle de notre ère, à partir de traditions de débat plus anciennes. Leur but reste spirituel : seule la connaissance juste délivre de la souffrance et du cycle des renaissances.&lt;/p&gt; &lt;p&gt;Le Nyâya reconnaît quatre moyens de connaissance valide (&lt;em&gt;pramāṇa&lt;/em&gt;) : la perception, l’inférence, la comparaison et le témoignage digne de foi. Il codifie l’inférence en un raisonnement à cinq membres, illustré par un exemple célèbre : la colline est en feu, parce qu’elle fume ; tout ce qui fume est en feu, comme un foyer de cuisine ; or la colline fume ; donc elle est en feu. Il dresse aussi la liste des sophismes et des ruses de la discussion. Réaliste, il soutient que le monde extérieur existe tel que nous le percevons, contre les bouddhistes. Il défend l’existence d’un Soi permanent et d’un Dieu cause du monde, notamment avec Udayana vers l’an mil. Associé à l’école &lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika" title=" Wikipedia"&gt;Vaiśeṣika&lt;/a&gt;, qui lui apporte sa théorie des atomes et des catégories, il forme avec elle le Nyāya-Vaiśeṣika.&lt;/p&gt; &lt;p&gt;Au XIVe siècle, Gaṅgeśa fonde le « nouveau Nyâya » (&lt;em&gt;Navya-Nyāya&lt;/em&gt;), dont le langage technique devient l’outil commun de toute la philosophie indienne. Ses analyses de l’inférence et du témoignage ont souvent été comparées à la logique d’Aristote.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
       <c r="J37" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>43</v>
@@ -4142,178 +4155,185 @@
         </is>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>188</v>
-      </c>
+    <row r="38" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="n">
+        <v>-100</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vaisheshika"  title=" Wikipedia"&gt;Le Vaisheshika&lt;/a&gt;, de &lt;em&gt;viśeṣa&lt;/em&gt;, « particularité », est l’une des six écoles orthodoxes de la philosophie indienne. Ses &lt;em&gt;Vaiśeṣika Sūtra&lt;/em&gt; sont attribués au sage Kaṇāda, dont le nom signifierait « mangeur de grains », et datent sans doute des débuts de notre ère. Son but est la délivrance (&lt;em&gt;mokṣa&lt;/em&gt;), que procure la connaissance exacte des catégories du réel. Le système est surtout connu par le traité de Praśastapāda (VIe siècle), qui l’organise et le complète.&lt;/p&gt; &lt;p&gt;Le Vaisheshika classe tout ce qui existe en six catégories (&lt;em&gt;padārtha&lt;/em&gt;), auxquelles on ajoute plus tard la non-existence : la substance, la qualité, l’action, l’universel, la particularité et l’inhérence, relation qui unit par exemple une qualité à sa substance. Il compte neuf substances : la terre, l’eau, le feu et l’air, faits d’atomes éternels et indivisibles (&lt;em&gt;paramāṇu&lt;/em&gt;), puis l’éther, le temps, l’espace, l’âme et le sens interne. Les atomes s’assemblent par deux, puis par trois, pour former les objets visibles, qui eux sont périssables. Leurs mouvements sont guidés par l’&lt;em&gt;adṛṣṭa&lt;/em&gt;, la force invisible des actes passés ; les auteurs plus tardifs y ajoutent un Dieu ordonnateur, Īśvara. L’âme délivrée retrouve un état pur, sans plaisir ni douleur, car toute qualité liée au corps a cessé.&lt;/p&gt; &lt;p&gt;Très tôt associé au Nyâya, qui lui apporte sa logique, il forme avec lui le Nyāya-Vaiśeṣika. Son atomisme a souvent été comparé à celui de &lt;a href="https://fr.wikipedia.org/wiki/D%C3%A9mocrite" title=" Wikipedia"&gt;Démocrite&lt;/a&gt; ; mais là où Démocrite voyait le hasard, le Vaisheshika voit un ordre moral.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
       <c r="J38" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N38" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="E39" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bouddhisme_mah%C4%81y%C4%81na" title="Wikipedia"&gt;Le Bouddhisme Mahayana&lt;/a&gt; (« Grand Véhicule ») est apparu en Inde au tournant de l'ère chrétienne, s'étendant progressivement vers la Chine, le Japon, la Corée et le Vietnam. Par rapport au Theravada, il représente une transformation profonde de la vision bouddhiste : l'éveil n'est plus un idéal solitaire mais une aspiration collective. Ses fidèles l’opposent au « Petit Véhicule » (Hīnayāna), expression polémique désignant les écoles anciennes.&lt;/p&gt;&lt;p&gt;L'idéal central du Mahayana est le bodhisattva : l'être qui, sur le point d'atteindre le Nirvana, choisit de demeurer dans le cycle des renaissances (samsara) pour guider et libérer tous les êtres sensibles. Cette compassion universelle (karuna) devient le moteur de la voie spirituelle, indissociable de la sagesse (prajna).&lt;/p&gt;&lt;p&gt;Le Mahayana introduit également la notion révolutionnaire de sunyata (vacuité) : toutes choses sont dénuées d'existence propre et intrinsèque — elles n'existent que de façon interdépendante. Nagarjuna, au IIe siècle, en développa la philosophie dans ses Stances du Milieu, fondant l'école Madhyamaka qui influença toute la pensée bouddhiste ultérieure. Au IVe siècle, Asaṅga et Vasubandhu fondent l’école Yogācāra, pour laquelle le monde n’est que représentation de la conscience.&lt;/p&gt;&lt;p&gt;C'est sur le sol du Mahayana que fleuriront le bouddhisme Zen, le bouddhisme tibétain Vajrayana, et l'École de la Terre Pure. Avec ses sutras nouveaux (Lotus, Vimalakirti, Prajnaparamita), le Mahayana offre une vision du monde d'une richesse philosophique et spirituelle sans équivalent.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>188</v>
+      </c>
       <c r="J39" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>196</v>
+        <v>22</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Védisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N39" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="B40" s="14"/>
-      <c r="C40" s="14" t="n">
-        <v>450</v>
+      <c r="C40" s="14" t="s">
+        <v>190</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="E40" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mazdakisme" title="Wikipedia"&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse à la fin du Ve siècle, sous l’Empire sassanide. Il tire son nom de Mazdak, prêtre réformateur dont la doctrine s’inspire d’un prédicateur plus ancien, Zaradusht de Fasa, et emprunte à la fois au zoroastrisme et au &lt;a href="https://fr.wikipedia.org/wiki/Manich%C3%A9isme_%28religion%29" title=" Wikipedia"&gt;manichéisme&lt;/a&gt;. Nous le connaissons surtout par ses adversaires, chroniqueurs perses, arabes et byzantins.&lt;/p&gt; &lt;p&gt;Comme les manichéens, Mazdak voit le monde comme un mélange de lumière et de ténèbres ; mais pour lui, la lumière agit librement et sciemment, tandis que les ténèbres agissent au hasard, ce qui rend la victoire du bien probable. Le mal humain vient surtout de cinq démons : l’envie, la colère, la vengeance, le besoin et la cupidité. Puisque l’inégalité des richesses nourrit ces passions, il faut partager les biens et, selon ses ennemis, les femmes, ce qui visait sans doute les vastes harems de l’aristocratie. Il prêche aussi la non-violence, le refus de tuer et un régime végétarien. Dans une période de famine, ce message rencontre un large écho populaire. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Kavadh_Ier" title=" Wikipedia"&gt;Kavadh Ier&lt;/a&gt; le soutient d’abord, peut-être pour affaiblir la noblesse et le clergé.&lt;/p&gt; &lt;p&gt;Mais vers 528, son fils, le futur &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, fait massacrer Mazdak et ses partisans. Le mouvement survit dans la clandestinité et inspire des révoltes en Iran à l’époque islamique. On l’a parfois présenté, de façon anachronique, comme un « communisme » avant la lettre.&lt;/p&gt;</t>
+        <v>191</v>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mimamsa"  title=" Wikipedia"&gt;La Mimamsa&lt;/a&gt;, « réflexion » ou « exégèse », est l’une des six écoles orthodoxes de la philosophie indienne. Elle est fondée par Jaimini, à qui l’on attribue les &lt;em&gt;Mīmāṃsā Sūtra&lt;/em&gt;, composés entre le IIIe et le Ier siècle avant notre ère. Son objet est l’interprétation des &lt;a href="https://fr.wikipedia.org/wiki/Veda" title=" Wikipedia"&gt;Védas&lt;/a&gt;, et surtout de leur partie rituelle : comment comprendre les injonctions des textes sacrés pour accomplir correctement les sacrifices et réaliser ainsi le &lt;em&gt;dharma&lt;/em&gt;, l’ordre juste du monde.&lt;/p&gt; &lt;p&gt;Pour la Mimamsa, les Védas sont éternels, sans auteur, ni humain ni divin, et donc infaillibles : ils sont la seule source de connaissance du devoir religieux. Pour les lire, elle développe une science très rigoureuse du langage et de l’interprétation, qui influencera le droit indien. Les injonctions (&lt;em&gt;vidhi&lt;/em&gt;) prescrivent des actes, et chaque acte rituel produit une force invisible, l’&lt;em&gt;apūrva&lt;/em&gt;, qui en porte les fruits dans cette vie ou dans une autre. La Mimamsa ancienne ne fait pas appel à un dieu créateur : l’efficacité des rites suffit à expliquer l’ordre du monde. Elle défend l’existence d’un Soi éternel et la réalité du monde extérieur. Au VIIe siècle, deux grands commentateurs, &lt;a href="https://fr.wikipedia.org/wiki/Kumarila_Bhatta" title=" Wikipedia"&gt;Kumarila Bhatta&lt;/a&gt; et Prabhakara, fondent deux écoles rivales, qui débattent avec le bouddhisme et le Nyāya de la valeur de la connaissance par le témoignage (&lt;em&gt;śabda&lt;/em&gt;).&lt;/p&gt; &lt;p&gt;On l’appelle aussi « première Mimamsa », par opposition au Vedānta, ou « Mimamsa ultérieure », qui s’attache à la partie spéculative des Védas, les Upanishads. Ses principes d’interprétation guident encore les pratiques des brahmanes.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F40" s="14" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="14"/>
       <c r="J40" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Védisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14" t="n">
+        <v>450</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mazdakisme" title="Wikipedia"&gt;Le Mazdakisme&lt;/a&gt; est un mouvement religieux et social apparu en Perse à la fin du Ve siècle, sous l’Empire sassanide. Il tire son nom de Mazdak, prêtre réformateur dont la doctrine s’inspire d’un prédicateur plus ancien, Zaradusht de Fasa, et emprunte à la fois au zoroastrisme et au &lt;a href="https://fr.wikipedia.org/wiki/Manich%C3%A9isme_%28religion%29" title=" Wikipedia"&gt;manichéisme&lt;/a&gt;. Nous le connaissons surtout par ses adversaires, chroniqueurs perses, arabes et byzantins.&lt;/p&gt; &lt;p&gt;Comme les manichéens, Mazdak voit le monde comme un mélange de lumière et de ténèbres ; mais pour lui, la lumière agit librement et sciemment, tandis que les ténèbres agissent au hasard, ce qui rend la victoire du bien probable. Le mal humain vient surtout de cinq démons : l’envie, la colère, la vengeance, le besoin et la cupidité. Puisque l’inégalité des richesses nourrit ces passions, il faut partager les biens et, selon ses ennemis, les femmes, ce qui visait sans doute les vastes harems de l’aristocratie. Il prêche aussi la non-violence, le refus de tuer et un régime végétarien. Dans une période de famine, ce message rencontre un large écho populaire. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Kavadh_Ier" title=" Wikipedia"&gt;Kavadh Ier&lt;/a&gt; le soutient d’abord, peut-être pour affaiblir la noblesse et le clergé.&lt;/p&gt; &lt;p&gt;Mais vers 528, son fils, le futur &lt;a href="https://fr.wikipedia.org/wiki/Khosro_Ier" title=" Wikipedia"&gt;Khosro Ier&lt;/a&gt;, fait massacrer Mazdak et ses partisans. Le mouvement survit dans la clandestinité et inspire des révoltes en Iran à l’époque islamique. On l’a parfois présenté, de façon anachronique, comme un « communisme » avant la lettre.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="H41" s="14"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zoroastrisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4322,74 +4342,122 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhismes</t>
+          <t xml:space="preserve">Proche-Orient ancien et Iran</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Zoroastrisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Zen" title="Wikipedia"&gt;Le Bouddhisme Zen&lt;/a&gt; (Chan en chinois, du sanskrit dhyana, « méditation ») est une branche du Mahayana qui se développa en Chine, selon la tradition sous l'impulsion de Bodhidharma, moine indien arrivé en Chine vers la fin du Ve siècle. Il se transmit ensuite au Japon (XIIe siècle), où il s'enracina profondément dans la culture, les arts et la philosophie.&lt;/p&gt;&lt;p&gt;Le Zen refuse les spéculations intellectuelles et les doctrines compliquées. Il repose sur une idée simple et radicale : l'éveil (satori) ne s'enseigne pas — il se réalise directement, au-delà des mots, dans l'expérience immédiate. La méditation assise (zazen), les koans (questions paradoxales insolubles par la logique), et la relation directe maître-disciple sont ses outils privilégiés. Au Japon, Eisai fonde à la fin du XIIe siècle l’école Rinzai, qui privilégie les kōans, et Dōgen, au XIIIe siècle, l’école Sōtō, centrée sur la simple assise (&lt;em&gt;shikantaza&lt;/em&gt;).&lt;/p&gt;&lt;p&gt;La philosophie zen a profondément irrigué l'art japonais : architecture des jardins de pierres, cérémonie du thé, poésie haïku, arts martiaux, calligraphie. L’esthétique du &lt;em&gt;wabi-sabi&lt;/em&gt;, la beauté de la simplicité et de l’imperfection, doit beaucoup à cette rencontre entre le Zen et la culture japonaise.&lt;/p&gt;&lt;p&gt;Au XXe siècle, le Zen fascina l'Occident — des poètes beat américains aux philosophes existentialistes, notamment grâce aux livres de D. T. Suzuki. Ses apports à la psychologie, à la thérapie et à la pleine conscience contemporaine témoignent de son extraordinaire vitalité hors d'Asie.&lt;/p&gt;</t>
+        </is>
       </c>
       <c r="F42" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M42" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhismes</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Mahayana;Taoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bouddhisme_vajrayana"  title="Wikipedia"&gt;Le Vajrayana&lt;/a&gt; (« Véhicule de Diamant ») est la troisième grande forme du bouddhisme, développée en Inde entre le VIIe et le Xe siècle, puis transmise au Tibet, en Mongolie et dans l'Himalaya. Il représente la voie tantrique du bouddhisme, utilisant des pratiques ésotériques pour accélérer le chemin vers l'éveil.&lt;/p&gt;&lt;p&gt;Là où le Theravada vise l'éveil en de nombreuses vies et le Mahayana en d'innombrables éons, le Vajrayana affirme qu'il est possible d'atteindre l'éveil en une seule vie — voire en un seul instant. Pour cela, il mobilise un arsenal de techniques : mantras, mandalas, mudras, visualisations de divinités, pratiques yogiques subtiles sur les énergies intérieures du corps. Ces pratiques sont transmises par un maître, le lama, après une initiation, et s’appuient sur des textes appelés tantras.&lt;/p&gt;&lt;p&gt;Le Bouddhisme tibétain, la forme la plus répandue du Vajrayana, s'est développé dès le VIIe siècle sous le règne du roi Songtsen Gampo. Il intègre des éléments de la religion Bön préexistante et du Mahayana indien. Ses figures tutélaires — Padmasambhava, Milarepa, Tsongkhapa — sont au cœur d'une tradition d'une richesse philosophique et rituelle incomparable. Le Tibet compte quatre grandes écoles : Nyingma, Kagyu, Sakya et Gelug, celle du dalaï-lama.&lt;/p&gt;&lt;p&gt;La notion de "nature de bouddha" (tathagatagarbha) — l'idée que chaque être possède en lui la graine de l'éveil — est centrale dans le Vajrayana. La pratique vise à reconnaître directement cette nature lumineuse originelle, au-delà des voiles de l'ignorance et de l’ego.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="N43" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P43" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhismes</t>
         </is>
       </c>
-      <c r="Q42" s="1" t="inlineStr">
+      <c r="Q43" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhisme Mahayana</t>
         </is>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="n">
+    <row r="44" customFormat="false" ht="306.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="n">
         <v>750</v>
       </c>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9" t="s">
+      <c r="B44" s="9"/>
+      <c r="C44" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D44" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mutazilisme"  title=" Wikipedia"&gt;Le Mutazilisme&lt;/a&gt;  était un courant théologique et philosophique qui a émergé au sein de l'islam sunnite. Le terme "mutazilisme" dérive du mot arabe "itizal", qui signifie "se séparer" ou "se retirer".  Il est considéré comme l'une des premières écoles théologiques islamiques rationalistes, cherchant à combiner la foi et la raison. Ils croyaient que la raison humaine était une source importante de connaissances et qu'elle devait être utilisée pour interpréter les enseignements religieux. Les mutazilites rejetaient l'idée que le Coran était la parole incréée de Dieu, affirmant plutôt que le Coran était créé et qu'il devait être interprété à la lumière de la raison. &lt;/p&gt; &lt;p&gt;
 Un des principaux enseignements du mutazilisme était la doctrine de la "Justice divine" (Al-'Adl wa al-Tawhid). Selon cette doctrine, Dieu était juste et ne pouvait pas ordonner ou commettre des actes injustes. Ils soutenaient également le concept de libre arbitre humain, affirmant que les humains étaient responsables de leurs propres actes et qu'ils devaient être récompensés ou punis en fonction de leurs actions. &lt;/p&gt; &lt;p&gt; Les principes fondamentaux du mutazilisme comprennent : &lt;/p&gt;
@@ -4399,112 +4467,65 @@
 &lt;p&gt;A partir du IXe siècle, le courant a perdu de son influence en raison de l'opposition des théologiens conservateurs et de l'arrivée au pouvoir de califes plus traditionalistes et a graduellement décliné en tant que courant théologique distinct, bien qu'il ait laissé une empreinte durable sur le développement de la pensée islamique. &lt;/p&gt; &lt;audio controls title="Le néo mutazilisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-13.10.2019-ITEMA_22174473-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F44" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G44" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="2" t="s">
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t xml:space="preserve">Kalâm</t>
         </is>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="14" t="n">
+    <row r="45" customFormat="false" ht="115.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="n">
         <v>750</v>
       </c>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14" t="s">
+      <c r="B45" s="14"/>
+      <c r="C45" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D45" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E44" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/V%C3%A9danta"  title=" Wikipedia"&gt;Le Védanta&lt;/a&gt; ou Uttara Mīmāṃsā, est l'école philosophique hindoue qui culmine les enseignements ésotériques des Upaniṣad, du Brahma Sūtra et de la Bhagavad Gītā, visant à réaliser l'unité entre l'ātman (Soi individuel) et le Brahman (Réalité absolue). C'est le couronnement des six darśanas orthodoxes, opposé à la Mīmāṃsā rituelle par son accent sur la jñāna (connaissance).&lt;/p&gt; &lt;p&gt; Il enseigne que seul le Brahman est réel (brahma satyam), le monde est illusoire (jagat mithyā) et l'individu n'est pas différent du Brahman (jīvo brahmaiva na aparah), l'ignorance (avidyā) causant la perception de dualité via māyā. Les guṇas (sattva, rajas, tamas) conditionnent cette apparence, et la libération (mokṣa) dissout l'illusion par la discrimination. &lt;/p&gt; &lt;p&gt; L'Advaita de Śaṅkara est non-dualiste : Brahman transcende toute distinction, avec trois niveaux de réalité (pāramārthika, vyāvahārika, prātibhāsika). Le Viśiṣṭādvaita de Rāmānuja est qualifié : Dieu (Viṣṇu), âmes et matière forment un tout organique. D'autres comme Dvaita (Madhva) sont dualistes.  &lt;/p&gt; &lt;p&gt; Via jñāna-yoga (discernement), bhakti (dévotion) ou karma-yoga, il guide vers kaivalya. Influençant hindouisme moderne (Vivekananda), yoga et spiritualité globale, il dialogue avec bouddhisme et illumine l'unité sous-jacente de l'existence. &lt;/p&gt;
-</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="s">
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/V%C3%A9danta"  title=" Wikipedia"&gt;Le Védanta&lt;/a&gt;, ou Uttara Mīmāṃsā (« seconde investigation »), est la plus influente des six écoles orthodoxes de la philosophie indienne. Son nom signifie « fin du Véda » : il s’appuie sur les Upanishad, dernière couche des textes védiques, sur les &lt;em&gt;Brahma-sūtra&lt;/em&gt; attribués à Bādarāyaṇa, qui en résument l’enseignement, et sur la &lt;em&gt;Bhagavad-Gītā&lt;/em&gt;. Contrairement à la Mīmāṃsā, centrée sur le rite, il cherche la connaissance (&lt;em&gt;jñāna&lt;/em&gt;) du Brahman, la réalité absolue, et de son rapport avec l’ātman, le Soi.&lt;/p&gt; &lt;p&gt;Les commentateurs de ces trois textes ont fondé des écoles rivales. L’Advaita de Śaṅkara (VIIIe siècle) est non dualiste : seul le Brahman est réel, le monde multiple n’est qu’une apparence (&lt;em&gt;māyā&lt;/em&gt;) produite par l’ignorance (&lt;em&gt;avidyā&lt;/em&gt;), et le Soi ne fait qu’un avec le Brahman. Le Viśiṣṭādvaita de Rāmānuja (XIe-XIIe siècle), « non-dualisme qualifié », fait du monde et des âmes le corps réel d’un Dieu personnel, Vishnou. Le Dvaita de Madhva (XIIIe siècle) est franchement dualiste : Dieu, les âmes et la matière sont éternellement distincts. D’autres écoles, comme celles de Nimbārka ou de Vallabha, cherchent des voies intermédiaires.&lt;/p&gt; &lt;p&gt;Selon les écoles, la délivrance (&lt;em&gt;mokṣa&lt;/em&gt;) s’obtient par la connaissance, par la dévotion (&lt;em&gt;bhakti&lt;/em&gt;) ou par l’action désintéressée. Au XIXe siècle, Vivekananda fait du Védanta le visage de l’hindouisme moderne, et il nourrit aujourd’hui le yoga et de nombreuses spiritualités dans le monde.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="G45" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="2" t="s">
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Brahmanisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>800</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>800</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adva%C3%AFta_v%C3%A9danta" title="Wikipedia"&gt;L’Advaïta Védanta&lt;/a&gt;, le « Védânta non dualiste », est la plus influente des écoles issues du Védânta, la réflexion sur les Upanishad, textes qui forment la « fin des Védas ». Sa thèse tient en une formule : le Soi individuel (&lt;em&gt;ātman&lt;/em&gt;) et l’Absolu (&lt;em&gt;brahman&lt;/em&gt;) ne font qu’un. Il est systématisé au VIIIe siècle par &lt;a href="https://fr.wikipedia.org/wiki/Adi_Shankara" title=" Wikipedia"&gt;Shankara&lt;/a&gt;, à la suite de Gaudapada.&lt;/p&gt; &lt;p&gt;Pour Shankara, seul le &lt;em&gt;brahman&lt;/em&gt; est pleinement réel : conscience pure, infinie et sans qualités, il est l’être même de toute chose. Le monde multiple que nous percevons n’est pas un pur néant, mais une apparence, &lt;em&gt;māyā&lt;/em&gt;, comparable à la corde que l’on prend dans la pénombre pour un serpent. Notre sentiment d’être un individu séparé vient de l’ignorance (&lt;em&gt;avidyā&lt;/em&gt;), qui attribue au Soi des caractères qui ne sont pas les siens : le corps, les sens, le moi. La délivrance (&lt;em&gt;mokṣa&lt;/em&gt;) n’est donc ni un lieu à atteindre ni le fruit d’actions ou de rites : elle est la connaissance directe de cette identité, exprimée par les grandes paroles des Upanishad, « Tu es Cela » ou « Je suis brahman ». Shankara fonde aussi des monastères aux quatre coins de l’Inde.&lt;/p&gt; &lt;p&gt;Contesté par Ramanuja et Madhva, qui défendent un Dieu personnel, l’Advaïta devient au XIXe siècle, avec &lt;a href="https://fr.wikipedia.org/wiki/Vivekananda" title=" Wikipedia"&gt;Vivekananda&lt;/a&gt;, le visage de l’hindouisme en Occident. Ramana Maharshi en a été au XXe siècle un maître célèbre, enseignant à ses visiteurs une seule question : « Qui suis-je ? ». On a souvent rapproché sa doctrine de Parménide, de Plotin ou de Spinoza.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>88</v>
@@ -4524,22 +4545,68 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brahmanisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="102" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>800</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Adva%C3%AFta_v%C3%A9danta" title="Wikipedia"&gt;L’Advaïta Védanta&lt;/a&gt;, le « Védânta non dualiste », est la plus influente des écoles issues du Védânta, la réflexion sur les Upanishad, textes qui forment la « fin des Védas ». Sa thèse tient en une formule : le Soi individuel (&lt;em&gt;ātman&lt;/em&gt;) et l’Absolu (&lt;em&gt;brahman&lt;/em&gt;) ne font qu’un. Il est systématisé au VIIIe siècle par &lt;a href="https://fr.wikipedia.org/wiki/Adi_Shankara" title=" Wikipedia"&gt;Shankara&lt;/a&gt;, à la suite de Gaudapada.&lt;/p&gt; &lt;p&gt;Pour Shankara, seul le &lt;em&gt;brahman&lt;/em&gt; est pleinement réel : conscience pure, infinie et sans qualités, il est l’être même de toute chose. Le monde multiple que nous percevons n’est pas un pur néant, mais une apparence, &lt;em&gt;māyā&lt;/em&gt;, comparable à la corde que l’on prend dans la pénombre pour un serpent. Notre sentiment d’être un individu séparé vient de l’ignorance (&lt;em&gt;avidyā&lt;/em&gt;), qui attribue au Soi des caractères qui ne sont pas les siens : le corps, les sens, le moi. La délivrance (&lt;em&gt;mokṣa&lt;/em&gt;) n’est donc ni un lieu à atteindre ni le fruit d’actions ou de rites : elle est la connaissance directe de cette identité, exprimée par les grandes paroles des Upanishad, « Tu es Cela » ou « Je suis brahman ». Shankara fonde aussi des monastères aux quatre coins de l’Inde.&lt;/p&gt; &lt;p&gt;Contesté par Ramanuja et Madhva, qui défendent un Dieu personnel, l’Advaïta devient au XIXe siècle, avec &lt;a href="https://fr.wikipedia.org/wiki/Vivekananda" title=" Wikipedia"&gt;Vivekananda&lt;/a&gt;, le visage de l’hindouisme en Occident. Ramana Maharshi en a été au XXe siècle un maître célèbre, enseignant à ses visiteurs une seule question : « Qui suis-je ? ». On a souvent rapproché sa doctrine de Parménide, de Plotin ou de Spinoza.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Les écoles orthodoxes de l’Inde</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Védanta</t>
         </is>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9" t="n">
+    <row r="47" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="n">
         <v>820</v>
       </c>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9" t="s">
+      <c r="B47" s="9"/>
+      <c r="C47" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D47" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E47" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Soufisme" title=" Wikipedia"&gt; Le Soufisme &lt;/a&gt;  est un courant spirituel de l'islam qui est apparu au début de l'ère islamique, vers le VIIIe siècle. Les soufis, qui sont les adeptes du soufisme, cherchent à atteindre une relation personnelle et directe avec Dieu à travers la pratique de la méditation, de la prière, de la récitation de poèmes mystiques, de la musique et d'autres pratiques spirituelles.&lt;/p&gt; &lt;p&gt;
 Les racines du soufisme remontent aux premiers temps de l'islam, lorsque les premiers musulmans cherchaient à approfondir leur relation avec Dieu en se concentrant sur l'intériorité de leur être. Cependant, le soufisme en tant que courant organisé est apparu plus tard, au VIIIe siècle, avec l'émergence de maîtres spirituels (ou "soufis") qui ont commencé à enseigner des méthodes spécifiques pour atteindre la proximité divine.&lt;/p&gt; &lt;p&gt; 
@@ -4548,60 +4615,16 @@
 Malgré sa popularité et son importance historique, le soufisme a été critiqué et même persécuté par certains courants de l'islam qui le considèrent comme une innovation religieuse non autorisée. Cependant, le soufisme a continué à exister et à se développer, et il reste une force spirituelle importante dans le monde musulman contemporain.&lt;/p&gt;  &lt;audio controls title="Qu'est ce que le Soufisme ? par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2015/03/s11/NET_FC_93b4dc90-9bec-4619-a90c-6e2baee39849.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F47" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="G46" s="11" t="s">
+      <c r="G47" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="H46" s="9"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="2" t="s">
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="O46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>850</v>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>850</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_islamique"   title=" Wikipedia"&gt;Falsafa&lt;/a&gt; est le nom donné à la philosophie rationnelle pratique  dans le monde arabo-islamique médiéval, de Bagdad à Cordoue, entre le IXe et le XIIe siècle. Née du grand mouvement de traduction des textes grecs (Aristote, Platon, Plotin) en arabe, elle tente d'harmoniser la raison grecque avec la révélation islamique.&lt;/p&gt;&lt;p&gt;Al-Kindi (801–873), considéré comme le "père de la Falsafa", fut le premier à introduire la philosophie grecque dans la pensée islamique. Al-Farabi (872–950) construisit une cité idéale philosophique inspirée de Platon. Avicenne (Ibn Sina, 980–1037) synthétisa Aristote et le néoplatonisme dans une vision de l'être, de l'âme et de l'intellect d'une portée immense.&lt;/p&gt;&lt;p&gt;Ces philosophes furent confrontés à une tension fondamentale : la raison peut-elle contredire la foi ? Al-Ghazali répondit par un "oui" dévastateur dans son Incohérence des philosophes. Averroès (Ibn Rushd, 1126–1198) répondit à son tour dans l'Incohérence de l'incohérence, défendant la compatibilité de la philosophie et de l'islam.&lt;/p&gt;&lt;p&gt;La Falsafa transmit aux philosophes chrétiens du Moyen Âge (Thomas d'Aquin, Albert le Grand) l'Aristote qui leur était inconnu. Sans elle, la scolastique européenne n'aurait pas existé sous la forme que nous lui connaissons. Elle reste l'un des grands carrefours de l'histoire intellectuelle de l'humanité.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>22</v>
@@ -4609,34 +4632,78 @@
       <c r="M47" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
+      <c r="N47" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P47" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie et mystique de l’islam</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+    </row>
+    <row r="48" customFormat="false" ht="129" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="n">
+        <v>850</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>850</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_islamique"   title=" Wikipedia"&gt;Falsafa&lt;/a&gt; est le nom donné à la philosophie rationnelle pratiquée  dans le monde arabo-islamique médiéval, de Bagdad à Cordoue, entre le IXe et le XIIe siècle. Née du grand mouvement de traduction des textes grecs (Aristote, Platon, Plotin) en arabe, elle tente d'harmoniser la raison grecque avec la révélation islamique.&lt;/p&gt;&lt;p&gt;Al-Kindi (801–873), considéré comme le "père de la Falsafa", fut le premier à introduire la philosophie grecque dans la pensée islamique. Al-Farabi (872–950) construisit une cité idéale philosophique inspirée de Platon. Avicenne (Ibn Sina, 980–1037) synthétisa Aristote et le néoplatonisme dans une vision de l'être, de l'âme et de l'intellect d'une portée immense.&lt;/p&gt;&lt;p&gt;Ces philosophes furent confrontés à une tension fondamentale : la raison peut-elle contredire la foi ? Dans &lt;em&gt;L’Incohérence des philosophes&lt;/em&gt;, al-Ghazali leur reproche de ne pas démontrer ce qu’ils avancent, et les juge impies sur trois points : l’éternité du monde, l’ignorance des choses particulières qu’ils prêtent à Dieu et le refus de la résurrection des corps. Averroès (Ibn Rushd, 1126–1198) répondit à son tour dans &lt;em&gt;L’Incohérence de l’incohérence&lt;/em&gt;, défendant la compatibilité de la philosophie et de l'islam.&lt;/p&gt;&lt;p&gt;La Falsafa transmit aux philosophes chrétiens du Moyen Âge (Thomas d'Aquin, Albert le Grand) l'Aristote qui leur était inconnu. Sans elle, la scolastique européenne n'aurait pas existé sous la forme que nous lui connaissons. Elle reste l'un des grands carrefours de l'histoire intellectuelle de l'humanité.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
         <is>
           <t xml:space="preserve">Aristotélisme;Néoplatonisme</t>
         </is>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="14" t="n">
+    <row r="49" customFormat="false" ht="290.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="n">
         <v>890</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14" t="s">
+      <c r="B49" s="14"/>
+      <c r="C49" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D49" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E49" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Acharisme"   title=" Wikipedia"&gt;L'Acharisme&lt;/a&gt; est une école théologique sunnite de l'islam, fondée par Abu al-Hasan al-Ash'ari. Il était à l'origine un théologien mutazilite, mais il a finalement rejeté leurs idées et a développé sa propre doctrine théologique qui est devenue connue sous le nom d'acharisme. &lt;/p&gt; &lt;p&gt;
 L'acharisme est basé sur la croyance en l'unicité de Dieu (tawhid) et l'acceptation de la révélation coranique et de la sunna (les enseignements et pratiques du prophète Mahomet). La principale préoccupation de l'acharisme est de défendre et de rationaliser les croyances islamiques face à diverses idées philosophiques et théologiques en circulation à l'époque. &lt;/p&gt; &lt;p&gt;
@@ -4646,66 +4713,19 @@
  &lt;/p&gt;   &lt;audio controls title="La doctrine acharite par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-23.04.2023-ITEMA_23356900-2023C26163E0013-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F49" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="G48" s="16" t="s">
+      <c r="G49" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="2" t="s">
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mutazilisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>900</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>58</v>
@@ -4717,62 +4737,63 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Théologie de l’islam (kalâm)</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mutazilisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="316.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="n">
+        <v>900</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Pensée juive</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t xml:space="preserve">Herméneutique juive;Falsafa</t>
         </is>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e" title=" Wikipedia"&gt;Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement de la pensée confucéenne dans la péninsule coréenne. Arrivé dès l’époque des Trois Royaumes, le confucianisme inspire sous la dynastie Goryeo l’organisation de l’État, avec l’instauration en 958 d’examens pour recruter les fonctionnaires. À la fin du XIIIe siècle, le néoconfucianisme de Zhu Xi est introduit depuis la Chine. Il devient la doctrine officielle de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9riode_Joseon" title=" Wikipedia"&gt;dynastie Joseon&lt;/a&gt; (1392-1910), dont les fondateurs s’appuient sur des lettrés qui veulent réformer l’État et réduire l’influence du bouddhisme.&lt;/p&gt; &lt;p&gt;Deux figures dominent ce courant au XVIe siècle. &lt;a href="https://fr.wikipedia.org/wiki/Yi_Hwang" title=" Wikipedia"&gt;Yi Hwang&lt;/a&gt;, dit Toegye (1501-1570), affirme la primauté du principe (&lt;em&gt;li&lt;/em&gt;), réalité immatérielle et morale, sur l’énergie matérielle (&lt;em&gt;gi&lt;/em&gt;). Il en sort une célèbre controverse, le « débat des quatre et des sept » : les quatre sentiments moraux, comme la compassion, naissent-ils du principe, et les sept émotions ordinaires, comme la colère ou la joie, de l’énergie ? &lt;a href="https://fr.wikipedia.org/wiki/Yi_I" title=" Wikipedia"&gt;Yi I&lt;/a&gt;, dit Yulgok (1536-1584), défend au contraire leur unité dynamique : le principe n’agit jamais sans l’énergie. Ce débat, qui oppose ensuite des écoles rivales, structure la philosophie coréenne pendant des siècles.&lt;/p&gt; &lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (&lt;em&gt;seonbi&lt;/em&gt;) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (&lt;em&gt;seowon&lt;/em&gt;) diffusent cet idéal dans tout le pays. Au XVIIIe siècle, le mouvement Silhak, le « savoir pratique », le tourne vers les réformes concrètes. Son empreinte demeure profonde dans la Corée d’aujourd’hui : respect des aînés, valorisation de l’éducation, rites familiaux et éthique du travail.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Néoconfucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
         <v>1000</v>
       </c>
@@ -4780,31 +4801,27 @@
         <v>1000</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_azt%C3%A8que" title=" Wikipedia"&gt;La Pensée nahua&lt;/a&gt; désigne la réflexion philosophique des peuples de langue nahuatl, dont les Aztèques ou Mexicas, dans le Mexique central avant la conquête espagnole de 1521. Elle était portée par les &lt;em&gt;tlamatinime&lt;/em&gt;, « ceux qui savent quelque chose », sages et maîtres du &lt;em&gt;calmecac&lt;/em&gt;, l’école où l’on formait les jeunes nobles. Nous la connaissons par des codex, des chants et des discours recueillis après la conquête, notamment par le franciscain Bernardino de Sahagún.&lt;/p&gt; &lt;p&gt;L’historien mexicain &lt;a href="https://fr.wikipedia.org/wiki/Miguel_Le%C3%B3n-Portilla" title=" Wikipedia"&gt;Miguel León-Portilla&lt;/a&gt; l’a fait connaître dans &lt;em&gt;La filosofía náhuatl estudiada en sus fuentes&lt;/em&gt; (1956). Les sages s’interrogent sur la fragilité de l’existence : sur terre tout est passager, comme les fleurs qui se fanent, et l’on se demande si quelque chose est vrai, enraciné. Leur réponse est &lt;em&gt;in xochitl in cuicatl&lt;/em&gt;, « la fleur et le chant », c’est-à-dire la poésie, seule capable peut-être de dire le vrai. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Nezahualc%C3%B3yotl" title=" Wikipedia"&gt;Nezahualcóyotl&lt;/a&gt;, souverain de Texcoco au XVe siècle, auquel on attribue de nombreux poèmes, en est la grande figure. Le principe suprême, Ometeotl, « dieu de la dualité », unit le masculin et le féminin ; le monde est fait de couples complémentaires, vie et mort, ordre et désordre, en équilibre instable. Le temps est cyclique : quatre « soleils », quatre âges du monde, ont déjà été détruits, et nous vivons sous le cinquième.&lt;/p&gt; &lt;p&gt;Plus récemment, le philosophe James Maffie a lu dans le &lt;em&gt;teotl&lt;/em&gt; une énergie sacrée, unique et toujours en mouvement, dont toutes choses sont des aspects. Cette pensée est aujourd’hui étudiée comme une véritable tradition philosophique.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mLi2f452GNo</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Aztec Philosophy with James Maffie" par Hermitix Podcast</t>
-        </is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Confucianisme_en_Cor%C3%A9e" title=" Wikipedia"&gt;Le Confucianisme coréen&lt;/a&gt; désigne l’adaptation et l’approfondissement de la pensée confucéenne dans la péninsule coréenne. Arrivé dès l’époque des Trois Royaumes, le confucianisme inspire sous la dynastie Goryeo l’organisation de l’État, avec l’instauration en 958 d’examens pour recruter les fonctionnaires. À la fin du XIIIe siècle, le néoconfucianisme de Zhu Xi est introduit depuis la Chine. Il devient la doctrine officielle de la &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9riode_Joseon" title=" Wikipedia"&gt;dynastie Joseon&lt;/a&gt; (1392-1910), dont les fondateurs s’appuient sur des lettrés qui veulent réformer l’État et réduire l’influence du bouddhisme.&lt;/p&gt; &lt;p&gt;Deux figures dominent ce courant au XVIe siècle. &lt;a href="https://fr.wikipedia.org/wiki/Yi_Hwang" title=" Wikipedia"&gt;Yi Hwang&lt;/a&gt;, dit Toegye (1501-1570), affirme la primauté du principe (&lt;em&gt;li&lt;/em&gt;), réalité immatérielle et morale, sur l’énergie matérielle (&lt;em&gt;gi&lt;/em&gt;). Il en sort une célèbre controverse, le « débat des quatre et des sept » : les quatre sentiments moraux, comme la compassion, naissent-ils du principe, et les sept émotions ordinaires, comme la colère ou la joie, de l’énergie ? &lt;a href="https://fr.wikipedia.org/wiki/Yi_I" title=" Wikipedia"&gt;Yi I&lt;/a&gt;, dit Yulgok (1536-1584), défend au contraire leur unité dynamique : le principe n’agit jamais sans l’énergie. Ce débat, qui oppose ensuite des écoles rivales, structure la philosophie coréenne pendant des siècles.&lt;/p&gt; &lt;p&gt;Au-delà de la métaphysique, le confucianisme coréen insiste sur la formation morale du lettré (&lt;em&gt;seonbi&lt;/em&gt;) : intégrité, sobriété, sens du devoir envers la communauté et l’État. Les académies privées (&lt;em&gt;seowon&lt;/em&gt;) diffusent cet idéal dans tout le pays. Au XVIIIe siècle, le mouvement Silhak, le « savoir pratique », le tourne vers les réformes concrètes. Son empreinte demeure profonde dans la Corée d’aujourd’hui : respect des aînés, valorisation de l’éducation, rites familiaux et éthique du travail.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4813,139 +4830,143 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pensées autochtones</t>
+          <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mysticisme mésoaméricain</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="228" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
-        <v>1150</v>
+        <v>1000</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>1150</v>
+        <v>1000</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Illuminationism"  title="Wikipedia"&gt;L’Ishraqisme&lt;/a&gt;, ou philosophie de l’Illumination (&lt;em&gt;ishrâq&lt;/em&gt;, le lever du soleil), est le courant fondé par le penseur persan &lt;a href="https://fr.wikipedia.org/wiki/Sohrawardi" title=" Wikipedia"&gt;Sohrawardi&lt;/a&gt; (1154-1191). Dans son &lt;em&gt;Livre de la sagesse orientale&lt;/em&gt;, où l’« Orient » désigne la source de la lumière plutôt qu’un lieu, il veut unir la philosophie grecque, en particulier Platon et le néoplatonisme, la sagesse de l’ancienne Perse et la mystique soufie en une vision fondée sur la lumière.&lt;/p&gt; &lt;p&gt;Pour Sohrawardi, toute la réalité est un déploiement de la Lumière des lumières, qui est Dieu. Les êtres s’ordonnent selon leur degré de lumière, des intelligences angéliques jusqu’aux ténèbres de la matière, qui n’est que lumière absente. La connaissance véritable n’est pas d’abord un raisonnement : c’est une « connaissance par présence », immédiate, comme celle que l’âme a d’elle-même. Elle s’acquiert par la purification et l’expérience spirituelle autant que par la logique, et Sohrawardi critique sur ce point Avicenne. Il décrit aussi un monde intermédiaire entre l’esprit et le corps, le monde des images, où se situent les visions des prophètes et des mystiques. Ses récits symboliques, comme &lt;em&gt;Le Bruissement des ailes de Gabriel&lt;/em&gt;, racontent l’exil de l’âme et son retour vers l’Orient de la lumière.&lt;/p&gt; &lt;p&gt;Accusé d’hérésie par les juristes, il est exécuté à Alep avec l’accord de Saladin, d’où son surnom de « maître tué » (&lt;em&gt;al-maqtûl&lt;/em&gt;). Sa pensée nourrit pourtant l’école d’Ispahan et &lt;a href="https://fr.wikipedia.org/wiki/Molla_Sadra_Chirazi" title=" Wikipedia"&gt;Mollâ Sadrâ&lt;/a&gt;. &lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin" title=" Wikipedia"&gt;Henry Corbin&lt;/a&gt; l’a fait connaître en Occident au XXe siècle, en le traduisant et en le commentant.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>272</v>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_azt%C3%A8que" title=" Wikipedia"&gt;La Pensée nahua&lt;/a&gt; désigne la réflexion philosophique des peuples de langue nahuatl, dont les Aztèques ou Mexicas, dans le Mexique central avant la conquête espagnole de 1521. Elle était portée par les &lt;em&gt;tlamatinime&lt;/em&gt;, « ceux qui savent quelque chose », sages et maîtres du &lt;em&gt;calmecac&lt;/em&gt;, l’école où l’on formait les jeunes nobles. Nous la connaissons par des codex, des chants et des discours recueillis après la conquête, notamment par le franciscain Bernardino de Sahagún.&lt;/p&gt; &lt;p&gt;L’historien mexicain &lt;a href="https://fr.wikipedia.org/wiki/Miguel_Le%C3%B3n-Portilla" title=" Wikipedia"&gt;Miguel León-Portilla&lt;/a&gt; l’a fait connaître dans &lt;em&gt;La filosofía náhuatl estudiada en sus fuentes&lt;/em&gt; (1956). Les sages s’interrogent sur la fragilité de l’existence : sur terre tout est passager, comme les fleurs qui se fanent, et l’on se demande si quelque chose est vrai, enraciné. Leur réponse est &lt;em&gt;in xochitl in cuicatl&lt;/em&gt;, « la fleur et le chant », c’est-à-dire la poésie, seule capable peut-être de dire le vrai. Le roi &lt;a href="https://fr.wikipedia.org/wiki/Nezahualc%C3%B3yotl" title=" Wikipedia"&gt;Nezahualcóyotl&lt;/a&gt;, souverain de Texcoco au XVe siècle, auquel on attribue de nombreux poèmes, en est la grande figure. Le principe suprême, Ometeotl, « dieu de la dualité », unit le masculin et le féminin ; le monde est fait de couples complémentaires, vie et mort, ordre et désordre, en équilibre instable. Le temps est cyclique : quatre « soleils », quatre âges du monde, ont déjà été détruits, et nous vivons sous le cinquième.&lt;/p&gt; &lt;p&gt;Plus récemment, le philosophe James Maffie a lu dans le &lt;em&gt;teotl&lt;/em&gt; une énergie sacrée, unique et toujours en mouvement, dont toutes choses sont des aspects. Cette pensée est aujourd’hui étudiée comme une véritable tradition philosophique.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mLi2f452GNo</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Aztec Philosophy with James Maffie" par Hermitix Podcast</t>
+        </is>
       </c>
       <c r="J52" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
-        </is>
-      </c>
-      <c r="Q52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Falsafa;Soufisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mysticisme mésoaméricain</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="225" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="n">
         <v>1150</v>
       </c>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="E53" s="22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oconfucianisme"  title=" Wikipedia"&gt;Le Néoconfucianisme&lt;/a&gt; est le renouveau du confucianisme qui s’épanouit en Chine sous la dynastie Song (960-1279). Face au bouddhisme et au taoïsme, qui offraient une métaphysique et une spiritualité plus riches, des lettrés relisent les Classiques pour donner à la morale confucéenne un fondement cosmique. Devenu orthodoxie d’État, il domine la Chine jusqu’en 1905, ainsi que la Corée, le Japon et le Vietnam.&lt;/p&gt; &lt;p&gt;Zhou Dunyi médite sur le « Faîte suprême » d’où naissent le yin et le yang ; les frères Cheng distinguent en toute chose le &lt;em&gt;li&lt;/em&gt;, principe ou ordre rationnel, et le &lt;em&gt;qi&lt;/em&gt;, souffle ou énergie matérielle. &lt;a href="https://fr.wikipedia.org/wiki/Zhu_Xi" title=" Wikipedia"&gt;Zhu Xi&lt;/a&gt; (1130-1200) fait la synthèse de cette « école du Principe » : chaque être porte en lui le principe universel, et la nature humaine est bonne, comme le disait Mencius, mais obscurcie par un souffle impur. On se perfectionne par l’« investigation des choses », l’étude et la méditation assise. Ses commentaires des Quatre Livres servent de base aux examens impériaux de 1313 à 1905. Contre lui, Lu Jiuyuan puis &lt;a href="https://fr.wikipedia.org/wiki/Wang_Yangming" title=" Wikipedia"&gt;Wang Yangming&lt;/a&gt; (1472-1529) fondent l’« école du Cœur » : le principe n’est pas à chercher dans les choses mais dans le cœur, et la connaissance est inséparable de l’action.&lt;/p&gt; &lt;p&gt;Critiqué au XVIIIe siècle par l’école des études critiques, le &lt;em&gt;kaozheng&lt;/em&gt;, puis par la modernisation, il inspire encore au XXe siècle le « nouveau confucianisme ». En Corée, Yi Hwang et Yi I en débattent au XVIe siècle, et au Japon la doctrine de Zhu Xi devient celle du shogunat Tokugawa.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
+      <c r="C53" s="1" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Illuminationism"  title="Wikipedia"&gt;L’Ishraqisme&lt;/a&gt;, ou philosophie de l’Illumination (&lt;em&gt;ishrâq&lt;/em&gt;, le lever du soleil), est le courant fondé par le penseur persan &lt;a href="https://fr.wikipedia.org/wiki/Sohrawardi" title=" Wikipedia"&gt;Sohrawardi&lt;/a&gt; (1154-1191). Dans son &lt;em&gt;Livre de la sagesse orientale&lt;/em&gt;, où l’« Orient » désigne la source de la lumière plutôt qu’un lieu, il veut unir la philosophie grecque, en particulier Platon et le néoplatonisme, la sagesse de l’ancienne Perse et la mystique soufie en une vision fondée sur la lumière.&lt;/p&gt; &lt;p&gt;Pour Sohrawardi, toute la réalité est un déploiement de la Lumière des lumières, qui est Dieu. Les êtres s’ordonnent selon leur degré de lumière, des intelligences angéliques jusqu’aux ténèbres de la matière, qui n’est que lumière absente. La connaissance véritable n’est pas d’abord un raisonnement : c’est une « connaissance par présence », immédiate, comme celle que l’âme a d’elle-même. Elle s’acquiert par la purification et l’expérience spirituelle autant que par la logique, et Sohrawardi critique sur ce point Avicenne. Il décrit aussi un monde intermédiaire entre l’esprit et le corps, le monde des images, où se situent les visions des prophètes et des mystiques. Ses récits symboliques, comme &lt;em&gt;Le Bruissement des ailes de Gabriel&lt;/em&gt;, racontent l’exil de l’âme et son retour vers l’Orient de la lumière.&lt;/p&gt; &lt;p&gt;Accusé d’hérésie par les juristes, il est exécuté à Alep avec l’accord de Saladin, d’où son surnom de « maître tué » (&lt;em&gt;al-maqtûl&lt;/em&gt;). Sa pensée nourrit pourtant l’école d’Ispahan et &lt;a href="https://fr.wikipedia.org/wiki/Molla_Sadra_Chirazi" title=" Wikipedia"&gt;Mollâ Sadrâ&lt;/a&gt;. &lt;a href="https://fr.wikipedia.org/wiki/Henry_Corbin" title=" Wikipedia"&gt;Henry Corbin&lt;/a&gt; l’a fait connaître en Occident au XXe siècle, en le traduisant et en le commentant.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>272</v>
+      </c>
       <c r="J53" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bushido" title="Wikipedia"&gt;Le Bushido&lt;/a&gt;, la « voie du guerrier », désigne l’éthique des samouraïs, la classe militaire qui domine le Japon de l’époque de Kamakura (1185-1333) jusqu’au milieu du XIXe siècle. Ce n’est pas un code écrit unique, mais un ensemble de valeurs qui se forment peu à peu et ne sont mises en forme qu’à l’époque d’Edo (1603-1868), quand les guerriers, en temps de paix, deviennent administrateurs.&lt;/p&gt; &lt;p&gt;Le bushido mêle plusieurs sources : du confucianisme, il retient la loyauté envers le seigneur, la piété filiale et le sens du devoir ; du bouddhisme zen, la maîtrise de soi et le détachement face à la mort ; du shintō, le respect des ancêtres. Le guerrier doit être droit, courageux, bienveillant, poli, sincère, et préférer l’honneur à la vie : le suicide rituel, le &lt;em&gt;seppuku&lt;/em&gt;, permet d’effacer une faute ou d’échapper à la honte. Au XVIIe siècle, Yamaga Sokō définit le rôle moral du samouraï en temps de paix, et Miyamoto Musashi, dans le &lt;em&gt;Traité des cinq roues&lt;/em&gt;, fait de l’art du sabre une voie de perfection. Le &lt;a href="https://fr.wikipedia.org/wiki/Hagakure" title=" Wikipedia"&gt;&lt;em&gt;Hagakure&lt;/em&gt;&lt;/a&gt;, recueil des propos de Yamamoto Tsunetomo, affirme : « la voie du samouraï, je l’ai trouvée dans la mort ».&lt;/p&gt; &lt;p&gt;L’image moderne du bushido doit beaucoup à &lt;a href="https://fr.wikipedia.org/wiki/Inaz%C5%8D_Nitobe" title=" Wikipedia"&gt;Nitobe Inazō&lt;/a&gt;, dont le livre &lt;em&gt;Bushido, l’âme du Japon&lt;/em&gt; (1900), écrit en anglais, le présente comme une morale nationale comparable à la chevalerie. Exalté par le militarisme japonais jusqu’en 1945, il survit dans les arts martiaux et nourrit encore l’image que le monde se fait du Japon.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>283</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophie et mystique de l’islam</t>
+        </is>
+      </c>
+      <c r="Q53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falsafa;Soufisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="219" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oconfucianisme"  title=" Wikipedia"&gt;Le Néoconfucianisme&lt;/a&gt; est le renouveau du confucianisme qui s’épanouit en Chine sous la dynastie Song (960-1279). Face au bouddhisme et au taoïsme, qui offraient une métaphysique et une spiritualité plus riches, des lettrés relisent les Classiques pour donner à la morale confucéenne un fondement cosmique. Devenu orthodoxie d’État, il domine la Chine jusqu’en 1905, ainsi que la Corée, le Japon et le Vietnam.&lt;/p&gt; &lt;p&gt;Zhou Dunyi médite sur le « Faîte suprême » d’où naissent le yin et le yang ; les frères Cheng distinguent en toute chose le &lt;em&gt;li&lt;/em&gt;, principe ou ordre rationnel, et le &lt;em&gt;qi&lt;/em&gt;, souffle ou énergie matérielle. &lt;a href="https://fr.wikipedia.org/wiki/Zhu_Xi" title=" Wikipedia"&gt;Zhu Xi&lt;/a&gt; (1130-1200) fait la synthèse de cette « école du Principe » : chaque être porte en lui le principe universel, et la nature humaine est bonne, comme le disait Mencius, mais obscurcie par un souffle impur. On se perfectionne par l’« investigation des choses », l’étude et la méditation assise. Ses commentaires des Quatre Livres servent de base aux examens impériaux de 1313 à 1905. Contre lui, Lu Jiuyuan puis &lt;a href="https://fr.wikipedia.org/wiki/Wang_Yangming" title=" Wikipedia"&gt;Wang Yangming&lt;/a&gt; (1472-1529) fondent l’« école du Cœur » : le principe n’est pas à chercher dans les choses mais dans le cœur, et la connaissance est inséparable de l’action.&lt;/p&gt; &lt;p&gt;Critiqué au XVIIIe siècle par l’école des études critiques, le &lt;em&gt;kaozheng&lt;/em&gt;, puis par la modernisation, il inspire encore au XXe siècle le « nouveau confucianisme ». En Corée, Yi Hwang et Yi I en débattent au XVIe siècle, et au Japon la doctrine de Zhu Xi devient celle du shogunat Tokugawa.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
       <c r="J54" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>101</v>
@@ -4957,45 +4978,41 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+          <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bouddhisme Zen;Shintoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+          <t xml:space="preserve">Confucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_vietnamienne" title=" Wikipedia"&gt;La Philosophie vietnamienne&lt;/a&gt; se caractérise par le Tam Giáo, les « trois enseignements » : une alliance durable entre le confucianisme, le bouddhisme et le taoïsme, à laquelle s’ajoutent le culte des ancêtres et celui des génies protecteurs des villages. Un adage vietnamien dit que « les trois enseignements ont une même source ». Chacun a son domaine : le confucianisme règle la famille et l’État, le bouddhisme la vie spirituelle, le taoïsme la médecine, la divination et les rites du quotidien.&lt;/p&gt; &lt;p&gt;Le bouddhisme arrive très tôt, dès les premiers siècles de notre ère, par la mer et par la Chine. Après l’indépendance, en 939, les dynasties Lý et Trần le favorisent : le roi &lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;Trần Nhân Tông&lt;/a&gt;, vainqueur des invasions mongoles, abdique en 1293 pour se faire moine et fonde l’école zen de Trúc Lâm, la « Forêt de bambous », proprement vietnamienne. Le confucianisme s’impose ensuite comme doctrine de l’État : le Temple de la Littérature est fondé à Hanoï en 1070, et les concours mandarinaux recrutent les fonctionnaires jusqu’en 1919. Mais les lettrés formés aux classiques confucéens pratiquaient souvent le bouddhisme dans leur vie personnelle et se retiraient volontiers en ermites taoïstes : les trois voies se complètent plus qu’elles ne s’opposent. &lt;a href="https://fr.wikipedia.org/wiki/Nguy%E1%BB%85n_Tr%C3%A3i" title=" Wikipedia"&gt;Nguyễn Trãi&lt;/a&gt; au XVe siècle, Nguyễn Bỉnh Khiêm au XVIe ou Lê Quý Đôn au XVIIIe illustrent cette sagesse composite.&lt;/p&gt; &lt;p&gt;Au XXe siècle, ce syncrétisme inspire de nouvelles religions comme le caodaïsme, tandis que le marxisme devient la doctrine officielle. L’empreinte du Tam Giáo demeure dans les rites familiaux et la morale.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOWcduKGZYI</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Sự khác nhau của Nho giáo, Đạo giáo và Phật giáo - Tam Giáo Đồng Nguyên là gì?" par Radio Suy Ngẫm</t>
-        </is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bushido" title="Wikipedia"&gt;Le Bushido&lt;/a&gt;, la « voie du guerrier », désigne l’éthique des samouraïs, la classe militaire qui domine le Japon de l’époque de Kamakura (1185-1333) jusqu’au milieu du XIXe siècle. Ce n’est pas un code écrit unique, mais un ensemble de valeurs qui se forment peu à peu et ne sont mises en forme qu’à l’époque d’Edo (1603-1868), quand les guerriers, en temps de paix, deviennent administrateurs.&lt;/p&gt; &lt;p&gt;Le bushido mêle plusieurs sources : du confucianisme, il retient la loyauté envers le seigneur, la piété filiale et le sens du devoir ; du bouddhisme zen, la maîtrise de soi et le détachement face à la mort ; du shintō, le respect des ancêtres. Le guerrier doit être droit, courageux, bienveillant, poli, sincère, et préférer l’honneur à la vie : le suicide rituel, le &lt;em&gt;seppuku&lt;/em&gt;, permet d’effacer une faute ou d’échapper à la honte. Au XVIIe siècle, Yamaga Sokō définit le rôle moral du samouraï en temps de paix, et Miyamoto Musashi, dans le &lt;em&gt;Traité des cinq roues&lt;/em&gt;, fait de l’art du sabre une voie de perfection. Le &lt;a href="https://fr.wikipedia.org/wiki/Hagakure" title=" Wikipedia"&gt;&lt;em&gt;Hagakure&lt;/em&gt;&lt;/a&gt;, recueil des propos de Yamamoto Tsunetomo, affirme : « la voie du samouraï, je l’ai trouvée dans la mort ».&lt;/p&gt; &lt;p&gt;L’image moderne du bushido doit beaucoup à &lt;a href="https://fr.wikipedia.org/wiki/Inaz%C5%8D_Nitobe" title=" Wikipedia"&gt;Nitobe Inazō&lt;/a&gt;, dont le livre &lt;em&gt;Bushido, l’âme du Japon&lt;/em&gt; (1900), écrit en anglais, le présente comme une morale nationale comparable à la chevalerie. Exalté par le militarisme japonais jusqu’en 1945, il survit dans les arts martiaux et nourrit encore l’image que le monde se fait du Japon.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>22</v>
+        <v>285</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>101</v>
@@ -5007,179 +5024,184 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Japon : shintō et voies nationales</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme Zen;Shintoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="249" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_vietnamienne" title=" Wikipedia"&gt;La Philosophie vietnamienne&lt;/a&gt; se caractérise par le Tam Giáo, les « trois enseignements » : une alliance durable entre le confucianisme, le bouddhisme et le taoïsme, à laquelle s’ajoutent le culte des ancêtres et celui des génies protecteurs des villages. Un adage vietnamien dit que « les trois enseignements ont une même source ». Chacun a son domaine : le confucianisme règle la famille et l’État, le bouddhisme la vie spirituelle, le taoïsme la médecine, la divination et les rites du quotidien.&lt;/p&gt; &lt;p&gt;Le bouddhisme arrive très tôt, dès les premiers siècles de notre ère, par la mer et par la Chine. Après l’indépendance, en 939, les dynasties Lý et Trần le favorisent : le roi &lt;a href="https://fr.wikipedia.org/wiki/Tr%E1%BA%A7n_Nh%C3%A2n_T%C3%B4ng" title=" Wikipedia"&gt;Trần Nhân Tông&lt;/a&gt;, vainqueur des invasions mongoles, abdique en 1293 pour se faire moine et fonde l’école zen de Trúc Lâm, la « Forêt de bambous », proprement vietnamienne. Le confucianisme s’impose ensuite comme doctrine de l’État : le Temple de la Littérature est fondé à Hanoï en 1070, et les concours mandarinaux recrutent les fonctionnaires jusqu’en 1919. Mais les lettrés formés aux classiques confucéens pratiquaient souvent le bouddhisme dans leur vie personnelle et se retiraient volontiers en ermites taoïstes : les trois voies se complètent plus qu’elles ne s’opposent. &lt;a href="https://fr.wikipedia.org/wiki/Nguy%E1%BB%85n_Tr%C3%A3i" title=" Wikipedia"&gt;Nguyễn Trãi&lt;/a&gt; au XVe siècle, Nguyễn Bỉnh Khiêm au XVIe ou Lê Quý Đôn au XVIIIe illustrent cette sagesse composite.&lt;/p&gt; &lt;p&gt;Au XXe siècle, ce syncrétisme inspire de nouvelles religions comme le caodaïsme, tandis que le marxisme devient la doctrine officielle. L’empreinte du Tam Giáo demeure dans les rites familiaux et la morale.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOWcduKGZYI</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Sự khác nhau của Nho giáo, Đạo giáo và Phật giáo - Tam Giáo Đồng Nguyên là gì?" par Radio Suy Ngẫm</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Taoïsme et syncrétismes</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianisme;Bouddhisme Mahayana</t>
         </is>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
+    <row r="57" customFormat="false" ht="295.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="D56" s="28" t="s">
+      <c r="D57" s="28" t="s">
         <v>455</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t xml:space="preserve">EqO4cPcG4KY</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">"Le SIKHISME : La religion qui affirme que "DIEU N'A PAS DE RELIGION" (Le message de l'Unité)" par Mystica</t>
         </is>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="J57" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="K57" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t xml:space="preserve">Hindouismes de dévotion</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t xml:space="preserve">Bhakti;Soufisme</t>
         </is>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="366" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
-        <v>1650</v>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>291</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>292</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J57" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="366" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
         <v>1650</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J58" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pensées autochtones</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D59" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F58" s="1" t="s">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Kaozheng"  title=" Wikipedia (en)"&gt;Le Kaozheng&lt;/a&gt; (« recherche des preuves ») désigne le grand mouvement d’érudition qui domine la vie intellectuelle chinoise sous la dynastie Qing, du XVIIe au début du XIXe siècle. Né du traumatisme de la chute des Ming en 1644, il reproche au néoconfucianisme, et surtout à l’école de Wang Yangming, de s’être perdu dans des spéculations creuses sur l’esprit et le principe.&lt;/p&gt; &lt;p&gt;Contre ces « paroles vides », ses lettrés prônent une « étude solide » : retrouver le sens originel des classiques confucéens en les débarrassant des commentaires des Song, grâce à la philologie, à la phonétique ancienne, à l’épigraphie, à l’astronomie et aux mathématiques. Yan Ruoqu démontre ainsi, à la fin du XVIIe siècle, que les chapitres en « texte ancien » du &lt;em&gt;Classique des documents&lt;/em&gt; sont des faux bien plus tardifs. Chaque affirmation doit reposer sur des preuves vérifiables, selon une méthode que les historiens ont souvent comparée à la critique historique européenne.&lt;/p&gt; &lt;p&gt;Fondé par Gu Yanwu, le mouvement atteint son apogée au XVIIIe siècle avec Dai Zhen et les savants des écoles de Suzhou et de l’Anhui, portés par les grands chantiers éditoriaux de l’empereur Qianlong. Mais la critique des textes conduit aussi à une critique des idées : Dai Zhen s’en sert pour contester une morale du principe opposée aux désirs.&lt;/p&gt; &lt;p&gt;Au début du XXe siècle, Liang Qichao et Hu Shi virent dans le Kaozheng une « renaissance » chinoise et une préfiguration de l’esprit scientifique moderne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G59" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="J58" s="2" t="s">
+      <c r="J59" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="K58" s="2" t="s">
+      <c r="K59" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="L58" s="1" t="s">
+      <c r="L59" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Néoconfucianisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="14" t="n">
-        <v>1680</v>
-      </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>101</v>
@@ -5191,535 +5213,535 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoconfucianisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="293.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="14" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B60" s="14"/>
+      <c r="C60" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Japon : shintō et voies nationales</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t xml:space="preserve">Shintoïsme</t>
         </is>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="14" t="n">
+    <row r="61" customFormat="false" ht="395.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="14" t="n">
         <v>1720</v>
       </c>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14" t="n">
+      <c r="B61" s="14"/>
+      <c r="C61" s="14" t="n">
         <v>1720</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D61" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="E60" s="19" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fondamentalisme"   title=" Wikipedia"&gt;Le Fondamentalisme&lt;/a&gt; désigne, au sens large, une adhésion rigide et militante à ce qui est considéré comme les « fondements » absolus d’une religion ou d’une idéologie, généralement accompagnée d’une interprétation littérale des textes sacrés ou fondateurs et d’un refus des compromis avec la modernité. Historiquement, le terme naît dans le protestantisme américain du début du XXᵉ siècle, mais il est aujourd’hui utilisé pour décrire des phénomènes similaires dans d’autres religions (islam, judaïsme, hindouisme, etc.) et même dans des courants séculiers. &lt;/p&gt; &lt;p&gt; Le mot « fondamentalisme » apparaît en orient, principalement dans les mouvements salafistes, puis aux États-Unis entre 1910 et 1915, avec la publication d’une série de brochures intitulées The Fundamentals, qui définissent les « fondamentaux » du christianisme face au libéralisme théologique, à la critique historique de la Bible et aux sciences modernes (darwinisme, etc.). Ce mouvement protestant conservateur insiste sur l’inerrance littérale de la Bible, la naissance virginale de Jésus, sa résurrection corporelle, et l’expiation par sa mort sacrificielle. Il se veut une réaction contre la modernité et une défense d’un christianisme « pur », perçu comme menacé par les Églises libérales et la culture sécularisée. &lt;/p&gt; &lt;p&gt; Le fondamentalisme n’est pas seulement une affaire de croyance privée : il devient souvent un projet politique visant à transformer la société selon une vision religieuse totale. Cela peut se traduire par : la contestation des lois civiles au nom de la loi divine ; la mobilisation électorale ou militante de groupes religieux ; parfois le recours à la violence au nom de la défense de la foi. Les régimes démocratiques sont alors confrontés à la tension entre liberté religieuse et protection de l’ordre constitutionnel laïque ou pluraliste. &lt;/p&gt; 
  &lt;audio controls title="les religions ; le fondamentalisme chrétien par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.11.2005-ITEMA_24088968-2005C3035S0229-MEM_000021718_RF-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F61" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="G61" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Fondamentalisme par Le Savoir Partagé</t>
         </is>
       </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="23" t="s">
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="K60" s="2" t="s">
+      <c r="K61" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="M61" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t xml:space="preserve">Réveils de l’islam moderne</t>
         </is>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1">
+    <row r="62" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1">
         <v>1740</v>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1740</t>
         </is>
       </c>
-      <c r="D61" s="28" t="inlineStr">
+      <c r="D62" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Hassidisme</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hassidisme" title=" Wikipedia"&gt;Le hassidisme&lt;/a&gt;, de l’hébreu &lt;em&gt;hassid&lt;/em&gt;, « pieux », est un mouvement de renouveau mystique du judaïsme né au XVIIIe siècle en Podolie, dans l’actuelle Ukraine, alors polonaise, autour du Baal Shem Tov, le « Maître du Bon Nom ». Il paraît dans des communautés juives pauvres et éprouvées par les massacres et par la faillite du faux messie Sabbataï Tsevi, où le savoir talmudique est réservé à une élite.&lt;/p&gt; &lt;p&gt;Reprenant les idées de la Kabbale, le hassidisme les met à la portée de tous. Dieu est présent partout, jusque dans les choses les plus humbles : on peut donc le servir non seulement par l’étude, mais par la prière fervente, le chant, la danse et chaque geste du quotidien, accompli avec attention. La joie est une forme de piété, la tristesse un obstacle. La ferveur du cœur compte plus que l’érudition, et le plus simple des fidèles peut s’unir à Dieu. Au centre de chaque communauté se tient le &lt;a href="https://fr.wikipedia.org/wiki/Tsadik" title=" Wikipedia"&gt;&lt;em&gt;tsaddik&lt;/em&gt;&lt;/a&gt;, le « juste », maître spirituel qui guide ses disciples et intercède pour eux. Les maîtres hassidiques enseignent par des récits et des paraboles, comme ceux de &lt;a href="https://fr.wikipedia.org/wiki/Nahman_de_Bratslav" title=" Wikipedia"&gt;Nahman de Bratslav&lt;/a&gt;, arrière-petit-fils du Baal Shem Tov.&lt;/p&gt; &lt;p&gt;Combattu d’abord par les rabbins traditionnels, les &lt;a href="https://fr.wikipedia.org/wiki/Mitnagdim" title=" Wikipedia"&gt;Mitnagdim&lt;/a&gt;, le mouvement gagne une grande partie des Juifs d’Europe de l’Est. Presque anéanti par la Shoah, il renaît aux États-Unis et en Israël, où ses communautés, comme celle de Loubavitch, sont aujourd’hui très vivantes. Martin Buber a fait connaître ses récits en Occident ; Abraham Heschel et Elie Wiesel, issus de familles hassidiques, en ont transmis l’esprit.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ph9ZTOd6E54</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">"C'est quoi le hassidisme ?" par Hugo Brdl</t>
         </is>
       </c>
-      <c r="J61" s="1" t="inlineStr">
+      <c r="J62" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">mouvement mystique juif né en Ukraine autour du Baal Shem Tov : servir Dieu dans la joie, l’humilité et chaque geste du quotidien.</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Théologie et spiritualité;Éthique</t>
         </is>
       </c>
-      <c r="L61" s="1" t="inlineStr">
+      <c r="L62" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">BAAL SHEM TOV;Martin BUBER</t>
         </is>
       </c>
-      <c r="M61" s="1" t="inlineStr">
+      <c r="M62" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
-      <c r="N61"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
+      <c r="N62"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensée juive</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t xml:space="preserve">Kabbale</t>
         </is>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
+    <row r="63" customFormat="false" ht="240.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="n">
         <v>1750</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C63" s="1" t="n">
         <v>1750</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D63" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Silhak" title=" Wikipedia"&gt;Le Silhak&lt;/a&gt;, ou « savoir pratique », est un mouvement de réforme intellectuelle né en Corée au XVIIe siècle, sous la dynastie Joseon, et qui s’épanouit au XVIIIe. Il naît d’un pays ruiné par les invasions japonaises (1592-1598) puis mandchoues (1627 et 1636) : des lettrés reprochent alors au néoconfucianisme officiel de s’enfermer dans des querelles métaphysiques sur le principe et l’énergie, pendant que les paysans meurent de faim. Leur mot d’ordre, venu de Chine, est de « chercher la vérité dans les faits ».&lt;/p&gt; &lt;p&gt;Le premier grand nom en est Yu Hyeongwon (1622-1673), qui propose de redistribuer les terres à ceux qui les cultivent. Yi Ik (1681-1763) poursuit cette école du « bon gouvernement du monde » en critiquant l’esclavage, les privilèges héréditaires et le mépris du travail manuel. Une seconde branche, l’école des « études du Nord », autour de Pak Ji-won (1737-1805) et de Pak Je-ga, veut plutôt développer le commerce, les routes et les techniques, à l’exemple de la Chine des Qing. Le Silhak s’ouvre aussi aux sciences occidentales introduites en Chine par les jésuites : astronomie, cartographie, mathématiques.&lt;/p&gt; &lt;p&gt;Il culmine avec &lt;a href="https://fr.wikipedia.org/wiki/Jeong_Yak-yong" title=" Wikipedia"&gt;Jeong Yak-yong&lt;/a&gt; (1762-1836), dit Dasan, qui réunit les deux branches. Exilé dix-huit ans après la persécution des catholiques de 1801, il y écrit près de cinq cents volumes, dont un manuel pour bien administrer le peuple. Le calligraphe Kim Jeong-hui (1786-1856) en est l’un des derniers représentants. Marginalisé en son temps, le Silhak est aujourd’hui vu comme l’un des ferments de la modernité coréenne.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F63" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="J62" s="2" t="s">
+      <c r="J63" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianismes</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianisme coréen</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="9" t="n">
-        <v>1760</v>
-      </c>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martinisme" title=" Wikipedia"&gt;Le Martinisme&lt;/a&gt; est un courant ésotérique et mystique d’inspiration judéo-chrétienne, né en France au XVIIIe siècle dans les milieux de la franc-maçonnerie. Il doit son nom à deux hommes que l’on confond souvent : Martinès de Pasqually (vers 1727-1774), théurge à l’origine mal connue, et son disciple &lt;a href="https://fr.wikipedia.org/wiki/Louis-Claude_de_Saint-Martin" title=" Wikipedia"&gt;Louis-Claude de Saint-Martin&lt;/a&gt; (1743-1803), dit le « Philosophe inconnu ». Son thème central est la « réintégration » : le retour de l’être humain à la dignité spirituelle qu’il avait avant la chute.&lt;/p&gt; &lt;p&gt;Vers 1761, Martinès fonde l’ordre des Élus Coëns, dont les loges s’établissent à Bordeaux, Lyon et Paris. Dans son &lt;em&gt;Traité de la réintégration des êtres&lt;/em&gt;, il enseigne que l’homme, créé pour servir d’intermédiaire entre Dieu et le monde, a chuté par orgueil, comme Adam, et se trouve exilé dans la matière. Pour se racheter, il doit pratiquer l’ascèse, la prière et la théurgie, des rites destinés à entrer en contact avec les esprits bienfaisants. Saint-Martin, d’abord son secrétaire, délaisse ces rites pour une « voie intérieure », celle du cœur, nourrie par le mystique allemand Jacob Böhme. À Lyon, Jean-Baptiste Willermoz transmet leur doctrine au Rite écossais rectifié, une branche de la franc-maçonnerie qui existe toujours.&lt;/p&gt; &lt;p&gt;À la fin du XIXe siècle, l’occultiste Papus fonde un Ordre martiniste, et au XXe siècle Robert Ambelain fait renaître les Élus Coëns. On distingue depuis le « martinésisme », théurgique, et le « saint-martinisme », mystique. Joseph de Maistre, Balzac ou Franz von Baader ont lu Saint-Martin.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="H63" s="9"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M63" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianismes</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme coréen</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="249.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="n">
+        <v>1760</v>
+      </c>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Martinisme" title=" Wikipedia"&gt;Le Martinisme&lt;/a&gt; est un courant ésotérique et mystique d’inspiration judéo-chrétienne, né en France au XVIIIe siècle dans les milieux de la franc-maçonnerie. Il doit son nom à deux hommes que l’on confond souvent : Martinès de Pasqually (vers 1727-1774), théurge à l’origine mal connue, et son disciple &lt;a href="https://fr.wikipedia.org/wiki/Louis-Claude_de_Saint-Martin" title=" Wikipedia"&gt;Louis-Claude de Saint-Martin&lt;/a&gt; (1743-1803), dit le « Philosophe inconnu ». Son thème central est la « réintégration » : le retour de l’être humain à la dignité spirituelle qu’il avait avant la chute.&lt;/p&gt; &lt;p&gt;Vers 1761, Martinès fonde l’ordre des Élus Coëns, dont les loges s’établissent à Bordeaux, Lyon et Paris. Dans son &lt;em&gt;Traité de la réintégration des êtres&lt;/em&gt;, il enseigne que l’homme, créé pour servir d’intermédiaire entre Dieu et le monde, a chuté par orgueil, comme Adam, et se trouve exilé dans la matière. Pour se racheter, il doit pratiquer l’ascèse, la prière et la théurgie, des rites destinés à entrer en contact avec les esprits bienfaisants. Saint-Martin, d’abord son secrétaire, délaisse ces rites pour une « voie intérieure », celle du cœur, nourrie par le mystique allemand Jacob Böhme. À Lyon, Jean-Baptiste Willermoz transmet leur doctrine au Rite écossais rectifié, une branche de la franc-maçonnerie qui existe toujours.&lt;/p&gt; &lt;p&gt;À la fin du XIXe siècle, l’occultiste Papus fonde un Ordre martiniste, et au XXe siècle Robert Ambelain fait renaître les Élus Coëns. On distingue depuis le « martinésisme », théurgique, et le « saint-martinisme », mystique. Joseph de Maistre, Balzac ou Franz von Baader ont lu Saint-Martin.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M64" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ésotérismes et gnoses</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t xml:space="preserve">Kabbale</t>
         </is>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1">
+    <row r="65" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1">
         <v>1770</v>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1770</t>
         </is>
       </c>
-      <c r="D64" s="28" t="inlineStr">
+      <c r="D65" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Haskala</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Haskala" title=" Wikipedia"&gt;La Haskala&lt;/a&gt;, de l’hébreu &lt;em&gt;sekhel&lt;/em&gt;, « intelligence », est le mouvement des Lumières juives, né à Berlin dans les années 1770. Ses partisans, les &lt;em&gt;maskilim&lt;/em&gt;, veulent faire sortir les Juifs du ghetto culturel où les ont enfermés des siècles de discriminations, en les ouvrant aux sciences, à la philosophie et aux langues de l’Europe, sans qu’ils renoncent pour autant à leur foi.&lt;/p&gt; &lt;p&gt;Son inspirateur est Moses Mendelssohn, surnommé le « Socrate de Berlin », admiré de Kant et ami de &lt;a href="https://fr.wikipedia.org/wiki/Gotthold_Ephraim_Lessing" title=" Wikipedia"&gt;Lessing&lt;/a&gt;, qui fait de lui le modèle de son &lt;em&gt;Nathan le Sage&lt;/em&gt;. Il traduit la Torah en allemand, imprimée en caractères hébraïques, pour que les Juifs apprennent la langue du pays. Dans &lt;em&gt;Jérusalem&lt;/em&gt; (1783), il défend la liberté de conscience et la séparation de l’État et de la religion : le judaïsme, dit-il, n’impose pas de croyances, il prescrit des pratiques, et ses vérités sont celles de la raison, accessibles à tous les hommes. Autour de lui, le médecin Marcus Herz, élève de Kant, et David Friedländer, qui plaide pour l’émancipation civile des Juifs de Prusse, poursuivent son œuvre. La Haskala fonde des écoles modernes, une presse et fait renaître l’hébreu comme langue littéraire profane.&lt;/p&gt; &lt;p&gt;Au XIXe siècle, elle gagne la Galicie et l’Empire russe. Elle prépare le &lt;a href="https://fr.wikipedia.org/wiki/Juda%C3%AFsme_r%C3%A9form%C3%A9" title=" Wikipedia"&gt;judaïsme libéral&lt;/a&gt;, la &lt;a href="https://fr.wikipedia.org/wiki/Wissenschaft_des_Judentums" title=" Wikipedia"&gt;« science du judaïsme »&lt;/a&gt;, l’étude historique de sa tradition, et indirectement le sionisme. Ses adversaires lui ont reproché d’ouvrir la voie à l’assimilation ; ses héritiers y voient l’entrée du judaïsme dans la modernité.&lt;/p&gt;  &lt;audio controls title="le jadudaîsme de la modernité par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13094-09.11.2014-ITEMA_20688848-2014C21364E0044-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t xml:space="preserve">0a3g3J3rIQc</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">"The Haskalah (Essential Lectures in Jewish History)" par Henry Abramson</t>
         </is>
       </c>
-      <c r="J64" s="1" t="inlineStr">
+      <c r="J65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">les « Lumières juives » de Mendelssohn : unir la fidélité au judaïsme, la raison et la culture européenne.</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie politique;Théologie et spiritualité</t>
         </is>
       </c>
-      <c r="L64" s="1" t="inlineStr">
+      <c r="L65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Moses MENDELSSOHN</t>
         </is>
       </c>
-      <c r="M64" s="1" t="inlineStr">
+      <c r="M65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensée juive</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t xml:space="preserve">Lumières</t>
         </is>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14" t="n">
+    <row r="66" customFormat="false" ht="304.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="14" t="n">
         <v>1820</v>
       </c>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14" t="n">
+      <c r="B66" s="14"/>
+      <c r="C66" s="14" t="n">
         <v>1820</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="D66" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="E65" s="16" t="s">
+      <c r="E66" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="F66" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="G65" s="16" t="s">
+      <c r="G66" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="H65" s="14"/>
-      <c r="I65" s="16"/>
-      <c r="J65" s="2" t="s">
+      <c r="H66" s="14"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="K65" s="2" t="s">
+      <c r="K66" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M65" s="2" t="s">
+      <c r="M66" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t xml:space="preserve">Romantisme;Idéalisme allemand</t>
         </is>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
+    <row r="67" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="n">
         <v>1830</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D67" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="E67" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G67" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="J67" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="K67" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="L66" s="2" t="s">
+      <c r="L67" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="M66" s="2" t="s">
+      <c r="M67" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t xml:space="preserve">Réveils de l’islam moderne</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t xml:space="preserve">Lumières</t>
         </is>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
+    <row r="68" customFormat="false" ht="184.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="n">
         <v>1840</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D68" s="12" t="s">
         <v>338</v>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Th%C3%A9osophie" title=" Wikipedia"&gt;La Théosophie&lt;/a&gt; est un courant ésotérique et spirituel fondé par &lt;a href="https://fr.wikipedia.org/wiki/Helena_Blavatsky" title=" Wikipedia"&gt;Helena Blavatsky&lt;/a&gt; (1831-1891), née dans l’Empire russe, qui crée à New York en 1875, avec le colonel américain Henry Steel Olcott et William Quan Judge, la &lt;a href="https://fr.wikipedia.org/wiki/Soci%C3%A9t%C3%A9_th%C3%A9osophique" title=" Wikipedia"&gt;Société théosophique&lt;/a&gt;. Le mot, du grec &lt;em&gt;theos&lt;/em&gt;, « dieu », et &lt;em&gt;sophia&lt;/em&gt;, « sagesse », signifie « sagesse divine » : la Théosophie se veut la redécouverte d’une sagesse universelle et cachée, dont les religions, les sciences et les philosophies ne seraient que des expressions partielles.&lt;/p&gt; &lt;p&gt;La Société se donne trois buts : former le noyau d’une fraternité universelle de l’humanité, sans distinction de race, de croyance, de sexe ou de caste ; encourager l’étude comparée des religions, des philosophies et des sciences ; étudier les lois inexpliquées de la nature et les pouvoirs latents de l’homme. Blavatsky expose sa doctrine dans &lt;em&gt;Isis dévoilée&lt;/em&gt; (1877) et &lt;em&gt;La Doctrine secrète&lt;/em&gt; (1888), où elle mêle le bouddhisme, l’hindouisme, la Kabbale et le néoplatonisme : l’univers procède d’un principe unique, l’humanité traverse de longs cycles d’évolution et l’âme progresse par réincarnations successives selon la loi du karma. Elle dit tenir ces enseignements de « Maîtres » vivant au Tibet. Les fondateurs s’installent en Inde en 1879, et le siège est fixé à Adyar, près de Madras, en 1882.&lt;/p&gt; &lt;p&gt;Annie Besant, présidente à partir de 1907, présente le jeune Jiddu Krishnamurti comme un futur instructeur du monde, rôle qu’il refuse en 1929. Rudolf Steiner s’en sépare pour fonder l’anthroposophie. La Théosophie a marqué des artistes comme Kandinsky et Mondrian, le mouvement New Age et la diffusion en Occident de l’hindouisme et du bouddhisme.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F68" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G68" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="J67" s="2" t="s">
+      <c r="J68" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="K67" s="2" t="s">
+      <c r="K68" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M67" s="2" t="s">
+      <c r="M68" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ésotérismes et gnoses</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t xml:space="preserve">Hermétisme;Hindouisme</t>
         </is>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14" t="n">
+    <row r="69" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="14" t="n">
         <v>1845</v>
       </c>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14" t="n">
+      <c r="B69" s="14"/>
+      <c r="C69" s="14" t="n">
         <v>1845</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D69" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E69" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Occidentalisme"  title=" Wikipedia"&gt; L’Occidentalisme&lt;/a&gt; désigne un courant de pensée valorisant les caractéristiques, valeurs et modèles occidentaux, souvent en opposition à l'orientalisme qui essentialise l'Orient de manière négative. Historiquement, il émerge en Russie comme mouvement réformateur pro-occidental prônant la modernisation politique, économique et culturelle sur le modèle européen. Plus largement, il défend la supériorité perçue de l'Occident (libéralisme, progrès, hédonisme) et justifie parfois son hégémonie globale, avec un accent atlantiste et anticommuniste. &lt;/p&gt; &lt;p&gt; Dans le contexte contemporain, il promeut l'apologie des peuples européens, leur art de vivre et leur capacité d'amélioration, rejetant la culpabilisation postcoloniale. Il s'oppose aux idéologies abstraites au profit d'un matérialisme réaliste, ancré dans le corps et l'efficacité, tout en soutenant le libéralisme économique et politique. Certains le voient comme un internationalisme défendant l'hégémonie occidentale via le marché libre. &lt;/p&gt; &lt;p&gt; Critiqué comme ethnocentrique ou hégémonique, l'occidentalisme est accusé de présenter l'Occident comme un bloc monolithique inapte à critiquer ses propres failles, alimentant des fractures civilisationnelles. Dans les guerres culturelles, il oppose parfois islamisme ou orientalisme, renforçant des stéréotypes mutuels. Aujourd'hui, des courants identitaires le revendiquent comme optimisme pro-européen face au déclin perçu. &lt;/p&gt; 
  &lt;audio controls title="l’Occidentalisme par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10073-02.10.2022-ITEMA_23152872-2022C26163E0007-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F68" s="14" t="s">
+      <c r="F69" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="G68" s="16" t="s">
+      <c r="G69" s="16" t="s">
         <v>346</v>
-      </c>
-      <c r="H68" s="14"/>
-      <c r="I68" s="16"/>
-      <c r="J68" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
-        </is>
-      </c>
-      <c r="Q68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Idéalisme allemand</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14" t="n">
-        <v>1850</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="E69" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="F69" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>351</v>
       </c>
       <c r="H69" s="14"/>
       <c r="I69" s="16"/>
       <c r="J69" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Inde moderne</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hindouisme;Lumières</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>76</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
+        </is>
+      </c>
+      <c r="Q69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idéalisme allemand</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="329.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="n">
         <v>1850</v>
       </c>
@@ -5727,322 +5749,325 @@
       <c r="C70" s="14" t="n">
         <v>1850</v>
       </c>
-      <c r="D70" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="E70" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Intuitivisme"  title=" Wikipedia"&gt; L’Intuitivisme&lt;/a&gt;  est un courant philosophique russe qui privilégie la connaissance immédiate par l'intuition plutôt que par la médiation des sens ou des concepts. Il s'inscrit dans une tradition mystique orthodoxe où philosophie et religion fusionnent, rejetant le dualisme sujet-objet propre à la pensée occidentale. Ses figures emblématiques, comme Nicolas Lossky et Siméon Frank, en font un pilier de la philosophie russe spiritualiste. &lt;/p&gt; &lt;p&gt; Ce courant repose sur le principe d'une saisie directe de la réalité, où l'être se présente originairement dans la conscience sans voile ni intermédiaire. Lossky, par exemple, critique le kantisme en affirmant que les objets de la connaissance sont les "choses en soi" et non des phénomènes construits, grâce à une intuition qui transcende les sensations. Vrai et être y sont identiques, garantissant une vérité objective par la présence même de l'objet dans l'esprit. &lt;/p&gt; &lt;p&gt; Lossky distingue trois formes d'intuition : sensible (sur le monde et le corps), intellectuelle (sur les lois idéales) et mystique (sur Dieu et les sphères métalogiques). Cette triade permet une connaissance intégrale, incluant le religieux sans justification épistémologique séparée. Elle surmonte ainsi le "dédoublement artificiel" du monde opéré par les sensations, vues comme trans-subjectives et objectives. &lt;/p&gt; &lt;p&gt; L'intuitivisme s'oppose à l'épistémologie occidentale, valorisant l'ontologisme où l'être prime sur le savoir. Il prolonge les slavophiles et Soloviev, dans un climat de tension entre Logos mystique et ratio discursive. Sous l'ère soviétique, des penseurs comme B. N. Babynine l'adaptent à un réalisme matérialiste, via des recueils comme Les voies du réalisme. &lt;/p&gt; &lt;p&gt; Malgré la révolution bolchevique, l'intuitivisme persiste en émigration et influence la pensée religieuse russe, affirmant une union possible entre l'esprit humain et le divin sur Terre. Il incarne le refus russe d'une connaissance fragmentée, au profit d'une vision unitaire et vivante de la réalité. Ce courant reste une clé pour comprendre la spécificité philosophique russe. &lt;/p&gt; 
-</t>
-        </is>
+      <c r="D70" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>349</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="G70" s="16" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="H70" s="14"/>
       <c r="I70" s="16"/>
       <c r="J70" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hindouisme;Lumières</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="267" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="B71" s="14"/>
+      <c r="C71" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Intuitivisme"  title=" Wikipedia"&gt; L’Intuitivisme&lt;/a&gt;  est un courant philosophique russe qui privilégie la connaissance immédiate par l'intuition plutôt que par la médiation des sens ou des concepts. Il s'inscrit dans une tradition mystique orthodoxe où philosophie et religion fusionnent, rejetant le dualisme sujet-objet propre à la pensée occidentale. Ses figures emblématiques, comme Nicolas Lossky et Siméon Frank, en font un pilier de la philosophie russe spiritualiste. &lt;/p&gt; &lt;p&gt; Ce courant repose sur le principe d'une saisie directe de la réalité, où l'être se présente originairement dans la conscience sans voile ni intermédiaire. Lossky, par exemple, critique le kantisme en affirmant que les objets de la connaissance sont les "choses en soi" et non des phénomènes construits, grâce à une intuition qui transcende les sensations. Vrai et être y sont identiques, garantissant une vérité objective par la présence même de l'objet dans l'esprit. &lt;/p&gt; &lt;p&gt; Lossky distingue trois formes d'intuition : sensible (sur le monde et le corps), intellectuelle (sur les lois idéales) et mystique (sur Dieu et les sphères métalogiques). Cette triade permet une connaissance intégrale, incluant le religieux sans justification épistémologique séparée. Elle surmonte ainsi le "dédoublement artificiel" du monde opéré par les sensations, vues comme trans-subjectives et objectives. &lt;/p&gt; &lt;p&gt; L'intuitivisme s'oppose à l'épistémologie occidentale, valorisant l'ontologisme où l'être prime sur le savoir. Il prolonge les slavophiles et Soloviev, dans un climat de tension entre Logos mystique et ratio discursive. Sous l'ère soviétique, des penseurs comme B. N. Babynine l'adaptent à un réalisme matérialiste, via des recueils comme Les voies du réalisme. &lt;/p&gt; &lt;p&gt; Malgré la révolution bolchevique, l'intuitivisme persiste en émigration et influence la pensée religieuse russe, affirmant une union possible entre l'esprit humain et le divin sur Terre. Il incarne le refus russe d'une connaissance fragmentée, au profit d'une vision unitaire et vivante de la réalité. Ce courant reste une clé pour comprendre la spécificité philosophique russe. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="H71" s="14"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="K70" s="2" t="s">
+      <c r="K71" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="M70" s="2" t="s">
+      <c r="M71" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie religieuse russe</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t xml:space="preserve">Slavophilisme</t>
         </is>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
+    <row r="72" customFormat="false" ht="185.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="n">
         <v>1860</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C72" s="1" t="n">
         <v>1860</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D72" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Donghak" title=" Wikipedia"&gt;Le Donghak&lt;/a&gt;, ou « savoir de l’Orient », est un mouvement religieux et social fondé en Corée en 1860 par Choe Je-u (1824-1864), un lettré déclassé. Il naît dans une société Joseon minée par la corruption, les épidémies et la misère paysanne, et inquiète devant l’Occident : la Chine vient d’être humiliée par la seconde guerre de l’opium, et le catholicisme, appelé « savoir de l’Occident » (&lt;em&gt;seohak&lt;/em&gt;), progresse malgré les persécutions. Choe Je-u dit avoir reçu une révélation du « Seigneur du Ciel » et veut opposer au savoir étranger une voie coréenne.&lt;/p&gt; &lt;p&gt;Sa doctrine mêle le confucianisme, le bouddhisme, le taoïsme et le chamanisme coréen. Son idée centrale est que chaque être humain « porte en lui le Ciel » (&lt;em&gt;si cheonju&lt;/em&gt;) : il faut donc « servir l’homme comme le Ciel », enseigne son successeur Choe Si-hyeong, et le mouvement finira par dire que « l’homme est le Ciel » (&lt;em&gt;in nae cheon&lt;/em&gt;). Il en découle une égalité radicale entre les nobles et les serviteurs, les hommes et les femmes, les riches et les pauvres. Les fidèles récitent une formule sacrée de vingt et un caractères et attendent l’« ouverture » d’un monde nouveau.&lt;/p&gt; &lt;p&gt;Choe Je-u est exécuté en 1864 pour hérésie, mais le mouvement gagne les campagnes et inspire en 1894 la &lt;a href="https://fr.wikipedia.org/wiki/R%C3%A9volution_paysanne_Donghak" title=" Wikipedia"&gt;révolution paysanne du Donghak&lt;/a&gt;, menée par Jeon Bong-jun ; l’arrivée de troupes chinoises et japonaises pour l’écraser déclenche la guerre sino-japonaise. Rebaptisé Cheondogyo, « religion de la Voie céleste », en 1905, il joue un grand rôle dans le mouvement d’indépendance du 1er mars 1919.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="G71" s="26" t="s">
+      <c r="G72" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Taoïsme et syncrétismes</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confucianisme coréen;Taoïsme</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>1865</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_(art)"  title=" Wikipedia"&gt;Le Symbolisme&lt;/a&gt; est un courant littéraire, artistique et philosophique né en France dans les années 1880 et qui s’épanouit en Russie au tournant du XXe siècle. Il prend pour modèle le sonnet « Correspondances » de &lt;a href="https://fr.wikipedia.org/wiki/Charles_Baudelaire" title=" Wikipedia"&gt;Baudelaire&lt;/a&gt;, où la nature est une « forêt de symboles » : derrière le monde visible se cache une réalité spirituelle que le poète peut faire pressentir. Le manifeste de Jean Moréas paraît en 1886 ; Mallarmé, Verlaine, et en peinture Gustave Moreau ou Odilon Redon, incarnent le mouvement.&lt;/p&gt; &lt;p&gt;En Russie, il naît dans les années 1890 avec Dmitri Merejkovski, Valéri Brioussov et Constantin Balmont, puis prend une dimension métaphysique et religieuse avec une seconde génération, nourrie de la philosophie de &lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir Soloviev&lt;/a&gt; et de sa figure de la Sophia, la Sagesse divine. Pour Viatcheslav Ivanov, dont l’appartement de Saint-Pétersbourg, la « Tour », est le grand salon de l’époque, l’art doit aller « du réel au plus réel ». Pour Andreï Biély, le symbole unit la connaissance et la création, et le symbolisme devient une véritable vision du monde. Alexandre Blok chante la « Belle Dame », figure mystique de la Sophia, avant d’écrire en 1918 &lt;em&gt;Les Douze&lt;/em&gt;, poème de la révolution. Ces poètes-philosophes conçoivent l’art comme une « théurgie », une action capable de transformer le monde et de préparer sa transfiguration. Le symbolisme russe mêle la mystique orthodoxe, l’idéalisme allemand et Nietzsche.&lt;/p&gt; &lt;p&gt;Vers 1910, il entre en crise et laisse place à l’acméisme et au futurisme. Il a profondément marqué la philosophie religieuse russe de l’âge d’argent.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M72" s="2" t="s">
+      <c r="L72" s="1"/>
+      <c r="M72" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taoïsme et syncrétismes</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confucianisme coréen;Taoïsme</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="n">
+        <v>1865</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_(art)"  title=" Wikipedia"&gt;Le Symbolisme&lt;/a&gt; est un courant littéraire, artistique et philosophique né en France dans les années 1880 et qui s’épanouit en Russie au tournant du XXe siècle. Il prend pour modèle le sonnet « Correspondances » de &lt;a href="https://fr.wikipedia.org/wiki/Charles_Baudelaire" title=" Wikipedia"&gt;Baudelaire&lt;/a&gt;, où la nature est une « forêt de symboles » : derrière le monde visible se cache une réalité spirituelle que le poète peut faire pressentir. Le manifeste de Jean Moréas paraît en 1886 ; Mallarmé, Verlaine, et en peinture Gustave Moreau ou Odilon Redon, incarnent le mouvement.&lt;/p&gt; &lt;p&gt;En Russie, il naît dans les années 1890 avec Dmitri Merejkovski, Valéri Brioussov et Constantin Balmont, puis prend une dimension métaphysique et religieuse avec une seconde génération, nourrie de la philosophie de &lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir Soloviev&lt;/a&gt; et de sa figure de la Sophia, la Sagesse divine. Pour Viatcheslav Ivanov, dont l’appartement de Saint-Pétersbourg, la « Tour », est le grand salon de l’époque, l’art doit aller « du réel au plus réel ». Pour Andreï Biély, le symbole unit la connaissance et la création, et le symbolisme devient une véritable vision du monde. Alexandre Blok chante la « Belle Dame », figure mystique de la Sophia, avant d’écrire en 1918 &lt;em&gt;Les Douze&lt;/em&gt;, poème de la révolution. Ces poètes-philosophes conçoivent l’art comme une « théurgie », une action capable de transformer le monde et de préparer sa transfiguration. Le symbolisme russe mêle la mystique orthodoxe, l’idéalisme allemand et Nietzsche.&lt;/p&gt; &lt;p&gt;Vers 1910, il entre en crise et laisse place à l’acméisme et au futurisme. Il a profondément marqué la philosophie religieuse russe de l’âge d’argent.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M73" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie religieuse russe</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t xml:space="preserve">Sophiologie</t>
         </is>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="9" t="n">
+    <row r="74" customFormat="false" ht="169.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="9" t="n">
         <v>1870</v>
       </c>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9" t="n">
+      <c r="B74" s="9"/>
+      <c r="C74" s="9" t="n">
         <v>1870</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D74" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="E73" s="27" t="s">
+      <c r="E74" s="27" t="s">
         <v>370</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F74" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="G74" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="H73" s="9"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="2" t="s">
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="K73" s="2" t="s">
+      <c r="K74" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M73" s="2" t="s">
+      <c r="M74" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t xml:space="preserve">Réveils de l’islam moderne</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nahda</t>
         </is>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="14" t="n">
+    <row r="75" customFormat="false" ht="138" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="14" t="n">
         <v>1878</v>
       </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14" t="n">
+      <c r="B75" s="14"/>
+      <c r="C75" s="14" t="n">
         <v>1878</v>
       </c>
-      <c r="D74" s="15" t="s">
+      <c r="D75" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="E74" s="16" t="s">
+      <c r="E75" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="F74" s="14" t="s">
+      <c r="F75" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="G74" s="16" t="s">
+      <c r="G75" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="H74" s="14"/>
-      <c r="I74" s="16"/>
-      <c r="J74" s="2" t="s">
+      <c r="H75" s="14"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="K74" s="2" t="s">
+      <c r="K75" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="M74" s="2" t="s">
+      <c r="M75" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie religieuse russe</t>
         </is>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
+    <row r="76" customFormat="false" ht="155.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="n">
         <v>1900</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C76" s="1" t="n">
         <v>1900</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D76" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="J75" s="2" t="s">
+      <c r="J76" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O75" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P75" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
-        </is>
-      </c>
-      <c r="Q75" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anticolonialisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>1905</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>108</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Inde moderne</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jaïnisme;Néo-védanta</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme et décolonisation</t>
+        </is>
+      </c>
+      <c r="Q76" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anticolonialisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="160.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
         <v>1905</v>
       </c>
@@ -6050,790 +6075,778 @@
         <v>1905</v>
       </c>
       <c r="D77" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jaïnisme;Néo-védanta</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="131.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="E77" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Empiriomonisme"  title="Wikipedia"&gt;L’Empiriomonisme&lt;/a&gt; est une doctrine philosophique développée par Alexandre Bogdanov qui cherche à penser la réalité comme une expérience unique et organisée, en refusant le dualisme strict entre matière et esprit. Bogdanov veut réunir l’empirisme et le monisme. Autrement dit, il affirme que toute connaissance vient de l’expérience, mais que cette expérience forme un tout cohérent, sans séparation fondamentale entre le monde physique et le monde psychique.&lt;/p&gt; &lt;p&gt; Les sources résument souvent sa pensée en trois grands points : le réalisme naïf, selon lequel nous percevons les choses telles qu’elles sont ; la primauté de la nature, qui signifie que les formes simples de la réalité sont premières ; le caractère secondaire de l’esprit, vu comme un produit de formes plus complexes d’organisation de l’expérience. &lt;/p&gt; &lt;p&gt; Dans cette perspective, la connaissance n’est pas une copie passive du monde : elle est une manière d’ordonner l’expérience. Bogdanov insiste sur des notions comme l’expérience et l’organisation, qui annoncent aussi sa future théorie de la tектologie, une science générale de l’organisation. &lt;/p&gt; &lt;p&gt; Il a été vivement critiqué par Lénine et Plekhanov, qui l’accusaient de dérive idéaliste et de révision du marxisme. Aujourd’hui, on le lit surtout comme un moment important des débats philosophiques du marxisme russe. &lt;/p&gt; 
+      <c r="E78" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Empiriomonisme"  title="Wikipedia"&gt;L’Empiriomonisme&lt;/a&gt; est une doctrine philosophique développée par Alexandre Bogdanov qui cherche à penser la réalité comme une expérience unique et organisée, en refusant le dualisme strict entre matière et esprit. Bogdanov veut réunir l’empirisme et le monisme. Autrement dit, il affirme que toute connaissance vient de l’expérience, mais que cette expérience forme un tout cohérent, sans séparation fondamentale entre le monde physique et le monde psychique. Bogdanov expose cette doctrine dans les trois volumes d’&lt;em&gt;Empiriomonisme&lt;/em&gt; (1904-1906), en s’inspirant d’Ernst Mach et de Richard Avenarius. Lénine lui répond en 1909 dans &lt;em&gt;Matérialisme et empiriocriticisme&lt;/em&gt;.&lt;/p&gt; &lt;p&gt; Les sources résument souvent sa pensée en trois grands points : le réalisme naïf, selon lequel nous percevons les choses telles qu’elles sont ; la primauté de la nature, qui signifie que les formes simples de la réalité sont premières ; le caractère secondaire de l’esprit, vu comme un produit de formes plus complexes d’organisation de l’expérience. &lt;/p&gt; &lt;p&gt; Dans cette perspective, la connaissance n’est pas une copie passive du monde : elle est une manière d’ordonner l’expérience. Bogdanov insiste sur des notions comme l’expérience et l’organisation, qui annoncent aussi sa future théorie de la tectologie, une science générale de l’organisation. &lt;/p&gt; &lt;p&gt; Il a été vivement critiqué par Lénine et Plekhanov, qui l’accusaient de dérive idéaliste et de révision du marxisme. Aujourd’hui, on le lit surtout comme un moment important des débats philosophiques du marxisme russe. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F78" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G78" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="J77" s="21" t="s">
+      <c r="J78" s="21" t="s">
         <v>394</v>
       </c>
-      <c r="K77" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M77" s="2" t="s">
+      <c r="M78" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
         <is>
           <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t xml:space="preserve">Marxisme</t>
         </is>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
+    <row r="79" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="n">
         <v>1911</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D79" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/%C3%89cole_de_Ky%C5%8Dto"  title=" Wikipedia"&gt;L’école de Kyōto&lt;/a&gt; désigne le premier grand courant de philosophie moderne né au Japon, autour de &lt;a href="https://fr.wikipedia.org/wiki/Kitar%C5%8D_Nishida" title=" Wikipedia"&gt;Kitarō Nishida&lt;/a&gt; (1870-1945) et de ses successeurs à l’université impériale de Kyōto. On en fixe souvent le point de départ à 1911, date de la &lt;em&gt;Recherche sur le bien&lt;/em&gt;, où Nishida part de l’« expérience pure », antérieure à la séparation du sujet et de l’objet.&lt;/p&gt; &lt;p&gt;Ses penseurs, formés à la philosophie allemande, de Kant et Hegel à Husserl et Heidegger, veulent exprimer dans le langage de la philosophie occidentale l’expérience spirituelle de l’Asie, en particulier celle du bouddhisme zen et de la Terre pure. Au centre de leur réflexion se trouve la notion de « néant absolu » : non pas un simple manque, mais le fond ouvert d’où tout surgit, que Nishida pense comme le « lieu » (&lt;em&gt;basho&lt;/em&gt;) de toute réalité. Tanabe Hajime en tire une « philosophie de la repentance », et &lt;a href="https://fr.wikipedia.org/wiki/Keiji_Nishitani" title=" Wikipedia"&gt;Nishitani Keiji&lt;/a&gt; affronte le nihilisme européen : on ne le surmonte qu’en le traversant jusqu’à la vacuité. Watsuji Tetsurō et Kuki Shūzō, proches du groupe, l’ouvrent à l’éthique et à l’esthétique.&lt;/p&gt; &lt;p&gt;Plusieurs de ses membres furent compromis dans la justification idéologique de la guerre du Pacifique, ce qui a longtemps pesé sur sa réception. Depuis les années 1980, l’école est étudiée dans le monde entier comme le lieu d’un dialogue majeur entre la philosophie occidentale et les traditions spirituelles d’Asie. Ueda Shizuteru, mort en 2019, en a prolongé la pensée jusqu’à notre siècle.&lt;/p&gt;  &lt;audio controls title="Philosophie japonaise: l’école de Kyôto par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-15.11.2013-ITEMA_20549374-2013C12410E0320-NET_FC_EE7092B3-7D80-40AA-947D-AFAD338FBA01-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F79" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G79" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="J78" s="2" t="s">
+      <c r="J79" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="K79" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="L79" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="M78" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t xml:space="preserve">Japon : shintō et voies nationales</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t xml:space="preserve">Bouddhisme Zen;Idéalisme allemand</t>
         </is>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
-        <v>1920</v>
-      </c>
-      <c r="C79" s="1" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>403</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">imzO0eNziD4</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"B.R. Ambedkar: The Life of the Mind &amp; a Life in Politics" par Library of Congress</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L’Inde moderne</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="173.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
         <v>1920</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imzO0eNziD4</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"B.R. Ambedkar: The Life of the Mind &amp; a Life in Politics" par Library of Congress</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L’Inde moderne</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouddhisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="181.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D81" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Logique_paracoh%C3%A9rente"  title=" Wikipedia"&gt;La Logique paraconsistante&lt;/a&gt; désigne les systèmes logiques qui peuvent contenir des contradictions sans s’effondrer. En logique classique, en effet, une seule contradiction suffit à tout démontrer : de « A et non-A », on peut déduire n’importe quelle proposition. C’est le &lt;a href="https://fr.wikipedia.org/wiki/Principe_d%27explosion" title=" Wikipedia"&gt;principe d’explosion&lt;/a&gt;, connu depuis le Moyen Âge sous la formule « du contradictoire suit n’importe quoi ». Une logique paraconsistante bloque cette explosion : une contradiction locale y reste locale, sans contaminer tout le reste.&lt;/p&gt; &lt;p&gt;L’idée apparaît en 1910, à Kazan, chez le philosophe russe Nikolaï Vassiliev (1880-1940). Il imagine une « logique imaginaire » où la loi de non-contradiction n’est plus un axiome nécessaire, de même que les géométries non euclidiennes, nées à Kazan avec Lobatchevski, avaient abandonné le postulat des parallèles. La même année, le Polonais Jan Łukasiewicz critique le principe de non-contradiction d’Aristote. Son élève Stanisław Jaśkowski construit en 1948 le premier système formel paraconsistant, et le Brésilien Newton da Costa développe à partir de 1963 toute une famille de ces logiques. Le mot « paraconsistant » est forgé en 1976 par le philosophe péruvien Francisco Miró Quesada. Certains vont plus loin, comme l’Australien &lt;a href="https://fr.wikipedia.org/wiki/Graham_Priest" title=" Wikipedia"&gt;Graham Priest&lt;/a&gt; : selon son « dialéthéisme », certaines contradictions sont vraies, par exemple le paradoxe du menteur, « cette phrase est fausse ».&lt;/p&gt; &lt;p&gt;Ces logiques servent en informatique, pour raisonner avec des bases de données incohérentes, en droit, face à des normes contradictoires, et en philosophie des sciences, quand des théories en conflit doivent coexister.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F81" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G81" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="J80" s="2" t="s">
+      <c r="J81" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="K80" s="2" t="s">
+      <c r="K81" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="M80" s="2" t="s">
+      <c r="M81" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie analytique et pragmatisme</t>
         </is>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
+    <row r="82" customFormat="false" ht="226.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="n">
         <v>1921</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D82" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nouveau_confucianisme"  title=" Wikipedia"&gt;Le nouveau confucianisme&lt;/a&gt; est un courant philosophique chinois du XXe siècle qui veut renouveler la tradition confucéenne pour l’accorder à la modernité. Il naît en réaction au mouvement du 4 Mai 1919 et à la Nouvelle Culture, qui rejetaient le confucianisme comme responsable du retard de la Chine et en appelaient à « Monsieur Science » et à « Monsieur Démocratie ». Ses penseurs veulent montrer qu’un confucianisme repensé peut accueillir la science et la démocratie sans perdre sa sagesse morale.&lt;/p&gt; &lt;p&gt;Le point de départ est l’ouvrage de &lt;a href="https://fr.wikipedia.org/wiki/Liang_Shuming" title=" Wikipedia"&gt;Liang Shuming&lt;/a&gt;, &lt;em&gt;Les Cultures d’Orient et d’Occident et leurs philosophies&lt;/em&gt; (1921), qui compare les voies de l’Occident, de la Chine et de l’Inde. &lt;a href="https://fr.wikipedia.org/wiki/Xiong_Shili" title=" Wikipedia"&gt;Xiong Shili&lt;/a&gt; donne au courant une métaphysique dans son &lt;em&gt;Nouveau traité de la conscience seule&lt;/em&gt; (1932) : s’inspirant du &lt;em&gt;Livre des mutations&lt;/em&gt;, il critique le bouddhisme pour qui le monde est illusion, et pense la réalité comme un mouvement créateur continu. Feng Youlan, dans son &lt;em&gt;Nouvel enseignement du principe&lt;/em&gt; (1939), relit Zhu Xi à l’aide de la logique moderne.&lt;/p&gt; &lt;p&gt;Après 1949, le courant se poursuit surtout à Hong Kong et à Taïwan. En 1958, Mou Zongsan, Tang Junyi, Xu Fuguan et Zhang Junmai publient un manifeste adressé au monde sur la culture chinoise. Mou Zongsan, traducteur des trois &lt;em&gt;Critiques&lt;/em&gt; de Kant, dialogue avec lui pour fonder une « métaphysique morale ». Une troisième génération, avec &lt;a href="https://fr.wikipedia.org/wiki/Tu_Weiming" title=" Wikipedia"&gt;Tu Weiming&lt;/a&gt; ou Liu Shu-hsien, a porté ce courant dans les universités américaines ; il connaît depuis les années 1980 un important renouveau en Chine continentale.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G82" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="J82" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="K81" s="2" t="s">
+      <c r="K82" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="L81" s="1" t="s">
+      <c r="L82" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="M81" s="2" t="s">
+      <c r="M82" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t xml:space="preserve">Confucianismes</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t xml:space="preserve">Néoconfucianisme</t>
         </is>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1">
+    <row r="83" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1">
         <v>1921</v>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1921</t>
         </is>
       </c>
-      <c r="D82" s="28" t="inlineStr">
+      <c r="D83" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Eurasisme</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;L’eurasisme&lt;/a&gt; est un courant de pensée né en 1921 dans l’émigration russe, après la révolution bolchevique, avec le recueil &lt;em&gt;L’Exode vers l’Orient&lt;/em&gt;, publié à Sofia par un petit groupe de jeunes intellectuels exilés : le linguiste &lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Sergue%C3%AFevitch_Troubetsko%C3%AF" title=" Wikipedia"&gt;Nikolaï Troubetskoï&lt;/a&gt;, le géographe Piotr Savitski, le musicologue Pierre Souvtchinski et le théologien Georges Florovsky.&lt;/p&gt; &lt;p&gt;Leur thèse est que la Russie n’est ni une partie de l’Europe ni une partie de l’Asie, mais un monde à part, l’« Eurasie », dont la grande plaine, des Carpates au Pacifique, a façonné l’unité des peuples slaves, turcs et finno-ougriens. Contre les occidentalistes, ils refusent l’idée d’une civilisation européenne universelle : dans &lt;em&gt;L’Europe et l’humanité&lt;/em&gt; (1920), Troubetskoï y voit l’égoïsme d’une culture « romano-germanique » qui s’impose aux autres. Contre les slavophiles, ils réhabilitent l’héritage asiatique de la Russie, et jusqu’à l’empire de Gengis Khan, qui aurait le premier unifié cet espace. Ils rêvent d’un État fondé sur une idéologie commune et sur l’orthodoxie, distinct à la fois de la démocratie libérale et du communisme. Florovsky s’en éloigne vite et critique en 1928 ce qu’il appelle une « vérité des questions » devenue une « erreur des réponses ». Le mouvement se divise à la fin des années 1920, une partie se rapprochant du régime soviétique.&lt;/p&gt; &lt;p&gt;Prolongé en URSS par l’historien &lt;a href="https://fr.wikipedia.org/wiki/Lev_Goumilev" title=" Wikipedia"&gt;Lev Goumilev&lt;/a&gt;, l’eurasisme renaît après 1991 sous la forme d’un « néo-eurasisme » porté par &lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Douguine" title=" Wikipedia"&gt;Alexandre Douguine&lt;/a&gt;, idéologue d’extrême droite, et influence aujourd’hui la géopolitique nationaliste et impériale de la Russie.&lt;/p&gt;  &lt;audio controls title="De l'idée à l'action : 4 doctrines géopolitiques . Eurasie : la Russie au centre du jeu par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18720-25.03.2021-ITEMA_22614994-2021C16756S0084.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t xml:space="preserve">QodQ2ORmtKg</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t xml:space="preserve">"L'EURASISME : le projet géopolitique de la Russie ? - C Ce soir du 24 février 2022" par C Ce Soir - France Télévisions</t>
         </is>
       </c>
-      <c r="J82" s="1" t="inlineStr">
+      <c r="J83" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">doctrine née dans l’émigration russe : la Russie ne serait ni l’Europe ni l’Asie, mais une civilisation à part, l’« Eurasie ».</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Philosophie politique</t>
         </is>
       </c>
-      <c r="L82" s="1" t="inlineStr">
+      <c r="L83" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Nikolaï TROUBETSKOÏ;Georges FLOROVSKY</t>
         </is>
       </c>
-      <c r="M82" s="1" t="inlineStr">
+      <c r="M83" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">russe</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t xml:space="preserve">asie-est</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t xml:space="preserve">Slavophiles, occidentalistes et nihilistes</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t xml:space="preserve">Slavophilisme</t>
         </is>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="14" t="n">
+    <row r="84" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="14" t="n">
         <v>1935</v>
       </c>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14" t="s">
+      <c r="B84" s="14"/>
+      <c r="C84" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="D83" s="15" t="s">
+      <c r="D84" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="E83" s="16" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9gritude"  title=" Wikipedia"&gt;La Négritude&lt;/a&gt; est un mouvement littéraire, culturel et politique né à Paris dans les années 1930 parmi les étudiants noirs venus d’Afrique et des Antilles. Le mot apparaît sous la plume du Martiniquais &lt;a href="https://fr.wikipedia.org/wiki/Aim%C3%A9_C%C3%A9saire" title=" Wikipedia"&gt;Aimé Césaire&lt;/a&gt; en 1935, dans la revue &lt;em&gt;L’Étudiant noir&lt;/em&gt;, puis dans son &lt;em&gt;Cahier d’un retour au pays natal&lt;/em&gt; (1939). Il retourne fièrement une insulte coloniale pour en faire l’affirmation d’une identité.&lt;/p&gt; &lt;p&gt;Avec le Sénégalais &lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9opold_S%C3%A9dar_Senghor" title=" Wikipedia"&gt;Léopold Sédar Senghor&lt;/a&gt; et le Guyanais &lt;a href="https://fr.wikipedia.org/wiki/L%C3%A9on-Gontran_Damas" title=" Wikipedia"&gt;Léon-Gontran Damas&lt;/a&gt;, Césaire refuse l’assimilation que propose la France coloniale, qui demande aux colonisés de renoncer à leur culture pour adopter celle de l’Europe. Ils revendiquent l’héritage des civilisations africaines, leurs arts, leurs langues et leurs valeurs. Pour Senghor, la négritude est « l’ensemble des valeurs culturelles du monde noir » ; il oppose parfois une raison africaine intuitive à la raison européenne analytique. Pour Césaire, elle est d’abord une révolte contre l’oppression : son &lt;em&gt;Discours sur le colonialisme&lt;/em&gt; (1950) dénonce la barbarie de l’Europe coloniale. En 1948, l’&lt;em&gt;Anthologie&lt;/em&gt; de Senghor, préfacée par Sartre sous le titre « Orphée noir », donne au mouvement un retentissement mondial.&lt;/p&gt; &lt;p&gt;Senghor devient en 1960 le premier président du Sénégal. La négritude a été critiquée pour son essentialisme, par Frantz Fanon, par Wole Soyinka (« le tigre ne proclame pas sa tigritude ») ou par les auteurs de la créolité, mais elle a ouvert la voie aux pensées postcoloniales.&lt;/p&gt;  &lt;audio controls title="Bonjour et adieu à la Négritude par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/13915-19.06.2022-ITEMA_23063672-2022C3372E0281-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F83" s="14" t="s">
+      <c r="F84" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="G83" s="16" t="s">
+      <c r="G84" s="16" t="s">
         <v>426</v>
       </c>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="2" t="s">
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="K83" s="2" t="s">
+      <c r="K84" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M83" s="2" t="s">
+      <c r="M84" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t xml:space="preserve">Pan-africanisme</t>
         </is>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
+    <row r="85" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="n">
         <v>1940</v>
       </c>
-      <c r="C84" s="1" t="n">
+      <c r="C85" s="1" t="n">
         <v>1940</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D85" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="E84" s="23" t="inlineStr">
+      <c r="E85" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Doctrine_Jdanov"  title=" Wikipedia"&gt;Le Jdanovisme&lt;/a&gt; est une doctrine idéologique et culturelle russe sous l’influence d’Andreï Jdanov, plutôt qu’une philosophie au sens classique. Il repose sur une vision très normative de l’art : la création doit servir le Parti, défendre le réalisme socialiste et rejeter les formes jugées “formalistes” ou trop éloignées du peuple. En ce sens, il propose bien une manière cohérente de penser le rôle de l’art dans la société. &lt;/p&gt; &lt;p&gt; On le décrit plus souvent comme un courant de pensée politico-culturel ou une ligne doctrinale, parce qu’il ne cherche pas d’abord à analyser librement le monde, mais à encadrer et orienter les productions intellectuelles et artistiques. Il s’agit donc moins d’une théorie ouverte que d’un ensemble de règles imposées. &lt;/p&gt; &lt;p&gt; Son principe central est le réalisme socialiste : l’art doit représenter la réalité de façon compréhensible, valoriser le peuple, le travail et le régime soviétique, et rejeter les formes jugées trop abstraites, expérimentales ou “formalistes”. Cela concernait la littérature, la musique, le cinéma, la peinture et plus largement toute production culturelle. &lt;/p&gt; &lt;p&gt; Dans les faits, le Jdanovisme artistique a renforcé la censure et la surveillance des artistes. Ceux qui ne suivaient pas la ligne officielle pouvaient être critiqués, marginalisés ou interdits de diffusion, notamment lorsqu’on leur reprochait de ne pas être assez “accessibles” au peuple. &lt;/p&gt; &lt;p&gt; Ce courant a eu un effet profond sur la vie culturelle soviétique, en imposant une norme esthétique très rigide. Il a favorisé les œuvres idéologiquement conformes, mais a aussi freiné l’innovation et limité la liberté de création. On peut le voir comme une forme de contrôle politique de l’art, où la valeur d’une œuvre dépendait moins de sa force créatrice que de sa conformité au projet idéologique soviétique. &lt;/p&gt; 
 </t>
         </is>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G85" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="J84" s="23" t="s">
+      <c r="J85" s="23" t="s">
         <v>432</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marxisme</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="C85" s="1" t="n">
-        <v>1945</v>
-      </c>
-      <c r="D85" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;La Philosophie africaine&lt;/a&gt; désigne la réflexion philosophique menée en Afrique ou par des penseurs africains, mais aussi le débat sur ce que peut être une telle philosophie. Les traditions de pensée du continent sont anciennes, des sagesses de l’Égypte pharaonique au &lt;em&gt;Hatata&lt;/em&gt; éthiopien du XVIIe siècle attribué à Zera Yacob ; mais la discipline moderne prend son essor en 1945, avec &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Tempels reconstruit, à partir de l’observation des Luba du Congo, une « vision du monde » cohérente centrée sur la force vitale : être, c’est être force, et le bien consiste à accroître la vie. Le prêtre rwandais Alexis Kagame prolonge cette démarche en étudiant les catégories de la langue kinyarwanda. Ce courant, appelé ethnophilosophie, est vivement critiqué par le Béninois &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976) : décrire une pensée collective et anonyme, que personne ne discute, ce n’est pas faire de la philosophie, qui suppose des auteurs, des textes et la critique.&lt;/p&gt; &lt;p&gt;Entre ces deux pôles, d’autres voies se sont ouvertes. Le Kényan Henry Odera Oruka recueille auprès des sages des villages une « philosophie de la sagesse » (&lt;em&gt;sage philosophy&lt;/em&gt;) personnelle et critique. Le Ghanéen &lt;a href="https://fr.wikipedia.org/wiki/Kwasi_Wiredu" title=" Wikipedia"&gt;Kwasi Wiredu&lt;/a&gt; appelle à une « décolonisation conceptuelle » qui examine les notions héritées de l’Occident à la lumière des langues africaines. Le Congolais Valentin-Yves Mudimbe étudie la manière dont l’Afrique a été « inventée » par le regard colonial. Le débat porte encore sur l’universalité de la raison.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>108</v>
       </c>
       <c r="M85" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Socialismes, marxismes et anarchismes</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marxisme</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="205.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>1945</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Philosophie_africaine" title=" Wikipedia"&gt;La Philosophie africaine&lt;/a&gt; désigne la réflexion philosophique menée en Afrique ou par des penseurs africains, mais aussi le débat sur ce que peut être une telle philosophie. Les traditions de pensée du continent sont anciennes, des sagesses de l’Égypte pharaonique au &lt;em&gt;Hatata&lt;/em&gt; éthiopien du XVIIe siècle attribué à Zera Yacob ; mais la discipline moderne prend son essor en 1945, avec &lt;em&gt;La Philosophie bantoue&lt;/em&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;.&lt;/p&gt; &lt;p&gt;Tempels reconstruit, à partir de l’observation des Luba du Congo, une « vision du monde » cohérente centrée sur la force vitale : être, c’est être force, et le bien consiste à accroître la vie. Le prêtre rwandais Alexis Kagame prolonge cette démarche en étudiant les catégories de la langue kinyarwanda. Ce courant, appelé ethnophilosophie, est vivement critiqué par le Béninois &lt;a href="https://fr.wikipedia.org/wiki/Paulin_Hountondji" title=" Wikipedia"&gt;Paulin Hountondji&lt;/a&gt; dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976) : décrire une pensée collective et anonyme, que personne ne discute, ce n’est pas faire de la philosophie, qui suppose des auteurs, des textes et la critique.&lt;/p&gt; &lt;p&gt;Entre ces deux pôles, d’autres voies se sont ouvertes. Le Kényan Henry Odera Oruka recueille auprès des sages des villages une « philosophie de la sagesse » (&lt;em&gt;sage philosophy&lt;/em&gt;) personnelle et critique. Le Ghanéen &lt;a href="https://fr.wikipedia.org/wiki/Kwasi_Wiredu" title=" Wikipedia"&gt;Kwasi Wiredu&lt;/a&gt; appelle à une « décolonisation conceptuelle » qui examine les notions héritées de l’Occident à la lumière des langues africaines. Le Congolais Valentin-Yves Mudimbe étudie la manière dont l’Afrique a été « inventée » par le regard colonial. Le débat porte encore sur l’universalité de la raison.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="M86" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1">
+    <row r="87" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="1">
         <v>1945</v>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1945</t>
         </is>
       </c>
-      <c r="D86" s="28" t="inlineStr">
+      <c r="D87" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ethnophilosophie</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ethnophilosophy" title=" Wikipedia (en)"&gt;L’ethnophilosophie&lt;/a&gt; désigne la démarche qui cherche la philosophie d’un peuple dans ses langues, ses proverbes, ses mythes et ses croyances, plutôt que dans les œuvres de penseurs individuels. Elle naît en 1945 avec &lt;a href="https://fr.wikipedia.org/wiki/La_Philosophie_bantoue" title=" Wikipedia"&gt;&lt;em&gt;La Philosophie bantoue&lt;/em&gt;&lt;/a&gt; du missionnaire belge &lt;a href="https://fr.wikipedia.org/wiki/Placide_Tempels" title=" Wikipedia"&gt;Placide Tempels&lt;/a&gt;, qui veut montrer, contre le préjugé colonial, que les Africains ont une pensée cohérente, fondée sur l’idée de « force vitale » : pour les Bantous, l’être est force, et toute chose est une force qui peut croître ou décroître.&lt;/p&gt; &lt;p&gt;Des penseurs africains reprennent cette démarche en la retournant contre le regard colonial. Le prêtre rwandais Alexis Kagame, dans &lt;em&gt;La Philosophie bantu-rwandaise de l’être&lt;/em&gt; (1956), dégage les catégories de la pensée à partir de la grammaire du kinyarwanda, comme Aristote l’avait fait, selon lui, à partir du grec. Le théologien kényan John Mbiti décrit dans &lt;em&gt;Religions et philosophie africaines&lt;/em&gt; (1969) une conception du temps tournée vers le passé plus que vers l’avenir. Dans l’esprit de la Négritude, il s’agit d’affirmer la dignité des cultures africaines.&lt;/p&gt; &lt;p&gt;À partir des années 1970, cette démarche est vivement critiquée par d’autres philosophes africains. Paulin Hountondji, dans &lt;em&gt;Sur la « philosophie africaine »&lt;/em&gt; (1976), dénonce le « mythe de l’unanimité » : une philosophie n’est pas une vision du monde collective et figée, mais un discours critique, signé, argumenté et ouvert à la discussion. Marcien Towa et Fabien Eboussi Boulaga vont dans le même sens. Le débat sur l’ethnophilosophie a structuré toute la philosophie africaine contemporaine.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t xml:space="preserve">WdgKfF8Ghn0</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t xml:space="preserve">"Révision BAC: La Philosophie Africaine Existe -t - Elle?" par Ibrahima Ngom - Attitude</t>
         </is>
       </c>
-      <c r="J86" s="1" t="inlineStr">
+      <c r="J87" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">recherche d’une philosophie africaine dans les langues, les croyances et les traditions des peuples, et débat qu’elle a suscité.</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Métaphysique;Épistémologie</t>
         </is>
       </c>
-      <c r="L86" s="1" t="inlineStr">
+      <c r="L87" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Placide TEMPELS;Alexis KAGAME;John MBITI</t>
         </is>
       </c>
-      <c r="M86" s="1" t="inlineStr">
+      <c r="M87" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
         </is>
       </c>
-      <c r="N86"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
+      <c r="N87"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t xml:space="preserve">Négritude</t>
         </is>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
+    <row r="88" customFormat="false" ht="190.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="n">
         <v>1964</v>
       </c>
-      <c r="C87" s="1" t="n">
+      <c r="C88" s="1" t="n">
         <v>1964</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D88" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nkrumaism" title=" Wikipedia (en)"&gt;Le Consciencisme&lt;/a&gt; est la philosophie politique de &lt;a href="https://fr.wikipedia.org/wiki/Kwame_Nkrumah" title=" Wikipedia"&gt;Kwame Nkrumah&lt;/a&gt; (1909-1972), qui conduit la Gold Coast britannique à l’indépendance en 1957 sous le nom de Ghana, premier pays d’Afrique subsaharienne à se libérer de la colonisation. Il l’expose dans &lt;em&gt;Consciencism : Philosophy and Ideology for Decolonization&lt;/em&gt; (1964). Pour Nkrumah, la décolonisation ne sera achevée que si elle s’accompagne d’une libération des consciences : l’Afrique doit penser par elle-même la société qu’elle veut construire.&lt;/p&gt; &lt;p&gt;Il part d’un constat : la conscience africaine est désormais faite de trois héritages, la tradition africaine, l’islam et le christianisme européen, qui coexistent en conflit. Le consciencisme veut les réunir en une synthèse cohérente, guidée par les valeurs humanistes et égalitaires de l’Afrique traditionnelle. Selon Nkrumah, les sociétés africaines précoloniales étaient « communalistes » : la terre appartenait à tous et nul ne vivait du travail d’autrui. Le socialisme n’est donc pas, pour l’Afrique, une importation, mais la forme moderne de ses propres valeurs ; il peut s’y construire sans passer par la lutte des classes. Sur le plan philosophique, Nkrumah défend un matérialisme dans lequel l’esprit naît de la matière, tout en affirmant l’égale dignité de chaque être humain. Son projet politique est le &lt;a href="https://fr.wikipedia.org/wiki/Panafricanisme" title=" Wikipedia"&gt;panafricanisme&lt;/a&gt; : une Afrique unie, seule capable de résister au néocolonialisme.&lt;/p&gt; &lt;p&gt;Renversé par un coup d’État en 1966, Nkrumah meurt en exil. Le consciencisme reste une référence des philosophies africaines de la décolonisation ; Kwame Gyekye en a critiqué l’idéalisation du passé.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F88" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">le consciencisme de Kwane Nkrumah par Renaissance Africaine</t>
         </is>
       </c>
-      <c r="J87" s="2" t="s">
+      <c r="J88" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="K87" s="2" t="s">
+      <c r="K88" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="M87" s="2" t="s">
+      <c r="M88" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensées africaines</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t xml:space="preserve">Socialisme africain</t>
         </is>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="n">
+    <row r="89" customFormat="false" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="n">
         <v>1970</v>
       </c>
-      <c r="C88" s="1" t="n">
+      <c r="C89" s="1" t="n">
         <v>1970</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D89" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Minjung" title=" Wikipedia"&gt;La pensée Minjung&lt;/a&gt;, du coréen &lt;em&gt;minjung&lt;/em&gt;, « le peuple » au sens des masses opprimées, est un courant théologique et philosophique né en Corée du Sud dans les années 1970, sous la dictature de Park Chung-hee. Elle naît parmi les chrétiens engagés aux côtés des ouvriers et des étudiants en lutte pour la démocratie, après l’immolation en 1970 de l’ouvrier du textile Jeon Tae-il, qui réclamait l’application du droit du travail.&lt;/p&gt; &lt;p&gt;Le &lt;em&gt;minjung&lt;/em&gt;, ce sont ceux qui sont opprimés politiquement, exploités économiquement et tenus à l’écart de la culture. Pour le bibliste Ahn Byung-mu, qui relit l’Évangile de Marc à partir de la foule qui suit Jésus, et pour le théologien Suh Nam-dong, ce peuple souffrant n’est pas seulement l’objet de la compassion : il est le véritable sujet de l’histoire, et c’est dans ses luttes que se révèle le sens des Écritures. La pensée Minjung s’appuie sur une notion coréenne, le &lt;em&gt;han&lt;/em&gt;, ce sentiment de souffrance et de ressentiment accumulés au fil des générations ; le poète Kim Chi-ha cherche comment en briser le cercle sans tomber dans la vengeance. Elle valorise aussi les formes de la culture populaire, comme la danse masquée ou le chant épique du &lt;em&gt;pansori&lt;/em&gt;. Elle a pour précurseur la philosophie de la « graine » (&lt;em&gt;ssial&lt;/em&gt;) de Ham Seok-heon, qui voyait dans le peuple le germe vivant de l’histoire.&lt;/p&gt; &lt;p&gt;Proche des théologies de la libération d’Amérique latine, la pensée Minjung a nourri la résistance au régime militaire, du &lt;a href="https://fr.wikipedia.org/wiki/Soul%C3%A8vement_de_Gwangju" title=" Wikipedia"&gt;soulèvement de Gwangju&lt;/a&gt; en 1980 à la démocratisation de 1987.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="G88" s="2" t="s">
+      <c r="G89" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="J88" s="2" t="s">
+      <c r="J89" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="K88" s="2" t="s">
+      <c r="K89" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="L88" s="1"/>
-      <c r="M88" s="2" t="s">
+      <c r="L89" s="1"/>
+      <c r="M89" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
+      <c r="O89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
         <is>
           <t xml:space="preserve">Théologies et philosophies de la libération</t>
         </is>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1">
+    <row r="90" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="1">
         <v>1981</v>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1981</t>
         </is>
       </c>
-      <c r="D89" s="28" t="inlineStr">
+      <c r="D90" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">Créolisation</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;La &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olisation_%28concept%29" title=" Wikipedia"&gt;créolisation&lt;/a&gt; est un courant de pensée né aux Antilles autour de l’œuvre d’Édouard Glissant. Le mot désigne d’abord la naissance des langues et des cultures créoles dans les sociétés de plantation des Caraïbes, où des peuples arrachés à l’Afrique, des colons européens, des Amérindiens et plus tard des travailleurs venus d’Inde ont dû inventer ensemble un monde nouveau. Glissant en fait un concept philosophique pour penser le monde entier.&lt;/p&gt; &lt;p&gt;Dans &lt;a href="https://fr.wikipedia.org/wiki/Le_Discours_antillais" title=" Wikipedia"&gt;&lt;em&gt;Le Discours antillais&lt;/em&gt;&lt;/a&gt; (1981), il développe d’abord l’&lt;a href="https://fr.wikipedia.org/wiki/Antillanit%C3%A9" title=" Wikipedia"&gt;antillanité&lt;/a&gt; : l’identité des Antilles ne se trouve ni dans un retour à l’Afrique, comme le voulait la Négritude, ni dans l’imitation de la France, mais dans l’archipel caribéen lui-même. Avec la créolisation, il montre que la rencontre des cultures ne produit pas un simple mélange prévisible, mais de l’inédit. Reprenant une image de Deleuze et Guattari, il oppose l’« identité-racine », unique, qui exclut l’autre, à l’« identité-rhizome », qui se construit dans la relation. Dans &lt;em&gt;Poétique de la Relation&lt;/em&gt; (1990), il défend le « droit à l’opacité » : comprendre l’autre ne signifie pas le réduire à soi. Il appelle &lt;a href="https://fr.wikipedia.org/wiki/Tout-Monde" title=" Wikipedia"&gt;« Tout-Monde »&lt;/a&gt; ce monde où toutes les cultures sont désormais en contact, pour le meilleur et pour le pire, et où nul ne peut plus vivre à l’écart des autres.&lt;/p&gt; &lt;p&gt;En 1989, les écrivains martiniquais Jean Bernabé, &lt;a href="https://fr.wikipedia.org/wiki/Patrick_Chamoiseau" title=" Wikipedia"&gt;Patrick Chamoiseau&lt;/a&gt; et Raphaël Confiant prolongent ce mouvement dans leur &lt;em&gt;Éloge de la &lt;a href="https://fr.wikipedia.org/wiki/Cr%C3%A9olit%C3%A9" title=" Wikipedia"&gt;créolité&lt;/a&gt;&lt;/em&gt;. La pensée de Glissant est aujourd’hui l’une des grandes références de la réflexion sur la mondialisation et les identités.&lt;/p&gt;  &lt;audio controls title="La Créolisation : un concept passé par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/20904-30.04.2026-ITEMA_24494160-2026F49089S0120-NET_MFI_5FD251D7-5286-4ED2-85CC-C785E6DDF90E-27-205638c71d84a7236a4f197db5a2f1f9.m4a" type="audio/mp4" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t xml:space="preserve">mLZ9uprUARg</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t xml:space="preserve">"Edouard Glissant : penser la créolisation" par France Culture</t>
         </is>
       </c>
-      <c r="J89" s="1" t="inlineStr">
+      <c r="J90" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">pensée antillaise de Glissant : les cultures en contact créent de l’imprévisible ; à l’identité-racine s’oppose l’identité-relation.</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Métaphysique;Philosophie politique</t>
         </is>
       </c>
-      <c r="L89" s="1" t="inlineStr">
+      <c r="L90" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Édouard GLISSANT</t>
         </is>
       </c>
-      <c r="M89" s="1" t="inlineStr">
+      <c r="M90" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">sud</t>
         </is>
       </c>
-      <c r="N89"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
+      <c r="N90"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t xml:space="preserve">Anticolonialisme et décolonisation</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t xml:space="preserve">Négritude</t>
         </is>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="n">
+    <row r="91" customFormat="false" ht="201.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="n">
         <v>1990</v>
       </c>
-      <c r="C90" s="1" t="n">
+      <c r="C91" s="1" t="n">
         <v>1990</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D91" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Buen_vivir" title=" Wikipedia"&gt;Le Buen Vivir&lt;/a&gt;, « bien vivre » en espagnol, traduit le &lt;em&gt;sumak kawsay&lt;/em&gt; des Quechuas et le &lt;em&gt;suma qamaña&lt;/em&gt; des Aymaras. C’est une philosophie issue des cosmovisions autochtones des Andes, formulée en termes contemporains à partir des années 1990 par des intellectuels et des mouvements indigènes d’Équateur et de Bolivie, rejoints par des penseurs critiques du développement.&lt;/p&gt; &lt;p&gt;Il s’oppose à l’idée occidentale du développement, mesuré par la croissance économique et l’accumulation de biens. Bien vivre, ce n’est pas vivre mieux, c’est-à-dire toujours plus, aux dépens des autres et de la nature : c’est vivre en harmonie au sein de la communauté et avec la &lt;a href="https://fr.wikipedia.org/wiki/Pachamama" title=" Wikipedia"&gt;Pachamama&lt;/a&gt;, la Terre-Mère. L’être humain n’y est ni séparé de la nature ni placé au-dessus d’elle : il fait partie d’un tout vivant tissé de relations, de réciprocité et de complémentarité, où les montagnes, les eaux et les êtres vivants ont leur place. La richesse tient à la qualité des liens plutôt qu’à l’abondance des choses. Ses défenseurs, comme l’économiste équatorien Alberto Acosta ou l’Uruguayen Eduardo Gudynas, y voient une alternative au modèle extractiviste.&lt;/p&gt; &lt;p&gt;La Constitution de l’Équateur de 2008 inscrit le &lt;em&gt;sumak kawsay&lt;/em&gt; parmi ses principes et reconnaît des &lt;a href="https://fr.wikipedia.org/wiki/Droits_de_la_nature" title=" Wikipedia"&gt;droits à la nature&lt;/a&gt; elle-même, une première mondiale. La Constitution bolivienne de 2009 en fait un principe éthique de l’État, et des lois de 2010 et 2012 y consacrent les droits de la Terre-Mère. Mais ces deux pays ont continué d’exploiter pétrole et minerais, ce qui nourrit le débat entre l’idéal et son usage politique.&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F91" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="G91" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="J90" s="2" t="s">
+      <c r="J91" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="K90" s="2" t="s">
+      <c r="K91" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M90" s="2" t="s">
+      <c r="M91" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
+      <c r="O91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mouvement</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t xml:space="preserve">Pensées autochtones</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1">
-        <v>575</v>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">575</t>
-        </is>
-      </c>
-      <c r="D91" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tiantai</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tiantai" title=" Wikipedia"&gt;Le Tiantai&lt;/a&gt; est la première grande école du bouddhisme née en Chine plutôt qu’importée d’Inde. Elle tire son nom du mont Tiantai, dans le Zhejiang, où le moine Zhiyi (538-597) s’installe en 575 et élabore sa doctrine. Face à la masse des sūtras traduits en chinois, souvent contradictoires, Zhiyi les classe en périodes et en méthodes d’enseignement : le Bouddha aurait adapté sa parole à ses auditeurs, et le &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_du_Lotus" title=" Wikipedia"&gt;&lt;em&gt;Sūtra du Lotus&lt;/em&gt;&lt;/a&gt; en serait le sommet, qui révèle que tous les êtres peuvent devenir bouddhas.&lt;/p&gt; &lt;p&gt;Sa philosophie repose sur la doctrine des « trois vérités » : toute chose est vide, car sans existence propre ; elle existe pourtant provisoirement, comme apparence ; et elle est le « milieu », qui unit les deux sans les séparer. Zhiyi en tire l’idée qu’« un instant de pensée contient trois mille mondes » : chaque moment de conscience renferme la totalité des états possibles de l’existence, des enfers jusqu’à l’éveil. Le salut n’est donc pas ailleurs : il se découvre au cœur même du monde ordinaire. Zhiyi va jusqu’à soutenir que la nature de bouddha contient aussi le mal, ce qui fait l’originalité de l’école. Il unit étroitement l’étude des textes et la méditation, qu’il expose dans de grands traités sur « l’arrêt et la contemplation ».&lt;/p&gt; &lt;p&gt;Introduite au Japon en 805 par Saichō sous le nom de &lt;a href="https://fr.wikipedia.org/wiki/Tendai" title=" Wikipedia"&gt;Tendai&lt;/a&gt;, l’école fait du monastère du mont Hiei le grand centre du bouddhisme japonais. Elle y forme la plupart des fondateurs des écoles ultérieures, dont Hōnen, Shinran, Dōgen et Nichiren, qui en reprend la dévotion au Lotus.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="J91" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">école bouddhiste chinoise fondée par Zhiyi sur le Sūtra du Lotus : trois vérités et trois mille mondes dans un instant de pensée.</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Théologie et spiritualité;Métaphysique</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZHIYI;SAICHŌ</t>
-        </is>
-      </c>
-      <c r="M91" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">asie-est</t>
-        </is>
-      </c>
-      <c r="N91"/>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mouvement</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhismes</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bouddhisme Mahayana;Madhyamaka</t>
         </is>
       </c>
     </row>
     <row r="92" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">600</t>
+          <t xml:space="preserve">575</t>
         </is>
       </c>
       <c r="D92" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huayan</t>
+          <t xml:space="preserve">Tiantai</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Huayan" title=" Wikipedia"&gt;Le Huayan&lt;/a&gt;, ou « école de l’Ornementation fleurie », est une école du bouddhisme chinois fondée sur l’&lt;a href="https://fr.wikipedia.org/wiki/Avata%E1%B9%83saka_s%C5%ABtra" title=" Wikipedia"&gt;&lt;em&gt;Avataṃsaka sūtra&lt;/em&gt;&lt;/a&gt;, immense texte qui décrit l’univers tel que le voit un bouddha éveillé. Elle se forme aux VIe et VIIe siècles autour de &lt;a href="https://fr.wikipedia.org/wiki/Dushun" title=" Wikipedia"&gt;Dushun&lt;/a&gt;, son premier patriarche, puis de Zhiyan, et trouve son grand systématicien en Fazang (643-712), qui l’expose à la cour de l’impératrice Wu Zetian.&lt;/p&gt; &lt;p&gt;Sa philosophie est celle de l’interdépendance totale : chaque chose contient toutes les autres et se trouve contenue en elles, sans que leurs différences soient abolies. Pour le faire comprendre à l’impératrice, Fazang prend l’image d’un lion d’or : l’or est la nature unique et vide, le lion la forme qu’elle prend, et chaque poil du lion contient le lion tout entier. Il reprend aussi celle du filet d’Indra, filet céleste dont chaque nœud porte une perle qui reflète toutes les autres perles, à l’infini. Le Huayan distingue quatre plans de réalité : celui des phénomènes, celui du principe, celui de leur non-obstruction mutuelle, et enfin celui de la non-obstruction de tous les phénomènes entre eux, qui est la vision de l’éveil.&lt;/p&gt; &lt;p&gt;En Chine, &lt;a href="https://fr.wikipedia.org/wiki/Zongmi" title=" Wikipedia"&gt;Zongmi&lt;/a&gt; (780-841) le concilie avec le chan. Ŭisang l’apporte en Corée, où il devient l’école Hwaeom, que Chinul unira plus tard à la méditation seon ; au Japon, il prend le nom de &lt;a href="https://fr.wikipedia.org/wiki/Kegon" title=" Wikipedia"&gt;Kegon&lt;/a&gt; et c’est à lui que se rattache le grand Bouddha de Nara. Le Huayan a profondément marqué le zen et le néoconfucianisme. On rapproche parfois aujourd’hui sa vision d’un monde entièrement relié de la pensée écologique.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Tiantai" title=" Wikipedia"&gt;Le Tiantai&lt;/a&gt; est la première grande école du bouddhisme née en Chine plutôt qu’importée d’Inde. Elle tire son nom du mont Tiantai, dans le Zhejiang, où le moine Zhiyi (538-597) s’installe en 575 et élabore sa doctrine. Face à la masse des sūtras traduits en chinois, souvent contradictoires, Zhiyi les classe en périodes et en méthodes d’enseignement : le Bouddha aurait adapté sa parole à ses auditeurs, et le &lt;a href="https://fr.wikipedia.org/wiki/S%C5%ABtra_du_Lotus" title=" Wikipedia"&gt;&lt;em&gt;Sūtra du Lotus&lt;/em&gt;&lt;/a&gt; en serait le s